--- a/workforceresult.xlsx
+++ b/workforceresult.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miiintra/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miintra/Library/Mobile Documents/com~apple~CloudDocs/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5D18CAC-C7B8-D64D-8D80-66ECC16043AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6758835-D610-DF49-AA0B-A2DA96016F06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16760" yWindow="3660" windowWidth="28040" windowHeight="17180" activeTab="1" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16120" activeTab="3" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
   </bookViews>
   <sheets>
     <sheet name="ALL" sheetId="1" r:id="rId1"/>
     <sheet name="GraphAll" sheetId="3" r:id="rId2"/>
     <sheet name="CPS" sheetId="2" r:id="rId3"/>
+    <sheet name="GraphCPS" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +30,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="32">
   <si>
     <t>Type</t>
   </si>
@@ -97,21 +97,6 @@
     <t>Plan</t>
   </si>
   <si>
-    <t>StaffCPS</t>
-  </si>
-  <si>
-    <t>Staff AVGCPS</t>
-  </si>
-  <si>
-    <t>PlanCPS</t>
-  </si>
-  <si>
-    <t>JANTest</t>
-  </si>
-  <si>
-    <t>MAR'27Test</t>
-  </si>
-  <si>
     <t>PAYROLL</t>
   </si>
   <si>
@@ -143,6 +128,12 @@
   </si>
   <si>
     <t>Q1'27</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>CPS</t>
   </si>
 </sst>
 </file>
@@ -762,7 +753,7 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="11" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>16</v>
@@ -815,7 +806,7 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>17</v>
@@ -868,7 +859,7 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" s="13" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>18</v>
@@ -941,7 +932,7 @@
     <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" s="8"/>
       <c r="B6" s="18" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C6" s="19">
         <v>0.88260000000000005</v>
@@ -992,7 +983,7 @@
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" s="17"/>
       <c r="B7" s="18" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C7" s="20">
         <v>17</v>
@@ -1064,7 +1055,7 @@
         <v>16</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C9" s="8">
         <v>121</v>
@@ -1117,7 +1108,7 @@
         <v>17</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C10" s="8">
         <v>117</v>
@@ -1170,7 +1161,7 @@
         <v>18</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C11" s="8">
         <v>105</v>
@@ -1242,7 +1233,7 @@
         <v>16</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C13" s="8">
         <v>21</v>
@@ -1295,7 +1286,7 @@
         <v>17</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C14" s="8">
         <v>21</v>
@@ -1348,7 +1339,7 @@
         <v>18</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C15" s="8">
         <v>20</v>
@@ -1420,7 +1411,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C17" s="8">
         <v>6</v>
@@ -1473,7 +1464,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C18" s="8">
         <v>11</v>
@@ -1526,7 +1517,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C19" s="8">
         <v>6</v>
@@ -1580,25 +1571,25 @@
         <v>0</v>
       </c>
       <c r="C31" s="22" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D31" s="23" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E31" s="23" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F31" s="23" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G31" s="24" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H31" s="25"/>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A32" s="11" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>16</v>
@@ -1622,7 +1613,7 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B33" s="9" t="s">
         <v>17</v>
@@ -1646,7 +1637,7 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="13" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B34" s="10" t="s">
         <v>18</v>
@@ -1691,7 +1682,7 @@
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="8"/>
       <c r="B36" s="18" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C36" s="29">
         <v>0.92500000000000004</v>
@@ -1713,7 +1704,7 @@
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="17"/>
       <c r="B37" s="18" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C37" s="30">
         <v>11</v>
@@ -1747,7 +1738,7 @@
         <v>16</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C39" s="26">
         <v>120</v>
@@ -1771,7 +1762,7 @@
         <v>17</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C40" s="26">
         <v>117</v>
@@ -1795,7 +1786,7 @@
         <v>18</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C41" s="26">
         <v>109</v>
@@ -1829,7 +1820,7 @@
         <v>16</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C43" s="26">
         <v>21</v>
@@ -1853,7 +1844,7 @@
         <v>17</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C44" s="26">
         <v>21</v>
@@ -1877,7 +1868,7 @@
         <v>18</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C45" s="26">
         <v>21</v>
@@ -1911,7 +1902,7 @@
         <v>16</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C47" s="26">
         <v>8</v>
@@ -1935,7 +1926,7 @@
         <v>17</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C48" s="26">
         <v>11</v>
@@ -1959,7 +1950,7 @@
         <v>18</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C49" s="26">
         <v>8</v>
@@ -3414,207 +3405,2686 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{594D1181-445D-3746-9BD8-A2C1C6213A7C}">
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:Q49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1" s="17"/>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A2" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="8">
+        <v>18</v>
+      </c>
+      <c r="D2" s="8">
+        <v>18</v>
+      </c>
+      <c r="E2" s="8">
+        <v>18</v>
+      </c>
+      <c r="F2" s="8">
+        <v>17</v>
+      </c>
+      <c r="G2" s="8">
+        <v>17</v>
+      </c>
+      <c r="H2" s="8">
+        <v>17</v>
+      </c>
+      <c r="I2" s="8">
+        <v>17</v>
+      </c>
+      <c r="J2" s="8">
+        <v>17</v>
+      </c>
+      <c r="K2" s="8">
+        <v>17</v>
+      </c>
+      <c r="L2" s="8">
+        <v>17</v>
+      </c>
+      <c r="M2" s="8">
+        <v>17</v>
+      </c>
+      <c r="N2" s="8">
+        <v>17</v>
+      </c>
+      <c r="O2" s="8">
+        <v>17</v>
+      </c>
+      <c r="P2" s="8">
+        <v>17</v>
+      </c>
+      <c r="Q2" s="8">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A3" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="8">
+        <v>17</v>
+      </c>
+      <c r="D3" s="8">
+        <v>17</v>
+      </c>
+      <c r="E3" s="8">
+        <v>17</v>
+      </c>
+      <c r="F3" s="8">
+        <v>17</v>
+      </c>
+      <c r="G3" s="8">
+        <v>17</v>
+      </c>
+      <c r="H3" s="8">
+        <v>17</v>
+      </c>
+      <c r="I3" s="8">
+        <v>17</v>
+      </c>
+      <c r="J3" s="8">
+        <v>17</v>
+      </c>
+      <c r="K3" s="8">
+        <v>17</v>
+      </c>
+      <c r="L3" s="8">
+        <v>17</v>
+      </c>
+      <c r="M3" s="8">
+        <v>17</v>
+      </c>
+      <c r="N3" s="8">
+        <v>17</v>
+      </c>
+      <c r="O3" s="8">
+        <v>17</v>
+      </c>
+      <c r="P3" s="8">
+        <v>17</v>
+      </c>
+      <c r="Q3" s="8">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A4" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="8">
+        <v>17</v>
+      </c>
+      <c r="D4" s="8">
+        <v>17</v>
+      </c>
+      <c r="E4" s="8">
+        <v>17</v>
+      </c>
+      <c r="F4" s="14">
+        <v>17</v>
+      </c>
+      <c r="G4" s="14">
+        <v>18</v>
+      </c>
+      <c r="H4" s="14">
+        <v>17</v>
+      </c>
+      <c r="I4" s="8">
+        <v>16</v>
+      </c>
+      <c r="J4" s="8">
+        <v>16</v>
+      </c>
+      <c r="K4" s="8">
+        <v>16</v>
+      </c>
+      <c r="L4" s="8">
+        <v>16</v>
+      </c>
+      <c r="M4" s="8">
+        <v>16</v>
+      </c>
+      <c r="N4" s="8">
+        <v>16</v>
+      </c>
+      <c r="O4" s="8">
+        <v>14</v>
+      </c>
+      <c r="P4" s="8">
+        <v>14</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A5" s="17"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
+      <c r="Q5" s="8"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A6" s="8"/>
+      <c r="B6" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="19">
+        <v>0.93610000000000004</v>
+      </c>
+      <c r="D6" s="19">
+        <v>0.94169999999999998</v>
+      </c>
+      <c r="E6" s="19">
+        <v>0.92500000000000004</v>
+      </c>
+      <c r="F6" s="19">
+        <v>1.0235000000000001</v>
+      </c>
+      <c r="G6" s="19">
+        <v>1.0294000000000001</v>
+      </c>
+      <c r="H6" s="19">
+        <v>1.0235000000000001</v>
+      </c>
+      <c r="I6" s="19">
+        <v>0.95289999999999997</v>
+      </c>
+      <c r="J6" s="19">
+        <v>0.94120000000000004</v>
+      </c>
+      <c r="K6" s="19">
+        <v>0.94120000000000004</v>
+      </c>
+      <c r="L6" s="19">
+        <v>0.93530000000000002</v>
+      </c>
+      <c r="M6" s="19">
+        <v>0.92349999999999999</v>
+      </c>
+      <c r="N6" s="19">
+        <v>0.92349999999999999</v>
+      </c>
+      <c r="O6" s="19">
+        <v>0.83530000000000004</v>
+      </c>
+      <c r="P6" s="19">
+        <v>0.83530000000000004</v>
+      </c>
+      <c r="Q6" s="19">
+        <v>0.83530000000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A7" s="17"/>
+      <c r="B7" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="20">
+        <v>1</v>
+      </c>
+      <c r="D7" s="20">
+        <v>1</v>
+      </c>
+      <c r="E7" s="20">
+        <v>1</v>
+      </c>
+      <c r="F7" s="20">
+        <v>0</v>
+      </c>
+      <c r="G7" s="20">
+        <v>0</v>
+      </c>
+      <c r="H7" s="20">
+        <v>0</v>
+      </c>
+      <c r="I7" s="20">
+        <v>1</v>
+      </c>
+      <c r="J7" s="20">
+        <v>1</v>
+      </c>
+      <c r="K7" s="20">
+        <v>1</v>
+      </c>
+      <c r="L7" s="20">
+        <v>1</v>
+      </c>
+      <c r="M7" s="20">
+        <v>1</v>
+      </c>
+      <c r="N7" s="20">
+        <v>1</v>
+      </c>
+      <c r="O7" s="20">
+        <v>3</v>
+      </c>
+      <c r="P7" s="20">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A8" s="17"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A9" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="8">
+        <v>18</v>
+      </c>
+      <c r="D9" s="8">
+        <v>18</v>
+      </c>
+      <c r="E9" s="8">
+        <v>18</v>
+      </c>
+      <c r="F9" s="8">
+        <v>17</v>
+      </c>
+      <c r="G9" s="8">
+        <v>17</v>
+      </c>
+      <c r="H9" s="8">
+        <v>17</v>
+      </c>
+      <c r="I9" s="8">
+        <v>17</v>
+      </c>
+      <c r="J9" s="8">
+        <v>17</v>
+      </c>
+      <c r="K9" s="8">
+        <v>17</v>
+      </c>
+      <c r="L9" s="8">
+        <v>17</v>
+      </c>
+      <c r="M9" s="8">
+        <v>17</v>
+      </c>
+      <c r="N9" s="8">
+        <v>17</v>
+      </c>
+      <c r="O9" s="8">
+        <v>17</v>
+      </c>
+      <c r="P9" s="8">
+        <v>17</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A10" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="8">
+        <v>17</v>
+      </c>
+      <c r="D10" s="8">
+        <v>17</v>
+      </c>
+      <c r="E10" s="8">
+        <v>17</v>
+      </c>
+      <c r="F10" s="8">
+        <v>17</v>
+      </c>
+      <c r="G10" s="8">
+        <v>17</v>
+      </c>
+      <c r="H10" s="8">
+        <v>17</v>
+      </c>
+      <c r="I10" s="8">
+        <v>17</v>
+      </c>
+      <c r="J10" s="8">
+        <v>17</v>
+      </c>
+      <c r="K10" s="8">
+        <v>17</v>
+      </c>
+      <c r="L10" s="8">
+        <v>17</v>
+      </c>
+      <c r="M10" s="8">
+        <v>17</v>
+      </c>
+      <c r="N10" s="8">
+        <v>17</v>
+      </c>
+      <c r="O10" s="8">
+        <v>17</v>
+      </c>
+      <c r="P10" s="8">
+        <v>17</v>
+      </c>
+      <c r="Q10" s="8">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A11" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="8">
+        <v>17</v>
+      </c>
+      <c r="D11" s="8">
+        <v>17</v>
+      </c>
+      <c r="E11" s="8">
+        <v>17</v>
+      </c>
+      <c r="F11" s="14">
+        <v>17</v>
+      </c>
+      <c r="G11" s="14">
+        <v>18</v>
+      </c>
+      <c r="H11" s="14">
+        <v>17</v>
+      </c>
+      <c r="I11" s="8">
+        <v>16</v>
+      </c>
+      <c r="J11" s="8">
+        <v>16</v>
+      </c>
+      <c r="K11" s="8">
+        <v>16</v>
+      </c>
+      <c r="L11" s="8">
+        <v>16</v>
+      </c>
+      <c r="M11" s="8">
+        <v>16</v>
+      </c>
+      <c r="N11" s="8">
+        <v>16</v>
+      </c>
+      <c r="O11" s="8">
+        <v>14</v>
+      </c>
+      <c r="P11" s="8">
+        <v>14</v>
+      </c>
+      <c r="Q11" s="8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A12" s="8"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
+      <c r="Q12" s="8"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A13" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="8">
+        <v>0</v>
+      </c>
+      <c r="D13" s="8">
+        <v>0</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0</v>
+      </c>
+      <c r="F13" s="8">
+        <v>0</v>
+      </c>
+      <c r="G13" s="8">
+        <v>0</v>
+      </c>
+      <c r="H13" s="8">
+        <v>0</v>
+      </c>
+      <c r="I13" s="8">
+        <v>0</v>
+      </c>
+      <c r="J13" s="8">
+        <v>0</v>
+      </c>
+      <c r="K13" s="8">
+        <v>0</v>
+      </c>
+      <c r="L13" s="8">
+        <v>0</v>
+      </c>
+      <c r="M13" s="8">
+        <v>0</v>
+      </c>
+      <c r="N13" s="8">
+        <v>0</v>
+      </c>
+      <c r="O13" s="8">
+        <v>0</v>
+      </c>
+      <c r="P13" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A14" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="8">
+        <v>0</v>
+      </c>
+      <c r="D14" s="8">
+        <v>0</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0</v>
+      </c>
+      <c r="F14" s="8">
+        <v>0</v>
+      </c>
+      <c r="G14" s="8">
+        <v>0</v>
+      </c>
+      <c r="H14" s="8">
+        <v>0</v>
+      </c>
+      <c r="I14" s="8">
+        <v>0</v>
+      </c>
+      <c r="J14" s="8">
+        <v>0</v>
+      </c>
+      <c r="K14" s="8">
+        <v>0</v>
+      </c>
+      <c r="L14" s="8">
+        <v>0</v>
+      </c>
+      <c r="M14" s="8">
+        <v>0</v>
+      </c>
+      <c r="N14" s="8">
+        <v>0</v>
+      </c>
+      <c r="O14" s="8">
+        <v>0</v>
+      </c>
+      <c r="P14" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A15" s="16">
+        <v>0</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="8">
+        <v>0</v>
+      </c>
+      <c r="D15" s="8">
+        <v>0</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0</v>
+      </c>
+      <c r="F15" s="8">
+        <v>0</v>
+      </c>
+      <c r="G15" s="8">
+        <v>0</v>
+      </c>
+      <c r="H15" s="8">
+        <v>0</v>
+      </c>
+      <c r="I15" s="8">
+        <v>0</v>
+      </c>
+      <c r="J15" s="8">
+        <v>0</v>
+      </c>
+      <c r="K15" s="8">
+        <v>0</v>
+      </c>
+      <c r="L15" s="8">
+        <v>0</v>
+      </c>
+      <c r="M15" s="8">
+        <v>0</v>
+      </c>
+      <c r="N15" s="8">
+        <v>0</v>
+      </c>
+      <c r="O15" s="8">
+        <v>0</v>
+      </c>
+      <c r="P15" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A16" s="8"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="8"/>
+      <c r="Q16" s="8"/>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A17" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="8">
+        <v>0</v>
+      </c>
+      <c r="D17" s="8">
+        <v>0</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0</v>
+      </c>
+      <c r="F17" s="8">
+        <v>0</v>
+      </c>
+      <c r="G17" s="8">
+        <v>0</v>
+      </c>
+      <c r="H17" s="8">
+        <v>0</v>
+      </c>
+      <c r="I17" s="8">
+        <v>0</v>
+      </c>
+      <c r="J17" s="8">
+        <v>0</v>
+      </c>
+      <c r="K17" s="8">
+        <v>0</v>
+      </c>
+      <c r="L17" s="8">
+        <v>0</v>
+      </c>
+      <c r="M17" s="8">
+        <v>0</v>
+      </c>
+      <c r="N17" s="8">
+        <v>0</v>
+      </c>
+      <c r="O17" s="8">
+        <v>0</v>
+      </c>
+      <c r="P17" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A18" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="8">
+        <v>0</v>
+      </c>
+      <c r="D18" s="8">
+        <v>0</v>
+      </c>
+      <c r="E18" s="8">
+        <v>0</v>
+      </c>
+      <c r="F18" s="8">
+        <v>0</v>
+      </c>
+      <c r="G18" s="8">
+        <v>0</v>
+      </c>
+      <c r="H18" s="8">
+        <v>0</v>
+      </c>
+      <c r="I18" s="8">
+        <v>0</v>
+      </c>
+      <c r="J18" s="8">
+        <v>0</v>
+      </c>
+      <c r="K18" s="8">
+        <v>0</v>
+      </c>
+      <c r="L18" s="8">
+        <v>0</v>
+      </c>
+      <c r="M18" s="8">
+        <v>0</v>
+      </c>
+      <c r="N18" s="8">
+        <v>0</v>
+      </c>
+      <c r="O18" s="8">
+        <v>0</v>
+      </c>
+      <c r="P18" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A19" s="16">
+        <v>0</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="8">
+        <v>0</v>
+      </c>
+      <c r="D19" s="8">
+        <v>0</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0</v>
+      </c>
+      <c r="F19" s="8">
+        <v>0</v>
+      </c>
+      <c r="G19" s="8">
+        <v>0</v>
+      </c>
+      <c r="H19" s="8">
+        <v>0</v>
+      </c>
+      <c r="I19" s="8">
+        <v>0</v>
+      </c>
+      <c r="J19" s="8">
+        <v>0</v>
+      </c>
+      <c r="K19" s="8">
+        <v>0</v>
+      </c>
+      <c r="L19" s="8">
+        <v>0</v>
+      </c>
+      <c r="M19" s="8">
+        <v>0</v>
+      </c>
+      <c r="N19" s="8">
+        <v>0</v>
+      </c>
+      <c r="O19" s="8">
+        <v>0</v>
+      </c>
+      <c r="P19" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A31" s="17"/>
+      <c r="B31" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C31" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="D31" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="E31" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F31" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="G31" s="24" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A32" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" s="26">
+        <v>18</v>
+      </c>
+      <c r="D32" s="21">
+        <v>17</v>
+      </c>
+      <c r="E32" s="21">
+        <v>17</v>
+      </c>
+      <c r="F32" s="21">
+        <v>17</v>
+      </c>
+      <c r="G32" s="21">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="26">
+        <v>17</v>
+      </c>
+      <c r="D33" s="21">
+        <v>17</v>
+      </c>
+      <c r="E33" s="21">
+        <v>17</v>
+      </c>
+      <c r="F33" s="21">
+        <v>17</v>
+      </c>
+      <c r="G33" s="21">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="26">
+        <v>17</v>
+      </c>
+      <c r="D34" s="14">
+        <v>17</v>
+      </c>
+      <c r="E34" s="21">
+        <v>16</v>
+      </c>
+      <c r="F34" s="21">
+        <v>16</v>
+      </c>
+      <c r="G34" s="21">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="17"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="27">
+        <v>6.5699999999999995E-2</v>
+      </c>
+      <c r="D35" s="28">
+        <v>-2.5499999999999998E-2</v>
+      </c>
+      <c r="E35" s="28">
+        <v>5.4899999999999997E-2</v>
+      </c>
+      <c r="F35" s="28">
+        <v>7.2499999999999995E-2</v>
+      </c>
+      <c r="G35" s="28">
+        <v>0.10589999999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="8"/>
+      <c r="B36" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C36" s="29">
+        <v>0.93430000000000002</v>
+      </c>
+      <c r="D36" s="19">
+        <v>1.0255000000000001</v>
+      </c>
+      <c r="E36" s="19">
+        <v>0.94510000000000005</v>
+      </c>
+      <c r="F36" s="19">
+        <v>0.92749999999999999</v>
+      </c>
+      <c r="G36" s="19">
+        <v>0.89410000000000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="17"/>
+      <c r="B37" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" s="30">
+        <v>1</v>
+      </c>
+      <c r="D37" s="20">
+        <v>0</v>
+      </c>
+      <c r="E37" s="20">
+        <v>1</v>
+      </c>
+      <c r="F37" s="20">
+        <v>1</v>
+      </c>
+      <c r="G37" s="20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="17"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="31"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C39" s="26">
+        <v>18</v>
+      </c>
+      <c r="D39" s="21">
+        <v>17</v>
+      </c>
+      <c r="E39" s="21">
+        <v>17</v>
+      </c>
+      <c r="F39" s="21">
+        <v>17</v>
+      </c>
+      <c r="G39" s="21">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A40" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C40" s="26">
+        <v>17</v>
+      </c>
+      <c r="D40" s="21">
+        <v>17</v>
+      </c>
+      <c r="E40" s="21">
+        <v>17</v>
+      </c>
+      <c r="F40" s="21">
+        <v>17</v>
+      </c>
+      <c r="G40" s="21">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A41" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B41" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C41" s="26">
+        <v>17</v>
+      </c>
+      <c r="D41" s="14">
+        <v>17</v>
+      </c>
+      <c r="E41" s="21">
+        <v>16</v>
+      </c>
+      <c r="F41" s="21">
+        <v>16</v>
+      </c>
+      <c r="G41" s="21">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A42" s="8"/>
+      <c r="B42" s="17"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="21"/>
+      <c r="G42" s="21"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A43" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C43" s="26">
+        <v>0</v>
+      </c>
+      <c r="D43" s="21">
+        <v>0</v>
+      </c>
+      <c r="E43" s="21">
+        <v>0</v>
+      </c>
+      <c r="F43" s="21">
+        <v>0</v>
+      </c>
+      <c r="G43" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A44" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" s="26">
+        <v>0</v>
+      </c>
+      <c r="D44" s="21">
+        <v>0</v>
+      </c>
+      <c r="E44" s="21">
+        <v>0</v>
+      </c>
+      <c r="F44" s="21">
+        <v>0</v>
+      </c>
+      <c r="G44" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A45" s="16">
+        <v>0</v>
+      </c>
+      <c r="B45" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C45" s="26">
+        <v>0</v>
+      </c>
+      <c r="D45" s="21">
+        <v>0</v>
+      </c>
+      <c r="E45" s="21">
+        <v>0</v>
+      </c>
+      <c r="F45" s="21">
+        <v>0</v>
+      </c>
+      <c r="G45" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A46" s="8"/>
+      <c r="B46" s="17"/>
+      <c r="C46" s="26"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="21"/>
+      <c r="F46" s="21"/>
+      <c r="G46" s="21"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A47" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C47" s="26">
+        <v>0</v>
+      </c>
+      <c r="D47" s="21">
+        <v>0</v>
+      </c>
+      <c r="E47" s="21">
+        <v>0</v>
+      </c>
+      <c r="F47" s="21">
+        <v>0</v>
+      </c>
+      <c r="G47" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A48" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C48" s="26">
+        <v>0</v>
+      </c>
+      <c r="D48" s="21">
+        <v>0</v>
+      </c>
+      <c r="E48" s="21">
+        <v>0</v>
+      </c>
+      <c r="F48" s="21">
+        <v>0</v>
+      </c>
+      <c r="G48" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A49" s="16">
+        <v>0</v>
+      </c>
+      <c r="B49" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C49" s="26">
+        <v>0</v>
+      </c>
+      <c r="D49" s="21">
+        <v>0</v>
+      </c>
+      <c r="E49" s="21">
+        <v>0</v>
+      </c>
+      <c r="F49" s="21">
+        <v>0</v>
+      </c>
+      <c r="G49" s="21">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FB985D5-E47B-3A4D-A324-92EE24F74B47}">
+  <dimension ref="A1:P47"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="6" t="s">
+      <c r="B1" t="str">
+        <f>IF(CPS!C1&gt;0,CPS!C1,"")</f>
+        <v>JAN</v>
+      </c>
+      <c r="C1" t="str">
+        <f>IF(CPS!D1&gt;0,CPS!D1,"")</f>
+        <v>FEB</v>
+      </c>
+      <c r="D1" t="str">
+        <f>IF(CPS!E1&gt;0,CPS!E1,"")</f>
+        <v>MAR</v>
+      </c>
+      <c r="E1" t="str">
+        <f>IF(CPS!F1&gt;0,CPS!F1,"")</f>
+        <v>APR</v>
+      </c>
+      <c r="F1" t="str">
+        <f>IF(CPS!G1&gt;0,CPS!G1,"")</f>
+        <v>MAY</v>
+      </c>
+      <c r="G1" t="str">
+        <f>IF(CPS!H1&gt;0,CPS!H1,"")</f>
+        <v>JUN</v>
+      </c>
+      <c r="H1" t="str">
+        <f>IF(CPS!I1&gt;0,CPS!I1,"")</f>
+        <v>JUL</v>
+      </c>
+      <c r="I1" t="str">
+        <f>IF(CPS!J1&gt;0,CPS!J1,"")</f>
+        <v>AUG</v>
+      </c>
+      <c r="J1" t="str">
+        <f>IF(CPS!K1&gt;0,CPS!K1,"")</f>
+        <v>SEP</v>
+      </c>
+      <c r="K1" t="str">
+        <f>IF(CPS!L1&gt;0,CPS!L1,"")</f>
+        <v>OCT</v>
+      </c>
+      <c r="L1" t="str">
+        <f>IF(CPS!M1&gt;0,CPS!M1,"")</f>
+        <v>NOV</v>
+      </c>
+      <c r="M1" t="str">
+        <f>IF(CPS!N1&gt;0,CPS!N1,"")</f>
+        <v>DEC</v>
+      </c>
+      <c r="N1" t="str">
+        <f>IF(CPS!O1&gt;0,CPS!O1,"")</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O1" t="str">
+        <f>IF(CPS!P1&gt;0,CPS!P1,"")</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P1" t="str">
+        <f>IF(CPS!Q1&gt;0,CPS!Q1,"")</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A2" t="str">
+        <f>IF(CPS!B2&gt;0,CPS!B2,"")</f>
+        <v>Staff</v>
+      </c>
+      <c r="B2">
+        <f>IF(CPS!C2&gt;0,CPS!C2,"")</f>
+        <v>18</v>
+      </c>
+      <c r="C2">
+        <f>IF(CPS!D2&gt;0,CPS!D2,"")</f>
+        <v>18</v>
+      </c>
+      <c r="D2">
+        <f>IF(CPS!E2&gt;0,CPS!E2,"")</f>
+        <v>18</v>
+      </c>
+      <c r="E2">
+        <f>IF(CPS!F2&gt;0,CPS!F2,"")</f>
+        <v>17</v>
+      </c>
+      <c r="F2">
+        <f>IF(CPS!G2&gt;0,CPS!G2,"")</f>
+        <v>17</v>
+      </c>
+      <c r="G2">
+        <f>IF(CPS!H2&gt;0,CPS!H2,"")</f>
+        <v>17</v>
+      </c>
+      <c r="H2">
+        <f>IF(CPS!I2&gt;0,CPS!I2,"")</f>
+        <v>17</v>
+      </c>
+      <c r="I2">
+        <f>IF(CPS!J2&gt;0,CPS!J2,"")</f>
+        <v>17</v>
+      </c>
+      <c r="J2">
+        <f>IF(CPS!K2&gt;0,CPS!K2,"")</f>
+        <v>17</v>
+      </c>
+      <c r="K2">
+        <f>IF(CPS!L2&gt;0,CPS!L2,"")</f>
+        <v>17</v>
+      </c>
+      <c r="L2">
+        <f>IF(CPS!M2&gt;0,CPS!M2,"")</f>
+        <v>17</v>
+      </c>
+      <c r="M2">
+        <f>IF(CPS!N2&gt;0,CPS!N2,"")</f>
+        <v>17</v>
+      </c>
+      <c r="N2">
+        <f>IF(CPS!O2&gt;0,CPS!O2,"")</f>
+        <v>17</v>
+      </c>
+      <c r="O2">
+        <f>IF(CPS!P2&gt;0,CPS!P2,"")</f>
+        <v>17</v>
+      </c>
+      <c r="P2">
+        <f>IF(CPS!Q2&gt;0,CPS!Q2,"")</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A3" t="str">
+        <f>IF(CPS!B3&gt;0,CPS!B3,"")</f>
+        <v>Staff AVG</v>
+      </c>
+      <c r="B3">
+        <f>IF(CPS!C3&gt;0,CPS!C3,"")</f>
+        <v>17</v>
+      </c>
+      <c r="C3">
+        <f>IF(CPS!D3&gt;0,CPS!D3,"")</f>
+        <v>17</v>
+      </c>
+      <c r="D3">
+        <f>IF(CPS!E3&gt;0,CPS!E3,"")</f>
+        <v>17</v>
+      </c>
+      <c r="E3">
+        <f>IF(CPS!F3&gt;0,CPS!F3,"")</f>
+        <v>17</v>
+      </c>
+      <c r="F3">
+        <f>IF(CPS!G3&gt;0,CPS!G3,"")</f>
+        <v>17</v>
+      </c>
+      <c r="G3">
+        <f>IF(CPS!H3&gt;0,CPS!H3,"")</f>
+        <v>17</v>
+      </c>
+      <c r="H3">
+        <f>IF(CPS!I3&gt;0,CPS!I3,"")</f>
+        <v>17</v>
+      </c>
+      <c r="I3">
+        <f>IF(CPS!J3&gt;0,CPS!J3,"")</f>
+        <v>17</v>
+      </c>
+      <c r="J3">
+        <f>IF(CPS!K3&gt;0,CPS!K3,"")</f>
+        <v>17</v>
+      </c>
+      <c r="K3">
+        <f>IF(CPS!L3&gt;0,CPS!L3,"")</f>
+        <v>17</v>
+      </c>
+      <c r="L3">
+        <f>IF(CPS!M3&gt;0,CPS!M3,"")</f>
+        <v>17</v>
+      </c>
+      <c r="M3">
+        <f>IF(CPS!N3&gt;0,CPS!N3,"")</f>
+        <v>17</v>
+      </c>
+      <c r="N3">
+        <f>IF(CPS!O3&gt;0,CPS!O3,"")</f>
+        <v>17</v>
+      </c>
+      <c r="O3">
+        <f>IF(CPS!P3&gt;0,CPS!P3,"")</f>
+        <v>17</v>
+      </c>
+      <c r="P3">
+        <f>IF(CPS!Q3&gt;0,CPS!Q3,"")</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A4" t="str">
+        <f>IF(CPS!B4&gt;0,CPS!B4,"")</f>
+        <v>Plan</v>
+      </c>
+      <c r="B4">
+        <f>IF(CPS!C4&gt;0,CPS!C4,"")</f>
+        <v>17</v>
+      </c>
+      <c r="C4">
+        <f>IF(CPS!D4&gt;0,CPS!D4,"")</f>
+        <v>17</v>
+      </c>
+      <c r="D4">
+        <f>IF(CPS!E4&gt;0,CPS!E4,"")</f>
+        <v>17</v>
+      </c>
+      <c r="E4">
+        <f>IF(CPS!F4&gt;0,CPS!F4,"")</f>
+        <v>17</v>
+      </c>
+      <c r="F4">
+        <f>IF(CPS!G4&gt;0,CPS!G4,"")</f>
+        <v>18</v>
+      </c>
+      <c r="G4">
+        <f>IF(CPS!H4&gt;0,CPS!H4,"")</f>
+        <v>17</v>
+      </c>
+      <c r="H4">
+        <f>IF(CPS!I4&gt;0,CPS!I4,"")</f>
+        <v>16</v>
+      </c>
+      <c r="I4">
+        <f>IF(CPS!J4&gt;0,CPS!J4,"")</f>
+        <v>16</v>
+      </c>
+      <c r="J4">
+        <f>IF(CPS!K4&gt;0,CPS!K4,"")</f>
+        <v>16</v>
+      </c>
+      <c r="K4">
+        <f>IF(CPS!L4&gt;0,CPS!L4,"")</f>
+        <v>16</v>
+      </c>
+      <c r="L4">
+        <f>IF(CPS!M4&gt;0,CPS!M4,"")</f>
+        <v>16</v>
+      </c>
+      <c r="M4">
+        <f>IF(CPS!N4&gt;0,CPS!N4,"")</f>
+        <v>16</v>
+      </c>
+      <c r="N4">
+        <f>IF(CPS!O4&gt;0,CPS!O4,"")</f>
         <v>14</v>
       </c>
-      <c r="P1" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A2" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="8">
-        <v>148</v>
-      </c>
-      <c r="C2" s="8">
-        <v>149</v>
-      </c>
-      <c r="D2" s="8">
-        <v>149</v>
-      </c>
-      <c r="E2" s="8">
-        <v>151</v>
-      </c>
-      <c r="F2" s="8">
-        <v>150</v>
-      </c>
-      <c r="G2" s="8">
-        <v>150</v>
-      </c>
-      <c r="H2" s="8">
-        <v>149</v>
-      </c>
-      <c r="I2" s="8">
-        <v>149</v>
-      </c>
-      <c r="J2" s="8">
-        <v>149</v>
-      </c>
-      <c r="K2" s="8">
-        <v>149</v>
-      </c>
-      <c r="L2" s="8">
-        <v>149</v>
-      </c>
-      <c r="M2" s="8">
-        <v>149</v>
-      </c>
-      <c r="N2" s="8">
-        <v>150</v>
-      </c>
-      <c r="O2" s="8">
-        <v>160</v>
-      </c>
-      <c r="P2" s="8">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A3" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="8">
-        <v>149</v>
-      </c>
-      <c r="C3" s="8">
-        <v>149</v>
-      </c>
-      <c r="D3" s="8">
-        <v>149</v>
-      </c>
-      <c r="E3" s="8">
-        <v>149</v>
-      </c>
-      <c r="F3" s="8">
-        <v>149</v>
-      </c>
-      <c r="G3" s="8">
-        <v>149</v>
-      </c>
-      <c r="H3" s="8">
-        <v>149</v>
-      </c>
-      <c r="I3" s="8">
-        <v>149</v>
-      </c>
-      <c r="J3" s="8">
-        <v>149</v>
-      </c>
-      <c r="K3" s="8">
-        <v>149</v>
-      </c>
-      <c r="L3" s="8">
-        <v>149</v>
-      </c>
-      <c r="M3" s="8">
-        <v>149</v>
-      </c>
-      <c r="N3" s="8">
-        <v>149</v>
-      </c>
-      <c r="O3" s="8">
-        <v>149</v>
-      </c>
-      <c r="P3" s="8">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A4" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="8">
-        <v>1</v>
-      </c>
-      <c r="C4" s="8">
-        <v>2</v>
-      </c>
-      <c r="D4" s="8">
-        <v>3</v>
-      </c>
-      <c r="E4" s="8">
-        <v>143</v>
-      </c>
-      <c r="F4" s="8">
-        <v>147</v>
-      </c>
-      <c r="G4" s="8">
-        <v>144</v>
-      </c>
-      <c r="H4" s="8">
-        <v>143</v>
-      </c>
-      <c r="I4" s="8">
-        <v>140</v>
-      </c>
-      <c r="J4" s="8">
-        <v>139</v>
-      </c>
-      <c r="K4" s="8">
-        <v>132</v>
-      </c>
-      <c r="L4" s="8">
-        <v>130</v>
-      </c>
-      <c r="M4" s="8">
-        <v>130</v>
-      </c>
-      <c r="N4" s="8">
-        <v>105</v>
-      </c>
-      <c r="O4" s="8">
-        <v>104</v>
-      </c>
-      <c r="P4" s="8">
-        <v>104</v>
+      <c r="O4">
+        <f>IF(CPS!P4&gt;0,CPS!P4,"")</f>
+        <v>14</v>
+      </c>
+      <c r="P4">
+        <f>IF(CPS!Q4&gt;0,CPS!Q4,"")</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A5" t="str">
+        <f>IF(CPS!B11&gt;0,CPS!B11,"")</f>
+        <v>PAYROLL</v>
+      </c>
+      <c r="B5">
+        <f>IF(CPS!C11&gt;0,CPS!C11,"")</f>
+        <v>17</v>
+      </c>
+      <c r="C5">
+        <f>IF(CPS!D11&gt;0,CPS!D11,"")</f>
+        <v>17</v>
+      </c>
+      <c r="D5">
+        <f>IF(CPS!E11&gt;0,CPS!E11,"")</f>
+        <v>17</v>
+      </c>
+      <c r="E5">
+        <f>IF(CPS!F11&gt;0,CPS!F11,"")</f>
+        <v>17</v>
+      </c>
+      <c r="F5">
+        <f>IF(CPS!G11&gt;0,CPS!G11,"")</f>
+        <v>18</v>
+      </c>
+      <c r="G5">
+        <f>IF(CPS!H11&gt;0,CPS!H11,"")</f>
+        <v>17</v>
+      </c>
+      <c r="H5">
+        <f>IF(CPS!I11&gt;0,CPS!I11,"")</f>
+        <v>16</v>
+      </c>
+      <c r="I5">
+        <f>IF(CPS!J11&gt;0,CPS!J11,"")</f>
+        <v>16</v>
+      </c>
+      <c r="J5">
+        <f>IF(CPS!K11&gt;0,CPS!K11,"")</f>
+        <v>16</v>
+      </c>
+      <c r="K5">
+        <f>IF(CPS!L11&gt;0,CPS!L11,"")</f>
+        <v>16</v>
+      </c>
+      <c r="L5">
+        <f>IF(CPS!M11&gt;0,CPS!M11,"")</f>
+        <v>16</v>
+      </c>
+      <c r="M5">
+        <f>IF(CPS!N11&gt;0,CPS!N11,"")</f>
+        <v>16</v>
+      </c>
+      <c r="N5">
+        <f>IF(CPS!O11&gt;0,CPS!O11,"")</f>
+        <v>14</v>
+      </c>
+      <c r="O5">
+        <f>IF(CPS!P11&gt;0,CPS!P11,"")</f>
+        <v>14</v>
+      </c>
+      <c r="P5">
+        <f>IF(CPS!Q11&gt;0,CPS!Q11,"")</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A6" t="str">
+        <f>IF(CPS!B15&gt;0,CPS!B15,"")</f>
+        <v>CONTRACTOR</v>
+      </c>
+      <c r="B6" t="str">
+        <f>IF(CPS!C15&gt;0,CPS!C15,"")</f>
+        <v/>
+      </c>
+      <c r="C6" t="str">
+        <f>IF(CPS!D15&gt;0,CPS!D15,"")</f>
+        <v/>
+      </c>
+      <c r="D6" t="str">
+        <f>IF(CPS!E15&gt;0,CPS!E15,"")</f>
+        <v/>
+      </c>
+      <c r="E6" t="str">
+        <f>IF(CPS!F15&gt;0,CPS!F15,"")</f>
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <f>IF(CPS!G15&gt;0,CPS!G15,"")</f>
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <f>IF(CPS!H15&gt;0,CPS!H15,"")</f>
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <f>IF(CPS!I15&gt;0,CPS!I15,"")</f>
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <f>IF(CPS!J15&gt;0,CPS!J15,"")</f>
+        <v/>
+      </c>
+      <c r="J6" t="str">
+        <f>IF(CPS!K15&gt;0,CPS!K15,"")</f>
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <f>IF(CPS!L15&gt;0,CPS!L15,"")</f>
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <f>IF(CPS!M15&gt;0,CPS!M15,"")</f>
+        <v/>
+      </c>
+      <c r="M6" t="str">
+        <f>IF(CPS!N15&gt;0,CPS!N15,"")</f>
+        <v/>
+      </c>
+      <c r="N6" t="str">
+        <f>IF(CPS!O15&gt;0,CPS!O15,"")</f>
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <f>IF(CPS!P15&gt;0,CPS!P15,"")</f>
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <f>IF(CPS!Q15&gt;0,CPS!Q15,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A7" t="str">
+        <f>IF(CPS!B19&gt;0,CPS!B19,"")</f>
+        <v>OUTSOURCE</v>
+      </c>
+      <c r="B7" t="str">
+        <f>IF(CPS!C19&gt;0,CPS!C19,"")</f>
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <f>IF(CPS!D19&gt;0,CPS!D19,"")</f>
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <f>IF(CPS!E19&gt;0,CPS!E19,"")</f>
+        <v/>
+      </c>
+      <c r="E7" t="str">
+        <f>IF(CPS!F19&gt;0,CPS!F19,"")</f>
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <f>IF(CPS!G19&gt;0,CPS!G19,"")</f>
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <f>IF(CPS!H19&gt;0,CPS!H19,"")</f>
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <f>IF(CPS!I19&gt;0,CPS!I19,"")</f>
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <f>IF(CPS!J19&gt;0,CPS!J19,"")</f>
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <f>IF(CPS!K19&gt;0,CPS!K19,"")</f>
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <f>IF(CPS!L19&gt;0,CPS!L19,"")</f>
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <f>IF(CPS!M19&gt;0,CPS!M19,"")</f>
+        <v/>
+      </c>
+      <c r="M7" t="str">
+        <f>IF(CPS!N19&gt;0,CPS!N19,"")</f>
+        <v/>
+      </c>
+      <c r="N7" t="str">
+        <f>IF(CPS!O19&gt;0,CPS!O19,"")</f>
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <f>IF(CPS!P19&gt;0,CPS!P19,"")</f>
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <f>IF(CPS!Q19&gt;0,CPS!Q19,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B11" t="str">
+        <f>IF(CPS!C1&gt;0,CPS!C1,"")</f>
+        <v>JAN</v>
+      </c>
+      <c r="C11" t="str">
+        <f>IF(CPS!D1&gt;0,CPS!D1,"")</f>
+        <v>FEB</v>
+      </c>
+      <c r="D11" t="str">
+        <f>IF(CPS!E1&gt;0,CPS!E1,"")</f>
+        <v>MAR</v>
+      </c>
+      <c r="E11" t="str">
+        <f>IF(CPS!F1&gt;0,CPS!F1,"")</f>
+        <v>APR</v>
+      </c>
+      <c r="F11" t="str">
+        <f>IF(CPS!G1&gt;0,CPS!G1,"")</f>
+        <v>MAY</v>
+      </c>
+      <c r="G11" t="str">
+        <f>IF(CPS!H1&gt;0,CPS!H1,"")</f>
+        <v>JUN</v>
+      </c>
+      <c r="H11" t="str">
+        <f>IF(CPS!I1&gt;0,CPS!I1,"")</f>
+        <v>JUL</v>
+      </c>
+      <c r="I11" t="str">
+        <f>IF(CPS!J1&gt;0,CPS!J1,"")</f>
+        <v>AUG</v>
+      </c>
+      <c r="J11" t="str">
+        <f>IF(CPS!K1&gt;0,CPS!K1,"")</f>
+        <v>SEP</v>
+      </c>
+      <c r="K11" t="str">
+        <f>IF(CPS!L1&gt;0,CPS!L1,"")</f>
+        <v>OCT</v>
+      </c>
+      <c r="L11" t="str">
+        <f>IF(CPS!M1&gt;0,CPS!M1,"")</f>
+        <v>NOV</v>
+      </c>
+      <c r="M11" t="str">
+        <f>IF(CPS!N1&gt;0,CPS!N1,"")</f>
+        <v>DEC</v>
+      </c>
+      <c r="N11" t="str">
+        <f>IF(CPS!O1&gt;0,CPS!O1,"")</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O11" t="str">
+        <f>IF(CPS!P1&gt;0,CPS!P1,"")</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P11" t="str">
+        <f>IF(CPS!Q1&gt;0,CPS!Q1,"")</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A12" t="str">
+        <f>IF(CPS!A9&gt;0,CPS!A9,"")</f>
+        <v>Staff</v>
+      </c>
+      <c r="B12">
+        <f>IF(CPS!C9&gt;0,CPS!C9,"")</f>
+        <v>18</v>
+      </c>
+      <c r="C12">
+        <f>IF(CPS!D9&gt;0,CPS!D9,"")</f>
+        <v>18</v>
+      </c>
+      <c r="D12">
+        <f>IF(CPS!E9&gt;0,CPS!E9,"")</f>
+        <v>18</v>
+      </c>
+      <c r="E12">
+        <f>IF(CPS!F9&gt;0,CPS!F9,"")</f>
+        <v>17</v>
+      </c>
+      <c r="F12">
+        <f>IF(CPS!G9&gt;0,CPS!G9,"")</f>
+        <v>17</v>
+      </c>
+      <c r="G12">
+        <f>IF(CPS!H9&gt;0,CPS!H9,"")</f>
+        <v>17</v>
+      </c>
+      <c r="H12">
+        <f>IF(CPS!I9&gt;0,CPS!I9,"")</f>
+        <v>17</v>
+      </c>
+      <c r="I12">
+        <f>IF(CPS!J9&gt;0,CPS!J9,"")</f>
+        <v>17</v>
+      </c>
+      <c r="J12">
+        <f>IF(CPS!K9&gt;0,CPS!K9,"")</f>
+        <v>17</v>
+      </c>
+      <c r="K12">
+        <f>IF(CPS!L9&gt;0,CPS!L9,"")</f>
+        <v>17</v>
+      </c>
+      <c r="L12">
+        <f>IF(CPS!M9&gt;0,CPS!M9,"")</f>
+        <v>17</v>
+      </c>
+      <c r="M12">
+        <f>IF(CPS!N9&gt;0,CPS!N9,"")</f>
+        <v>17</v>
+      </c>
+      <c r="N12">
+        <f>IF(CPS!O9&gt;0,CPS!O9,"")</f>
+        <v>17</v>
+      </c>
+      <c r="O12">
+        <f>IF(CPS!P9&gt;0,CPS!P9,"")</f>
+        <v>17</v>
+      </c>
+      <c r="P12">
+        <f>IF(CPS!Q9&gt;0,CPS!Q9,"")</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A13" t="str">
+        <f>IF(CPS!A10&gt;0,CPS!A10,"")</f>
+        <v>Staff AVG</v>
+      </c>
+      <c r="B13">
+        <f>IF(CPS!C10&gt;0,CPS!C10,"")</f>
+        <v>17</v>
+      </c>
+      <c r="C13">
+        <f>IF(CPS!D10&gt;0,CPS!D10,"")</f>
+        <v>17</v>
+      </c>
+      <c r="D13">
+        <f>IF(CPS!E10&gt;0,CPS!E10,"")</f>
+        <v>17</v>
+      </c>
+      <c r="E13">
+        <f>IF(CPS!F10&gt;0,CPS!F10,"")</f>
+        <v>17</v>
+      </c>
+      <c r="F13">
+        <f>IF(CPS!G10&gt;0,CPS!G10,"")</f>
+        <v>17</v>
+      </c>
+      <c r="G13">
+        <f>IF(CPS!H10&gt;0,CPS!H10,"")</f>
+        <v>17</v>
+      </c>
+      <c r="H13">
+        <f>IF(CPS!I10&gt;0,CPS!I10,"")</f>
+        <v>17</v>
+      </c>
+      <c r="I13">
+        <f>IF(CPS!J10&gt;0,CPS!J10,"")</f>
+        <v>17</v>
+      </c>
+      <c r="J13">
+        <f>IF(CPS!K10&gt;0,CPS!K10,"")</f>
+        <v>17</v>
+      </c>
+      <c r="K13">
+        <f>IF(CPS!L10&gt;0,CPS!L10,"")</f>
+        <v>17</v>
+      </c>
+      <c r="L13">
+        <f>IF(CPS!M10&gt;0,CPS!M10,"")</f>
+        <v>17</v>
+      </c>
+      <c r="M13">
+        <f>IF(CPS!N10&gt;0,CPS!N10,"")</f>
+        <v>17</v>
+      </c>
+      <c r="N13">
+        <f>IF(CPS!O10&gt;0,CPS!O10,"")</f>
+        <v>17</v>
+      </c>
+      <c r="O13">
+        <f>IF(CPS!P10&gt;0,CPS!P10,"")</f>
+        <v>17</v>
+      </c>
+      <c r="P13">
+        <f>IF(CPS!Q10&gt;0,CPS!Q10,"")</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A14" t="str">
+        <f>IF(CPS!A11&gt;0,CPS!A11,"")</f>
+        <v>Plan</v>
+      </c>
+      <c r="B14">
+        <f>IF(CPS!C11&gt;0,CPS!C11,"")</f>
+        <v>17</v>
+      </c>
+      <c r="C14">
+        <f>IF(CPS!D11&gt;0,CPS!D11,"")</f>
+        <v>17</v>
+      </c>
+      <c r="D14">
+        <f>IF(CPS!E11&gt;0,CPS!E11,"")</f>
+        <v>17</v>
+      </c>
+      <c r="E14">
+        <f>IF(CPS!F11&gt;0,CPS!F11,"")</f>
+        <v>17</v>
+      </c>
+      <c r="F14">
+        <f>IF(CPS!G11&gt;0,CPS!G11,"")</f>
+        <v>18</v>
+      </c>
+      <c r="G14">
+        <f>IF(CPS!H11&gt;0,CPS!H11,"")</f>
+        <v>17</v>
+      </c>
+      <c r="H14">
+        <f>IF(CPS!I11&gt;0,CPS!I11,"")</f>
+        <v>16</v>
+      </c>
+      <c r="I14">
+        <f>IF(CPS!J11&gt;0,CPS!J11,"")</f>
+        <v>16</v>
+      </c>
+      <c r="J14">
+        <f>IF(CPS!K11&gt;0,CPS!K11,"")</f>
+        <v>16</v>
+      </c>
+      <c r="K14">
+        <f>IF(CPS!L11&gt;0,CPS!L11,"")</f>
+        <v>16</v>
+      </c>
+      <c r="L14">
+        <f>IF(CPS!M11&gt;0,CPS!M11,"")</f>
+        <v>16</v>
+      </c>
+      <c r="M14">
+        <f>IF(CPS!N11&gt;0,CPS!N11,"")</f>
+        <v>16</v>
+      </c>
+      <c r="N14">
+        <f>IF(CPS!O11&gt;0,CPS!O11,"")</f>
+        <v>14</v>
+      </c>
+      <c r="O14">
+        <f>IF(CPS!P11&gt;0,CPS!P11,"")</f>
+        <v>14</v>
+      </c>
+      <c r="P14">
+        <f>IF(CPS!Q11&gt;0,CPS!Q11,"")</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B21" t="str">
+        <f>IF(CPS!C1&gt;0,CPS!C1,"")</f>
+        <v>JAN</v>
+      </c>
+      <c r="C21" t="str">
+        <f>IF(CPS!D1&gt;0,CPS!D1,"")</f>
+        <v>FEB</v>
+      </c>
+      <c r="D21" t="str">
+        <f>IF(CPS!E1&gt;0,CPS!E1,"")</f>
+        <v>MAR</v>
+      </c>
+      <c r="E21" t="str">
+        <f>IF(CPS!F1&gt;0,CPS!F1,"")</f>
+        <v>APR</v>
+      </c>
+      <c r="F21" t="str">
+        <f>IF(CPS!G1&gt;0,CPS!G1,"")</f>
+        <v>MAY</v>
+      </c>
+      <c r="G21" t="str">
+        <f>IF(CPS!H1&gt;0,CPS!H1,"")</f>
+        <v>JUN</v>
+      </c>
+      <c r="H21" t="str">
+        <f>IF(CPS!I1&gt;0,CPS!I1,"")</f>
+        <v>JUL</v>
+      </c>
+      <c r="I21" t="str">
+        <f>IF(CPS!J1&gt;0,CPS!J1,"")</f>
+        <v>AUG</v>
+      </c>
+      <c r="J21" t="str">
+        <f>IF(CPS!K1&gt;0,CPS!K1,"")</f>
+        <v>SEP</v>
+      </c>
+      <c r="K21" t="str">
+        <f>IF(CPS!L1&gt;0,CPS!L1,"")</f>
+        <v>OCT</v>
+      </c>
+      <c r="L21" t="str">
+        <f>IF(CPS!M1&gt;0,CPS!M1,"")</f>
+        <v>NOV</v>
+      </c>
+      <c r="M21" t="str">
+        <f>IF(CPS!N1&gt;0,CPS!N1,"")</f>
+        <v>DEC</v>
+      </c>
+      <c r="N21" t="str">
+        <f>IF(CPS!O1&gt;0,CPS!O1,"")</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O21" t="str">
+        <f>IF(CPS!P1&gt;0,CPS!P1,"")</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P21" t="str">
+        <f>IF(CPS!Q1&gt;0,CPS!Q1,"")</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A22" t="str">
+        <f>IF(CPS!A13&gt;0,CPS!A13,"")</f>
+        <v>Grand Total</v>
+      </c>
+      <c r="B22" t="str">
+        <f>IF(CPS!C13&gt;0,CPS!C13,"")</f>
+        <v/>
+      </c>
+      <c r="C22" t="str">
+        <f>IF(CPS!D13&gt;0,CPS!D13,"")</f>
+        <v/>
+      </c>
+      <c r="D22" t="str">
+        <f>IF(CPS!E13&gt;0,CPS!E13,"")</f>
+        <v/>
+      </c>
+      <c r="E22" t="str">
+        <f>IF(CPS!F13&gt;0,CPS!F13,"")</f>
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <f>IF(CPS!G13&gt;0,CPS!G13,"")</f>
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <f>IF(CPS!H13&gt;0,CPS!H13,"")</f>
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <f>IF(CPS!I13&gt;0,CPS!I13,"")</f>
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <f>IF(CPS!J13&gt;0,CPS!J13,"")</f>
+        <v/>
+      </c>
+      <c r="J22" t="str">
+        <f>IF(CPS!K13&gt;0,CPS!K13,"")</f>
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <f>IF(CPS!L13&gt;0,CPS!L13,"")</f>
+        <v/>
+      </c>
+      <c r="L22" t="str">
+        <f>IF(CPS!M13&gt;0,CPS!M13,"")</f>
+        <v/>
+      </c>
+      <c r="M22" t="str">
+        <f>IF(CPS!N13&gt;0,CPS!N13,"")</f>
+        <v/>
+      </c>
+      <c r="N22" t="str">
+        <f>IF(CPS!O13&gt;0,CPS!O13,"")</f>
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <f>IF(CPS!P13&gt;0,CPS!P13,"")</f>
+        <v/>
+      </c>
+      <c r="P22" t="str">
+        <f>IF(CPS!Q13&gt;0,CPS!Q13,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A23" t="str">
+        <f>IF(CPS!A14&gt;0,CPS!A14,"")</f>
+        <v>Staff AVG</v>
+      </c>
+      <c r="B23" t="str">
+        <f>IF(CPS!C14&gt;0,CPS!C14,"")</f>
+        <v/>
+      </c>
+      <c r="C23" t="str">
+        <f>IF(CPS!D14&gt;0,CPS!D14,"")</f>
+        <v/>
+      </c>
+      <c r="D23" t="str">
+        <f>IF(CPS!E14&gt;0,CPS!E14,"")</f>
+        <v/>
+      </c>
+      <c r="E23" t="str">
+        <f>IF(CPS!F14&gt;0,CPS!F14,"")</f>
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <f>IF(CPS!G14&gt;0,CPS!G14,"")</f>
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <f>IF(CPS!H14&gt;0,CPS!H14,"")</f>
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <f>IF(CPS!I14&gt;0,CPS!I14,"")</f>
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <f>IF(CPS!J14&gt;0,CPS!J14,"")</f>
+        <v/>
+      </c>
+      <c r="J23" t="str">
+        <f>IF(CPS!K14&gt;0,CPS!K14,"")</f>
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <f>IF(CPS!L14&gt;0,CPS!L14,"")</f>
+        <v/>
+      </c>
+      <c r="L23" t="str">
+        <f>IF(CPS!M14&gt;0,CPS!M14,"")</f>
+        <v/>
+      </c>
+      <c r="M23" t="str">
+        <f>IF(CPS!N14&gt;0,CPS!N14,"")</f>
+        <v/>
+      </c>
+      <c r="N23" t="str">
+        <f>IF(CPS!O14&gt;0,CPS!O14,"")</f>
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <f>IF(CPS!P14&gt;0,CPS!P14,"")</f>
+        <v/>
+      </c>
+      <c r="P23" t="str">
+        <f>IF(CPS!Q14&gt;0,CPS!Q14,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A24" t="str">
+        <f>IF(CPS!A15&gt;0,CPS!A15,"")</f>
+        <v/>
+      </c>
+      <c r="B24" t="str">
+        <f>IF(CPS!C15&gt;0,CPS!C15,"")</f>
+        <v/>
+      </c>
+      <c r="C24" t="str">
+        <f>IF(CPS!D15&gt;0,CPS!D15,"")</f>
+        <v/>
+      </c>
+      <c r="D24" t="str">
+        <f>IF(CPS!E15&gt;0,CPS!E15,"")</f>
+        <v/>
+      </c>
+      <c r="E24" t="str">
+        <f>IF(CPS!F15&gt;0,CPS!F15,"")</f>
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <f>IF(CPS!G15&gt;0,CPS!G15,"")</f>
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <f>IF(CPS!H15&gt;0,CPS!H15,"")</f>
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <f>IF(CPS!I15&gt;0,CPS!I15,"")</f>
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <f>IF(CPS!J15&gt;0,CPS!J15,"")</f>
+        <v/>
+      </c>
+      <c r="J24" t="str">
+        <f>IF(CPS!K15&gt;0,CPS!K15,"")</f>
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <f>IF(CPS!L15&gt;0,CPS!L15,"")</f>
+        <v/>
+      </c>
+      <c r="L24" t="str">
+        <f>IF(CPS!M15&gt;0,CPS!M15,"")</f>
+        <v/>
+      </c>
+      <c r="M24" t="str">
+        <f>IF(CPS!N15&gt;0,CPS!N15,"")</f>
+        <v/>
+      </c>
+      <c r="N24" t="str">
+        <f>IF(CPS!O15&gt;0,CPS!O15,"")</f>
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <f>IF(CPS!P15&gt;0,CPS!P15,"")</f>
+        <v/>
+      </c>
+      <c r="P24" t="str">
+        <f>IF(CPS!Q15&gt;0,CPS!Q15,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B31" t="str">
+        <f>IF(CPS!C1&gt;0,CPS!C1,"")</f>
+        <v>JAN</v>
+      </c>
+      <c r="C31" t="str">
+        <f>IF(CPS!D1&gt;0,CPS!D1,"")</f>
+        <v>FEB</v>
+      </c>
+      <c r="D31" t="str">
+        <f>IF(CPS!E1&gt;0,CPS!E1,"")</f>
+        <v>MAR</v>
+      </c>
+      <c r="E31" t="str">
+        <f>IF(CPS!F1&gt;0,CPS!F1,"")</f>
+        <v>APR</v>
+      </c>
+      <c r="F31" t="str">
+        <f>IF(CPS!G1&gt;0,CPS!G1,"")</f>
+        <v>MAY</v>
+      </c>
+      <c r="G31" t="str">
+        <f>IF(CPS!H1&gt;0,CPS!H1,"")</f>
+        <v>JUN</v>
+      </c>
+      <c r="H31" t="str">
+        <f>IF(CPS!I1&gt;0,CPS!I1,"")</f>
+        <v>JUL</v>
+      </c>
+      <c r="I31" t="str">
+        <f>IF(CPS!J1&gt;0,CPS!J1,"")</f>
+        <v>AUG</v>
+      </c>
+      <c r="J31" t="str">
+        <f>IF(CPS!K1&gt;0,CPS!K1,"")</f>
+        <v>SEP</v>
+      </c>
+      <c r="K31" t="str">
+        <f>IF(CPS!L1&gt;0,CPS!L1,"")</f>
+        <v>OCT</v>
+      </c>
+      <c r="L31" t="str">
+        <f>IF(CPS!M1&gt;0,CPS!M1,"")</f>
+        <v>NOV</v>
+      </c>
+      <c r="M31" t="str">
+        <f>IF(CPS!N1&gt;0,CPS!N1,"")</f>
+        <v>DEC</v>
+      </c>
+      <c r="N31" t="str">
+        <f>IF(CPS!O1&gt;0,CPS!O1,"")</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O31" t="str">
+        <f>IF(CPS!P1&gt;0,CPS!P1,"")</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P31" t="str">
+        <f>IF(CPS!Q1&gt;0,CPS!Q1,"")</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A32" t="str">
+        <f>IF(CPS!A17&gt;0,CPS!A17,"")</f>
+        <v>Grand Total</v>
+      </c>
+      <c r="B32" t="str">
+        <f>IF(CPS!C17&gt;0,CPS!C17,"")</f>
+        <v/>
+      </c>
+      <c r="C32" t="str">
+        <f>IF(CPS!D17&gt;0,CPS!D17,"")</f>
+        <v/>
+      </c>
+      <c r="D32" t="str">
+        <f>IF(CPS!E17&gt;0,CPS!E17,"")</f>
+        <v/>
+      </c>
+      <c r="E32" t="str">
+        <f>IF(CPS!F17&gt;0,CPS!F17,"")</f>
+        <v/>
+      </c>
+      <c r="F32" t="str">
+        <f>IF(CPS!G17&gt;0,CPS!G17,"")</f>
+        <v/>
+      </c>
+      <c r="G32" t="str">
+        <f>IF(CPS!H17&gt;0,CPS!H17,"")</f>
+        <v/>
+      </c>
+      <c r="H32" t="str">
+        <f>IF(CPS!I17&gt;0,CPS!I17,"")</f>
+        <v/>
+      </c>
+      <c r="I32" t="str">
+        <f>IF(CPS!J17&gt;0,CPS!J17,"")</f>
+        <v/>
+      </c>
+      <c r="J32" t="str">
+        <f>IF(CPS!K17&gt;0,CPS!K17,"")</f>
+        <v/>
+      </c>
+      <c r="K32" t="str">
+        <f>IF(CPS!L17&gt;0,CPS!L17,"")</f>
+        <v/>
+      </c>
+      <c r="L32" t="str">
+        <f>IF(CPS!M17&gt;0,CPS!M17,"")</f>
+        <v/>
+      </c>
+      <c r="M32" t="str">
+        <f>IF(CPS!N17&gt;0,CPS!N17,"")</f>
+        <v/>
+      </c>
+      <c r="N32" t="str">
+        <f>IF(CPS!O17&gt;0,CPS!O17,"")</f>
+        <v/>
+      </c>
+      <c r="O32" t="str">
+        <f>IF(CPS!P17&gt;0,CPS!P17,"")</f>
+        <v/>
+      </c>
+      <c r="P32" t="str">
+        <f>IF(CPS!Q17&gt;0,CPS!Q17,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A33" t="str">
+        <f>IF(CPS!A18&gt;0,CPS!A18,"")</f>
+        <v>Staff AVG</v>
+      </c>
+      <c r="B33" t="str">
+        <f>IF(CPS!C18&gt;0,CPS!C18,"")</f>
+        <v/>
+      </c>
+      <c r="C33" t="str">
+        <f>IF(CPS!D18&gt;0,CPS!D18,"")</f>
+        <v/>
+      </c>
+      <c r="D33" t="str">
+        <f>IF(CPS!E18&gt;0,CPS!E18,"")</f>
+        <v/>
+      </c>
+      <c r="E33" t="str">
+        <f>IF(CPS!F18&gt;0,CPS!F18,"")</f>
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <f>IF(CPS!G18&gt;0,CPS!G18,"")</f>
+        <v/>
+      </c>
+      <c r="G33" t="str">
+        <f>IF(CPS!H18&gt;0,CPS!H18,"")</f>
+        <v/>
+      </c>
+      <c r="H33" t="str">
+        <f>IF(CPS!I18&gt;0,CPS!I18,"")</f>
+        <v/>
+      </c>
+      <c r="I33" t="str">
+        <f>IF(CPS!J18&gt;0,CPS!J18,"")</f>
+        <v/>
+      </c>
+      <c r="J33" t="str">
+        <f>IF(CPS!K18&gt;0,CPS!K18,"")</f>
+        <v/>
+      </c>
+      <c r="K33" t="str">
+        <f>IF(CPS!L18&gt;0,CPS!L18,"")</f>
+        <v/>
+      </c>
+      <c r="L33" t="str">
+        <f>IF(CPS!M18&gt;0,CPS!M18,"")</f>
+        <v/>
+      </c>
+      <c r="M33" t="str">
+        <f>IF(CPS!N18&gt;0,CPS!N18,"")</f>
+        <v/>
+      </c>
+      <c r="N33" t="str">
+        <f>IF(CPS!O18&gt;0,CPS!O18,"")</f>
+        <v/>
+      </c>
+      <c r="O33" t="str">
+        <f>IF(CPS!P18&gt;0,CPS!P18,"")</f>
+        <v/>
+      </c>
+      <c r="P33" t="str">
+        <f>IF(CPS!Q18&gt;0,CPS!Q18,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A34" t="str">
+        <f>IF(CPS!A19&gt;0,CPS!A19,"")</f>
+        <v/>
+      </c>
+      <c r="B34" t="str">
+        <f>IF(CPS!C19&gt;0,CPS!C19,"")</f>
+        <v/>
+      </c>
+      <c r="C34" t="str">
+        <f>IF(CPS!D19&gt;0,CPS!D19,"")</f>
+        <v/>
+      </c>
+      <c r="D34" t="str">
+        <f>IF(CPS!E19&gt;0,CPS!E19,"")</f>
+        <v/>
+      </c>
+      <c r="E34" t="str">
+        <f>IF(CPS!F19&gt;0,CPS!F19,"")</f>
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <f>IF(CPS!G19&gt;0,CPS!G19,"")</f>
+        <v/>
+      </c>
+      <c r="G34" t="str">
+        <f>IF(CPS!H19&gt;0,CPS!H19,"")</f>
+        <v/>
+      </c>
+      <c r="H34" t="str">
+        <f>IF(CPS!I19&gt;0,CPS!I19,"")</f>
+        <v/>
+      </c>
+      <c r="I34" t="str">
+        <f>IF(CPS!J19&gt;0,CPS!J19,"")</f>
+        <v/>
+      </c>
+      <c r="J34" t="str">
+        <f>IF(CPS!K19&gt;0,CPS!K19,"")</f>
+        <v/>
+      </c>
+      <c r="K34" t="str">
+        <f>IF(CPS!L19&gt;0,CPS!L19,"")</f>
+        <v/>
+      </c>
+      <c r="L34" t="str">
+        <f>IF(CPS!M19&gt;0,CPS!M19,"")</f>
+        <v/>
+      </c>
+      <c r="M34" t="str">
+        <f>IF(CPS!N19&gt;0,CPS!N19,"")</f>
+        <v/>
+      </c>
+      <c r="N34" t="str">
+        <f>IF(CPS!O19&gt;0,CPS!O19,"")</f>
+        <v/>
+      </c>
+      <c r="O34" t="str">
+        <f>IF(CPS!P19&gt;0,CPS!P19,"")</f>
+        <v/>
+      </c>
+      <c r="P34" t="str">
+        <f>IF(CPS!Q19&gt;0,CPS!Q19,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B41" t="str">
+        <f>IF(CPS!C31&gt;0,CPS!C31,"")</f>
+        <v>Q1</v>
+      </c>
+      <c r="C41" t="str">
+        <f>IF(CPS!D31&gt;0,CPS!D31,"")</f>
+        <v>Q2</v>
+      </c>
+      <c r="D41" t="str">
+        <f>IF(CPS!E31&gt;0,CPS!E31,"")</f>
+        <v>Q3</v>
+      </c>
+      <c r="E41" t="str">
+        <f>IF(CPS!F31&gt;0,CPS!F31,"")</f>
+        <v>Q4</v>
+      </c>
+      <c r="F41" t="str">
+        <f>IF(CPS!G31&gt;0,CPS!G31,"")</f>
+        <v>Q1'27</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A42" t="str">
+        <f>IF(CPS!B32&gt;0,CPS!B32,"")</f>
+        <v>Staff</v>
+      </c>
+      <c r="B42">
+        <f>IF(CPS!C32&gt;0,CPS!C32,"")</f>
+        <v>18</v>
+      </c>
+      <c r="C42">
+        <f>IF(CPS!D32&gt;0,CPS!D32,"")</f>
+        <v>17</v>
+      </c>
+      <c r="D42">
+        <f>IF(CPS!E32&gt;0,CPS!E32,"")</f>
+        <v>17</v>
+      </c>
+      <c r="E42">
+        <f>IF(CPS!F32&gt;0,CPS!F32,"")</f>
+        <v>17</v>
+      </c>
+      <c r="F42">
+        <f>IF(CPS!G32&gt;0,CPS!G32,"")</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A43" t="str">
+        <f>IF(CPS!B33&gt;0,CPS!B33,"")</f>
+        <v>Staff AVG</v>
+      </c>
+      <c r="B43">
+        <f>IF(CPS!C33&gt;0,CPS!C33,"")</f>
+        <v>17</v>
+      </c>
+      <c r="C43">
+        <f>IF(CPS!D33&gt;0,CPS!D33,"")</f>
+        <v>17</v>
+      </c>
+      <c r="D43">
+        <f>IF(CPS!E33&gt;0,CPS!E33,"")</f>
+        <v>17</v>
+      </c>
+      <c r="E43">
+        <f>IF(CPS!F33&gt;0,CPS!F33,"")</f>
+        <v>17</v>
+      </c>
+      <c r="F43">
+        <f>IF(CPS!G33&gt;0,CPS!G33,"")</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A44" t="str">
+        <f>IF(CPS!B34&gt;0,CPS!B34,"")</f>
+        <v>Plan</v>
+      </c>
+      <c r="B44">
+        <f>IF(CPS!C34&gt;0,CPS!C34,"")</f>
+        <v>17</v>
+      </c>
+      <c r="C44">
+        <f>IF(CPS!D34&gt;0,CPS!D34,"")</f>
+        <v>17</v>
+      </c>
+      <c r="D44">
+        <f>IF(CPS!E34&gt;0,CPS!E34,"")</f>
+        <v>16</v>
+      </c>
+      <c r="E44">
+        <f>IF(CPS!F34&gt;0,CPS!F34,"")</f>
+        <v>16</v>
+      </c>
+      <c r="F44">
+        <f>IF(CPS!G34&gt;0,CPS!G34,"")</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A45" t="str">
+        <f>IF(CPS!B41&gt;0,CPS!B41,"")</f>
+        <v>PAYROLL</v>
+      </c>
+      <c r="B45">
+        <f>IF(CPS!C41&gt;0,CPS!C41,"")</f>
+        <v>17</v>
+      </c>
+      <c r="C45">
+        <f>IF(CPS!D41&gt;0,CPS!D41,"")</f>
+        <v>17</v>
+      </c>
+      <c r="D45">
+        <f>IF(CPS!E41&gt;0,CPS!E41,"")</f>
+        <v>16</v>
+      </c>
+      <c r="E45">
+        <f>IF(CPS!F41&gt;0,CPS!F41,"")</f>
+        <v>16</v>
+      </c>
+      <c r="F45">
+        <f>IF(CPS!G41&gt;0,CPS!G41,"")</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A46" t="str">
+        <f>IF(CPS!B45&gt;0,CPS!B45,"")</f>
+        <v>CONTRACTOR</v>
+      </c>
+      <c r="B46" t="str">
+        <f>IF(CPS!C45&gt;0,CPS!C45,"")</f>
+        <v/>
+      </c>
+      <c r="C46" t="str">
+        <f>IF(CPS!D45&gt;0,CPS!D45,"")</f>
+        <v/>
+      </c>
+      <c r="D46" t="str">
+        <f>IF(CPS!E45&gt;0,CPS!E45,"")</f>
+        <v/>
+      </c>
+      <c r="E46" t="str">
+        <f>IF(CPS!F45&gt;0,CPS!F45,"")</f>
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <f>IF(CPS!G45&gt;0,CPS!G45,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A47" t="str">
+        <f>IF(CPS!B49&gt;0,CPS!B49,"")</f>
+        <v>OUTSOURCE</v>
+      </c>
+      <c r="B47" t="str">
+        <f>IF(CPS!C49&gt;0,CPS!C49,"")</f>
+        <v/>
+      </c>
+      <c r="C47" t="str">
+        <f>IF(CPS!D49&gt;0,CPS!D49,"")</f>
+        <v/>
+      </c>
+      <c r="D47" t="str">
+        <f>IF(CPS!E49&gt;0,CPS!E49,"")</f>
+        <v/>
+      </c>
+      <c r="E47" t="str">
+        <f>IF(CPS!F49&gt;0,CPS!F49,"")</f>
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <f>IF(CPS!G49&gt;0,CPS!G49,"")</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/workforceresult.xlsx
+++ b/workforceresult.xlsx
@@ -1,22 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miintra/Library/Mobile Documents/com~apple~CloudDocs/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miiintra/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6758835-D610-DF49-AA0B-A2DA96016F06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEA01787-D86A-754E-919A-7A21D34DAB96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16120" activeTab="3" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
+    <workbookView xWindow="14500" yWindow="3140" windowWidth="28800" windowHeight="18680" activeTab="9" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
   </bookViews>
   <sheets>
     <sheet name="ALL" sheetId="1" r:id="rId1"/>
     <sheet name="GraphAll" sheetId="3" r:id="rId2"/>
     <sheet name="CPS" sheetId="2" r:id="rId3"/>
     <sheet name="GraphCPS" sheetId="4" r:id="rId4"/>
+    <sheet name="PSE" sheetId="5" r:id="rId5"/>
+    <sheet name="GraphPSE" sheetId="6" r:id="rId6"/>
+    <sheet name="SD" sheetId="7" r:id="rId7"/>
+    <sheet name="GraphSD" sheetId="8" r:id="rId8"/>
+    <sheet name="AIC" sheetId="9" r:id="rId9"/>
+    <sheet name="GraphAIC" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="35">
   <si>
     <t>Type</t>
   </si>
@@ -134,6 +140,15 @@
   </si>
   <si>
     <t>CPS</t>
+  </si>
+  <si>
+    <t>PSE</t>
+  </si>
+  <si>
+    <t>SD</t>
+  </si>
+  <si>
+    <t>AIC</t>
   </si>
 </sst>
 </file>
@@ -310,7 +325,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -363,6 +378,7 @@
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -383,7 +399,7 @@
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -391,34 +407,34 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -697,6 +713,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{151C9BC8-0901-2D49-9889-BA2630F40C73}">
+  <sheetPr>
+    <tabColor theme="4"/>
+  </sheetPr>
   <dimension ref="A1:Q49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
@@ -1974,8 +1993,1443 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2091888F-7B75-244A-B119-7132B64EC1D8}">
+  <sheetPr>
+    <tabColor theme="9" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:P47"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B1" t="str">
+        <f>IF(AIC!C1&gt;0,AIC!C1,"")</f>
+        <v>JAN</v>
+      </c>
+      <c r="C1" t="str">
+        <f>IF(AIC!D1&gt;0,AIC!D1,"")</f>
+        <v>FEB</v>
+      </c>
+      <c r="D1" t="str">
+        <f>IF(AIC!E1&gt;0,AIC!E1,"")</f>
+        <v>MAR</v>
+      </c>
+      <c r="E1" t="str">
+        <f>IF(AIC!F1&gt;0,AIC!F1,"")</f>
+        <v>APR</v>
+      </c>
+      <c r="F1" t="str">
+        <f>IF(AIC!G1&gt;0,AIC!G1,"")</f>
+        <v>MAY</v>
+      </c>
+      <c r="G1" t="str">
+        <f>IF(AIC!H1&gt;0,AIC!H1,"")</f>
+        <v>JUN</v>
+      </c>
+      <c r="H1" t="str">
+        <f>IF(AIC!I1&gt;0,AIC!I1,"")</f>
+        <v>JUL</v>
+      </c>
+      <c r="I1" t="str">
+        <f>IF(AIC!J1&gt;0,AIC!J1,"")</f>
+        <v>AUG</v>
+      </c>
+      <c r="J1" t="str">
+        <f>IF(AIC!K1&gt;0,AIC!K1,"")</f>
+        <v>SEP</v>
+      </c>
+      <c r="K1" t="str">
+        <f>IF(AIC!L1&gt;0,AIC!L1,"")</f>
+        <v>OCT</v>
+      </c>
+      <c r="L1" t="str">
+        <f>IF(AIC!M1&gt;0,AIC!M1,"")</f>
+        <v>NOV</v>
+      </c>
+      <c r="M1" t="str">
+        <f>IF(AIC!N1&gt;0,AIC!N1,"")</f>
+        <v>DEC</v>
+      </c>
+      <c r="N1" t="str">
+        <f>IF(AIC!O1&gt;0,AIC!O1,"")</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O1" t="str">
+        <f>IF(AIC!P1&gt;0,AIC!P1,"")</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P1" t="str">
+        <f>IF(AIC!Q1&gt;0,AIC!Q1,"")</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A2" t="str">
+        <f>IF(AIC!B2&gt;0,AIC!B2,"")</f>
+        <v>Staff</v>
+      </c>
+      <c r="B2">
+        <f>IF(AIC!C2&gt;0,AIC!C2,"")</f>
+        <v>24</v>
+      </c>
+      <c r="C2">
+        <f>IF(AIC!D2&gt;0,AIC!D2,"")</f>
+        <v>23</v>
+      </c>
+      <c r="D2">
+        <f>IF(AIC!E2&gt;0,AIC!E2,"")</f>
+        <v>22</v>
+      </c>
+      <c r="E2">
+        <f>IF(AIC!F2&gt;0,AIC!F2,"")</f>
+        <v>21</v>
+      </c>
+      <c r="F2">
+        <f>IF(AIC!G2&gt;0,AIC!G2,"")</f>
+        <v>20</v>
+      </c>
+      <c r="G2">
+        <f>IF(AIC!H2&gt;0,AIC!H2,"")</f>
+        <v>20</v>
+      </c>
+      <c r="H2">
+        <f>IF(AIC!I2&gt;0,AIC!I2,"")</f>
+        <v>19</v>
+      </c>
+      <c r="I2">
+        <f>IF(AIC!J2&gt;0,AIC!J2,"")</f>
+        <v>19</v>
+      </c>
+      <c r="J2">
+        <f>IF(AIC!K2&gt;0,AIC!K2,"")</f>
+        <v>19</v>
+      </c>
+      <c r="K2">
+        <f>IF(AIC!L2&gt;0,AIC!L2,"")</f>
+        <v>19</v>
+      </c>
+      <c r="L2">
+        <f>IF(AIC!M2&gt;0,AIC!M2,"")</f>
+        <v>19</v>
+      </c>
+      <c r="M2">
+        <f>IF(AIC!N2&gt;0,AIC!N2,"")</f>
+        <v>19</v>
+      </c>
+      <c r="N2">
+        <f>IF(AIC!O2&gt;0,AIC!O2,"")</f>
+        <v>19</v>
+      </c>
+      <c r="O2">
+        <f>IF(AIC!P2&gt;0,AIC!P2,"")</f>
+        <v>19</v>
+      </c>
+      <c r="P2">
+        <f>IF(AIC!Q2&gt;0,AIC!Q2,"")</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A3" t="str">
+        <f>IF(AIC!B3&gt;0,AIC!B3,"")</f>
+        <v>Staff AVG</v>
+      </c>
+      <c r="B3">
+        <f>IF(AIC!C3&gt;0,AIC!C3,"")</f>
+        <v>20</v>
+      </c>
+      <c r="C3">
+        <f>IF(AIC!D3&gt;0,AIC!D3,"")</f>
+        <v>20</v>
+      </c>
+      <c r="D3">
+        <f>IF(AIC!E3&gt;0,AIC!E3,"")</f>
+        <v>20</v>
+      </c>
+      <c r="E3">
+        <f>IF(AIC!F3&gt;0,AIC!F3,"")</f>
+        <v>19</v>
+      </c>
+      <c r="F3">
+        <f>IF(AIC!G3&gt;0,AIC!G3,"")</f>
+        <v>19</v>
+      </c>
+      <c r="G3">
+        <f>IF(AIC!H3&gt;0,AIC!H3,"")</f>
+        <v>19</v>
+      </c>
+      <c r="H3">
+        <f>IF(AIC!I3&gt;0,AIC!I3,"")</f>
+        <v>19</v>
+      </c>
+      <c r="I3">
+        <f>IF(AIC!J3&gt;0,AIC!J3,"")</f>
+        <v>19</v>
+      </c>
+      <c r="J3">
+        <f>IF(AIC!K3&gt;0,AIC!K3,"")</f>
+        <v>19</v>
+      </c>
+      <c r="K3">
+        <f>IF(AIC!L3&gt;0,AIC!L3,"")</f>
+        <v>19</v>
+      </c>
+      <c r="L3">
+        <f>IF(AIC!M3&gt;0,AIC!M3,"")</f>
+        <v>19</v>
+      </c>
+      <c r="M3">
+        <f>IF(AIC!N3&gt;0,AIC!N3,"")</f>
+        <v>19</v>
+      </c>
+      <c r="N3">
+        <f>IF(AIC!O3&gt;0,AIC!O3,"")</f>
+        <v>19</v>
+      </c>
+      <c r="O3">
+        <f>IF(AIC!P3&gt;0,AIC!P3,"")</f>
+        <v>19</v>
+      </c>
+      <c r="P3">
+        <f>IF(AIC!Q3&gt;0,AIC!Q3,"")</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A4" t="str">
+        <f>IF(AIC!B4&gt;0,AIC!B4,"")</f>
+        <v>Plan</v>
+      </c>
+      <c r="B4">
+        <f>IF(AIC!C4&gt;0,AIC!C4,"")</f>
+        <v>16</v>
+      </c>
+      <c r="C4">
+        <f>IF(AIC!D4&gt;0,AIC!D4,"")</f>
+        <v>17</v>
+      </c>
+      <c r="D4">
+        <f>IF(AIC!E4&gt;0,AIC!E4,"")</f>
+        <v>16</v>
+      </c>
+      <c r="E4">
+        <f>IF(AIC!F4&gt;0,AIC!F4,"")</f>
+        <v>19</v>
+      </c>
+      <c r="F4">
+        <f>IF(AIC!G4&gt;0,AIC!G4,"")</f>
+        <v>18</v>
+      </c>
+      <c r="G4">
+        <f>IF(AIC!H4&gt;0,AIC!H4,"")</f>
+        <v>18</v>
+      </c>
+      <c r="H4">
+        <f>IF(AIC!I4&gt;0,AIC!I4,"")</f>
+        <v>16</v>
+      </c>
+      <c r="I4">
+        <f>IF(AIC!J4&gt;0,AIC!J4,"")</f>
+        <v>15</v>
+      </c>
+      <c r="J4">
+        <f>IF(AIC!K4&gt;0,AIC!K4,"")</f>
+        <v>14</v>
+      </c>
+      <c r="K4">
+        <f>IF(AIC!L4&gt;0,AIC!L4,"")</f>
+        <v>14</v>
+      </c>
+      <c r="L4">
+        <f>IF(AIC!M4&gt;0,AIC!M4,"")</f>
+        <v>14</v>
+      </c>
+      <c r="M4">
+        <f>IF(AIC!N4&gt;0,AIC!N4,"")</f>
+        <v>13</v>
+      </c>
+      <c r="N4">
+        <f>IF(AIC!O4&gt;0,AIC!O4,"")</f>
+        <v>8</v>
+      </c>
+      <c r="O4">
+        <f>IF(AIC!P4&gt;0,AIC!P4,"")</f>
+        <v>8</v>
+      </c>
+      <c r="P4">
+        <f>IF(AIC!Q4&gt;0,AIC!Q4,"")</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A5" t="str">
+        <f>IF(AIC!B11&gt;0,AIC!B11,"")</f>
+        <v>PAYROLL</v>
+      </c>
+      <c r="B5">
+        <f>IF(AIC!C11&gt;0,AIC!C11,"")</f>
+        <v>16</v>
+      </c>
+      <c r="C5">
+        <f>IF(AIC!D11&gt;0,AIC!D11,"")</f>
+        <v>17</v>
+      </c>
+      <c r="D5">
+        <f>IF(AIC!E11&gt;0,AIC!E11,"")</f>
+        <v>16</v>
+      </c>
+      <c r="E5">
+        <f>IF(AIC!F11&gt;0,AIC!F11,"")</f>
+        <v>19</v>
+      </c>
+      <c r="F5">
+        <f>IF(AIC!G11&gt;0,AIC!G11,"")</f>
+        <v>18</v>
+      </c>
+      <c r="G5">
+        <f>IF(AIC!H11&gt;0,AIC!H11,"")</f>
+        <v>18</v>
+      </c>
+      <c r="H5">
+        <f>IF(AIC!I11&gt;0,AIC!I11,"")</f>
+        <v>16</v>
+      </c>
+      <c r="I5">
+        <f>IF(AIC!J11&gt;0,AIC!J11,"")</f>
+        <v>15</v>
+      </c>
+      <c r="J5">
+        <f>IF(AIC!K11&gt;0,AIC!K11,"")</f>
+        <v>14</v>
+      </c>
+      <c r="K5">
+        <f>IF(AIC!L11&gt;0,AIC!L11,"")</f>
+        <v>14</v>
+      </c>
+      <c r="L5">
+        <f>IF(AIC!M11&gt;0,AIC!M11,"")</f>
+        <v>14</v>
+      </c>
+      <c r="M5">
+        <f>IF(AIC!N11&gt;0,AIC!N11,"")</f>
+        <v>13</v>
+      </c>
+      <c r="N5">
+        <f>IF(AIC!O11&gt;0,AIC!O11,"")</f>
+        <v>8</v>
+      </c>
+      <c r="O5">
+        <f>IF(AIC!P11&gt;0,AIC!P11,"")</f>
+        <v>8</v>
+      </c>
+      <c r="P5">
+        <f>IF(AIC!Q11&gt;0,AIC!Q11,"")</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A6" t="str">
+        <f>IF(AIC!B15&gt;0,AIC!B15,"")</f>
+        <v>CONTRACTOR</v>
+      </c>
+      <c r="B6" t="str">
+        <f>IF(AIC!C15&gt;0,AIC!C15,"")</f>
+        <v/>
+      </c>
+      <c r="C6" t="str">
+        <f>IF(AIC!D15&gt;0,AIC!D15,"")</f>
+        <v/>
+      </c>
+      <c r="D6" t="str">
+        <f>IF(AIC!E15&gt;0,AIC!E15,"")</f>
+        <v/>
+      </c>
+      <c r="E6" t="str">
+        <f>IF(AIC!F15&gt;0,AIC!F15,"")</f>
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <f>IF(AIC!G15&gt;0,AIC!G15,"")</f>
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <f>IF(AIC!H15&gt;0,AIC!H15,"")</f>
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <f>IF(AIC!I15&gt;0,AIC!I15,"")</f>
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <f>IF(AIC!J15&gt;0,AIC!J15,"")</f>
+        <v/>
+      </c>
+      <c r="J6" t="str">
+        <f>IF(AIC!K15&gt;0,AIC!K15,"")</f>
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <f>IF(AIC!L15&gt;0,AIC!L15,"")</f>
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <f>IF(AIC!M15&gt;0,AIC!M15,"")</f>
+        <v/>
+      </c>
+      <c r="M6" t="str">
+        <f>IF(AIC!N15&gt;0,AIC!N15,"")</f>
+        <v/>
+      </c>
+      <c r="N6" t="str">
+        <f>IF(AIC!O15&gt;0,AIC!O15,"")</f>
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <f>IF(AIC!P15&gt;0,AIC!P15,"")</f>
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <f>IF(AIC!Q15&gt;0,AIC!Q15,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A7" t="str">
+        <f>IF(AIC!B19&gt;0,AIC!B19,"")</f>
+        <v>OUTSOURCE</v>
+      </c>
+      <c r="B7" t="str">
+        <f>IF(AIC!C19&gt;0,AIC!C19,"")</f>
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <f>IF(AIC!D19&gt;0,AIC!D19,"")</f>
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <f>IF(AIC!E19&gt;0,AIC!E19,"")</f>
+        <v/>
+      </c>
+      <c r="E7" t="str">
+        <f>IF(AIC!F19&gt;0,AIC!F19,"")</f>
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <f>IF(AIC!G19&gt;0,AIC!G19,"")</f>
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <f>IF(AIC!H19&gt;0,AIC!H19,"")</f>
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <f>IF(AIC!I19&gt;0,AIC!I19,"")</f>
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <f>IF(AIC!J19&gt;0,AIC!J19,"")</f>
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <f>IF(AIC!K19&gt;0,AIC!K19,"")</f>
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <f>IF(AIC!L19&gt;0,AIC!L19,"")</f>
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <f>IF(AIC!M19&gt;0,AIC!M19,"")</f>
+        <v/>
+      </c>
+      <c r="M7" t="str">
+        <f>IF(AIC!N19&gt;0,AIC!N19,"")</f>
+        <v/>
+      </c>
+      <c r="N7" t="str">
+        <f>IF(AIC!O19&gt;0,AIC!O19,"")</f>
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <f>IF(AIC!P19&gt;0,AIC!P19,"")</f>
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <f>IF(AIC!Q19&gt;0,AIC!Q19,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B11" t="str">
+        <f>IF(AIC!C1&gt;0,AIC!C1,"")</f>
+        <v>JAN</v>
+      </c>
+      <c r="C11" t="str">
+        <f>IF(AIC!D1&gt;0,AIC!D1,"")</f>
+        <v>FEB</v>
+      </c>
+      <c r="D11" t="str">
+        <f>IF(AIC!E1&gt;0,AIC!E1,"")</f>
+        <v>MAR</v>
+      </c>
+      <c r="E11" t="str">
+        <f>IF(AIC!F1&gt;0,AIC!F1,"")</f>
+        <v>APR</v>
+      </c>
+      <c r="F11" t="str">
+        <f>IF(AIC!G1&gt;0,AIC!G1,"")</f>
+        <v>MAY</v>
+      </c>
+      <c r="G11" t="str">
+        <f>IF(AIC!H1&gt;0,AIC!H1,"")</f>
+        <v>JUN</v>
+      </c>
+      <c r="H11" t="str">
+        <f>IF(AIC!I1&gt;0,AIC!I1,"")</f>
+        <v>JUL</v>
+      </c>
+      <c r="I11" t="str">
+        <f>IF(AIC!J1&gt;0,AIC!J1,"")</f>
+        <v>AUG</v>
+      </c>
+      <c r="J11" t="str">
+        <f>IF(AIC!K1&gt;0,AIC!K1,"")</f>
+        <v>SEP</v>
+      </c>
+      <c r="K11" t="str">
+        <f>IF(AIC!L1&gt;0,AIC!L1,"")</f>
+        <v>OCT</v>
+      </c>
+      <c r="L11" t="str">
+        <f>IF(AIC!M1&gt;0,AIC!M1,"")</f>
+        <v>NOV</v>
+      </c>
+      <c r="M11" t="str">
+        <f>IF(AIC!N1&gt;0,AIC!N1,"")</f>
+        <v>DEC</v>
+      </c>
+      <c r="N11" t="str">
+        <f>IF(AIC!O1&gt;0,AIC!O1,"")</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O11" t="str">
+        <f>IF(AIC!P1&gt;0,AIC!P1,"")</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P11" t="str">
+        <f>IF(AIC!Q1&gt;0,AIC!Q1,"")</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A12" t="str">
+        <f>IF(AIC!A9&gt;0,AIC!A9,"")</f>
+        <v>Staff</v>
+      </c>
+      <c r="B12">
+        <f>IF(AIC!C9&gt;0,AIC!C9,"")</f>
+        <v>24</v>
+      </c>
+      <c r="C12">
+        <f>IF(AIC!D9&gt;0,AIC!D9,"")</f>
+        <v>23</v>
+      </c>
+      <c r="D12">
+        <f>IF(AIC!E9&gt;0,AIC!E9,"")</f>
+        <v>22</v>
+      </c>
+      <c r="E12">
+        <f>IF(AIC!F9&gt;0,AIC!F9,"")</f>
+        <v>21</v>
+      </c>
+      <c r="F12">
+        <f>IF(AIC!G9&gt;0,AIC!G9,"")</f>
+        <v>20</v>
+      </c>
+      <c r="G12">
+        <f>IF(AIC!H9&gt;0,AIC!H9,"")</f>
+        <v>20</v>
+      </c>
+      <c r="H12">
+        <f>IF(AIC!I9&gt;0,AIC!I9,"")</f>
+        <v>19</v>
+      </c>
+      <c r="I12">
+        <f>IF(AIC!J9&gt;0,AIC!J9,"")</f>
+        <v>19</v>
+      </c>
+      <c r="J12">
+        <f>IF(AIC!K9&gt;0,AIC!K9,"")</f>
+        <v>19</v>
+      </c>
+      <c r="K12">
+        <f>IF(AIC!L9&gt;0,AIC!L9,"")</f>
+        <v>19</v>
+      </c>
+      <c r="L12">
+        <f>IF(AIC!M9&gt;0,AIC!M9,"")</f>
+        <v>19</v>
+      </c>
+      <c r="M12">
+        <f>IF(AIC!N9&gt;0,AIC!N9,"")</f>
+        <v>19</v>
+      </c>
+      <c r="N12">
+        <f>IF(AIC!O9&gt;0,AIC!O9,"")</f>
+        <v>19</v>
+      </c>
+      <c r="O12">
+        <f>IF(AIC!P9&gt;0,AIC!P9,"")</f>
+        <v>19</v>
+      </c>
+      <c r="P12">
+        <f>IF(AIC!Q9&gt;0,AIC!Q9,"")</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A13" t="str">
+        <f>IF(AIC!A10&gt;0,AIC!A10,"")</f>
+        <v>Staff AVG</v>
+      </c>
+      <c r="B13">
+        <f>IF(AIC!C10&gt;0,AIC!C10,"")</f>
+        <v>20</v>
+      </c>
+      <c r="C13">
+        <f>IF(AIC!D10&gt;0,AIC!D10,"")</f>
+        <v>20</v>
+      </c>
+      <c r="D13">
+        <f>IF(AIC!E10&gt;0,AIC!E10,"")</f>
+        <v>20</v>
+      </c>
+      <c r="E13">
+        <f>IF(AIC!F10&gt;0,AIC!F10,"")</f>
+        <v>19</v>
+      </c>
+      <c r="F13">
+        <f>IF(AIC!G10&gt;0,AIC!G10,"")</f>
+        <v>19</v>
+      </c>
+      <c r="G13">
+        <f>IF(AIC!H10&gt;0,AIC!H10,"")</f>
+        <v>19</v>
+      </c>
+      <c r="H13">
+        <f>IF(AIC!I10&gt;0,AIC!I10,"")</f>
+        <v>19</v>
+      </c>
+      <c r="I13">
+        <f>IF(AIC!J10&gt;0,AIC!J10,"")</f>
+        <v>19</v>
+      </c>
+      <c r="J13">
+        <f>IF(AIC!K10&gt;0,AIC!K10,"")</f>
+        <v>19</v>
+      </c>
+      <c r="K13">
+        <f>IF(AIC!L10&gt;0,AIC!L10,"")</f>
+        <v>19</v>
+      </c>
+      <c r="L13">
+        <f>IF(AIC!M10&gt;0,AIC!M10,"")</f>
+        <v>19</v>
+      </c>
+      <c r="M13">
+        <f>IF(AIC!N10&gt;0,AIC!N10,"")</f>
+        <v>19</v>
+      </c>
+      <c r="N13">
+        <f>IF(AIC!O10&gt;0,AIC!O10,"")</f>
+        <v>19</v>
+      </c>
+      <c r="O13">
+        <f>IF(AIC!P10&gt;0,AIC!P10,"")</f>
+        <v>19</v>
+      </c>
+      <c r="P13">
+        <f>IF(AIC!Q10&gt;0,AIC!Q10,"")</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A14" t="str">
+        <f>IF(AIC!A11&gt;0,AIC!A11,"")</f>
+        <v>Plan</v>
+      </c>
+      <c r="B14">
+        <f>IF(AIC!C11&gt;0,AIC!C11,"")</f>
+        <v>16</v>
+      </c>
+      <c r="C14">
+        <f>IF(AIC!D11&gt;0,AIC!D11,"")</f>
+        <v>17</v>
+      </c>
+      <c r="D14">
+        <f>IF(AIC!E11&gt;0,AIC!E11,"")</f>
+        <v>16</v>
+      </c>
+      <c r="E14">
+        <f>IF(AIC!F11&gt;0,AIC!F11,"")</f>
+        <v>19</v>
+      </c>
+      <c r="F14">
+        <f>IF(AIC!G11&gt;0,AIC!G11,"")</f>
+        <v>18</v>
+      </c>
+      <c r="G14">
+        <f>IF(AIC!H11&gt;0,AIC!H11,"")</f>
+        <v>18</v>
+      </c>
+      <c r="H14">
+        <f>IF(AIC!I11&gt;0,AIC!I11,"")</f>
+        <v>16</v>
+      </c>
+      <c r="I14">
+        <f>IF(AIC!J11&gt;0,AIC!J11,"")</f>
+        <v>15</v>
+      </c>
+      <c r="J14">
+        <f>IF(AIC!K11&gt;0,AIC!K11,"")</f>
+        <v>14</v>
+      </c>
+      <c r="K14">
+        <f>IF(AIC!L11&gt;0,AIC!L11,"")</f>
+        <v>14</v>
+      </c>
+      <c r="L14">
+        <f>IF(AIC!M11&gt;0,AIC!M11,"")</f>
+        <v>14</v>
+      </c>
+      <c r="M14">
+        <f>IF(AIC!N11&gt;0,AIC!N11,"")</f>
+        <v>13</v>
+      </c>
+      <c r="N14">
+        <f>IF(AIC!O11&gt;0,AIC!O11,"")</f>
+        <v>8</v>
+      </c>
+      <c r="O14">
+        <f>IF(AIC!P11&gt;0,AIC!P11,"")</f>
+        <v>8</v>
+      </c>
+      <c r="P14">
+        <f>IF(AIC!Q11&gt;0,AIC!Q11,"")</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B21" t="str">
+        <f>IF(AIC!C1&gt;0,AIC!C1,"")</f>
+        <v>JAN</v>
+      </c>
+      <c r="C21" t="str">
+        <f>IF(AIC!D1&gt;0,AIC!D1,"")</f>
+        <v>FEB</v>
+      </c>
+      <c r="D21" t="str">
+        <f>IF(AIC!E1&gt;0,AIC!E1,"")</f>
+        <v>MAR</v>
+      </c>
+      <c r="E21" t="str">
+        <f>IF(AIC!F1&gt;0,AIC!F1,"")</f>
+        <v>APR</v>
+      </c>
+      <c r="F21" t="str">
+        <f>IF(AIC!G1&gt;0,AIC!G1,"")</f>
+        <v>MAY</v>
+      </c>
+      <c r="G21" t="str">
+        <f>IF(AIC!H1&gt;0,AIC!H1,"")</f>
+        <v>JUN</v>
+      </c>
+      <c r="H21" t="str">
+        <f>IF(AIC!I1&gt;0,AIC!I1,"")</f>
+        <v>JUL</v>
+      </c>
+      <c r="I21" t="str">
+        <f>IF(AIC!J1&gt;0,AIC!J1,"")</f>
+        <v>AUG</v>
+      </c>
+      <c r="J21" t="str">
+        <f>IF(AIC!K1&gt;0,AIC!K1,"")</f>
+        <v>SEP</v>
+      </c>
+      <c r="K21" t="str">
+        <f>IF(AIC!L1&gt;0,AIC!L1,"")</f>
+        <v>OCT</v>
+      </c>
+      <c r="L21" t="str">
+        <f>IF(AIC!M1&gt;0,AIC!M1,"")</f>
+        <v>NOV</v>
+      </c>
+      <c r="M21" t="str">
+        <f>IF(AIC!N1&gt;0,AIC!N1,"")</f>
+        <v>DEC</v>
+      </c>
+      <c r="N21" t="str">
+        <f>IF(AIC!O1&gt;0,AIC!O1,"")</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O21" t="str">
+        <f>IF(AIC!P1&gt;0,AIC!P1,"")</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P21" t="str">
+        <f>IF(AIC!Q1&gt;0,AIC!Q1,"")</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A22" t="str">
+        <f>IF(AIC!A13&gt;0,AIC!A13,"")</f>
+        <v>Grand Total</v>
+      </c>
+      <c r="B22" t="str">
+        <f>IF(AIC!C13&gt;0,AIC!C13,"")</f>
+        <v/>
+      </c>
+      <c r="C22" t="str">
+        <f>IF(AIC!D13&gt;0,AIC!D13,"")</f>
+        <v/>
+      </c>
+      <c r="D22" t="str">
+        <f>IF(AIC!E13&gt;0,AIC!E13,"")</f>
+        <v/>
+      </c>
+      <c r="E22" t="str">
+        <f>IF(AIC!F13&gt;0,AIC!F13,"")</f>
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <f>IF(AIC!G13&gt;0,AIC!G13,"")</f>
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <f>IF(AIC!H13&gt;0,AIC!H13,"")</f>
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <f>IF(AIC!I13&gt;0,AIC!I13,"")</f>
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <f>IF(AIC!J13&gt;0,AIC!J13,"")</f>
+        <v/>
+      </c>
+      <c r="J22" t="str">
+        <f>IF(AIC!K13&gt;0,AIC!K13,"")</f>
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <f>IF(AIC!L13&gt;0,AIC!L13,"")</f>
+        <v/>
+      </c>
+      <c r="L22" t="str">
+        <f>IF(AIC!M13&gt;0,AIC!M13,"")</f>
+        <v/>
+      </c>
+      <c r="M22" t="str">
+        <f>IF(AIC!N13&gt;0,AIC!N13,"")</f>
+        <v/>
+      </c>
+      <c r="N22" t="str">
+        <f>IF(AIC!O13&gt;0,AIC!O13,"")</f>
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <f>IF(AIC!P13&gt;0,AIC!P13,"")</f>
+        <v/>
+      </c>
+      <c r="P22" t="str">
+        <f>IF(AIC!Q13&gt;0,AIC!Q13,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A23" t="str">
+        <f>IF(AIC!A14&gt;0,AIC!A14,"")</f>
+        <v>Staff AVG</v>
+      </c>
+      <c r="B23" t="str">
+        <f>IF(AIC!C14&gt;0,AIC!C14,"")</f>
+        <v/>
+      </c>
+      <c r="C23" t="str">
+        <f>IF(AIC!D14&gt;0,AIC!D14,"")</f>
+        <v/>
+      </c>
+      <c r="D23" t="str">
+        <f>IF(AIC!E14&gt;0,AIC!E14,"")</f>
+        <v/>
+      </c>
+      <c r="E23" t="str">
+        <f>IF(AIC!F14&gt;0,AIC!F14,"")</f>
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <f>IF(AIC!G14&gt;0,AIC!G14,"")</f>
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <f>IF(AIC!H14&gt;0,AIC!H14,"")</f>
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <f>IF(AIC!I14&gt;0,AIC!I14,"")</f>
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <f>IF(AIC!J14&gt;0,AIC!J14,"")</f>
+        <v/>
+      </c>
+      <c r="J23" t="str">
+        <f>IF(AIC!K14&gt;0,AIC!K14,"")</f>
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <f>IF(AIC!L14&gt;0,AIC!L14,"")</f>
+        <v/>
+      </c>
+      <c r="L23" t="str">
+        <f>IF(AIC!M14&gt;0,AIC!M14,"")</f>
+        <v/>
+      </c>
+      <c r="M23" t="str">
+        <f>IF(AIC!N14&gt;0,AIC!N14,"")</f>
+        <v/>
+      </c>
+      <c r="N23" t="str">
+        <f>IF(AIC!O14&gt;0,AIC!O14,"")</f>
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <f>IF(AIC!P14&gt;0,AIC!P14,"")</f>
+        <v/>
+      </c>
+      <c r="P23" t="str">
+        <f>IF(AIC!Q14&gt;0,AIC!Q14,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A24" t="str">
+        <f>IF(AIC!A15&gt;0,AIC!A15,"")</f>
+        <v/>
+      </c>
+      <c r="B24" t="str">
+        <f>IF(AIC!C15&gt;0,AIC!C15,"")</f>
+        <v/>
+      </c>
+      <c r="C24" t="str">
+        <f>IF(AIC!D15&gt;0,AIC!D15,"")</f>
+        <v/>
+      </c>
+      <c r="D24" t="str">
+        <f>IF(AIC!E15&gt;0,AIC!E15,"")</f>
+        <v/>
+      </c>
+      <c r="E24" t="str">
+        <f>IF(AIC!F15&gt;0,AIC!F15,"")</f>
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <f>IF(AIC!G15&gt;0,AIC!G15,"")</f>
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <f>IF(AIC!H15&gt;0,AIC!H15,"")</f>
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <f>IF(AIC!I15&gt;0,AIC!I15,"")</f>
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <f>IF(AIC!J15&gt;0,AIC!J15,"")</f>
+        <v/>
+      </c>
+      <c r="J24" t="str">
+        <f>IF(AIC!K15&gt;0,AIC!K15,"")</f>
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <f>IF(AIC!L15&gt;0,AIC!L15,"")</f>
+        <v/>
+      </c>
+      <c r="L24" t="str">
+        <f>IF(AIC!M15&gt;0,AIC!M15,"")</f>
+        <v/>
+      </c>
+      <c r="M24" t="str">
+        <f>IF(AIC!N15&gt;0,AIC!N15,"")</f>
+        <v/>
+      </c>
+      <c r="N24" t="str">
+        <f>IF(AIC!O15&gt;0,AIC!O15,"")</f>
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <f>IF(AIC!P15&gt;0,AIC!P15,"")</f>
+        <v/>
+      </c>
+      <c r="P24" t="str">
+        <f>IF(AIC!Q15&gt;0,AIC!Q15,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B31" t="str">
+        <f>IF(AIC!C1&gt;0,AIC!C1,"")</f>
+        <v>JAN</v>
+      </c>
+      <c r="C31" t="str">
+        <f>IF(AIC!D1&gt;0,AIC!D1,"")</f>
+        <v>FEB</v>
+      </c>
+      <c r="D31" t="str">
+        <f>IF(AIC!E1&gt;0,AIC!E1,"")</f>
+        <v>MAR</v>
+      </c>
+      <c r="E31" t="str">
+        <f>IF(AIC!F1&gt;0,AIC!F1,"")</f>
+        <v>APR</v>
+      </c>
+      <c r="F31" t="str">
+        <f>IF(AIC!G1&gt;0,AIC!G1,"")</f>
+        <v>MAY</v>
+      </c>
+      <c r="G31" t="str">
+        <f>IF(AIC!H1&gt;0,AIC!H1,"")</f>
+        <v>JUN</v>
+      </c>
+      <c r="H31" t="str">
+        <f>IF(AIC!I1&gt;0,AIC!I1,"")</f>
+        <v>JUL</v>
+      </c>
+      <c r="I31" t="str">
+        <f>IF(AIC!J1&gt;0,AIC!J1,"")</f>
+        <v>AUG</v>
+      </c>
+      <c r="J31" t="str">
+        <f>IF(AIC!K1&gt;0,AIC!K1,"")</f>
+        <v>SEP</v>
+      </c>
+      <c r="K31" t="str">
+        <f>IF(AIC!L1&gt;0,AIC!L1,"")</f>
+        <v>OCT</v>
+      </c>
+      <c r="L31" t="str">
+        <f>IF(AIC!M1&gt;0,AIC!M1,"")</f>
+        <v>NOV</v>
+      </c>
+      <c r="M31" t="str">
+        <f>IF(AIC!N1&gt;0,AIC!N1,"")</f>
+        <v>DEC</v>
+      </c>
+      <c r="N31" t="str">
+        <f>IF(AIC!O1&gt;0,AIC!O1,"")</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O31" t="str">
+        <f>IF(AIC!P1&gt;0,AIC!P1,"")</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P31" t="str">
+        <f>IF(AIC!Q1&gt;0,AIC!Q1,"")</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A32" t="str">
+        <f>IF(AIC!A17&gt;0,AIC!A17,"")</f>
+        <v>Grand Total</v>
+      </c>
+      <c r="B32" t="str">
+        <f>IF(AIC!C17&gt;0,AIC!C17,"")</f>
+        <v/>
+      </c>
+      <c r="C32" t="str">
+        <f>IF(AIC!D17&gt;0,AIC!D17,"")</f>
+        <v/>
+      </c>
+      <c r="D32" t="str">
+        <f>IF(AIC!E17&gt;0,AIC!E17,"")</f>
+        <v/>
+      </c>
+      <c r="E32" t="str">
+        <f>IF(AIC!F17&gt;0,AIC!F17,"")</f>
+        <v/>
+      </c>
+      <c r="F32" t="str">
+        <f>IF(AIC!G17&gt;0,AIC!G17,"")</f>
+        <v/>
+      </c>
+      <c r="G32" t="str">
+        <f>IF(AIC!H17&gt;0,AIC!H17,"")</f>
+        <v/>
+      </c>
+      <c r="H32" t="str">
+        <f>IF(AIC!I17&gt;0,AIC!I17,"")</f>
+        <v/>
+      </c>
+      <c r="I32" t="str">
+        <f>IF(AIC!J17&gt;0,AIC!J17,"")</f>
+        <v/>
+      </c>
+      <c r="J32" t="str">
+        <f>IF(AIC!K17&gt;0,AIC!K17,"")</f>
+        <v/>
+      </c>
+      <c r="K32" t="str">
+        <f>IF(AIC!L17&gt;0,AIC!L17,"")</f>
+        <v/>
+      </c>
+      <c r="L32" t="str">
+        <f>IF(AIC!M17&gt;0,AIC!M17,"")</f>
+        <v/>
+      </c>
+      <c r="M32" t="str">
+        <f>IF(AIC!N17&gt;0,AIC!N17,"")</f>
+        <v/>
+      </c>
+      <c r="N32" t="str">
+        <f>IF(AIC!O17&gt;0,AIC!O17,"")</f>
+        <v/>
+      </c>
+      <c r="O32" t="str">
+        <f>IF(AIC!P17&gt;0,AIC!P17,"")</f>
+        <v/>
+      </c>
+      <c r="P32" t="str">
+        <f>IF(AIC!Q17&gt;0,AIC!Q17,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A33" t="str">
+        <f>IF(AIC!A18&gt;0,AIC!A18,"")</f>
+        <v>Staff AVG</v>
+      </c>
+      <c r="B33" t="str">
+        <f>IF(AIC!C18&gt;0,AIC!C18,"")</f>
+        <v/>
+      </c>
+      <c r="C33" t="str">
+        <f>IF(AIC!D18&gt;0,AIC!D18,"")</f>
+        <v/>
+      </c>
+      <c r="D33" t="str">
+        <f>IF(AIC!E18&gt;0,AIC!E18,"")</f>
+        <v/>
+      </c>
+      <c r="E33" t="str">
+        <f>IF(AIC!F18&gt;0,AIC!F18,"")</f>
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <f>IF(AIC!G18&gt;0,AIC!G18,"")</f>
+        <v/>
+      </c>
+      <c r="G33" t="str">
+        <f>IF(AIC!H18&gt;0,AIC!H18,"")</f>
+        <v/>
+      </c>
+      <c r="H33" t="str">
+        <f>IF(AIC!I18&gt;0,AIC!I18,"")</f>
+        <v/>
+      </c>
+      <c r="I33" t="str">
+        <f>IF(AIC!J18&gt;0,AIC!J18,"")</f>
+        <v/>
+      </c>
+      <c r="J33" t="str">
+        <f>IF(AIC!K18&gt;0,AIC!K18,"")</f>
+        <v/>
+      </c>
+      <c r="K33" t="str">
+        <f>IF(AIC!L18&gt;0,AIC!L18,"")</f>
+        <v/>
+      </c>
+      <c r="L33" t="str">
+        <f>IF(AIC!M18&gt;0,AIC!M18,"")</f>
+        <v/>
+      </c>
+      <c r="M33" t="str">
+        <f>IF(AIC!N18&gt;0,AIC!N18,"")</f>
+        <v/>
+      </c>
+      <c r="N33" t="str">
+        <f>IF(AIC!O18&gt;0,AIC!O18,"")</f>
+        <v/>
+      </c>
+      <c r="O33" t="str">
+        <f>IF(AIC!P18&gt;0,AIC!P18,"")</f>
+        <v/>
+      </c>
+      <c r="P33" t="str">
+        <f>IF(AIC!Q18&gt;0,AIC!Q18,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A34" t="str">
+        <f>IF(AIC!A19&gt;0,AIC!A19,"")</f>
+        <v/>
+      </c>
+      <c r="B34" t="str">
+        <f>IF(AIC!C19&gt;0,AIC!C19,"")</f>
+        <v/>
+      </c>
+      <c r="C34" t="str">
+        <f>IF(AIC!D19&gt;0,AIC!D19,"")</f>
+        <v/>
+      </c>
+      <c r="D34" t="str">
+        <f>IF(AIC!E19&gt;0,AIC!E19,"")</f>
+        <v/>
+      </c>
+      <c r="E34" t="str">
+        <f>IF(AIC!F19&gt;0,AIC!F19,"")</f>
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <f>IF(AIC!G19&gt;0,AIC!G19,"")</f>
+        <v/>
+      </c>
+      <c r="G34" t="str">
+        <f>IF(AIC!H19&gt;0,AIC!H19,"")</f>
+        <v/>
+      </c>
+      <c r="H34" t="str">
+        <f>IF(AIC!I19&gt;0,AIC!I19,"")</f>
+        <v/>
+      </c>
+      <c r="I34" t="str">
+        <f>IF(AIC!J19&gt;0,AIC!J19,"")</f>
+        <v/>
+      </c>
+      <c r="J34" t="str">
+        <f>IF(AIC!K19&gt;0,AIC!K19,"")</f>
+        <v/>
+      </c>
+      <c r="K34" t="str">
+        <f>IF(AIC!L19&gt;0,AIC!L19,"")</f>
+        <v/>
+      </c>
+      <c r="L34" t="str">
+        <f>IF(AIC!M19&gt;0,AIC!M19,"")</f>
+        <v/>
+      </c>
+      <c r="M34" t="str">
+        <f>IF(AIC!N19&gt;0,AIC!N19,"")</f>
+        <v/>
+      </c>
+      <c r="N34" t="str">
+        <f>IF(AIC!O19&gt;0,AIC!O19,"")</f>
+        <v/>
+      </c>
+      <c r="O34" t="str">
+        <f>IF(AIC!P19&gt;0,AIC!P19,"")</f>
+        <v/>
+      </c>
+      <c r="P34" t="str">
+        <f>IF(AIC!Q19&gt;0,AIC!Q19,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B41" t="str">
+        <f>IF(AIC!C31&gt;0,AIC!C31,"")</f>
+        <v>Q1</v>
+      </c>
+      <c r="C41" t="str">
+        <f>IF(AIC!D31&gt;0,AIC!D31,"")</f>
+        <v>Q2</v>
+      </c>
+      <c r="D41" t="str">
+        <f>IF(AIC!E31&gt;0,AIC!E31,"")</f>
+        <v>Q3</v>
+      </c>
+      <c r="E41" t="str">
+        <f>IF(AIC!F31&gt;0,AIC!F31,"")</f>
+        <v>Q4</v>
+      </c>
+      <c r="F41" t="str">
+        <f>IF(AIC!G31&gt;0,AIC!G31,"")</f>
+        <v>Q1'27</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A42" t="str">
+        <f>IF(AIC!B32&gt;0,AIC!B32,"")</f>
+        <v>Staff</v>
+      </c>
+      <c r="B42">
+        <f>IF(AIC!C32&gt;0,AIC!C32,"")</f>
+        <v>23</v>
+      </c>
+      <c r="C42">
+        <f>IF(AIC!D32&gt;0,AIC!D32,"")</f>
+        <v>20</v>
+      </c>
+      <c r="D42">
+        <f>IF(AIC!E32&gt;0,AIC!E32,"")</f>
+        <v>19</v>
+      </c>
+      <c r="E42">
+        <f>IF(AIC!F32&gt;0,AIC!F32,"")</f>
+        <v>19</v>
+      </c>
+      <c r="F42">
+        <f>IF(AIC!G32&gt;0,AIC!G32,"")</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A43" t="str">
+        <f>IF(AIC!B33&gt;0,AIC!B33,"")</f>
+        <v>Staff AVG</v>
+      </c>
+      <c r="B43">
+        <f>IF(AIC!C33&gt;0,AIC!C33,"")</f>
+        <v>20</v>
+      </c>
+      <c r="C43">
+        <f>IF(AIC!D33&gt;0,AIC!D33,"")</f>
+        <v>19</v>
+      </c>
+      <c r="D43">
+        <f>IF(AIC!E33&gt;0,AIC!E33,"")</f>
+        <v>19</v>
+      </c>
+      <c r="E43">
+        <f>IF(AIC!F33&gt;0,AIC!F33,"")</f>
+        <v>19</v>
+      </c>
+      <c r="F43">
+        <f>IF(AIC!G33&gt;0,AIC!G33,"")</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A44" t="str">
+        <f>IF(AIC!B34&gt;0,AIC!B34,"")</f>
+        <v>Plan</v>
+      </c>
+      <c r="B44">
+        <f>IF(AIC!C34&gt;0,AIC!C34,"")</f>
+        <v>17</v>
+      </c>
+      <c r="C44">
+        <f>IF(AIC!D34&gt;0,AIC!D34,"")</f>
+        <v>18</v>
+      </c>
+      <c r="D44">
+        <f>IF(AIC!E34&gt;0,AIC!E34,"")</f>
+        <v>15</v>
+      </c>
+      <c r="E44">
+        <f>IF(AIC!F34&gt;0,AIC!F34,"")</f>
+        <v>14</v>
+      </c>
+      <c r="F44">
+        <f>IF(AIC!G34&gt;0,AIC!G34,"")</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A45" t="str">
+        <f>IF(AIC!B41&gt;0,AIC!B41,"")</f>
+        <v>PAYROLL</v>
+      </c>
+      <c r="B45">
+        <f>IF(AIC!C41&gt;0,AIC!C41,"")</f>
+        <v>17</v>
+      </c>
+      <c r="C45">
+        <f>IF(AIC!D41&gt;0,AIC!D41,"")</f>
+        <v>18</v>
+      </c>
+      <c r="D45">
+        <f>IF(AIC!E41&gt;0,AIC!E41,"")</f>
+        <v>15</v>
+      </c>
+      <c r="E45">
+        <f>IF(AIC!F41&gt;0,AIC!F41,"")</f>
+        <v>14</v>
+      </c>
+      <c r="F45">
+        <f>IF(AIC!G41&gt;0,AIC!G41,"")</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A46" t="str">
+        <f>IF(AIC!B45&gt;0,AIC!B45,"")</f>
+        <v>CONTRACTOR</v>
+      </c>
+      <c r="B46" t="str">
+        <f>IF(AIC!C45&gt;0,AIC!C45,"")</f>
+        <v/>
+      </c>
+      <c r="C46" t="str">
+        <f>IF(AIC!D45&gt;0,AIC!D45,"")</f>
+        <v/>
+      </c>
+      <c r="D46" t="str">
+        <f>IF(AIC!E45&gt;0,AIC!E45,"")</f>
+        <v/>
+      </c>
+      <c r="E46" t="str">
+        <f>IF(AIC!F45&gt;0,AIC!F45,"")</f>
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <f>IF(AIC!G45&gt;0,AIC!G45,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A47" t="str">
+        <f>IF(AIC!B49&gt;0,AIC!B49,"")</f>
+        <v>OUTSOURCE</v>
+      </c>
+      <c r="B47" t="str">
+        <f>IF(AIC!C49&gt;0,AIC!C49,"")</f>
+        <v/>
+      </c>
+      <c r="C47" t="str">
+        <f>IF(AIC!D49&gt;0,AIC!D49,"")</f>
+        <v/>
+      </c>
+      <c r="D47" t="str">
+        <f>IF(AIC!E49&gt;0,AIC!E49,"")</f>
+        <v/>
+      </c>
+      <c r="E47" t="str">
+        <f>IF(AIC!F49&gt;0,AIC!F49,"")</f>
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <f>IF(AIC!G49&gt;0,AIC!G49,"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D240BEDF-2DC8-5B43-A028-CE573B9B779F}">
+  <sheetPr>
+    <tabColor theme="4" tint="0.79998168889431442"/>
+  </sheetPr>
   <dimension ref="A1:P47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -3405,6 +4859,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{594D1181-445D-3746-9BD8-A2C1C6213A7C}">
+  <sheetPr>
+    <tabColor theme="5"/>
+  </sheetPr>
   <dimension ref="A1:Q49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
@@ -4665,6 +6122,9 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FB985D5-E47B-3A4D-A324-92EE24F74B47}">
+  <sheetPr>
+    <tabColor theme="5" tint="0.79998168889431442"/>
+  </sheetPr>
   <dimension ref="A1:P47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -6090,4 +7550,6657 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{556F0F82-0DFA-1E4B-A728-96791579F303}">
+  <sheetPr>
+    <tabColor theme="7"/>
+  </sheetPr>
+  <dimension ref="A1:Q49"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1" s="17"/>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A2" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="8">
+        <v>45</v>
+      </c>
+      <c r="D2" s="8">
+        <v>45</v>
+      </c>
+      <c r="E2" s="8">
+        <v>45</v>
+      </c>
+      <c r="F2" s="8">
+        <v>48</v>
+      </c>
+      <c r="G2" s="8">
+        <v>48</v>
+      </c>
+      <c r="H2" s="8">
+        <v>48</v>
+      </c>
+      <c r="I2" s="8">
+        <v>48</v>
+      </c>
+      <c r="J2" s="8">
+        <v>48</v>
+      </c>
+      <c r="K2" s="8">
+        <v>48</v>
+      </c>
+      <c r="L2" s="8">
+        <v>48</v>
+      </c>
+      <c r="M2" s="8">
+        <v>48</v>
+      </c>
+      <c r="N2" s="8">
+        <v>48</v>
+      </c>
+      <c r="O2" s="8">
+        <v>48</v>
+      </c>
+      <c r="P2" s="8">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="8">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A3" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="8">
+        <v>47</v>
+      </c>
+      <c r="D3" s="8">
+        <v>47</v>
+      </c>
+      <c r="E3" s="8">
+        <v>47</v>
+      </c>
+      <c r="F3" s="8">
+        <v>48</v>
+      </c>
+      <c r="G3" s="8">
+        <v>48</v>
+      </c>
+      <c r="H3" s="8">
+        <v>48</v>
+      </c>
+      <c r="I3" s="8">
+        <v>48</v>
+      </c>
+      <c r="J3" s="8">
+        <v>48</v>
+      </c>
+      <c r="K3" s="8">
+        <v>48</v>
+      </c>
+      <c r="L3" s="8">
+        <v>48</v>
+      </c>
+      <c r="M3" s="8">
+        <v>48</v>
+      </c>
+      <c r="N3" s="8">
+        <v>48</v>
+      </c>
+      <c r="O3" s="8">
+        <v>48</v>
+      </c>
+      <c r="P3" s="8">
+        <v>48</v>
+      </c>
+      <c r="Q3" s="8">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A4" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="8">
+        <v>40</v>
+      </c>
+      <c r="D4" s="8">
+        <v>42</v>
+      </c>
+      <c r="E4" s="8">
+        <v>44</v>
+      </c>
+      <c r="F4" s="8">
+        <v>45</v>
+      </c>
+      <c r="G4" s="8">
+        <v>47</v>
+      </c>
+      <c r="H4" s="8">
+        <v>44</v>
+      </c>
+      <c r="I4" s="8">
+        <v>45</v>
+      </c>
+      <c r="J4" s="8">
+        <v>45</v>
+      </c>
+      <c r="K4" s="8">
+        <v>45</v>
+      </c>
+      <c r="L4" s="8">
+        <v>42</v>
+      </c>
+      <c r="M4" s="8">
+        <v>41</v>
+      </c>
+      <c r="N4" s="8">
+        <v>41</v>
+      </c>
+      <c r="O4" s="8">
+        <v>32</v>
+      </c>
+      <c r="P4" s="8">
+        <v>32</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A5" s="17"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
+      <c r="Q5" s="8"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A6" s="8"/>
+      <c r="B6" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="19">
+        <v>0.89780000000000004</v>
+      </c>
+      <c r="D6" s="19">
+        <v>0.94130000000000003</v>
+      </c>
+      <c r="E6" s="19">
+        <v>0.98819999999999997</v>
+      </c>
+      <c r="F6" s="19">
+        <v>0.94650000000000001</v>
+      </c>
+      <c r="G6" s="19">
+        <v>0.97460000000000002</v>
+      </c>
+      <c r="H6" s="19">
+        <v>0.91479999999999995</v>
+      </c>
+      <c r="I6" s="19">
+        <v>0.93979999999999997</v>
+      </c>
+      <c r="J6" s="19">
+        <v>0.92830000000000001</v>
+      </c>
+      <c r="K6" s="19">
+        <v>0.93879999999999997</v>
+      </c>
+      <c r="L6" s="19">
+        <v>0.86850000000000005</v>
+      </c>
+      <c r="M6" s="19">
+        <v>0.85419999999999996</v>
+      </c>
+      <c r="N6" s="19">
+        <v>0.85419999999999996</v>
+      </c>
+      <c r="O6" s="19">
+        <v>0.65939999999999999</v>
+      </c>
+      <c r="P6" s="19">
+        <v>0.65939999999999999</v>
+      </c>
+      <c r="Q6" s="19">
+        <v>0.65939999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A7" s="17"/>
+      <c r="B7" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="20">
+        <v>5</v>
+      </c>
+      <c r="D7" s="20">
+        <v>3</v>
+      </c>
+      <c r="E7" s="20">
+        <v>1</v>
+      </c>
+      <c r="F7" s="20">
+        <v>3</v>
+      </c>
+      <c r="G7" s="20">
+        <v>1</v>
+      </c>
+      <c r="H7" s="20">
+        <v>4</v>
+      </c>
+      <c r="I7" s="20">
+        <v>3</v>
+      </c>
+      <c r="J7" s="20">
+        <v>3</v>
+      </c>
+      <c r="K7" s="20">
+        <v>3</v>
+      </c>
+      <c r="L7" s="20">
+        <v>6</v>
+      </c>
+      <c r="M7" s="20">
+        <v>7</v>
+      </c>
+      <c r="N7" s="20">
+        <v>7</v>
+      </c>
+      <c r="O7" s="20">
+        <v>16</v>
+      </c>
+      <c r="P7" s="20">
+        <v>16</v>
+      </c>
+      <c r="Q7" s="20">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A8" s="17"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A9" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="8">
+        <v>28</v>
+      </c>
+      <c r="D9" s="8">
+        <v>28</v>
+      </c>
+      <c r="E9" s="8">
+        <v>27</v>
+      </c>
+      <c r="F9" s="8">
+        <v>28</v>
+      </c>
+      <c r="G9" s="8">
+        <v>28</v>
+      </c>
+      <c r="H9" s="8">
+        <v>28</v>
+      </c>
+      <c r="I9" s="8">
+        <v>28</v>
+      </c>
+      <c r="J9" s="8">
+        <v>28</v>
+      </c>
+      <c r="K9" s="8">
+        <v>28</v>
+      </c>
+      <c r="L9" s="8">
+        <v>28</v>
+      </c>
+      <c r="M9" s="8">
+        <v>28</v>
+      </c>
+      <c r="N9" s="8">
+        <v>28</v>
+      </c>
+      <c r="O9" s="8">
+        <v>28</v>
+      </c>
+      <c r="P9" s="8">
+        <v>28</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A10" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="8">
+        <v>28</v>
+      </c>
+      <c r="D10" s="8">
+        <v>28</v>
+      </c>
+      <c r="E10" s="8">
+        <v>28</v>
+      </c>
+      <c r="F10" s="8">
+        <v>28</v>
+      </c>
+      <c r="G10" s="8">
+        <v>28</v>
+      </c>
+      <c r="H10" s="8">
+        <v>28</v>
+      </c>
+      <c r="I10" s="8">
+        <v>28</v>
+      </c>
+      <c r="J10" s="8">
+        <v>28</v>
+      </c>
+      <c r="K10" s="8">
+        <v>28</v>
+      </c>
+      <c r="L10" s="8">
+        <v>28</v>
+      </c>
+      <c r="M10" s="8">
+        <v>28</v>
+      </c>
+      <c r="N10" s="8">
+        <v>28</v>
+      </c>
+      <c r="O10" s="8">
+        <v>28</v>
+      </c>
+      <c r="P10" s="8">
+        <v>28</v>
+      </c>
+      <c r="Q10" s="8">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A11" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="8">
+        <v>24</v>
+      </c>
+      <c r="D11" s="8">
+        <v>26</v>
+      </c>
+      <c r="E11" s="8">
+        <v>26</v>
+      </c>
+      <c r="F11" s="8">
+        <v>27</v>
+      </c>
+      <c r="G11" s="8">
+        <v>27</v>
+      </c>
+      <c r="H11" s="8">
+        <v>25</v>
+      </c>
+      <c r="I11" s="8">
+        <v>27</v>
+      </c>
+      <c r="J11" s="8">
+        <v>26</v>
+      </c>
+      <c r="K11" s="8">
+        <v>26</v>
+      </c>
+      <c r="L11" s="8">
+        <v>25</v>
+      </c>
+      <c r="M11" s="8">
+        <v>24</v>
+      </c>
+      <c r="N11" s="8">
+        <v>24</v>
+      </c>
+      <c r="O11" s="8">
+        <v>19</v>
+      </c>
+      <c r="P11" s="8">
+        <v>19</v>
+      </c>
+      <c r="Q11" s="8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A12" s="8"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
+      <c r="Q12" s="8"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A13" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="8">
+        <v>17</v>
+      </c>
+      <c r="D13" s="8">
+        <v>17</v>
+      </c>
+      <c r="E13" s="8">
+        <v>17</v>
+      </c>
+      <c r="F13" s="8">
+        <v>17</v>
+      </c>
+      <c r="G13" s="8">
+        <v>17</v>
+      </c>
+      <c r="H13" s="8">
+        <v>17</v>
+      </c>
+      <c r="I13" s="8">
+        <v>17</v>
+      </c>
+      <c r="J13" s="8">
+        <v>17</v>
+      </c>
+      <c r="K13" s="8">
+        <v>17</v>
+      </c>
+      <c r="L13" s="8">
+        <v>17</v>
+      </c>
+      <c r="M13" s="8">
+        <v>17</v>
+      </c>
+      <c r="N13" s="8">
+        <v>17</v>
+      </c>
+      <c r="O13" s="8">
+        <v>17</v>
+      </c>
+      <c r="P13" s="8">
+        <v>17</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A14" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="8">
+        <v>17</v>
+      </c>
+      <c r="D14" s="8">
+        <v>17</v>
+      </c>
+      <c r="E14" s="8">
+        <v>17</v>
+      </c>
+      <c r="F14" s="8">
+        <v>17</v>
+      </c>
+      <c r="G14" s="8">
+        <v>17</v>
+      </c>
+      <c r="H14" s="8">
+        <v>17</v>
+      </c>
+      <c r="I14" s="8">
+        <v>17</v>
+      </c>
+      <c r="J14" s="8">
+        <v>17</v>
+      </c>
+      <c r="K14" s="8">
+        <v>17</v>
+      </c>
+      <c r="L14" s="8">
+        <v>17</v>
+      </c>
+      <c r="M14" s="8">
+        <v>17</v>
+      </c>
+      <c r="N14" s="8">
+        <v>17</v>
+      </c>
+      <c r="O14" s="8">
+        <v>17</v>
+      </c>
+      <c r="P14" s="8">
+        <v>17</v>
+      </c>
+      <c r="Q14" s="8">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A15" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="8">
+        <v>16</v>
+      </c>
+      <c r="D15" s="8">
+        <v>16</v>
+      </c>
+      <c r="E15" s="14">
+        <v>18</v>
+      </c>
+      <c r="F15" s="8">
+        <v>17</v>
+      </c>
+      <c r="G15" s="8">
+        <v>17</v>
+      </c>
+      <c r="H15" s="8">
+        <v>16</v>
+      </c>
+      <c r="I15" s="8">
+        <v>16</v>
+      </c>
+      <c r="J15" s="8">
+        <v>16</v>
+      </c>
+      <c r="K15" s="8">
+        <v>16</v>
+      </c>
+      <c r="L15" s="8">
+        <v>15</v>
+      </c>
+      <c r="M15" s="8">
+        <v>15</v>
+      </c>
+      <c r="N15" s="8">
+        <v>15</v>
+      </c>
+      <c r="O15" s="8">
+        <v>13</v>
+      </c>
+      <c r="P15" s="8">
+        <v>13</v>
+      </c>
+      <c r="Q15" s="8">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A16" s="8"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="8"/>
+      <c r="Q16" s="8"/>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A17" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="8">
+        <v>0</v>
+      </c>
+      <c r="D17" s="8">
+        <v>0</v>
+      </c>
+      <c r="E17" s="8">
+        <v>1</v>
+      </c>
+      <c r="F17" s="8">
+        <v>3</v>
+      </c>
+      <c r="G17" s="8">
+        <v>3</v>
+      </c>
+      <c r="H17" s="8">
+        <v>3</v>
+      </c>
+      <c r="I17" s="8">
+        <v>3</v>
+      </c>
+      <c r="J17" s="8">
+        <v>3</v>
+      </c>
+      <c r="K17" s="8">
+        <v>3</v>
+      </c>
+      <c r="L17" s="8">
+        <v>3</v>
+      </c>
+      <c r="M17" s="8">
+        <v>3</v>
+      </c>
+      <c r="N17" s="8">
+        <v>3</v>
+      </c>
+      <c r="O17" s="8">
+        <v>3</v>
+      </c>
+      <c r="P17" s="8">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A18" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="8">
+        <v>2</v>
+      </c>
+      <c r="D18" s="8">
+        <v>2</v>
+      </c>
+      <c r="E18" s="8">
+        <v>2</v>
+      </c>
+      <c r="F18" s="8">
+        <v>2</v>
+      </c>
+      <c r="G18" s="8">
+        <v>2</v>
+      </c>
+      <c r="H18" s="8">
+        <v>2</v>
+      </c>
+      <c r="I18" s="8">
+        <v>2</v>
+      </c>
+      <c r="J18" s="8">
+        <v>2</v>
+      </c>
+      <c r="K18" s="8">
+        <v>2</v>
+      </c>
+      <c r="L18" s="8">
+        <v>2</v>
+      </c>
+      <c r="M18" s="8">
+        <v>2</v>
+      </c>
+      <c r="N18" s="8">
+        <v>2</v>
+      </c>
+      <c r="O18" s="8">
+        <v>2</v>
+      </c>
+      <c r="P18" s="8">
+        <v>2</v>
+      </c>
+      <c r="Q18" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A19" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="8">
+        <v>0</v>
+      </c>
+      <c r="D19" s="8">
+        <v>0</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0</v>
+      </c>
+      <c r="F19" s="8">
+        <v>1</v>
+      </c>
+      <c r="G19" s="8">
+        <v>3</v>
+      </c>
+      <c r="H19" s="8">
+        <v>3</v>
+      </c>
+      <c r="I19" s="8">
+        <v>3</v>
+      </c>
+      <c r="J19" s="8">
+        <v>3</v>
+      </c>
+      <c r="K19" s="8">
+        <v>3</v>
+      </c>
+      <c r="L19" s="8">
+        <v>2</v>
+      </c>
+      <c r="M19" s="8">
+        <v>2</v>
+      </c>
+      <c r="N19" s="8">
+        <v>2</v>
+      </c>
+      <c r="O19" s="8">
+        <v>0</v>
+      </c>
+      <c r="P19" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A31" s="17"/>
+      <c r="B31" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C31" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="D31" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="E31" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F31" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="G31" s="24" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A32" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" s="26">
+        <v>45</v>
+      </c>
+      <c r="D32" s="21">
+        <v>48</v>
+      </c>
+      <c r="E32" s="21">
+        <v>48</v>
+      </c>
+      <c r="F32" s="21">
+        <v>48</v>
+      </c>
+      <c r="G32" s="21">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="26">
+        <v>47</v>
+      </c>
+      <c r="D33" s="21">
+        <v>48</v>
+      </c>
+      <c r="E33" s="21">
+        <v>48</v>
+      </c>
+      <c r="F33" s="21">
+        <v>48</v>
+      </c>
+      <c r="G33" s="21">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="26">
+        <v>42</v>
+      </c>
+      <c r="D34" s="21">
+        <v>45</v>
+      </c>
+      <c r="E34" s="21">
+        <v>45</v>
+      </c>
+      <c r="F34" s="21">
+        <v>41</v>
+      </c>
+      <c r="G34" s="21">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="17"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="27">
+        <v>5.7599999999999998E-2</v>
+      </c>
+      <c r="D35" s="28">
+        <v>5.4699999999999999E-2</v>
+      </c>
+      <c r="E35" s="28">
+        <v>6.4399999999999999E-2</v>
+      </c>
+      <c r="F35" s="28">
+        <v>0.14099999999999999</v>
+      </c>
+      <c r="G35" s="28">
+        <v>0.21079999999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="8"/>
+      <c r="B36" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C36" s="29">
+        <v>0.94240000000000002</v>
+      </c>
+      <c r="D36" s="19">
+        <v>0.94530000000000003</v>
+      </c>
+      <c r="E36" s="19">
+        <v>0.93559999999999999</v>
+      </c>
+      <c r="F36" s="19">
+        <v>0.85899999999999999</v>
+      </c>
+      <c r="G36" s="19">
+        <v>0.78920000000000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="17"/>
+      <c r="B37" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" s="30">
+        <v>3</v>
+      </c>
+      <c r="D37" s="20">
+        <v>3</v>
+      </c>
+      <c r="E37" s="20">
+        <v>3</v>
+      </c>
+      <c r="F37" s="20">
+        <v>7</v>
+      </c>
+      <c r="G37" s="20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="17"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="31"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C39" s="26">
+        <v>28</v>
+      </c>
+      <c r="D39" s="21">
+        <v>28</v>
+      </c>
+      <c r="E39" s="21">
+        <v>28</v>
+      </c>
+      <c r="F39" s="21">
+        <v>28</v>
+      </c>
+      <c r="G39" s="21">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A40" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C40" s="26">
+        <v>28</v>
+      </c>
+      <c r="D40" s="21">
+        <v>28</v>
+      </c>
+      <c r="E40" s="21">
+        <v>28</v>
+      </c>
+      <c r="F40" s="21">
+        <v>28</v>
+      </c>
+      <c r="G40" s="21">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A41" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B41" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C41" s="26">
+        <v>26</v>
+      </c>
+      <c r="D41" s="21">
+        <v>27</v>
+      </c>
+      <c r="E41" s="21">
+        <v>26</v>
+      </c>
+      <c r="F41" s="21">
+        <v>24</v>
+      </c>
+      <c r="G41" s="21">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A42" s="8"/>
+      <c r="B42" s="17"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="21"/>
+      <c r="G42" s="21"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A43" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C43" s="26">
+        <v>17</v>
+      </c>
+      <c r="D43" s="21">
+        <v>17</v>
+      </c>
+      <c r="E43" s="21">
+        <v>17</v>
+      </c>
+      <c r="F43" s="21">
+        <v>17</v>
+      </c>
+      <c r="G43" s="21">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A44" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" s="26">
+        <v>17</v>
+      </c>
+      <c r="D44" s="21">
+        <v>17</v>
+      </c>
+      <c r="E44" s="21">
+        <v>17</v>
+      </c>
+      <c r="F44" s="21">
+        <v>17</v>
+      </c>
+      <c r="G44" s="21">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A45" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B45" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C45" s="26">
+        <v>17</v>
+      </c>
+      <c r="D45" s="21">
+        <v>17</v>
+      </c>
+      <c r="E45" s="21">
+        <v>16</v>
+      </c>
+      <c r="F45" s="21">
+        <v>15</v>
+      </c>
+      <c r="G45" s="21">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A46" s="8"/>
+      <c r="B46" s="17"/>
+      <c r="C46" s="26"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="21"/>
+      <c r="F46" s="21"/>
+      <c r="G46" s="21"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A47" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C47" s="26">
+        <v>0</v>
+      </c>
+      <c r="D47" s="21">
+        <v>3</v>
+      </c>
+      <c r="E47" s="21">
+        <v>3</v>
+      </c>
+      <c r="F47" s="21">
+        <v>3</v>
+      </c>
+      <c r="G47" s="21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A48" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C48" s="26">
+        <v>2</v>
+      </c>
+      <c r="D48" s="21">
+        <v>2</v>
+      </c>
+      <c r="E48" s="21">
+        <v>2</v>
+      </c>
+      <c r="F48" s="21">
+        <v>2</v>
+      </c>
+      <c r="G48" s="21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A49" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B49" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C49" s="26">
+        <v>0</v>
+      </c>
+      <c r="D49" s="21">
+        <v>2</v>
+      </c>
+      <c r="E49" s="21">
+        <v>3</v>
+      </c>
+      <c r="F49" s="21">
+        <v>2</v>
+      </c>
+      <c r="G49" s="21">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D26C1373-E770-0140-BF3F-1CD6E7CFCFB4}">
+  <sheetPr>
+    <tabColor theme="7" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:P47"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B1" t="str">
+        <f>IF(PSE!C1&gt;0,PSE!C1,"")</f>
+        <v>JAN</v>
+      </c>
+      <c r="C1" t="str">
+        <f>IF(PSE!D1&gt;0,PSE!D1,"")</f>
+        <v>FEB</v>
+      </c>
+      <c r="D1" t="str">
+        <f>IF(PSE!E1&gt;0,PSE!E1,"")</f>
+        <v>MAR</v>
+      </c>
+      <c r="E1" t="str">
+        <f>IF(PSE!F1&gt;0,PSE!F1,"")</f>
+        <v>APR</v>
+      </c>
+      <c r="F1" t="str">
+        <f>IF(PSE!G1&gt;0,PSE!G1,"")</f>
+        <v>MAY</v>
+      </c>
+      <c r="G1" t="str">
+        <f>IF(PSE!H1&gt;0,PSE!H1,"")</f>
+        <v>JUN</v>
+      </c>
+      <c r="H1" t="str">
+        <f>IF(PSE!I1&gt;0,PSE!I1,"")</f>
+        <v>JUL</v>
+      </c>
+      <c r="I1" t="str">
+        <f>IF(PSE!J1&gt;0,PSE!J1,"")</f>
+        <v>AUG</v>
+      </c>
+      <c r="J1" t="str">
+        <f>IF(PSE!K1&gt;0,PSE!K1,"")</f>
+        <v>SEP</v>
+      </c>
+      <c r="K1" t="str">
+        <f>IF(PSE!L1&gt;0,PSE!L1,"")</f>
+        <v>OCT</v>
+      </c>
+      <c r="L1" t="str">
+        <f>IF(PSE!M1&gt;0,PSE!M1,"")</f>
+        <v>NOV</v>
+      </c>
+      <c r="M1" t="str">
+        <f>IF(PSE!N1&gt;0,PSE!N1,"")</f>
+        <v>DEC</v>
+      </c>
+      <c r="N1" t="str">
+        <f>IF(PSE!O1&gt;0,PSE!O1,"")</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O1" t="str">
+        <f>IF(PSE!P1&gt;0,PSE!P1,"")</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P1" t="str">
+        <f>IF(PSE!Q1&gt;0,PSE!Q1,"")</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A2" t="str">
+        <f>IF(PSE!B2&gt;0,PSE!B2,"")</f>
+        <v>Staff</v>
+      </c>
+      <c r="B2">
+        <f>IF(PSE!C2&gt;0,PSE!C2,"")</f>
+        <v>45</v>
+      </c>
+      <c r="C2">
+        <f>IF(PSE!D2&gt;0,PSE!D2,"")</f>
+        <v>45</v>
+      </c>
+      <c r="D2">
+        <f>IF(PSE!E2&gt;0,PSE!E2,"")</f>
+        <v>45</v>
+      </c>
+      <c r="E2">
+        <f>IF(PSE!F2&gt;0,PSE!F2,"")</f>
+        <v>48</v>
+      </c>
+      <c r="F2">
+        <f>IF(PSE!G2&gt;0,PSE!G2,"")</f>
+        <v>48</v>
+      </c>
+      <c r="G2">
+        <f>IF(PSE!H2&gt;0,PSE!H2,"")</f>
+        <v>48</v>
+      </c>
+      <c r="H2">
+        <f>IF(PSE!I2&gt;0,PSE!I2,"")</f>
+        <v>48</v>
+      </c>
+      <c r="I2">
+        <f>IF(PSE!J2&gt;0,PSE!J2,"")</f>
+        <v>48</v>
+      </c>
+      <c r="J2">
+        <f>IF(PSE!K2&gt;0,PSE!K2,"")</f>
+        <v>48</v>
+      </c>
+      <c r="K2">
+        <f>IF(PSE!L2&gt;0,PSE!L2,"")</f>
+        <v>48</v>
+      </c>
+      <c r="L2">
+        <f>IF(PSE!M2&gt;0,PSE!M2,"")</f>
+        <v>48</v>
+      </c>
+      <c r="M2">
+        <f>IF(PSE!N2&gt;0,PSE!N2,"")</f>
+        <v>48</v>
+      </c>
+      <c r="N2">
+        <f>IF(PSE!O2&gt;0,PSE!O2,"")</f>
+        <v>48</v>
+      </c>
+      <c r="O2">
+        <f>IF(PSE!P2&gt;0,PSE!P2,"")</f>
+        <v>48</v>
+      </c>
+      <c r="P2">
+        <f>IF(PSE!Q2&gt;0,PSE!Q2,"")</f>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A3" t="str">
+        <f>IF(PSE!B3&gt;0,PSE!B3,"")</f>
+        <v>Staff AVG</v>
+      </c>
+      <c r="B3">
+        <f>IF(PSE!C3&gt;0,PSE!C3,"")</f>
+        <v>47</v>
+      </c>
+      <c r="C3">
+        <f>IF(PSE!D3&gt;0,PSE!D3,"")</f>
+        <v>47</v>
+      </c>
+      <c r="D3">
+        <f>IF(PSE!E3&gt;0,PSE!E3,"")</f>
+        <v>47</v>
+      </c>
+      <c r="E3">
+        <f>IF(PSE!F3&gt;0,PSE!F3,"")</f>
+        <v>48</v>
+      </c>
+      <c r="F3">
+        <f>IF(PSE!G3&gt;0,PSE!G3,"")</f>
+        <v>48</v>
+      </c>
+      <c r="G3">
+        <f>IF(PSE!H3&gt;0,PSE!H3,"")</f>
+        <v>48</v>
+      </c>
+      <c r="H3">
+        <f>IF(PSE!I3&gt;0,PSE!I3,"")</f>
+        <v>48</v>
+      </c>
+      <c r="I3">
+        <f>IF(PSE!J3&gt;0,PSE!J3,"")</f>
+        <v>48</v>
+      </c>
+      <c r="J3">
+        <f>IF(PSE!K3&gt;0,PSE!K3,"")</f>
+        <v>48</v>
+      </c>
+      <c r="K3">
+        <f>IF(PSE!L3&gt;0,PSE!L3,"")</f>
+        <v>48</v>
+      </c>
+      <c r="L3">
+        <f>IF(PSE!M3&gt;0,PSE!M3,"")</f>
+        <v>48</v>
+      </c>
+      <c r="M3">
+        <f>IF(PSE!N3&gt;0,PSE!N3,"")</f>
+        <v>48</v>
+      </c>
+      <c r="N3">
+        <f>IF(PSE!O3&gt;0,PSE!O3,"")</f>
+        <v>48</v>
+      </c>
+      <c r="O3">
+        <f>IF(PSE!P3&gt;0,PSE!P3,"")</f>
+        <v>48</v>
+      </c>
+      <c r="P3">
+        <f>IF(PSE!Q3&gt;0,PSE!Q3,"")</f>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A4" t="str">
+        <f>IF(PSE!B4&gt;0,PSE!B4,"")</f>
+        <v>Plan</v>
+      </c>
+      <c r="B4">
+        <f>IF(PSE!C4&gt;0,PSE!C4,"")</f>
+        <v>40</v>
+      </c>
+      <c r="C4">
+        <f>IF(PSE!D4&gt;0,PSE!D4,"")</f>
+        <v>42</v>
+      </c>
+      <c r="D4">
+        <f>IF(PSE!E4&gt;0,PSE!E4,"")</f>
+        <v>44</v>
+      </c>
+      <c r="E4">
+        <f>IF(PSE!F4&gt;0,PSE!F4,"")</f>
+        <v>45</v>
+      </c>
+      <c r="F4">
+        <f>IF(PSE!G4&gt;0,PSE!G4,"")</f>
+        <v>47</v>
+      </c>
+      <c r="G4">
+        <f>IF(PSE!H4&gt;0,PSE!H4,"")</f>
+        <v>44</v>
+      </c>
+      <c r="H4">
+        <f>IF(PSE!I4&gt;0,PSE!I4,"")</f>
+        <v>45</v>
+      </c>
+      <c r="I4">
+        <f>IF(PSE!J4&gt;0,PSE!J4,"")</f>
+        <v>45</v>
+      </c>
+      <c r="J4">
+        <f>IF(PSE!K4&gt;0,PSE!K4,"")</f>
+        <v>45</v>
+      </c>
+      <c r="K4">
+        <f>IF(PSE!L4&gt;0,PSE!L4,"")</f>
+        <v>42</v>
+      </c>
+      <c r="L4">
+        <f>IF(PSE!M4&gt;0,PSE!M4,"")</f>
+        <v>41</v>
+      </c>
+      <c r="M4">
+        <f>IF(PSE!N4&gt;0,PSE!N4,"")</f>
+        <v>41</v>
+      </c>
+      <c r="N4">
+        <f>IF(PSE!O4&gt;0,PSE!O4,"")</f>
+        <v>32</v>
+      </c>
+      <c r="O4">
+        <f>IF(PSE!P4&gt;0,PSE!P4,"")</f>
+        <v>32</v>
+      </c>
+      <c r="P4">
+        <f>IF(PSE!Q4&gt;0,PSE!Q4,"")</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A5" t="str">
+        <f>IF(PSE!B11&gt;0,PSE!B11,"")</f>
+        <v>PAYROLL</v>
+      </c>
+      <c r="B5">
+        <f>IF(PSE!C11&gt;0,PSE!C11,"")</f>
+        <v>24</v>
+      </c>
+      <c r="C5">
+        <f>IF(PSE!D11&gt;0,PSE!D11,"")</f>
+        <v>26</v>
+      </c>
+      <c r="D5">
+        <f>IF(PSE!E11&gt;0,PSE!E11,"")</f>
+        <v>26</v>
+      </c>
+      <c r="E5">
+        <f>IF(PSE!F11&gt;0,PSE!F11,"")</f>
+        <v>27</v>
+      </c>
+      <c r="F5">
+        <f>IF(PSE!G11&gt;0,PSE!G11,"")</f>
+        <v>27</v>
+      </c>
+      <c r="G5">
+        <f>IF(PSE!H11&gt;0,PSE!H11,"")</f>
+        <v>25</v>
+      </c>
+      <c r="H5">
+        <f>IF(PSE!I11&gt;0,PSE!I11,"")</f>
+        <v>27</v>
+      </c>
+      <c r="I5">
+        <f>IF(PSE!J11&gt;0,PSE!J11,"")</f>
+        <v>26</v>
+      </c>
+      <c r="J5">
+        <f>IF(PSE!K11&gt;0,PSE!K11,"")</f>
+        <v>26</v>
+      </c>
+      <c r="K5">
+        <f>IF(PSE!L11&gt;0,PSE!L11,"")</f>
+        <v>25</v>
+      </c>
+      <c r="L5">
+        <f>IF(PSE!M11&gt;0,PSE!M11,"")</f>
+        <v>24</v>
+      </c>
+      <c r="M5">
+        <f>IF(PSE!N11&gt;0,PSE!N11,"")</f>
+        <v>24</v>
+      </c>
+      <c r="N5">
+        <f>IF(PSE!O11&gt;0,PSE!O11,"")</f>
+        <v>19</v>
+      </c>
+      <c r="O5">
+        <f>IF(PSE!P11&gt;0,PSE!P11,"")</f>
+        <v>19</v>
+      </c>
+      <c r="P5">
+        <f>IF(PSE!Q11&gt;0,PSE!Q11,"")</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A6" t="str">
+        <f>IF(PSE!B15&gt;0,PSE!B15,"")</f>
+        <v>CONTRACTOR</v>
+      </c>
+      <c r="B6">
+        <f>IF(PSE!C15&gt;0,PSE!C15,"")</f>
+        <v>16</v>
+      </c>
+      <c r="C6">
+        <f>IF(PSE!D15&gt;0,PSE!D15,"")</f>
+        <v>16</v>
+      </c>
+      <c r="D6">
+        <f>IF(PSE!E15&gt;0,PSE!E15,"")</f>
+        <v>18</v>
+      </c>
+      <c r="E6">
+        <f>IF(PSE!F15&gt;0,PSE!F15,"")</f>
+        <v>17</v>
+      </c>
+      <c r="F6">
+        <f>IF(PSE!G15&gt;0,PSE!G15,"")</f>
+        <v>17</v>
+      </c>
+      <c r="G6">
+        <f>IF(PSE!H15&gt;0,PSE!H15,"")</f>
+        <v>16</v>
+      </c>
+      <c r="H6">
+        <f>IF(PSE!I15&gt;0,PSE!I15,"")</f>
+        <v>16</v>
+      </c>
+      <c r="I6">
+        <f>IF(PSE!J15&gt;0,PSE!J15,"")</f>
+        <v>16</v>
+      </c>
+      <c r="J6">
+        <f>IF(PSE!K15&gt;0,PSE!K15,"")</f>
+        <v>16</v>
+      </c>
+      <c r="K6">
+        <f>IF(PSE!L15&gt;0,PSE!L15,"")</f>
+        <v>15</v>
+      </c>
+      <c r="L6">
+        <f>IF(PSE!M15&gt;0,PSE!M15,"")</f>
+        <v>15</v>
+      </c>
+      <c r="M6">
+        <f>IF(PSE!N15&gt;0,PSE!N15,"")</f>
+        <v>15</v>
+      </c>
+      <c r="N6">
+        <f>IF(PSE!O15&gt;0,PSE!O15,"")</f>
+        <v>13</v>
+      </c>
+      <c r="O6">
+        <f>IF(PSE!P15&gt;0,PSE!P15,"")</f>
+        <v>13</v>
+      </c>
+      <c r="P6">
+        <f>IF(PSE!Q15&gt;0,PSE!Q15,"")</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A7" t="str">
+        <f>IF(PSE!B19&gt;0,PSE!B19,"")</f>
+        <v>OUTSOURCE</v>
+      </c>
+      <c r="B7" t="str">
+        <f>IF(PSE!C19&gt;0,PSE!C19,"")</f>
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <f>IF(PSE!D19&gt;0,PSE!D19,"")</f>
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <f>IF(PSE!E19&gt;0,PSE!E19,"")</f>
+        <v/>
+      </c>
+      <c r="E7">
+        <f>IF(PSE!F19&gt;0,PSE!F19,"")</f>
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <f>IF(PSE!G19&gt;0,PSE!G19,"")</f>
+        <v>3</v>
+      </c>
+      <c r="G7">
+        <f>IF(PSE!H19&gt;0,PSE!H19,"")</f>
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <f>IF(PSE!I19&gt;0,PSE!I19,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I7">
+        <f>IF(PSE!J19&gt;0,PSE!J19,"")</f>
+        <v>3</v>
+      </c>
+      <c r="J7">
+        <f>IF(PSE!K19&gt;0,PSE!K19,"")</f>
+        <v>3</v>
+      </c>
+      <c r="K7">
+        <f>IF(PSE!L19&gt;0,PSE!L19,"")</f>
+        <v>2</v>
+      </c>
+      <c r="L7">
+        <f>IF(PSE!M19&gt;0,PSE!M19,"")</f>
+        <v>2</v>
+      </c>
+      <c r="M7">
+        <f>IF(PSE!N19&gt;0,PSE!N19,"")</f>
+        <v>2</v>
+      </c>
+      <c r="N7" t="str">
+        <f>IF(PSE!O19&gt;0,PSE!O19,"")</f>
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <f>IF(PSE!P19&gt;0,PSE!P19,"")</f>
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <f>IF(PSE!Q19&gt;0,PSE!Q19,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B11" t="str">
+        <f>IF(PSE!C1&gt;0,PSE!C1,"")</f>
+        <v>JAN</v>
+      </c>
+      <c r="C11" t="str">
+        <f>IF(PSE!D1&gt;0,PSE!D1,"")</f>
+        <v>FEB</v>
+      </c>
+      <c r="D11" t="str">
+        <f>IF(PSE!E1&gt;0,PSE!E1,"")</f>
+        <v>MAR</v>
+      </c>
+      <c r="E11" t="str">
+        <f>IF(PSE!F1&gt;0,PSE!F1,"")</f>
+        <v>APR</v>
+      </c>
+      <c r="F11" t="str">
+        <f>IF(PSE!G1&gt;0,PSE!G1,"")</f>
+        <v>MAY</v>
+      </c>
+      <c r="G11" t="str">
+        <f>IF(PSE!H1&gt;0,PSE!H1,"")</f>
+        <v>JUN</v>
+      </c>
+      <c r="H11" t="str">
+        <f>IF(PSE!I1&gt;0,PSE!I1,"")</f>
+        <v>JUL</v>
+      </c>
+      <c r="I11" t="str">
+        <f>IF(PSE!J1&gt;0,PSE!J1,"")</f>
+        <v>AUG</v>
+      </c>
+      <c r="J11" t="str">
+        <f>IF(PSE!K1&gt;0,PSE!K1,"")</f>
+        <v>SEP</v>
+      </c>
+      <c r="K11" t="str">
+        <f>IF(PSE!L1&gt;0,PSE!L1,"")</f>
+        <v>OCT</v>
+      </c>
+      <c r="L11" t="str">
+        <f>IF(PSE!M1&gt;0,PSE!M1,"")</f>
+        <v>NOV</v>
+      </c>
+      <c r="M11" t="str">
+        <f>IF(PSE!N1&gt;0,PSE!N1,"")</f>
+        <v>DEC</v>
+      </c>
+      <c r="N11" t="str">
+        <f>IF(PSE!O1&gt;0,PSE!O1,"")</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O11" t="str">
+        <f>IF(PSE!P1&gt;0,PSE!P1,"")</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P11" t="str">
+        <f>IF(PSE!Q1&gt;0,PSE!Q1,"")</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A12" t="str">
+        <f>IF(PSE!A9&gt;0,PSE!A9,"")</f>
+        <v>Staff</v>
+      </c>
+      <c r="B12">
+        <f>IF(PSE!C9&gt;0,PSE!C9,"")</f>
+        <v>28</v>
+      </c>
+      <c r="C12">
+        <f>IF(PSE!D9&gt;0,PSE!D9,"")</f>
+        <v>28</v>
+      </c>
+      <c r="D12">
+        <f>IF(PSE!E9&gt;0,PSE!E9,"")</f>
+        <v>27</v>
+      </c>
+      <c r="E12">
+        <f>IF(PSE!F9&gt;0,PSE!F9,"")</f>
+        <v>28</v>
+      </c>
+      <c r="F12">
+        <f>IF(PSE!G9&gt;0,PSE!G9,"")</f>
+        <v>28</v>
+      </c>
+      <c r="G12">
+        <f>IF(PSE!H9&gt;0,PSE!H9,"")</f>
+        <v>28</v>
+      </c>
+      <c r="H12">
+        <f>IF(PSE!I9&gt;0,PSE!I9,"")</f>
+        <v>28</v>
+      </c>
+      <c r="I12">
+        <f>IF(PSE!J9&gt;0,PSE!J9,"")</f>
+        <v>28</v>
+      </c>
+      <c r="J12">
+        <f>IF(PSE!K9&gt;0,PSE!K9,"")</f>
+        <v>28</v>
+      </c>
+      <c r="K12">
+        <f>IF(PSE!L9&gt;0,PSE!L9,"")</f>
+        <v>28</v>
+      </c>
+      <c r="L12">
+        <f>IF(PSE!M9&gt;0,PSE!M9,"")</f>
+        <v>28</v>
+      </c>
+      <c r="M12">
+        <f>IF(PSE!N9&gt;0,PSE!N9,"")</f>
+        <v>28</v>
+      </c>
+      <c r="N12">
+        <f>IF(PSE!O9&gt;0,PSE!O9,"")</f>
+        <v>28</v>
+      </c>
+      <c r="O12">
+        <f>IF(PSE!P9&gt;0,PSE!P9,"")</f>
+        <v>28</v>
+      </c>
+      <c r="P12">
+        <f>IF(PSE!Q9&gt;0,PSE!Q9,"")</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A13" t="str">
+        <f>IF(PSE!A10&gt;0,PSE!A10,"")</f>
+        <v>Staff AVG</v>
+      </c>
+      <c r="B13">
+        <f>IF(PSE!C10&gt;0,PSE!C10,"")</f>
+        <v>28</v>
+      </c>
+      <c r="C13">
+        <f>IF(PSE!D10&gt;0,PSE!D10,"")</f>
+        <v>28</v>
+      </c>
+      <c r="D13">
+        <f>IF(PSE!E10&gt;0,PSE!E10,"")</f>
+        <v>28</v>
+      </c>
+      <c r="E13">
+        <f>IF(PSE!F10&gt;0,PSE!F10,"")</f>
+        <v>28</v>
+      </c>
+      <c r="F13">
+        <f>IF(PSE!G10&gt;0,PSE!G10,"")</f>
+        <v>28</v>
+      </c>
+      <c r="G13">
+        <f>IF(PSE!H10&gt;0,PSE!H10,"")</f>
+        <v>28</v>
+      </c>
+      <c r="H13">
+        <f>IF(PSE!I10&gt;0,PSE!I10,"")</f>
+        <v>28</v>
+      </c>
+      <c r="I13">
+        <f>IF(PSE!J10&gt;0,PSE!J10,"")</f>
+        <v>28</v>
+      </c>
+      <c r="J13">
+        <f>IF(PSE!K10&gt;0,PSE!K10,"")</f>
+        <v>28</v>
+      </c>
+      <c r="K13">
+        <f>IF(PSE!L10&gt;0,PSE!L10,"")</f>
+        <v>28</v>
+      </c>
+      <c r="L13">
+        <f>IF(PSE!M10&gt;0,PSE!M10,"")</f>
+        <v>28</v>
+      </c>
+      <c r="M13">
+        <f>IF(PSE!N10&gt;0,PSE!N10,"")</f>
+        <v>28</v>
+      </c>
+      <c r="N13">
+        <f>IF(PSE!O10&gt;0,PSE!O10,"")</f>
+        <v>28</v>
+      </c>
+      <c r="O13">
+        <f>IF(PSE!P10&gt;0,PSE!P10,"")</f>
+        <v>28</v>
+      </c>
+      <c r="P13">
+        <f>IF(PSE!Q10&gt;0,PSE!Q10,"")</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A14" t="str">
+        <f>IF(PSE!A11&gt;0,PSE!A11,"")</f>
+        <v>Plan</v>
+      </c>
+      <c r="B14">
+        <f>IF(PSE!C11&gt;0,PSE!C11,"")</f>
+        <v>24</v>
+      </c>
+      <c r="C14">
+        <f>IF(PSE!D11&gt;0,PSE!D11,"")</f>
+        <v>26</v>
+      </c>
+      <c r="D14">
+        <f>IF(PSE!E11&gt;0,PSE!E11,"")</f>
+        <v>26</v>
+      </c>
+      <c r="E14">
+        <f>IF(PSE!F11&gt;0,PSE!F11,"")</f>
+        <v>27</v>
+      </c>
+      <c r="F14">
+        <f>IF(PSE!G11&gt;0,PSE!G11,"")</f>
+        <v>27</v>
+      </c>
+      <c r="G14">
+        <f>IF(PSE!H11&gt;0,PSE!H11,"")</f>
+        <v>25</v>
+      </c>
+      <c r="H14">
+        <f>IF(PSE!I11&gt;0,PSE!I11,"")</f>
+        <v>27</v>
+      </c>
+      <c r="I14">
+        <f>IF(PSE!J11&gt;0,PSE!J11,"")</f>
+        <v>26</v>
+      </c>
+      <c r="J14">
+        <f>IF(PSE!K11&gt;0,PSE!K11,"")</f>
+        <v>26</v>
+      </c>
+      <c r="K14">
+        <f>IF(PSE!L11&gt;0,PSE!L11,"")</f>
+        <v>25</v>
+      </c>
+      <c r="L14">
+        <f>IF(PSE!M11&gt;0,PSE!M11,"")</f>
+        <v>24</v>
+      </c>
+      <c r="M14">
+        <f>IF(PSE!N11&gt;0,PSE!N11,"")</f>
+        <v>24</v>
+      </c>
+      <c r="N14">
+        <f>IF(PSE!O11&gt;0,PSE!O11,"")</f>
+        <v>19</v>
+      </c>
+      <c r="O14">
+        <f>IF(PSE!P11&gt;0,PSE!P11,"")</f>
+        <v>19</v>
+      </c>
+      <c r="P14">
+        <f>IF(PSE!Q11&gt;0,PSE!Q11,"")</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B21" t="str">
+        <f>IF(PSE!C1&gt;0,PSE!C1,"")</f>
+        <v>JAN</v>
+      </c>
+      <c r="C21" t="str">
+        <f>IF(PSE!D1&gt;0,PSE!D1,"")</f>
+        <v>FEB</v>
+      </c>
+      <c r="D21" t="str">
+        <f>IF(PSE!E1&gt;0,PSE!E1,"")</f>
+        <v>MAR</v>
+      </c>
+      <c r="E21" t="str">
+        <f>IF(PSE!F1&gt;0,PSE!F1,"")</f>
+        <v>APR</v>
+      </c>
+      <c r="F21" t="str">
+        <f>IF(PSE!G1&gt;0,PSE!G1,"")</f>
+        <v>MAY</v>
+      </c>
+      <c r="G21" t="str">
+        <f>IF(PSE!H1&gt;0,PSE!H1,"")</f>
+        <v>JUN</v>
+      </c>
+      <c r="H21" t="str">
+        <f>IF(PSE!I1&gt;0,PSE!I1,"")</f>
+        <v>JUL</v>
+      </c>
+      <c r="I21" t="str">
+        <f>IF(PSE!J1&gt;0,PSE!J1,"")</f>
+        <v>AUG</v>
+      </c>
+      <c r="J21" t="str">
+        <f>IF(PSE!K1&gt;0,PSE!K1,"")</f>
+        <v>SEP</v>
+      </c>
+      <c r="K21" t="str">
+        <f>IF(PSE!L1&gt;0,PSE!L1,"")</f>
+        <v>OCT</v>
+      </c>
+      <c r="L21" t="str">
+        <f>IF(PSE!M1&gt;0,PSE!M1,"")</f>
+        <v>NOV</v>
+      </c>
+      <c r="M21" t="str">
+        <f>IF(PSE!N1&gt;0,PSE!N1,"")</f>
+        <v>DEC</v>
+      </c>
+      <c r="N21" t="str">
+        <f>IF(PSE!O1&gt;0,PSE!O1,"")</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O21" t="str">
+        <f>IF(PSE!P1&gt;0,PSE!P1,"")</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P21" t="str">
+        <f>IF(PSE!Q1&gt;0,PSE!Q1,"")</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A22" t="str">
+        <f>IF(PSE!A13&gt;0,PSE!A13,"")</f>
+        <v>Staff</v>
+      </c>
+      <c r="B22">
+        <f>IF(PSE!C13&gt;0,PSE!C13,"")</f>
+        <v>17</v>
+      </c>
+      <c r="C22">
+        <f>IF(PSE!D13&gt;0,PSE!D13,"")</f>
+        <v>17</v>
+      </c>
+      <c r="D22">
+        <f>IF(PSE!E13&gt;0,PSE!E13,"")</f>
+        <v>17</v>
+      </c>
+      <c r="E22">
+        <f>IF(PSE!F13&gt;0,PSE!F13,"")</f>
+        <v>17</v>
+      </c>
+      <c r="F22">
+        <f>IF(PSE!G13&gt;0,PSE!G13,"")</f>
+        <v>17</v>
+      </c>
+      <c r="G22">
+        <f>IF(PSE!H13&gt;0,PSE!H13,"")</f>
+        <v>17</v>
+      </c>
+      <c r="H22">
+        <f>IF(PSE!I13&gt;0,PSE!I13,"")</f>
+        <v>17</v>
+      </c>
+      <c r="I22">
+        <f>IF(PSE!J13&gt;0,PSE!J13,"")</f>
+        <v>17</v>
+      </c>
+      <c r="J22">
+        <f>IF(PSE!K13&gt;0,PSE!K13,"")</f>
+        <v>17</v>
+      </c>
+      <c r="K22">
+        <f>IF(PSE!L13&gt;0,PSE!L13,"")</f>
+        <v>17</v>
+      </c>
+      <c r="L22">
+        <f>IF(PSE!M13&gt;0,PSE!M13,"")</f>
+        <v>17</v>
+      </c>
+      <c r="M22">
+        <f>IF(PSE!N13&gt;0,PSE!N13,"")</f>
+        <v>17</v>
+      </c>
+      <c r="N22">
+        <f>IF(PSE!O13&gt;0,PSE!O13,"")</f>
+        <v>17</v>
+      </c>
+      <c r="O22">
+        <f>IF(PSE!P13&gt;0,PSE!P13,"")</f>
+        <v>17</v>
+      </c>
+      <c r="P22">
+        <f>IF(PSE!Q13&gt;0,PSE!Q13,"")</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A23" t="str">
+        <f>IF(PSE!A14&gt;0,PSE!A14,"")</f>
+        <v>Staff AVG</v>
+      </c>
+      <c r="B23">
+        <f>IF(PSE!C14&gt;0,PSE!C14,"")</f>
+        <v>17</v>
+      </c>
+      <c r="C23">
+        <f>IF(PSE!D14&gt;0,PSE!D14,"")</f>
+        <v>17</v>
+      </c>
+      <c r="D23">
+        <f>IF(PSE!E14&gt;0,PSE!E14,"")</f>
+        <v>17</v>
+      </c>
+      <c r="E23">
+        <f>IF(PSE!F14&gt;0,PSE!F14,"")</f>
+        <v>17</v>
+      </c>
+      <c r="F23">
+        <f>IF(PSE!G14&gt;0,PSE!G14,"")</f>
+        <v>17</v>
+      </c>
+      <c r="G23">
+        <f>IF(PSE!H14&gt;0,PSE!H14,"")</f>
+        <v>17</v>
+      </c>
+      <c r="H23">
+        <f>IF(PSE!I14&gt;0,PSE!I14,"")</f>
+        <v>17</v>
+      </c>
+      <c r="I23">
+        <f>IF(PSE!J14&gt;0,PSE!J14,"")</f>
+        <v>17</v>
+      </c>
+      <c r="J23">
+        <f>IF(PSE!K14&gt;0,PSE!K14,"")</f>
+        <v>17</v>
+      </c>
+      <c r="K23">
+        <f>IF(PSE!L14&gt;0,PSE!L14,"")</f>
+        <v>17</v>
+      </c>
+      <c r="L23">
+        <f>IF(PSE!M14&gt;0,PSE!M14,"")</f>
+        <v>17</v>
+      </c>
+      <c r="M23">
+        <f>IF(PSE!N14&gt;0,PSE!N14,"")</f>
+        <v>17</v>
+      </c>
+      <c r="N23">
+        <f>IF(PSE!O14&gt;0,PSE!O14,"")</f>
+        <v>17</v>
+      </c>
+      <c r="O23">
+        <f>IF(PSE!P14&gt;0,PSE!P14,"")</f>
+        <v>17</v>
+      </c>
+      <c r="P23">
+        <f>IF(PSE!Q14&gt;0,PSE!Q14,"")</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A24" t="str">
+        <f>IF(PSE!A15&gt;0,PSE!A15,"")</f>
+        <v>Plan</v>
+      </c>
+      <c r="B24">
+        <f>IF(PSE!C15&gt;0,PSE!C15,"")</f>
+        <v>16</v>
+      </c>
+      <c r="C24">
+        <f>IF(PSE!D15&gt;0,PSE!D15,"")</f>
+        <v>16</v>
+      </c>
+      <c r="D24">
+        <f>IF(PSE!E15&gt;0,PSE!E15,"")</f>
+        <v>18</v>
+      </c>
+      <c r="E24">
+        <f>IF(PSE!F15&gt;0,PSE!F15,"")</f>
+        <v>17</v>
+      </c>
+      <c r="F24">
+        <f>IF(PSE!G15&gt;0,PSE!G15,"")</f>
+        <v>17</v>
+      </c>
+      <c r="G24">
+        <f>IF(PSE!H15&gt;0,PSE!H15,"")</f>
+        <v>16</v>
+      </c>
+      <c r="H24">
+        <f>IF(PSE!I15&gt;0,PSE!I15,"")</f>
+        <v>16</v>
+      </c>
+      <c r="I24">
+        <f>IF(PSE!J15&gt;0,PSE!J15,"")</f>
+        <v>16</v>
+      </c>
+      <c r="J24">
+        <f>IF(PSE!K15&gt;0,PSE!K15,"")</f>
+        <v>16</v>
+      </c>
+      <c r="K24">
+        <f>IF(PSE!L15&gt;0,PSE!L15,"")</f>
+        <v>15</v>
+      </c>
+      <c r="L24">
+        <f>IF(PSE!M15&gt;0,PSE!M15,"")</f>
+        <v>15</v>
+      </c>
+      <c r="M24">
+        <f>IF(PSE!N15&gt;0,PSE!N15,"")</f>
+        <v>15</v>
+      </c>
+      <c r="N24">
+        <f>IF(PSE!O15&gt;0,PSE!O15,"")</f>
+        <v>13</v>
+      </c>
+      <c r="O24">
+        <f>IF(PSE!P15&gt;0,PSE!P15,"")</f>
+        <v>13</v>
+      </c>
+      <c r="P24">
+        <f>IF(PSE!Q15&gt;0,PSE!Q15,"")</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B31" t="str">
+        <f>IF(PSE!C1&gt;0,PSE!C1,"")</f>
+        <v>JAN</v>
+      </c>
+      <c r="C31" t="str">
+        <f>IF(PSE!D1&gt;0,PSE!D1,"")</f>
+        <v>FEB</v>
+      </c>
+      <c r="D31" t="str">
+        <f>IF(PSE!E1&gt;0,PSE!E1,"")</f>
+        <v>MAR</v>
+      </c>
+      <c r="E31" t="str">
+        <f>IF(PSE!F1&gt;0,PSE!F1,"")</f>
+        <v>APR</v>
+      </c>
+      <c r="F31" t="str">
+        <f>IF(PSE!G1&gt;0,PSE!G1,"")</f>
+        <v>MAY</v>
+      </c>
+      <c r="G31" t="str">
+        <f>IF(PSE!H1&gt;0,PSE!H1,"")</f>
+        <v>JUN</v>
+      </c>
+      <c r="H31" t="str">
+        <f>IF(PSE!I1&gt;0,PSE!I1,"")</f>
+        <v>JUL</v>
+      </c>
+      <c r="I31" t="str">
+        <f>IF(PSE!J1&gt;0,PSE!J1,"")</f>
+        <v>AUG</v>
+      </c>
+      <c r="J31" t="str">
+        <f>IF(PSE!K1&gt;0,PSE!K1,"")</f>
+        <v>SEP</v>
+      </c>
+      <c r="K31" t="str">
+        <f>IF(PSE!L1&gt;0,PSE!L1,"")</f>
+        <v>OCT</v>
+      </c>
+      <c r="L31" t="str">
+        <f>IF(PSE!M1&gt;0,PSE!M1,"")</f>
+        <v>NOV</v>
+      </c>
+      <c r="M31" t="str">
+        <f>IF(PSE!N1&gt;0,PSE!N1,"")</f>
+        <v>DEC</v>
+      </c>
+      <c r="N31" t="str">
+        <f>IF(PSE!O1&gt;0,PSE!O1,"")</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O31" t="str">
+        <f>IF(PSE!P1&gt;0,PSE!P1,"")</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P31" t="str">
+        <f>IF(PSE!Q1&gt;0,PSE!Q1,"")</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A32" t="str">
+        <f>IF(PSE!A17&gt;0,PSE!A17,"")</f>
+        <v>Staff</v>
+      </c>
+      <c r="B32" t="str">
+        <f>IF(PSE!C17&gt;0,PSE!C17,"")</f>
+        <v/>
+      </c>
+      <c r="C32" t="str">
+        <f>IF(PSE!D17&gt;0,PSE!D17,"")</f>
+        <v/>
+      </c>
+      <c r="D32">
+        <f>IF(PSE!E17&gt;0,PSE!E17,"")</f>
+        <v>1</v>
+      </c>
+      <c r="E32">
+        <f>IF(PSE!F17&gt;0,PSE!F17,"")</f>
+        <v>3</v>
+      </c>
+      <c r="F32">
+        <f>IF(PSE!G17&gt;0,PSE!G17,"")</f>
+        <v>3</v>
+      </c>
+      <c r="G32">
+        <f>IF(PSE!H17&gt;0,PSE!H17,"")</f>
+        <v>3</v>
+      </c>
+      <c r="H32">
+        <f>IF(PSE!I17&gt;0,PSE!I17,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I32">
+        <f>IF(PSE!J17&gt;0,PSE!J17,"")</f>
+        <v>3</v>
+      </c>
+      <c r="J32">
+        <f>IF(PSE!K17&gt;0,PSE!K17,"")</f>
+        <v>3</v>
+      </c>
+      <c r="K32">
+        <f>IF(PSE!L17&gt;0,PSE!L17,"")</f>
+        <v>3</v>
+      </c>
+      <c r="L32">
+        <f>IF(PSE!M17&gt;0,PSE!M17,"")</f>
+        <v>3</v>
+      </c>
+      <c r="M32">
+        <f>IF(PSE!N17&gt;0,PSE!N17,"")</f>
+        <v>3</v>
+      </c>
+      <c r="N32">
+        <f>IF(PSE!O17&gt;0,PSE!O17,"")</f>
+        <v>3</v>
+      </c>
+      <c r="O32">
+        <f>IF(PSE!P17&gt;0,PSE!P17,"")</f>
+        <v>3</v>
+      </c>
+      <c r="P32">
+        <f>IF(PSE!Q17&gt;0,PSE!Q17,"")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A33" t="str">
+        <f>IF(PSE!A18&gt;0,PSE!A18,"")</f>
+        <v>Staff AVG</v>
+      </c>
+      <c r="B33">
+        <f>IF(PSE!C18&gt;0,PSE!C18,"")</f>
+        <v>2</v>
+      </c>
+      <c r="C33">
+        <f>IF(PSE!D18&gt;0,PSE!D18,"")</f>
+        <v>2</v>
+      </c>
+      <c r="D33">
+        <f>IF(PSE!E18&gt;0,PSE!E18,"")</f>
+        <v>2</v>
+      </c>
+      <c r="E33">
+        <f>IF(PSE!F18&gt;0,PSE!F18,"")</f>
+        <v>2</v>
+      </c>
+      <c r="F33">
+        <f>IF(PSE!G18&gt;0,PSE!G18,"")</f>
+        <v>2</v>
+      </c>
+      <c r="G33">
+        <f>IF(PSE!H18&gt;0,PSE!H18,"")</f>
+        <v>2</v>
+      </c>
+      <c r="H33">
+        <f>IF(PSE!I18&gt;0,PSE!I18,"")</f>
+        <v>2</v>
+      </c>
+      <c r="I33">
+        <f>IF(PSE!J18&gt;0,PSE!J18,"")</f>
+        <v>2</v>
+      </c>
+      <c r="J33">
+        <f>IF(PSE!K18&gt;0,PSE!K18,"")</f>
+        <v>2</v>
+      </c>
+      <c r="K33">
+        <f>IF(PSE!L18&gt;0,PSE!L18,"")</f>
+        <v>2</v>
+      </c>
+      <c r="L33">
+        <f>IF(PSE!M18&gt;0,PSE!M18,"")</f>
+        <v>2</v>
+      </c>
+      <c r="M33">
+        <f>IF(PSE!N18&gt;0,PSE!N18,"")</f>
+        <v>2</v>
+      </c>
+      <c r="N33">
+        <f>IF(PSE!O18&gt;0,PSE!O18,"")</f>
+        <v>2</v>
+      </c>
+      <c r="O33">
+        <f>IF(PSE!P18&gt;0,PSE!P18,"")</f>
+        <v>2</v>
+      </c>
+      <c r="P33">
+        <f>IF(PSE!Q18&gt;0,PSE!Q18,"")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A34" t="str">
+        <f>IF(PSE!A19&gt;0,PSE!A19,"")</f>
+        <v>Plan</v>
+      </c>
+      <c r="B34" t="str">
+        <f>IF(PSE!C19&gt;0,PSE!C19,"")</f>
+        <v/>
+      </c>
+      <c r="C34" t="str">
+        <f>IF(PSE!D19&gt;0,PSE!D19,"")</f>
+        <v/>
+      </c>
+      <c r="D34" t="str">
+        <f>IF(PSE!E19&gt;0,PSE!E19,"")</f>
+        <v/>
+      </c>
+      <c r="E34">
+        <f>IF(PSE!F19&gt;0,PSE!F19,"")</f>
+        <v>1</v>
+      </c>
+      <c r="F34">
+        <f>IF(PSE!G19&gt;0,PSE!G19,"")</f>
+        <v>3</v>
+      </c>
+      <c r="G34">
+        <f>IF(PSE!H19&gt;0,PSE!H19,"")</f>
+        <v>3</v>
+      </c>
+      <c r="H34">
+        <f>IF(PSE!I19&gt;0,PSE!I19,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I34">
+        <f>IF(PSE!J19&gt;0,PSE!J19,"")</f>
+        <v>3</v>
+      </c>
+      <c r="J34">
+        <f>IF(PSE!K19&gt;0,PSE!K19,"")</f>
+        <v>3</v>
+      </c>
+      <c r="K34">
+        <f>IF(PSE!L19&gt;0,PSE!L19,"")</f>
+        <v>2</v>
+      </c>
+      <c r="L34">
+        <f>IF(PSE!M19&gt;0,PSE!M19,"")</f>
+        <v>2</v>
+      </c>
+      <c r="M34">
+        <f>IF(PSE!N19&gt;0,PSE!N19,"")</f>
+        <v>2</v>
+      </c>
+      <c r="N34" t="str">
+        <f>IF(PSE!O19&gt;0,PSE!O19,"")</f>
+        <v/>
+      </c>
+      <c r="O34" t="str">
+        <f>IF(PSE!P19&gt;0,PSE!P19,"")</f>
+        <v/>
+      </c>
+      <c r="P34" t="str">
+        <f>IF(PSE!Q19&gt;0,PSE!Q19,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B41" t="str">
+        <f>IF(PSE!C31&gt;0,PSE!C31,"")</f>
+        <v>Q1</v>
+      </c>
+      <c r="C41" t="str">
+        <f>IF(PSE!D31&gt;0,PSE!D31,"")</f>
+        <v>Q2</v>
+      </c>
+      <c r="D41" t="str">
+        <f>IF(PSE!E31&gt;0,PSE!E31,"")</f>
+        <v>Q3</v>
+      </c>
+      <c r="E41" t="str">
+        <f>IF(PSE!F31&gt;0,PSE!F31,"")</f>
+        <v>Q4</v>
+      </c>
+      <c r="F41" t="str">
+        <f>IF(PSE!G31&gt;0,PSE!G31,"")</f>
+        <v>Q1'27</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A42" t="str">
+        <f>IF(PSE!B32&gt;0,PSE!B32,"")</f>
+        <v>Staff</v>
+      </c>
+      <c r="B42">
+        <f>IF(PSE!C32&gt;0,PSE!C32,"")</f>
+        <v>45</v>
+      </c>
+      <c r="C42">
+        <f>IF(PSE!D32&gt;0,PSE!D32,"")</f>
+        <v>48</v>
+      </c>
+      <c r="D42">
+        <f>IF(PSE!E32&gt;0,PSE!E32,"")</f>
+        <v>48</v>
+      </c>
+      <c r="E42">
+        <f>IF(PSE!F32&gt;0,PSE!F32,"")</f>
+        <v>48</v>
+      </c>
+      <c r="F42">
+        <f>IF(PSE!G32&gt;0,PSE!G32,"")</f>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A43" t="str">
+        <f>IF(PSE!B33&gt;0,PSE!B33,"")</f>
+        <v>Staff AVG</v>
+      </c>
+      <c r="B43">
+        <f>IF(PSE!C33&gt;0,PSE!C33,"")</f>
+        <v>47</v>
+      </c>
+      <c r="C43">
+        <f>IF(PSE!D33&gt;0,PSE!D33,"")</f>
+        <v>48</v>
+      </c>
+      <c r="D43">
+        <f>IF(PSE!E33&gt;0,PSE!E33,"")</f>
+        <v>48</v>
+      </c>
+      <c r="E43">
+        <f>IF(PSE!F33&gt;0,PSE!F33,"")</f>
+        <v>48</v>
+      </c>
+      <c r="F43">
+        <f>IF(PSE!G33&gt;0,PSE!G33,"")</f>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A44" t="str">
+        <f>IF(PSE!B34&gt;0,PSE!B34,"")</f>
+        <v>Plan</v>
+      </c>
+      <c r="B44">
+        <f>IF(PSE!C34&gt;0,PSE!C34,"")</f>
+        <v>42</v>
+      </c>
+      <c r="C44">
+        <f>IF(PSE!D34&gt;0,PSE!D34,"")</f>
+        <v>45</v>
+      </c>
+      <c r="D44">
+        <f>IF(PSE!E34&gt;0,PSE!E34,"")</f>
+        <v>45</v>
+      </c>
+      <c r="E44">
+        <f>IF(PSE!F34&gt;0,PSE!F34,"")</f>
+        <v>41</v>
+      </c>
+      <c r="F44">
+        <f>IF(PSE!G34&gt;0,PSE!G34,"")</f>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A45" t="str">
+        <f>IF(PSE!B41&gt;0,PSE!B41,"")</f>
+        <v>PAYROLL</v>
+      </c>
+      <c r="B45">
+        <f>IF(PSE!C41&gt;0,PSE!C41,"")</f>
+        <v>26</v>
+      </c>
+      <c r="C45">
+        <f>IF(PSE!D41&gt;0,PSE!D41,"")</f>
+        <v>27</v>
+      </c>
+      <c r="D45">
+        <f>IF(PSE!E41&gt;0,PSE!E41,"")</f>
+        <v>26</v>
+      </c>
+      <c r="E45">
+        <f>IF(PSE!F41&gt;0,PSE!F41,"")</f>
+        <v>24</v>
+      </c>
+      <c r="F45">
+        <f>IF(PSE!G41&gt;0,PSE!G41,"")</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A46" t="str">
+        <f>IF(PSE!B45&gt;0,PSE!B45,"")</f>
+        <v>CONTRACTOR</v>
+      </c>
+      <c r="B46">
+        <f>IF(PSE!C45&gt;0,PSE!C45,"")</f>
+        <v>17</v>
+      </c>
+      <c r="C46">
+        <f>IF(PSE!D45&gt;0,PSE!D45,"")</f>
+        <v>17</v>
+      </c>
+      <c r="D46">
+        <f>IF(PSE!E45&gt;0,PSE!E45,"")</f>
+        <v>16</v>
+      </c>
+      <c r="E46">
+        <f>IF(PSE!F45&gt;0,PSE!F45,"")</f>
+        <v>15</v>
+      </c>
+      <c r="F46">
+        <f>IF(PSE!G45&gt;0,PSE!G45,"")</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A47" t="str">
+        <f>IF(PSE!B49&gt;0,PSE!B49,"")</f>
+        <v>OUTSOURCE</v>
+      </c>
+      <c r="B47" t="str">
+        <f>IF(PSE!C49&gt;0,PSE!C49,"")</f>
+        <v/>
+      </c>
+      <c r="C47">
+        <f>IF(PSE!D49&gt;0,PSE!D49,"")</f>
+        <v>2</v>
+      </c>
+      <c r="D47">
+        <f>IF(PSE!E49&gt;0,PSE!E49,"")</f>
+        <v>3</v>
+      </c>
+      <c r="E47">
+        <f>IF(PSE!F49&gt;0,PSE!F49,"")</f>
+        <v>2</v>
+      </c>
+      <c r="F47">
+        <f>IF(PSE!G49&gt;0,PSE!G49,"")</f>
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D735CCF-D520-E042-A4A6-56A7360DBCC0}">
+  <sheetPr>
+    <tabColor theme="8"/>
+  </sheetPr>
+  <dimension ref="A1:Q49"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1" s="17"/>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A2" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="8">
+        <v>43</v>
+      </c>
+      <c r="D2" s="8">
+        <v>45</v>
+      </c>
+      <c r="E2" s="8">
+        <v>46</v>
+      </c>
+      <c r="F2" s="8">
+        <v>46</v>
+      </c>
+      <c r="G2" s="8">
+        <v>46</v>
+      </c>
+      <c r="H2" s="8">
+        <v>46</v>
+      </c>
+      <c r="I2" s="8">
+        <v>46</v>
+      </c>
+      <c r="J2" s="8">
+        <v>46</v>
+      </c>
+      <c r="K2" s="8">
+        <v>46</v>
+      </c>
+      <c r="L2" s="8">
+        <v>46</v>
+      </c>
+      <c r="M2" s="8">
+        <v>46</v>
+      </c>
+      <c r="N2" s="8">
+        <v>46</v>
+      </c>
+      <c r="O2" s="8">
+        <v>46</v>
+      </c>
+      <c r="P2" s="8">
+        <v>46</v>
+      </c>
+      <c r="Q2" s="8">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A3" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="8">
+        <v>46</v>
+      </c>
+      <c r="D3" s="8">
+        <v>46</v>
+      </c>
+      <c r="E3" s="8">
+        <v>46</v>
+      </c>
+      <c r="F3" s="8">
+        <v>46</v>
+      </c>
+      <c r="G3" s="8">
+        <v>46</v>
+      </c>
+      <c r="H3" s="8">
+        <v>46</v>
+      </c>
+      <c r="I3" s="8">
+        <v>46</v>
+      </c>
+      <c r="J3" s="8">
+        <v>46</v>
+      </c>
+      <c r="K3" s="8">
+        <v>46</v>
+      </c>
+      <c r="L3" s="8">
+        <v>46</v>
+      </c>
+      <c r="M3" s="8">
+        <v>46</v>
+      </c>
+      <c r="N3" s="8">
+        <v>46</v>
+      </c>
+      <c r="O3" s="8">
+        <v>46</v>
+      </c>
+      <c r="P3" s="8">
+        <v>46</v>
+      </c>
+      <c r="Q3" s="8">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A4" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="8">
+        <v>40</v>
+      </c>
+      <c r="D4" s="14">
+        <v>46</v>
+      </c>
+      <c r="E4" s="14">
+        <v>48</v>
+      </c>
+      <c r="F4" s="8">
+        <v>44</v>
+      </c>
+      <c r="G4" s="14">
+        <v>46</v>
+      </c>
+      <c r="H4" s="14">
+        <v>46</v>
+      </c>
+      <c r="I4" s="14">
+        <v>48</v>
+      </c>
+      <c r="J4" s="14">
+        <v>46</v>
+      </c>
+      <c r="K4" s="8">
+        <v>45</v>
+      </c>
+      <c r="L4" s="8">
+        <v>42</v>
+      </c>
+      <c r="M4" s="8">
+        <v>42</v>
+      </c>
+      <c r="N4" s="8">
+        <v>42</v>
+      </c>
+      <c r="O4" s="8">
+        <v>32</v>
+      </c>
+      <c r="P4" s="8">
+        <v>32</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A5" s="17"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
+      <c r="Q5" s="8"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A6" s="8"/>
+      <c r="B6" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="19">
+        <v>0.94089999999999996</v>
+      </c>
+      <c r="D6" s="19">
+        <v>1.0186999999999999</v>
+      </c>
+      <c r="E6" s="19">
+        <v>1.0399</v>
+      </c>
+      <c r="F6" s="19">
+        <v>0.95079999999999998</v>
+      </c>
+      <c r="G6" s="19">
+        <v>1.0044999999999999</v>
+      </c>
+      <c r="H6" s="19">
+        <v>1.0102</v>
+      </c>
+      <c r="I6" s="19">
+        <v>1.0387</v>
+      </c>
+      <c r="J6" s="19">
+        <v>1.0035000000000001</v>
+      </c>
+      <c r="K6" s="19">
+        <v>0.98709999999999998</v>
+      </c>
+      <c r="L6" s="19">
+        <v>0.92390000000000005</v>
+      </c>
+      <c r="M6" s="19">
+        <v>0.91090000000000004</v>
+      </c>
+      <c r="N6" s="19">
+        <v>0.9022</v>
+      </c>
+      <c r="O6" s="19">
+        <v>0.70440000000000003</v>
+      </c>
+      <c r="P6" s="19">
+        <v>0.69789999999999996</v>
+      </c>
+      <c r="Q6" s="19">
+        <v>0.69789999999999996</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A7" s="17"/>
+      <c r="B7" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="20">
+        <v>3</v>
+      </c>
+      <c r="D7" s="20">
+        <v>-1</v>
+      </c>
+      <c r="E7" s="20">
+        <v>-2</v>
+      </c>
+      <c r="F7" s="20">
+        <v>2</v>
+      </c>
+      <c r="G7" s="20">
+        <v>0</v>
+      </c>
+      <c r="H7" s="20">
+        <v>0</v>
+      </c>
+      <c r="I7" s="20">
+        <v>-2</v>
+      </c>
+      <c r="J7" s="20">
+        <v>0</v>
+      </c>
+      <c r="K7" s="20">
+        <v>1</v>
+      </c>
+      <c r="L7" s="20">
+        <v>4</v>
+      </c>
+      <c r="M7" s="20">
+        <v>4</v>
+      </c>
+      <c r="N7" s="20">
+        <v>4</v>
+      </c>
+      <c r="O7" s="20">
+        <v>14</v>
+      </c>
+      <c r="P7" s="20">
+        <v>14</v>
+      </c>
+      <c r="Q7" s="20">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A8" s="17"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A9" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="8">
+        <v>35</v>
+      </c>
+      <c r="D9" s="8">
+        <v>35</v>
+      </c>
+      <c r="E9" s="8">
+        <v>35</v>
+      </c>
+      <c r="F9" s="8">
+        <v>35</v>
+      </c>
+      <c r="G9" s="8">
+        <v>35</v>
+      </c>
+      <c r="H9" s="8">
+        <v>35</v>
+      </c>
+      <c r="I9" s="8">
+        <v>35</v>
+      </c>
+      <c r="J9" s="8">
+        <v>35</v>
+      </c>
+      <c r="K9" s="8">
+        <v>35</v>
+      </c>
+      <c r="L9" s="8">
+        <v>35</v>
+      </c>
+      <c r="M9" s="8">
+        <v>35</v>
+      </c>
+      <c r="N9" s="8">
+        <v>35</v>
+      </c>
+      <c r="O9" s="8">
+        <v>35</v>
+      </c>
+      <c r="P9" s="8">
+        <v>35</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A10" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="8">
+        <v>35</v>
+      </c>
+      <c r="D10" s="8">
+        <v>35</v>
+      </c>
+      <c r="E10" s="8">
+        <v>35</v>
+      </c>
+      <c r="F10" s="8">
+        <v>35</v>
+      </c>
+      <c r="G10" s="8">
+        <v>35</v>
+      </c>
+      <c r="H10" s="8">
+        <v>35</v>
+      </c>
+      <c r="I10" s="8">
+        <v>35</v>
+      </c>
+      <c r="J10" s="8">
+        <v>35</v>
+      </c>
+      <c r="K10" s="8">
+        <v>35</v>
+      </c>
+      <c r="L10" s="8">
+        <v>35</v>
+      </c>
+      <c r="M10" s="8">
+        <v>35</v>
+      </c>
+      <c r="N10" s="8">
+        <v>35</v>
+      </c>
+      <c r="O10" s="8">
+        <v>35</v>
+      </c>
+      <c r="P10" s="8">
+        <v>35</v>
+      </c>
+      <c r="Q10" s="8">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A11" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="8">
+        <v>33</v>
+      </c>
+      <c r="D11" s="14">
+        <v>35</v>
+      </c>
+      <c r="E11" s="14">
+        <v>36</v>
+      </c>
+      <c r="F11" s="8">
+        <v>33</v>
+      </c>
+      <c r="G11" s="8">
+        <v>34</v>
+      </c>
+      <c r="H11" s="8">
+        <v>34</v>
+      </c>
+      <c r="I11" s="8">
+        <v>33</v>
+      </c>
+      <c r="J11" s="8">
+        <v>32</v>
+      </c>
+      <c r="K11" s="8">
+        <v>31</v>
+      </c>
+      <c r="L11" s="8">
+        <v>30</v>
+      </c>
+      <c r="M11" s="8">
+        <v>30</v>
+      </c>
+      <c r="N11" s="8">
+        <v>29</v>
+      </c>
+      <c r="O11" s="8">
+        <v>23</v>
+      </c>
+      <c r="P11" s="8">
+        <v>23</v>
+      </c>
+      <c r="Q11" s="8">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A12" s="8"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
+      <c r="Q12" s="8"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A13" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="8">
+        <v>2</v>
+      </c>
+      <c r="D13" s="8">
+        <v>2</v>
+      </c>
+      <c r="E13" s="8">
+        <v>2</v>
+      </c>
+      <c r="F13" s="8">
+        <v>2</v>
+      </c>
+      <c r="G13" s="8">
+        <v>2</v>
+      </c>
+      <c r="H13" s="8">
+        <v>2</v>
+      </c>
+      <c r="I13" s="8">
+        <v>2</v>
+      </c>
+      <c r="J13" s="8">
+        <v>2</v>
+      </c>
+      <c r="K13" s="8">
+        <v>2</v>
+      </c>
+      <c r="L13" s="8">
+        <v>2</v>
+      </c>
+      <c r="M13" s="8">
+        <v>2</v>
+      </c>
+      <c r="N13" s="8">
+        <v>2</v>
+      </c>
+      <c r="O13" s="8">
+        <v>2</v>
+      </c>
+      <c r="P13" s="8">
+        <v>2</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A14" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="8">
+        <v>2</v>
+      </c>
+      <c r="D14" s="8">
+        <v>2</v>
+      </c>
+      <c r="E14" s="8">
+        <v>2</v>
+      </c>
+      <c r="F14" s="8">
+        <v>2</v>
+      </c>
+      <c r="G14" s="8">
+        <v>2</v>
+      </c>
+      <c r="H14" s="8">
+        <v>2</v>
+      </c>
+      <c r="I14" s="8">
+        <v>2</v>
+      </c>
+      <c r="J14" s="8">
+        <v>2</v>
+      </c>
+      <c r="K14" s="8">
+        <v>2</v>
+      </c>
+      <c r="L14" s="8">
+        <v>2</v>
+      </c>
+      <c r="M14" s="8">
+        <v>2</v>
+      </c>
+      <c r="N14" s="8">
+        <v>2</v>
+      </c>
+      <c r="O14" s="8">
+        <v>2</v>
+      </c>
+      <c r="P14" s="8">
+        <v>2</v>
+      </c>
+      <c r="Q14" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A15" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="8">
+        <v>2</v>
+      </c>
+      <c r="D15" s="8">
+        <v>2</v>
+      </c>
+      <c r="E15" s="8">
+        <v>2</v>
+      </c>
+      <c r="F15" s="8">
+        <v>2</v>
+      </c>
+      <c r="G15" s="8">
+        <v>2</v>
+      </c>
+      <c r="H15" s="8">
+        <v>2</v>
+      </c>
+      <c r="I15" s="8">
+        <v>2</v>
+      </c>
+      <c r="J15" s="8">
+        <v>2</v>
+      </c>
+      <c r="K15" s="8">
+        <v>2</v>
+      </c>
+      <c r="L15" s="8">
+        <v>2</v>
+      </c>
+      <c r="M15" s="8">
+        <v>2</v>
+      </c>
+      <c r="N15" s="8">
+        <v>2</v>
+      </c>
+      <c r="O15" s="8">
+        <v>2</v>
+      </c>
+      <c r="P15" s="8">
+        <v>2</v>
+      </c>
+      <c r="Q15" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A16" s="8"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="8"/>
+      <c r="Q16" s="8"/>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A17" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="8">
+        <v>6</v>
+      </c>
+      <c r="D17" s="8">
+        <v>8</v>
+      </c>
+      <c r="E17" s="8">
+        <v>9</v>
+      </c>
+      <c r="F17" s="8">
+        <v>9</v>
+      </c>
+      <c r="G17" s="8">
+        <v>9</v>
+      </c>
+      <c r="H17" s="8">
+        <v>9</v>
+      </c>
+      <c r="I17" s="8">
+        <v>9</v>
+      </c>
+      <c r="J17" s="8">
+        <v>9</v>
+      </c>
+      <c r="K17" s="8">
+        <v>9</v>
+      </c>
+      <c r="L17" s="8">
+        <v>9</v>
+      </c>
+      <c r="M17" s="8">
+        <v>9</v>
+      </c>
+      <c r="N17" s="8">
+        <v>9</v>
+      </c>
+      <c r="O17" s="8">
+        <v>9</v>
+      </c>
+      <c r="P17" s="8">
+        <v>9</v>
+      </c>
+      <c r="Q17" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A18" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="8">
+        <v>9</v>
+      </c>
+      <c r="D18" s="8">
+        <v>9</v>
+      </c>
+      <c r="E18" s="8">
+        <v>9</v>
+      </c>
+      <c r="F18" s="8">
+        <v>9</v>
+      </c>
+      <c r="G18" s="8">
+        <v>9</v>
+      </c>
+      <c r="H18" s="8">
+        <v>9</v>
+      </c>
+      <c r="I18" s="8">
+        <v>9</v>
+      </c>
+      <c r="J18" s="8">
+        <v>9</v>
+      </c>
+      <c r="K18" s="8">
+        <v>9</v>
+      </c>
+      <c r="L18" s="8">
+        <v>9</v>
+      </c>
+      <c r="M18" s="8">
+        <v>9</v>
+      </c>
+      <c r="N18" s="8">
+        <v>9</v>
+      </c>
+      <c r="O18" s="8">
+        <v>9</v>
+      </c>
+      <c r="P18" s="8">
+        <v>9</v>
+      </c>
+      <c r="Q18" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A19" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="8">
+        <v>6</v>
+      </c>
+      <c r="D19" s="14">
+        <v>8</v>
+      </c>
+      <c r="E19" s="14">
+        <v>10</v>
+      </c>
+      <c r="F19" s="8">
+        <v>9</v>
+      </c>
+      <c r="G19" s="14">
+        <v>10</v>
+      </c>
+      <c r="H19" s="14">
+        <v>11</v>
+      </c>
+      <c r="I19" s="14">
+        <v>12</v>
+      </c>
+      <c r="J19" s="14">
+        <v>12</v>
+      </c>
+      <c r="K19" s="14">
+        <v>13</v>
+      </c>
+      <c r="L19" s="14">
+        <v>10</v>
+      </c>
+      <c r="M19" s="14">
+        <v>10</v>
+      </c>
+      <c r="N19" s="14">
+        <v>10</v>
+      </c>
+      <c r="O19" s="8">
+        <v>7</v>
+      </c>
+      <c r="P19" s="8">
+        <v>7</v>
+      </c>
+      <c r="Q19" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A31" s="17"/>
+      <c r="B31" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C31" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="D31" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="E31" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F31" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="G31" s="24" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A32" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" s="26">
+        <v>45</v>
+      </c>
+      <c r="D32" s="21">
+        <v>46</v>
+      </c>
+      <c r="E32" s="21">
+        <v>46</v>
+      </c>
+      <c r="F32" s="21">
+        <v>46</v>
+      </c>
+      <c r="G32" s="21">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="26">
+        <v>46</v>
+      </c>
+      <c r="D33" s="21">
+        <v>46</v>
+      </c>
+      <c r="E33" s="21">
+        <v>46</v>
+      </c>
+      <c r="F33" s="21">
+        <v>46</v>
+      </c>
+      <c r="G33" s="21">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="32">
+        <v>45</v>
+      </c>
+      <c r="D34" s="21">
+        <v>45</v>
+      </c>
+      <c r="E34" s="14">
+        <v>46</v>
+      </c>
+      <c r="F34" s="21">
+        <v>42</v>
+      </c>
+      <c r="G34" s="21">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="17"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="27">
+        <v>-1E-3</v>
+      </c>
+      <c r="D35" s="28">
+        <v>1.15E-2</v>
+      </c>
+      <c r="E35" s="28">
+        <v>-9.7999999999999997E-3</v>
+      </c>
+      <c r="F35" s="28">
+        <v>8.7599999999999997E-2</v>
+      </c>
+      <c r="G35" s="28">
+        <v>0.1608</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="8"/>
+      <c r="B36" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C36" s="29">
+        <v>1.0009999999999999</v>
+      </c>
+      <c r="D36" s="19">
+        <v>0.98850000000000005</v>
+      </c>
+      <c r="E36" s="19">
+        <v>1.0098</v>
+      </c>
+      <c r="F36" s="19">
+        <v>0.91239999999999999</v>
+      </c>
+      <c r="G36" s="19">
+        <v>0.83919999999999995</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="17"/>
+      <c r="B37" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" s="30">
+        <v>0</v>
+      </c>
+      <c r="D37" s="20">
+        <v>1</v>
+      </c>
+      <c r="E37" s="20">
+        <v>0</v>
+      </c>
+      <c r="F37" s="20">
+        <v>4</v>
+      </c>
+      <c r="G37" s="20">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="17"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="31"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C39" s="26">
+        <v>35</v>
+      </c>
+      <c r="D39" s="21">
+        <v>35</v>
+      </c>
+      <c r="E39" s="21">
+        <v>35</v>
+      </c>
+      <c r="F39" s="21">
+        <v>35</v>
+      </c>
+      <c r="G39" s="21">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A40" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C40" s="26">
+        <v>35</v>
+      </c>
+      <c r="D40" s="21">
+        <v>35</v>
+      </c>
+      <c r="E40" s="21">
+        <v>35</v>
+      </c>
+      <c r="F40" s="21">
+        <v>35</v>
+      </c>
+      <c r="G40" s="21">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A41" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B41" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C41" s="26">
+        <v>35</v>
+      </c>
+      <c r="D41" s="21">
+        <v>34</v>
+      </c>
+      <c r="E41" s="21">
+        <v>32</v>
+      </c>
+      <c r="F41" s="21">
+        <v>30</v>
+      </c>
+      <c r="G41" s="21">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A42" s="8"/>
+      <c r="B42" s="17"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="21"/>
+      <c r="G42" s="21"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A43" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C43" s="26">
+        <v>2</v>
+      </c>
+      <c r="D43" s="21">
+        <v>2</v>
+      </c>
+      <c r="E43" s="21">
+        <v>2</v>
+      </c>
+      <c r="F43" s="21">
+        <v>2</v>
+      </c>
+      <c r="G43" s="21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A44" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" s="26">
+        <v>2</v>
+      </c>
+      <c r="D44" s="21">
+        <v>2</v>
+      </c>
+      <c r="E44" s="21">
+        <v>2</v>
+      </c>
+      <c r="F44" s="21">
+        <v>2</v>
+      </c>
+      <c r="G44" s="21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A45" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B45" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C45" s="26">
+        <v>2</v>
+      </c>
+      <c r="D45" s="21">
+        <v>2</v>
+      </c>
+      <c r="E45" s="21">
+        <v>2</v>
+      </c>
+      <c r="F45" s="21">
+        <v>2</v>
+      </c>
+      <c r="G45" s="21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A46" s="8"/>
+      <c r="B46" s="17"/>
+      <c r="C46" s="26"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="21"/>
+      <c r="F46" s="21"/>
+      <c r="G46" s="21"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A47" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C47" s="26">
+        <v>8</v>
+      </c>
+      <c r="D47" s="21">
+        <v>9</v>
+      </c>
+      <c r="E47" s="21">
+        <v>9</v>
+      </c>
+      <c r="F47" s="21">
+        <v>9</v>
+      </c>
+      <c r="G47" s="21">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A48" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C48" s="26">
+        <v>9</v>
+      </c>
+      <c r="D48" s="21">
+        <v>9</v>
+      </c>
+      <c r="E48" s="21">
+        <v>9</v>
+      </c>
+      <c r="F48" s="21">
+        <v>9</v>
+      </c>
+      <c r="G48" s="21">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A49" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B49" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C49" s="32">
+        <v>8</v>
+      </c>
+      <c r="D49" s="14">
+        <v>10</v>
+      </c>
+      <c r="E49" s="14">
+        <v>12</v>
+      </c>
+      <c r="F49" s="14">
+        <v>10</v>
+      </c>
+      <c r="G49" s="14">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E4DECC7-A84D-544D-B660-F6AF46B2986D}">
+  <sheetPr>
+    <tabColor theme="8" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:P47"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B1" t="str">
+        <f>IF(SD!C1&gt;0,SD!C1,"")</f>
+        <v>JAN</v>
+      </c>
+      <c r="C1" t="str">
+        <f>IF(SD!D1&gt;0,SD!D1,"")</f>
+        <v>FEB</v>
+      </c>
+      <c r="D1" t="str">
+        <f>IF(SD!E1&gt;0,SD!E1,"")</f>
+        <v>MAR</v>
+      </c>
+      <c r="E1" t="str">
+        <f>IF(SD!F1&gt;0,SD!F1,"")</f>
+        <v>APR</v>
+      </c>
+      <c r="F1" t="str">
+        <f>IF(SD!G1&gt;0,SD!G1,"")</f>
+        <v>MAY</v>
+      </c>
+      <c r="G1" t="str">
+        <f>IF(SD!H1&gt;0,SD!H1,"")</f>
+        <v>JUN</v>
+      </c>
+      <c r="H1" t="str">
+        <f>IF(SD!I1&gt;0,SD!I1,"")</f>
+        <v>JUL</v>
+      </c>
+      <c r="I1" t="str">
+        <f>IF(SD!J1&gt;0,SD!J1,"")</f>
+        <v>AUG</v>
+      </c>
+      <c r="J1" t="str">
+        <f>IF(SD!K1&gt;0,SD!K1,"")</f>
+        <v>SEP</v>
+      </c>
+      <c r="K1" t="str">
+        <f>IF(SD!L1&gt;0,SD!L1,"")</f>
+        <v>OCT</v>
+      </c>
+      <c r="L1" t="str">
+        <f>IF(SD!M1&gt;0,SD!M1,"")</f>
+        <v>NOV</v>
+      </c>
+      <c r="M1" t="str">
+        <f>IF(SD!N1&gt;0,SD!N1,"")</f>
+        <v>DEC</v>
+      </c>
+      <c r="N1" t="str">
+        <f>IF(SD!O1&gt;0,SD!O1,"")</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O1" t="str">
+        <f>IF(SD!P1&gt;0,SD!P1,"")</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P1" t="str">
+        <f>IF(SD!Q1&gt;0,SD!Q1,"")</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A2" t="str">
+        <f>IF(SD!B2&gt;0,SD!B2,"")</f>
+        <v>Staff</v>
+      </c>
+      <c r="B2">
+        <f>IF(SD!C2&gt;0,SD!C2,"")</f>
+        <v>43</v>
+      </c>
+      <c r="C2">
+        <f>IF(SD!D2&gt;0,SD!D2,"")</f>
+        <v>45</v>
+      </c>
+      <c r="D2">
+        <f>IF(SD!E2&gt;0,SD!E2,"")</f>
+        <v>46</v>
+      </c>
+      <c r="E2">
+        <f>IF(SD!F2&gt;0,SD!F2,"")</f>
+        <v>46</v>
+      </c>
+      <c r="F2">
+        <f>IF(SD!G2&gt;0,SD!G2,"")</f>
+        <v>46</v>
+      </c>
+      <c r="G2">
+        <f>IF(SD!H2&gt;0,SD!H2,"")</f>
+        <v>46</v>
+      </c>
+      <c r="H2">
+        <f>IF(SD!I2&gt;0,SD!I2,"")</f>
+        <v>46</v>
+      </c>
+      <c r="I2">
+        <f>IF(SD!J2&gt;0,SD!J2,"")</f>
+        <v>46</v>
+      </c>
+      <c r="J2">
+        <f>IF(SD!K2&gt;0,SD!K2,"")</f>
+        <v>46</v>
+      </c>
+      <c r="K2">
+        <f>IF(SD!L2&gt;0,SD!L2,"")</f>
+        <v>46</v>
+      </c>
+      <c r="L2">
+        <f>IF(SD!M2&gt;0,SD!M2,"")</f>
+        <v>46</v>
+      </c>
+      <c r="M2">
+        <f>IF(SD!N2&gt;0,SD!N2,"")</f>
+        <v>46</v>
+      </c>
+      <c r="N2">
+        <f>IF(SD!O2&gt;0,SD!O2,"")</f>
+        <v>46</v>
+      </c>
+      <c r="O2">
+        <f>IF(SD!P2&gt;0,SD!P2,"")</f>
+        <v>46</v>
+      </c>
+      <c r="P2">
+        <f>IF(SD!Q2&gt;0,SD!Q2,"")</f>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A3" t="str">
+        <f>IF(SD!B3&gt;0,SD!B3,"")</f>
+        <v>Staff AVG</v>
+      </c>
+      <c r="B3">
+        <f>IF(SD!C3&gt;0,SD!C3,"")</f>
+        <v>46</v>
+      </c>
+      <c r="C3">
+        <f>IF(SD!D3&gt;0,SD!D3,"")</f>
+        <v>46</v>
+      </c>
+      <c r="D3">
+        <f>IF(SD!E3&gt;0,SD!E3,"")</f>
+        <v>46</v>
+      </c>
+      <c r="E3">
+        <f>IF(SD!F3&gt;0,SD!F3,"")</f>
+        <v>46</v>
+      </c>
+      <c r="F3">
+        <f>IF(SD!G3&gt;0,SD!G3,"")</f>
+        <v>46</v>
+      </c>
+      <c r="G3">
+        <f>IF(SD!H3&gt;0,SD!H3,"")</f>
+        <v>46</v>
+      </c>
+      <c r="H3">
+        <f>IF(SD!I3&gt;0,SD!I3,"")</f>
+        <v>46</v>
+      </c>
+      <c r="I3">
+        <f>IF(SD!J3&gt;0,SD!J3,"")</f>
+        <v>46</v>
+      </c>
+      <c r="J3">
+        <f>IF(SD!K3&gt;0,SD!K3,"")</f>
+        <v>46</v>
+      </c>
+      <c r="K3">
+        <f>IF(SD!L3&gt;0,SD!L3,"")</f>
+        <v>46</v>
+      </c>
+      <c r="L3">
+        <f>IF(SD!M3&gt;0,SD!M3,"")</f>
+        <v>46</v>
+      </c>
+      <c r="M3">
+        <f>IF(SD!N3&gt;0,SD!N3,"")</f>
+        <v>46</v>
+      </c>
+      <c r="N3">
+        <f>IF(SD!O3&gt;0,SD!O3,"")</f>
+        <v>46</v>
+      </c>
+      <c r="O3">
+        <f>IF(SD!P3&gt;0,SD!P3,"")</f>
+        <v>46</v>
+      </c>
+      <c r="P3">
+        <f>IF(SD!Q3&gt;0,SD!Q3,"")</f>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A4" t="str">
+        <f>IF(SD!B4&gt;0,SD!B4,"")</f>
+        <v>Plan</v>
+      </c>
+      <c r="B4">
+        <f>IF(SD!C4&gt;0,SD!C4,"")</f>
+        <v>40</v>
+      </c>
+      <c r="C4">
+        <f>IF(SD!D4&gt;0,SD!D4,"")</f>
+        <v>46</v>
+      </c>
+      <c r="D4">
+        <f>IF(SD!E4&gt;0,SD!E4,"")</f>
+        <v>48</v>
+      </c>
+      <c r="E4">
+        <f>IF(SD!F4&gt;0,SD!F4,"")</f>
+        <v>44</v>
+      </c>
+      <c r="F4">
+        <f>IF(SD!G4&gt;0,SD!G4,"")</f>
+        <v>46</v>
+      </c>
+      <c r="G4">
+        <f>IF(SD!H4&gt;0,SD!H4,"")</f>
+        <v>46</v>
+      </c>
+      <c r="H4">
+        <f>IF(SD!I4&gt;0,SD!I4,"")</f>
+        <v>48</v>
+      </c>
+      <c r="I4">
+        <f>IF(SD!J4&gt;0,SD!J4,"")</f>
+        <v>46</v>
+      </c>
+      <c r="J4">
+        <f>IF(SD!K4&gt;0,SD!K4,"")</f>
+        <v>45</v>
+      </c>
+      <c r="K4">
+        <f>IF(SD!L4&gt;0,SD!L4,"")</f>
+        <v>42</v>
+      </c>
+      <c r="L4">
+        <f>IF(SD!M4&gt;0,SD!M4,"")</f>
+        <v>42</v>
+      </c>
+      <c r="M4">
+        <f>IF(SD!N4&gt;0,SD!N4,"")</f>
+        <v>42</v>
+      </c>
+      <c r="N4">
+        <f>IF(SD!O4&gt;0,SD!O4,"")</f>
+        <v>32</v>
+      </c>
+      <c r="O4">
+        <f>IF(SD!P4&gt;0,SD!P4,"")</f>
+        <v>32</v>
+      </c>
+      <c r="P4">
+        <f>IF(SD!Q4&gt;0,SD!Q4,"")</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A5" t="str">
+        <f>IF(SD!B11&gt;0,SD!B11,"")</f>
+        <v>PAYROLL</v>
+      </c>
+      <c r="B5">
+        <f>IF(SD!C11&gt;0,SD!C11,"")</f>
+        <v>33</v>
+      </c>
+      <c r="C5">
+        <f>IF(SD!D11&gt;0,SD!D11,"")</f>
+        <v>35</v>
+      </c>
+      <c r="D5">
+        <f>IF(SD!E11&gt;0,SD!E11,"")</f>
+        <v>36</v>
+      </c>
+      <c r="E5">
+        <f>IF(SD!F11&gt;0,SD!F11,"")</f>
+        <v>33</v>
+      </c>
+      <c r="F5">
+        <f>IF(SD!G11&gt;0,SD!G11,"")</f>
+        <v>34</v>
+      </c>
+      <c r="G5">
+        <f>IF(SD!H11&gt;0,SD!H11,"")</f>
+        <v>34</v>
+      </c>
+      <c r="H5">
+        <f>IF(SD!I11&gt;0,SD!I11,"")</f>
+        <v>33</v>
+      </c>
+      <c r="I5">
+        <f>IF(SD!J11&gt;0,SD!J11,"")</f>
+        <v>32</v>
+      </c>
+      <c r="J5">
+        <f>IF(SD!K11&gt;0,SD!K11,"")</f>
+        <v>31</v>
+      </c>
+      <c r="K5">
+        <f>IF(SD!L11&gt;0,SD!L11,"")</f>
+        <v>30</v>
+      </c>
+      <c r="L5">
+        <f>IF(SD!M11&gt;0,SD!M11,"")</f>
+        <v>30</v>
+      </c>
+      <c r="M5">
+        <f>IF(SD!N11&gt;0,SD!N11,"")</f>
+        <v>29</v>
+      </c>
+      <c r="N5">
+        <f>IF(SD!O11&gt;0,SD!O11,"")</f>
+        <v>23</v>
+      </c>
+      <c r="O5">
+        <f>IF(SD!P11&gt;0,SD!P11,"")</f>
+        <v>23</v>
+      </c>
+      <c r="P5">
+        <f>IF(SD!Q11&gt;0,SD!Q11,"")</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A6" t="str">
+        <f>IF(SD!B15&gt;0,SD!B15,"")</f>
+        <v>CONTRACTOR</v>
+      </c>
+      <c r="B6">
+        <f>IF(SD!C15&gt;0,SD!C15,"")</f>
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <f>IF(SD!D15&gt;0,SD!D15,"")</f>
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <f>IF(SD!E15&gt;0,SD!E15,"")</f>
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <f>IF(SD!F15&gt;0,SD!F15,"")</f>
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <f>IF(SD!G15&gt;0,SD!G15,"")</f>
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <f>IF(SD!H15&gt;0,SD!H15,"")</f>
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <f>IF(SD!I15&gt;0,SD!I15,"")</f>
+        <v>2</v>
+      </c>
+      <c r="I6">
+        <f>IF(SD!J15&gt;0,SD!J15,"")</f>
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <f>IF(SD!K15&gt;0,SD!K15,"")</f>
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <f>IF(SD!L15&gt;0,SD!L15,"")</f>
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <f>IF(SD!M15&gt;0,SD!M15,"")</f>
+        <v>2</v>
+      </c>
+      <c r="M6">
+        <f>IF(SD!N15&gt;0,SD!N15,"")</f>
+        <v>2</v>
+      </c>
+      <c r="N6">
+        <f>IF(SD!O15&gt;0,SD!O15,"")</f>
+        <v>2</v>
+      </c>
+      <c r="O6">
+        <f>IF(SD!P15&gt;0,SD!P15,"")</f>
+        <v>2</v>
+      </c>
+      <c r="P6">
+        <f>IF(SD!Q15&gt;0,SD!Q15,"")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A7" t="str">
+        <f>IF(SD!B19&gt;0,SD!B19,"")</f>
+        <v>OUTSOURCE</v>
+      </c>
+      <c r="B7">
+        <f>IF(SD!C19&gt;0,SD!C19,"")</f>
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <f>IF(SD!D19&gt;0,SD!D19,"")</f>
+        <v>8</v>
+      </c>
+      <c r="D7">
+        <f>IF(SD!E19&gt;0,SD!E19,"")</f>
+        <v>10</v>
+      </c>
+      <c r="E7">
+        <f>IF(SD!F19&gt;0,SD!F19,"")</f>
+        <v>9</v>
+      </c>
+      <c r="F7">
+        <f>IF(SD!G19&gt;0,SD!G19,"")</f>
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <f>IF(SD!H19&gt;0,SD!H19,"")</f>
+        <v>11</v>
+      </c>
+      <c r="H7">
+        <f>IF(SD!I19&gt;0,SD!I19,"")</f>
+        <v>12</v>
+      </c>
+      <c r="I7">
+        <f>IF(SD!J19&gt;0,SD!J19,"")</f>
+        <v>12</v>
+      </c>
+      <c r="J7">
+        <f>IF(SD!K19&gt;0,SD!K19,"")</f>
+        <v>13</v>
+      </c>
+      <c r="K7">
+        <f>IF(SD!L19&gt;0,SD!L19,"")</f>
+        <v>10</v>
+      </c>
+      <c r="L7">
+        <f>IF(SD!M19&gt;0,SD!M19,"")</f>
+        <v>10</v>
+      </c>
+      <c r="M7">
+        <f>IF(SD!N19&gt;0,SD!N19,"")</f>
+        <v>10</v>
+      </c>
+      <c r="N7">
+        <f>IF(SD!O19&gt;0,SD!O19,"")</f>
+        <v>7</v>
+      </c>
+      <c r="O7">
+        <f>IF(SD!P19&gt;0,SD!P19,"")</f>
+        <v>7</v>
+      </c>
+      <c r="P7">
+        <f>IF(SD!Q19&gt;0,SD!Q19,"")</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B11" t="str">
+        <f>IF(SD!C1&gt;0,SD!C1,"")</f>
+        <v>JAN</v>
+      </c>
+      <c r="C11" t="str">
+        <f>IF(SD!D1&gt;0,SD!D1,"")</f>
+        <v>FEB</v>
+      </c>
+      <c r="D11" t="str">
+        <f>IF(SD!E1&gt;0,SD!E1,"")</f>
+        <v>MAR</v>
+      </c>
+      <c r="E11" t="str">
+        <f>IF(SD!F1&gt;0,SD!F1,"")</f>
+        <v>APR</v>
+      </c>
+      <c r="F11" t="str">
+        <f>IF(SD!G1&gt;0,SD!G1,"")</f>
+        <v>MAY</v>
+      </c>
+      <c r="G11" t="str">
+        <f>IF(SD!H1&gt;0,SD!H1,"")</f>
+        <v>JUN</v>
+      </c>
+      <c r="H11" t="str">
+        <f>IF(SD!I1&gt;0,SD!I1,"")</f>
+        <v>JUL</v>
+      </c>
+      <c r="I11" t="str">
+        <f>IF(SD!J1&gt;0,SD!J1,"")</f>
+        <v>AUG</v>
+      </c>
+      <c r="J11" t="str">
+        <f>IF(SD!K1&gt;0,SD!K1,"")</f>
+        <v>SEP</v>
+      </c>
+      <c r="K11" t="str">
+        <f>IF(SD!L1&gt;0,SD!L1,"")</f>
+        <v>OCT</v>
+      </c>
+      <c r="L11" t="str">
+        <f>IF(SD!M1&gt;0,SD!M1,"")</f>
+        <v>NOV</v>
+      </c>
+      <c r="M11" t="str">
+        <f>IF(SD!N1&gt;0,SD!N1,"")</f>
+        <v>DEC</v>
+      </c>
+      <c r="N11" t="str">
+        <f>IF(SD!O1&gt;0,SD!O1,"")</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O11" t="str">
+        <f>IF(SD!P1&gt;0,SD!P1,"")</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P11" t="str">
+        <f>IF(SD!Q1&gt;0,SD!Q1,"")</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A12" t="str">
+        <f>IF(SD!A9&gt;0,SD!A9,"")</f>
+        <v>Staff</v>
+      </c>
+      <c r="B12">
+        <f>IF(SD!C9&gt;0,SD!C9,"")</f>
+        <v>35</v>
+      </c>
+      <c r="C12">
+        <f>IF(SD!D9&gt;0,SD!D9,"")</f>
+        <v>35</v>
+      </c>
+      <c r="D12">
+        <f>IF(SD!E9&gt;0,SD!E9,"")</f>
+        <v>35</v>
+      </c>
+      <c r="E12">
+        <f>IF(SD!F9&gt;0,SD!F9,"")</f>
+        <v>35</v>
+      </c>
+      <c r="F12">
+        <f>IF(SD!G9&gt;0,SD!G9,"")</f>
+        <v>35</v>
+      </c>
+      <c r="G12">
+        <f>IF(SD!H9&gt;0,SD!H9,"")</f>
+        <v>35</v>
+      </c>
+      <c r="H12">
+        <f>IF(SD!I9&gt;0,SD!I9,"")</f>
+        <v>35</v>
+      </c>
+      <c r="I12">
+        <f>IF(SD!J9&gt;0,SD!J9,"")</f>
+        <v>35</v>
+      </c>
+      <c r="J12">
+        <f>IF(SD!K9&gt;0,SD!K9,"")</f>
+        <v>35</v>
+      </c>
+      <c r="K12">
+        <f>IF(SD!L9&gt;0,SD!L9,"")</f>
+        <v>35</v>
+      </c>
+      <c r="L12">
+        <f>IF(SD!M9&gt;0,SD!M9,"")</f>
+        <v>35</v>
+      </c>
+      <c r="M12">
+        <f>IF(SD!N9&gt;0,SD!N9,"")</f>
+        <v>35</v>
+      </c>
+      <c r="N12">
+        <f>IF(SD!O9&gt;0,SD!O9,"")</f>
+        <v>35</v>
+      </c>
+      <c r="O12">
+        <f>IF(SD!P9&gt;0,SD!P9,"")</f>
+        <v>35</v>
+      </c>
+      <c r="P12">
+        <f>IF(SD!Q9&gt;0,SD!Q9,"")</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A13" t="str">
+        <f>IF(SD!A10&gt;0,SD!A10,"")</f>
+        <v>Staff AVG</v>
+      </c>
+      <c r="B13">
+        <f>IF(SD!C10&gt;0,SD!C10,"")</f>
+        <v>35</v>
+      </c>
+      <c r="C13">
+        <f>IF(SD!D10&gt;0,SD!D10,"")</f>
+        <v>35</v>
+      </c>
+      <c r="D13">
+        <f>IF(SD!E10&gt;0,SD!E10,"")</f>
+        <v>35</v>
+      </c>
+      <c r="E13">
+        <f>IF(SD!F10&gt;0,SD!F10,"")</f>
+        <v>35</v>
+      </c>
+      <c r="F13">
+        <f>IF(SD!G10&gt;0,SD!G10,"")</f>
+        <v>35</v>
+      </c>
+      <c r="G13">
+        <f>IF(SD!H10&gt;0,SD!H10,"")</f>
+        <v>35</v>
+      </c>
+      <c r="H13">
+        <f>IF(SD!I10&gt;0,SD!I10,"")</f>
+        <v>35</v>
+      </c>
+      <c r="I13">
+        <f>IF(SD!J10&gt;0,SD!J10,"")</f>
+        <v>35</v>
+      </c>
+      <c r="J13">
+        <f>IF(SD!K10&gt;0,SD!K10,"")</f>
+        <v>35</v>
+      </c>
+      <c r="K13">
+        <f>IF(SD!L10&gt;0,SD!L10,"")</f>
+        <v>35</v>
+      </c>
+      <c r="L13">
+        <f>IF(SD!M10&gt;0,SD!M10,"")</f>
+        <v>35</v>
+      </c>
+      <c r="M13">
+        <f>IF(SD!N10&gt;0,SD!N10,"")</f>
+        <v>35</v>
+      </c>
+      <c r="N13">
+        <f>IF(SD!O10&gt;0,SD!O10,"")</f>
+        <v>35</v>
+      </c>
+      <c r="O13">
+        <f>IF(SD!P10&gt;0,SD!P10,"")</f>
+        <v>35</v>
+      </c>
+      <c r="P13">
+        <f>IF(SD!Q10&gt;0,SD!Q10,"")</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A14" t="str">
+        <f>IF(SD!A11&gt;0,SD!A11,"")</f>
+        <v>Plan</v>
+      </c>
+      <c r="B14">
+        <f>IF(SD!C11&gt;0,SD!C11,"")</f>
+        <v>33</v>
+      </c>
+      <c r="C14">
+        <f>IF(SD!D11&gt;0,SD!D11,"")</f>
+        <v>35</v>
+      </c>
+      <c r="D14">
+        <f>IF(SD!E11&gt;0,SD!E11,"")</f>
+        <v>36</v>
+      </c>
+      <c r="E14">
+        <f>IF(SD!F11&gt;0,SD!F11,"")</f>
+        <v>33</v>
+      </c>
+      <c r="F14">
+        <f>IF(SD!G11&gt;0,SD!G11,"")</f>
+        <v>34</v>
+      </c>
+      <c r="G14">
+        <f>IF(SD!H11&gt;0,SD!H11,"")</f>
+        <v>34</v>
+      </c>
+      <c r="H14">
+        <f>IF(SD!I11&gt;0,SD!I11,"")</f>
+        <v>33</v>
+      </c>
+      <c r="I14">
+        <f>IF(SD!J11&gt;0,SD!J11,"")</f>
+        <v>32</v>
+      </c>
+      <c r="J14">
+        <f>IF(SD!K11&gt;0,SD!K11,"")</f>
+        <v>31</v>
+      </c>
+      <c r="K14">
+        <f>IF(SD!L11&gt;0,SD!L11,"")</f>
+        <v>30</v>
+      </c>
+      <c r="L14">
+        <f>IF(SD!M11&gt;0,SD!M11,"")</f>
+        <v>30</v>
+      </c>
+      <c r="M14">
+        <f>IF(SD!N11&gt;0,SD!N11,"")</f>
+        <v>29</v>
+      </c>
+      <c r="N14">
+        <f>IF(SD!O11&gt;0,SD!O11,"")</f>
+        <v>23</v>
+      </c>
+      <c r="O14">
+        <f>IF(SD!P11&gt;0,SD!P11,"")</f>
+        <v>23</v>
+      </c>
+      <c r="P14">
+        <f>IF(SD!Q11&gt;0,SD!Q11,"")</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B21" t="str">
+        <f>IF(SD!C1&gt;0,SD!C1,"")</f>
+        <v>JAN</v>
+      </c>
+      <c r="C21" t="str">
+        <f>IF(SD!D1&gt;0,SD!D1,"")</f>
+        <v>FEB</v>
+      </c>
+      <c r="D21" t="str">
+        <f>IF(SD!E1&gt;0,SD!E1,"")</f>
+        <v>MAR</v>
+      </c>
+      <c r="E21" t="str">
+        <f>IF(SD!F1&gt;0,SD!F1,"")</f>
+        <v>APR</v>
+      </c>
+      <c r="F21" t="str">
+        <f>IF(SD!G1&gt;0,SD!G1,"")</f>
+        <v>MAY</v>
+      </c>
+      <c r="G21" t="str">
+        <f>IF(SD!H1&gt;0,SD!H1,"")</f>
+        <v>JUN</v>
+      </c>
+      <c r="H21" t="str">
+        <f>IF(SD!I1&gt;0,SD!I1,"")</f>
+        <v>JUL</v>
+      </c>
+      <c r="I21" t="str">
+        <f>IF(SD!J1&gt;0,SD!J1,"")</f>
+        <v>AUG</v>
+      </c>
+      <c r="J21" t="str">
+        <f>IF(SD!K1&gt;0,SD!K1,"")</f>
+        <v>SEP</v>
+      </c>
+      <c r="K21" t="str">
+        <f>IF(SD!L1&gt;0,SD!L1,"")</f>
+        <v>OCT</v>
+      </c>
+      <c r="L21" t="str">
+        <f>IF(SD!M1&gt;0,SD!M1,"")</f>
+        <v>NOV</v>
+      </c>
+      <c r="M21" t="str">
+        <f>IF(SD!N1&gt;0,SD!N1,"")</f>
+        <v>DEC</v>
+      </c>
+      <c r="N21" t="str">
+        <f>IF(SD!O1&gt;0,SD!O1,"")</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O21" t="str">
+        <f>IF(SD!P1&gt;0,SD!P1,"")</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P21" t="str">
+        <f>IF(SD!Q1&gt;0,SD!Q1,"")</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A22" t="str">
+        <f>IF(SD!A13&gt;0,SD!A13,"")</f>
+        <v>Staff</v>
+      </c>
+      <c r="B22">
+        <f>IF(SD!C13&gt;0,SD!C13,"")</f>
+        <v>2</v>
+      </c>
+      <c r="C22">
+        <f>IF(SD!D13&gt;0,SD!D13,"")</f>
+        <v>2</v>
+      </c>
+      <c r="D22">
+        <f>IF(SD!E13&gt;0,SD!E13,"")</f>
+        <v>2</v>
+      </c>
+      <c r="E22">
+        <f>IF(SD!F13&gt;0,SD!F13,"")</f>
+        <v>2</v>
+      </c>
+      <c r="F22">
+        <f>IF(SD!G13&gt;0,SD!G13,"")</f>
+        <v>2</v>
+      </c>
+      <c r="G22">
+        <f>IF(SD!H13&gt;0,SD!H13,"")</f>
+        <v>2</v>
+      </c>
+      <c r="H22">
+        <f>IF(SD!I13&gt;0,SD!I13,"")</f>
+        <v>2</v>
+      </c>
+      <c r="I22">
+        <f>IF(SD!J13&gt;0,SD!J13,"")</f>
+        <v>2</v>
+      </c>
+      <c r="J22">
+        <f>IF(SD!K13&gt;0,SD!K13,"")</f>
+        <v>2</v>
+      </c>
+      <c r="K22">
+        <f>IF(SD!L13&gt;0,SD!L13,"")</f>
+        <v>2</v>
+      </c>
+      <c r="L22">
+        <f>IF(SD!M13&gt;0,SD!M13,"")</f>
+        <v>2</v>
+      </c>
+      <c r="M22">
+        <f>IF(SD!N13&gt;0,SD!N13,"")</f>
+        <v>2</v>
+      </c>
+      <c r="N22">
+        <f>IF(SD!O13&gt;0,SD!O13,"")</f>
+        <v>2</v>
+      </c>
+      <c r="O22">
+        <f>IF(SD!P13&gt;0,SD!P13,"")</f>
+        <v>2</v>
+      </c>
+      <c r="P22">
+        <f>IF(SD!Q13&gt;0,SD!Q13,"")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A23" t="str">
+        <f>IF(SD!A14&gt;0,SD!A14,"")</f>
+        <v>Staff AVG</v>
+      </c>
+      <c r="B23">
+        <f>IF(SD!C14&gt;0,SD!C14,"")</f>
+        <v>2</v>
+      </c>
+      <c r="C23">
+        <f>IF(SD!D14&gt;0,SD!D14,"")</f>
+        <v>2</v>
+      </c>
+      <c r="D23">
+        <f>IF(SD!E14&gt;0,SD!E14,"")</f>
+        <v>2</v>
+      </c>
+      <c r="E23">
+        <f>IF(SD!F14&gt;0,SD!F14,"")</f>
+        <v>2</v>
+      </c>
+      <c r="F23">
+        <f>IF(SD!G14&gt;0,SD!G14,"")</f>
+        <v>2</v>
+      </c>
+      <c r="G23">
+        <f>IF(SD!H14&gt;0,SD!H14,"")</f>
+        <v>2</v>
+      </c>
+      <c r="H23">
+        <f>IF(SD!I14&gt;0,SD!I14,"")</f>
+        <v>2</v>
+      </c>
+      <c r="I23">
+        <f>IF(SD!J14&gt;0,SD!J14,"")</f>
+        <v>2</v>
+      </c>
+      <c r="J23">
+        <f>IF(SD!K14&gt;0,SD!K14,"")</f>
+        <v>2</v>
+      </c>
+      <c r="K23">
+        <f>IF(SD!L14&gt;0,SD!L14,"")</f>
+        <v>2</v>
+      </c>
+      <c r="L23">
+        <f>IF(SD!M14&gt;0,SD!M14,"")</f>
+        <v>2</v>
+      </c>
+      <c r="M23">
+        <f>IF(SD!N14&gt;0,SD!N14,"")</f>
+        <v>2</v>
+      </c>
+      <c r="N23">
+        <f>IF(SD!O14&gt;0,SD!O14,"")</f>
+        <v>2</v>
+      </c>
+      <c r="O23">
+        <f>IF(SD!P14&gt;0,SD!P14,"")</f>
+        <v>2</v>
+      </c>
+      <c r="P23">
+        <f>IF(SD!Q14&gt;0,SD!Q14,"")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A24" t="str">
+        <f>IF(SD!A15&gt;0,SD!A15,"")</f>
+        <v>Plan</v>
+      </c>
+      <c r="B24">
+        <f>IF(SD!C15&gt;0,SD!C15,"")</f>
+        <v>2</v>
+      </c>
+      <c r="C24">
+        <f>IF(SD!D15&gt;0,SD!D15,"")</f>
+        <v>2</v>
+      </c>
+      <c r="D24">
+        <f>IF(SD!E15&gt;0,SD!E15,"")</f>
+        <v>2</v>
+      </c>
+      <c r="E24">
+        <f>IF(SD!F15&gt;0,SD!F15,"")</f>
+        <v>2</v>
+      </c>
+      <c r="F24">
+        <f>IF(SD!G15&gt;0,SD!G15,"")</f>
+        <v>2</v>
+      </c>
+      <c r="G24">
+        <f>IF(SD!H15&gt;0,SD!H15,"")</f>
+        <v>2</v>
+      </c>
+      <c r="H24">
+        <f>IF(SD!I15&gt;0,SD!I15,"")</f>
+        <v>2</v>
+      </c>
+      <c r="I24">
+        <f>IF(SD!J15&gt;0,SD!J15,"")</f>
+        <v>2</v>
+      </c>
+      <c r="J24">
+        <f>IF(SD!K15&gt;0,SD!K15,"")</f>
+        <v>2</v>
+      </c>
+      <c r="K24">
+        <f>IF(SD!L15&gt;0,SD!L15,"")</f>
+        <v>2</v>
+      </c>
+      <c r="L24">
+        <f>IF(SD!M15&gt;0,SD!M15,"")</f>
+        <v>2</v>
+      </c>
+      <c r="M24">
+        <f>IF(SD!N15&gt;0,SD!N15,"")</f>
+        <v>2</v>
+      </c>
+      <c r="N24">
+        <f>IF(SD!O15&gt;0,SD!O15,"")</f>
+        <v>2</v>
+      </c>
+      <c r="O24">
+        <f>IF(SD!P15&gt;0,SD!P15,"")</f>
+        <v>2</v>
+      </c>
+      <c r="P24">
+        <f>IF(SD!Q15&gt;0,SD!Q15,"")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B31" t="str">
+        <f>IF(SD!C1&gt;0,SD!C1,"")</f>
+        <v>JAN</v>
+      </c>
+      <c r="C31" t="str">
+        <f>IF(SD!D1&gt;0,SD!D1,"")</f>
+        <v>FEB</v>
+      </c>
+      <c r="D31" t="str">
+        <f>IF(SD!E1&gt;0,SD!E1,"")</f>
+        <v>MAR</v>
+      </c>
+      <c r="E31" t="str">
+        <f>IF(SD!F1&gt;0,SD!F1,"")</f>
+        <v>APR</v>
+      </c>
+      <c r="F31" t="str">
+        <f>IF(SD!G1&gt;0,SD!G1,"")</f>
+        <v>MAY</v>
+      </c>
+      <c r="G31" t="str">
+        <f>IF(SD!H1&gt;0,SD!H1,"")</f>
+        <v>JUN</v>
+      </c>
+      <c r="H31" t="str">
+        <f>IF(SD!I1&gt;0,SD!I1,"")</f>
+        <v>JUL</v>
+      </c>
+      <c r="I31" t="str">
+        <f>IF(SD!J1&gt;0,SD!J1,"")</f>
+        <v>AUG</v>
+      </c>
+      <c r="J31" t="str">
+        <f>IF(SD!K1&gt;0,SD!K1,"")</f>
+        <v>SEP</v>
+      </c>
+      <c r="K31" t="str">
+        <f>IF(SD!L1&gt;0,SD!L1,"")</f>
+        <v>OCT</v>
+      </c>
+      <c r="L31" t="str">
+        <f>IF(SD!M1&gt;0,SD!M1,"")</f>
+        <v>NOV</v>
+      </c>
+      <c r="M31" t="str">
+        <f>IF(SD!N1&gt;0,SD!N1,"")</f>
+        <v>DEC</v>
+      </c>
+      <c r="N31" t="str">
+        <f>IF(SD!O1&gt;0,SD!O1,"")</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O31" t="str">
+        <f>IF(SD!P1&gt;0,SD!P1,"")</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P31" t="str">
+        <f>IF(SD!Q1&gt;0,SD!Q1,"")</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A32" t="str">
+        <f>IF(SD!A17&gt;0,SD!A17,"")</f>
+        <v>Staff</v>
+      </c>
+      <c r="B32">
+        <f>IF(SD!C17&gt;0,SD!C17,"")</f>
+        <v>6</v>
+      </c>
+      <c r="C32">
+        <f>IF(SD!D17&gt;0,SD!D17,"")</f>
+        <v>8</v>
+      </c>
+      <c r="D32">
+        <f>IF(SD!E17&gt;0,SD!E17,"")</f>
+        <v>9</v>
+      </c>
+      <c r="E32">
+        <f>IF(SD!F17&gt;0,SD!F17,"")</f>
+        <v>9</v>
+      </c>
+      <c r="F32">
+        <f>IF(SD!G17&gt;0,SD!G17,"")</f>
+        <v>9</v>
+      </c>
+      <c r="G32">
+        <f>IF(SD!H17&gt;0,SD!H17,"")</f>
+        <v>9</v>
+      </c>
+      <c r="H32">
+        <f>IF(SD!I17&gt;0,SD!I17,"")</f>
+        <v>9</v>
+      </c>
+      <c r="I32">
+        <f>IF(SD!J17&gt;0,SD!J17,"")</f>
+        <v>9</v>
+      </c>
+      <c r="J32">
+        <f>IF(SD!K17&gt;0,SD!K17,"")</f>
+        <v>9</v>
+      </c>
+      <c r="K32">
+        <f>IF(SD!L17&gt;0,SD!L17,"")</f>
+        <v>9</v>
+      </c>
+      <c r="L32">
+        <f>IF(SD!M17&gt;0,SD!M17,"")</f>
+        <v>9</v>
+      </c>
+      <c r="M32">
+        <f>IF(SD!N17&gt;0,SD!N17,"")</f>
+        <v>9</v>
+      </c>
+      <c r="N32">
+        <f>IF(SD!O17&gt;0,SD!O17,"")</f>
+        <v>9</v>
+      </c>
+      <c r="O32">
+        <f>IF(SD!P17&gt;0,SD!P17,"")</f>
+        <v>9</v>
+      </c>
+      <c r="P32">
+        <f>IF(SD!Q17&gt;0,SD!Q17,"")</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A33" t="str">
+        <f>IF(SD!A18&gt;0,SD!A18,"")</f>
+        <v>Staff AVG</v>
+      </c>
+      <c r="B33">
+        <f>IF(SD!C18&gt;0,SD!C18,"")</f>
+        <v>9</v>
+      </c>
+      <c r="C33">
+        <f>IF(SD!D18&gt;0,SD!D18,"")</f>
+        <v>9</v>
+      </c>
+      <c r="D33">
+        <f>IF(SD!E18&gt;0,SD!E18,"")</f>
+        <v>9</v>
+      </c>
+      <c r="E33">
+        <f>IF(SD!F18&gt;0,SD!F18,"")</f>
+        <v>9</v>
+      </c>
+      <c r="F33">
+        <f>IF(SD!G18&gt;0,SD!G18,"")</f>
+        <v>9</v>
+      </c>
+      <c r="G33">
+        <f>IF(SD!H18&gt;0,SD!H18,"")</f>
+        <v>9</v>
+      </c>
+      <c r="H33">
+        <f>IF(SD!I18&gt;0,SD!I18,"")</f>
+        <v>9</v>
+      </c>
+      <c r="I33">
+        <f>IF(SD!J18&gt;0,SD!J18,"")</f>
+        <v>9</v>
+      </c>
+      <c r="J33">
+        <f>IF(SD!K18&gt;0,SD!K18,"")</f>
+        <v>9</v>
+      </c>
+      <c r="K33">
+        <f>IF(SD!L18&gt;0,SD!L18,"")</f>
+        <v>9</v>
+      </c>
+      <c r="L33">
+        <f>IF(SD!M18&gt;0,SD!M18,"")</f>
+        <v>9</v>
+      </c>
+      <c r="M33">
+        <f>IF(SD!N18&gt;0,SD!N18,"")</f>
+        <v>9</v>
+      </c>
+      <c r="N33">
+        <f>IF(SD!O18&gt;0,SD!O18,"")</f>
+        <v>9</v>
+      </c>
+      <c r="O33">
+        <f>IF(SD!P18&gt;0,SD!P18,"")</f>
+        <v>9</v>
+      </c>
+      <c r="P33">
+        <f>IF(SD!Q18&gt;0,SD!Q18,"")</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A34" t="str">
+        <f>IF(SD!A19&gt;0,SD!A19,"")</f>
+        <v>Plan</v>
+      </c>
+      <c r="B34">
+        <f>IF(SD!C19&gt;0,SD!C19,"")</f>
+        <v>6</v>
+      </c>
+      <c r="C34">
+        <f>IF(SD!D19&gt;0,SD!D19,"")</f>
+        <v>8</v>
+      </c>
+      <c r="D34">
+        <f>IF(SD!E19&gt;0,SD!E19,"")</f>
+        <v>10</v>
+      </c>
+      <c r="E34">
+        <f>IF(SD!F19&gt;0,SD!F19,"")</f>
+        <v>9</v>
+      </c>
+      <c r="F34">
+        <f>IF(SD!G19&gt;0,SD!G19,"")</f>
+        <v>10</v>
+      </c>
+      <c r="G34">
+        <f>IF(SD!H19&gt;0,SD!H19,"")</f>
+        <v>11</v>
+      </c>
+      <c r="H34">
+        <f>IF(SD!I19&gt;0,SD!I19,"")</f>
+        <v>12</v>
+      </c>
+      <c r="I34">
+        <f>IF(SD!J19&gt;0,SD!J19,"")</f>
+        <v>12</v>
+      </c>
+      <c r="J34">
+        <f>IF(SD!K19&gt;0,SD!K19,"")</f>
+        <v>13</v>
+      </c>
+      <c r="K34">
+        <f>IF(SD!L19&gt;0,SD!L19,"")</f>
+        <v>10</v>
+      </c>
+      <c r="L34">
+        <f>IF(SD!M19&gt;0,SD!M19,"")</f>
+        <v>10</v>
+      </c>
+      <c r="M34">
+        <f>IF(SD!N19&gt;0,SD!N19,"")</f>
+        <v>10</v>
+      </c>
+      <c r="N34">
+        <f>IF(SD!O19&gt;0,SD!O19,"")</f>
+        <v>7</v>
+      </c>
+      <c r="O34">
+        <f>IF(SD!P19&gt;0,SD!P19,"")</f>
+        <v>7</v>
+      </c>
+      <c r="P34">
+        <f>IF(SD!Q19&gt;0,SD!Q19,"")</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B41" t="str">
+        <f>IF(SD!C31&gt;0,SD!C31,"")</f>
+        <v>Q1</v>
+      </c>
+      <c r="C41" t="str">
+        <f>IF(SD!D31&gt;0,SD!D31,"")</f>
+        <v>Q2</v>
+      </c>
+      <c r="D41" t="str">
+        <f>IF(SD!E31&gt;0,SD!E31,"")</f>
+        <v>Q3</v>
+      </c>
+      <c r="E41" t="str">
+        <f>IF(SD!F31&gt;0,SD!F31,"")</f>
+        <v>Q4</v>
+      </c>
+      <c r="F41" t="str">
+        <f>IF(SD!G31&gt;0,SD!G31,"")</f>
+        <v>Q1'27</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A42" t="str">
+        <f>IF(SD!B32&gt;0,SD!B32,"")</f>
+        <v>Staff</v>
+      </c>
+      <c r="B42">
+        <f>IF(SD!C32&gt;0,SD!C32,"")</f>
+        <v>45</v>
+      </c>
+      <c r="C42">
+        <f>IF(SD!D32&gt;0,SD!D32,"")</f>
+        <v>46</v>
+      </c>
+      <c r="D42">
+        <f>IF(SD!E32&gt;0,SD!E32,"")</f>
+        <v>46</v>
+      </c>
+      <c r="E42">
+        <f>IF(SD!F32&gt;0,SD!F32,"")</f>
+        <v>46</v>
+      </c>
+      <c r="F42">
+        <f>IF(SD!G32&gt;0,SD!G32,"")</f>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A43" t="str">
+        <f>IF(SD!B33&gt;0,SD!B33,"")</f>
+        <v>Staff AVG</v>
+      </c>
+      <c r="B43">
+        <f>IF(SD!C33&gt;0,SD!C33,"")</f>
+        <v>46</v>
+      </c>
+      <c r="C43">
+        <f>IF(SD!D33&gt;0,SD!D33,"")</f>
+        <v>46</v>
+      </c>
+      <c r="D43">
+        <f>IF(SD!E33&gt;0,SD!E33,"")</f>
+        <v>46</v>
+      </c>
+      <c r="E43">
+        <f>IF(SD!F33&gt;0,SD!F33,"")</f>
+        <v>46</v>
+      </c>
+      <c r="F43">
+        <f>IF(SD!G33&gt;0,SD!G33,"")</f>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A44" t="str">
+        <f>IF(SD!B34&gt;0,SD!B34,"")</f>
+        <v>Plan</v>
+      </c>
+      <c r="B44">
+        <f>IF(SD!C34&gt;0,SD!C34,"")</f>
+        <v>45</v>
+      </c>
+      <c r="C44">
+        <f>IF(SD!D34&gt;0,SD!D34,"")</f>
+        <v>45</v>
+      </c>
+      <c r="D44">
+        <f>IF(SD!E34&gt;0,SD!E34,"")</f>
+        <v>46</v>
+      </c>
+      <c r="E44">
+        <f>IF(SD!F34&gt;0,SD!F34,"")</f>
+        <v>42</v>
+      </c>
+      <c r="F44">
+        <f>IF(SD!G34&gt;0,SD!G34,"")</f>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A45" t="str">
+        <f>IF(SD!B41&gt;0,SD!B41,"")</f>
+        <v>PAYROLL</v>
+      </c>
+      <c r="B45">
+        <f>IF(SD!C41&gt;0,SD!C41,"")</f>
+        <v>35</v>
+      </c>
+      <c r="C45">
+        <f>IF(SD!D41&gt;0,SD!D41,"")</f>
+        <v>34</v>
+      </c>
+      <c r="D45">
+        <f>IF(SD!E41&gt;0,SD!E41,"")</f>
+        <v>32</v>
+      </c>
+      <c r="E45">
+        <f>IF(SD!F41&gt;0,SD!F41,"")</f>
+        <v>30</v>
+      </c>
+      <c r="F45">
+        <f>IF(SD!G41&gt;0,SD!G41,"")</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A46" t="str">
+        <f>IF(SD!B45&gt;0,SD!B45,"")</f>
+        <v>CONTRACTOR</v>
+      </c>
+      <c r="B46">
+        <f>IF(SD!C45&gt;0,SD!C45,"")</f>
+        <v>2</v>
+      </c>
+      <c r="C46">
+        <f>IF(SD!D45&gt;0,SD!D45,"")</f>
+        <v>2</v>
+      </c>
+      <c r="D46">
+        <f>IF(SD!E45&gt;0,SD!E45,"")</f>
+        <v>2</v>
+      </c>
+      <c r="E46">
+        <f>IF(SD!F45&gt;0,SD!F45,"")</f>
+        <v>2</v>
+      </c>
+      <c r="F46">
+        <f>IF(SD!G45&gt;0,SD!G45,"")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A47" t="str">
+        <f>IF(SD!B49&gt;0,SD!B49,"")</f>
+        <v>OUTSOURCE</v>
+      </c>
+      <c r="B47">
+        <f>IF(SD!C49&gt;0,SD!C49,"")</f>
+        <v>8</v>
+      </c>
+      <c r="C47">
+        <f>IF(SD!D49&gt;0,SD!D49,"")</f>
+        <v>10</v>
+      </c>
+      <c r="D47">
+        <f>IF(SD!E49&gt;0,SD!E49,"")</f>
+        <v>12</v>
+      </c>
+      <c r="E47">
+        <f>IF(SD!F49&gt;0,SD!F49,"")</f>
+        <v>10</v>
+      </c>
+      <c r="F47">
+        <f>IF(SD!G49&gt;0,SD!G49,"")</f>
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BC06D1C-51D2-2344-A21E-D05900EFAAB3}">
+  <sheetPr>
+    <tabColor theme="9"/>
+  </sheetPr>
+  <dimension ref="A1:Q49"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1" s="17"/>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A2" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="8">
+        <v>24</v>
+      </c>
+      <c r="D2" s="8">
+        <v>23</v>
+      </c>
+      <c r="E2" s="8">
+        <v>22</v>
+      </c>
+      <c r="F2" s="8">
+        <v>21</v>
+      </c>
+      <c r="G2" s="8">
+        <v>20</v>
+      </c>
+      <c r="H2" s="8">
+        <v>20</v>
+      </c>
+      <c r="I2" s="8">
+        <v>19</v>
+      </c>
+      <c r="J2" s="8">
+        <v>19</v>
+      </c>
+      <c r="K2" s="8">
+        <v>19</v>
+      </c>
+      <c r="L2" s="8">
+        <v>19</v>
+      </c>
+      <c r="M2" s="8">
+        <v>19</v>
+      </c>
+      <c r="N2" s="8">
+        <v>19</v>
+      </c>
+      <c r="O2" s="8">
+        <v>19</v>
+      </c>
+      <c r="P2" s="8">
+        <v>19</v>
+      </c>
+      <c r="Q2" s="8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A3" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="8">
+        <v>20</v>
+      </c>
+      <c r="D3" s="8">
+        <v>20</v>
+      </c>
+      <c r="E3" s="8">
+        <v>20</v>
+      </c>
+      <c r="F3" s="8">
+        <v>19</v>
+      </c>
+      <c r="G3" s="8">
+        <v>19</v>
+      </c>
+      <c r="H3" s="8">
+        <v>19</v>
+      </c>
+      <c r="I3" s="8">
+        <v>19</v>
+      </c>
+      <c r="J3" s="8">
+        <v>19</v>
+      </c>
+      <c r="K3" s="8">
+        <v>19</v>
+      </c>
+      <c r="L3" s="8">
+        <v>19</v>
+      </c>
+      <c r="M3" s="8">
+        <v>19</v>
+      </c>
+      <c r="N3" s="8">
+        <v>19</v>
+      </c>
+      <c r="O3" s="8">
+        <v>19</v>
+      </c>
+      <c r="P3" s="8">
+        <v>19</v>
+      </c>
+      <c r="Q3" s="8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A4" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="8">
+        <v>16</v>
+      </c>
+      <c r="D4" s="8">
+        <v>17</v>
+      </c>
+      <c r="E4" s="8">
+        <v>16</v>
+      </c>
+      <c r="F4" s="8">
+        <v>19</v>
+      </c>
+      <c r="G4" s="8">
+        <v>18</v>
+      </c>
+      <c r="H4" s="8">
+        <v>18</v>
+      </c>
+      <c r="I4" s="8">
+        <v>16</v>
+      </c>
+      <c r="J4" s="8">
+        <v>15</v>
+      </c>
+      <c r="K4" s="8">
+        <v>14</v>
+      </c>
+      <c r="L4" s="8">
+        <v>14</v>
+      </c>
+      <c r="M4" s="8">
+        <v>14</v>
+      </c>
+      <c r="N4" s="8">
+        <v>13</v>
+      </c>
+      <c r="O4" s="8">
+        <v>8</v>
+      </c>
+      <c r="P4" s="8">
+        <v>8</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A5" s="17"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
+      <c r="Q5" s="8"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A6" s="8"/>
+      <c r="B6" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="19">
+        <v>0.66300000000000003</v>
+      </c>
+      <c r="D6" s="19">
+        <v>0.75390000000000001</v>
+      </c>
+      <c r="E6" s="19">
+        <v>0.749</v>
+      </c>
+      <c r="F6" s="19">
+        <v>0.88400000000000001</v>
+      </c>
+      <c r="G6" s="19">
+        <v>0.91969999999999996</v>
+      </c>
+      <c r="H6" s="19">
+        <v>0.8982</v>
+      </c>
+      <c r="I6" s="19">
+        <v>0.83279999999999998</v>
+      </c>
+      <c r="J6" s="19">
+        <v>0.78800000000000003</v>
+      </c>
+      <c r="K6" s="19">
+        <v>0.75639999999999996</v>
+      </c>
+      <c r="L6" s="19">
+        <v>0.71499999999999997</v>
+      </c>
+      <c r="M6" s="19">
+        <v>0.71760000000000002</v>
+      </c>
+      <c r="N6" s="19">
+        <v>0.70179999999999998</v>
+      </c>
+      <c r="O6" s="19">
+        <v>0.44130000000000003</v>
+      </c>
+      <c r="P6" s="19">
+        <v>0.44130000000000003</v>
+      </c>
+      <c r="Q6" s="19">
+        <v>0.44130000000000003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A7" s="17"/>
+      <c r="B7" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="20">
+        <v>8</v>
+      </c>
+      <c r="D7" s="20">
+        <v>6</v>
+      </c>
+      <c r="E7" s="20">
+        <v>6</v>
+      </c>
+      <c r="F7" s="20">
+        <v>2</v>
+      </c>
+      <c r="G7" s="20">
+        <v>2</v>
+      </c>
+      <c r="H7" s="20">
+        <v>2</v>
+      </c>
+      <c r="I7" s="20">
+        <v>3</v>
+      </c>
+      <c r="J7" s="20">
+        <v>4</v>
+      </c>
+      <c r="K7" s="20">
+        <v>5</v>
+      </c>
+      <c r="L7" s="20">
+        <v>5</v>
+      </c>
+      <c r="M7" s="20">
+        <v>5</v>
+      </c>
+      <c r="N7" s="20">
+        <v>6</v>
+      </c>
+      <c r="O7" s="20">
+        <v>11</v>
+      </c>
+      <c r="P7" s="20">
+        <v>11</v>
+      </c>
+      <c r="Q7" s="20">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A8" s="17"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A9" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="8">
+        <v>24</v>
+      </c>
+      <c r="D9" s="8">
+        <v>23</v>
+      </c>
+      <c r="E9" s="8">
+        <v>22</v>
+      </c>
+      <c r="F9" s="8">
+        <v>21</v>
+      </c>
+      <c r="G9" s="8">
+        <v>20</v>
+      </c>
+      <c r="H9" s="8">
+        <v>20</v>
+      </c>
+      <c r="I9" s="8">
+        <v>19</v>
+      </c>
+      <c r="J9" s="8">
+        <v>19</v>
+      </c>
+      <c r="K9" s="8">
+        <v>19</v>
+      </c>
+      <c r="L9" s="8">
+        <v>19</v>
+      </c>
+      <c r="M9" s="8">
+        <v>19</v>
+      </c>
+      <c r="N9" s="8">
+        <v>19</v>
+      </c>
+      <c r="O9" s="8">
+        <v>19</v>
+      </c>
+      <c r="P9" s="8">
+        <v>19</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A10" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="8">
+        <v>20</v>
+      </c>
+      <c r="D10" s="8">
+        <v>20</v>
+      </c>
+      <c r="E10" s="8">
+        <v>20</v>
+      </c>
+      <c r="F10" s="8">
+        <v>19</v>
+      </c>
+      <c r="G10" s="8">
+        <v>19</v>
+      </c>
+      <c r="H10" s="8">
+        <v>19</v>
+      </c>
+      <c r="I10" s="8">
+        <v>19</v>
+      </c>
+      <c r="J10" s="8">
+        <v>19</v>
+      </c>
+      <c r="K10" s="8">
+        <v>19</v>
+      </c>
+      <c r="L10" s="8">
+        <v>19</v>
+      </c>
+      <c r="M10" s="8">
+        <v>19</v>
+      </c>
+      <c r="N10" s="8">
+        <v>19</v>
+      </c>
+      <c r="O10" s="8">
+        <v>19</v>
+      </c>
+      <c r="P10" s="8">
+        <v>19</v>
+      </c>
+      <c r="Q10" s="8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A11" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="8">
+        <v>16</v>
+      </c>
+      <c r="D11" s="8">
+        <v>17</v>
+      </c>
+      <c r="E11" s="8">
+        <v>16</v>
+      </c>
+      <c r="F11" s="8">
+        <v>19</v>
+      </c>
+      <c r="G11" s="8">
+        <v>18</v>
+      </c>
+      <c r="H11" s="8">
+        <v>18</v>
+      </c>
+      <c r="I11" s="8">
+        <v>16</v>
+      </c>
+      <c r="J11" s="8">
+        <v>15</v>
+      </c>
+      <c r="K11" s="8">
+        <v>14</v>
+      </c>
+      <c r="L11" s="8">
+        <v>14</v>
+      </c>
+      <c r="M11" s="8">
+        <v>14</v>
+      </c>
+      <c r="N11" s="8">
+        <v>13</v>
+      </c>
+      <c r="O11" s="8">
+        <v>8</v>
+      </c>
+      <c r="P11" s="8">
+        <v>8</v>
+      </c>
+      <c r="Q11" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A12" s="8"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
+      <c r="Q12" s="8"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A13" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="8">
+        <v>0</v>
+      </c>
+      <c r="D13" s="8">
+        <v>0</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0</v>
+      </c>
+      <c r="F13" s="8">
+        <v>0</v>
+      </c>
+      <c r="G13" s="8">
+        <v>0</v>
+      </c>
+      <c r="H13" s="8">
+        <v>0</v>
+      </c>
+      <c r="I13" s="8">
+        <v>0</v>
+      </c>
+      <c r="J13" s="8">
+        <v>0</v>
+      </c>
+      <c r="K13" s="8">
+        <v>0</v>
+      </c>
+      <c r="L13" s="8">
+        <v>0</v>
+      </c>
+      <c r="M13" s="8">
+        <v>0</v>
+      </c>
+      <c r="N13" s="8">
+        <v>0</v>
+      </c>
+      <c r="O13" s="8">
+        <v>0</v>
+      </c>
+      <c r="P13" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A14" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="8">
+        <v>0</v>
+      </c>
+      <c r="D14" s="8">
+        <v>0</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0</v>
+      </c>
+      <c r="F14" s="8">
+        <v>0</v>
+      </c>
+      <c r="G14" s="8">
+        <v>0</v>
+      </c>
+      <c r="H14" s="8">
+        <v>0</v>
+      </c>
+      <c r="I14" s="8">
+        <v>0</v>
+      </c>
+      <c r="J14" s="8">
+        <v>0</v>
+      </c>
+      <c r="K14" s="8">
+        <v>0</v>
+      </c>
+      <c r="L14" s="8">
+        <v>0</v>
+      </c>
+      <c r="M14" s="8">
+        <v>0</v>
+      </c>
+      <c r="N14" s="8">
+        <v>0</v>
+      </c>
+      <c r="O14" s="8">
+        <v>0</v>
+      </c>
+      <c r="P14" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A15" s="16">
+        <v>0</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="8">
+        <v>0</v>
+      </c>
+      <c r="D15" s="8">
+        <v>0</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0</v>
+      </c>
+      <c r="F15" s="8">
+        <v>0</v>
+      </c>
+      <c r="G15" s="8">
+        <v>0</v>
+      </c>
+      <c r="H15" s="8">
+        <v>0</v>
+      </c>
+      <c r="I15" s="8">
+        <v>0</v>
+      </c>
+      <c r="J15" s="8">
+        <v>0</v>
+      </c>
+      <c r="K15" s="8">
+        <v>0</v>
+      </c>
+      <c r="L15" s="8">
+        <v>0</v>
+      </c>
+      <c r="M15" s="8">
+        <v>0</v>
+      </c>
+      <c r="N15" s="8">
+        <v>0</v>
+      </c>
+      <c r="O15" s="8">
+        <v>0</v>
+      </c>
+      <c r="P15" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A16" s="8"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="8"/>
+      <c r="Q16" s="8"/>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A17" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="8">
+        <v>0</v>
+      </c>
+      <c r="D17" s="8">
+        <v>0</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0</v>
+      </c>
+      <c r="F17" s="8">
+        <v>0</v>
+      </c>
+      <c r="G17" s="8">
+        <v>0</v>
+      </c>
+      <c r="H17" s="8">
+        <v>0</v>
+      </c>
+      <c r="I17" s="8">
+        <v>0</v>
+      </c>
+      <c r="J17" s="8">
+        <v>0</v>
+      </c>
+      <c r="K17" s="8">
+        <v>0</v>
+      </c>
+      <c r="L17" s="8">
+        <v>0</v>
+      </c>
+      <c r="M17" s="8">
+        <v>0</v>
+      </c>
+      <c r="N17" s="8">
+        <v>0</v>
+      </c>
+      <c r="O17" s="8">
+        <v>0</v>
+      </c>
+      <c r="P17" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A18" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="8">
+        <v>0</v>
+      </c>
+      <c r="D18" s="8">
+        <v>0</v>
+      </c>
+      <c r="E18" s="8">
+        <v>0</v>
+      </c>
+      <c r="F18" s="8">
+        <v>0</v>
+      </c>
+      <c r="G18" s="8">
+        <v>0</v>
+      </c>
+      <c r="H18" s="8">
+        <v>0</v>
+      </c>
+      <c r="I18" s="8">
+        <v>0</v>
+      </c>
+      <c r="J18" s="8">
+        <v>0</v>
+      </c>
+      <c r="K18" s="8">
+        <v>0</v>
+      </c>
+      <c r="L18" s="8">
+        <v>0</v>
+      </c>
+      <c r="M18" s="8">
+        <v>0</v>
+      </c>
+      <c r="N18" s="8">
+        <v>0</v>
+      </c>
+      <c r="O18" s="8">
+        <v>0</v>
+      </c>
+      <c r="P18" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A19" s="16">
+        <v>0</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="8">
+        <v>0</v>
+      </c>
+      <c r="D19" s="8">
+        <v>0</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0</v>
+      </c>
+      <c r="F19" s="8">
+        <v>0</v>
+      </c>
+      <c r="G19" s="8">
+        <v>0</v>
+      </c>
+      <c r="H19" s="8">
+        <v>0</v>
+      </c>
+      <c r="I19" s="8">
+        <v>0</v>
+      </c>
+      <c r="J19" s="8">
+        <v>0</v>
+      </c>
+      <c r="K19" s="8">
+        <v>0</v>
+      </c>
+      <c r="L19" s="8">
+        <v>0</v>
+      </c>
+      <c r="M19" s="8">
+        <v>0</v>
+      </c>
+      <c r="N19" s="8">
+        <v>0</v>
+      </c>
+      <c r="O19" s="8">
+        <v>0</v>
+      </c>
+      <c r="P19" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A31" s="17"/>
+      <c r="B31" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C31" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="D31" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="E31" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F31" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="G31" s="24" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A32" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" s="26">
+        <v>23</v>
+      </c>
+      <c r="D32" s="21">
+        <v>20</v>
+      </c>
+      <c r="E32" s="21">
+        <v>19</v>
+      </c>
+      <c r="F32" s="21">
+        <v>19</v>
+      </c>
+      <c r="G32" s="21">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="26">
+        <v>20</v>
+      </c>
+      <c r="D33" s="21">
+        <v>19</v>
+      </c>
+      <c r="E33" s="21">
+        <v>19</v>
+      </c>
+      <c r="F33" s="21">
+        <v>19</v>
+      </c>
+      <c r="G33" s="21">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="26">
+        <v>17</v>
+      </c>
+      <c r="D34" s="21">
+        <v>18</v>
+      </c>
+      <c r="E34" s="21">
+        <v>15</v>
+      </c>
+      <c r="F34" s="21">
+        <v>14</v>
+      </c>
+      <c r="G34" s="21">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="17"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="27">
+        <v>0.27929999999999999</v>
+      </c>
+      <c r="D35" s="28">
+        <v>9.9699999999999997E-2</v>
+      </c>
+      <c r="E35" s="28">
+        <v>0.20760000000000001</v>
+      </c>
+      <c r="F35" s="28">
+        <v>0.28849999999999998</v>
+      </c>
+      <c r="G35" s="28">
+        <v>0.37969999999999998</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="8"/>
+      <c r="B36" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C36" s="29">
+        <v>0.72070000000000001</v>
+      </c>
+      <c r="D36" s="19">
+        <v>0.90029999999999999</v>
+      </c>
+      <c r="E36" s="19">
+        <v>0.79239999999999999</v>
+      </c>
+      <c r="F36" s="19">
+        <v>0.71150000000000002</v>
+      </c>
+      <c r="G36" s="19">
+        <v>0.62029999999999996</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="17"/>
+      <c r="B37" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" s="30">
+        <v>6</v>
+      </c>
+      <c r="D37" s="20">
+        <v>2</v>
+      </c>
+      <c r="E37" s="20">
+        <v>4</v>
+      </c>
+      <c r="F37" s="20">
+        <v>5</v>
+      </c>
+      <c r="G37" s="20">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="17"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="31"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C39" s="26">
+        <v>23</v>
+      </c>
+      <c r="D39" s="21">
+        <v>20</v>
+      </c>
+      <c r="E39" s="21">
+        <v>19</v>
+      </c>
+      <c r="F39" s="21">
+        <v>19</v>
+      </c>
+      <c r="G39" s="21">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A40" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C40" s="26">
+        <v>20</v>
+      </c>
+      <c r="D40" s="21">
+        <v>19</v>
+      </c>
+      <c r="E40" s="21">
+        <v>19</v>
+      </c>
+      <c r="F40" s="21">
+        <v>19</v>
+      </c>
+      <c r="G40" s="21">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A41" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B41" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C41" s="26">
+        <v>17</v>
+      </c>
+      <c r="D41" s="21">
+        <v>18</v>
+      </c>
+      <c r="E41" s="21">
+        <v>15</v>
+      </c>
+      <c r="F41" s="21">
+        <v>14</v>
+      </c>
+      <c r="G41" s="21">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A42" s="8"/>
+      <c r="B42" s="17"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="21"/>
+      <c r="G42" s="21"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A43" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C43" s="26">
+        <v>0</v>
+      </c>
+      <c r="D43" s="21">
+        <v>0</v>
+      </c>
+      <c r="E43" s="21">
+        <v>0</v>
+      </c>
+      <c r="F43" s="21">
+        <v>0</v>
+      </c>
+      <c r="G43" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A44" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" s="26">
+        <v>0</v>
+      </c>
+      <c r="D44" s="21">
+        <v>0</v>
+      </c>
+      <c r="E44" s="21">
+        <v>0</v>
+      </c>
+      <c r="F44" s="21">
+        <v>0</v>
+      </c>
+      <c r="G44" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A45" s="16">
+        <v>0</v>
+      </c>
+      <c r="B45" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C45" s="26">
+        <v>0</v>
+      </c>
+      <c r="D45" s="21">
+        <v>0</v>
+      </c>
+      <c r="E45" s="21">
+        <v>0</v>
+      </c>
+      <c r="F45" s="21">
+        <v>0</v>
+      </c>
+      <c r="G45" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A46" s="8"/>
+      <c r="B46" s="17"/>
+      <c r="C46" s="26"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="21"/>
+      <c r="F46" s="21"/>
+      <c r="G46" s="21"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A47" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C47" s="26">
+        <v>0</v>
+      </c>
+      <c r="D47" s="21">
+        <v>0</v>
+      </c>
+      <c r="E47" s="21">
+        <v>0</v>
+      </c>
+      <c r="F47" s="21">
+        <v>0</v>
+      </c>
+      <c r="G47" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A48" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C48" s="26">
+        <v>0</v>
+      </c>
+      <c r="D48" s="21">
+        <v>0</v>
+      </c>
+      <c r="E48" s="21">
+        <v>0</v>
+      </c>
+      <c r="F48" s="21">
+        <v>0</v>
+      </c>
+      <c r="G48" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A49" s="16">
+        <v>0</v>
+      </c>
+      <c r="B49" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C49" s="26">
+        <v>0</v>
+      </c>
+      <c r="D49" s="21">
+        <v>0</v>
+      </c>
+      <c r="E49" s="21">
+        <v>0</v>
+      </c>
+      <c r="F49" s="21">
+        <v>0</v>
+      </c>
+      <c r="G49" s="21">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/workforceresult.xlsx
+++ b/workforceresult.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miiintra/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEA01787-D86A-754E-919A-7A21D34DAB96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55E74702-662D-5D44-96A2-D291D4F6D613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14500" yWindow="3140" windowWidth="28800" windowHeight="18680" activeTab="9" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
   </bookViews>
@@ -2526,7 +2526,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" t="str">
-        <f>IF(AIC!A9&gt;0,AIC!A9,"")</f>
+        <f>IF(AIC!B2&gt;0,AIC!B2,"")</f>
         <v>Staff</v>
       </c>
       <c r="B12">
@@ -2592,7 +2592,7 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" t="str">
-        <f>IF(AIC!A10&gt;0,AIC!A10,"")</f>
+        <f>IF(AIC!B3&gt;0,AIC!B3,"")</f>
         <v>Staff AVG</v>
       </c>
       <c r="B13">
@@ -2658,7 +2658,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" t="str">
-        <f>IF(AIC!A11&gt;0,AIC!A11,"")</f>
+        <f>IF(AIC!B4&gt;0,AIC!B4,"")</f>
         <v>Plan</v>
       </c>
       <c r="B14">
@@ -2786,8 +2786,8 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" t="str">
-        <f>IF(AIC!A13&gt;0,AIC!A13,"")</f>
-        <v>Grand Total</v>
+        <f>IF(AIC!B2&gt;0,AIC!B2,"")</f>
+        <v>Staff</v>
       </c>
       <c r="B22" t="str">
         <f>IF(AIC!C13&gt;0,AIC!C13,"")</f>
@@ -2852,7 +2852,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" t="str">
-        <f>IF(AIC!A14&gt;0,AIC!A14,"")</f>
+        <f>IF(AIC!B3&gt;0,AIC!B3,"")</f>
         <v>Staff AVG</v>
       </c>
       <c r="B23" t="str">
@@ -2918,8 +2918,8 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" t="str">
-        <f>IF(AIC!A15&gt;0,AIC!A15,"")</f>
-        <v/>
+        <f>IF(AIC!B4&gt;0,AIC!B4,"")</f>
+        <v>Plan</v>
       </c>
       <c r="B24" t="str">
         <f>IF(AIC!C15&gt;0,AIC!C15,"")</f>
@@ -3046,8 +3046,8 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" t="str">
-        <f>IF(AIC!A17&gt;0,AIC!A17,"")</f>
-        <v>Grand Total</v>
+        <f>IF(AIC!B2&gt;0,AIC!B2,"")</f>
+        <v>Staff</v>
       </c>
       <c r="B32" t="str">
         <f>IF(AIC!C17&gt;0,AIC!C17,"")</f>
@@ -3112,7 +3112,7 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33" t="str">
-        <f>IF(AIC!A18&gt;0,AIC!A18,"")</f>
+        <f>IF(AIC!B3&gt;0,AIC!B3,"")</f>
         <v>Staff AVG</v>
       </c>
       <c r="B33" t="str">
@@ -3178,8 +3178,8 @@
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34" t="str">
-        <f>IF(AIC!A19&gt;0,AIC!A19,"")</f>
-        <v/>
+        <f>IF(AIC!B4&gt;0,AIC!B4,"")</f>
+        <v>Plan</v>
       </c>
       <c r="B34" t="str">
         <f>IF(AIC!C19&gt;0,AIC!C19,"")</f>
@@ -6653,7 +6653,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" t="str">
-        <f>IF(CPS!A9&gt;0,CPS!A9,"")</f>
+        <f>IF(CPS!B2&gt;0,CPS!B2,"")</f>
         <v>Staff</v>
       </c>
       <c r="B12">
@@ -6719,7 +6719,7 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" t="str">
-        <f>IF(CPS!A10&gt;0,CPS!A10,"")</f>
+        <f>IF(CPS!B3&gt;0,CPS!B3,"")</f>
         <v>Staff AVG</v>
       </c>
       <c r="B13">
@@ -6785,7 +6785,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" t="str">
-        <f>IF(CPS!A11&gt;0,CPS!A11,"")</f>
+        <f>IF(CPS!B4&gt;0,CPS!B4,"")</f>
         <v>Plan</v>
       </c>
       <c r="B14">
@@ -6913,8 +6913,8 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" t="str">
-        <f>IF(CPS!A13&gt;0,CPS!A13,"")</f>
-        <v>Grand Total</v>
+        <f>IF(CPS!B2&gt;0,CPS!B2,"")</f>
+        <v>Staff</v>
       </c>
       <c r="B22" t="str">
         <f>IF(CPS!C13&gt;0,CPS!C13,"")</f>
@@ -6979,7 +6979,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" t="str">
-        <f>IF(CPS!A14&gt;0,CPS!A14,"")</f>
+        <f>IF(CPS!B3&gt;0,CPS!B3,"")</f>
         <v>Staff AVG</v>
       </c>
       <c r="B23" t="str">
@@ -7045,8 +7045,8 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" t="str">
-        <f>IF(CPS!A15&gt;0,CPS!A15,"")</f>
-        <v/>
+        <f>IF(CPS!B4&gt;0,CPS!B4,"")</f>
+        <v>Plan</v>
       </c>
       <c r="B24" t="str">
         <f>IF(CPS!C15&gt;0,CPS!C15,"")</f>
@@ -7173,8 +7173,8 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" t="str">
-        <f>IF(CPS!A17&gt;0,CPS!A17,"")</f>
-        <v>Grand Total</v>
+        <f>IF(CPS!B2&gt;0,CPS!B2,"")</f>
+        <v>Staff</v>
       </c>
       <c r="B32" t="str">
         <f>IF(CPS!C17&gt;0,CPS!C17,"")</f>
@@ -7239,7 +7239,7 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33" t="str">
-        <f>IF(CPS!A18&gt;0,CPS!A18,"")</f>
+        <f>IF(CPS!B3&gt;0,CPS!B3,"")</f>
         <v>Staff AVG</v>
       </c>
       <c r="B33" t="str">
@@ -7305,8 +7305,8 @@
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34" t="str">
-        <f>IF(CPS!A19&gt;0,CPS!A19,"")</f>
-        <v/>
+        <f>IF(CPS!B4&gt;0,CPS!B4,"")</f>
+        <v>Plan</v>
       </c>
       <c r="B34" t="str">
         <f>IF(CPS!C19&gt;0,CPS!C19,"")</f>
@@ -9348,7 +9348,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" t="str">
-        <f>IF(PSE!A9&gt;0,PSE!A9,"")</f>
+        <f>IF(PSE!B2&gt;0,PSE!B2,"")</f>
         <v>Staff</v>
       </c>
       <c r="B12">
@@ -9414,7 +9414,7 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" t="str">
-        <f>IF(PSE!A10&gt;0,PSE!A10,"")</f>
+        <f>IF(PSE!B3&gt;0,PSE!B3,"")</f>
         <v>Staff AVG</v>
       </c>
       <c r="B13">
@@ -9480,7 +9480,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" t="str">
-        <f>IF(PSE!A11&gt;0,PSE!A11,"")</f>
+        <f>IF(PSE!B4&gt;0,PSE!B4,"")</f>
         <v>Plan</v>
       </c>
       <c r="B14">
@@ -9608,7 +9608,7 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" t="str">
-        <f>IF(PSE!A13&gt;0,PSE!A13,"")</f>
+        <f>IF(PSE!B2&gt;0,PSE!B2,"")</f>
         <v>Staff</v>
       </c>
       <c r="B22">
@@ -9674,7 +9674,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" t="str">
-        <f>IF(PSE!A14&gt;0,PSE!A14,"")</f>
+        <f>IF(PSE!B3&gt;0,PSE!B3,"")</f>
         <v>Staff AVG</v>
       </c>
       <c r="B23">
@@ -9740,7 +9740,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" t="str">
-        <f>IF(PSE!A15&gt;0,PSE!A15,"")</f>
+        <f>IF(PSE!B4&gt;0,PSE!B4,"")</f>
         <v>Plan</v>
       </c>
       <c r="B24">
@@ -9868,7 +9868,7 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" t="str">
-        <f>IF(PSE!A17&gt;0,PSE!A17,"")</f>
+        <f>IF(PSE!B2&gt;0,PSE!B2,"")</f>
         <v>Staff</v>
       </c>
       <c r="B32" t="str">
@@ -9934,7 +9934,7 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33" t="str">
-        <f>IF(PSE!A18&gt;0,PSE!A18,"")</f>
+        <f>IF(PSE!B3&gt;0,PSE!B3,"")</f>
         <v>Staff AVG</v>
       </c>
       <c r="B33">
@@ -10000,7 +10000,7 @@
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34" t="str">
-        <f>IF(PSE!A19&gt;0,PSE!A19,"")</f>
+        <f>IF(PSE!B4&gt;0,PSE!B4,"")</f>
         <v>Plan</v>
       </c>
       <c r="B34" t="str">
@@ -12043,7 +12043,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" t="str">
-        <f>IF(SD!A9&gt;0,SD!A9,"")</f>
+        <f>IF(SD!B2&gt;0,SD!B2,"")</f>
         <v>Staff</v>
       </c>
       <c r="B12">
@@ -12109,7 +12109,7 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" t="str">
-        <f>IF(SD!A10&gt;0,SD!A10,"")</f>
+        <f>IF(SD!B3&gt;0,SD!B3,"")</f>
         <v>Staff AVG</v>
       </c>
       <c r="B13">
@@ -12175,7 +12175,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" t="str">
-        <f>IF(SD!A11&gt;0,SD!A11,"")</f>
+        <f>IF(SD!B4&gt;0,SD!B4,"")</f>
         <v>Plan</v>
       </c>
       <c r="B14">
@@ -12303,7 +12303,7 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" t="str">
-        <f>IF(SD!A13&gt;0,SD!A13,"")</f>
+        <f>IF(SD!B2&gt;0,SD!B2,"")</f>
         <v>Staff</v>
       </c>
       <c r="B22">
@@ -12369,7 +12369,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" t="str">
-        <f>IF(SD!A14&gt;0,SD!A14,"")</f>
+        <f>IF(SD!B3&gt;0,SD!B3,"")</f>
         <v>Staff AVG</v>
       </c>
       <c r="B23">
@@ -12435,7 +12435,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" t="str">
-        <f>IF(SD!A15&gt;0,SD!A15,"")</f>
+        <f>IF(SD!B4&gt;0,SD!B4,"")</f>
         <v>Plan</v>
       </c>
       <c r="B24">
@@ -12563,7 +12563,7 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" t="str">
-        <f>IF(SD!A17&gt;0,SD!A17,"")</f>
+        <f>IF(SD!B2&gt;0,SD!B2,"")</f>
         <v>Staff</v>
       </c>
       <c r="B32">
@@ -12629,7 +12629,7 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33" t="str">
-        <f>IF(SD!A18&gt;0,SD!A18,"")</f>
+        <f>IF(SD!B3&gt;0,SD!B3,"")</f>
         <v>Staff AVG</v>
       </c>
       <c r="B33">
@@ -12695,7 +12695,7 @@
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34" t="str">
-        <f>IF(SD!A19&gt;0,SD!A19,"")</f>
+        <f>IF(SD!B4&gt;0,SD!B4,"")</f>
         <v>Plan</v>
       </c>
       <c r="B34">

--- a/workforceresult.xlsx
+++ b/workforceresult.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miiintra/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55E74702-662D-5D44-96A2-D291D4F6D613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5247C21A-2649-E140-AEDA-80984B3C94CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14500" yWindow="3140" windowWidth="28800" windowHeight="18680" activeTab="9" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
+    <workbookView xWindow="14500" yWindow="620" windowWidth="28800" windowHeight="21200" activeTab="9" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
   </bookViews>
   <sheets>
     <sheet name="ALL" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="77">
   <si>
     <t>Type</t>
   </si>
@@ -150,12 +150,268 @@
   <si>
     <t>AIC</t>
   </si>
+  <si>
+    <t>Section</t>
+  </si>
+  <si>
+    <t>Commercial Products &amp; Solutions</t>
+  </si>
+  <si>
+    <t>Business Development &amp; Partnerships</t>
+  </si>
+  <si>
+    <t>Product Commercialization</t>
+  </si>
+  <si>
+    <t>Platform &amp; Software Engineering</t>
+  </si>
+  <si>
+    <t>Platform Engineering</t>
+  </si>
+  <si>
+    <r>
+      <t>Platform Engineering:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF7B7B7B"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>TH</t>
+    </r>
+  </si>
+  <si>
+    <t>Platform Engineering:TH</t>
+  </si>
+  <si>
+    <r>
+      <t>Platform Engineering:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF7B7B7B"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>CT</t>
+    </r>
+  </si>
+  <si>
+    <t>Platform Engineering:CT</t>
+  </si>
+  <si>
+    <t>Software Engineering</t>
+  </si>
+  <si>
+    <r>
+      <t>Software Engineering:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF7B7B7B"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>TH</t>
+    </r>
+  </si>
+  <si>
+    <t>Software Engineering:TH</t>
+  </si>
+  <si>
+    <r>
+      <t>Software Engineering:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF7B7B7B"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>CT</t>
+    </r>
+  </si>
+  <si>
+    <t>Software Engineering:CT</t>
+  </si>
+  <si>
+    <r>
+      <t>Software Engineering:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF7B7B7B"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>OS</t>
+    </r>
+  </si>
+  <si>
+    <t>Software Engineering:OS</t>
+  </si>
+  <si>
+    <t>Solution Delivery</t>
+  </si>
+  <si>
+    <t>Design</t>
+  </si>
+  <si>
+    <t>Data Technology</t>
+  </si>
+  <si>
+    <r>
+      <t>Data Technology:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF7B7B7B"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>TH</t>
+    </r>
+  </si>
+  <si>
+    <t>Data Technology:TH</t>
+  </si>
+  <si>
+    <r>
+      <t>Data Technology:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF7B7B7B"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>CT</t>
+    </r>
+  </si>
+  <si>
+    <t>Data Technology:CT</t>
+  </si>
+  <si>
+    <t>Solution Architecture</t>
+  </si>
+  <si>
+    <t>Site Reliability Engineering</t>
+  </si>
+  <si>
+    <t>Cyber Security</t>
+  </si>
+  <si>
+    <t>Project Management</t>
+  </si>
+  <si>
+    <t>Technology Analyst</t>
+  </si>
+  <si>
+    <t>Technology QA</t>
+  </si>
+  <si>
+    <r>
+      <t>Technology QA:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF7B7B7B"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>TH</t>
+    </r>
+  </si>
+  <si>
+    <t>Technology QA:TH</t>
+  </si>
+  <si>
+    <r>
+      <t>Technology QA:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF7B7B7B"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>CT</t>
+    </r>
+  </si>
+  <si>
+    <t>Technology QA:CT</t>
+  </si>
+  <si>
+    <r>
+      <t>Technology QA:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF7B7B7B"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>OS</t>
+    </r>
+  </si>
+  <si>
+    <t>Technology QA:OS</t>
+  </si>
+  <si>
+    <t>Technology Management</t>
+  </si>
+  <si>
+    <t>AI Research &amp; Alliance</t>
+  </si>
+  <si>
+    <t>AIET AI Engineering</t>
+  </si>
+  <si>
+    <t>AIET IoT Engineering</t>
+  </si>
+  <si>
+    <t>AIET Spatial AI Engineering</t>
+  </si>
+  <si>
+    <t>Product Innovation</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -223,8 +479,36 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFDDEBF7"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7B7B7B"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7B7B7B"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FFEDEDED"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -303,8 +587,20 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5B9BD5"/>
+        <bgColor rgb="FF5B9BD5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5B9BD5"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -321,11 +617,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -379,6 +684,30 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1998,7 +2327,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:P47"/>
+  <dimension ref="A1:P93"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.83203125" bestFit="1" customWidth="1"/>
@@ -3418,6 +3747,996 @@
       <c r="F47" t="str">
         <f>IF(AIC!G49&gt;0,AIC!G49,"")</f>
         <v/>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A51" t="str">
+        <f>AIC!A64</f>
+        <v>AI Research &amp; Alliance</v>
+      </c>
+      <c r="B51" t="str">
+        <f>AIC!C$61</f>
+        <v>JAN</v>
+      </c>
+      <c r="C51" t="str">
+        <f>AIC!D$61</f>
+        <v>FEB</v>
+      </c>
+      <c r="D51" t="str">
+        <f>AIC!E$61</f>
+        <v>MAR</v>
+      </c>
+      <c r="E51" t="str">
+        <f>AIC!F$61</f>
+        <v>APR</v>
+      </c>
+      <c r="F51" t="str">
+        <f>AIC!G$61</f>
+        <v>MAY</v>
+      </c>
+      <c r="G51" t="str">
+        <f>AIC!H$61</f>
+        <v>JUN</v>
+      </c>
+      <c r="H51" t="str">
+        <f>AIC!I$61</f>
+        <v>JUL</v>
+      </c>
+      <c r="I51" t="str">
+        <f>AIC!J$61</f>
+        <v>AUG</v>
+      </c>
+      <c r="J51" t="str">
+        <f>AIC!K$61</f>
+        <v>SEP</v>
+      </c>
+      <c r="K51" t="str">
+        <f>AIC!L$61</f>
+        <v>OCT</v>
+      </c>
+      <c r="L51" t="str">
+        <f>AIC!M$61</f>
+        <v>NOV</v>
+      </c>
+      <c r="M51" t="str">
+        <f>AIC!N$61</f>
+        <v>DEC</v>
+      </c>
+      <c r="N51" t="str">
+        <f>AIC!O$61</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O51" t="str">
+        <f>AIC!P$61</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P51" t="str">
+        <f>AIC!Q$61</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A52" t="str">
+        <f>IF(AIC!B64&gt;0,AIC!B64,"")</f>
+        <v>Staff</v>
+      </c>
+      <c r="B52">
+        <f>IF(AIC!C64&gt;0,AIC!C64,"")</f>
+        <v>4</v>
+      </c>
+      <c r="C52">
+        <f>IF(AIC!D64&gt;0,AIC!D64,"")</f>
+        <v>4</v>
+      </c>
+      <c r="D52">
+        <f>IF(AIC!E64&gt;0,AIC!E64,"")</f>
+        <v>3</v>
+      </c>
+      <c r="E52">
+        <f>IF(AIC!F64&gt;0,AIC!F64,"")</f>
+        <v>3</v>
+      </c>
+      <c r="F52">
+        <f>IF(AIC!G64&gt;0,AIC!G64,"")</f>
+        <v>3</v>
+      </c>
+      <c r="G52">
+        <f>IF(AIC!H64&gt;0,AIC!H64,"")</f>
+        <v>3</v>
+      </c>
+      <c r="H52">
+        <f>IF(AIC!I64&gt;0,AIC!I64,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I52">
+        <f>IF(AIC!J64&gt;0,AIC!J64,"")</f>
+        <v>3</v>
+      </c>
+      <c r="J52">
+        <f>IF(AIC!K64&gt;0,AIC!K64,"")</f>
+        <v>3</v>
+      </c>
+      <c r="K52">
+        <f>IF(AIC!L64&gt;0,AIC!L64,"")</f>
+        <v>3</v>
+      </c>
+      <c r="L52">
+        <f>IF(AIC!M64&gt;0,AIC!M64,"")</f>
+        <v>3</v>
+      </c>
+      <c r="M52">
+        <f>IF(AIC!N64&gt;0,AIC!N64,"")</f>
+        <v>3</v>
+      </c>
+      <c r="N52">
+        <f>IF(AIC!O64&gt;0,AIC!O64,"")</f>
+        <v>3</v>
+      </c>
+      <c r="O52">
+        <f>IF(AIC!P64&gt;0,AIC!P64,"")</f>
+        <v>3</v>
+      </c>
+      <c r="P52">
+        <f>IF(AIC!Q64&gt;0,AIC!Q64,"")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A53" t="str">
+        <f>IF(AIC!B65&gt;0,AIC!B65,"")</f>
+        <v>Plan</v>
+      </c>
+      <c r="B53">
+        <f>IF(AIC!C65&gt;0,AIC!C65,"")</f>
+        <v>2.8</v>
+      </c>
+      <c r="C53">
+        <f>IF(AIC!D65&gt;0,AIC!D65,"")</f>
+        <v>2.8</v>
+      </c>
+      <c r="D53">
+        <f>IF(AIC!E65&gt;0,AIC!E65,"")</f>
+        <v>2.8</v>
+      </c>
+      <c r="E53">
+        <f>IF(AIC!F65&gt;0,AIC!F65,"")</f>
+        <v>2.9</v>
+      </c>
+      <c r="F53">
+        <f>IF(AIC!G65&gt;0,AIC!G65,"")</f>
+        <v>2.9</v>
+      </c>
+      <c r="G53">
+        <f>IF(AIC!H65&gt;0,AIC!H65,"")</f>
+        <v>2.9</v>
+      </c>
+      <c r="H53">
+        <f>IF(AIC!I65&gt;0,AIC!I65,"")</f>
+        <v>2.9</v>
+      </c>
+      <c r="I53">
+        <f>IF(AIC!J65&gt;0,AIC!J65,"")</f>
+        <v>2.9</v>
+      </c>
+      <c r="J53">
+        <f>IF(AIC!K65&gt;0,AIC!K65,"")</f>
+        <v>2.9</v>
+      </c>
+      <c r="K53">
+        <f>IF(AIC!L65&gt;0,AIC!L65,"")</f>
+        <v>2.9</v>
+      </c>
+      <c r="L53">
+        <f>IF(AIC!M65&gt;0,AIC!M65,"")</f>
+        <v>2.9</v>
+      </c>
+      <c r="M53">
+        <f>IF(AIC!N65&gt;0,AIC!N65,"")</f>
+        <v>2.9</v>
+      </c>
+      <c r="N53">
+        <f>IF(AIC!O65&gt;0,AIC!O65,"")</f>
+        <v>2.9</v>
+      </c>
+      <c r="O53">
+        <f>IF(AIC!P65&gt;0,AIC!P65,"")</f>
+        <v>2.9</v>
+      </c>
+      <c r="P53">
+        <f>IF(AIC!Q65&gt;0,AIC!Q65,"")</f>
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A61" t="str">
+        <f>AIC!A66</f>
+        <v>AIET AI Engineering</v>
+      </c>
+      <c r="B61" t="str">
+        <f>AIC!C$61</f>
+        <v>JAN</v>
+      </c>
+      <c r="C61" t="str">
+        <f>AIC!D$61</f>
+        <v>FEB</v>
+      </c>
+      <c r="D61" t="str">
+        <f>AIC!E$61</f>
+        <v>MAR</v>
+      </c>
+      <c r="E61" t="str">
+        <f>AIC!F$61</f>
+        <v>APR</v>
+      </c>
+      <c r="F61" t="str">
+        <f>AIC!G$61</f>
+        <v>MAY</v>
+      </c>
+      <c r="G61" t="str">
+        <f>AIC!H$61</f>
+        <v>JUN</v>
+      </c>
+      <c r="H61" t="str">
+        <f>AIC!I$61</f>
+        <v>JUL</v>
+      </c>
+      <c r="I61" t="str">
+        <f>AIC!J$61</f>
+        <v>AUG</v>
+      </c>
+      <c r="J61" t="str">
+        <f>AIC!K$61</f>
+        <v>SEP</v>
+      </c>
+      <c r="K61" t="str">
+        <f>AIC!L$61</f>
+        <v>OCT</v>
+      </c>
+      <c r="L61" t="str">
+        <f>AIC!M$61</f>
+        <v>NOV</v>
+      </c>
+      <c r="M61" t="str">
+        <f>AIC!N$61</f>
+        <v>DEC</v>
+      </c>
+      <c r="N61" t="str">
+        <f>AIC!O$61</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O61" t="str">
+        <f>AIC!P$61</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P61" t="str">
+        <f>AIC!Q$61</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A62" t="str">
+        <f>AIC!B66</f>
+        <v>Staff</v>
+      </c>
+      <c r="B62">
+        <f>AIC!C66</f>
+        <v>8</v>
+      </c>
+      <c r="C62">
+        <f>AIC!D66</f>
+        <v>8</v>
+      </c>
+      <c r="D62">
+        <f>AIC!E66</f>
+        <v>8</v>
+      </c>
+      <c r="E62">
+        <f>AIC!F66</f>
+        <v>8</v>
+      </c>
+      <c r="F62">
+        <f>AIC!G66</f>
+        <v>8</v>
+      </c>
+      <c r="G62">
+        <f>AIC!H66</f>
+        <v>8</v>
+      </c>
+      <c r="H62">
+        <f>AIC!I66</f>
+        <v>8</v>
+      </c>
+      <c r="I62">
+        <f>AIC!J66</f>
+        <v>8</v>
+      </c>
+      <c r="J62">
+        <f>AIC!K66</f>
+        <v>8</v>
+      </c>
+      <c r="K62">
+        <f>AIC!L66</f>
+        <v>8</v>
+      </c>
+      <c r="L62">
+        <f>AIC!M66</f>
+        <v>8</v>
+      </c>
+      <c r="M62">
+        <f>AIC!N66</f>
+        <v>8</v>
+      </c>
+      <c r="N62">
+        <f>AIC!O66</f>
+        <v>8</v>
+      </c>
+      <c r="O62">
+        <f>AIC!P66</f>
+        <v>8</v>
+      </c>
+      <c r="P62">
+        <f>AIC!Q66</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A63" t="str">
+        <f>AIC!B67</f>
+        <v>Plan</v>
+      </c>
+      <c r="B63">
+        <f>AIC!C67</f>
+        <v>5.2125000000000004</v>
+      </c>
+      <c r="C63">
+        <f>AIC!D67</f>
+        <v>6.2406249999999996</v>
+      </c>
+      <c r="D63">
+        <f>AIC!E67</f>
+        <v>6.140625</v>
+      </c>
+      <c r="E63">
+        <f>AIC!F67</f>
+        <v>7.0131249999999996</v>
+      </c>
+      <c r="F63">
+        <f>AIC!G67</f>
+        <v>7.0881249999999998</v>
+      </c>
+      <c r="G63">
+        <f>AIC!H67</f>
+        <v>6.9881250000000001</v>
+      </c>
+      <c r="H63">
+        <f>AIC!I67</f>
+        <v>5.3475000000000001</v>
+      </c>
+      <c r="I63">
+        <f>AIC!J67</f>
+        <v>5.1475</v>
+      </c>
+      <c r="J63">
+        <f>AIC!K67</f>
+        <v>5.1475</v>
+      </c>
+      <c r="K63">
+        <f>AIC!L67</f>
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="L63">
+        <f>AIC!M67</f>
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="M63">
+        <f>AIC!N67</f>
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="N63">
+        <f>AIC!O67</f>
+        <v>3.6850000000000001</v>
+      </c>
+      <c r="O63">
+        <f>AIC!P67</f>
+        <v>3.6850000000000001</v>
+      </c>
+      <c r="P63">
+        <f>AIC!Q67</f>
+        <v>3.6850000000000001</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A71" t="str">
+        <f>AIC!A68</f>
+        <v>AIET IoT Engineering</v>
+      </c>
+      <c r="B71" t="str">
+        <f>AIC!C$61</f>
+        <v>JAN</v>
+      </c>
+      <c r="C71" t="str">
+        <f>AIC!D$61</f>
+        <v>FEB</v>
+      </c>
+      <c r="D71" t="str">
+        <f>AIC!E$61</f>
+        <v>MAR</v>
+      </c>
+      <c r="E71" t="str">
+        <f>AIC!F$61</f>
+        <v>APR</v>
+      </c>
+      <c r="F71" t="str">
+        <f>AIC!G$61</f>
+        <v>MAY</v>
+      </c>
+      <c r="G71" t="str">
+        <f>AIC!H$61</f>
+        <v>JUN</v>
+      </c>
+      <c r="H71" t="str">
+        <f>AIC!I$61</f>
+        <v>JUL</v>
+      </c>
+      <c r="I71" t="str">
+        <f>AIC!J$61</f>
+        <v>AUG</v>
+      </c>
+      <c r="J71" t="str">
+        <f>AIC!K$61</f>
+        <v>SEP</v>
+      </c>
+      <c r="K71" t="str">
+        <f>AIC!L$61</f>
+        <v>OCT</v>
+      </c>
+      <c r="L71" t="str">
+        <f>AIC!M$61</f>
+        <v>NOV</v>
+      </c>
+      <c r="M71" t="str">
+        <f>AIC!N$61</f>
+        <v>DEC</v>
+      </c>
+      <c r="N71" t="str">
+        <f>AIC!O$61</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O71" t="str">
+        <f>AIC!P$61</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P71" t="str">
+        <f>AIC!Q$61</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A72" t="str">
+        <f>AIC!B68</f>
+        <v>Staff</v>
+      </c>
+      <c r="B72">
+        <f>AIC!C68</f>
+        <v>7</v>
+      </c>
+      <c r="C72">
+        <f>AIC!D68</f>
+        <v>6</v>
+      </c>
+      <c r="D72">
+        <f>AIC!E68</f>
+        <v>6</v>
+      </c>
+      <c r="E72">
+        <f>AIC!F68</f>
+        <v>6</v>
+      </c>
+      <c r="F72">
+        <f>AIC!G68</f>
+        <v>6</v>
+      </c>
+      <c r="G72">
+        <f>AIC!H68</f>
+        <v>6</v>
+      </c>
+      <c r="H72">
+        <f>AIC!I68</f>
+        <v>5</v>
+      </c>
+      <c r="I72">
+        <f>AIC!J68</f>
+        <v>5</v>
+      </c>
+      <c r="J72">
+        <f>AIC!K68</f>
+        <v>5</v>
+      </c>
+      <c r="K72">
+        <f>AIC!L68</f>
+        <v>5</v>
+      </c>
+      <c r="L72">
+        <f>AIC!M68</f>
+        <v>5</v>
+      </c>
+      <c r="M72">
+        <f>AIC!N68</f>
+        <v>5</v>
+      </c>
+      <c r="N72">
+        <f>AIC!O68</f>
+        <v>5</v>
+      </c>
+      <c r="O72">
+        <f>AIC!P68</f>
+        <v>5</v>
+      </c>
+      <c r="P72">
+        <f>AIC!Q68</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A73" t="str">
+        <f>AIC!B69</f>
+        <v>Plan</v>
+      </c>
+      <c r="B73">
+        <f>AIC!C69</f>
+        <v>4.2</v>
+      </c>
+      <c r="C73">
+        <f>AIC!D69</f>
+        <v>4.5</v>
+      </c>
+      <c r="D73">
+        <f>AIC!E69</f>
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="E73">
+        <f>AIC!F69</f>
+        <v>5.05</v>
+      </c>
+      <c r="F73">
+        <f>AIC!G69</f>
+        <v>5.3</v>
+      </c>
+      <c r="G73">
+        <f>AIC!H69</f>
+        <v>4.95</v>
+      </c>
+      <c r="H73">
+        <f>AIC!I69</f>
+        <v>4.45</v>
+      </c>
+      <c r="I73">
+        <f>AIC!J69</f>
+        <v>3.8</v>
+      </c>
+      <c r="J73">
+        <f>AIC!K69</f>
+        <v>3.75</v>
+      </c>
+      <c r="K73">
+        <f>AIC!L69</f>
+        <v>3.7</v>
+      </c>
+      <c r="L73">
+        <f>AIC!M69</f>
+        <v>3.7</v>
+      </c>
+      <c r="M73">
+        <f>AIC!N69</f>
+        <v>3.7</v>
+      </c>
+      <c r="N73">
+        <f>AIC!O69</f>
+        <v>1.4</v>
+      </c>
+      <c r="O73">
+        <f>AIC!P69</f>
+        <v>1.4</v>
+      </c>
+      <c r="P73">
+        <f>AIC!Q69</f>
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A81" t="str">
+        <f>AIC!A70</f>
+        <v>AIET Spatial AI Engineering</v>
+      </c>
+      <c r="B81" t="str">
+        <f>AIC!C$61</f>
+        <v>JAN</v>
+      </c>
+      <c r="C81" t="str">
+        <f>AIC!D$61</f>
+        <v>FEB</v>
+      </c>
+      <c r="D81" t="str">
+        <f>AIC!E$61</f>
+        <v>MAR</v>
+      </c>
+      <c r="E81" t="str">
+        <f>AIC!F$61</f>
+        <v>APR</v>
+      </c>
+      <c r="F81" t="str">
+        <f>AIC!G$61</f>
+        <v>MAY</v>
+      </c>
+      <c r="G81" t="str">
+        <f>AIC!H$61</f>
+        <v>JUN</v>
+      </c>
+      <c r="H81" t="str">
+        <f>AIC!I$61</f>
+        <v>JUL</v>
+      </c>
+      <c r="I81" t="str">
+        <f>AIC!J$61</f>
+        <v>AUG</v>
+      </c>
+      <c r="J81" t="str">
+        <f>AIC!K$61</f>
+        <v>SEP</v>
+      </c>
+      <c r="K81" t="str">
+        <f>AIC!L$61</f>
+        <v>OCT</v>
+      </c>
+      <c r="L81" t="str">
+        <f>AIC!M$61</f>
+        <v>NOV</v>
+      </c>
+      <c r="M81" t="str">
+        <f>AIC!N$61</f>
+        <v>DEC</v>
+      </c>
+      <c r="N81" t="str">
+        <f>AIC!O$61</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O81" t="str">
+        <f>AIC!P$61</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P81" t="str">
+        <f>AIC!Q$61</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A82" t="str">
+        <f>AIC!B70</f>
+        <v>Staff</v>
+      </c>
+      <c r="B82">
+        <f>AIC!C70</f>
+        <v>4</v>
+      </c>
+      <c r="C82">
+        <f>AIC!D70</f>
+        <v>4</v>
+      </c>
+      <c r="D82">
+        <f>AIC!E70</f>
+        <v>4</v>
+      </c>
+      <c r="E82">
+        <f>AIC!F70</f>
+        <v>4</v>
+      </c>
+      <c r="F82">
+        <f>AIC!G70</f>
+        <v>3</v>
+      </c>
+      <c r="G82">
+        <f>AIC!H70</f>
+        <v>3</v>
+      </c>
+      <c r="H82">
+        <f>AIC!I70</f>
+        <v>3</v>
+      </c>
+      <c r="I82">
+        <f>AIC!J70</f>
+        <v>3</v>
+      </c>
+      <c r="J82">
+        <f>AIC!K70</f>
+        <v>3</v>
+      </c>
+      <c r="K82">
+        <f>AIC!L70</f>
+        <v>3</v>
+      </c>
+      <c r="L82">
+        <f>AIC!M70</f>
+        <v>3</v>
+      </c>
+      <c r="M82">
+        <f>AIC!N70</f>
+        <v>3</v>
+      </c>
+      <c r="N82">
+        <f>AIC!O70</f>
+        <v>3</v>
+      </c>
+      <c r="O82">
+        <f>AIC!P70</f>
+        <v>3</v>
+      </c>
+      <c r="P82">
+        <f>AIC!Q70</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A83" t="str">
+        <f>AIC!B71</f>
+        <v>Plan</v>
+      </c>
+      <c r="B83">
+        <f>AIC!C71</f>
+        <v>3.1</v>
+      </c>
+      <c r="C83">
+        <f>AIC!D71</f>
+        <v>3.2</v>
+      </c>
+      <c r="D83">
+        <f>AIC!E71</f>
+        <v>2.9874999999999998</v>
+      </c>
+      <c r="E83">
+        <f>AIC!F71</f>
+        <v>3.6</v>
+      </c>
+      <c r="F83">
+        <f>AIC!G71</f>
+        <v>3.105</v>
+      </c>
+      <c r="G83">
+        <f>AIC!H71</f>
+        <v>3.125</v>
+      </c>
+      <c r="H83">
+        <f>AIC!I71</f>
+        <v>3.125</v>
+      </c>
+      <c r="I83">
+        <f>AIC!J71</f>
+        <v>3.125</v>
+      </c>
+      <c r="J83">
+        <f>AIC!K71</f>
+        <v>2.5750000000000002</v>
+      </c>
+      <c r="K83">
+        <f>AIC!L71</f>
+        <v>2.875</v>
+      </c>
+      <c r="L83">
+        <f>AIC!M71</f>
+        <v>2.9249999999999998</v>
+      </c>
+      <c r="M83">
+        <f>AIC!N71</f>
+        <v>2.625</v>
+      </c>
+      <c r="N83">
+        <f>AIC!O71</f>
+        <v>0.4</v>
+      </c>
+      <c r="O83">
+        <f>AIC!P71</f>
+        <v>0.4</v>
+      </c>
+      <c r="P83">
+        <f>AIC!Q71</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A91" t="str">
+        <f>AIC!A72</f>
+        <v>Product Innovation</v>
+      </c>
+      <c r="B91" t="str">
+        <f>AIC!C$61</f>
+        <v>JAN</v>
+      </c>
+      <c r="C91" t="str">
+        <f>AIC!D$61</f>
+        <v>FEB</v>
+      </c>
+      <c r="D91" t="str">
+        <f>AIC!E$61</f>
+        <v>MAR</v>
+      </c>
+      <c r="E91" t="str">
+        <f>AIC!F$61</f>
+        <v>APR</v>
+      </c>
+      <c r="F91" t="str">
+        <f>AIC!G$61</f>
+        <v>MAY</v>
+      </c>
+      <c r="G91" t="str">
+        <f>AIC!H$61</f>
+        <v>JUN</v>
+      </c>
+      <c r="H91" t="str">
+        <f>AIC!I$61</f>
+        <v>JUL</v>
+      </c>
+      <c r="I91" t="str">
+        <f>AIC!J$61</f>
+        <v>AUG</v>
+      </c>
+      <c r="J91" t="str">
+        <f>AIC!K$61</f>
+        <v>SEP</v>
+      </c>
+      <c r="K91" t="str">
+        <f>AIC!L$61</f>
+        <v>OCT</v>
+      </c>
+      <c r="L91" t="str">
+        <f>AIC!M$61</f>
+        <v>NOV</v>
+      </c>
+      <c r="M91" t="str">
+        <f>AIC!N$61</f>
+        <v>DEC</v>
+      </c>
+      <c r="N91" t="str">
+        <f>AIC!O$61</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O91" t="str">
+        <f>AIC!P$61</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P91" t="str">
+        <f>AIC!Q$61</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A92" t="str">
+        <f>AIC!B72</f>
+        <v>Staff</v>
+      </c>
+      <c r="B92">
+        <f>AIC!C72</f>
+        <v>1</v>
+      </c>
+      <c r="C92">
+        <f>AIC!D72</f>
+        <v>1</v>
+      </c>
+      <c r="D92">
+        <f>AIC!E72</f>
+        <v>1</v>
+      </c>
+      <c r="E92">
+        <f>AIC!F72</f>
+        <v>0</v>
+      </c>
+      <c r="F92">
+        <f>AIC!G72</f>
+        <v>0</v>
+      </c>
+      <c r="G92">
+        <f>AIC!H72</f>
+        <v>0</v>
+      </c>
+      <c r="H92">
+        <f>AIC!I72</f>
+        <v>0</v>
+      </c>
+      <c r="I92">
+        <f>AIC!J72</f>
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <f>AIC!K72</f>
+        <v>0</v>
+      </c>
+      <c r="K92">
+        <f>AIC!L72</f>
+        <v>0</v>
+      </c>
+      <c r="L92">
+        <f>AIC!M72</f>
+        <v>0</v>
+      </c>
+      <c r="M92">
+        <f>AIC!N72</f>
+        <v>0</v>
+      </c>
+      <c r="N92">
+        <f>AIC!O72</f>
+        <v>0</v>
+      </c>
+      <c r="O92">
+        <f>AIC!P72</f>
+        <v>0</v>
+      </c>
+      <c r="P92">
+        <f>AIC!Q72</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A93" t="str">
+        <f>AIC!B73</f>
+        <v>Plan</v>
+      </c>
+      <c r="B93">
+        <f>AIC!C73</f>
+        <v>0.6</v>
+      </c>
+      <c r="C93">
+        <f>AIC!D73</f>
+        <v>0.6</v>
+      </c>
+      <c r="D93">
+        <f>AIC!E73</f>
+        <v>0.4</v>
+      </c>
+      <c r="E93">
+        <f>AIC!F73</f>
+        <v>0</v>
+      </c>
+      <c r="F93">
+        <f>AIC!G73</f>
+        <v>0</v>
+      </c>
+      <c r="G93">
+        <f>AIC!H73</f>
+        <v>0</v>
+      </c>
+      <c r="H93">
+        <f>AIC!I73</f>
+        <v>0</v>
+      </c>
+      <c r="I93">
+        <f>AIC!J73</f>
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <f>AIC!K73</f>
+        <v>0</v>
+      </c>
+      <c r="K93">
+        <f>AIC!L73</f>
+        <v>0</v>
+      </c>
+      <c r="L93">
+        <f>AIC!M73</f>
+        <v>0</v>
+      </c>
+      <c r="M93">
+        <f>AIC!N73</f>
+        <v>0</v>
+      </c>
+      <c r="N93">
+        <f>AIC!O73</f>
+        <v>0</v>
+      </c>
+      <c r="O93">
+        <f>AIC!P73</f>
+        <v>0</v>
+      </c>
+      <c r="P93">
+        <f>AIC!Q73</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4862,7 +6181,7 @@
   <sheetPr>
     <tabColor theme="5"/>
   </sheetPr>
-  <dimension ref="A1:Q49"/>
+  <dimension ref="A1:Q69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.2">
@@ -6092,7 +7411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A49" s="16">
         <v>0</v>
       </c>
@@ -6113,6 +7432,477 @@
       </c>
       <c r="G49" s="21">
         <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A61" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="B61" s="34"/>
+      <c r="C61" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I61" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J61" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="K61" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="L61" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="M61" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="N61" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O61" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="P61" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q61" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A62" s="12"/>
+      <c r="B62" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" s="35">
+        <v>18</v>
+      </c>
+      <c r="D62" s="35">
+        <v>18</v>
+      </c>
+      <c r="E62" s="35">
+        <v>18</v>
+      </c>
+      <c r="F62" s="35">
+        <v>17</v>
+      </c>
+      <c r="G62" s="35">
+        <v>17</v>
+      </c>
+      <c r="H62" s="35">
+        <v>17</v>
+      </c>
+      <c r="I62" s="35">
+        <v>17</v>
+      </c>
+      <c r="J62" s="35">
+        <v>17</v>
+      </c>
+      <c r="K62" s="35">
+        <v>17</v>
+      </c>
+      <c r="L62" s="35">
+        <v>17</v>
+      </c>
+      <c r="M62" s="35">
+        <v>17</v>
+      </c>
+      <c r="N62" s="35">
+        <v>17</v>
+      </c>
+      <c r="O62" s="35">
+        <v>17</v>
+      </c>
+      <c r="P62" s="35">
+        <v>17</v>
+      </c>
+      <c r="Q62" s="35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A63" s="36"/>
+      <c r="B63" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" s="38">
+        <v>16.850000000000001</v>
+      </c>
+      <c r="D63" s="38">
+        <v>16.95</v>
+      </c>
+      <c r="E63" s="38">
+        <v>16.649999999999999</v>
+      </c>
+      <c r="F63" s="38">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="G63" s="38">
+        <v>17.5</v>
+      </c>
+      <c r="H63" s="38">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="I63" s="38">
+        <v>16.2</v>
+      </c>
+      <c r="J63" s="38">
+        <v>16</v>
+      </c>
+      <c r="K63" s="38">
+        <v>16</v>
+      </c>
+      <c r="L63" s="38">
+        <v>15.9</v>
+      </c>
+      <c r="M63" s="38">
+        <v>15.7</v>
+      </c>
+      <c r="N63" s="38">
+        <v>15.7</v>
+      </c>
+      <c r="O63" s="38">
+        <v>14.2</v>
+      </c>
+      <c r="P63" s="38">
+        <v>14.2</v>
+      </c>
+      <c r="Q63" s="38">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A64" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" s="15">
+        <v>1</v>
+      </c>
+      <c r="D64" s="15">
+        <v>1</v>
+      </c>
+      <c r="E64" s="15">
+        <v>1</v>
+      </c>
+      <c r="F64" s="15">
+        <v>1</v>
+      </c>
+      <c r="G64" s="15">
+        <v>1</v>
+      </c>
+      <c r="H64" s="15">
+        <v>1</v>
+      </c>
+      <c r="I64" s="15">
+        <v>1</v>
+      </c>
+      <c r="J64" s="15">
+        <v>1</v>
+      </c>
+      <c r="K64" s="15">
+        <v>1</v>
+      </c>
+      <c r="L64" s="15">
+        <v>1</v>
+      </c>
+      <c r="M64" s="15">
+        <v>1</v>
+      </c>
+      <c r="N64" s="15">
+        <v>1</v>
+      </c>
+      <c r="O64" s="15">
+        <v>1</v>
+      </c>
+      <c r="P64" s="15">
+        <v>1</v>
+      </c>
+      <c r="Q64" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A65" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="B65" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C65" s="8">
+        <v>1</v>
+      </c>
+      <c r="D65" s="8">
+        <v>1</v>
+      </c>
+      <c r="E65" s="8">
+        <v>1</v>
+      </c>
+      <c r="F65" s="8">
+        <v>1</v>
+      </c>
+      <c r="G65" s="8">
+        <v>1</v>
+      </c>
+      <c r="H65" s="8">
+        <v>1</v>
+      </c>
+      <c r="I65" s="8">
+        <v>1</v>
+      </c>
+      <c r="J65" s="8">
+        <v>1</v>
+      </c>
+      <c r="K65" s="8">
+        <v>1</v>
+      </c>
+      <c r="L65" s="8">
+        <v>1</v>
+      </c>
+      <c r="M65" s="8">
+        <v>1</v>
+      </c>
+      <c r="N65" s="8">
+        <v>1</v>
+      </c>
+      <c r="O65" s="8">
+        <v>1</v>
+      </c>
+      <c r="P65" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q65" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A66" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" s="15">
+        <v>12</v>
+      </c>
+      <c r="D66" s="15">
+        <v>12</v>
+      </c>
+      <c r="E66" s="15">
+        <v>12</v>
+      </c>
+      <c r="F66" s="15">
+        <v>11</v>
+      </c>
+      <c r="G66" s="15">
+        <v>11</v>
+      </c>
+      <c r="H66" s="15">
+        <v>11</v>
+      </c>
+      <c r="I66" s="15">
+        <v>11</v>
+      </c>
+      <c r="J66" s="15">
+        <v>11</v>
+      </c>
+      <c r="K66" s="15">
+        <v>11</v>
+      </c>
+      <c r="L66" s="15">
+        <v>11</v>
+      </c>
+      <c r="M66" s="15">
+        <v>11</v>
+      </c>
+      <c r="N66" s="15">
+        <v>11</v>
+      </c>
+      <c r="O66" s="15">
+        <v>11</v>
+      </c>
+      <c r="P66" s="15">
+        <v>11</v>
+      </c>
+      <c r="Q66" s="15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A67" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="B67" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C67" s="8">
+        <v>11.25</v>
+      </c>
+      <c r="D67" s="8">
+        <v>11.35</v>
+      </c>
+      <c r="E67" s="8">
+        <v>11.05</v>
+      </c>
+      <c r="F67" s="8">
+        <v>11.4</v>
+      </c>
+      <c r="G67" s="8">
+        <v>11.5</v>
+      </c>
+      <c r="H67" s="8">
+        <v>11.4</v>
+      </c>
+      <c r="I67" s="8">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="J67" s="8">
+        <v>10</v>
+      </c>
+      <c r="K67" s="8">
+        <v>10</v>
+      </c>
+      <c r="L67" s="8">
+        <v>9.9</v>
+      </c>
+      <c r="M67" s="8">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="N67" s="8">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="O67" s="8">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="P67" s="8">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="Q67" s="8">
+        <v>8.1999999999999993</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A68" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" s="15">
+        <v>5</v>
+      </c>
+      <c r="D68" s="15">
+        <v>5</v>
+      </c>
+      <c r="E68" s="15">
+        <v>5</v>
+      </c>
+      <c r="F68" s="15">
+        <v>5</v>
+      </c>
+      <c r="G68" s="15">
+        <v>5</v>
+      </c>
+      <c r="H68" s="15">
+        <v>5</v>
+      </c>
+      <c r="I68" s="15">
+        <v>5</v>
+      </c>
+      <c r="J68" s="15">
+        <v>5</v>
+      </c>
+      <c r="K68" s="15">
+        <v>5</v>
+      </c>
+      <c r="L68" s="15">
+        <v>5</v>
+      </c>
+      <c r="M68" s="15">
+        <v>5</v>
+      </c>
+      <c r="N68" s="15">
+        <v>5</v>
+      </c>
+      <c r="O68" s="15">
+        <v>5</v>
+      </c>
+      <c r="P68" s="15">
+        <v>5</v>
+      </c>
+      <c r="Q68" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A69" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="B69" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C69" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="D69" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="E69" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="F69" s="8">
+        <v>5</v>
+      </c>
+      <c r="G69" s="8">
+        <v>5</v>
+      </c>
+      <c r="H69" s="8">
+        <v>5</v>
+      </c>
+      <c r="I69" s="8">
+        <v>5</v>
+      </c>
+      <c r="J69" s="8">
+        <v>5</v>
+      </c>
+      <c r="K69" s="8">
+        <v>5</v>
+      </c>
+      <c r="L69" s="8">
+        <v>5</v>
+      </c>
+      <c r="M69" s="8">
+        <v>5</v>
+      </c>
+      <c r="N69" s="8">
+        <v>5</v>
+      </c>
+      <c r="O69" s="8">
+        <v>5</v>
+      </c>
+      <c r="P69" s="8">
+        <v>5</v>
+      </c>
+      <c r="Q69" s="8">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6125,7 +7915,7 @@
   <sheetPr>
     <tabColor theme="5" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:P47"/>
+  <dimension ref="A1:P63"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.83203125" bestFit="1" customWidth="1"/>
@@ -7545,6 +9335,402 @@
       <c r="F47" t="str">
         <f>IF(CPS!G49&gt;0,CPS!G49,"")</f>
         <v/>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A51" t="str">
+        <f>CPS!A66</f>
+        <v>Business Development &amp; Partnerships</v>
+      </c>
+      <c r="B51" t="str">
+        <f>CPS!C61</f>
+        <v>JAN</v>
+      </c>
+      <c r="C51" t="str">
+        <f>CPS!D61</f>
+        <v>FEB</v>
+      </c>
+      <c r="D51" t="str">
+        <f>CPS!E61</f>
+        <v>MAR</v>
+      </c>
+      <c r="E51" t="str">
+        <f>CPS!F61</f>
+        <v>APR</v>
+      </c>
+      <c r="F51" t="str">
+        <f>CPS!G61</f>
+        <v>MAY</v>
+      </c>
+      <c r="G51" t="str">
+        <f>CPS!H61</f>
+        <v>JUN</v>
+      </c>
+      <c r="H51" t="str">
+        <f>CPS!I61</f>
+        <v>JUL</v>
+      </c>
+      <c r="I51" t="str">
+        <f>CPS!J61</f>
+        <v>AUG</v>
+      </c>
+      <c r="J51" t="str">
+        <f>CPS!K61</f>
+        <v>SEP</v>
+      </c>
+      <c r="K51" t="str">
+        <f>CPS!L61</f>
+        <v>OCT</v>
+      </c>
+      <c r="L51" t="str">
+        <f>CPS!M61</f>
+        <v>NOV</v>
+      </c>
+      <c r="M51" t="str">
+        <f>CPS!N61</f>
+        <v>DEC</v>
+      </c>
+      <c r="N51" t="str">
+        <f>CPS!O61</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O51" t="str">
+        <f>CPS!P61</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P51" t="str">
+        <f>CPS!Q61</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A52" t="str">
+        <f>CPS!B66</f>
+        <v>Staff</v>
+      </c>
+      <c r="B52">
+        <f>CPS!C66</f>
+        <v>12</v>
+      </c>
+      <c r="C52">
+        <f>CPS!D66</f>
+        <v>12</v>
+      </c>
+      <c r="D52">
+        <f>CPS!E66</f>
+        <v>12</v>
+      </c>
+      <c r="E52">
+        <f>CPS!F66</f>
+        <v>11</v>
+      </c>
+      <c r="F52">
+        <f>CPS!G66</f>
+        <v>11</v>
+      </c>
+      <c r="G52">
+        <f>CPS!H66</f>
+        <v>11</v>
+      </c>
+      <c r="H52">
+        <f>CPS!I66</f>
+        <v>11</v>
+      </c>
+      <c r="I52">
+        <f>CPS!J66</f>
+        <v>11</v>
+      </c>
+      <c r="J52">
+        <f>CPS!K66</f>
+        <v>11</v>
+      </c>
+      <c r="K52">
+        <f>CPS!L66</f>
+        <v>11</v>
+      </c>
+      <c r="L52">
+        <f>CPS!M66</f>
+        <v>11</v>
+      </c>
+      <c r="M52">
+        <f>CPS!N66</f>
+        <v>11</v>
+      </c>
+      <c r="N52">
+        <f>CPS!O66</f>
+        <v>11</v>
+      </c>
+      <c r="O52">
+        <f>CPS!P66</f>
+        <v>11</v>
+      </c>
+      <c r="P52">
+        <f>CPS!Q66</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A53" t="str">
+        <f>CPS!B67</f>
+        <v>Plan</v>
+      </c>
+      <c r="B53">
+        <f>CPS!C67</f>
+        <v>11.25</v>
+      </c>
+      <c r="C53">
+        <f>CPS!D67</f>
+        <v>11.35</v>
+      </c>
+      <c r="D53">
+        <f>CPS!E67</f>
+        <v>11.05</v>
+      </c>
+      <c r="E53">
+        <f>CPS!F67</f>
+        <v>11.4</v>
+      </c>
+      <c r="F53">
+        <f>CPS!G67</f>
+        <v>11.5</v>
+      </c>
+      <c r="G53">
+        <f>CPS!H67</f>
+        <v>11.4</v>
+      </c>
+      <c r="H53">
+        <f>CPS!I67</f>
+        <v>10.199999999999999</v>
+      </c>
+      <c r="I53">
+        <f>CPS!J67</f>
+        <v>10</v>
+      </c>
+      <c r="J53">
+        <f>CPS!K67</f>
+        <v>10</v>
+      </c>
+      <c r="K53">
+        <f>CPS!L67</f>
+        <v>9.9</v>
+      </c>
+      <c r="L53">
+        <f>CPS!M67</f>
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="M53">
+        <f>CPS!N67</f>
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="N53">
+        <f>CPS!O67</f>
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="O53">
+        <f>CPS!P67</f>
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="P53">
+        <f>CPS!Q67</f>
+        <v>8.1999999999999993</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A61" t="str">
+        <f>CPS!A68</f>
+        <v>Product Commercialization</v>
+      </c>
+      <c r="B61" t="str">
+        <f>CPS!C61</f>
+        <v>JAN</v>
+      </c>
+      <c r="C61" t="str">
+        <f>CPS!D61</f>
+        <v>FEB</v>
+      </c>
+      <c r="D61" t="str">
+        <f>CPS!E61</f>
+        <v>MAR</v>
+      </c>
+      <c r="E61" t="str">
+        <f>CPS!F61</f>
+        <v>APR</v>
+      </c>
+      <c r="F61" t="str">
+        <f>CPS!G61</f>
+        <v>MAY</v>
+      </c>
+      <c r="G61" t="str">
+        <f>CPS!H61</f>
+        <v>JUN</v>
+      </c>
+      <c r="H61" t="str">
+        <f>CPS!I61</f>
+        <v>JUL</v>
+      </c>
+      <c r="I61" t="str">
+        <f>CPS!J61</f>
+        <v>AUG</v>
+      </c>
+      <c r="J61" t="str">
+        <f>CPS!K61</f>
+        <v>SEP</v>
+      </c>
+      <c r="K61" t="str">
+        <f>CPS!L61</f>
+        <v>OCT</v>
+      </c>
+      <c r="L61" t="str">
+        <f>CPS!M61</f>
+        <v>NOV</v>
+      </c>
+      <c r="M61" t="str">
+        <f>CPS!N61</f>
+        <v>DEC</v>
+      </c>
+      <c r="N61" t="str">
+        <f>CPS!O61</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O61" t="str">
+        <f>CPS!P61</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P61" t="str">
+        <f>CPS!Q61</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A62" t="str">
+        <f>CPS!B68</f>
+        <v>Staff</v>
+      </c>
+      <c r="B62">
+        <f>CPS!C68</f>
+        <v>5</v>
+      </c>
+      <c r="C62">
+        <f>CPS!D68</f>
+        <v>5</v>
+      </c>
+      <c r="D62">
+        <f>CPS!E68</f>
+        <v>5</v>
+      </c>
+      <c r="E62">
+        <f>CPS!F68</f>
+        <v>5</v>
+      </c>
+      <c r="F62">
+        <f>CPS!G68</f>
+        <v>5</v>
+      </c>
+      <c r="G62">
+        <f>CPS!H68</f>
+        <v>5</v>
+      </c>
+      <c r="H62">
+        <f>CPS!I68</f>
+        <v>5</v>
+      </c>
+      <c r="I62">
+        <f>CPS!J68</f>
+        <v>5</v>
+      </c>
+      <c r="J62">
+        <f>CPS!K68</f>
+        <v>5</v>
+      </c>
+      <c r="K62">
+        <f>CPS!L68</f>
+        <v>5</v>
+      </c>
+      <c r="L62">
+        <f>CPS!M68</f>
+        <v>5</v>
+      </c>
+      <c r="M62">
+        <f>CPS!N68</f>
+        <v>5</v>
+      </c>
+      <c r="N62">
+        <f>CPS!O68</f>
+        <v>5</v>
+      </c>
+      <c r="O62">
+        <f>CPS!P68</f>
+        <v>5</v>
+      </c>
+      <c r="P62">
+        <f>CPS!Q68</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A63" t="str">
+        <f>CPS!B69</f>
+        <v>Plan</v>
+      </c>
+      <c r="B63">
+        <f>CPS!C69</f>
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="C63">
+        <f>CPS!D69</f>
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="D63">
+        <f>CPS!E69</f>
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="E63">
+        <f>CPS!F69</f>
+        <v>5</v>
+      </c>
+      <c r="F63">
+        <f>CPS!G69</f>
+        <v>5</v>
+      </c>
+      <c r="G63">
+        <f>CPS!H69</f>
+        <v>5</v>
+      </c>
+      <c r="H63">
+        <f>CPS!I69</f>
+        <v>5</v>
+      </c>
+      <c r="I63">
+        <f>CPS!J69</f>
+        <v>5</v>
+      </c>
+      <c r="J63">
+        <f>CPS!K69</f>
+        <v>5</v>
+      </c>
+      <c r="K63">
+        <f>CPS!L69</f>
+        <v>5</v>
+      </c>
+      <c r="L63">
+        <f>CPS!M69</f>
+        <v>5</v>
+      </c>
+      <c r="M63">
+        <f>CPS!N69</f>
+        <v>5</v>
+      </c>
+      <c r="N63">
+        <f>CPS!O69</f>
+        <v>5</v>
+      </c>
+      <c r="O63">
+        <f>CPS!P69</f>
+        <v>5</v>
+      </c>
+      <c r="P63">
+        <f>CPS!Q69</f>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -7557,7 +9743,7 @@
   <sheetPr>
     <tabColor theme="7"/>
   </sheetPr>
-  <dimension ref="A1:Q49"/>
+  <dimension ref="A1:Q79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.2">
@@ -8787,7 +10973,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A49" s="16" t="s">
         <v>18</v>
       </c>
@@ -8808,6 +10994,1007 @@
       </c>
       <c r="G49" s="21">
         <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A61" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="B61" s="34"/>
+      <c r="C61" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="D61" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="E61" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I61" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J61" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="K61" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="L61" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="M61" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="N61" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O61" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="P61" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q61" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A62" s="12"/>
+      <c r="B62" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" s="35">
+        <v>45</v>
+      </c>
+      <c r="D62" s="35">
+        <v>45</v>
+      </c>
+      <c r="E62" s="35">
+        <v>45</v>
+      </c>
+      <c r="F62" s="35">
+        <v>48</v>
+      </c>
+      <c r="G62" s="35">
+        <v>48</v>
+      </c>
+      <c r="H62" s="35">
+        <v>48</v>
+      </c>
+      <c r="I62" s="35">
+        <v>48</v>
+      </c>
+      <c r="J62" s="35">
+        <v>48</v>
+      </c>
+      <c r="K62" s="35">
+        <v>48</v>
+      </c>
+      <c r="L62" s="35">
+        <v>48</v>
+      </c>
+      <c r="M62" s="35">
+        <v>48</v>
+      </c>
+      <c r="N62" s="35">
+        <v>48</v>
+      </c>
+      <c r="O62" s="35">
+        <v>48</v>
+      </c>
+      <c r="P62" s="35">
+        <v>48</v>
+      </c>
+      <c r="Q62" s="35">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A63" s="36"/>
+      <c r="B63" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" s="38">
+        <v>40.4</v>
+      </c>
+      <c r="D63" s="38">
+        <v>42.36</v>
+      </c>
+      <c r="E63" s="38">
+        <v>44.47</v>
+      </c>
+      <c r="F63" s="38">
+        <v>45.43</v>
+      </c>
+      <c r="G63" s="38">
+        <v>46.78</v>
+      </c>
+      <c r="H63" s="38">
+        <v>43.91</v>
+      </c>
+      <c r="I63" s="38">
+        <v>45.11</v>
+      </c>
+      <c r="J63" s="38">
+        <v>44.56</v>
+      </c>
+      <c r="K63" s="38">
+        <v>45.06</v>
+      </c>
+      <c r="L63" s="38">
+        <v>41.69</v>
+      </c>
+      <c r="M63" s="38">
+        <v>41</v>
+      </c>
+      <c r="N63" s="38">
+        <v>41</v>
+      </c>
+      <c r="O63" s="38">
+        <v>31.65</v>
+      </c>
+      <c r="P63" s="38">
+        <v>31.65</v>
+      </c>
+      <c r="Q63" s="38">
+        <v>31.65</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A64" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" s="15">
+        <v>1</v>
+      </c>
+      <c r="D64" s="15">
+        <v>1</v>
+      </c>
+      <c r="E64" s="15">
+        <v>1</v>
+      </c>
+      <c r="F64" s="15">
+        <v>1</v>
+      </c>
+      <c r="G64" s="15">
+        <v>1</v>
+      </c>
+      <c r="H64" s="15">
+        <v>1</v>
+      </c>
+      <c r="I64" s="15">
+        <v>1</v>
+      </c>
+      <c r="J64" s="15">
+        <v>1</v>
+      </c>
+      <c r="K64" s="15">
+        <v>1</v>
+      </c>
+      <c r="L64" s="15">
+        <v>1</v>
+      </c>
+      <c r="M64" s="15">
+        <v>1</v>
+      </c>
+      <c r="N64" s="15">
+        <v>1</v>
+      </c>
+      <c r="O64" s="15">
+        <v>1</v>
+      </c>
+      <c r="P64" s="15">
+        <v>1</v>
+      </c>
+      <c r="Q64" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A65" s="39" t="s">
+        <v>39</v>
+      </c>
+      <c r="B65" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C65" s="8">
+        <v>1</v>
+      </c>
+      <c r="D65" s="8">
+        <v>1</v>
+      </c>
+      <c r="E65" s="8">
+        <v>1</v>
+      </c>
+      <c r="F65" s="8">
+        <v>1</v>
+      </c>
+      <c r="G65" s="8">
+        <v>1</v>
+      </c>
+      <c r="H65" s="8">
+        <v>1</v>
+      </c>
+      <c r="I65" s="8">
+        <v>1</v>
+      </c>
+      <c r="J65" s="8">
+        <v>1</v>
+      </c>
+      <c r="K65" s="8">
+        <v>1</v>
+      </c>
+      <c r="L65" s="8">
+        <v>1</v>
+      </c>
+      <c r="M65" s="8">
+        <v>1</v>
+      </c>
+      <c r="N65" s="8">
+        <v>1</v>
+      </c>
+      <c r="O65" s="8">
+        <v>1</v>
+      </c>
+      <c r="P65" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q65" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A66" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" s="15">
+        <v>5</v>
+      </c>
+      <c r="D66" s="15">
+        <v>5</v>
+      </c>
+      <c r="E66" s="15">
+        <v>5</v>
+      </c>
+      <c r="F66" s="15">
+        <v>6</v>
+      </c>
+      <c r="G66" s="15">
+        <v>6</v>
+      </c>
+      <c r="H66" s="15">
+        <v>6</v>
+      </c>
+      <c r="I66" s="15">
+        <v>6</v>
+      </c>
+      <c r="J66" s="15">
+        <v>6</v>
+      </c>
+      <c r="K66" s="15">
+        <v>6</v>
+      </c>
+      <c r="L66" s="15">
+        <v>6</v>
+      </c>
+      <c r="M66" s="15">
+        <v>6</v>
+      </c>
+      <c r="N66" s="15">
+        <v>6</v>
+      </c>
+      <c r="O66" s="15">
+        <v>6</v>
+      </c>
+      <c r="P66" s="15">
+        <v>6</v>
+      </c>
+      <c r="Q66" s="15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A67" s="39" t="s">
+        <v>40</v>
+      </c>
+      <c r="B67" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C67" s="8">
+        <v>5</v>
+      </c>
+      <c r="D67" s="8">
+        <v>5</v>
+      </c>
+      <c r="E67" s="8">
+        <v>5</v>
+      </c>
+      <c r="F67" s="8">
+        <v>6</v>
+      </c>
+      <c r="G67" s="8">
+        <v>6</v>
+      </c>
+      <c r="H67" s="8">
+        <v>6</v>
+      </c>
+      <c r="I67" s="8">
+        <v>6</v>
+      </c>
+      <c r="J67" s="8">
+        <v>6</v>
+      </c>
+      <c r="K67" s="8">
+        <v>6</v>
+      </c>
+      <c r="L67" s="8">
+        <v>6</v>
+      </c>
+      <c r="M67" s="8">
+        <v>6</v>
+      </c>
+      <c r="N67" s="8">
+        <v>6</v>
+      </c>
+      <c r="O67" s="8">
+        <v>6</v>
+      </c>
+      <c r="P67" s="8">
+        <v>6</v>
+      </c>
+      <c r="Q67" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A68" s="42" t="s">
+        <v>41</v>
+      </c>
+      <c r="B68" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" s="43">
+        <v>4</v>
+      </c>
+      <c r="D68" s="43">
+        <v>4</v>
+      </c>
+      <c r="E68" s="43">
+        <v>4</v>
+      </c>
+      <c r="F68" s="43">
+        <v>5</v>
+      </c>
+      <c r="G68" s="43">
+        <v>5</v>
+      </c>
+      <c r="H68" s="43">
+        <v>5</v>
+      </c>
+      <c r="I68" s="43">
+        <v>5</v>
+      </c>
+      <c r="J68" s="43">
+        <v>5</v>
+      </c>
+      <c r="K68" s="43">
+        <v>5</v>
+      </c>
+      <c r="L68" s="43">
+        <v>5</v>
+      </c>
+      <c r="M68" s="43">
+        <v>5</v>
+      </c>
+      <c r="N68" s="43">
+        <v>5</v>
+      </c>
+      <c r="O68" s="43">
+        <v>5</v>
+      </c>
+      <c r="P68" s="43">
+        <v>5</v>
+      </c>
+      <c r="Q68" s="43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A69" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="B69" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="C69" s="41">
+        <v>4</v>
+      </c>
+      <c r="D69" s="41">
+        <v>4</v>
+      </c>
+      <c r="E69" s="41">
+        <v>4</v>
+      </c>
+      <c r="F69" s="41">
+        <v>5</v>
+      </c>
+      <c r="G69" s="41">
+        <v>5</v>
+      </c>
+      <c r="H69" s="41">
+        <v>5</v>
+      </c>
+      <c r="I69" s="41">
+        <v>5</v>
+      </c>
+      <c r="J69" s="41">
+        <v>5</v>
+      </c>
+      <c r="K69" s="41">
+        <v>5</v>
+      </c>
+      <c r="L69" s="41">
+        <v>5</v>
+      </c>
+      <c r="M69" s="41">
+        <v>5</v>
+      </c>
+      <c r="N69" s="41">
+        <v>5</v>
+      </c>
+      <c r="O69" s="41">
+        <v>5</v>
+      </c>
+      <c r="P69" s="41">
+        <v>5</v>
+      </c>
+      <c r="Q69" s="41">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A70" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="B70" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" s="43">
+        <v>1</v>
+      </c>
+      <c r="D70" s="43">
+        <v>1</v>
+      </c>
+      <c r="E70" s="43">
+        <v>1</v>
+      </c>
+      <c r="F70" s="43">
+        <v>1</v>
+      </c>
+      <c r="G70" s="43">
+        <v>1</v>
+      </c>
+      <c r="H70" s="43">
+        <v>1</v>
+      </c>
+      <c r="I70" s="43">
+        <v>1</v>
+      </c>
+      <c r="J70" s="43">
+        <v>1</v>
+      </c>
+      <c r="K70" s="43">
+        <v>1</v>
+      </c>
+      <c r="L70" s="43">
+        <v>1</v>
+      </c>
+      <c r="M70" s="43">
+        <v>1</v>
+      </c>
+      <c r="N70" s="43">
+        <v>1</v>
+      </c>
+      <c r="O70" s="43">
+        <v>1</v>
+      </c>
+      <c r="P70" s="43">
+        <v>1</v>
+      </c>
+      <c r="Q70" s="43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A71" s="44" t="s">
+        <v>44</v>
+      </c>
+      <c r="B71" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="C71" s="41">
+        <v>1</v>
+      </c>
+      <c r="D71" s="41">
+        <v>1</v>
+      </c>
+      <c r="E71" s="41">
+        <v>1</v>
+      </c>
+      <c r="F71" s="41">
+        <v>1</v>
+      </c>
+      <c r="G71" s="41">
+        <v>1</v>
+      </c>
+      <c r="H71" s="41">
+        <v>1</v>
+      </c>
+      <c r="I71" s="41">
+        <v>1</v>
+      </c>
+      <c r="J71" s="41">
+        <v>1</v>
+      </c>
+      <c r="K71" s="41">
+        <v>1</v>
+      </c>
+      <c r="L71" s="41">
+        <v>1</v>
+      </c>
+      <c r="M71" s="41">
+        <v>1</v>
+      </c>
+      <c r="N71" s="41">
+        <v>1</v>
+      </c>
+      <c r="O71" s="41">
+        <v>1</v>
+      </c>
+      <c r="P71" s="41">
+        <v>1</v>
+      </c>
+      <c r="Q71" s="41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A72" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" s="15">
+        <v>39</v>
+      </c>
+      <c r="D72" s="15">
+        <v>39</v>
+      </c>
+      <c r="E72" s="15">
+        <v>39</v>
+      </c>
+      <c r="F72" s="15">
+        <v>41</v>
+      </c>
+      <c r="G72" s="15">
+        <v>41</v>
+      </c>
+      <c r="H72" s="15">
+        <v>41</v>
+      </c>
+      <c r="I72" s="15">
+        <v>41</v>
+      </c>
+      <c r="J72" s="15">
+        <v>41</v>
+      </c>
+      <c r="K72" s="15">
+        <v>41</v>
+      </c>
+      <c r="L72" s="15">
+        <v>41</v>
+      </c>
+      <c r="M72" s="15">
+        <v>41</v>
+      </c>
+      <c r="N72" s="15">
+        <v>41</v>
+      </c>
+      <c r="O72" s="15">
+        <v>41</v>
+      </c>
+      <c r="P72" s="15">
+        <v>41</v>
+      </c>
+      <c r="Q72" s="15">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A73" s="39" t="s">
+        <v>45</v>
+      </c>
+      <c r="B73" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C73" s="8">
+        <v>34.4</v>
+      </c>
+      <c r="D73" s="8">
+        <v>36.36</v>
+      </c>
+      <c r="E73" s="8">
+        <v>38.47</v>
+      </c>
+      <c r="F73" s="8">
+        <v>38.43</v>
+      </c>
+      <c r="G73" s="8">
+        <v>39.78</v>
+      </c>
+      <c r="H73" s="8">
+        <v>36.909999999999997</v>
+      </c>
+      <c r="I73" s="8">
+        <v>38.11</v>
+      </c>
+      <c r="J73" s="8">
+        <v>37.56</v>
+      </c>
+      <c r="K73" s="8">
+        <v>38.06</v>
+      </c>
+      <c r="L73" s="8">
+        <v>34.69</v>
+      </c>
+      <c r="M73" s="8">
+        <v>34</v>
+      </c>
+      <c r="N73" s="8">
+        <v>34</v>
+      </c>
+      <c r="O73" s="8">
+        <v>24.65</v>
+      </c>
+      <c r="P73" s="8">
+        <v>24.65</v>
+      </c>
+      <c r="Q73" s="8">
+        <v>24.65</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A74" s="42" t="s">
+        <v>46</v>
+      </c>
+      <c r="B74" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" s="43">
+        <v>23</v>
+      </c>
+      <c r="D74" s="43">
+        <v>23</v>
+      </c>
+      <c r="E74" s="43">
+        <v>22</v>
+      </c>
+      <c r="F74" s="43">
+        <v>22</v>
+      </c>
+      <c r="G74" s="43">
+        <v>22</v>
+      </c>
+      <c r="H74" s="43">
+        <v>22</v>
+      </c>
+      <c r="I74" s="43">
+        <v>22</v>
+      </c>
+      <c r="J74" s="43">
+        <v>22</v>
+      </c>
+      <c r="K74" s="43">
+        <v>22</v>
+      </c>
+      <c r="L74" s="43">
+        <v>22</v>
+      </c>
+      <c r="M74" s="43">
+        <v>22</v>
+      </c>
+      <c r="N74" s="43">
+        <v>22</v>
+      </c>
+      <c r="O74" s="43">
+        <v>22</v>
+      </c>
+      <c r="P74" s="43">
+        <v>22</v>
+      </c>
+      <c r="Q74" s="43">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A75" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="B75" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="C75" s="41">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="D75" s="41">
+        <v>21.36</v>
+      </c>
+      <c r="E75" s="41">
+        <v>21.47</v>
+      </c>
+      <c r="F75" s="41">
+        <v>21.43</v>
+      </c>
+      <c r="G75" s="41">
+        <v>21.28</v>
+      </c>
+      <c r="H75" s="41">
+        <v>19.36</v>
+      </c>
+      <c r="I75" s="41">
+        <v>20.51</v>
+      </c>
+      <c r="J75" s="41">
+        <v>19.96</v>
+      </c>
+      <c r="K75" s="41">
+        <v>19.96</v>
+      </c>
+      <c r="L75" s="41">
+        <v>18.79</v>
+      </c>
+      <c r="M75" s="41">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="N75" s="41">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="O75" s="41">
+        <v>13.15</v>
+      </c>
+      <c r="P75" s="41">
+        <v>13.15</v>
+      </c>
+      <c r="Q75" s="41">
+        <v>13.15</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A76" s="42" t="s">
+        <v>48</v>
+      </c>
+      <c r="B76" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" s="43">
+        <v>16</v>
+      </c>
+      <c r="D76" s="43">
+        <v>16</v>
+      </c>
+      <c r="E76" s="43">
+        <v>16</v>
+      </c>
+      <c r="F76" s="43">
+        <v>16</v>
+      </c>
+      <c r="G76" s="43">
+        <v>16</v>
+      </c>
+      <c r="H76" s="43">
+        <v>16</v>
+      </c>
+      <c r="I76" s="43">
+        <v>16</v>
+      </c>
+      <c r="J76" s="43">
+        <v>16</v>
+      </c>
+      <c r="K76" s="43">
+        <v>16</v>
+      </c>
+      <c r="L76" s="43">
+        <v>16</v>
+      </c>
+      <c r="M76" s="43">
+        <v>16</v>
+      </c>
+      <c r="N76" s="43">
+        <v>16</v>
+      </c>
+      <c r="O76" s="43">
+        <v>16</v>
+      </c>
+      <c r="P76" s="43">
+        <v>16</v>
+      </c>
+      <c r="Q76" s="43">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A77" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="B77" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="C77" s="41">
+        <v>15</v>
+      </c>
+      <c r="D77" s="41">
+        <v>15</v>
+      </c>
+      <c r="E77" s="41">
+        <v>17</v>
+      </c>
+      <c r="F77" s="41">
+        <v>16</v>
+      </c>
+      <c r="G77" s="41">
+        <v>16</v>
+      </c>
+      <c r="H77" s="41">
+        <v>14.55</v>
+      </c>
+      <c r="I77" s="41">
+        <v>14.6</v>
+      </c>
+      <c r="J77" s="41">
+        <v>14.6</v>
+      </c>
+      <c r="K77" s="41">
+        <v>15.1</v>
+      </c>
+      <c r="L77" s="41">
+        <v>13.9</v>
+      </c>
+      <c r="M77" s="41">
+        <v>13.9</v>
+      </c>
+      <c r="N77" s="41">
+        <v>13.9</v>
+      </c>
+      <c r="O77" s="41">
+        <v>11.5</v>
+      </c>
+      <c r="P77" s="41">
+        <v>11.5</v>
+      </c>
+      <c r="Q77" s="41">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A78" s="42" t="s">
+        <v>50</v>
+      </c>
+      <c r="B78" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" s="43">
+        <v>0</v>
+      </c>
+      <c r="D78" s="43">
+        <v>0</v>
+      </c>
+      <c r="E78" s="43">
+        <v>1</v>
+      </c>
+      <c r="F78" s="43">
+        <v>3</v>
+      </c>
+      <c r="G78" s="43">
+        <v>3</v>
+      </c>
+      <c r="H78" s="43">
+        <v>3</v>
+      </c>
+      <c r="I78" s="43">
+        <v>3</v>
+      </c>
+      <c r="J78" s="43">
+        <v>3</v>
+      </c>
+      <c r="K78" s="43">
+        <v>3</v>
+      </c>
+      <c r="L78" s="43">
+        <v>3</v>
+      </c>
+      <c r="M78" s="43">
+        <v>3</v>
+      </c>
+      <c r="N78" s="43">
+        <v>3</v>
+      </c>
+      <c r="O78" s="43">
+        <v>3</v>
+      </c>
+      <c r="P78" s="43">
+        <v>3</v>
+      </c>
+      <c r="Q78" s="43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A79" s="44" t="s">
+        <v>51</v>
+      </c>
+      <c r="B79" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="C79" s="41">
+        <v>0</v>
+      </c>
+      <c r="D79" s="41">
+        <v>0</v>
+      </c>
+      <c r="E79" s="41">
+        <v>0</v>
+      </c>
+      <c r="F79" s="41">
+        <v>1</v>
+      </c>
+      <c r="G79" s="41">
+        <v>2.5</v>
+      </c>
+      <c r="H79" s="41">
+        <v>3</v>
+      </c>
+      <c r="I79" s="41">
+        <v>3</v>
+      </c>
+      <c r="J79" s="41">
+        <v>3</v>
+      </c>
+      <c r="K79" s="41">
+        <v>3</v>
+      </c>
+      <c r="L79" s="41">
+        <v>2</v>
+      </c>
+      <c r="M79" s="41">
+        <v>2</v>
+      </c>
+      <c r="N79" s="41">
+        <v>2</v>
+      </c>
+      <c r="O79" s="41">
+        <v>0</v>
+      </c>
+      <c r="P79" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="41">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -8820,7 +12007,7 @@
   <sheetPr>
     <tabColor theme="7" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:P47"/>
+  <dimension ref="A1:P63"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.83203125" bestFit="1" customWidth="1"/>
@@ -10240,6 +13427,402 @@
       <c r="F47">
         <f>IF(PSE!G49&gt;0,PSE!G49,"")</f>
         <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A51" t="str">
+        <f>PSE!A66</f>
+        <v>Platform Engineering</v>
+      </c>
+      <c r="B51" t="str">
+        <f>PSE!C61</f>
+        <v>JAN</v>
+      </c>
+      <c r="C51" t="str">
+        <f>PSE!D61</f>
+        <v>FEB</v>
+      </c>
+      <c r="D51" t="str">
+        <f>PSE!E61</f>
+        <v>MAR</v>
+      </c>
+      <c r="E51" t="str">
+        <f>PSE!F61</f>
+        <v>APR</v>
+      </c>
+      <c r="F51" t="str">
+        <f>PSE!G61</f>
+        <v>MAY</v>
+      </c>
+      <c r="G51" t="str">
+        <f>PSE!H61</f>
+        <v>JUN</v>
+      </c>
+      <c r="H51" t="str">
+        <f>PSE!I61</f>
+        <v>JUL</v>
+      </c>
+      <c r="I51" t="str">
+        <f>PSE!J61</f>
+        <v>AUG</v>
+      </c>
+      <c r="J51" t="str">
+        <f>PSE!K61</f>
+        <v>SEP</v>
+      </c>
+      <c r="K51" t="str">
+        <f>PSE!L61</f>
+        <v>OCT</v>
+      </c>
+      <c r="L51" t="str">
+        <f>PSE!M61</f>
+        <v>NOV</v>
+      </c>
+      <c r="M51" t="str">
+        <f>PSE!N61</f>
+        <v>DEC</v>
+      </c>
+      <c r="N51" t="str">
+        <f>PSE!O61</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O51" t="str">
+        <f>PSE!P61</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P51" t="str">
+        <f>PSE!Q61</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A52" t="str">
+        <f>PSE!B66</f>
+        <v>Staff</v>
+      </c>
+      <c r="B52">
+        <f>PSE!C66</f>
+        <v>5</v>
+      </c>
+      <c r="C52">
+        <f>PSE!D66</f>
+        <v>5</v>
+      </c>
+      <c r="D52">
+        <f>PSE!E66</f>
+        <v>5</v>
+      </c>
+      <c r="E52">
+        <f>PSE!F66</f>
+        <v>6</v>
+      </c>
+      <c r="F52">
+        <f>PSE!G66</f>
+        <v>6</v>
+      </c>
+      <c r="G52">
+        <f>PSE!H66</f>
+        <v>6</v>
+      </c>
+      <c r="H52">
+        <f>PSE!I66</f>
+        <v>6</v>
+      </c>
+      <c r="I52">
+        <f>PSE!J66</f>
+        <v>6</v>
+      </c>
+      <c r="J52">
+        <f>PSE!K66</f>
+        <v>6</v>
+      </c>
+      <c r="K52">
+        <f>PSE!L66</f>
+        <v>6</v>
+      </c>
+      <c r="L52">
+        <f>PSE!M66</f>
+        <v>6</v>
+      </c>
+      <c r="M52">
+        <f>PSE!N66</f>
+        <v>6</v>
+      </c>
+      <c r="N52">
+        <f>PSE!O66</f>
+        <v>6</v>
+      </c>
+      <c r="O52">
+        <f>PSE!P66</f>
+        <v>6</v>
+      </c>
+      <c r="P52">
+        <f>PSE!Q66</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A53" t="str">
+        <f>PSE!B67</f>
+        <v>Plan</v>
+      </c>
+      <c r="B53">
+        <f>PSE!C67</f>
+        <v>5</v>
+      </c>
+      <c r="C53">
+        <f>PSE!D67</f>
+        <v>5</v>
+      </c>
+      <c r="D53">
+        <f>PSE!E67</f>
+        <v>5</v>
+      </c>
+      <c r="E53">
+        <f>PSE!F67</f>
+        <v>6</v>
+      </c>
+      <c r="F53">
+        <f>PSE!G67</f>
+        <v>6</v>
+      </c>
+      <c r="G53">
+        <f>PSE!H67</f>
+        <v>6</v>
+      </c>
+      <c r="H53">
+        <f>PSE!I67</f>
+        <v>6</v>
+      </c>
+      <c r="I53">
+        <f>PSE!J67</f>
+        <v>6</v>
+      </c>
+      <c r="J53">
+        <f>PSE!K67</f>
+        <v>6</v>
+      </c>
+      <c r="K53">
+        <f>PSE!L67</f>
+        <v>6</v>
+      </c>
+      <c r="L53">
+        <f>PSE!M67</f>
+        <v>6</v>
+      </c>
+      <c r="M53">
+        <f>PSE!N67</f>
+        <v>6</v>
+      </c>
+      <c r="N53">
+        <f>PSE!O67</f>
+        <v>6</v>
+      </c>
+      <c r="O53">
+        <f>PSE!P67</f>
+        <v>6</v>
+      </c>
+      <c r="P53">
+        <f>PSE!Q67</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A61" t="str">
+        <f>PSE!A72</f>
+        <v>Software Engineering</v>
+      </c>
+      <c r="B61" t="str">
+        <f>PSE!C61</f>
+        <v>JAN</v>
+      </c>
+      <c r="C61" t="str">
+        <f>PSE!D61</f>
+        <v>FEB</v>
+      </c>
+      <c r="D61" t="str">
+        <f>PSE!E61</f>
+        <v>MAR</v>
+      </c>
+      <c r="E61" t="str">
+        <f>PSE!F61</f>
+        <v>APR</v>
+      </c>
+      <c r="F61" t="str">
+        <f>PSE!G61</f>
+        <v>MAY</v>
+      </c>
+      <c r="G61" t="str">
+        <f>PSE!H61</f>
+        <v>JUN</v>
+      </c>
+      <c r="H61" t="str">
+        <f>PSE!I61</f>
+        <v>JUL</v>
+      </c>
+      <c r="I61" t="str">
+        <f>PSE!J61</f>
+        <v>AUG</v>
+      </c>
+      <c r="J61" t="str">
+        <f>PSE!K61</f>
+        <v>SEP</v>
+      </c>
+      <c r="K61" t="str">
+        <f>PSE!L61</f>
+        <v>OCT</v>
+      </c>
+      <c r="L61" t="str">
+        <f>PSE!M61</f>
+        <v>NOV</v>
+      </c>
+      <c r="M61" t="str">
+        <f>PSE!N61</f>
+        <v>DEC</v>
+      </c>
+      <c r="N61" t="str">
+        <f>PSE!O61</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O61" t="str">
+        <f>PSE!P61</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P61" t="str">
+        <f>PSE!Q61</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A62" t="str">
+        <f>PSE!B72</f>
+        <v>Staff</v>
+      </c>
+      <c r="B62">
+        <f>PSE!C72</f>
+        <v>39</v>
+      </c>
+      <c r="C62">
+        <f>PSE!D72</f>
+        <v>39</v>
+      </c>
+      <c r="D62">
+        <f>PSE!E72</f>
+        <v>39</v>
+      </c>
+      <c r="E62">
+        <f>PSE!F72</f>
+        <v>41</v>
+      </c>
+      <c r="F62">
+        <f>PSE!G72</f>
+        <v>41</v>
+      </c>
+      <c r="G62">
+        <f>PSE!H72</f>
+        <v>41</v>
+      </c>
+      <c r="H62">
+        <f>PSE!I72</f>
+        <v>41</v>
+      </c>
+      <c r="I62">
+        <f>PSE!J72</f>
+        <v>41</v>
+      </c>
+      <c r="J62">
+        <f>PSE!K72</f>
+        <v>41</v>
+      </c>
+      <c r="K62">
+        <f>PSE!L72</f>
+        <v>41</v>
+      </c>
+      <c r="L62">
+        <f>PSE!M72</f>
+        <v>41</v>
+      </c>
+      <c r="M62">
+        <f>PSE!N72</f>
+        <v>41</v>
+      </c>
+      <c r="N62">
+        <f>PSE!O72</f>
+        <v>41</v>
+      </c>
+      <c r="O62">
+        <f>PSE!P72</f>
+        <v>41</v>
+      </c>
+      <c r="P62">
+        <f>PSE!Q72</f>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A63" t="str">
+        <f>PSE!B73</f>
+        <v>Plan</v>
+      </c>
+      <c r="B63">
+        <f>PSE!C73</f>
+        <v>34.4</v>
+      </c>
+      <c r="C63">
+        <f>PSE!D73</f>
+        <v>36.36</v>
+      </c>
+      <c r="D63">
+        <f>PSE!E73</f>
+        <v>38.47</v>
+      </c>
+      <c r="E63">
+        <f>PSE!F73</f>
+        <v>38.43</v>
+      </c>
+      <c r="F63">
+        <f>PSE!G73</f>
+        <v>39.78</v>
+      </c>
+      <c r="G63">
+        <f>PSE!H73</f>
+        <v>36.909999999999997</v>
+      </c>
+      <c r="H63">
+        <f>PSE!I73</f>
+        <v>38.11</v>
+      </c>
+      <c r="I63">
+        <f>PSE!J73</f>
+        <v>37.56</v>
+      </c>
+      <c r="J63">
+        <f>PSE!K73</f>
+        <v>38.06</v>
+      </c>
+      <c r="K63">
+        <f>PSE!L73</f>
+        <v>34.69</v>
+      </c>
+      <c r="L63">
+        <f>PSE!M73</f>
+        <v>34</v>
+      </c>
+      <c r="M63">
+        <f>PSE!N73</f>
+        <v>34</v>
+      </c>
+      <c r="N63">
+        <f>PSE!O73</f>
+        <v>24.65</v>
+      </c>
+      <c r="O63">
+        <f>PSE!P73</f>
+        <v>24.65</v>
+      </c>
+      <c r="P63">
+        <f>PSE!Q73</f>
+        <v>24.65</v>
       </c>
     </row>
   </sheetData>
@@ -10252,7 +13835,7 @@
   <sheetPr>
     <tabColor theme="8"/>
   </sheetPr>
-  <dimension ref="A1:Q49"/>
+  <dimension ref="A1:Q93"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.2">
@@ -11482,7 +15065,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A49" s="16" t="s">
         <v>18</v>
       </c>
@@ -11503,6 +15086,1749 @@
       </c>
       <c r="G49" s="14">
         <v>9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A61" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="B61" s="34"/>
+      <c r="C61" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="D61" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="E61" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I61" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J61" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="K61" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="L61" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="M61" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="N61" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O61" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="P61" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q61" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A62" s="12"/>
+      <c r="B62" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" s="12">
+        <v>43</v>
+      </c>
+      <c r="D62" s="12">
+        <v>45</v>
+      </c>
+      <c r="E62" s="12">
+        <v>46</v>
+      </c>
+      <c r="F62" s="12">
+        <v>46</v>
+      </c>
+      <c r="G62" s="12">
+        <v>46</v>
+      </c>
+      <c r="H62" s="12">
+        <v>46</v>
+      </c>
+      <c r="I62" s="12">
+        <v>46</v>
+      </c>
+      <c r="J62" s="12">
+        <v>46</v>
+      </c>
+      <c r="K62" s="12">
+        <v>46</v>
+      </c>
+      <c r="L62" s="12">
+        <v>46</v>
+      </c>
+      <c r="M62" s="12">
+        <v>46</v>
+      </c>
+      <c r="N62" s="12">
+        <v>46</v>
+      </c>
+      <c r="O62" s="12">
+        <v>46</v>
+      </c>
+      <c r="P62" s="12">
+        <v>46</v>
+      </c>
+      <c r="Q62" s="12">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A63" s="36"/>
+      <c r="B63" s="47" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" s="48">
+        <v>34.077500000000001</v>
+      </c>
+      <c r="D63" s="48">
+        <v>38.524999999999999</v>
+      </c>
+      <c r="E63" s="48">
+        <v>40.520000000000003</v>
+      </c>
+      <c r="F63" s="48">
+        <v>36.765000000000001</v>
+      </c>
+      <c r="G63" s="48">
+        <v>39.619999999999997</v>
+      </c>
+      <c r="H63" s="48">
+        <v>39.774999999999999</v>
+      </c>
+      <c r="I63" s="48">
+        <v>40.583750000000002</v>
+      </c>
+      <c r="J63" s="48">
+        <v>38.893250000000002</v>
+      </c>
+      <c r="K63" s="48">
+        <v>38.455750000000002</v>
+      </c>
+      <c r="L63" s="48">
+        <v>35.549500000000002</v>
+      </c>
+      <c r="M63" s="48">
+        <v>34.582500000000003</v>
+      </c>
+      <c r="N63" s="48">
+        <v>33.2575</v>
+      </c>
+      <c r="O63" s="48">
+        <v>24.421250000000001</v>
+      </c>
+      <c r="P63" s="48">
+        <v>24.12125</v>
+      </c>
+      <c r="Q63" s="48">
+        <v>24.12125</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A64" s="49" t="s">
+        <v>52</v>
+      </c>
+      <c r="B64" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" s="49">
+        <v>1</v>
+      </c>
+      <c r="D64" s="49">
+        <v>1</v>
+      </c>
+      <c r="E64" s="49">
+        <v>1</v>
+      </c>
+      <c r="F64" s="49">
+        <v>1</v>
+      </c>
+      <c r="G64" s="49">
+        <v>1</v>
+      </c>
+      <c r="H64" s="49">
+        <v>1</v>
+      </c>
+      <c r="I64" s="49">
+        <v>1</v>
+      </c>
+      <c r="J64" s="49">
+        <v>1</v>
+      </c>
+      <c r="K64" s="49">
+        <v>1</v>
+      </c>
+      <c r="L64" s="49">
+        <v>1</v>
+      </c>
+      <c r="M64" s="49">
+        <v>1</v>
+      </c>
+      <c r="N64" s="49">
+        <v>1</v>
+      </c>
+      <c r="O64" s="49">
+        <v>1</v>
+      </c>
+      <c r="P64" s="49">
+        <v>1</v>
+      </c>
+      <c r="Q64" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A65" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="B65" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C65" s="8">
+        <v>1</v>
+      </c>
+      <c r="D65" s="8">
+        <v>1</v>
+      </c>
+      <c r="E65" s="8">
+        <v>1</v>
+      </c>
+      <c r="F65" s="8">
+        <v>1</v>
+      </c>
+      <c r="G65" s="8">
+        <v>1</v>
+      </c>
+      <c r="H65" s="8">
+        <v>1</v>
+      </c>
+      <c r="I65" s="8">
+        <v>1</v>
+      </c>
+      <c r="J65" s="8">
+        <v>1</v>
+      </c>
+      <c r="K65" s="8">
+        <v>1</v>
+      </c>
+      <c r="L65" s="8">
+        <v>1</v>
+      </c>
+      <c r="M65" s="8">
+        <v>1</v>
+      </c>
+      <c r="N65" s="8">
+        <v>1</v>
+      </c>
+      <c r="O65" s="8">
+        <v>1</v>
+      </c>
+      <c r="P65" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q65" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A66" s="49" t="s">
+        <v>53</v>
+      </c>
+      <c r="B66" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" s="49">
+        <v>4</v>
+      </c>
+      <c r="D66" s="49">
+        <v>4</v>
+      </c>
+      <c r="E66" s="49">
+        <v>4</v>
+      </c>
+      <c r="F66" s="49">
+        <v>4</v>
+      </c>
+      <c r="G66" s="49">
+        <v>4</v>
+      </c>
+      <c r="H66" s="49">
+        <v>4</v>
+      </c>
+      <c r="I66" s="49">
+        <v>4</v>
+      </c>
+      <c r="J66" s="49">
+        <v>4</v>
+      </c>
+      <c r="K66" s="49">
+        <v>4</v>
+      </c>
+      <c r="L66" s="49">
+        <v>4</v>
+      </c>
+      <c r="M66" s="49">
+        <v>4</v>
+      </c>
+      <c r="N66" s="49">
+        <v>4</v>
+      </c>
+      <c r="O66" s="49">
+        <v>4</v>
+      </c>
+      <c r="P66" s="49">
+        <v>4</v>
+      </c>
+      <c r="Q66" s="49">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A67" s="39" t="s">
+        <v>53</v>
+      </c>
+      <c r="B67" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C67" s="8">
+        <v>3.0625</v>
+      </c>
+      <c r="D67" s="8">
+        <v>3.85</v>
+      </c>
+      <c r="E67" s="8">
+        <v>3.65</v>
+      </c>
+      <c r="F67" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="G67" s="8">
+        <v>4.0250000000000004</v>
+      </c>
+      <c r="H67" s="8">
+        <v>4.0250000000000004</v>
+      </c>
+      <c r="I67" s="8">
+        <v>3.9812500000000002</v>
+      </c>
+      <c r="J67" s="8">
+        <v>3.2937500000000002</v>
+      </c>
+      <c r="K67" s="8">
+        <v>2.9312499999999999</v>
+      </c>
+      <c r="L67" s="8">
+        <v>2.7124999999999999</v>
+      </c>
+      <c r="M67" s="8">
+        <v>2.5874999999999999</v>
+      </c>
+      <c r="N67" s="8">
+        <v>2.3875000000000002</v>
+      </c>
+      <c r="O67" s="8">
+        <v>1.28125</v>
+      </c>
+      <c r="P67" s="8">
+        <v>1.03125</v>
+      </c>
+      <c r="Q67" s="8">
+        <v>1.03125</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A68" s="49" t="s">
+        <v>54</v>
+      </c>
+      <c r="B68" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" s="49">
+        <v>7</v>
+      </c>
+      <c r="D68" s="49">
+        <v>7</v>
+      </c>
+      <c r="E68" s="49">
+        <v>7</v>
+      </c>
+      <c r="F68" s="49">
+        <v>7</v>
+      </c>
+      <c r="G68" s="49">
+        <v>7</v>
+      </c>
+      <c r="H68" s="49">
+        <v>7</v>
+      </c>
+      <c r="I68" s="49">
+        <v>7</v>
+      </c>
+      <c r="J68" s="49">
+        <v>7</v>
+      </c>
+      <c r="K68" s="49">
+        <v>7</v>
+      </c>
+      <c r="L68" s="49">
+        <v>7</v>
+      </c>
+      <c r="M68" s="49">
+        <v>7</v>
+      </c>
+      <c r="N68" s="49">
+        <v>7</v>
+      </c>
+      <c r="O68" s="49">
+        <v>7</v>
+      </c>
+      <c r="P68" s="49">
+        <v>7</v>
+      </c>
+      <c r="Q68" s="49">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A69" s="39" t="s">
+        <v>54</v>
+      </c>
+      <c r="B69" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C69" s="8">
+        <v>7.0750000000000002</v>
+      </c>
+      <c r="D69" s="8">
+        <v>7.2249999999999996</v>
+      </c>
+      <c r="E69" s="8">
+        <v>6.8650000000000002</v>
+      </c>
+      <c r="F69" s="8">
+        <v>6.12</v>
+      </c>
+      <c r="G69" s="8">
+        <v>5.7074999999999996</v>
+      </c>
+      <c r="H69" s="8">
+        <v>6.4124999999999996</v>
+      </c>
+      <c r="I69" s="8">
+        <v>5.8624999999999998</v>
+      </c>
+      <c r="J69" s="8">
+        <v>5.6325000000000003</v>
+      </c>
+      <c r="K69" s="8">
+        <v>5.6325000000000003</v>
+      </c>
+      <c r="L69" s="8">
+        <v>5.2949999999999999</v>
+      </c>
+      <c r="M69" s="8">
+        <v>5.1449999999999996</v>
+      </c>
+      <c r="N69" s="8">
+        <v>5.1449999999999996</v>
+      </c>
+      <c r="O69" s="8">
+        <v>4.3150000000000004</v>
+      </c>
+      <c r="P69" s="8">
+        <v>4.3150000000000004</v>
+      </c>
+      <c r="Q69" s="8">
+        <v>4.3150000000000004</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A70" s="42" t="s">
+        <v>55</v>
+      </c>
+      <c r="B70" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" s="43">
+        <v>6</v>
+      </c>
+      <c r="D70" s="43">
+        <v>6</v>
+      </c>
+      <c r="E70" s="43">
+        <v>6</v>
+      </c>
+      <c r="F70" s="43">
+        <v>6</v>
+      </c>
+      <c r="G70" s="43">
+        <v>6</v>
+      </c>
+      <c r="H70" s="43">
+        <v>6</v>
+      </c>
+      <c r="I70" s="43">
+        <v>6</v>
+      </c>
+      <c r="J70" s="43">
+        <v>6</v>
+      </c>
+      <c r="K70" s="43">
+        <v>6</v>
+      </c>
+      <c r="L70" s="43">
+        <v>6</v>
+      </c>
+      <c r="M70" s="43">
+        <v>6</v>
+      </c>
+      <c r="N70" s="43">
+        <v>6</v>
+      </c>
+      <c r="O70" s="43">
+        <v>6</v>
+      </c>
+      <c r="P70" s="43">
+        <v>6</v>
+      </c>
+      <c r="Q70" s="43">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A71" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="B71" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="C71" s="41">
+        <v>6.0750000000000002</v>
+      </c>
+      <c r="D71" s="41">
+        <v>6.2249999999999996</v>
+      </c>
+      <c r="E71" s="41">
+        <v>5.8650000000000002</v>
+      </c>
+      <c r="F71" s="41">
+        <v>5.12</v>
+      </c>
+      <c r="G71" s="41">
+        <v>4.7074999999999996</v>
+      </c>
+      <c r="H71" s="41">
+        <v>5.4124999999999996</v>
+      </c>
+      <c r="I71" s="41">
+        <v>4.8624999999999998</v>
+      </c>
+      <c r="J71" s="41">
+        <v>4.6325000000000003</v>
+      </c>
+      <c r="K71" s="41">
+        <v>4.6325000000000003</v>
+      </c>
+      <c r="L71" s="41">
+        <v>4.2949999999999999</v>
+      </c>
+      <c r="M71" s="41">
+        <v>4.1449999999999996</v>
+      </c>
+      <c r="N71" s="41">
+        <v>4.1449999999999996</v>
+      </c>
+      <c r="O71" s="41">
+        <v>3.3149999999999999</v>
+      </c>
+      <c r="P71" s="41">
+        <v>3.3149999999999999</v>
+      </c>
+      <c r="Q71" s="41">
+        <v>3.3149999999999999</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A72" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="B72" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" s="43">
+        <v>1</v>
+      </c>
+      <c r="D72" s="43">
+        <v>1</v>
+      </c>
+      <c r="E72" s="43">
+        <v>1</v>
+      </c>
+      <c r="F72" s="43">
+        <v>1</v>
+      </c>
+      <c r="G72" s="43">
+        <v>1</v>
+      </c>
+      <c r="H72" s="43">
+        <v>1</v>
+      </c>
+      <c r="I72" s="43">
+        <v>1</v>
+      </c>
+      <c r="J72" s="43">
+        <v>1</v>
+      </c>
+      <c r="K72" s="43">
+        <v>1</v>
+      </c>
+      <c r="L72" s="43">
+        <v>1</v>
+      </c>
+      <c r="M72" s="43">
+        <v>1</v>
+      </c>
+      <c r="N72" s="43">
+        <v>1</v>
+      </c>
+      <c r="O72" s="43">
+        <v>1</v>
+      </c>
+      <c r="P72" s="43">
+        <v>1</v>
+      </c>
+      <c r="Q72" s="43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A73" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="B73" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="C73" s="41">
+        <v>1</v>
+      </c>
+      <c r="D73" s="41">
+        <v>1</v>
+      </c>
+      <c r="E73" s="41">
+        <v>1</v>
+      </c>
+      <c r="F73" s="41">
+        <v>1</v>
+      </c>
+      <c r="G73" s="41">
+        <v>1</v>
+      </c>
+      <c r="H73" s="41">
+        <v>1</v>
+      </c>
+      <c r="I73" s="41">
+        <v>1</v>
+      </c>
+      <c r="J73" s="41">
+        <v>1</v>
+      </c>
+      <c r="K73" s="41">
+        <v>1</v>
+      </c>
+      <c r="L73" s="41">
+        <v>1</v>
+      </c>
+      <c r="M73" s="41">
+        <v>1</v>
+      </c>
+      <c r="N73" s="41">
+        <v>1</v>
+      </c>
+      <c r="O73" s="41">
+        <v>1</v>
+      </c>
+      <c r="P73" s="41">
+        <v>1</v>
+      </c>
+      <c r="Q73" s="41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A74" s="49" t="s">
+        <v>59</v>
+      </c>
+      <c r="B74" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" s="49">
+        <v>4</v>
+      </c>
+      <c r="D74" s="49">
+        <v>4</v>
+      </c>
+      <c r="E74" s="49">
+        <v>4</v>
+      </c>
+      <c r="F74" s="49">
+        <v>4</v>
+      </c>
+      <c r="G74" s="49">
+        <v>4</v>
+      </c>
+      <c r="H74" s="49">
+        <v>4</v>
+      </c>
+      <c r="I74" s="49">
+        <v>4</v>
+      </c>
+      <c r="J74" s="49">
+        <v>4</v>
+      </c>
+      <c r="K74" s="49">
+        <v>4</v>
+      </c>
+      <c r="L74" s="49">
+        <v>4</v>
+      </c>
+      <c r="M74" s="49">
+        <v>4</v>
+      </c>
+      <c r="N74" s="49">
+        <v>4</v>
+      </c>
+      <c r="O74" s="49">
+        <v>4</v>
+      </c>
+      <c r="P74" s="49">
+        <v>4</v>
+      </c>
+      <c r="Q74" s="49">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A75" s="39" t="s">
+        <v>59</v>
+      </c>
+      <c r="B75" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C75" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="D75" s="8">
+        <v>4.375</v>
+      </c>
+      <c r="E75" s="8">
+        <v>4.3250000000000002</v>
+      </c>
+      <c r="F75" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="G75" s="8">
+        <v>3.5150000000000001</v>
+      </c>
+      <c r="H75" s="8">
+        <v>3.4649999999999999</v>
+      </c>
+      <c r="I75" s="8">
+        <v>3.3650000000000002</v>
+      </c>
+      <c r="J75" s="8">
+        <v>3.44</v>
+      </c>
+      <c r="K75" s="8">
+        <v>3.12</v>
+      </c>
+      <c r="L75" s="8">
+        <v>3.12</v>
+      </c>
+      <c r="M75" s="8">
+        <v>3.12</v>
+      </c>
+      <c r="N75" s="8">
+        <v>3.0449999999999999</v>
+      </c>
+      <c r="O75" s="8">
+        <v>2.78</v>
+      </c>
+      <c r="P75" s="8">
+        <v>2.78</v>
+      </c>
+      <c r="Q75" s="8">
+        <v>2.78</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A76" s="49" t="s">
+        <v>60</v>
+      </c>
+      <c r="B76" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" s="49">
+        <v>2</v>
+      </c>
+      <c r="D76" s="49">
+        <v>2</v>
+      </c>
+      <c r="E76" s="49">
+        <v>2</v>
+      </c>
+      <c r="F76" s="49">
+        <v>2</v>
+      </c>
+      <c r="G76" s="49">
+        <v>2</v>
+      </c>
+      <c r="H76" s="49">
+        <v>2</v>
+      </c>
+      <c r="I76" s="49">
+        <v>2</v>
+      </c>
+      <c r="J76" s="49">
+        <v>2</v>
+      </c>
+      <c r="K76" s="49">
+        <v>2</v>
+      </c>
+      <c r="L76" s="49">
+        <v>2</v>
+      </c>
+      <c r="M76" s="49">
+        <v>2</v>
+      </c>
+      <c r="N76" s="49">
+        <v>2</v>
+      </c>
+      <c r="O76" s="49">
+        <v>2</v>
+      </c>
+      <c r="P76" s="49">
+        <v>2</v>
+      </c>
+      <c r="Q76" s="49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A77" s="39" t="s">
+        <v>60</v>
+      </c>
+      <c r="B77" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C77" s="8">
+        <v>3.3849999999999998</v>
+      </c>
+      <c r="D77" s="8">
+        <v>3.0750000000000002</v>
+      </c>
+      <c r="E77" s="8">
+        <v>4.22</v>
+      </c>
+      <c r="F77" s="8">
+        <v>2.6549999999999998</v>
+      </c>
+      <c r="G77" s="8">
+        <v>2.6850000000000001</v>
+      </c>
+      <c r="H77" s="8">
+        <v>2.4649999999999999</v>
+      </c>
+      <c r="I77" s="8">
+        <v>2.3149999999999999</v>
+      </c>
+      <c r="J77" s="8">
+        <v>2.2650000000000001</v>
+      </c>
+      <c r="K77" s="8">
+        <v>2.1150000000000002</v>
+      </c>
+      <c r="L77" s="8">
+        <v>2.2650000000000001</v>
+      </c>
+      <c r="M77" s="8">
+        <v>2.0649999999999999</v>
+      </c>
+      <c r="N77" s="8">
+        <v>2.0649999999999999</v>
+      </c>
+      <c r="O77" s="8">
+        <v>1.5049999999999999</v>
+      </c>
+      <c r="P77" s="8">
+        <v>1.4550000000000001</v>
+      </c>
+      <c r="Q77" s="8">
+        <v>1.4550000000000001</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A78" s="49" t="s">
+        <v>61</v>
+      </c>
+      <c r="B78" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" s="49">
+        <v>3</v>
+      </c>
+      <c r="D78" s="49">
+        <v>3</v>
+      </c>
+      <c r="E78" s="49">
+        <v>3</v>
+      </c>
+      <c r="F78" s="49">
+        <v>3</v>
+      </c>
+      <c r="G78" s="49">
+        <v>3</v>
+      </c>
+      <c r="H78" s="49">
+        <v>3</v>
+      </c>
+      <c r="I78" s="49">
+        <v>3</v>
+      </c>
+      <c r="J78" s="49">
+        <v>3</v>
+      </c>
+      <c r="K78" s="49">
+        <v>3</v>
+      </c>
+      <c r="L78" s="49">
+        <v>3</v>
+      </c>
+      <c r="M78" s="49">
+        <v>3</v>
+      </c>
+      <c r="N78" s="49">
+        <v>3</v>
+      </c>
+      <c r="O78" s="49">
+        <v>3</v>
+      </c>
+      <c r="P78" s="49">
+        <v>3</v>
+      </c>
+      <c r="Q78" s="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A79" s="39" t="s">
+        <v>61</v>
+      </c>
+      <c r="B79" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C79" s="8">
+        <v>3.2749999999999999</v>
+      </c>
+      <c r="D79" s="8">
+        <v>3.2749999999999999</v>
+      </c>
+      <c r="E79" s="8">
+        <v>3.2250000000000001</v>
+      </c>
+      <c r="F79" s="8">
+        <v>2.875</v>
+      </c>
+      <c r="G79" s="8">
+        <v>3.1124999999999998</v>
+      </c>
+      <c r="H79" s="8">
+        <v>2.8624999999999998</v>
+      </c>
+      <c r="I79" s="8">
+        <v>2.6</v>
+      </c>
+      <c r="J79" s="8">
+        <v>2.6</v>
+      </c>
+      <c r="K79" s="8">
+        <v>2.6</v>
+      </c>
+      <c r="L79" s="8">
+        <v>2.6</v>
+      </c>
+      <c r="M79" s="8">
+        <v>2.6</v>
+      </c>
+      <c r="N79" s="8">
+        <v>2.6</v>
+      </c>
+      <c r="O79" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="P79" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="Q79" s="8">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A80" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="B80" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" s="49">
+        <v>4</v>
+      </c>
+      <c r="D80" s="49">
+        <v>4</v>
+      </c>
+      <c r="E80" s="49">
+        <v>4</v>
+      </c>
+      <c r="F80" s="49">
+        <v>4</v>
+      </c>
+      <c r="G80" s="49">
+        <v>4</v>
+      </c>
+      <c r="H80" s="49">
+        <v>4</v>
+      </c>
+      <c r="I80" s="49">
+        <v>4</v>
+      </c>
+      <c r="J80" s="49">
+        <v>4</v>
+      </c>
+      <c r="K80" s="49">
+        <v>4</v>
+      </c>
+      <c r="L80" s="49">
+        <v>4</v>
+      </c>
+      <c r="M80" s="49">
+        <v>4</v>
+      </c>
+      <c r="N80" s="49">
+        <v>4</v>
+      </c>
+      <c r="O80" s="49">
+        <v>4</v>
+      </c>
+      <c r="P80" s="49">
+        <v>4</v>
+      </c>
+      <c r="Q80" s="49">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A81" s="39" t="s">
+        <v>62</v>
+      </c>
+      <c r="B81" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C81" s="8">
+        <v>3.65</v>
+      </c>
+      <c r="D81" s="8">
+        <v>3.75</v>
+      </c>
+      <c r="E81" s="8">
+        <v>4</v>
+      </c>
+      <c r="F81" s="8">
+        <v>3.85</v>
+      </c>
+      <c r="G81" s="8">
+        <v>4.16</v>
+      </c>
+      <c r="H81" s="8">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="I81" s="8">
+        <v>4.2750000000000004</v>
+      </c>
+      <c r="J81" s="8">
+        <v>4.1520000000000001</v>
+      </c>
+      <c r="K81" s="8">
+        <v>3.927</v>
+      </c>
+      <c r="L81" s="8">
+        <v>3.7269999999999999</v>
+      </c>
+      <c r="M81" s="8">
+        <v>3.4849999999999999</v>
+      </c>
+      <c r="N81" s="8">
+        <v>2.71</v>
+      </c>
+      <c r="O81" s="8">
+        <v>1</v>
+      </c>
+      <c r="P81" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q81" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A82" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="B82" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" s="49">
+        <v>5</v>
+      </c>
+      <c r="D82" s="49">
+        <v>5</v>
+      </c>
+      <c r="E82" s="49">
+        <v>5</v>
+      </c>
+      <c r="F82" s="49">
+        <v>5</v>
+      </c>
+      <c r="G82" s="49">
+        <v>5</v>
+      </c>
+      <c r="H82" s="49">
+        <v>5</v>
+      </c>
+      <c r="I82" s="49">
+        <v>5</v>
+      </c>
+      <c r="J82" s="49">
+        <v>5</v>
+      </c>
+      <c r="K82" s="49">
+        <v>5</v>
+      </c>
+      <c r="L82" s="49">
+        <v>5</v>
+      </c>
+      <c r="M82" s="49">
+        <v>5</v>
+      </c>
+      <c r="N82" s="49">
+        <v>5</v>
+      </c>
+      <c r="O82" s="49">
+        <v>5</v>
+      </c>
+      <c r="P82" s="49">
+        <v>5</v>
+      </c>
+      <c r="Q82" s="49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A83" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="B83" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C83" s="8">
+        <v>4.7</v>
+      </c>
+      <c r="D83" s="8">
+        <v>5.05</v>
+      </c>
+      <c r="E83" s="8">
+        <v>5.05</v>
+      </c>
+      <c r="F83" s="8">
+        <v>5.28</v>
+      </c>
+      <c r="G83" s="8">
+        <v>5.99</v>
+      </c>
+      <c r="H83" s="8">
+        <v>5.49</v>
+      </c>
+      <c r="I83" s="8">
+        <v>5.15</v>
+      </c>
+      <c r="J83" s="8">
+        <v>4.7</v>
+      </c>
+      <c r="K83" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="L83" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="M83" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="N83" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="O83" s="8">
+        <v>3.22</v>
+      </c>
+      <c r="P83" s="8">
+        <v>3.22</v>
+      </c>
+      <c r="Q83" s="8">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A84" s="49" t="s">
+        <v>64</v>
+      </c>
+      <c r="B84" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84" s="49">
+        <v>9</v>
+      </c>
+      <c r="D84" s="49">
+        <v>11</v>
+      </c>
+      <c r="E84" s="49">
+        <v>12</v>
+      </c>
+      <c r="F84" s="49">
+        <v>12</v>
+      </c>
+      <c r="G84" s="49">
+        <v>12</v>
+      </c>
+      <c r="H84" s="49">
+        <v>12</v>
+      </c>
+      <c r="I84" s="49">
+        <v>12</v>
+      </c>
+      <c r="J84" s="49">
+        <v>12</v>
+      </c>
+      <c r="K84" s="49">
+        <v>12</v>
+      </c>
+      <c r="L84" s="49">
+        <v>12</v>
+      </c>
+      <c r="M84" s="49">
+        <v>12</v>
+      </c>
+      <c r="N84" s="49">
+        <v>12</v>
+      </c>
+      <c r="O84" s="49">
+        <v>12</v>
+      </c>
+      <c r="P84" s="49">
+        <v>12</v>
+      </c>
+      <c r="Q84" s="49">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A85" s="39" t="s">
+        <v>64</v>
+      </c>
+      <c r="B85" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C85" s="8">
+        <v>7.93</v>
+      </c>
+      <c r="D85" s="8">
+        <v>11.3</v>
+      </c>
+      <c r="E85" s="8">
+        <v>12.51</v>
+      </c>
+      <c r="F85" s="8">
+        <v>11.685</v>
+      </c>
+      <c r="G85" s="8">
+        <v>12.94</v>
+      </c>
+      <c r="H85" s="8">
+        <v>13.46</v>
+      </c>
+      <c r="I85" s="8">
+        <v>15.4</v>
+      </c>
+      <c r="J85" s="8">
+        <v>15.25</v>
+      </c>
+      <c r="K85" s="8">
+        <v>15.75</v>
+      </c>
+      <c r="L85" s="8">
+        <v>13.45</v>
+      </c>
+      <c r="M85" s="8">
+        <v>13.2</v>
+      </c>
+      <c r="N85" s="8">
+        <v>12.85</v>
+      </c>
+      <c r="O85" s="8">
+        <v>9.6</v>
+      </c>
+      <c r="P85" s="8">
+        <v>9.6</v>
+      </c>
+      <c r="Q85" s="8">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A86" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="B86" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" s="43">
+        <v>2</v>
+      </c>
+      <c r="D86" s="43">
+        <v>2</v>
+      </c>
+      <c r="E86" s="43">
+        <v>2</v>
+      </c>
+      <c r="F86" s="43">
+        <v>2</v>
+      </c>
+      <c r="G86" s="43">
+        <v>2</v>
+      </c>
+      <c r="H86" s="43">
+        <v>2</v>
+      </c>
+      <c r="I86" s="43">
+        <v>2</v>
+      </c>
+      <c r="J86" s="43">
+        <v>2</v>
+      </c>
+      <c r="K86" s="43">
+        <v>2</v>
+      </c>
+      <c r="L86" s="43">
+        <v>2</v>
+      </c>
+      <c r="M86" s="43">
+        <v>2</v>
+      </c>
+      <c r="N86" s="43">
+        <v>2</v>
+      </c>
+      <c r="O86" s="43">
+        <v>2</v>
+      </c>
+      <c r="P86" s="43">
+        <v>2</v>
+      </c>
+      <c r="Q86" s="43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A87" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="B87" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="C87" s="41">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D87" s="41">
+        <v>1.9</v>
+      </c>
+      <c r="E87" s="41">
+        <v>1.96</v>
+      </c>
+      <c r="F87" s="41">
+        <v>1.885</v>
+      </c>
+      <c r="G87" s="41">
+        <v>1.99</v>
+      </c>
+      <c r="H87" s="41">
+        <v>1.96</v>
+      </c>
+      <c r="I87" s="41">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="J87" s="41">
+        <v>1.9</v>
+      </c>
+      <c r="K87" s="41">
+        <v>2.15</v>
+      </c>
+      <c r="L87" s="41">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="M87" s="41">
+        <v>1.8</v>
+      </c>
+      <c r="N87" s="41">
+        <v>1.6</v>
+      </c>
+      <c r="O87" s="41">
+        <v>1.6</v>
+      </c>
+      <c r="P87" s="41">
+        <v>1.6</v>
+      </c>
+      <c r="Q87" s="41">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A88" s="42" t="s">
+        <v>67</v>
+      </c>
+      <c r="B88" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C88" s="43">
+        <v>1</v>
+      </c>
+      <c r="D88" s="43">
+        <v>1</v>
+      </c>
+      <c r="E88" s="43">
+        <v>1</v>
+      </c>
+      <c r="F88" s="43">
+        <v>1</v>
+      </c>
+      <c r="G88" s="43">
+        <v>1</v>
+      </c>
+      <c r="H88" s="43">
+        <v>1</v>
+      </c>
+      <c r="I88" s="43">
+        <v>1</v>
+      </c>
+      <c r="J88" s="43">
+        <v>1</v>
+      </c>
+      <c r="K88" s="43">
+        <v>1</v>
+      </c>
+      <c r="L88" s="43">
+        <v>1</v>
+      </c>
+      <c r="M88" s="43">
+        <v>1</v>
+      </c>
+      <c r="N88" s="43">
+        <v>1</v>
+      </c>
+      <c r="O88" s="43">
+        <v>1</v>
+      </c>
+      <c r="P88" s="43">
+        <v>1</v>
+      </c>
+      <c r="Q88" s="43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A89" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="B89" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="C89" s="41">
+        <v>1</v>
+      </c>
+      <c r="D89" s="41">
+        <v>1</v>
+      </c>
+      <c r="E89" s="41">
+        <v>1</v>
+      </c>
+      <c r="F89" s="41">
+        <v>1</v>
+      </c>
+      <c r="G89" s="41">
+        <v>1</v>
+      </c>
+      <c r="H89" s="41">
+        <v>1</v>
+      </c>
+      <c r="I89" s="41">
+        <v>1</v>
+      </c>
+      <c r="J89" s="41">
+        <v>1</v>
+      </c>
+      <c r="K89" s="41">
+        <v>1</v>
+      </c>
+      <c r="L89" s="41">
+        <v>1</v>
+      </c>
+      <c r="M89" s="41">
+        <v>1</v>
+      </c>
+      <c r="N89" s="41">
+        <v>1</v>
+      </c>
+      <c r="O89" s="41">
+        <v>1</v>
+      </c>
+      <c r="P89" s="41">
+        <v>1</v>
+      </c>
+      <c r="Q89" s="41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A90" s="42" t="s">
+        <v>69</v>
+      </c>
+      <c r="B90" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C90" s="43">
+        <v>6</v>
+      </c>
+      <c r="D90" s="43">
+        <v>8</v>
+      </c>
+      <c r="E90" s="43">
+        <v>9</v>
+      </c>
+      <c r="F90" s="43">
+        <v>9</v>
+      </c>
+      <c r="G90" s="43">
+        <v>9</v>
+      </c>
+      <c r="H90" s="43">
+        <v>9</v>
+      </c>
+      <c r="I90" s="43">
+        <v>9</v>
+      </c>
+      <c r="J90" s="43">
+        <v>9</v>
+      </c>
+      <c r="K90" s="43">
+        <v>9</v>
+      </c>
+      <c r="L90" s="43">
+        <v>9</v>
+      </c>
+      <c r="M90" s="43">
+        <v>9</v>
+      </c>
+      <c r="N90" s="43">
+        <v>9</v>
+      </c>
+      <c r="O90" s="43">
+        <v>9</v>
+      </c>
+      <c r="P90" s="43">
+        <v>9</v>
+      </c>
+      <c r="Q90" s="43">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A91" s="44" t="s">
+        <v>70</v>
+      </c>
+      <c r="B91" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="C91" s="41">
+        <v>5.83</v>
+      </c>
+      <c r="D91" s="41">
+        <v>8.4</v>
+      </c>
+      <c r="E91" s="41">
+        <v>9.5500000000000007</v>
+      </c>
+      <c r="F91" s="41">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="G91" s="41">
+        <v>9.9499999999999993</v>
+      </c>
+      <c r="H91" s="41">
+        <v>10.5</v>
+      </c>
+      <c r="I91" s="41">
+        <v>12.35</v>
+      </c>
+      <c r="J91" s="41">
+        <v>12.35</v>
+      </c>
+      <c r="K91" s="41">
+        <v>12.6</v>
+      </c>
+      <c r="L91" s="41">
+        <v>10.4</v>
+      </c>
+      <c r="M91" s="41">
+        <v>10.4</v>
+      </c>
+      <c r="N91" s="41">
+        <v>10.25</v>
+      </c>
+      <c r="O91" s="41">
+        <v>7</v>
+      </c>
+      <c r="P91" s="41">
+        <v>7</v>
+      </c>
+      <c r="Q91" s="41">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A92" s="49" t="s">
+        <v>71</v>
+      </c>
+      <c r="B92" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" s="49">
+        <v>4</v>
+      </c>
+      <c r="D92" s="49">
+        <v>4</v>
+      </c>
+      <c r="E92" s="49">
+        <v>4</v>
+      </c>
+      <c r="F92" s="49">
+        <v>4</v>
+      </c>
+      <c r="G92" s="49">
+        <v>4</v>
+      </c>
+      <c r="H92" s="49">
+        <v>4</v>
+      </c>
+      <c r="I92" s="49">
+        <v>4</v>
+      </c>
+      <c r="J92" s="49">
+        <v>4</v>
+      </c>
+      <c r="K92" s="49">
+        <v>4</v>
+      </c>
+      <c r="L92" s="49">
+        <v>4</v>
+      </c>
+      <c r="M92" s="49">
+        <v>4</v>
+      </c>
+      <c r="N92" s="49">
+        <v>4</v>
+      </c>
+      <c r="O92" s="49">
+        <v>4</v>
+      </c>
+      <c r="P92" s="49">
+        <v>4</v>
+      </c>
+      <c r="Q92" s="49">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A93" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="B93" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C93" s="8">
+        <v>3.08</v>
+      </c>
+      <c r="D93" s="8">
+        <v>2.94</v>
+      </c>
+      <c r="E93" s="8">
+        <v>2.99</v>
+      </c>
+      <c r="F93" s="8">
+        <v>3.07</v>
+      </c>
+      <c r="G93" s="8">
+        <v>3.07</v>
+      </c>
+      <c r="H93" s="8">
+        <v>3.23</v>
+      </c>
+      <c r="I93" s="8">
+        <v>3.83</v>
+      </c>
+      <c r="J93" s="8">
+        <v>3.83</v>
+      </c>
+      <c r="K93" s="8">
+        <v>3.83</v>
+      </c>
+      <c r="L93" s="8">
+        <v>3.83</v>
+      </c>
+      <c r="M93" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="N93" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="O93" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="P93" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="Q93" s="8">
+        <v>5.2</v>
       </c>
     </row>
   </sheetData>
@@ -11515,7 +16841,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:P47"/>
+  <dimension ref="A1:P133"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.83203125" bestFit="1" customWidth="1"/>
@@ -12935,6 +18261,1788 @@
       <c r="F47">
         <f>IF(SD!G49&gt;0,SD!G49,"")</f>
         <v>9</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A51" t="str">
+        <f>SD!A66</f>
+        <v>Design</v>
+      </c>
+      <c r="B51" t="str">
+        <f>SD!C$61</f>
+        <v>JAN</v>
+      </c>
+      <c r="C51" t="str">
+        <f>SD!D$61</f>
+        <v>FEB</v>
+      </c>
+      <c r="D51" t="str">
+        <f>SD!E$61</f>
+        <v>MAR</v>
+      </c>
+      <c r="E51" t="str">
+        <f>SD!F$61</f>
+        <v>APR</v>
+      </c>
+      <c r="F51" t="str">
+        <f>SD!G$61</f>
+        <v>MAY</v>
+      </c>
+      <c r="G51" t="str">
+        <f>SD!H$61</f>
+        <v>JUN</v>
+      </c>
+      <c r="H51" t="str">
+        <f>SD!I$61</f>
+        <v>JUL</v>
+      </c>
+      <c r="I51" t="str">
+        <f>SD!J$61</f>
+        <v>AUG</v>
+      </c>
+      <c r="J51" t="str">
+        <f>SD!K$61</f>
+        <v>SEP</v>
+      </c>
+      <c r="K51" t="str">
+        <f>SD!L$61</f>
+        <v>OCT</v>
+      </c>
+      <c r="L51" t="str">
+        <f>SD!M$61</f>
+        <v>NOV</v>
+      </c>
+      <c r="M51" t="str">
+        <f>SD!N$61</f>
+        <v>DEC</v>
+      </c>
+      <c r="N51" t="str">
+        <f>SD!O$61</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O51" t="str">
+        <f>SD!P$61</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P51" t="str">
+        <f>SD!Q$61</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A52" t="str">
+        <f>SD!B66</f>
+        <v>Staff</v>
+      </c>
+      <c r="B52">
+        <f>SD!C66</f>
+        <v>4</v>
+      </c>
+      <c r="C52">
+        <f>SD!D66</f>
+        <v>4</v>
+      </c>
+      <c r="D52">
+        <f>SD!E66</f>
+        <v>4</v>
+      </c>
+      <c r="E52">
+        <f>SD!F66</f>
+        <v>4</v>
+      </c>
+      <c r="F52">
+        <f>SD!G66</f>
+        <v>4</v>
+      </c>
+      <c r="G52">
+        <f>SD!H66</f>
+        <v>4</v>
+      </c>
+      <c r="H52">
+        <f>SD!I66</f>
+        <v>4</v>
+      </c>
+      <c r="I52">
+        <f>SD!J66</f>
+        <v>4</v>
+      </c>
+      <c r="J52">
+        <f>SD!K66</f>
+        <v>4</v>
+      </c>
+      <c r="K52">
+        <f>SD!L66</f>
+        <v>4</v>
+      </c>
+      <c r="L52">
+        <f>SD!M66</f>
+        <v>4</v>
+      </c>
+      <c r="M52">
+        <f>SD!N66</f>
+        <v>4</v>
+      </c>
+      <c r="N52">
+        <f>SD!O66</f>
+        <v>4</v>
+      </c>
+      <c r="O52">
+        <f>SD!P66</f>
+        <v>4</v>
+      </c>
+      <c r="P52">
+        <f>SD!Q66</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A53" t="str">
+        <f>SD!B67</f>
+        <v>Plan</v>
+      </c>
+      <c r="B53">
+        <f>SD!C67</f>
+        <v>3.0625</v>
+      </c>
+      <c r="C53">
+        <f>SD!D67</f>
+        <v>3.85</v>
+      </c>
+      <c r="D53">
+        <f>SD!E67</f>
+        <v>3.65</v>
+      </c>
+      <c r="E53">
+        <f>SD!F67</f>
+        <v>3.3</v>
+      </c>
+      <c r="F53">
+        <f>SD!G67</f>
+        <v>4.0250000000000004</v>
+      </c>
+      <c r="G53">
+        <f>SD!H67</f>
+        <v>4.0250000000000004</v>
+      </c>
+      <c r="H53">
+        <f>SD!I67</f>
+        <v>3.9812500000000002</v>
+      </c>
+      <c r="I53">
+        <f>SD!J67</f>
+        <v>3.2937500000000002</v>
+      </c>
+      <c r="J53">
+        <f>SD!K67</f>
+        <v>2.9312499999999999</v>
+      </c>
+      <c r="K53">
+        <f>SD!L67</f>
+        <v>2.7124999999999999</v>
+      </c>
+      <c r="L53">
+        <f>SD!M67</f>
+        <v>2.5874999999999999</v>
+      </c>
+      <c r="M53">
+        <f>SD!N67</f>
+        <v>2.3875000000000002</v>
+      </c>
+      <c r="N53">
+        <f>SD!O67</f>
+        <v>1.28125</v>
+      </c>
+      <c r="O53">
+        <f>SD!P67</f>
+        <v>1.03125</v>
+      </c>
+      <c r="P53">
+        <f>SD!Q67</f>
+        <v>1.03125</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A61" t="str">
+        <f>SD!A68</f>
+        <v>Data Technology</v>
+      </c>
+      <c r="B61" t="str">
+        <f>SD!C$61</f>
+        <v>JAN</v>
+      </c>
+      <c r="C61" t="str">
+        <f>SD!D$61</f>
+        <v>FEB</v>
+      </c>
+      <c r="D61" t="str">
+        <f>SD!E$61</f>
+        <v>MAR</v>
+      </c>
+      <c r="E61" t="str">
+        <f>SD!F$61</f>
+        <v>APR</v>
+      </c>
+      <c r="F61" t="str">
+        <f>SD!G$61</f>
+        <v>MAY</v>
+      </c>
+      <c r="G61" t="str">
+        <f>SD!H$61</f>
+        <v>JUN</v>
+      </c>
+      <c r="H61" t="str">
+        <f>SD!I$61</f>
+        <v>JUL</v>
+      </c>
+      <c r="I61" t="str">
+        <f>SD!J$61</f>
+        <v>AUG</v>
+      </c>
+      <c r="J61" t="str">
+        <f>SD!K$61</f>
+        <v>SEP</v>
+      </c>
+      <c r="K61" t="str">
+        <f>SD!L$61</f>
+        <v>OCT</v>
+      </c>
+      <c r="L61" t="str">
+        <f>SD!M$61</f>
+        <v>NOV</v>
+      </c>
+      <c r="M61" t="str">
+        <f>SD!N$61</f>
+        <v>DEC</v>
+      </c>
+      <c r="N61" t="str">
+        <f>SD!O$61</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O61" t="str">
+        <f>SD!P$61</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P61" t="str">
+        <f>SD!Q$61</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A62" t="str">
+        <f>SD!B68</f>
+        <v>Staff</v>
+      </c>
+      <c r="B62">
+        <f>SD!C68</f>
+        <v>7</v>
+      </c>
+      <c r="C62">
+        <f>SD!D68</f>
+        <v>7</v>
+      </c>
+      <c r="D62">
+        <f>SD!E68</f>
+        <v>7</v>
+      </c>
+      <c r="E62">
+        <f>SD!F68</f>
+        <v>7</v>
+      </c>
+      <c r="F62">
+        <f>SD!G68</f>
+        <v>7</v>
+      </c>
+      <c r="G62">
+        <f>SD!H68</f>
+        <v>7</v>
+      </c>
+      <c r="H62">
+        <f>SD!I68</f>
+        <v>7</v>
+      </c>
+      <c r="I62">
+        <f>SD!J68</f>
+        <v>7</v>
+      </c>
+      <c r="J62">
+        <f>SD!K68</f>
+        <v>7</v>
+      </c>
+      <c r="K62">
+        <f>SD!L68</f>
+        <v>7</v>
+      </c>
+      <c r="L62">
+        <f>SD!M68</f>
+        <v>7</v>
+      </c>
+      <c r="M62">
+        <f>SD!N68</f>
+        <v>7</v>
+      </c>
+      <c r="N62">
+        <f>SD!O68</f>
+        <v>7</v>
+      </c>
+      <c r="O62">
+        <f>SD!P68</f>
+        <v>7</v>
+      </c>
+      <c r="P62">
+        <f>SD!Q68</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A63" t="str">
+        <f>SD!B69</f>
+        <v>Plan</v>
+      </c>
+      <c r="B63">
+        <f>SD!C69</f>
+        <v>7.0750000000000002</v>
+      </c>
+      <c r="C63">
+        <f>SD!D69</f>
+        <v>7.2249999999999996</v>
+      </c>
+      <c r="D63">
+        <f>SD!E69</f>
+        <v>6.8650000000000002</v>
+      </c>
+      <c r="E63">
+        <f>SD!F69</f>
+        <v>6.12</v>
+      </c>
+      <c r="F63">
+        <f>SD!G69</f>
+        <v>5.7074999999999996</v>
+      </c>
+      <c r="G63">
+        <f>SD!H69</f>
+        <v>6.4124999999999996</v>
+      </c>
+      <c r="H63">
+        <f>SD!I69</f>
+        <v>5.8624999999999998</v>
+      </c>
+      <c r="I63">
+        <f>SD!J69</f>
+        <v>5.6325000000000003</v>
+      </c>
+      <c r="J63">
+        <f>SD!K69</f>
+        <v>5.6325000000000003</v>
+      </c>
+      <c r="K63">
+        <f>SD!L69</f>
+        <v>5.2949999999999999</v>
+      </c>
+      <c r="L63">
+        <f>SD!M69</f>
+        <v>5.1449999999999996</v>
+      </c>
+      <c r="M63">
+        <f>SD!N69</f>
+        <v>5.1449999999999996</v>
+      </c>
+      <c r="N63">
+        <f>SD!O69</f>
+        <v>4.3150000000000004</v>
+      </c>
+      <c r="O63">
+        <f>SD!P69</f>
+        <v>4.3150000000000004</v>
+      </c>
+      <c r="P63">
+        <f>SD!Q69</f>
+        <v>4.3150000000000004</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A71" t="str">
+        <f>SD!A74</f>
+        <v>Solution Architecture</v>
+      </c>
+      <c r="B71" t="str">
+        <f>SD!C$61</f>
+        <v>JAN</v>
+      </c>
+      <c r="C71" t="str">
+        <f>SD!D$61</f>
+        <v>FEB</v>
+      </c>
+      <c r="D71" t="str">
+        <f>SD!E$61</f>
+        <v>MAR</v>
+      </c>
+      <c r="E71" t="str">
+        <f>SD!F$61</f>
+        <v>APR</v>
+      </c>
+      <c r="F71" t="str">
+        <f>SD!G$61</f>
+        <v>MAY</v>
+      </c>
+      <c r="G71" t="str">
+        <f>SD!H$61</f>
+        <v>JUN</v>
+      </c>
+      <c r="H71" t="str">
+        <f>SD!I$61</f>
+        <v>JUL</v>
+      </c>
+      <c r="I71" t="str">
+        <f>SD!J$61</f>
+        <v>AUG</v>
+      </c>
+      <c r="J71" t="str">
+        <f>SD!K$61</f>
+        <v>SEP</v>
+      </c>
+      <c r="K71" t="str">
+        <f>SD!L$61</f>
+        <v>OCT</v>
+      </c>
+      <c r="L71" t="str">
+        <f>SD!M$61</f>
+        <v>NOV</v>
+      </c>
+      <c r="M71" t="str">
+        <f>SD!N$61</f>
+        <v>DEC</v>
+      </c>
+      <c r="N71" t="str">
+        <f>SD!O$61</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O71" t="str">
+        <f>SD!P$61</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P71" t="str">
+        <f>SD!Q$61</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A72" t="str">
+        <f>SD!B74</f>
+        <v>Staff</v>
+      </c>
+      <c r="B72">
+        <f>SD!C74</f>
+        <v>4</v>
+      </c>
+      <c r="C72">
+        <f>SD!D74</f>
+        <v>4</v>
+      </c>
+      <c r="D72">
+        <f>SD!E74</f>
+        <v>4</v>
+      </c>
+      <c r="E72">
+        <f>SD!F74</f>
+        <v>4</v>
+      </c>
+      <c r="F72">
+        <f>SD!G74</f>
+        <v>4</v>
+      </c>
+      <c r="G72">
+        <f>SD!H74</f>
+        <v>4</v>
+      </c>
+      <c r="H72">
+        <f>SD!I74</f>
+        <v>4</v>
+      </c>
+      <c r="I72">
+        <f>SD!J74</f>
+        <v>4</v>
+      </c>
+      <c r="J72">
+        <f>SD!K74</f>
+        <v>4</v>
+      </c>
+      <c r="K72">
+        <f>SD!L74</f>
+        <v>4</v>
+      </c>
+      <c r="L72">
+        <f>SD!M74</f>
+        <v>4</v>
+      </c>
+      <c r="M72">
+        <f>SD!N74</f>
+        <v>4</v>
+      </c>
+      <c r="N72">
+        <f>SD!O74</f>
+        <v>4</v>
+      </c>
+      <c r="O72">
+        <f>SD!P74</f>
+        <v>4</v>
+      </c>
+      <c r="P72">
+        <f>SD!Q74</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A73" t="str">
+        <f>SD!B75</f>
+        <v>Plan</v>
+      </c>
+      <c r="B73">
+        <f>SD!C75</f>
+        <v>3.3</v>
+      </c>
+      <c r="C73">
+        <f>SD!D75</f>
+        <v>4.375</v>
+      </c>
+      <c r="D73">
+        <f>SD!E75</f>
+        <v>4.3250000000000002</v>
+      </c>
+      <c r="E73">
+        <f>SD!F75</f>
+        <v>3.9</v>
+      </c>
+      <c r="F73">
+        <f>SD!G75</f>
+        <v>3.5150000000000001</v>
+      </c>
+      <c r="G73">
+        <f>SD!H75</f>
+        <v>3.4649999999999999</v>
+      </c>
+      <c r="H73">
+        <f>SD!I75</f>
+        <v>3.3650000000000002</v>
+      </c>
+      <c r="I73">
+        <f>SD!J75</f>
+        <v>3.44</v>
+      </c>
+      <c r="J73">
+        <f>SD!K75</f>
+        <v>3.12</v>
+      </c>
+      <c r="K73">
+        <f>SD!L75</f>
+        <v>3.12</v>
+      </c>
+      <c r="L73">
+        <f>SD!M75</f>
+        <v>3.12</v>
+      </c>
+      <c r="M73">
+        <f>SD!N75</f>
+        <v>3.0449999999999999</v>
+      </c>
+      <c r="N73">
+        <f>SD!O75</f>
+        <v>2.78</v>
+      </c>
+      <c r="O73">
+        <f>SD!P75</f>
+        <v>2.78</v>
+      </c>
+      <c r="P73">
+        <f>SD!Q75</f>
+        <v>2.78</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A81" t="str">
+        <f>SD!A76</f>
+        <v>Site Reliability Engineering</v>
+      </c>
+      <c r="B81" t="str">
+        <f>SD!C$61</f>
+        <v>JAN</v>
+      </c>
+      <c r="C81" t="str">
+        <f>SD!D$61</f>
+        <v>FEB</v>
+      </c>
+      <c r="D81" t="str">
+        <f>SD!E$61</f>
+        <v>MAR</v>
+      </c>
+      <c r="E81" t="str">
+        <f>SD!F$61</f>
+        <v>APR</v>
+      </c>
+      <c r="F81" t="str">
+        <f>SD!G$61</f>
+        <v>MAY</v>
+      </c>
+      <c r="G81" t="str">
+        <f>SD!H$61</f>
+        <v>JUN</v>
+      </c>
+      <c r="H81" t="str">
+        <f>SD!I$61</f>
+        <v>JUL</v>
+      </c>
+      <c r="I81" t="str">
+        <f>SD!J$61</f>
+        <v>AUG</v>
+      </c>
+      <c r="J81" t="str">
+        <f>SD!K$61</f>
+        <v>SEP</v>
+      </c>
+      <c r="K81" t="str">
+        <f>SD!L$61</f>
+        <v>OCT</v>
+      </c>
+      <c r="L81" t="str">
+        <f>SD!M$61</f>
+        <v>NOV</v>
+      </c>
+      <c r="M81" t="str">
+        <f>SD!N$61</f>
+        <v>DEC</v>
+      </c>
+      <c r="N81" t="str">
+        <f>SD!O$61</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O81" t="str">
+        <f>SD!P$61</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P81" t="str">
+        <f>SD!Q$61</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A82" t="str">
+        <f>SD!B76</f>
+        <v>Staff</v>
+      </c>
+      <c r="B82">
+        <f>SD!C76</f>
+        <v>2</v>
+      </c>
+      <c r="C82">
+        <f>SD!D76</f>
+        <v>2</v>
+      </c>
+      <c r="D82">
+        <f>SD!E76</f>
+        <v>2</v>
+      </c>
+      <c r="E82">
+        <f>SD!F76</f>
+        <v>2</v>
+      </c>
+      <c r="F82">
+        <f>SD!G76</f>
+        <v>2</v>
+      </c>
+      <c r="G82">
+        <f>SD!H76</f>
+        <v>2</v>
+      </c>
+      <c r="H82">
+        <f>SD!I76</f>
+        <v>2</v>
+      </c>
+      <c r="I82">
+        <f>SD!J76</f>
+        <v>2</v>
+      </c>
+      <c r="J82">
+        <f>SD!K76</f>
+        <v>2</v>
+      </c>
+      <c r="K82">
+        <f>SD!L76</f>
+        <v>2</v>
+      </c>
+      <c r="L82">
+        <f>SD!M76</f>
+        <v>2</v>
+      </c>
+      <c r="M82">
+        <f>SD!N76</f>
+        <v>2</v>
+      </c>
+      <c r="N82">
+        <f>SD!O76</f>
+        <v>2</v>
+      </c>
+      <c r="O82">
+        <f>SD!P76</f>
+        <v>2</v>
+      </c>
+      <c r="P82">
+        <f>SD!Q76</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A83" t="str">
+        <f>SD!B77</f>
+        <v>Plan</v>
+      </c>
+      <c r="B83">
+        <f>SD!C77</f>
+        <v>3.3849999999999998</v>
+      </c>
+      <c r="C83">
+        <f>SD!D77</f>
+        <v>3.0750000000000002</v>
+      </c>
+      <c r="D83">
+        <f>SD!E77</f>
+        <v>4.22</v>
+      </c>
+      <c r="E83">
+        <f>SD!F77</f>
+        <v>2.6549999999999998</v>
+      </c>
+      <c r="F83">
+        <f>SD!G77</f>
+        <v>2.6850000000000001</v>
+      </c>
+      <c r="G83">
+        <f>SD!H77</f>
+        <v>2.4649999999999999</v>
+      </c>
+      <c r="H83">
+        <f>SD!I77</f>
+        <v>2.3149999999999999</v>
+      </c>
+      <c r="I83">
+        <f>SD!J77</f>
+        <v>2.2650000000000001</v>
+      </c>
+      <c r="J83">
+        <f>SD!K77</f>
+        <v>2.1150000000000002</v>
+      </c>
+      <c r="K83">
+        <f>SD!L77</f>
+        <v>2.2650000000000001</v>
+      </c>
+      <c r="L83">
+        <f>SD!M77</f>
+        <v>2.0649999999999999</v>
+      </c>
+      <c r="M83">
+        <f>SD!N77</f>
+        <v>2.0649999999999999</v>
+      </c>
+      <c r="N83">
+        <f>SD!O77</f>
+        <v>1.5049999999999999</v>
+      </c>
+      <c r="O83">
+        <f>SD!P77</f>
+        <v>1.4550000000000001</v>
+      </c>
+      <c r="P83">
+        <f>SD!Q77</f>
+        <v>1.4550000000000001</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A91" t="str">
+        <f>SD!A78</f>
+        <v>Cyber Security</v>
+      </c>
+      <c r="B91" t="str">
+        <f>SD!C$61</f>
+        <v>JAN</v>
+      </c>
+      <c r="C91" t="str">
+        <f>SD!D$61</f>
+        <v>FEB</v>
+      </c>
+      <c r="D91" t="str">
+        <f>SD!E$61</f>
+        <v>MAR</v>
+      </c>
+      <c r="E91" t="str">
+        <f>SD!F$61</f>
+        <v>APR</v>
+      </c>
+      <c r="F91" t="str">
+        <f>SD!G$61</f>
+        <v>MAY</v>
+      </c>
+      <c r="G91" t="str">
+        <f>SD!H$61</f>
+        <v>JUN</v>
+      </c>
+      <c r="H91" t="str">
+        <f>SD!I$61</f>
+        <v>JUL</v>
+      </c>
+      <c r="I91" t="str">
+        <f>SD!J$61</f>
+        <v>AUG</v>
+      </c>
+      <c r="J91" t="str">
+        <f>SD!K$61</f>
+        <v>SEP</v>
+      </c>
+      <c r="K91" t="str">
+        <f>SD!L$61</f>
+        <v>OCT</v>
+      </c>
+      <c r="L91" t="str">
+        <f>SD!M$61</f>
+        <v>NOV</v>
+      </c>
+      <c r="M91" t="str">
+        <f>SD!N$61</f>
+        <v>DEC</v>
+      </c>
+      <c r="N91" t="str">
+        <f>SD!O$61</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O91" t="str">
+        <f>SD!P$61</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P91" t="str">
+        <f>SD!Q$61</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A92" t="str">
+        <f>SD!B78</f>
+        <v>Staff</v>
+      </c>
+      <c r="B92">
+        <f>SD!C78</f>
+        <v>3</v>
+      </c>
+      <c r="C92">
+        <f>SD!D78</f>
+        <v>3</v>
+      </c>
+      <c r="D92">
+        <f>SD!E78</f>
+        <v>3</v>
+      </c>
+      <c r="E92">
+        <f>SD!F78</f>
+        <v>3</v>
+      </c>
+      <c r="F92">
+        <f>SD!G78</f>
+        <v>3</v>
+      </c>
+      <c r="G92">
+        <f>SD!H78</f>
+        <v>3</v>
+      </c>
+      <c r="H92">
+        <f>SD!I78</f>
+        <v>3</v>
+      </c>
+      <c r="I92">
+        <f>SD!J78</f>
+        <v>3</v>
+      </c>
+      <c r="J92">
+        <f>SD!K78</f>
+        <v>3</v>
+      </c>
+      <c r="K92">
+        <f>SD!L78</f>
+        <v>3</v>
+      </c>
+      <c r="L92">
+        <f>SD!M78</f>
+        <v>3</v>
+      </c>
+      <c r="M92">
+        <f>SD!N78</f>
+        <v>3</v>
+      </c>
+      <c r="N92">
+        <f>SD!O78</f>
+        <v>3</v>
+      </c>
+      <c r="O92">
+        <f>SD!P78</f>
+        <v>3</v>
+      </c>
+      <c r="P92">
+        <f>SD!Q78</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A93" t="str">
+        <f>SD!B79</f>
+        <v>Plan</v>
+      </c>
+      <c r="B93">
+        <f>SD!C79</f>
+        <v>3.2749999999999999</v>
+      </c>
+      <c r="C93">
+        <f>SD!D79</f>
+        <v>3.2749999999999999</v>
+      </c>
+      <c r="D93">
+        <f>SD!E79</f>
+        <v>3.2250000000000001</v>
+      </c>
+      <c r="E93">
+        <f>SD!F79</f>
+        <v>2.875</v>
+      </c>
+      <c r="F93">
+        <f>SD!G79</f>
+        <v>3.1124999999999998</v>
+      </c>
+      <c r="G93">
+        <f>SD!H79</f>
+        <v>2.8624999999999998</v>
+      </c>
+      <c r="H93">
+        <f>SD!I79</f>
+        <v>2.6</v>
+      </c>
+      <c r="I93">
+        <f>SD!J79</f>
+        <v>2.6</v>
+      </c>
+      <c r="J93">
+        <f>SD!K79</f>
+        <v>2.6</v>
+      </c>
+      <c r="K93">
+        <f>SD!L79</f>
+        <v>2.6</v>
+      </c>
+      <c r="L93">
+        <f>SD!M79</f>
+        <v>2.6</v>
+      </c>
+      <c r="M93">
+        <f>SD!N79</f>
+        <v>2.6</v>
+      </c>
+      <c r="N93">
+        <f>SD!O79</f>
+        <v>2.5</v>
+      </c>
+      <c r="O93">
+        <f>SD!P79</f>
+        <v>2.5</v>
+      </c>
+      <c r="P93">
+        <f>SD!Q79</f>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A101" t="str">
+        <f>SD!A80</f>
+        <v>Project Management</v>
+      </c>
+      <c r="B101" t="str">
+        <f>SD!C$61</f>
+        <v>JAN</v>
+      </c>
+      <c r="C101" t="str">
+        <f>SD!D$61</f>
+        <v>FEB</v>
+      </c>
+      <c r="D101" t="str">
+        <f>SD!E$61</f>
+        <v>MAR</v>
+      </c>
+      <c r="E101" t="str">
+        <f>SD!F$61</f>
+        <v>APR</v>
+      </c>
+      <c r="F101" t="str">
+        <f>SD!G$61</f>
+        <v>MAY</v>
+      </c>
+      <c r="G101" t="str">
+        <f>SD!H$61</f>
+        <v>JUN</v>
+      </c>
+      <c r="H101" t="str">
+        <f>SD!I$61</f>
+        <v>JUL</v>
+      </c>
+      <c r="I101" t="str">
+        <f>SD!J$61</f>
+        <v>AUG</v>
+      </c>
+      <c r="J101" t="str">
+        <f>SD!K$61</f>
+        <v>SEP</v>
+      </c>
+      <c r="K101" t="str">
+        <f>SD!L$61</f>
+        <v>OCT</v>
+      </c>
+      <c r="L101" t="str">
+        <f>SD!M$61</f>
+        <v>NOV</v>
+      </c>
+      <c r="M101" t="str">
+        <f>SD!N$61</f>
+        <v>DEC</v>
+      </c>
+      <c r="N101" t="str">
+        <f>SD!O$61</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O101" t="str">
+        <f>SD!P$61</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P101" t="str">
+        <f>SD!Q$61</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A102" t="str">
+        <f>SD!B80</f>
+        <v>Staff</v>
+      </c>
+      <c r="B102">
+        <f>SD!C80</f>
+        <v>4</v>
+      </c>
+      <c r="C102">
+        <f>SD!D80</f>
+        <v>4</v>
+      </c>
+      <c r="D102">
+        <f>SD!E80</f>
+        <v>4</v>
+      </c>
+      <c r="E102">
+        <f>SD!F80</f>
+        <v>4</v>
+      </c>
+      <c r="F102">
+        <f>SD!G80</f>
+        <v>4</v>
+      </c>
+      <c r="G102">
+        <f>SD!H80</f>
+        <v>4</v>
+      </c>
+      <c r="H102">
+        <f>SD!I80</f>
+        <v>4</v>
+      </c>
+      <c r="I102">
+        <f>SD!J80</f>
+        <v>4</v>
+      </c>
+      <c r="J102">
+        <f>SD!K80</f>
+        <v>4</v>
+      </c>
+      <c r="K102">
+        <f>SD!L80</f>
+        <v>4</v>
+      </c>
+      <c r="L102">
+        <f>SD!M80</f>
+        <v>4</v>
+      </c>
+      <c r="M102">
+        <f>SD!N80</f>
+        <v>4</v>
+      </c>
+      <c r="N102">
+        <f>SD!O80</f>
+        <v>4</v>
+      </c>
+      <c r="O102">
+        <f>SD!P80</f>
+        <v>4</v>
+      </c>
+      <c r="P102">
+        <f>SD!Q80</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A103" t="str">
+        <f>SD!B81</f>
+        <v>Plan</v>
+      </c>
+      <c r="B103">
+        <f>SD!C81</f>
+        <v>3.65</v>
+      </c>
+      <c r="C103">
+        <f>SD!D81</f>
+        <v>3.75</v>
+      </c>
+      <c r="D103">
+        <f>SD!E81</f>
+        <v>4</v>
+      </c>
+      <c r="E103">
+        <f>SD!F81</f>
+        <v>3.85</v>
+      </c>
+      <c r="F103">
+        <f>SD!G81</f>
+        <v>4.16</v>
+      </c>
+      <c r="G103">
+        <f>SD!H81</f>
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="H103">
+        <f>SD!I81</f>
+        <v>4.2750000000000004</v>
+      </c>
+      <c r="I103">
+        <f>SD!J81</f>
+        <v>4.1520000000000001</v>
+      </c>
+      <c r="J103">
+        <f>SD!K81</f>
+        <v>3.927</v>
+      </c>
+      <c r="K103">
+        <f>SD!L81</f>
+        <v>3.7269999999999999</v>
+      </c>
+      <c r="L103">
+        <f>SD!M81</f>
+        <v>3.4849999999999999</v>
+      </c>
+      <c r="M103">
+        <f>SD!N81</f>
+        <v>2.71</v>
+      </c>
+      <c r="N103">
+        <f>SD!O81</f>
+        <v>1</v>
+      </c>
+      <c r="O103">
+        <f>SD!P81</f>
+        <v>1</v>
+      </c>
+      <c r="P103">
+        <f>SD!Q81</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A111" t="str">
+        <f>SD!A82</f>
+        <v>Technology Analyst</v>
+      </c>
+      <c r="B111" t="str">
+        <f>SD!C$61</f>
+        <v>JAN</v>
+      </c>
+      <c r="C111" t="str">
+        <f>SD!D$61</f>
+        <v>FEB</v>
+      </c>
+      <c r="D111" t="str">
+        <f>SD!E$61</f>
+        <v>MAR</v>
+      </c>
+      <c r="E111" t="str">
+        <f>SD!F$61</f>
+        <v>APR</v>
+      </c>
+      <c r="F111" t="str">
+        <f>SD!G$61</f>
+        <v>MAY</v>
+      </c>
+      <c r="G111" t="str">
+        <f>SD!H$61</f>
+        <v>JUN</v>
+      </c>
+      <c r="H111" t="str">
+        <f>SD!I$61</f>
+        <v>JUL</v>
+      </c>
+      <c r="I111" t="str">
+        <f>SD!J$61</f>
+        <v>AUG</v>
+      </c>
+      <c r="J111" t="str">
+        <f>SD!K$61</f>
+        <v>SEP</v>
+      </c>
+      <c r="K111" t="str">
+        <f>SD!L$61</f>
+        <v>OCT</v>
+      </c>
+      <c r="L111" t="str">
+        <f>SD!M$61</f>
+        <v>NOV</v>
+      </c>
+      <c r="M111" t="str">
+        <f>SD!N$61</f>
+        <v>DEC</v>
+      </c>
+      <c r="N111" t="str">
+        <f>SD!O$61</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O111" t="str">
+        <f>SD!P$61</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P111" t="str">
+        <f>SD!Q$61</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A112" t="str">
+        <f>SD!B82</f>
+        <v>Staff</v>
+      </c>
+      <c r="B112">
+        <f>SD!C82</f>
+        <v>5</v>
+      </c>
+      <c r="C112">
+        <f>SD!D82</f>
+        <v>5</v>
+      </c>
+      <c r="D112">
+        <f>SD!E82</f>
+        <v>5</v>
+      </c>
+      <c r="E112">
+        <f>SD!F82</f>
+        <v>5</v>
+      </c>
+      <c r="F112">
+        <f>SD!G82</f>
+        <v>5</v>
+      </c>
+      <c r="G112">
+        <f>SD!H82</f>
+        <v>5</v>
+      </c>
+      <c r="H112">
+        <f>SD!I82</f>
+        <v>5</v>
+      </c>
+      <c r="I112">
+        <f>SD!J82</f>
+        <v>5</v>
+      </c>
+      <c r="J112">
+        <f>SD!K82</f>
+        <v>5</v>
+      </c>
+      <c r="K112">
+        <f>SD!L82</f>
+        <v>5</v>
+      </c>
+      <c r="L112">
+        <f>SD!M82</f>
+        <v>5</v>
+      </c>
+      <c r="M112">
+        <f>SD!N82</f>
+        <v>5</v>
+      </c>
+      <c r="N112">
+        <f>SD!O82</f>
+        <v>5</v>
+      </c>
+      <c r="O112">
+        <f>SD!P82</f>
+        <v>5</v>
+      </c>
+      <c r="P112">
+        <f>SD!Q82</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A113" t="str">
+        <f>SD!B83</f>
+        <v>Plan</v>
+      </c>
+      <c r="B113">
+        <f>SD!C83</f>
+        <v>4.7</v>
+      </c>
+      <c r="C113">
+        <f>SD!D83</f>
+        <v>5.05</v>
+      </c>
+      <c r="D113">
+        <f>SD!E83</f>
+        <v>5.05</v>
+      </c>
+      <c r="E113">
+        <f>SD!F83</f>
+        <v>5.28</v>
+      </c>
+      <c r="F113">
+        <f>SD!G83</f>
+        <v>5.99</v>
+      </c>
+      <c r="G113">
+        <f>SD!H83</f>
+        <v>5.49</v>
+      </c>
+      <c r="H113">
+        <f>SD!I83</f>
+        <v>5.15</v>
+      </c>
+      <c r="I113">
+        <f>SD!J83</f>
+        <v>4.7</v>
+      </c>
+      <c r="J113">
+        <f>SD!K83</f>
+        <v>4.5</v>
+      </c>
+      <c r="K113">
+        <f>SD!L83</f>
+        <v>4.5</v>
+      </c>
+      <c r="L113">
+        <f>SD!M83</f>
+        <v>4.5</v>
+      </c>
+      <c r="M113">
+        <f>SD!N83</f>
+        <v>4.5</v>
+      </c>
+      <c r="N113">
+        <f>SD!O83</f>
+        <v>3.22</v>
+      </c>
+      <c r="O113">
+        <f>SD!P83</f>
+        <v>3.22</v>
+      </c>
+      <c r="P113">
+        <f>SD!Q83</f>
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A121" t="str">
+        <f>SD!A84</f>
+        <v>Technology QA</v>
+      </c>
+      <c r="B121" t="str">
+        <f>SD!C$61</f>
+        <v>JAN</v>
+      </c>
+      <c r="C121" t="str">
+        <f>SD!D$61</f>
+        <v>FEB</v>
+      </c>
+      <c r="D121" t="str">
+        <f>SD!E$61</f>
+        <v>MAR</v>
+      </c>
+      <c r="E121" t="str">
+        <f>SD!F$61</f>
+        <v>APR</v>
+      </c>
+      <c r="F121" t="str">
+        <f>SD!G$61</f>
+        <v>MAY</v>
+      </c>
+      <c r="G121" t="str">
+        <f>SD!H$61</f>
+        <v>JUN</v>
+      </c>
+      <c r="H121" t="str">
+        <f>SD!I$61</f>
+        <v>JUL</v>
+      </c>
+      <c r="I121" t="str">
+        <f>SD!J$61</f>
+        <v>AUG</v>
+      </c>
+      <c r="J121" t="str">
+        <f>SD!K$61</f>
+        <v>SEP</v>
+      </c>
+      <c r="K121" t="str">
+        <f>SD!L$61</f>
+        <v>OCT</v>
+      </c>
+      <c r="L121" t="str">
+        <f>SD!M$61</f>
+        <v>NOV</v>
+      </c>
+      <c r="M121" t="str">
+        <f>SD!N$61</f>
+        <v>DEC</v>
+      </c>
+      <c r="N121" t="str">
+        <f>SD!O$61</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O121" t="str">
+        <f>SD!P$61</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P121" t="str">
+        <f>SD!Q$61</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="122" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A122" t="str">
+        <f>SD!B84</f>
+        <v>Staff</v>
+      </c>
+      <c r="B122">
+        <f>SD!C84</f>
+        <v>9</v>
+      </c>
+      <c r="C122">
+        <f>SD!D84</f>
+        <v>11</v>
+      </c>
+      <c r="D122">
+        <f>SD!E84</f>
+        <v>12</v>
+      </c>
+      <c r="E122">
+        <f>SD!F84</f>
+        <v>12</v>
+      </c>
+      <c r="F122">
+        <f>SD!G84</f>
+        <v>12</v>
+      </c>
+      <c r="G122">
+        <f>SD!H84</f>
+        <v>12</v>
+      </c>
+      <c r="H122">
+        <f>SD!I84</f>
+        <v>12</v>
+      </c>
+      <c r="I122">
+        <f>SD!J84</f>
+        <v>12</v>
+      </c>
+      <c r="J122">
+        <f>SD!K84</f>
+        <v>12</v>
+      </c>
+      <c r="K122">
+        <f>SD!L84</f>
+        <v>12</v>
+      </c>
+      <c r="L122">
+        <f>SD!M84</f>
+        <v>12</v>
+      </c>
+      <c r="M122">
+        <f>SD!N84</f>
+        <v>12</v>
+      </c>
+      <c r="N122">
+        <f>SD!O84</f>
+        <v>12</v>
+      </c>
+      <c r="O122">
+        <f>SD!P84</f>
+        <v>12</v>
+      </c>
+      <c r="P122">
+        <f>SD!Q84</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A123" t="str">
+        <f>SD!B85</f>
+        <v>Plan</v>
+      </c>
+      <c r="B123">
+        <f>SD!C85</f>
+        <v>7.93</v>
+      </c>
+      <c r="C123">
+        <f>SD!D85</f>
+        <v>11.3</v>
+      </c>
+      <c r="D123">
+        <f>SD!E85</f>
+        <v>12.51</v>
+      </c>
+      <c r="E123">
+        <f>SD!F85</f>
+        <v>11.685</v>
+      </c>
+      <c r="F123">
+        <f>SD!G85</f>
+        <v>12.94</v>
+      </c>
+      <c r="G123">
+        <f>SD!H85</f>
+        <v>13.46</v>
+      </c>
+      <c r="H123">
+        <f>SD!I85</f>
+        <v>15.4</v>
+      </c>
+      <c r="I123">
+        <f>SD!J85</f>
+        <v>15.25</v>
+      </c>
+      <c r="J123">
+        <f>SD!K85</f>
+        <v>15.75</v>
+      </c>
+      <c r="K123">
+        <f>SD!L85</f>
+        <v>13.45</v>
+      </c>
+      <c r="L123">
+        <f>SD!M85</f>
+        <v>13.2</v>
+      </c>
+      <c r="M123">
+        <f>SD!N85</f>
+        <v>12.85</v>
+      </c>
+      <c r="N123">
+        <f>SD!O85</f>
+        <v>9.6</v>
+      </c>
+      <c r="O123">
+        <f>SD!P85</f>
+        <v>9.6</v>
+      </c>
+      <c r="P123">
+        <f>SD!Q85</f>
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="131" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A131" t="str">
+        <f>SD!A92</f>
+        <v>Technology Management</v>
+      </c>
+      <c r="B131" t="str">
+        <f>SD!C$61</f>
+        <v>JAN</v>
+      </c>
+      <c r="C131" t="str">
+        <f>SD!D$61</f>
+        <v>FEB</v>
+      </c>
+      <c r="D131" t="str">
+        <f>SD!E$61</f>
+        <v>MAR</v>
+      </c>
+      <c r="E131" t="str">
+        <f>SD!F$61</f>
+        <v>APR</v>
+      </c>
+      <c r="F131" t="str">
+        <f>SD!G$61</f>
+        <v>MAY</v>
+      </c>
+      <c r="G131" t="str">
+        <f>SD!H$61</f>
+        <v>JUN</v>
+      </c>
+      <c r="H131" t="str">
+        <f>SD!I$61</f>
+        <v>JUL</v>
+      </c>
+      <c r="I131" t="str">
+        <f>SD!J$61</f>
+        <v>AUG</v>
+      </c>
+      <c r="J131" t="str">
+        <f>SD!K$61</f>
+        <v>SEP</v>
+      </c>
+      <c r="K131" t="str">
+        <f>SD!L$61</f>
+        <v>OCT</v>
+      </c>
+      <c r="L131" t="str">
+        <f>SD!M$61</f>
+        <v>NOV</v>
+      </c>
+      <c r="M131" t="str">
+        <f>SD!N$61</f>
+        <v>DEC</v>
+      </c>
+      <c r="N131" t="str">
+        <f>SD!O$61</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O131" t="str">
+        <f>SD!P$61</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P131" t="str">
+        <f>SD!Q$61</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="132" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A132" t="str">
+        <f>SD!B92</f>
+        <v>Staff</v>
+      </c>
+      <c r="B132">
+        <f>SD!C92</f>
+        <v>4</v>
+      </c>
+      <c r="C132">
+        <f>SD!D92</f>
+        <v>4</v>
+      </c>
+      <c r="D132">
+        <f>SD!E92</f>
+        <v>4</v>
+      </c>
+      <c r="E132">
+        <f>SD!F92</f>
+        <v>4</v>
+      </c>
+      <c r="F132">
+        <f>SD!G92</f>
+        <v>4</v>
+      </c>
+      <c r="G132">
+        <f>SD!H92</f>
+        <v>4</v>
+      </c>
+      <c r="H132">
+        <f>SD!I92</f>
+        <v>4</v>
+      </c>
+      <c r="I132">
+        <f>SD!J92</f>
+        <v>4</v>
+      </c>
+      <c r="J132">
+        <f>SD!K92</f>
+        <v>4</v>
+      </c>
+      <c r="K132">
+        <f>SD!L92</f>
+        <v>4</v>
+      </c>
+      <c r="L132">
+        <f>SD!M92</f>
+        <v>4</v>
+      </c>
+      <c r="M132">
+        <f>SD!N92</f>
+        <v>4</v>
+      </c>
+      <c r="N132">
+        <f>SD!O92</f>
+        <v>4</v>
+      </c>
+      <c r="O132">
+        <f>SD!P92</f>
+        <v>4</v>
+      </c>
+      <c r="P132">
+        <f>SD!Q92</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A133" t="str">
+        <f>SD!B93</f>
+        <v>Plan</v>
+      </c>
+      <c r="B133">
+        <f>SD!C93</f>
+        <v>3.08</v>
+      </c>
+      <c r="C133">
+        <f>SD!D93</f>
+        <v>2.94</v>
+      </c>
+      <c r="D133">
+        <f>SD!E93</f>
+        <v>2.99</v>
+      </c>
+      <c r="E133">
+        <f>SD!F93</f>
+        <v>3.07</v>
+      </c>
+      <c r="F133">
+        <f>SD!G93</f>
+        <v>3.07</v>
+      </c>
+      <c r="G133">
+        <f>SD!H93</f>
+        <v>3.23</v>
+      </c>
+      <c r="H133">
+        <f>SD!I93</f>
+        <v>3.83</v>
+      </c>
+      <c r="I133">
+        <f>SD!J93</f>
+        <v>3.83</v>
+      </c>
+      <c r="J133">
+        <f>SD!K93</f>
+        <v>3.83</v>
+      </c>
+      <c r="K133">
+        <f>SD!L93</f>
+        <v>3.83</v>
+      </c>
+      <c r="L133">
+        <f>SD!M93</f>
+        <v>4.2</v>
+      </c>
+      <c r="M133">
+        <f>SD!N93</f>
+        <v>5.2</v>
+      </c>
+      <c r="N133">
+        <f>SD!O93</f>
+        <v>5.2</v>
+      </c>
+      <c r="O133">
+        <f>SD!P93</f>
+        <v>5.2</v>
+      </c>
+      <c r="P133">
+        <f>SD!Q93</f>
+        <v>5.2</v>
       </c>
     </row>
   </sheetData>
@@ -12947,7 +20055,7 @@
   <sheetPr>
     <tabColor theme="9"/>
   </sheetPr>
-  <dimension ref="A1:Q49"/>
+  <dimension ref="A1:Q73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.2">
@@ -14177,7 +21285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A49" s="16">
         <v>0</v>
       </c>
@@ -14197,6 +21305,689 @@
         <v>0</v>
       </c>
       <c r="G49" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A61" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="B61" s="34"/>
+      <c r="C61" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="D61" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="E61" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I61" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J61" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="K61" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="L61" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="M61" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="N61" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O61" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="P61" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q61" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A62" s="12"/>
+      <c r="B62" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" s="12">
+        <v>24</v>
+      </c>
+      <c r="D62" s="12">
+        <v>23</v>
+      </c>
+      <c r="E62" s="12">
+        <v>22</v>
+      </c>
+      <c r="F62" s="12">
+        <v>21</v>
+      </c>
+      <c r="G62" s="12">
+        <v>20</v>
+      </c>
+      <c r="H62" s="12">
+        <v>20</v>
+      </c>
+      <c r="I62" s="12">
+        <v>19</v>
+      </c>
+      <c r="J62" s="12">
+        <v>19</v>
+      </c>
+      <c r="K62" s="12">
+        <v>19</v>
+      </c>
+      <c r="L62" s="12">
+        <v>19</v>
+      </c>
+      <c r="M62" s="12">
+        <v>19</v>
+      </c>
+      <c r="N62" s="12">
+        <v>19</v>
+      </c>
+      <c r="O62" s="12">
+        <v>19</v>
+      </c>
+      <c r="P62" s="12">
+        <v>19</v>
+      </c>
+      <c r="Q62" s="12">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A63" s="36"/>
+      <c r="B63" s="47" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" s="48">
+        <v>15.9125</v>
+      </c>
+      <c r="D63" s="48">
+        <v>17.340624999999999</v>
+      </c>
+      <c r="E63" s="48">
+        <v>16.478124999999999</v>
+      </c>
+      <c r="F63" s="48">
+        <v>18.563124999999999</v>
+      </c>
+      <c r="G63" s="48">
+        <v>18.393125000000001</v>
+      </c>
+      <c r="H63" s="48">
+        <v>17.963125000000002</v>
+      </c>
+      <c r="I63" s="48">
+        <v>15.8225</v>
+      </c>
+      <c r="J63" s="48">
+        <v>14.9725</v>
+      </c>
+      <c r="K63" s="48">
+        <v>14.3725</v>
+      </c>
+      <c r="L63" s="48">
+        <v>13.585000000000001</v>
+      </c>
+      <c r="M63" s="48">
+        <v>13.635</v>
+      </c>
+      <c r="N63" s="48">
+        <v>13.335000000000001</v>
+      </c>
+      <c r="O63" s="48">
+        <v>8.3849999999999998</v>
+      </c>
+      <c r="P63" s="48">
+        <v>8.3849999999999998</v>
+      </c>
+      <c r="Q63" s="48">
+        <v>8.3849999999999998</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A64" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" s="35">
+        <v>4</v>
+      </c>
+      <c r="D64" s="35">
+        <v>4</v>
+      </c>
+      <c r="E64" s="35">
+        <v>3</v>
+      </c>
+      <c r="F64" s="35">
+        <v>3</v>
+      </c>
+      <c r="G64" s="35">
+        <v>3</v>
+      </c>
+      <c r="H64" s="35">
+        <v>3</v>
+      </c>
+      <c r="I64" s="35">
+        <v>3</v>
+      </c>
+      <c r="J64" s="35">
+        <v>3</v>
+      </c>
+      <c r="K64" s="35">
+        <v>3</v>
+      </c>
+      <c r="L64" s="35">
+        <v>3</v>
+      </c>
+      <c r="M64" s="35">
+        <v>3</v>
+      </c>
+      <c r="N64" s="35">
+        <v>3</v>
+      </c>
+      <c r="O64" s="35">
+        <v>3</v>
+      </c>
+      <c r="P64" s="35">
+        <v>3</v>
+      </c>
+      <c r="Q64" s="35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A65" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="B65" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C65" s="8">
+        <v>2.8</v>
+      </c>
+      <c r="D65" s="8">
+        <v>2.8</v>
+      </c>
+      <c r="E65" s="8">
+        <v>2.8</v>
+      </c>
+      <c r="F65" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="G65" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="H65" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="I65" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="J65" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="K65" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="L65" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="M65" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="N65" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="O65" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="P65" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="Q65" s="8">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A66" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" s="35">
+        <v>8</v>
+      </c>
+      <c r="D66" s="35">
+        <v>8</v>
+      </c>
+      <c r="E66" s="35">
+        <v>8</v>
+      </c>
+      <c r="F66" s="35">
+        <v>8</v>
+      </c>
+      <c r="G66" s="35">
+        <v>8</v>
+      </c>
+      <c r="H66" s="35">
+        <v>8</v>
+      </c>
+      <c r="I66" s="35">
+        <v>8</v>
+      </c>
+      <c r="J66" s="35">
+        <v>8</v>
+      </c>
+      <c r="K66" s="35">
+        <v>8</v>
+      </c>
+      <c r="L66" s="35">
+        <v>8</v>
+      </c>
+      <c r="M66" s="35">
+        <v>8</v>
+      </c>
+      <c r="N66" s="35">
+        <v>8</v>
+      </c>
+      <c r="O66" s="35">
+        <v>8</v>
+      </c>
+      <c r="P66" s="35">
+        <v>8</v>
+      </c>
+      <c r="Q66" s="35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A67" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="B67" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C67" s="8">
+        <v>5.2125000000000004</v>
+      </c>
+      <c r="D67" s="8">
+        <v>6.2406249999999996</v>
+      </c>
+      <c r="E67" s="8">
+        <v>6.140625</v>
+      </c>
+      <c r="F67" s="8">
+        <v>7.0131249999999996</v>
+      </c>
+      <c r="G67" s="8">
+        <v>7.0881249999999998</v>
+      </c>
+      <c r="H67" s="8">
+        <v>6.9881250000000001</v>
+      </c>
+      <c r="I67" s="8">
+        <v>5.3475000000000001</v>
+      </c>
+      <c r="J67" s="8">
+        <v>5.1475</v>
+      </c>
+      <c r="K67" s="8">
+        <v>5.1475</v>
+      </c>
+      <c r="L67" s="8">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="M67" s="8">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="N67" s="8">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="O67" s="8">
+        <v>3.6850000000000001</v>
+      </c>
+      <c r="P67" s="8">
+        <v>3.6850000000000001</v>
+      </c>
+      <c r="Q67" s="8">
+        <v>3.6850000000000001</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A68" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" s="35">
+        <v>7</v>
+      </c>
+      <c r="D68" s="35">
+        <v>6</v>
+      </c>
+      <c r="E68" s="35">
+        <v>6</v>
+      </c>
+      <c r="F68" s="35">
+        <v>6</v>
+      </c>
+      <c r="G68" s="35">
+        <v>6</v>
+      </c>
+      <c r="H68" s="35">
+        <v>6</v>
+      </c>
+      <c r="I68" s="35">
+        <v>5</v>
+      </c>
+      <c r="J68" s="35">
+        <v>5</v>
+      </c>
+      <c r="K68" s="35">
+        <v>5</v>
+      </c>
+      <c r="L68" s="35">
+        <v>5</v>
+      </c>
+      <c r="M68" s="35">
+        <v>5</v>
+      </c>
+      <c r="N68" s="35">
+        <v>5</v>
+      </c>
+      <c r="O68" s="35">
+        <v>5</v>
+      </c>
+      <c r="P68" s="35">
+        <v>5</v>
+      </c>
+      <c r="Q68" s="35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A69" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="B69" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C69" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="D69" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="E69" s="8">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="F69" s="8">
+        <v>5.05</v>
+      </c>
+      <c r="G69" s="8">
+        <v>5.3</v>
+      </c>
+      <c r="H69" s="8">
+        <v>4.95</v>
+      </c>
+      <c r="I69" s="8">
+        <v>4.45</v>
+      </c>
+      <c r="J69" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="K69" s="8">
+        <v>3.75</v>
+      </c>
+      <c r="L69" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="M69" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="N69" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="O69" s="8">
+        <v>1.4</v>
+      </c>
+      <c r="P69" s="8">
+        <v>1.4</v>
+      </c>
+      <c r="Q69" s="8">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A70" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" s="35">
+        <v>4</v>
+      </c>
+      <c r="D70" s="35">
+        <v>4</v>
+      </c>
+      <c r="E70" s="35">
+        <v>4</v>
+      </c>
+      <c r="F70" s="35">
+        <v>4</v>
+      </c>
+      <c r="G70" s="35">
+        <v>3</v>
+      </c>
+      <c r="H70" s="35">
+        <v>3</v>
+      </c>
+      <c r="I70" s="35">
+        <v>3</v>
+      </c>
+      <c r="J70" s="35">
+        <v>3</v>
+      </c>
+      <c r="K70" s="35">
+        <v>3</v>
+      </c>
+      <c r="L70" s="35">
+        <v>3</v>
+      </c>
+      <c r="M70" s="35">
+        <v>3</v>
+      </c>
+      <c r="N70" s="35">
+        <v>3</v>
+      </c>
+      <c r="O70" s="35">
+        <v>3</v>
+      </c>
+      <c r="P70" s="35">
+        <v>3</v>
+      </c>
+      <c r="Q70" s="35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A71" s="39" t="s">
+        <v>75</v>
+      </c>
+      <c r="B71" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C71" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="D71" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="E71" s="8">
+        <v>2.9874999999999998</v>
+      </c>
+      <c r="F71" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="G71" s="8">
+        <v>3.105</v>
+      </c>
+      <c r="H71" s="8">
+        <v>3.125</v>
+      </c>
+      <c r="I71" s="8">
+        <v>3.125</v>
+      </c>
+      <c r="J71" s="8">
+        <v>3.125</v>
+      </c>
+      <c r="K71" s="8">
+        <v>2.5750000000000002</v>
+      </c>
+      <c r="L71" s="8">
+        <v>2.875</v>
+      </c>
+      <c r="M71" s="8">
+        <v>2.9249999999999998</v>
+      </c>
+      <c r="N71" s="8">
+        <v>2.625</v>
+      </c>
+      <c r="O71" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="P71" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="Q71" s="8">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A72" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" s="35">
+        <v>1</v>
+      </c>
+      <c r="D72" s="35">
+        <v>1</v>
+      </c>
+      <c r="E72" s="35">
+        <v>1</v>
+      </c>
+      <c r="F72" s="35">
+        <v>0</v>
+      </c>
+      <c r="G72" s="35">
+        <v>0</v>
+      </c>
+      <c r="H72" s="35">
+        <v>0</v>
+      </c>
+      <c r="I72" s="35">
+        <v>0</v>
+      </c>
+      <c r="J72" s="35">
+        <v>0</v>
+      </c>
+      <c r="K72" s="35">
+        <v>0</v>
+      </c>
+      <c r="L72" s="35">
+        <v>0</v>
+      </c>
+      <c r="M72" s="35">
+        <v>0</v>
+      </c>
+      <c r="N72" s="35">
+        <v>0</v>
+      </c>
+      <c r="O72" s="35">
+        <v>0</v>
+      </c>
+      <c r="P72" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A73" s="39" t="s">
+        <v>76</v>
+      </c>
+      <c r="B73" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C73" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="D73" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="E73" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="F73" s="8">
+        <v>0</v>
+      </c>
+      <c r="G73" s="8">
+        <v>0</v>
+      </c>
+      <c r="H73" s="8">
+        <v>0</v>
+      </c>
+      <c r="I73" s="8">
+        <v>0</v>
+      </c>
+      <c r="J73" s="8">
+        <v>0</v>
+      </c>
+      <c r="K73" s="8">
+        <v>0</v>
+      </c>
+      <c r="L73" s="8">
+        <v>0</v>
+      </c>
+      <c r="M73" s="8">
+        <v>0</v>
+      </c>
+      <c r="N73" s="8">
+        <v>0</v>
+      </c>
+      <c r="O73" s="8">
+        <v>0</v>
+      </c>
+      <c r="P73" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="8">
         <v>0</v>
       </c>
     </row>

--- a/workforceresult.xlsx
+++ b/workforceresult.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miiintra/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5247C21A-2649-E140-AEDA-80984B3C94CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C20E1BE-35C6-EE41-8510-9A2491E74160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14500" yWindow="620" windowWidth="28800" windowHeight="21200" activeTab="9" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
+    <workbookView xWindow="14500" yWindow="620" windowWidth="28800" windowHeight="21200" activeTab="1" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
   </bookViews>
   <sheets>
     <sheet name="ALL" sheetId="1" r:id="rId1"/>
@@ -3118,65 +3118,65 @@
         <f>IF(AIC!B2&gt;0,AIC!B2,"")</f>
         <v>Staff</v>
       </c>
-      <c r="B22" t="str">
-        <f>IF(AIC!C13&gt;0,AIC!C13,"")</f>
-        <v/>
-      </c>
-      <c r="C22" t="str">
-        <f>IF(AIC!D13&gt;0,AIC!D13,"")</f>
-        <v/>
-      </c>
-      <c r="D22" t="str">
-        <f>IF(AIC!E13&gt;0,AIC!E13,"")</f>
-        <v/>
-      </c>
-      <c r="E22" t="str">
-        <f>IF(AIC!F13&gt;0,AIC!F13,"")</f>
-        <v/>
-      </c>
-      <c r="F22" t="str">
-        <f>IF(AIC!G13&gt;0,AIC!G13,"")</f>
-        <v/>
-      </c>
-      <c r="G22" t="str">
-        <f>IF(AIC!H13&gt;0,AIC!H13,"")</f>
-        <v/>
-      </c>
-      <c r="H22" t="str">
-        <f>IF(AIC!I13&gt;0,AIC!I13,"")</f>
-        <v/>
-      </c>
-      <c r="I22" t="str">
-        <f>IF(AIC!J13&gt;0,AIC!J13,"")</f>
-        <v/>
-      </c>
-      <c r="J22" t="str">
-        <f>IF(AIC!K13&gt;0,AIC!K13,"")</f>
-        <v/>
-      </c>
-      <c r="K22" t="str">
-        <f>IF(AIC!L13&gt;0,AIC!L13,"")</f>
-        <v/>
-      </c>
-      <c r="L22" t="str">
-        <f>IF(AIC!M13&gt;0,AIC!M13,"")</f>
-        <v/>
-      </c>
-      <c r="M22" t="str">
-        <f>IF(AIC!N13&gt;0,AIC!N13,"")</f>
-        <v/>
-      </c>
-      <c r="N22" t="str">
-        <f>IF(AIC!O13&gt;0,AIC!O13,"")</f>
-        <v/>
-      </c>
-      <c r="O22" t="str">
-        <f>IF(AIC!P13&gt;0,AIC!P13,"")</f>
-        <v/>
-      </c>
-      <c r="P22" t="str">
-        <f>IF(AIC!Q13&gt;0,AIC!Q13,"")</f>
-        <v/>
+      <c r="B22">
+        <f>AIC!C13</f>
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <f>AIC!D13</f>
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <f>AIC!E13</f>
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <f>AIC!F13</f>
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <f>AIC!G13</f>
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <f>AIC!H13</f>
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <f>AIC!I13</f>
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <f>AIC!J13</f>
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <f>AIC!K13</f>
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <f>AIC!L13</f>
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <f>AIC!M13</f>
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <f>AIC!N13</f>
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <f>AIC!O13</f>
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <f>AIC!P13</f>
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <f>AIC!Q13</f>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.2">
@@ -3184,65 +3184,65 @@
         <f>IF(AIC!B3&gt;0,AIC!B3,"")</f>
         <v>Staff AVG</v>
       </c>
-      <c r="B23" t="str">
-        <f>IF(AIC!C14&gt;0,AIC!C14,"")</f>
-        <v/>
-      </c>
-      <c r="C23" t="str">
-        <f>IF(AIC!D14&gt;0,AIC!D14,"")</f>
-        <v/>
-      </c>
-      <c r="D23" t="str">
-        <f>IF(AIC!E14&gt;0,AIC!E14,"")</f>
-        <v/>
-      </c>
-      <c r="E23" t="str">
-        <f>IF(AIC!F14&gt;0,AIC!F14,"")</f>
-        <v/>
-      </c>
-      <c r="F23" t="str">
-        <f>IF(AIC!G14&gt;0,AIC!G14,"")</f>
-        <v/>
-      </c>
-      <c r="G23" t="str">
-        <f>IF(AIC!H14&gt;0,AIC!H14,"")</f>
-        <v/>
-      </c>
-      <c r="H23" t="str">
-        <f>IF(AIC!I14&gt;0,AIC!I14,"")</f>
-        <v/>
-      </c>
-      <c r="I23" t="str">
-        <f>IF(AIC!J14&gt;0,AIC!J14,"")</f>
-        <v/>
-      </c>
-      <c r="J23" t="str">
-        <f>IF(AIC!K14&gt;0,AIC!K14,"")</f>
-        <v/>
-      </c>
-      <c r="K23" t="str">
-        <f>IF(AIC!L14&gt;0,AIC!L14,"")</f>
-        <v/>
-      </c>
-      <c r="L23" t="str">
-        <f>IF(AIC!M14&gt;0,AIC!M14,"")</f>
-        <v/>
-      </c>
-      <c r="M23" t="str">
-        <f>IF(AIC!N14&gt;0,AIC!N14,"")</f>
-        <v/>
-      </c>
-      <c r="N23" t="str">
-        <f>IF(AIC!O14&gt;0,AIC!O14,"")</f>
-        <v/>
-      </c>
-      <c r="O23" t="str">
-        <f>IF(AIC!P14&gt;0,AIC!P14,"")</f>
-        <v/>
-      </c>
-      <c r="P23" t="str">
-        <f>IF(AIC!Q14&gt;0,AIC!Q14,"")</f>
-        <v/>
+      <c r="B23">
+        <f>AIC!C14</f>
+        <v>0</v>
+      </c>
+      <c r="C23">
+        <f>AIC!D14</f>
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <f>AIC!E14</f>
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <f>AIC!F14</f>
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <f>AIC!G14</f>
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <f>AIC!H14</f>
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <f>AIC!I14</f>
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <f>AIC!J14</f>
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <f>AIC!K14</f>
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <f>AIC!L14</f>
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <f>AIC!M14</f>
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <f>AIC!N14</f>
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <f>AIC!O14</f>
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <f>AIC!P14</f>
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <f>AIC!Q14</f>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.2">
@@ -3250,65 +3250,65 @@
         <f>IF(AIC!B4&gt;0,AIC!B4,"")</f>
         <v>Plan</v>
       </c>
-      <c r="B24" t="str">
-        <f>IF(AIC!C15&gt;0,AIC!C15,"")</f>
-        <v/>
-      </c>
-      <c r="C24" t="str">
-        <f>IF(AIC!D15&gt;0,AIC!D15,"")</f>
-        <v/>
-      </c>
-      <c r="D24" t="str">
-        <f>IF(AIC!E15&gt;0,AIC!E15,"")</f>
-        <v/>
-      </c>
-      <c r="E24" t="str">
-        <f>IF(AIC!F15&gt;0,AIC!F15,"")</f>
-        <v/>
-      </c>
-      <c r="F24" t="str">
-        <f>IF(AIC!G15&gt;0,AIC!G15,"")</f>
-        <v/>
-      </c>
-      <c r="G24" t="str">
-        <f>IF(AIC!H15&gt;0,AIC!H15,"")</f>
-        <v/>
-      </c>
-      <c r="H24" t="str">
-        <f>IF(AIC!I15&gt;0,AIC!I15,"")</f>
-        <v/>
-      </c>
-      <c r="I24" t="str">
-        <f>IF(AIC!J15&gt;0,AIC!J15,"")</f>
-        <v/>
-      </c>
-      <c r="J24" t="str">
-        <f>IF(AIC!K15&gt;0,AIC!K15,"")</f>
-        <v/>
-      </c>
-      <c r="K24" t="str">
-        <f>IF(AIC!L15&gt;0,AIC!L15,"")</f>
-        <v/>
-      </c>
-      <c r="L24" t="str">
-        <f>IF(AIC!M15&gt;0,AIC!M15,"")</f>
-        <v/>
-      </c>
-      <c r="M24" t="str">
-        <f>IF(AIC!N15&gt;0,AIC!N15,"")</f>
-        <v/>
-      </c>
-      <c r="N24" t="str">
-        <f>IF(AIC!O15&gt;0,AIC!O15,"")</f>
-        <v/>
-      </c>
-      <c r="O24" t="str">
-        <f>IF(AIC!P15&gt;0,AIC!P15,"")</f>
-        <v/>
-      </c>
-      <c r="P24" t="str">
-        <f>IF(AIC!Q15&gt;0,AIC!Q15,"")</f>
-        <v/>
+      <c r="B24">
+        <f>AIC!C15</f>
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <f>AIC!D15</f>
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <f>AIC!E15</f>
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <f>AIC!F15</f>
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <f>AIC!G15</f>
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <f>AIC!H15</f>
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <f>AIC!I15</f>
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <f>AIC!J15</f>
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <f>AIC!K15</f>
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <f>AIC!L15</f>
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <f>AIC!M15</f>
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <f>AIC!N15</f>
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <f>AIC!O15</f>
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <f>AIC!P15</f>
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <f>AIC!Q15</f>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.2">
@@ -3378,65 +3378,65 @@
         <f>IF(AIC!B2&gt;0,AIC!B2,"")</f>
         <v>Staff</v>
       </c>
-      <c r="B32" t="str">
-        <f>IF(AIC!C17&gt;0,AIC!C17,"")</f>
-        <v/>
-      </c>
-      <c r="C32" t="str">
-        <f>IF(AIC!D17&gt;0,AIC!D17,"")</f>
-        <v/>
-      </c>
-      <c r="D32" t="str">
-        <f>IF(AIC!E17&gt;0,AIC!E17,"")</f>
-        <v/>
-      </c>
-      <c r="E32" t="str">
-        <f>IF(AIC!F17&gt;0,AIC!F17,"")</f>
-        <v/>
-      </c>
-      <c r="F32" t="str">
-        <f>IF(AIC!G17&gt;0,AIC!G17,"")</f>
-        <v/>
-      </c>
-      <c r="G32" t="str">
-        <f>IF(AIC!H17&gt;0,AIC!H17,"")</f>
-        <v/>
-      </c>
-      <c r="H32" t="str">
-        <f>IF(AIC!I17&gt;0,AIC!I17,"")</f>
-        <v/>
-      </c>
-      <c r="I32" t="str">
-        <f>IF(AIC!J17&gt;0,AIC!J17,"")</f>
-        <v/>
-      </c>
-      <c r="J32" t="str">
-        <f>IF(AIC!K17&gt;0,AIC!K17,"")</f>
-        <v/>
-      </c>
-      <c r="K32" t="str">
-        <f>IF(AIC!L17&gt;0,AIC!L17,"")</f>
-        <v/>
-      </c>
-      <c r="L32" t="str">
-        <f>IF(AIC!M17&gt;0,AIC!M17,"")</f>
-        <v/>
-      </c>
-      <c r="M32" t="str">
-        <f>IF(AIC!N17&gt;0,AIC!N17,"")</f>
-        <v/>
-      </c>
-      <c r="N32" t="str">
-        <f>IF(AIC!O17&gt;0,AIC!O17,"")</f>
-        <v/>
-      </c>
-      <c r="O32" t="str">
-        <f>IF(AIC!P17&gt;0,AIC!P17,"")</f>
-        <v/>
-      </c>
-      <c r="P32" t="str">
-        <f>IF(AIC!Q17&gt;0,AIC!Q17,"")</f>
-        <v/>
+      <c r="B32">
+        <f>AIC!C17</f>
+        <v>0</v>
+      </c>
+      <c r="C32">
+        <f>AIC!D17</f>
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <f>AIC!E17</f>
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <f>AIC!F17</f>
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <f>AIC!G17</f>
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <f>AIC!H17</f>
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <f>AIC!I17</f>
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <f>AIC!J17</f>
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <f>AIC!K17</f>
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <f>AIC!L17</f>
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <f>AIC!M17</f>
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <f>AIC!N17</f>
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <f>AIC!O17</f>
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <f>AIC!P17</f>
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <f>AIC!Q17</f>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.2">
@@ -3444,65 +3444,65 @@
         <f>IF(AIC!B3&gt;0,AIC!B3,"")</f>
         <v>Staff AVG</v>
       </c>
-      <c r="B33" t="str">
-        <f>IF(AIC!C18&gt;0,AIC!C18,"")</f>
-        <v/>
-      </c>
-      <c r="C33" t="str">
-        <f>IF(AIC!D18&gt;0,AIC!D18,"")</f>
-        <v/>
-      </c>
-      <c r="D33" t="str">
-        <f>IF(AIC!E18&gt;0,AIC!E18,"")</f>
-        <v/>
-      </c>
-      <c r="E33" t="str">
-        <f>IF(AIC!F18&gt;0,AIC!F18,"")</f>
-        <v/>
-      </c>
-      <c r="F33" t="str">
-        <f>IF(AIC!G18&gt;0,AIC!G18,"")</f>
-        <v/>
-      </c>
-      <c r="G33" t="str">
-        <f>IF(AIC!H18&gt;0,AIC!H18,"")</f>
-        <v/>
-      </c>
-      <c r="H33" t="str">
-        <f>IF(AIC!I18&gt;0,AIC!I18,"")</f>
-        <v/>
-      </c>
-      <c r="I33" t="str">
-        <f>IF(AIC!J18&gt;0,AIC!J18,"")</f>
-        <v/>
-      </c>
-      <c r="J33" t="str">
-        <f>IF(AIC!K18&gt;0,AIC!K18,"")</f>
-        <v/>
-      </c>
-      <c r="K33" t="str">
-        <f>IF(AIC!L18&gt;0,AIC!L18,"")</f>
-        <v/>
-      </c>
-      <c r="L33" t="str">
-        <f>IF(AIC!M18&gt;0,AIC!M18,"")</f>
-        <v/>
-      </c>
-      <c r="M33" t="str">
-        <f>IF(AIC!N18&gt;0,AIC!N18,"")</f>
-        <v/>
-      </c>
-      <c r="N33" t="str">
-        <f>IF(AIC!O18&gt;0,AIC!O18,"")</f>
-        <v/>
-      </c>
-      <c r="O33" t="str">
-        <f>IF(AIC!P18&gt;0,AIC!P18,"")</f>
-        <v/>
-      </c>
-      <c r="P33" t="str">
-        <f>IF(AIC!Q18&gt;0,AIC!Q18,"")</f>
-        <v/>
+      <c r="B33">
+        <f>AIC!C18</f>
+        <v>0</v>
+      </c>
+      <c r="C33">
+        <f>AIC!D18</f>
+        <v>0</v>
+      </c>
+      <c r="D33">
+        <f>AIC!E18</f>
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <f>AIC!F18</f>
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <f>AIC!G18</f>
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <f>AIC!H18</f>
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <f>AIC!I18</f>
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <f>AIC!J18</f>
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <f>AIC!K18</f>
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <f>AIC!L18</f>
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <f>AIC!M18</f>
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <f>AIC!N18</f>
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <f>AIC!O18</f>
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <f>AIC!P18</f>
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <f>AIC!Q18</f>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.2">
@@ -3510,65 +3510,65 @@
         <f>IF(AIC!B4&gt;0,AIC!B4,"")</f>
         <v>Plan</v>
       </c>
-      <c r="B34" t="str">
-        <f>IF(AIC!C19&gt;0,AIC!C19,"")</f>
-        <v/>
-      </c>
-      <c r="C34" t="str">
-        <f>IF(AIC!D19&gt;0,AIC!D19,"")</f>
-        <v/>
-      </c>
-      <c r="D34" t="str">
-        <f>IF(AIC!E19&gt;0,AIC!E19,"")</f>
-        <v/>
-      </c>
-      <c r="E34" t="str">
-        <f>IF(AIC!F19&gt;0,AIC!F19,"")</f>
-        <v/>
-      </c>
-      <c r="F34" t="str">
-        <f>IF(AIC!G19&gt;0,AIC!G19,"")</f>
-        <v/>
-      </c>
-      <c r="G34" t="str">
-        <f>IF(AIC!H19&gt;0,AIC!H19,"")</f>
-        <v/>
-      </c>
-      <c r="H34" t="str">
-        <f>IF(AIC!I19&gt;0,AIC!I19,"")</f>
-        <v/>
-      </c>
-      <c r="I34" t="str">
-        <f>IF(AIC!J19&gt;0,AIC!J19,"")</f>
-        <v/>
-      </c>
-      <c r="J34" t="str">
-        <f>IF(AIC!K19&gt;0,AIC!K19,"")</f>
-        <v/>
-      </c>
-      <c r="K34" t="str">
-        <f>IF(AIC!L19&gt;0,AIC!L19,"")</f>
-        <v/>
-      </c>
-      <c r="L34" t="str">
-        <f>IF(AIC!M19&gt;0,AIC!M19,"")</f>
-        <v/>
-      </c>
-      <c r="M34" t="str">
-        <f>IF(AIC!N19&gt;0,AIC!N19,"")</f>
-        <v/>
-      </c>
-      <c r="N34" t="str">
-        <f>IF(AIC!O19&gt;0,AIC!O19,"")</f>
-        <v/>
-      </c>
-      <c r="O34" t="str">
-        <f>IF(AIC!P19&gt;0,AIC!P19,"")</f>
-        <v/>
-      </c>
-      <c r="P34" t="str">
-        <f>IF(AIC!Q19&gt;0,AIC!Q19,"")</f>
-        <v/>
+      <c r="B34">
+        <f>AIC!C19</f>
+        <v>0</v>
+      </c>
+      <c r="C34">
+        <f>AIC!D19</f>
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <f>AIC!E19</f>
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <f>AIC!F19</f>
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <f>AIC!G19</f>
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <f>AIC!H19</f>
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <f>AIC!I19</f>
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <f>AIC!J19</f>
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <f>AIC!K19</f>
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <f>AIC!L19</f>
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <f>AIC!M19</f>
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <f>AIC!N19</f>
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <f>AIC!O19</f>
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <f>AIC!P19</f>
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <f>AIC!Q19</f>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.2">
@@ -8703,200 +8703,200 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" t="str">
-        <f>IF(CPS!B2&gt;0,CPS!B2,"")</f>
+        <f>CPS!B2</f>
         <v>Staff</v>
       </c>
-      <c r="B22" t="str">
-        <f>IF(CPS!C13&gt;0,CPS!C13,"")</f>
-        <v/>
-      </c>
-      <c r="C22" t="str">
-        <f>IF(CPS!D13&gt;0,CPS!D13,"")</f>
-        <v/>
-      </c>
-      <c r="D22" t="str">
-        <f>IF(CPS!E13&gt;0,CPS!E13,"")</f>
-        <v/>
-      </c>
-      <c r="E22" t="str">
-        <f>IF(CPS!F13&gt;0,CPS!F13,"")</f>
-        <v/>
-      </c>
-      <c r="F22" t="str">
-        <f>IF(CPS!G13&gt;0,CPS!G13,"")</f>
-        <v/>
-      </c>
-      <c r="G22" t="str">
-        <f>IF(CPS!H13&gt;0,CPS!H13,"")</f>
-        <v/>
-      </c>
-      <c r="H22" t="str">
-        <f>IF(CPS!I13&gt;0,CPS!I13,"")</f>
-        <v/>
-      </c>
-      <c r="I22" t="str">
-        <f>IF(CPS!J13&gt;0,CPS!J13,"")</f>
-        <v/>
-      </c>
-      <c r="J22" t="str">
-        <f>IF(CPS!K13&gt;0,CPS!K13,"")</f>
-        <v/>
-      </c>
-      <c r="K22" t="str">
-        <f>IF(CPS!L13&gt;0,CPS!L13,"")</f>
-        <v/>
-      </c>
-      <c r="L22" t="str">
-        <f>IF(CPS!M13&gt;0,CPS!M13,"")</f>
-        <v/>
-      </c>
-      <c r="M22" t="str">
-        <f>IF(CPS!N13&gt;0,CPS!N13,"")</f>
-        <v/>
-      </c>
-      <c r="N22" t="str">
-        <f>IF(CPS!O13&gt;0,CPS!O13,"")</f>
-        <v/>
-      </c>
-      <c r="O22" t="str">
-        <f>IF(CPS!P13&gt;0,CPS!P13,"")</f>
-        <v/>
-      </c>
-      <c r="P22" t="str">
-        <f>IF(CPS!Q13&gt;0,CPS!Q13,"")</f>
-        <v/>
+      <c r="B22">
+        <f>CPS!C13</f>
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <f>CPS!D13</f>
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <f>CPS!E13</f>
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <f>CPS!F13</f>
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <f>CPS!G13</f>
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <f>CPS!H13</f>
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <f>CPS!I13</f>
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <f>CPS!J13</f>
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <f>CPS!K13</f>
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <f>CPS!L13</f>
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <f>CPS!M13</f>
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <f>CPS!N13</f>
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <f>CPS!O13</f>
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <f>CPS!P13</f>
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <f>CPS!Q13</f>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" t="str">
-        <f>IF(CPS!B3&gt;0,CPS!B3,"")</f>
+        <f>CPS!B3</f>
         <v>Staff AVG</v>
       </c>
-      <c r="B23" t="str">
-        <f>IF(CPS!C14&gt;0,CPS!C14,"")</f>
-        <v/>
-      </c>
-      <c r="C23" t="str">
-        <f>IF(CPS!D14&gt;0,CPS!D14,"")</f>
-        <v/>
-      </c>
-      <c r="D23" t="str">
-        <f>IF(CPS!E14&gt;0,CPS!E14,"")</f>
-        <v/>
-      </c>
-      <c r="E23" t="str">
-        <f>IF(CPS!F14&gt;0,CPS!F14,"")</f>
-        <v/>
-      </c>
-      <c r="F23" t="str">
-        <f>IF(CPS!G14&gt;0,CPS!G14,"")</f>
-        <v/>
-      </c>
-      <c r="G23" t="str">
-        <f>IF(CPS!H14&gt;0,CPS!H14,"")</f>
-        <v/>
-      </c>
-      <c r="H23" t="str">
-        <f>IF(CPS!I14&gt;0,CPS!I14,"")</f>
-        <v/>
-      </c>
-      <c r="I23" t="str">
-        <f>IF(CPS!J14&gt;0,CPS!J14,"")</f>
-        <v/>
-      </c>
-      <c r="J23" t="str">
-        <f>IF(CPS!K14&gt;0,CPS!K14,"")</f>
-        <v/>
-      </c>
-      <c r="K23" t="str">
-        <f>IF(CPS!L14&gt;0,CPS!L14,"")</f>
-        <v/>
-      </c>
-      <c r="L23" t="str">
-        <f>IF(CPS!M14&gt;0,CPS!M14,"")</f>
-        <v/>
-      </c>
-      <c r="M23" t="str">
-        <f>IF(CPS!N14&gt;0,CPS!N14,"")</f>
-        <v/>
-      </c>
-      <c r="N23" t="str">
-        <f>IF(CPS!O14&gt;0,CPS!O14,"")</f>
-        <v/>
-      </c>
-      <c r="O23" t="str">
-        <f>IF(CPS!P14&gt;0,CPS!P14,"")</f>
-        <v/>
-      </c>
-      <c r="P23" t="str">
-        <f>IF(CPS!Q14&gt;0,CPS!Q14,"")</f>
-        <v/>
+      <c r="B23">
+        <f>CPS!C14</f>
+        <v>0</v>
+      </c>
+      <c r="C23">
+        <f>CPS!D14</f>
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <f>CPS!E14</f>
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <f>CPS!F14</f>
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <f>CPS!G14</f>
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <f>CPS!H14</f>
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <f>CPS!I14</f>
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <f>CPS!J14</f>
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <f>CPS!K14</f>
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <f>CPS!L14</f>
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <f>CPS!M14</f>
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <f>CPS!N14</f>
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <f>CPS!O14</f>
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <f>CPS!P14</f>
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <f>CPS!Q14</f>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" t="str">
-        <f>IF(CPS!B4&gt;0,CPS!B4,"")</f>
+        <f>CPS!B4</f>
         <v>Plan</v>
       </c>
-      <c r="B24" t="str">
-        <f>IF(CPS!C15&gt;0,CPS!C15,"")</f>
-        <v/>
-      </c>
-      <c r="C24" t="str">
-        <f>IF(CPS!D15&gt;0,CPS!D15,"")</f>
-        <v/>
-      </c>
-      <c r="D24" t="str">
-        <f>IF(CPS!E15&gt;0,CPS!E15,"")</f>
-        <v/>
-      </c>
-      <c r="E24" t="str">
-        <f>IF(CPS!F15&gt;0,CPS!F15,"")</f>
-        <v/>
-      </c>
-      <c r="F24" t="str">
-        <f>IF(CPS!G15&gt;0,CPS!G15,"")</f>
-        <v/>
-      </c>
-      <c r="G24" t="str">
-        <f>IF(CPS!H15&gt;0,CPS!H15,"")</f>
-        <v/>
-      </c>
-      <c r="H24" t="str">
-        <f>IF(CPS!I15&gt;0,CPS!I15,"")</f>
-        <v/>
-      </c>
-      <c r="I24" t="str">
-        <f>IF(CPS!J15&gt;0,CPS!J15,"")</f>
-        <v/>
-      </c>
-      <c r="J24" t="str">
-        <f>IF(CPS!K15&gt;0,CPS!K15,"")</f>
-        <v/>
-      </c>
-      <c r="K24" t="str">
-        <f>IF(CPS!L15&gt;0,CPS!L15,"")</f>
-        <v/>
-      </c>
-      <c r="L24" t="str">
-        <f>IF(CPS!M15&gt;0,CPS!M15,"")</f>
-        <v/>
-      </c>
-      <c r="M24" t="str">
-        <f>IF(CPS!N15&gt;0,CPS!N15,"")</f>
-        <v/>
-      </c>
-      <c r="N24" t="str">
-        <f>IF(CPS!O15&gt;0,CPS!O15,"")</f>
-        <v/>
-      </c>
-      <c r="O24" t="str">
-        <f>IF(CPS!P15&gt;0,CPS!P15,"")</f>
-        <v/>
-      </c>
-      <c r="P24" t="str">
-        <f>IF(CPS!Q15&gt;0,CPS!Q15,"")</f>
-        <v/>
+      <c r="B24">
+        <f>CPS!C15</f>
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <f>CPS!D15</f>
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <f>CPS!E15</f>
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <f>CPS!F15</f>
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <f>CPS!G15</f>
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <f>CPS!H15</f>
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <f>CPS!I15</f>
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <f>CPS!J15</f>
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <f>CPS!K15</f>
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <f>CPS!L15</f>
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <f>CPS!M15</f>
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <f>CPS!N15</f>
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <f>CPS!O15</f>
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <f>CPS!P15</f>
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <f>CPS!Q15</f>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.2">
@@ -8966,65 +8966,65 @@
         <f>IF(CPS!B2&gt;0,CPS!B2,"")</f>
         <v>Staff</v>
       </c>
-      <c r="B32" t="str">
-        <f>IF(CPS!C17&gt;0,CPS!C17,"")</f>
-        <v/>
-      </c>
-      <c r="C32" t="str">
-        <f>IF(CPS!D17&gt;0,CPS!D17,"")</f>
-        <v/>
-      </c>
-      <c r="D32" t="str">
-        <f>IF(CPS!E17&gt;0,CPS!E17,"")</f>
-        <v/>
-      </c>
-      <c r="E32" t="str">
-        <f>IF(CPS!F17&gt;0,CPS!F17,"")</f>
-        <v/>
-      </c>
-      <c r="F32" t="str">
-        <f>IF(CPS!G17&gt;0,CPS!G17,"")</f>
-        <v/>
-      </c>
-      <c r="G32" t="str">
-        <f>IF(CPS!H17&gt;0,CPS!H17,"")</f>
-        <v/>
-      </c>
-      <c r="H32" t="str">
-        <f>IF(CPS!I17&gt;0,CPS!I17,"")</f>
-        <v/>
-      </c>
-      <c r="I32" t="str">
-        <f>IF(CPS!J17&gt;0,CPS!J17,"")</f>
-        <v/>
-      </c>
-      <c r="J32" t="str">
-        <f>IF(CPS!K17&gt;0,CPS!K17,"")</f>
-        <v/>
-      </c>
-      <c r="K32" t="str">
-        <f>IF(CPS!L17&gt;0,CPS!L17,"")</f>
-        <v/>
-      </c>
-      <c r="L32" t="str">
-        <f>IF(CPS!M17&gt;0,CPS!M17,"")</f>
-        <v/>
-      </c>
-      <c r="M32" t="str">
-        <f>IF(CPS!N17&gt;0,CPS!N17,"")</f>
-        <v/>
-      </c>
-      <c r="N32" t="str">
-        <f>IF(CPS!O17&gt;0,CPS!O17,"")</f>
-        <v/>
-      </c>
-      <c r="O32" t="str">
-        <f>IF(CPS!P17&gt;0,CPS!P17,"")</f>
-        <v/>
-      </c>
-      <c r="P32" t="str">
-        <f>IF(CPS!Q17&gt;0,CPS!Q17,"")</f>
-        <v/>
+      <c r="B32">
+        <f>CPS!C17</f>
+        <v>0</v>
+      </c>
+      <c r="C32">
+        <f>CPS!D17</f>
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <f>CPS!E17</f>
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <f>CPS!F17</f>
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <f>CPS!G17</f>
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <f>CPS!H17</f>
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <f>CPS!I17</f>
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <f>CPS!J17</f>
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <f>CPS!K17</f>
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <f>CPS!L17</f>
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <f>CPS!M17</f>
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <f>CPS!N17</f>
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <f>CPS!O17</f>
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <f>CPS!P17</f>
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <f>CPS!Q17</f>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.2">
@@ -9032,65 +9032,65 @@
         <f>IF(CPS!B3&gt;0,CPS!B3,"")</f>
         <v>Staff AVG</v>
       </c>
-      <c r="B33" t="str">
-        <f>IF(CPS!C18&gt;0,CPS!C18,"")</f>
-        <v/>
-      </c>
-      <c r="C33" t="str">
-        <f>IF(CPS!D18&gt;0,CPS!D18,"")</f>
-        <v/>
-      </c>
-      <c r="D33" t="str">
-        <f>IF(CPS!E18&gt;0,CPS!E18,"")</f>
-        <v/>
-      </c>
-      <c r="E33" t="str">
-        <f>IF(CPS!F18&gt;0,CPS!F18,"")</f>
-        <v/>
-      </c>
-      <c r="F33" t="str">
-        <f>IF(CPS!G18&gt;0,CPS!G18,"")</f>
-        <v/>
-      </c>
-      <c r="G33" t="str">
-        <f>IF(CPS!H18&gt;0,CPS!H18,"")</f>
-        <v/>
-      </c>
-      <c r="H33" t="str">
-        <f>IF(CPS!I18&gt;0,CPS!I18,"")</f>
-        <v/>
-      </c>
-      <c r="I33" t="str">
-        <f>IF(CPS!J18&gt;0,CPS!J18,"")</f>
-        <v/>
-      </c>
-      <c r="J33" t="str">
-        <f>IF(CPS!K18&gt;0,CPS!K18,"")</f>
-        <v/>
-      </c>
-      <c r="K33" t="str">
-        <f>IF(CPS!L18&gt;0,CPS!L18,"")</f>
-        <v/>
-      </c>
-      <c r="L33" t="str">
-        <f>IF(CPS!M18&gt;0,CPS!M18,"")</f>
-        <v/>
-      </c>
-      <c r="M33" t="str">
-        <f>IF(CPS!N18&gt;0,CPS!N18,"")</f>
-        <v/>
-      </c>
-      <c r="N33" t="str">
-        <f>IF(CPS!O18&gt;0,CPS!O18,"")</f>
-        <v/>
-      </c>
-      <c r="O33" t="str">
-        <f>IF(CPS!P18&gt;0,CPS!P18,"")</f>
-        <v/>
-      </c>
-      <c r="P33" t="str">
-        <f>IF(CPS!Q18&gt;0,CPS!Q18,"")</f>
-        <v/>
+      <c r="B33">
+        <f>CPS!C18</f>
+        <v>0</v>
+      </c>
+      <c r="C33">
+        <f>CPS!D18</f>
+        <v>0</v>
+      </c>
+      <c r="D33">
+        <f>CPS!E18</f>
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <f>CPS!F18</f>
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <f>CPS!G18</f>
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <f>CPS!H18</f>
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <f>CPS!I18</f>
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <f>CPS!J18</f>
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <f>CPS!K18</f>
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <f>CPS!L18</f>
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <f>CPS!M18</f>
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <f>CPS!N18</f>
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <f>CPS!O18</f>
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <f>CPS!P18</f>
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <f>CPS!Q18</f>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.2">
@@ -9098,65 +9098,65 @@
         <f>IF(CPS!B4&gt;0,CPS!B4,"")</f>
         <v>Plan</v>
       </c>
-      <c r="B34" t="str">
-        <f>IF(CPS!C19&gt;0,CPS!C19,"")</f>
-        <v/>
-      </c>
-      <c r="C34" t="str">
-        <f>IF(CPS!D19&gt;0,CPS!D19,"")</f>
-        <v/>
-      </c>
-      <c r="D34" t="str">
-        <f>IF(CPS!E19&gt;0,CPS!E19,"")</f>
-        <v/>
-      </c>
-      <c r="E34" t="str">
-        <f>IF(CPS!F19&gt;0,CPS!F19,"")</f>
-        <v/>
-      </c>
-      <c r="F34" t="str">
-        <f>IF(CPS!G19&gt;0,CPS!G19,"")</f>
-        <v/>
-      </c>
-      <c r="G34" t="str">
-        <f>IF(CPS!H19&gt;0,CPS!H19,"")</f>
-        <v/>
-      </c>
-      <c r="H34" t="str">
-        <f>IF(CPS!I19&gt;0,CPS!I19,"")</f>
-        <v/>
-      </c>
-      <c r="I34" t="str">
-        <f>IF(CPS!J19&gt;0,CPS!J19,"")</f>
-        <v/>
-      </c>
-      <c r="J34" t="str">
-        <f>IF(CPS!K19&gt;0,CPS!K19,"")</f>
-        <v/>
-      </c>
-      <c r="K34" t="str">
-        <f>IF(CPS!L19&gt;0,CPS!L19,"")</f>
-        <v/>
-      </c>
-      <c r="L34" t="str">
-        <f>IF(CPS!M19&gt;0,CPS!M19,"")</f>
-        <v/>
-      </c>
-      <c r="M34" t="str">
-        <f>IF(CPS!N19&gt;0,CPS!N19,"")</f>
-        <v/>
-      </c>
-      <c r="N34" t="str">
-        <f>IF(CPS!O19&gt;0,CPS!O19,"")</f>
-        <v/>
-      </c>
-      <c r="O34" t="str">
-        <f>IF(CPS!P19&gt;0,CPS!P19,"")</f>
-        <v/>
-      </c>
-      <c r="P34" t="str">
-        <f>IF(CPS!Q19&gt;0,CPS!Q19,"")</f>
-        <v/>
+      <c r="B34">
+        <f>CPS!C19</f>
+        <v>0</v>
+      </c>
+      <c r="C34">
+        <f>CPS!D19</f>
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <f>CPS!E19</f>
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <f>CPS!F19</f>
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <f>CPS!G19</f>
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <f>CPS!H19</f>
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <f>CPS!I19</f>
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <f>CPS!J19</f>
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <f>CPS!K19</f>
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <f>CPS!L19</f>
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <f>CPS!M19</f>
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <f>CPS!N19</f>
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <f>CPS!O19</f>
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <f>CPS!P19</f>
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <f>CPS!Q19</f>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.2">
@@ -12799,63 +12799,63 @@
         <v>Staff</v>
       </c>
       <c r="B22">
-        <f>IF(PSE!C13&gt;0,PSE!C13,"")</f>
+        <f>PSE!C13</f>
         <v>17</v>
       </c>
       <c r="C22">
-        <f>IF(PSE!D13&gt;0,PSE!D13,"")</f>
+        <f>PSE!D13</f>
         <v>17</v>
       </c>
       <c r="D22">
-        <f>IF(PSE!E13&gt;0,PSE!E13,"")</f>
+        <f>PSE!E13</f>
         <v>17</v>
       </c>
       <c r="E22">
-        <f>IF(PSE!F13&gt;0,PSE!F13,"")</f>
+        <f>PSE!F13</f>
         <v>17</v>
       </c>
       <c r="F22">
-        <f>IF(PSE!G13&gt;0,PSE!G13,"")</f>
+        <f>PSE!G13</f>
         <v>17</v>
       </c>
       <c r="G22">
-        <f>IF(PSE!H13&gt;0,PSE!H13,"")</f>
+        <f>PSE!H13</f>
         <v>17</v>
       </c>
       <c r="H22">
-        <f>IF(PSE!I13&gt;0,PSE!I13,"")</f>
+        <f>PSE!I13</f>
         <v>17</v>
       </c>
       <c r="I22">
-        <f>IF(PSE!J13&gt;0,PSE!J13,"")</f>
+        <f>PSE!J13</f>
         <v>17</v>
       </c>
       <c r="J22">
-        <f>IF(PSE!K13&gt;0,PSE!K13,"")</f>
+        <f>PSE!K13</f>
         <v>17</v>
       </c>
       <c r="K22">
-        <f>IF(PSE!L13&gt;0,PSE!L13,"")</f>
+        <f>PSE!L13</f>
         <v>17</v>
       </c>
       <c r="L22">
-        <f>IF(PSE!M13&gt;0,PSE!M13,"")</f>
+        <f>PSE!M13</f>
         <v>17</v>
       </c>
       <c r="M22">
-        <f>IF(PSE!N13&gt;0,PSE!N13,"")</f>
+        <f>PSE!N13</f>
         <v>17</v>
       </c>
       <c r="N22">
-        <f>IF(PSE!O13&gt;0,PSE!O13,"")</f>
+        <f>PSE!O13</f>
         <v>17</v>
       </c>
       <c r="O22">
-        <f>IF(PSE!P13&gt;0,PSE!P13,"")</f>
+        <f>PSE!P13</f>
         <v>17</v>
       </c>
       <c r="P22">
-        <f>IF(PSE!Q13&gt;0,PSE!Q13,"")</f>
+        <f>PSE!Q13</f>
         <v>17</v>
       </c>
     </row>
@@ -12865,63 +12865,63 @@
         <v>Staff AVG</v>
       </c>
       <c r="B23">
-        <f>IF(PSE!C14&gt;0,PSE!C14,"")</f>
+        <f>PSE!C14</f>
         <v>17</v>
       </c>
       <c r="C23">
-        <f>IF(PSE!D14&gt;0,PSE!D14,"")</f>
+        <f>PSE!D14</f>
         <v>17</v>
       </c>
       <c r="D23">
-        <f>IF(PSE!E14&gt;0,PSE!E14,"")</f>
+        <f>PSE!E14</f>
         <v>17</v>
       </c>
       <c r="E23">
-        <f>IF(PSE!F14&gt;0,PSE!F14,"")</f>
+        <f>PSE!F14</f>
         <v>17</v>
       </c>
       <c r="F23">
-        <f>IF(PSE!G14&gt;0,PSE!G14,"")</f>
+        <f>PSE!G14</f>
         <v>17</v>
       </c>
       <c r="G23">
-        <f>IF(PSE!H14&gt;0,PSE!H14,"")</f>
+        <f>PSE!H14</f>
         <v>17</v>
       </c>
       <c r="H23">
-        <f>IF(PSE!I14&gt;0,PSE!I14,"")</f>
+        <f>PSE!I14</f>
         <v>17</v>
       </c>
       <c r="I23">
-        <f>IF(PSE!J14&gt;0,PSE!J14,"")</f>
+        <f>PSE!J14</f>
         <v>17</v>
       </c>
       <c r="J23">
-        <f>IF(PSE!K14&gt;0,PSE!K14,"")</f>
+        <f>PSE!K14</f>
         <v>17</v>
       </c>
       <c r="K23">
-        <f>IF(PSE!L14&gt;0,PSE!L14,"")</f>
+        <f>PSE!L14</f>
         <v>17</v>
       </c>
       <c r="L23">
-        <f>IF(PSE!M14&gt;0,PSE!M14,"")</f>
+        <f>PSE!M14</f>
         <v>17</v>
       </c>
       <c r="M23">
-        <f>IF(PSE!N14&gt;0,PSE!N14,"")</f>
+        <f>PSE!N14</f>
         <v>17</v>
       </c>
       <c r="N23">
-        <f>IF(PSE!O14&gt;0,PSE!O14,"")</f>
+        <f>PSE!O14</f>
         <v>17</v>
       </c>
       <c r="O23">
-        <f>IF(PSE!P14&gt;0,PSE!P14,"")</f>
+        <f>PSE!P14</f>
         <v>17</v>
       </c>
       <c r="P23">
-        <f>IF(PSE!Q14&gt;0,PSE!Q14,"")</f>
+        <f>PSE!Q14</f>
         <v>17</v>
       </c>
     </row>
@@ -12931,63 +12931,63 @@
         <v>Plan</v>
       </c>
       <c r="B24">
-        <f>IF(PSE!C15&gt;0,PSE!C15,"")</f>
+        <f>PSE!C15</f>
         <v>16</v>
       </c>
       <c r="C24">
-        <f>IF(PSE!D15&gt;0,PSE!D15,"")</f>
+        <f>PSE!D15</f>
         <v>16</v>
       </c>
       <c r="D24">
-        <f>IF(PSE!E15&gt;0,PSE!E15,"")</f>
+        <f>PSE!E15</f>
         <v>18</v>
       </c>
       <c r="E24">
-        <f>IF(PSE!F15&gt;0,PSE!F15,"")</f>
+        <f>PSE!F15</f>
         <v>17</v>
       </c>
       <c r="F24">
-        <f>IF(PSE!G15&gt;0,PSE!G15,"")</f>
+        <f>PSE!G15</f>
         <v>17</v>
       </c>
       <c r="G24">
-        <f>IF(PSE!H15&gt;0,PSE!H15,"")</f>
+        <f>PSE!H15</f>
         <v>16</v>
       </c>
       <c r="H24">
-        <f>IF(PSE!I15&gt;0,PSE!I15,"")</f>
+        <f>PSE!I15</f>
         <v>16</v>
       </c>
       <c r="I24">
-        <f>IF(PSE!J15&gt;0,PSE!J15,"")</f>
+        <f>PSE!J15</f>
         <v>16</v>
       </c>
       <c r="J24">
-        <f>IF(PSE!K15&gt;0,PSE!K15,"")</f>
+        <f>PSE!K15</f>
         <v>16</v>
       </c>
       <c r="K24">
-        <f>IF(PSE!L15&gt;0,PSE!L15,"")</f>
+        <f>PSE!L15</f>
         <v>15</v>
       </c>
       <c r="L24">
-        <f>IF(PSE!M15&gt;0,PSE!M15,"")</f>
+        <f>PSE!M15</f>
         <v>15</v>
       </c>
       <c r="M24">
-        <f>IF(PSE!N15&gt;0,PSE!N15,"")</f>
+        <f>PSE!N15</f>
         <v>15</v>
       </c>
       <c r="N24">
-        <f>IF(PSE!O15&gt;0,PSE!O15,"")</f>
+        <f>PSE!O15</f>
         <v>13</v>
       </c>
       <c r="O24">
-        <f>IF(PSE!P15&gt;0,PSE!P15,"")</f>
+        <f>PSE!P15</f>
         <v>13</v>
       </c>
       <c r="P24">
-        <f>IF(PSE!Q15&gt;0,PSE!Q15,"")</f>
+        <f>PSE!Q15</f>
         <v>13</v>
       </c>
     </row>
@@ -13058,64 +13058,64 @@
         <f>IF(PSE!B2&gt;0,PSE!B2,"")</f>
         <v>Staff</v>
       </c>
-      <c r="B32" t="str">
-        <f>IF(PSE!C17&gt;0,PSE!C17,"")</f>
-        <v/>
-      </c>
-      <c r="C32" t="str">
-        <f>IF(PSE!D17&gt;0,PSE!D17,"")</f>
-        <v/>
+      <c r="B32">
+        <f>PSE!C17</f>
+        <v>0</v>
+      </c>
+      <c r="C32">
+        <f>PSE!D17</f>
+        <v>0</v>
       </c>
       <c r="D32">
-        <f>IF(PSE!E17&gt;0,PSE!E17,"")</f>
+        <f>PSE!E17</f>
         <v>1</v>
       </c>
       <c r="E32">
-        <f>IF(PSE!F17&gt;0,PSE!F17,"")</f>
+        <f>PSE!F17</f>
         <v>3</v>
       </c>
       <c r="F32">
-        <f>IF(PSE!G17&gt;0,PSE!G17,"")</f>
+        <f>PSE!G17</f>
         <v>3</v>
       </c>
       <c r="G32">
-        <f>IF(PSE!H17&gt;0,PSE!H17,"")</f>
+        <f>PSE!H17</f>
         <v>3</v>
       </c>
       <c r="H32">
-        <f>IF(PSE!I17&gt;0,PSE!I17,"")</f>
+        <f>PSE!I17</f>
         <v>3</v>
       </c>
       <c r="I32">
-        <f>IF(PSE!J17&gt;0,PSE!J17,"")</f>
+        <f>PSE!J17</f>
         <v>3</v>
       </c>
       <c r="J32">
-        <f>IF(PSE!K17&gt;0,PSE!K17,"")</f>
+        <f>PSE!K17</f>
         <v>3</v>
       </c>
       <c r="K32">
-        <f>IF(PSE!L17&gt;0,PSE!L17,"")</f>
+        <f>PSE!L17</f>
         <v>3</v>
       </c>
       <c r="L32">
-        <f>IF(PSE!M17&gt;0,PSE!M17,"")</f>
+        <f>PSE!M17</f>
         <v>3</v>
       </c>
       <c r="M32">
-        <f>IF(PSE!N17&gt;0,PSE!N17,"")</f>
+        <f>PSE!N17</f>
         <v>3</v>
       </c>
       <c r="N32">
-        <f>IF(PSE!O17&gt;0,PSE!O17,"")</f>
+        <f>PSE!O17</f>
         <v>3</v>
       </c>
       <c r="O32">
-        <f>IF(PSE!P17&gt;0,PSE!P17,"")</f>
+        <f>PSE!P17</f>
         <v>3</v>
       </c>
       <c r="P32">
-        <f>IF(PSE!Q17&gt;0,PSE!Q17,"")</f>
+        <f>PSE!Q17</f>
         <v>3</v>
       </c>
     </row>
@@ -13125,63 +13125,63 @@
         <v>Staff AVG</v>
       </c>
       <c r="B33">
-        <f>IF(PSE!C18&gt;0,PSE!C18,"")</f>
+        <f>PSE!C18</f>
         <v>2</v>
       </c>
       <c r="C33">
-        <f>IF(PSE!D18&gt;0,PSE!D18,"")</f>
+        <f>PSE!D18</f>
         <v>2</v>
       </c>
       <c r="D33">
-        <f>IF(PSE!E18&gt;0,PSE!E18,"")</f>
+        <f>PSE!E18</f>
         <v>2</v>
       </c>
       <c r="E33">
-        <f>IF(PSE!F18&gt;0,PSE!F18,"")</f>
+        <f>PSE!F18</f>
         <v>2</v>
       </c>
       <c r="F33">
-        <f>IF(PSE!G18&gt;0,PSE!G18,"")</f>
+        <f>PSE!G18</f>
         <v>2</v>
       </c>
       <c r="G33">
-        <f>IF(PSE!H18&gt;0,PSE!H18,"")</f>
+        <f>PSE!H18</f>
         <v>2</v>
       </c>
       <c r="H33">
-        <f>IF(PSE!I18&gt;0,PSE!I18,"")</f>
+        <f>PSE!I18</f>
         <v>2</v>
       </c>
       <c r="I33">
-        <f>IF(PSE!J18&gt;0,PSE!J18,"")</f>
+        <f>PSE!J18</f>
         <v>2</v>
       </c>
       <c r="J33">
-        <f>IF(PSE!K18&gt;0,PSE!K18,"")</f>
+        <f>PSE!K18</f>
         <v>2</v>
       </c>
       <c r="K33">
-        <f>IF(PSE!L18&gt;0,PSE!L18,"")</f>
+        <f>PSE!L18</f>
         <v>2</v>
       </c>
       <c r="L33">
-        <f>IF(PSE!M18&gt;0,PSE!M18,"")</f>
+        <f>PSE!M18</f>
         <v>2</v>
       </c>
       <c r="M33">
-        <f>IF(PSE!N18&gt;0,PSE!N18,"")</f>
+        <f>PSE!N18</f>
         <v>2</v>
       </c>
       <c r="N33">
-        <f>IF(PSE!O18&gt;0,PSE!O18,"")</f>
+        <f>PSE!O18</f>
         <v>2</v>
       </c>
       <c r="O33">
-        <f>IF(PSE!P18&gt;0,PSE!P18,"")</f>
+        <f>PSE!P18</f>
         <v>2</v>
       </c>
       <c r="P33">
-        <f>IF(PSE!Q18&gt;0,PSE!Q18,"")</f>
+        <f>PSE!Q18</f>
         <v>2</v>
       </c>
     </row>
@@ -13190,65 +13190,65 @@
         <f>IF(PSE!B4&gt;0,PSE!B4,"")</f>
         <v>Plan</v>
       </c>
-      <c r="B34" t="str">
-        <f>IF(PSE!C19&gt;0,PSE!C19,"")</f>
-        <v/>
-      </c>
-      <c r="C34" t="str">
-        <f>IF(PSE!D19&gt;0,PSE!D19,"")</f>
-        <v/>
-      </c>
-      <c r="D34" t="str">
-        <f>IF(PSE!E19&gt;0,PSE!E19,"")</f>
-        <v/>
+      <c r="B34">
+        <f>PSE!C19</f>
+        <v>0</v>
+      </c>
+      <c r="C34">
+        <f>PSE!D19</f>
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <f>PSE!E19</f>
+        <v>0</v>
       </c>
       <c r="E34">
-        <f>IF(PSE!F19&gt;0,PSE!F19,"")</f>
+        <f>PSE!F19</f>
         <v>1</v>
       </c>
       <c r="F34">
-        <f>IF(PSE!G19&gt;0,PSE!G19,"")</f>
+        <f>PSE!G19</f>
         <v>3</v>
       </c>
       <c r="G34">
-        <f>IF(PSE!H19&gt;0,PSE!H19,"")</f>
+        <f>PSE!H19</f>
         <v>3</v>
       </c>
       <c r="H34">
-        <f>IF(PSE!I19&gt;0,PSE!I19,"")</f>
+        <f>PSE!I19</f>
         <v>3</v>
       </c>
       <c r="I34">
-        <f>IF(PSE!J19&gt;0,PSE!J19,"")</f>
+        <f>PSE!J19</f>
         <v>3</v>
       </c>
       <c r="J34">
-        <f>IF(PSE!K19&gt;0,PSE!K19,"")</f>
+        <f>PSE!K19</f>
         <v>3</v>
       </c>
       <c r="K34">
-        <f>IF(PSE!L19&gt;0,PSE!L19,"")</f>
+        <f>PSE!L19</f>
         <v>2</v>
       </c>
       <c r="L34">
-        <f>IF(PSE!M19&gt;0,PSE!M19,"")</f>
+        <f>PSE!M19</f>
         <v>2</v>
       </c>
       <c r="M34">
-        <f>IF(PSE!N19&gt;0,PSE!N19,"")</f>
-        <v>2</v>
-      </c>
-      <c r="N34" t="str">
-        <f>IF(PSE!O19&gt;0,PSE!O19,"")</f>
-        <v/>
-      </c>
-      <c r="O34" t="str">
-        <f>IF(PSE!P19&gt;0,PSE!P19,"")</f>
-        <v/>
-      </c>
-      <c r="P34" t="str">
-        <f>IF(PSE!Q19&gt;0,PSE!Q19,"")</f>
-        <v/>
+        <f>PSE!N19</f>
+        <v>2</v>
+      </c>
+      <c r="N34">
+        <f>PSE!O19</f>
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <f>PSE!P19</f>
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <f>PSE!Q19</f>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.2">

--- a/workforceresult.xlsx
+++ b/workforceresult.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miiintra/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C20E1BE-35C6-EE41-8510-9A2491E74160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBCFA21D-FA6E-1D4A-A696-6A097918C605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14500" yWindow="620" windowWidth="28800" windowHeight="21200" activeTab="1" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
+    <workbookView xWindow="14500" yWindow="620" windowWidth="28800" windowHeight="21200" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
   </bookViews>
   <sheets>
     <sheet name="ALL" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,8 @@
     <sheet name="GraphSD" sheetId="8" r:id="rId8"/>
     <sheet name="AIC" sheetId="9" r:id="rId9"/>
     <sheet name="GraphAIC" sheetId="10" r:id="rId10"/>
+    <sheet name="TDE" sheetId="11" r:id="rId11"/>
+    <sheet name="GraphTDE" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="91">
   <si>
     <t>Type</t>
   </si>
@@ -406,12 +408,106 @@
   <si>
     <t>Product Innovation</t>
   </si>
+  <si>
+    <t>TDE</t>
+  </si>
+  <si>
+    <t>Talent &amp; Digital Enablement</t>
+  </si>
+  <si>
+    <t>Financial Management</t>
+  </si>
+  <si>
+    <t>Resource Management</t>
+  </si>
+  <si>
+    <r>
+      <t>Resource Management:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF7B7B7B"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>TH</t>
+    </r>
+  </si>
+  <si>
+    <t>Resource Management:TH</t>
+  </si>
+  <si>
+    <r>
+      <t>Resource Management:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF7B7B7B"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>CT</t>
+    </r>
+  </si>
+  <si>
+    <t>Resource Management:CT</t>
+  </si>
+  <si>
+    <t>Talent Experience &amp; Development</t>
+  </si>
+  <si>
+    <r>
+      <t>Talent Experience &amp; Development:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF7B7B7B"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>TH</t>
+    </r>
+  </si>
+  <si>
+    <t>Talent Experience &amp; Development:TH</t>
+  </si>
+  <si>
+    <r>
+      <t>Talent Experience &amp; Development:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF7B7B7B"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>CT</t>
+    </r>
+  </si>
+  <si>
+    <t>Talent Experience &amp; Development:CT</t>
+  </si>
+  <si>
+    <t>Center of Excellences</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -504,6 +600,12 @@
       <i/>
       <sz val="11"/>
       <color rgb="FFEDEDED"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF7B7B7B"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -630,7 +732,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -708,6 +810,8 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2480,51 +2584,51 @@
       </c>
       <c r="E3">
         <f>IF(AIC!F3&gt;0,AIC!F3,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3">
         <f>IF(AIC!G3&gt;0,AIC!G3,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3">
         <f>IF(AIC!H3&gt;0,AIC!H3,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H3">
         <f>IF(AIC!I3&gt;0,AIC!I3,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I3">
         <f>IF(AIC!J3&gt;0,AIC!J3,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J3">
         <f>IF(AIC!K3&gt;0,AIC!K3,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K3">
         <f>IF(AIC!L3&gt;0,AIC!L3,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L3">
         <f>IF(AIC!M3&gt;0,AIC!M3,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M3">
         <f>IF(AIC!N3&gt;0,AIC!N3,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N3">
         <f>IF(AIC!O3&gt;0,AIC!O3,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O3">
         <f>IF(AIC!P3&gt;0,AIC!P3,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P3">
         <f>IF(AIC!Q3&gt;0,AIC!Q3,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
@@ -4737,6 +4841,4798 @@
       <c r="P93">
         <f>AIC!Q73</f>
         <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4503C198-0F99-6748-AF46-FB3CC9A0A00A}">
+  <sheetPr>
+    <tabColor theme="3"/>
+  </sheetPr>
+  <dimension ref="A1:Q81"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1" s="17"/>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A2" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="8">
+        <v>15</v>
+      </c>
+      <c r="D2" s="8">
+        <v>15</v>
+      </c>
+      <c r="E2" s="8">
+        <v>15</v>
+      </c>
+      <c r="F2" s="8">
+        <v>16</v>
+      </c>
+      <c r="G2" s="8">
+        <v>16</v>
+      </c>
+      <c r="H2" s="8">
+        <v>16</v>
+      </c>
+      <c r="I2" s="8">
+        <v>16</v>
+      </c>
+      <c r="J2" s="8">
+        <v>16</v>
+      </c>
+      <c r="K2" s="8">
+        <v>16</v>
+      </c>
+      <c r="L2" s="8">
+        <v>16</v>
+      </c>
+      <c r="M2" s="8">
+        <v>16</v>
+      </c>
+      <c r="N2" s="8">
+        <v>16</v>
+      </c>
+      <c r="O2" s="8">
+        <v>16</v>
+      </c>
+      <c r="P2" s="8">
+        <v>16</v>
+      </c>
+      <c r="Q2" s="8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A3" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="8">
+        <v>16</v>
+      </c>
+      <c r="D3" s="8">
+        <v>16</v>
+      </c>
+      <c r="E3" s="8">
+        <v>16</v>
+      </c>
+      <c r="F3" s="8">
+        <v>16</v>
+      </c>
+      <c r="G3" s="8">
+        <v>16</v>
+      </c>
+      <c r="H3" s="8">
+        <v>16</v>
+      </c>
+      <c r="I3" s="8">
+        <v>16</v>
+      </c>
+      <c r="J3" s="8">
+        <v>16</v>
+      </c>
+      <c r="K3" s="8">
+        <v>16</v>
+      </c>
+      <c r="L3" s="8">
+        <v>16</v>
+      </c>
+      <c r="M3" s="8">
+        <v>16</v>
+      </c>
+      <c r="N3" s="8">
+        <v>16</v>
+      </c>
+      <c r="O3" s="8">
+        <v>16</v>
+      </c>
+      <c r="P3" s="8">
+        <v>16</v>
+      </c>
+      <c r="Q3" s="8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A4" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="8">
+        <v>15</v>
+      </c>
+      <c r="D4" s="8">
+        <v>15</v>
+      </c>
+      <c r="E4" s="8">
+        <v>15</v>
+      </c>
+      <c r="F4" s="8">
+        <v>16</v>
+      </c>
+      <c r="G4" s="8">
+        <v>16</v>
+      </c>
+      <c r="H4" s="8">
+        <v>16</v>
+      </c>
+      <c r="I4" s="8">
+        <v>16</v>
+      </c>
+      <c r="J4" s="8">
+        <v>16</v>
+      </c>
+      <c r="K4" s="8">
+        <v>16</v>
+      </c>
+      <c r="L4" s="8">
+        <v>16</v>
+      </c>
+      <c r="M4" s="8">
+        <v>16</v>
+      </c>
+      <c r="N4" s="8">
+        <v>16</v>
+      </c>
+      <c r="O4" s="8">
+        <v>16</v>
+      </c>
+      <c r="P4" s="8">
+        <v>16</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A5" s="17"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
+      <c r="Q5" s="8"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A6" s="8"/>
+      <c r="B6" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="19">
+        <v>1</v>
+      </c>
+      <c r="D6" s="19">
+        <v>1</v>
+      </c>
+      <c r="E6" s="19">
+        <v>1</v>
+      </c>
+      <c r="F6" s="19">
+        <v>1</v>
+      </c>
+      <c r="G6" s="19">
+        <v>1</v>
+      </c>
+      <c r="H6" s="19">
+        <v>1</v>
+      </c>
+      <c r="I6" s="19">
+        <v>1</v>
+      </c>
+      <c r="J6" s="19">
+        <v>1</v>
+      </c>
+      <c r="K6" s="19">
+        <v>1</v>
+      </c>
+      <c r="L6" s="19">
+        <v>1</v>
+      </c>
+      <c r="M6" s="19">
+        <v>1</v>
+      </c>
+      <c r="N6" s="19">
+        <v>1</v>
+      </c>
+      <c r="O6" s="19">
+        <v>1</v>
+      </c>
+      <c r="P6" s="19">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A7" s="17"/>
+      <c r="B7" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="20">
+        <v>0</v>
+      </c>
+      <c r="D7" s="20">
+        <v>0</v>
+      </c>
+      <c r="E7" s="20">
+        <v>0</v>
+      </c>
+      <c r="F7" s="20">
+        <v>0</v>
+      </c>
+      <c r="G7" s="20">
+        <v>0</v>
+      </c>
+      <c r="H7" s="20">
+        <v>0</v>
+      </c>
+      <c r="I7" s="20">
+        <v>0</v>
+      </c>
+      <c r="J7" s="20">
+        <v>0</v>
+      </c>
+      <c r="K7" s="20">
+        <v>0</v>
+      </c>
+      <c r="L7" s="20">
+        <v>0</v>
+      </c>
+      <c r="M7" s="20">
+        <v>0</v>
+      </c>
+      <c r="N7" s="20">
+        <v>0</v>
+      </c>
+      <c r="O7" s="20">
+        <v>0</v>
+      </c>
+      <c r="P7" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A8" s="17"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A9" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="8">
+        <v>13</v>
+      </c>
+      <c r="D9" s="8">
+        <v>13</v>
+      </c>
+      <c r="E9" s="8">
+        <v>13</v>
+      </c>
+      <c r="F9" s="8">
+        <v>14</v>
+      </c>
+      <c r="G9" s="8">
+        <v>14</v>
+      </c>
+      <c r="H9" s="8">
+        <v>14</v>
+      </c>
+      <c r="I9" s="8">
+        <v>14</v>
+      </c>
+      <c r="J9" s="8">
+        <v>14</v>
+      </c>
+      <c r="K9" s="8">
+        <v>14</v>
+      </c>
+      <c r="L9" s="8">
+        <v>14</v>
+      </c>
+      <c r="M9" s="8">
+        <v>14</v>
+      </c>
+      <c r="N9" s="8">
+        <v>14</v>
+      </c>
+      <c r="O9" s="8">
+        <v>14</v>
+      </c>
+      <c r="P9" s="8">
+        <v>14</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A10" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="8">
+        <v>14</v>
+      </c>
+      <c r="D10" s="8">
+        <v>14</v>
+      </c>
+      <c r="E10" s="8">
+        <v>14</v>
+      </c>
+      <c r="F10" s="8">
+        <v>14</v>
+      </c>
+      <c r="G10" s="8">
+        <v>14</v>
+      </c>
+      <c r="H10" s="8">
+        <v>14</v>
+      </c>
+      <c r="I10" s="8">
+        <v>14</v>
+      </c>
+      <c r="J10" s="8">
+        <v>14</v>
+      </c>
+      <c r="K10" s="8">
+        <v>14</v>
+      </c>
+      <c r="L10" s="8">
+        <v>14</v>
+      </c>
+      <c r="M10" s="8">
+        <v>14</v>
+      </c>
+      <c r="N10" s="8">
+        <v>14</v>
+      </c>
+      <c r="O10" s="8">
+        <v>14</v>
+      </c>
+      <c r="P10" s="8">
+        <v>14</v>
+      </c>
+      <c r="Q10" s="8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A11" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="8">
+        <v>13</v>
+      </c>
+      <c r="D11" s="8">
+        <v>13</v>
+      </c>
+      <c r="E11" s="8">
+        <v>13</v>
+      </c>
+      <c r="F11" s="8">
+        <v>14</v>
+      </c>
+      <c r="G11" s="8">
+        <v>14</v>
+      </c>
+      <c r="H11" s="8">
+        <v>14</v>
+      </c>
+      <c r="I11" s="8">
+        <v>14</v>
+      </c>
+      <c r="J11" s="8">
+        <v>14</v>
+      </c>
+      <c r="K11" s="8">
+        <v>14</v>
+      </c>
+      <c r="L11" s="8">
+        <v>14</v>
+      </c>
+      <c r="M11" s="8">
+        <v>14</v>
+      </c>
+      <c r="N11" s="8">
+        <v>14</v>
+      </c>
+      <c r="O11" s="8">
+        <v>14</v>
+      </c>
+      <c r="P11" s="8">
+        <v>14</v>
+      </c>
+      <c r="Q11" s="8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A12" s="8"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
+      <c r="Q12" s="8"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A13" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="8">
+        <v>2</v>
+      </c>
+      <c r="D13" s="8">
+        <v>2</v>
+      </c>
+      <c r="E13" s="8">
+        <v>2</v>
+      </c>
+      <c r="F13" s="8">
+        <v>2</v>
+      </c>
+      <c r="G13" s="8">
+        <v>2</v>
+      </c>
+      <c r="H13" s="8">
+        <v>2</v>
+      </c>
+      <c r="I13" s="8">
+        <v>2</v>
+      </c>
+      <c r="J13" s="8">
+        <v>2</v>
+      </c>
+      <c r="K13" s="8">
+        <v>2</v>
+      </c>
+      <c r="L13" s="8">
+        <v>2</v>
+      </c>
+      <c r="M13" s="8">
+        <v>2</v>
+      </c>
+      <c r="N13" s="8">
+        <v>2</v>
+      </c>
+      <c r="O13" s="8">
+        <v>2</v>
+      </c>
+      <c r="P13" s="8">
+        <v>2</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A14" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="8">
+        <v>2</v>
+      </c>
+      <c r="D14" s="8">
+        <v>2</v>
+      </c>
+      <c r="E14" s="8">
+        <v>2</v>
+      </c>
+      <c r="F14" s="8">
+        <v>2</v>
+      </c>
+      <c r="G14" s="8">
+        <v>2</v>
+      </c>
+      <c r="H14" s="8">
+        <v>2</v>
+      </c>
+      <c r="I14" s="8">
+        <v>2</v>
+      </c>
+      <c r="J14" s="8">
+        <v>2</v>
+      </c>
+      <c r="K14" s="8">
+        <v>2</v>
+      </c>
+      <c r="L14" s="8">
+        <v>2</v>
+      </c>
+      <c r="M14" s="8">
+        <v>2</v>
+      </c>
+      <c r="N14" s="8">
+        <v>2</v>
+      </c>
+      <c r="O14" s="8">
+        <v>2</v>
+      </c>
+      <c r="P14" s="8">
+        <v>2</v>
+      </c>
+      <c r="Q14" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A15" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="8">
+        <v>2</v>
+      </c>
+      <c r="D15" s="8">
+        <v>2</v>
+      </c>
+      <c r="E15" s="8">
+        <v>2</v>
+      </c>
+      <c r="F15" s="8">
+        <v>2</v>
+      </c>
+      <c r="G15" s="8">
+        <v>2</v>
+      </c>
+      <c r="H15" s="8">
+        <v>2</v>
+      </c>
+      <c r="I15" s="8">
+        <v>2</v>
+      </c>
+      <c r="J15" s="8">
+        <v>2</v>
+      </c>
+      <c r="K15" s="8">
+        <v>2</v>
+      </c>
+      <c r="L15" s="8">
+        <v>2</v>
+      </c>
+      <c r="M15" s="8">
+        <v>2</v>
+      </c>
+      <c r="N15" s="8">
+        <v>2</v>
+      </c>
+      <c r="O15" s="8">
+        <v>2</v>
+      </c>
+      <c r="P15" s="8">
+        <v>2</v>
+      </c>
+      <c r="Q15" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A16" s="8"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="8"/>
+      <c r="Q16" s="8"/>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A17" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="8">
+        <v>0</v>
+      </c>
+      <c r="D17" s="8">
+        <v>0</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0</v>
+      </c>
+      <c r="F17" s="8">
+        <v>0</v>
+      </c>
+      <c r="G17" s="8">
+        <v>0</v>
+      </c>
+      <c r="H17" s="8">
+        <v>0</v>
+      </c>
+      <c r="I17" s="8">
+        <v>0</v>
+      </c>
+      <c r="J17" s="8">
+        <v>0</v>
+      </c>
+      <c r="K17" s="8">
+        <v>0</v>
+      </c>
+      <c r="L17" s="8">
+        <v>0</v>
+      </c>
+      <c r="M17" s="8">
+        <v>0</v>
+      </c>
+      <c r="N17" s="8">
+        <v>0</v>
+      </c>
+      <c r="O17" s="8">
+        <v>0</v>
+      </c>
+      <c r="P17" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A18" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="8">
+        <v>0</v>
+      </c>
+      <c r="D18" s="8">
+        <v>0</v>
+      </c>
+      <c r="E18" s="8">
+        <v>0</v>
+      </c>
+      <c r="F18" s="8">
+        <v>0</v>
+      </c>
+      <c r="G18" s="8">
+        <v>0</v>
+      </c>
+      <c r="H18" s="8">
+        <v>0</v>
+      </c>
+      <c r="I18" s="8">
+        <v>0</v>
+      </c>
+      <c r="J18" s="8">
+        <v>0</v>
+      </c>
+      <c r="K18" s="8">
+        <v>0</v>
+      </c>
+      <c r="L18" s="8">
+        <v>0</v>
+      </c>
+      <c r="M18" s="8">
+        <v>0</v>
+      </c>
+      <c r="N18" s="8">
+        <v>0</v>
+      </c>
+      <c r="O18" s="8">
+        <v>0</v>
+      </c>
+      <c r="P18" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A19" s="16">
+        <v>0</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="8">
+        <v>0</v>
+      </c>
+      <c r="D19" s="8">
+        <v>0</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0</v>
+      </c>
+      <c r="F19" s="8">
+        <v>0</v>
+      </c>
+      <c r="G19" s="8">
+        <v>0</v>
+      </c>
+      <c r="H19" s="8">
+        <v>0</v>
+      </c>
+      <c r="I19" s="8">
+        <v>0</v>
+      </c>
+      <c r="J19" s="8">
+        <v>0</v>
+      </c>
+      <c r="K19" s="8">
+        <v>0</v>
+      </c>
+      <c r="L19" s="8">
+        <v>0</v>
+      </c>
+      <c r="M19" s="8">
+        <v>0</v>
+      </c>
+      <c r="N19" s="8">
+        <v>0</v>
+      </c>
+      <c r="O19" s="8">
+        <v>0</v>
+      </c>
+      <c r="P19" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A31" s="17"/>
+      <c r="B31" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C31" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="D31" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="E31" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F31" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="G31" s="24" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A32" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" s="26">
+        <v>15</v>
+      </c>
+      <c r="D32" s="21">
+        <v>16</v>
+      </c>
+      <c r="E32" s="21">
+        <v>16</v>
+      </c>
+      <c r="F32" s="21">
+        <v>16</v>
+      </c>
+      <c r="G32" s="21">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="26">
+        <v>16</v>
+      </c>
+      <c r="D33" s="21">
+        <v>16</v>
+      </c>
+      <c r="E33" s="21">
+        <v>16</v>
+      </c>
+      <c r="F33" s="21">
+        <v>16</v>
+      </c>
+      <c r="G33" s="21">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="26">
+        <v>15</v>
+      </c>
+      <c r="D34" s="21">
+        <v>16</v>
+      </c>
+      <c r="E34" s="21">
+        <v>16</v>
+      </c>
+      <c r="F34" s="21">
+        <v>16</v>
+      </c>
+      <c r="G34" s="21">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="17"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="27">
+        <v>0</v>
+      </c>
+      <c r="D35" s="28">
+        <v>0</v>
+      </c>
+      <c r="E35" s="28">
+        <v>0</v>
+      </c>
+      <c r="F35" s="28">
+        <v>0</v>
+      </c>
+      <c r="G35" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="8"/>
+      <c r="B36" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C36" s="29">
+        <v>1</v>
+      </c>
+      <c r="D36" s="19">
+        <v>1</v>
+      </c>
+      <c r="E36" s="19">
+        <v>1</v>
+      </c>
+      <c r="F36" s="19">
+        <v>1</v>
+      </c>
+      <c r="G36" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="17"/>
+      <c r="B37" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" s="30">
+        <v>0</v>
+      </c>
+      <c r="D37" s="20">
+        <v>0</v>
+      </c>
+      <c r="E37" s="20">
+        <v>0</v>
+      </c>
+      <c r="F37" s="20">
+        <v>0</v>
+      </c>
+      <c r="G37" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="17"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="31"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C39" s="26">
+        <v>13</v>
+      </c>
+      <c r="D39" s="21">
+        <v>14</v>
+      </c>
+      <c r="E39" s="21">
+        <v>14</v>
+      </c>
+      <c r="F39" s="21">
+        <v>14</v>
+      </c>
+      <c r="G39" s="21">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A40" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C40" s="26">
+        <v>14</v>
+      </c>
+      <c r="D40" s="21">
+        <v>14</v>
+      </c>
+      <c r="E40" s="21">
+        <v>14</v>
+      </c>
+      <c r="F40" s="21">
+        <v>14</v>
+      </c>
+      <c r="G40" s="21">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A41" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B41" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C41" s="26">
+        <v>13</v>
+      </c>
+      <c r="D41" s="21">
+        <v>14</v>
+      </c>
+      <c r="E41" s="21">
+        <v>14</v>
+      </c>
+      <c r="F41" s="21">
+        <v>14</v>
+      </c>
+      <c r="G41" s="21">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A42" s="8"/>
+      <c r="B42" s="17"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="21"/>
+      <c r="G42" s="21"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A43" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C43" s="26">
+        <v>2</v>
+      </c>
+      <c r="D43" s="21">
+        <v>2</v>
+      </c>
+      <c r="E43" s="21">
+        <v>2</v>
+      </c>
+      <c r="F43" s="21">
+        <v>2</v>
+      </c>
+      <c r="G43" s="21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A44" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" s="26">
+        <v>2</v>
+      </c>
+      <c r="D44" s="21">
+        <v>2</v>
+      </c>
+      <c r="E44" s="21">
+        <v>2</v>
+      </c>
+      <c r="F44" s="21">
+        <v>2</v>
+      </c>
+      <c r="G44" s="21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A45" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B45" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C45" s="26">
+        <v>2</v>
+      </c>
+      <c r="D45" s="21">
+        <v>2</v>
+      </c>
+      <c r="E45" s="21">
+        <v>2</v>
+      </c>
+      <c r="F45" s="21">
+        <v>2</v>
+      </c>
+      <c r="G45" s="21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A46" s="8"/>
+      <c r="B46" s="17"/>
+      <c r="C46" s="26"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="21"/>
+      <c r="F46" s="21"/>
+      <c r="G46" s="21"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A47" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C47" s="26">
+        <v>0</v>
+      </c>
+      <c r="D47" s="21">
+        <v>0</v>
+      </c>
+      <c r="E47" s="21">
+        <v>0</v>
+      </c>
+      <c r="F47" s="21">
+        <v>0</v>
+      </c>
+      <c r="G47" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A48" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C48" s="26">
+        <v>0</v>
+      </c>
+      <c r="D48" s="21">
+        <v>0</v>
+      </c>
+      <c r="E48" s="21">
+        <v>0</v>
+      </c>
+      <c r="F48" s="21">
+        <v>0</v>
+      </c>
+      <c r="G48" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A49" s="16">
+        <v>0</v>
+      </c>
+      <c r="B49" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C49" s="26">
+        <v>0</v>
+      </c>
+      <c r="D49" s="21">
+        <v>0</v>
+      </c>
+      <c r="E49" s="21">
+        <v>0</v>
+      </c>
+      <c r="F49" s="21">
+        <v>0</v>
+      </c>
+      <c r="G49" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A61" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="B61" s="34"/>
+      <c r="C61" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="D61" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="E61" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I61" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J61" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="K61" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="L61" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="M61" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="N61" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O61" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="P61" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q61" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A62" s="12"/>
+      <c r="B62" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" s="12">
+        <v>15</v>
+      </c>
+      <c r="D62" s="12">
+        <v>15</v>
+      </c>
+      <c r="E62" s="12">
+        <v>15</v>
+      </c>
+      <c r="F62" s="12">
+        <v>16</v>
+      </c>
+      <c r="G62" s="12">
+        <v>16</v>
+      </c>
+      <c r="H62" s="12">
+        <v>16</v>
+      </c>
+      <c r="I62" s="12">
+        <v>16</v>
+      </c>
+      <c r="J62" s="12">
+        <v>16</v>
+      </c>
+      <c r="K62" s="12">
+        <v>16</v>
+      </c>
+      <c r="L62" s="12">
+        <v>16</v>
+      </c>
+      <c r="M62" s="12">
+        <v>16</v>
+      </c>
+      <c r="N62" s="12">
+        <v>16</v>
+      </c>
+      <c r="O62" s="12">
+        <v>16</v>
+      </c>
+      <c r="P62" s="12">
+        <v>16</v>
+      </c>
+      <c r="Q62" s="12">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A63" s="36"/>
+      <c r="B63" s="47" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" s="48">
+        <v>15</v>
+      </c>
+      <c r="D63" s="48">
+        <v>15</v>
+      </c>
+      <c r="E63" s="48">
+        <v>15</v>
+      </c>
+      <c r="F63" s="48">
+        <v>16</v>
+      </c>
+      <c r="G63" s="48">
+        <v>16</v>
+      </c>
+      <c r="H63" s="48">
+        <v>16</v>
+      </c>
+      <c r="I63" s="48">
+        <v>16</v>
+      </c>
+      <c r="J63" s="48">
+        <v>16</v>
+      </c>
+      <c r="K63" s="48">
+        <v>16</v>
+      </c>
+      <c r="L63" s="48">
+        <v>16</v>
+      </c>
+      <c r="M63" s="48">
+        <v>16</v>
+      </c>
+      <c r="N63" s="48">
+        <v>16</v>
+      </c>
+      <c r="O63" s="48">
+        <v>16</v>
+      </c>
+      <c r="P63" s="48">
+        <v>16</v>
+      </c>
+      <c r="Q63" s="48">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A64" s="49" t="s">
+        <v>78</v>
+      </c>
+      <c r="B64" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" s="49">
+        <v>1</v>
+      </c>
+      <c r="D64" s="49">
+        <v>1</v>
+      </c>
+      <c r="E64" s="49">
+        <v>1</v>
+      </c>
+      <c r="F64" s="49">
+        <v>1</v>
+      </c>
+      <c r="G64" s="49">
+        <v>1</v>
+      </c>
+      <c r="H64" s="49">
+        <v>1</v>
+      </c>
+      <c r="I64" s="49">
+        <v>1</v>
+      </c>
+      <c r="J64" s="49">
+        <v>1</v>
+      </c>
+      <c r="K64" s="49">
+        <v>1</v>
+      </c>
+      <c r="L64" s="49">
+        <v>1</v>
+      </c>
+      <c r="M64" s="49">
+        <v>1</v>
+      </c>
+      <c r="N64" s="49">
+        <v>1</v>
+      </c>
+      <c r="O64" s="49">
+        <v>1</v>
+      </c>
+      <c r="P64" s="49">
+        <v>1</v>
+      </c>
+      <c r="Q64" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A65" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="B65" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C65" s="8">
+        <v>1</v>
+      </c>
+      <c r="D65" s="8">
+        <v>1</v>
+      </c>
+      <c r="E65" s="8">
+        <v>1</v>
+      </c>
+      <c r="F65" s="8">
+        <v>1</v>
+      </c>
+      <c r="G65" s="8">
+        <v>1</v>
+      </c>
+      <c r="H65" s="8">
+        <v>1</v>
+      </c>
+      <c r="I65" s="8">
+        <v>1</v>
+      </c>
+      <c r="J65" s="8">
+        <v>1</v>
+      </c>
+      <c r="K65" s="8">
+        <v>1</v>
+      </c>
+      <c r="L65" s="8">
+        <v>1</v>
+      </c>
+      <c r="M65" s="8">
+        <v>1</v>
+      </c>
+      <c r="N65" s="8">
+        <v>1</v>
+      </c>
+      <c r="O65" s="8">
+        <v>1</v>
+      </c>
+      <c r="P65" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q65" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A66" s="49" t="s">
+        <v>79</v>
+      </c>
+      <c r="B66" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" s="49">
+        <v>4</v>
+      </c>
+      <c r="D66" s="49">
+        <v>4</v>
+      </c>
+      <c r="E66" s="49">
+        <v>4</v>
+      </c>
+      <c r="F66" s="49">
+        <v>4</v>
+      </c>
+      <c r="G66" s="49">
+        <v>4</v>
+      </c>
+      <c r="H66" s="49">
+        <v>4</v>
+      </c>
+      <c r="I66" s="49">
+        <v>4</v>
+      </c>
+      <c r="J66" s="49">
+        <v>4</v>
+      </c>
+      <c r="K66" s="49">
+        <v>4</v>
+      </c>
+      <c r="L66" s="49">
+        <v>4</v>
+      </c>
+      <c r="M66" s="49">
+        <v>4</v>
+      </c>
+      <c r="N66" s="49">
+        <v>4</v>
+      </c>
+      <c r="O66" s="49">
+        <v>4</v>
+      </c>
+      <c r="P66" s="49">
+        <v>4</v>
+      </c>
+      <c r="Q66" s="49">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A67" s="39" t="s">
+        <v>79</v>
+      </c>
+      <c r="B67" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C67" s="8">
+        <v>4</v>
+      </c>
+      <c r="D67" s="8">
+        <v>4</v>
+      </c>
+      <c r="E67" s="8">
+        <v>4</v>
+      </c>
+      <c r="F67" s="8">
+        <v>4</v>
+      </c>
+      <c r="G67" s="8">
+        <v>4</v>
+      </c>
+      <c r="H67" s="8">
+        <v>4</v>
+      </c>
+      <c r="I67" s="8">
+        <v>4</v>
+      </c>
+      <c r="J67" s="8">
+        <v>4</v>
+      </c>
+      <c r="K67" s="8">
+        <v>4</v>
+      </c>
+      <c r="L67" s="8">
+        <v>4</v>
+      </c>
+      <c r="M67" s="8">
+        <v>4</v>
+      </c>
+      <c r="N67" s="8">
+        <v>4</v>
+      </c>
+      <c r="O67" s="8">
+        <v>4</v>
+      </c>
+      <c r="P67" s="8">
+        <v>4</v>
+      </c>
+      <c r="Q67" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A68" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B68" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" s="49">
+        <v>5</v>
+      </c>
+      <c r="D68" s="49">
+        <v>5</v>
+      </c>
+      <c r="E68" s="49">
+        <v>5</v>
+      </c>
+      <c r="F68" s="49">
+        <v>5</v>
+      </c>
+      <c r="G68" s="49">
+        <v>5</v>
+      </c>
+      <c r="H68" s="49">
+        <v>5</v>
+      </c>
+      <c r="I68" s="49">
+        <v>5</v>
+      </c>
+      <c r="J68" s="49">
+        <v>5</v>
+      </c>
+      <c r="K68" s="49">
+        <v>5</v>
+      </c>
+      <c r="L68" s="49">
+        <v>5</v>
+      </c>
+      <c r="M68" s="49">
+        <v>5</v>
+      </c>
+      <c r="N68" s="49">
+        <v>5</v>
+      </c>
+      <c r="O68" s="49">
+        <v>5</v>
+      </c>
+      <c r="P68" s="49">
+        <v>5</v>
+      </c>
+      <c r="Q68" s="49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A69" s="39" t="s">
+        <v>80</v>
+      </c>
+      <c r="B69" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C69" s="8">
+        <v>5</v>
+      </c>
+      <c r="D69" s="8">
+        <v>5</v>
+      </c>
+      <c r="E69" s="8">
+        <v>5</v>
+      </c>
+      <c r="F69" s="8">
+        <v>5</v>
+      </c>
+      <c r="G69" s="8">
+        <v>5</v>
+      </c>
+      <c r="H69" s="8">
+        <v>5</v>
+      </c>
+      <c r="I69" s="8">
+        <v>5</v>
+      </c>
+      <c r="J69" s="8">
+        <v>5</v>
+      </c>
+      <c r="K69" s="8">
+        <v>5</v>
+      </c>
+      <c r="L69" s="8">
+        <v>5</v>
+      </c>
+      <c r="M69" s="8">
+        <v>5</v>
+      </c>
+      <c r="N69" s="8">
+        <v>5</v>
+      </c>
+      <c r="O69" s="8">
+        <v>5</v>
+      </c>
+      <c r="P69" s="8">
+        <v>5</v>
+      </c>
+      <c r="Q69" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A70" s="42" t="s">
+        <v>81</v>
+      </c>
+      <c r="B70" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" s="51">
+        <v>4</v>
+      </c>
+      <c r="D70" s="51">
+        <v>4</v>
+      </c>
+      <c r="E70" s="51">
+        <v>4</v>
+      </c>
+      <c r="F70" s="51">
+        <v>4</v>
+      </c>
+      <c r="G70" s="51">
+        <v>4</v>
+      </c>
+      <c r="H70" s="51">
+        <v>4</v>
+      </c>
+      <c r="I70" s="51">
+        <v>4</v>
+      </c>
+      <c r="J70" s="51">
+        <v>4</v>
+      </c>
+      <c r="K70" s="51">
+        <v>4</v>
+      </c>
+      <c r="L70" s="51">
+        <v>4</v>
+      </c>
+      <c r="M70" s="51">
+        <v>4</v>
+      </c>
+      <c r="N70" s="51">
+        <v>4</v>
+      </c>
+      <c r="O70" s="51">
+        <v>4</v>
+      </c>
+      <c r="P70" s="51">
+        <v>4</v>
+      </c>
+      <c r="Q70" s="51">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A71" s="44" t="s">
+        <v>82</v>
+      </c>
+      <c r="B71" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="C71" s="52">
+        <v>4</v>
+      </c>
+      <c r="D71" s="52">
+        <v>4</v>
+      </c>
+      <c r="E71" s="52">
+        <v>4</v>
+      </c>
+      <c r="F71" s="52">
+        <v>4</v>
+      </c>
+      <c r="G71" s="52">
+        <v>4</v>
+      </c>
+      <c r="H71" s="52">
+        <v>4</v>
+      </c>
+      <c r="I71" s="52">
+        <v>4</v>
+      </c>
+      <c r="J71" s="52">
+        <v>4</v>
+      </c>
+      <c r="K71" s="52">
+        <v>4</v>
+      </c>
+      <c r="L71" s="52">
+        <v>4</v>
+      </c>
+      <c r="M71" s="52">
+        <v>4</v>
+      </c>
+      <c r="N71" s="52">
+        <v>4</v>
+      </c>
+      <c r="O71" s="52">
+        <v>4</v>
+      </c>
+      <c r="P71" s="52">
+        <v>4</v>
+      </c>
+      <c r="Q71" s="52">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A72" s="42" t="s">
+        <v>83</v>
+      </c>
+      <c r="B72" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" s="51">
+        <v>1</v>
+      </c>
+      <c r="D72" s="51">
+        <v>1</v>
+      </c>
+      <c r="E72" s="51">
+        <v>1</v>
+      </c>
+      <c r="F72" s="51">
+        <v>1</v>
+      </c>
+      <c r="G72" s="51">
+        <v>1</v>
+      </c>
+      <c r="H72" s="51">
+        <v>1</v>
+      </c>
+      <c r="I72" s="51">
+        <v>1</v>
+      </c>
+      <c r="J72" s="51">
+        <v>1</v>
+      </c>
+      <c r="K72" s="51">
+        <v>1</v>
+      </c>
+      <c r="L72" s="51">
+        <v>1</v>
+      </c>
+      <c r="M72" s="51">
+        <v>1</v>
+      </c>
+      <c r="N72" s="51">
+        <v>1</v>
+      </c>
+      <c r="O72" s="51">
+        <v>1</v>
+      </c>
+      <c r="P72" s="51">
+        <v>1</v>
+      </c>
+      <c r="Q72" s="51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A73" s="44" t="s">
+        <v>84</v>
+      </c>
+      <c r="B73" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="C73" s="52">
+        <v>1</v>
+      </c>
+      <c r="D73" s="52">
+        <v>1</v>
+      </c>
+      <c r="E73" s="52">
+        <v>1</v>
+      </c>
+      <c r="F73" s="52">
+        <v>1</v>
+      </c>
+      <c r="G73" s="52">
+        <v>1</v>
+      </c>
+      <c r="H73" s="52">
+        <v>1</v>
+      </c>
+      <c r="I73" s="52">
+        <v>1</v>
+      </c>
+      <c r="J73" s="52">
+        <v>1</v>
+      </c>
+      <c r="K73" s="52">
+        <v>1</v>
+      </c>
+      <c r="L73" s="52">
+        <v>1</v>
+      </c>
+      <c r="M73" s="52">
+        <v>1</v>
+      </c>
+      <c r="N73" s="52">
+        <v>1</v>
+      </c>
+      <c r="O73" s="52">
+        <v>1</v>
+      </c>
+      <c r="P73" s="52">
+        <v>1</v>
+      </c>
+      <c r="Q73" s="52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A74" s="49" t="s">
+        <v>85</v>
+      </c>
+      <c r="B74" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" s="49">
+        <v>3</v>
+      </c>
+      <c r="D74" s="49">
+        <v>3</v>
+      </c>
+      <c r="E74" s="49">
+        <v>3</v>
+      </c>
+      <c r="F74" s="49">
+        <v>3</v>
+      </c>
+      <c r="G74" s="49">
+        <v>3</v>
+      </c>
+      <c r="H74" s="49">
+        <v>3</v>
+      </c>
+      <c r="I74" s="49">
+        <v>3</v>
+      </c>
+      <c r="J74" s="49">
+        <v>3</v>
+      </c>
+      <c r="K74" s="49">
+        <v>3</v>
+      </c>
+      <c r="L74" s="49">
+        <v>3</v>
+      </c>
+      <c r="M74" s="49">
+        <v>3</v>
+      </c>
+      <c r="N74" s="49">
+        <v>3</v>
+      </c>
+      <c r="O74" s="49">
+        <v>3</v>
+      </c>
+      <c r="P74" s="49">
+        <v>3</v>
+      </c>
+      <c r="Q74" s="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A75" s="39" t="s">
+        <v>85</v>
+      </c>
+      <c r="B75" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C75" s="8">
+        <v>3</v>
+      </c>
+      <c r="D75" s="8">
+        <v>3</v>
+      </c>
+      <c r="E75" s="8">
+        <v>3</v>
+      </c>
+      <c r="F75" s="8">
+        <v>3</v>
+      </c>
+      <c r="G75" s="8">
+        <v>3</v>
+      </c>
+      <c r="H75" s="8">
+        <v>3</v>
+      </c>
+      <c r="I75" s="8">
+        <v>3</v>
+      </c>
+      <c r="J75" s="8">
+        <v>3</v>
+      </c>
+      <c r="K75" s="8">
+        <v>3</v>
+      </c>
+      <c r="L75" s="8">
+        <v>3</v>
+      </c>
+      <c r="M75" s="8">
+        <v>3</v>
+      </c>
+      <c r="N75" s="8">
+        <v>3</v>
+      </c>
+      <c r="O75" s="8">
+        <v>3</v>
+      </c>
+      <c r="P75" s="8">
+        <v>3</v>
+      </c>
+      <c r="Q75" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A76" s="42" t="s">
+        <v>86</v>
+      </c>
+      <c r="B76" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" s="51">
+        <v>2</v>
+      </c>
+      <c r="D76" s="51">
+        <v>2</v>
+      </c>
+      <c r="E76" s="51">
+        <v>2</v>
+      </c>
+      <c r="F76" s="51">
+        <v>2</v>
+      </c>
+      <c r="G76" s="51">
+        <v>2</v>
+      </c>
+      <c r="H76" s="51">
+        <v>2</v>
+      </c>
+      <c r="I76" s="51">
+        <v>2</v>
+      </c>
+      <c r="J76" s="51">
+        <v>2</v>
+      </c>
+      <c r="K76" s="51">
+        <v>2</v>
+      </c>
+      <c r="L76" s="51">
+        <v>2</v>
+      </c>
+      <c r="M76" s="51">
+        <v>2</v>
+      </c>
+      <c r="N76" s="51">
+        <v>2</v>
+      </c>
+      <c r="O76" s="51">
+        <v>2</v>
+      </c>
+      <c r="P76" s="51">
+        <v>2</v>
+      </c>
+      <c r="Q76" s="51">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A77" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="B77" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="C77" s="52">
+        <v>2</v>
+      </c>
+      <c r="D77" s="52">
+        <v>2</v>
+      </c>
+      <c r="E77" s="52">
+        <v>2</v>
+      </c>
+      <c r="F77" s="52">
+        <v>2</v>
+      </c>
+      <c r="G77" s="52">
+        <v>2</v>
+      </c>
+      <c r="H77" s="52">
+        <v>2</v>
+      </c>
+      <c r="I77" s="52">
+        <v>2</v>
+      </c>
+      <c r="J77" s="52">
+        <v>2</v>
+      </c>
+      <c r="K77" s="52">
+        <v>2</v>
+      </c>
+      <c r="L77" s="52">
+        <v>2</v>
+      </c>
+      <c r="M77" s="52">
+        <v>2</v>
+      </c>
+      <c r="N77" s="52">
+        <v>2</v>
+      </c>
+      <c r="O77" s="52">
+        <v>2</v>
+      </c>
+      <c r="P77" s="52">
+        <v>2</v>
+      </c>
+      <c r="Q77" s="52">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A78" s="42" t="s">
+        <v>88</v>
+      </c>
+      <c r="B78" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" s="51">
+        <v>1</v>
+      </c>
+      <c r="D78" s="51">
+        <v>1</v>
+      </c>
+      <c r="E78" s="51">
+        <v>1</v>
+      </c>
+      <c r="F78" s="51">
+        <v>1</v>
+      </c>
+      <c r="G78" s="51">
+        <v>1</v>
+      </c>
+      <c r="H78" s="51">
+        <v>1</v>
+      </c>
+      <c r="I78" s="51">
+        <v>1</v>
+      </c>
+      <c r="J78" s="51">
+        <v>1</v>
+      </c>
+      <c r="K78" s="51">
+        <v>1</v>
+      </c>
+      <c r="L78" s="51">
+        <v>1</v>
+      </c>
+      <c r="M78" s="51">
+        <v>1</v>
+      </c>
+      <c r="N78" s="51">
+        <v>1</v>
+      </c>
+      <c r="O78" s="51">
+        <v>1</v>
+      </c>
+      <c r="P78" s="51">
+        <v>1</v>
+      </c>
+      <c r="Q78" s="51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A79" s="44" t="s">
+        <v>89</v>
+      </c>
+      <c r="B79" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="C79" s="52">
+        <v>1</v>
+      </c>
+      <c r="D79" s="52">
+        <v>1</v>
+      </c>
+      <c r="E79" s="52">
+        <v>1</v>
+      </c>
+      <c r="F79" s="52">
+        <v>1</v>
+      </c>
+      <c r="G79" s="52">
+        <v>1</v>
+      </c>
+      <c r="H79" s="52">
+        <v>1</v>
+      </c>
+      <c r="I79" s="52">
+        <v>1</v>
+      </c>
+      <c r="J79" s="52">
+        <v>1</v>
+      </c>
+      <c r="K79" s="52">
+        <v>1</v>
+      </c>
+      <c r="L79" s="52">
+        <v>1</v>
+      </c>
+      <c r="M79" s="52">
+        <v>1</v>
+      </c>
+      <c r="N79" s="52">
+        <v>1</v>
+      </c>
+      <c r="O79" s="52">
+        <v>1</v>
+      </c>
+      <c r="P79" s="52">
+        <v>1</v>
+      </c>
+      <c r="Q79" s="52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A80" s="49" t="s">
+        <v>90</v>
+      </c>
+      <c r="B80" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" s="49">
+        <v>2</v>
+      </c>
+      <c r="D80" s="49">
+        <v>2</v>
+      </c>
+      <c r="E80" s="49">
+        <v>2</v>
+      </c>
+      <c r="F80" s="49">
+        <v>3</v>
+      </c>
+      <c r="G80" s="49">
+        <v>3</v>
+      </c>
+      <c r="H80" s="49">
+        <v>3</v>
+      </c>
+      <c r="I80" s="49">
+        <v>3</v>
+      </c>
+      <c r="J80" s="49">
+        <v>3</v>
+      </c>
+      <c r="K80" s="49">
+        <v>3</v>
+      </c>
+      <c r="L80" s="49">
+        <v>3</v>
+      </c>
+      <c r="M80" s="49">
+        <v>3</v>
+      </c>
+      <c r="N80" s="49">
+        <v>3</v>
+      </c>
+      <c r="O80" s="49">
+        <v>3</v>
+      </c>
+      <c r="P80" s="49">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A81" s="39" t="s">
+        <v>90</v>
+      </c>
+      <c r="B81" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C81" s="8">
+        <v>2</v>
+      </c>
+      <c r="D81" s="8">
+        <v>2</v>
+      </c>
+      <c r="E81" s="8">
+        <v>2</v>
+      </c>
+      <c r="F81" s="8">
+        <v>3</v>
+      </c>
+      <c r="G81" s="8">
+        <v>3</v>
+      </c>
+      <c r="H81" s="8">
+        <v>3</v>
+      </c>
+      <c r="I81" s="8">
+        <v>3</v>
+      </c>
+      <c r="J81" s="8">
+        <v>3</v>
+      </c>
+      <c r="K81" s="8">
+        <v>3</v>
+      </c>
+      <c r="L81" s="8">
+        <v>3</v>
+      </c>
+      <c r="M81" s="8">
+        <v>3</v>
+      </c>
+      <c r="N81" s="8">
+        <v>3</v>
+      </c>
+      <c r="O81" s="8">
+        <v>3</v>
+      </c>
+      <c r="P81" s="8">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="8">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A17034E-6C79-ED4C-B19B-860240F0490A}">
+  <sheetPr>
+    <tabColor theme="3" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:P93"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="28.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B1" t="str">
+        <f>IF(TDE!C1&gt;0,TDE!C1,"")</f>
+        <v>JAN</v>
+      </c>
+      <c r="C1" t="str">
+        <f>IF(TDE!D1&gt;0,TDE!D1,"")</f>
+        <v>FEB</v>
+      </c>
+      <c r="D1" t="str">
+        <f>IF(TDE!E1&gt;0,TDE!E1,"")</f>
+        <v>MAR</v>
+      </c>
+      <c r="E1" t="str">
+        <f>IF(TDE!F1&gt;0,TDE!F1,"")</f>
+        <v>APR</v>
+      </c>
+      <c r="F1" t="str">
+        <f>IF(TDE!G1&gt;0,TDE!G1,"")</f>
+        <v>MAY</v>
+      </c>
+      <c r="G1" t="str">
+        <f>IF(TDE!H1&gt;0,TDE!H1,"")</f>
+        <v>JUN</v>
+      </c>
+      <c r="H1" t="str">
+        <f>IF(TDE!I1&gt;0,TDE!I1,"")</f>
+        <v>JUL</v>
+      </c>
+      <c r="I1" t="str">
+        <f>IF(TDE!J1&gt;0,TDE!J1,"")</f>
+        <v>AUG</v>
+      </c>
+      <c r="J1" t="str">
+        <f>IF(TDE!K1&gt;0,TDE!K1,"")</f>
+        <v>SEP</v>
+      </c>
+      <c r="K1" t="str">
+        <f>IF(TDE!L1&gt;0,TDE!L1,"")</f>
+        <v>OCT</v>
+      </c>
+      <c r="L1" t="str">
+        <f>IF(TDE!M1&gt;0,TDE!M1,"")</f>
+        <v>NOV</v>
+      </c>
+      <c r="M1" t="str">
+        <f>IF(TDE!N1&gt;0,TDE!N1,"")</f>
+        <v>DEC</v>
+      </c>
+      <c r="N1" t="str">
+        <f>IF(TDE!O1&gt;0,TDE!O1,"")</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O1" t="str">
+        <f>IF(TDE!P1&gt;0,TDE!P1,"")</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P1" t="str">
+        <f>IF(TDE!Q1&gt;0,TDE!Q1,"")</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A2" t="str">
+        <f>IF(TDE!B2&gt;0,TDE!B2,"")</f>
+        <v>Staff</v>
+      </c>
+      <c r="B2">
+        <f>IF(TDE!C2&gt;0,TDE!C2,"")</f>
+        <v>15</v>
+      </c>
+      <c r="C2">
+        <f>IF(TDE!D2&gt;0,TDE!D2,"")</f>
+        <v>15</v>
+      </c>
+      <c r="D2">
+        <f>IF(TDE!E2&gt;0,TDE!E2,"")</f>
+        <v>15</v>
+      </c>
+      <c r="E2">
+        <f>IF(TDE!F2&gt;0,TDE!F2,"")</f>
+        <v>16</v>
+      </c>
+      <c r="F2">
+        <f>IF(TDE!G2&gt;0,TDE!G2,"")</f>
+        <v>16</v>
+      </c>
+      <c r="G2">
+        <f>IF(TDE!H2&gt;0,TDE!H2,"")</f>
+        <v>16</v>
+      </c>
+      <c r="H2">
+        <f>IF(TDE!I2&gt;0,TDE!I2,"")</f>
+        <v>16</v>
+      </c>
+      <c r="I2">
+        <f>IF(TDE!J2&gt;0,TDE!J2,"")</f>
+        <v>16</v>
+      </c>
+      <c r="J2">
+        <f>IF(TDE!K2&gt;0,TDE!K2,"")</f>
+        <v>16</v>
+      </c>
+      <c r="K2">
+        <f>IF(TDE!L2&gt;0,TDE!L2,"")</f>
+        <v>16</v>
+      </c>
+      <c r="L2">
+        <f>IF(TDE!M2&gt;0,TDE!M2,"")</f>
+        <v>16</v>
+      </c>
+      <c r="M2">
+        <f>IF(TDE!N2&gt;0,TDE!N2,"")</f>
+        <v>16</v>
+      </c>
+      <c r="N2">
+        <f>IF(TDE!O2&gt;0,TDE!O2,"")</f>
+        <v>16</v>
+      </c>
+      <c r="O2">
+        <f>IF(TDE!P2&gt;0,TDE!P2,"")</f>
+        <v>16</v>
+      </c>
+      <c r="P2">
+        <f>IF(TDE!Q2&gt;0,TDE!Q2,"")</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A3" t="str">
+        <f>IF(TDE!B3&gt;0,TDE!B3,"")</f>
+        <v>Staff AVG</v>
+      </c>
+      <c r="B3">
+        <f>IF(TDE!C3&gt;0,TDE!C3,"")</f>
+        <v>16</v>
+      </c>
+      <c r="C3">
+        <f>IF(TDE!D3&gt;0,TDE!D3,"")</f>
+        <v>16</v>
+      </c>
+      <c r="D3">
+        <f>IF(TDE!E3&gt;0,TDE!E3,"")</f>
+        <v>16</v>
+      </c>
+      <c r="E3">
+        <f>IF(TDE!F3&gt;0,TDE!F3,"")</f>
+        <v>16</v>
+      </c>
+      <c r="F3">
+        <f>IF(TDE!G3&gt;0,TDE!G3,"")</f>
+        <v>16</v>
+      </c>
+      <c r="G3">
+        <f>IF(TDE!H3&gt;0,TDE!H3,"")</f>
+        <v>16</v>
+      </c>
+      <c r="H3">
+        <f>IF(TDE!I3&gt;0,TDE!I3,"")</f>
+        <v>16</v>
+      </c>
+      <c r="I3">
+        <f>IF(TDE!J3&gt;0,TDE!J3,"")</f>
+        <v>16</v>
+      </c>
+      <c r="J3">
+        <f>IF(TDE!K3&gt;0,TDE!K3,"")</f>
+        <v>16</v>
+      </c>
+      <c r="K3">
+        <f>IF(TDE!L3&gt;0,TDE!L3,"")</f>
+        <v>16</v>
+      </c>
+      <c r="L3">
+        <f>IF(TDE!M3&gt;0,TDE!M3,"")</f>
+        <v>16</v>
+      </c>
+      <c r="M3">
+        <f>IF(TDE!N3&gt;0,TDE!N3,"")</f>
+        <v>16</v>
+      </c>
+      <c r="N3">
+        <f>IF(TDE!O3&gt;0,TDE!O3,"")</f>
+        <v>16</v>
+      </c>
+      <c r="O3">
+        <f>IF(TDE!P3&gt;0,TDE!P3,"")</f>
+        <v>16</v>
+      </c>
+      <c r="P3">
+        <f>IF(TDE!Q3&gt;0,TDE!Q3,"")</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A4" t="str">
+        <f>IF(TDE!B4&gt;0,TDE!B4,"")</f>
+        <v>Plan</v>
+      </c>
+      <c r="B4">
+        <f>IF(TDE!C4&gt;0,TDE!C4,"")</f>
+        <v>15</v>
+      </c>
+      <c r="C4">
+        <f>IF(TDE!D4&gt;0,TDE!D4,"")</f>
+        <v>15</v>
+      </c>
+      <c r="D4">
+        <f>IF(TDE!E4&gt;0,TDE!E4,"")</f>
+        <v>15</v>
+      </c>
+      <c r="E4">
+        <f>IF(TDE!F4&gt;0,TDE!F4,"")</f>
+        <v>16</v>
+      </c>
+      <c r="F4">
+        <f>IF(TDE!G4&gt;0,TDE!G4,"")</f>
+        <v>16</v>
+      </c>
+      <c r="G4">
+        <f>IF(TDE!H4&gt;0,TDE!H4,"")</f>
+        <v>16</v>
+      </c>
+      <c r="H4">
+        <f>IF(TDE!I4&gt;0,TDE!I4,"")</f>
+        <v>16</v>
+      </c>
+      <c r="I4">
+        <f>IF(TDE!J4&gt;0,TDE!J4,"")</f>
+        <v>16</v>
+      </c>
+      <c r="J4">
+        <f>IF(TDE!K4&gt;0,TDE!K4,"")</f>
+        <v>16</v>
+      </c>
+      <c r="K4">
+        <f>IF(TDE!L4&gt;0,TDE!L4,"")</f>
+        <v>16</v>
+      </c>
+      <c r="L4">
+        <f>IF(TDE!M4&gt;0,TDE!M4,"")</f>
+        <v>16</v>
+      </c>
+      <c r="M4">
+        <f>IF(TDE!N4&gt;0,TDE!N4,"")</f>
+        <v>16</v>
+      </c>
+      <c r="N4">
+        <f>IF(TDE!O4&gt;0,TDE!O4,"")</f>
+        <v>16</v>
+      </c>
+      <c r="O4">
+        <f>IF(TDE!P4&gt;0,TDE!P4,"")</f>
+        <v>16</v>
+      </c>
+      <c r="P4">
+        <f>IF(TDE!Q4&gt;0,TDE!Q4,"")</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A5" t="str">
+        <f>IF(TDE!B11&gt;0,TDE!B11,"")</f>
+        <v>PAYROLL</v>
+      </c>
+      <c r="B5">
+        <f>IF(TDE!C11&gt;0,TDE!C11,"")</f>
+        <v>13</v>
+      </c>
+      <c r="C5">
+        <f>IF(TDE!D11&gt;0,TDE!D11,"")</f>
+        <v>13</v>
+      </c>
+      <c r="D5">
+        <f>IF(TDE!E11&gt;0,TDE!E11,"")</f>
+        <v>13</v>
+      </c>
+      <c r="E5">
+        <f>IF(TDE!F11&gt;0,TDE!F11,"")</f>
+        <v>14</v>
+      </c>
+      <c r="F5">
+        <f>IF(TDE!G11&gt;0,TDE!G11,"")</f>
+        <v>14</v>
+      </c>
+      <c r="G5">
+        <f>IF(TDE!H11&gt;0,TDE!H11,"")</f>
+        <v>14</v>
+      </c>
+      <c r="H5">
+        <f>IF(TDE!I11&gt;0,TDE!I11,"")</f>
+        <v>14</v>
+      </c>
+      <c r="I5">
+        <f>IF(TDE!J11&gt;0,TDE!J11,"")</f>
+        <v>14</v>
+      </c>
+      <c r="J5">
+        <f>IF(TDE!K11&gt;0,TDE!K11,"")</f>
+        <v>14</v>
+      </c>
+      <c r="K5">
+        <f>IF(TDE!L11&gt;0,TDE!L11,"")</f>
+        <v>14</v>
+      </c>
+      <c r="L5">
+        <f>IF(TDE!M11&gt;0,TDE!M11,"")</f>
+        <v>14</v>
+      </c>
+      <c r="M5">
+        <f>IF(TDE!N11&gt;0,TDE!N11,"")</f>
+        <v>14</v>
+      </c>
+      <c r="N5">
+        <f>IF(TDE!O11&gt;0,TDE!O11,"")</f>
+        <v>14</v>
+      </c>
+      <c r="O5">
+        <f>IF(TDE!P11&gt;0,TDE!P11,"")</f>
+        <v>14</v>
+      </c>
+      <c r="P5">
+        <f>IF(TDE!Q11&gt;0,TDE!Q11,"")</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A6" t="str">
+        <f>IF(TDE!B15&gt;0,TDE!B15,"")</f>
+        <v>CONTRACTOR</v>
+      </c>
+      <c r="B6">
+        <f>IF(TDE!C15&gt;0,TDE!C15,"")</f>
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <f>IF(TDE!D15&gt;0,TDE!D15,"")</f>
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <f>IF(TDE!E15&gt;0,TDE!E15,"")</f>
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <f>IF(TDE!F15&gt;0,TDE!F15,"")</f>
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <f>IF(TDE!G15&gt;0,TDE!G15,"")</f>
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <f>IF(TDE!H15&gt;0,TDE!H15,"")</f>
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <f>IF(TDE!I15&gt;0,TDE!I15,"")</f>
+        <v>2</v>
+      </c>
+      <c r="I6">
+        <f>IF(TDE!J15&gt;0,TDE!J15,"")</f>
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <f>IF(TDE!K15&gt;0,TDE!K15,"")</f>
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <f>IF(TDE!L15&gt;0,TDE!L15,"")</f>
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <f>IF(TDE!M15&gt;0,TDE!M15,"")</f>
+        <v>2</v>
+      </c>
+      <c r="M6">
+        <f>IF(TDE!N15&gt;0,TDE!N15,"")</f>
+        <v>2</v>
+      </c>
+      <c r="N6">
+        <f>IF(TDE!O15&gt;0,TDE!O15,"")</f>
+        <v>2</v>
+      </c>
+      <c r="O6">
+        <f>IF(TDE!P15&gt;0,TDE!P15,"")</f>
+        <v>2</v>
+      </c>
+      <c r="P6">
+        <f>IF(TDE!Q15&gt;0,TDE!Q15,"")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A7" t="str">
+        <f>IF(TDE!B19&gt;0,TDE!B19,"")</f>
+        <v>OUTSOURCE</v>
+      </c>
+      <c r="B7" t="str">
+        <f>IF(TDE!C19&gt;0,TDE!C19,"")</f>
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <f>IF(TDE!D19&gt;0,TDE!D19,"")</f>
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <f>IF(TDE!E19&gt;0,TDE!E19,"")</f>
+        <v/>
+      </c>
+      <c r="E7" t="str">
+        <f>IF(TDE!F19&gt;0,TDE!F19,"")</f>
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <f>IF(TDE!G19&gt;0,TDE!G19,"")</f>
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <f>IF(TDE!H19&gt;0,TDE!H19,"")</f>
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <f>IF(TDE!I19&gt;0,TDE!I19,"")</f>
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <f>IF(TDE!J19&gt;0,TDE!J19,"")</f>
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <f>IF(TDE!K19&gt;0,TDE!K19,"")</f>
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <f>IF(TDE!L19&gt;0,TDE!L19,"")</f>
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <f>IF(TDE!M19&gt;0,TDE!M19,"")</f>
+        <v/>
+      </c>
+      <c r="M7" t="str">
+        <f>IF(TDE!N19&gt;0,TDE!N19,"")</f>
+        <v/>
+      </c>
+      <c r="N7" t="str">
+        <f>IF(TDE!O19&gt;0,TDE!O19,"")</f>
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <f>IF(TDE!P19&gt;0,TDE!P19,"")</f>
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <f>IF(TDE!Q19&gt;0,TDE!Q19,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B11" t="str">
+        <f>IF(TDE!C1&gt;0,TDE!C1,"")</f>
+        <v>JAN</v>
+      </c>
+      <c r="C11" t="str">
+        <f>IF(TDE!D1&gt;0,TDE!D1,"")</f>
+        <v>FEB</v>
+      </c>
+      <c r="D11" t="str">
+        <f>IF(TDE!E1&gt;0,TDE!E1,"")</f>
+        <v>MAR</v>
+      </c>
+      <c r="E11" t="str">
+        <f>IF(TDE!F1&gt;0,TDE!F1,"")</f>
+        <v>APR</v>
+      </c>
+      <c r="F11" t="str">
+        <f>IF(TDE!G1&gt;0,TDE!G1,"")</f>
+        <v>MAY</v>
+      </c>
+      <c r="G11" t="str">
+        <f>IF(TDE!H1&gt;0,TDE!H1,"")</f>
+        <v>JUN</v>
+      </c>
+      <c r="H11" t="str">
+        <f>IF(TDE!I1&gt;0,TDE!I1,"")</f>
+        <v>JUL</v>
+      </c>
+      <c r="I11" t="str">
+        <f>IF(TDE!J1&gt;0,TDE!J1,"")</f>
+        <v>AUG</v>
+      </c>
+      <c r="J11" t="str">
+        <f>IF(TDE!K1&gt;0,TDE!K1,"")</f>
+        <v>SEP</v>
+      </c>
+      <c r="K11" t="str">
+        <f>IF(TDE!L1&gt;0,TDE!L1,"")</f>
+        <v>OCT</v>
+      </c>
+      <c r="L11" t="str">
+        <f>IF(TDE!M1&gt;0,TDE!M1,"")</f>
+        <v>NOV</v>
+      </c>
+      <c r="M11" t="str">
+        <f>IF(TDE!N1&gt;0,TDE!N1,"")</f>
+        <v>DEC</v>
+      </c>
+      <c r="N11" t="str">
+        <f>IF(TDE!O1&gt;0,TDE!O1,"")</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O11" t="str">
+        <f>IF(TDE!P1&gt;0,TDE!P1,"")</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P11" t="str">
+        <f>IF(TDE!Q1&gt;0,TDE!Q1,"")</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A12" t="str">
+        <f>IF(TDE!B2&gt;0,TDE!B2,"")</f>
+        <v>Staff</v>
+      </c>
+      <c r="B12">
+        <f>IF(TDE!C9&gt;0,TDE!C9,"")</f>
+        <v>13</v>
+      </c>
+      <c r="C12">
+        <f>IF(TDE!D9&gt;0,TDE!D9,"")</f>
+        <v>13</v>
+      </c>
+      <c r="D12">
+        <f>IF(TDE!E9&gt;0,TDE!E9,"")</f>
+        <v>13</v>
+      </c>
+      <c r="E12">
+        <f>IF(TDE!F9&gt;0,TDE!F9,"")</f>
+        <v>14</v>
+      </c>
+      <c r="F12">
+        <f>IF(TDE!G9&gt;0,TDE!G9,"")</f>
+        <v>14</v>
+      </c>
+      <c r="G12">
+        <f>IF(TDE!H9&gt;0,TDE!H9,"")</f>
+        <v>14</v>
+      </c>
+      <c r="H12">
+        <f>IF(TDE!I9&gt;0,TDE!I9,"")</f>
+        <v>14</v>
+      </c>
+      <c r="I12">
+        <f>IF(TDE!J9&gt;0,TDE!J9,"")</f>
+        <v>14</v>
+      </c>
+      <c r="J12">
+        <f>IF(TDE!K9&gt;0,TDE!K9,"")</f>
+        <v>14</v>
+      </c>
+      <c r="K12">
+        <f>IF(TDE!L9&gt;0,TDE!L9,"")</f>
+        <v>14</v>
+      </c>
+      <c r="L12">
+        <f>IF(TDE!M9&gt;0,TDE!M9,"")</f>
+        <v>14</v>
+      </c>
+      <c r="M12">
+        <f>IF(TDE!N9&gt;0,TDE!N9,"")</f>
+        <v>14</v>
+      </c>
+      <c r="N12">
+        <f>IF(TDE!O9&gt;0,TDE!O9,"")</f>
+        <v>14</v>
+      </c>
+      <c r="O12">
+        <f>IF(TDE!P9&gt;0,TDE!P9,"")</f>
+        <v>14</v>
+      </c>
+      <c r="P12">
+        <f>IF(TDE!Q9&gt;0,TDE!Q9,"")</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A13" t="str">
+        <f>IF(TDE!B3&gt;0,TDE!B3,"")</f>
+        <v>Staff AVG</v>
+      </c>
+      <c r="B13">
+        <f>IF(TDE!C10&gt;0,TDE!C10,"")</f>
+        <v>14</v>
+      </c>
+      <c r="C13">
+        <f>IF(TDE!D10&gt;0,TDE!D10,"")</f>
+        <v>14</v>
+      </c>
+      <c r="D13">
+        <f>IF(TDE!E10&gt;0,TDE!E10,"")</f>
+        <v>14</v>
+      </c>
+      <c r="E13">
+        <f>IF(TDE!F10&gt;0,TDE!F10,"")</f>
+        <v>14</v>
+      </c>
+      <c r="F13">
+        <f>IF(TDE!G10&gt;0,TDE!G10,"")</f>
+        <v>14</v>
+      </c>
+      <c r="G13">
+        <f>IF(TDE!H10&gt;0,TDE!H10,"")</f>
+        <v>14</v>
+      </c>
+      <c r="H13">
+        <f>IF(TDE!I10&gt;0,TDE!I10,"")</f>
+        <v>14</v>
+      </c>
+      <c r="I13">
+        <f>IF(TDE!J10&gt;0,TDE!J10,"")</f>
+        <v>14</v>
+      </c>
+      <c r="J13">
+        <f>IF(TDE!K10&gt;0,TDE!K10,"")</f>
+        <v>14</v>
+      </c>
+      <c r="K13">
+        <f>IF(TDE!L10&gt;0,TDE!L10,"")</f>
+        <v>14</v>
+      </c>
+      <c r="L13">
+        <f>IF(TDE!M10&gt;0,TDE!M10,"")</f>
+        <v>14</v>
+      </c>
+      <c r="M13">
+        <f>IF(TDE!N10&gt;0,TDE!N10,"")</f>
+        <v>14</v>
+      </c>
+      <c r="N13">
+        <f>IF(TDE!O10&gt;0,TDE!O10,"")</f>
+        <v>14</v>
+      </c>
+      <c r="O13">
+        <f>IF(TDE!P10&gt;0,TDE!P10,"")</f>
+        <v>14</v>
+      </c>
+      <c r="P13">
+        <f>IF(TDE!Q10&gt;0,TDE!Q10,"")</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A14" t="str">
+        <f>IF(TDE!B4&gt;0,TDE!B4,"")</f>
+        <v>Plan</v>
+      </c>
+      <c r="B14">
+        <f>IF(TDE!C11&gt;0,TDE!C11,"")</f>
+        <v>13</v>
+      </c>
+      <c r="C14">
+        <f>IF(TDE!D11&gt;0,TDE!D11,"")</f>
+        <v>13</v>
+      </c>
+      <c r="D14">
+        <f>IF(TDE!E11&gt;0,TDE!E11,"")</f>
+        <v>13</v>
+      </c>
+      <c r="E14">
+        <f>IF(TDE!F11&gt;0,TDE!F11,"")</f>
+        <v>14</v>
+      </c>
+      <c r="F14">
+        <f>IF(TDE!G11&gt;0,TDE!G11,"")</f>
+        <v>14</v>
+      </c>
+      <c r="G14">
+        <f>IF(TDE!H11&gt;0,TDE!H11,"")</f>
+        <v>14</v>
+      </c>
+      <c r="H14">
+        <f>IF(TDE!I11&gt;0,TDE!I11,"")</f>
+        <v>14</v>
+      </c>
+      <c r="I14">
+        <f>IF(TDE!J11&gt;0,TDE!J11,"")</f>
+        <v>14</v>
+      </c>
+      <c r="J14">
+        <f>IF(TDE!K11&gt;0,TDE!K11,"")</f>
+        <v>14</v>
+      </c>
+      <c r="K14">
+        <f>IF(TDE!L11&gt;0,TDE!L11,"")</f>
+        <v>14</v>
+      </c>
+      <c r="L14">
+        <f>IF(TDE!M11&gt;0,TDE!M11,"")</f>
+        <v>14</v>
+      </c>
+      <c r="M14">
+        <f>IF(TDE!N11&gt;0,TDE!N11,"")</f>
+        <v>14</v>
+      </c>
+      <c r="N14">
+        <f>IF(TDE!O11&gt;0,TDE!O11,"")</f>
+        <v>14</v>
+      </c>
+      <c r="O14">
+        <f>IF(TDE!P11&gt;0,TDE!P11,"")</f>
+        <v>14</v>
+      </c>
+      <c r="P14">
+        <f>IF(TDE!Q11&gt;0,TDE!Q11,"")</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B21" t="str">
+        <f>IF(TDE!C1&gt;0,TDE!C1,"")</f>
+        <v>JAN</v>
+      </c>
+      <c r="C21" t="str">
+        <f>IF(TDE!D1&gt;0,TDE!D1,"")</f>
+        <v>FEB</v>
+      </c>
+      <c r="D21" t="str">
+        <f>IF(TDE!E1&gt;0,TDE!E1,"")</f>
+        <v>MAR</v>
+      </c>
+      <c r="E21" t="str">
+        <f>IF(TDE!F1&gt;0,TDE!F1,"")</f>
+        <v>APR</v>
+      </c>
+      <c r="F21" t="str">
+        <f>IF(TDE!G1&gt;0,TDE!G1,"")</f>
+        <v>MAY</v>
+      </c>
+      <c r="G21" t="str">
+        <f>IF(TDE!H1&gt;0,TDE!H1,"")</f>
+        <v>JUN</v>
+      </c>
+      <c r="H21" t="str">
+        <f>IF(TDE!I1&gt;0,TDE!I1,"")</f>
+        <v>JUL</v>
+      </c>
+      <c r="I21" t="str">
+        <f>IF(TDE!J1&gt;0,TDE!J1,"")</f>
+        <v>AUG</v>
+      </c>
+      <c r="J21" t="str">
+        <f>IF(TDE!K1&gt;0,TDE!K1,"")</f>
+        <v>SEP</v>
+      </c>
+      <c r="K21" t="str">
+        <f>IF(TDE!L1&gt;0,TDE!L1,"")</f>
+        <v>OCT</v>
+      </c>
+      <c r="L21" t="str">
+        <f>IF(TDE!M1&gt;0,TDE!M1,"")</f>
+        <v>NOV</v>
+      </c>
+      <c r="M21" t="str">
+        <f>IF(TDE!N1&gt;0,TDE!N1,"")</f>
+        <v>DEC</v>
+      </c>
+      <c r="N21" t="str">
+        <f>IF(TDE!O1&gt;0,TDE!O1,"")</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O21" t="str">
+        <f>IF(TDE!P1&gt;0,TDE!P1,"")</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P21" t="str">
+        <f>IF(TDE!Q1&gt;0,TDE!Q1,"")</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A22" t="str">
+        <f>IF(TDE!B2&gt;0,TDE!B2,"")</f>
+        <v>Staff</v>
+      </c>
+      <c r="B22">
+        <f>TDE!C13</f>
+        <v>2</v>
+      </c>
+      <c r="C22">
+        <f>TDE!D13</f>
+        <v>2</v>
+      </c>
+      <c r="D22">
+        <f>TDE!E13</f>
+        <v>2</v>
+      </c>
+      <c r="E22">
+        <f>TDE!F13</f>
+        <v>2</v>
+      </c>
+      <c r="F22">
+        <f>TDE!G13</f>
+        <v>2</v>
+      </c>
+      <c r="G22">
+        <f>TDE!H13</f>
+        <v>2</v>
+      </c>
+      <c r="H22">
+        <f>TDE!I13</f>
+        <v>2</v>
+      </c>
+      <c r="I22">
+        <f>TDE!J13</f>
+        <v>2</v>
+      </c>
+      <c r="J22">
+        <f>TDE!K13</f>
+        <v>2</v>
+      </c>
+      <c r="K22">
+        <f>TDE!L13</f>
+        <v>2</v>
+      </c>
+      <c r="L22">
+        <f>TDE!M13</f>
+        <v>2</v>
+      </c>
+      <c r="M22">
+        <f>TDE!N13</f>
+        <v>2</v>
+      </c>
+      <c r="N22">
+        <f>TDE!O13</f>
+        <v>2</v>
+      </c>
+      <c r="O22">
+        <f>TDE!P13</f>
+        <v>2</v>
+      </c>
+      <c r="P22">
+        <f>TDE!Q13</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A23" t="str">
+        <f>IF(TDE!B3&gt;0,TDE!B3,"")</f>
+        <v>Staff AVG</v>
+      </c>
+      <c r="B23">
+        <f>TDE!C14</f>
+        <v>2</v>
+      </c>
+      <c r="C23">
+        <f>TDE!D14</f>
+        <v>2</v>
+      </c>
+      <c r="D23">
+        <f>TDE!E14</f>
+        <v>2</v>
+      </c>
+      <c r="E23">
+        <f>TDE!F14</f>
+        <v>2</v>
+      </c>
+      <c r="F23">
+        <f>TDE!G14</f>
+        <v>2</v>
+      </c>
+      <c r="G23">
+        <f>TDE!H14</f>
+        <v>2</v>
+      </c>
+      <c r="H23">
+        <f>TDE!I14</f>
+        <v>2</v>
+      </c>
+      <c r="I23">
+        <f>TDE!J14</f>
+        <v>2</v>
+      </c>
+      <c r="J23">
+        <f>TDE!K14</f>
+        <v>2</v>
+      </c>
+      <c r="K23">
+        <f>TDE!L14</f>
+        <v>2</v>
+      </c>
+      <c r="L23">
+        <f>TDE!M14</f>
+        <v>2</v>
+      </c>
+      <c r="M23">
+        <f>TDE!N14</f>
+        <v>2</v>
+      </c>
+      <c r="N23">
+        <f>TDE!O14</f>
+        <v>2</v>
+      </c>
+      <c r="O23">
+        <f>TDE!P14</f>
+        <v>2</v>
+      </c>
+      <c r="P23">
+        <f>TDE!Q14</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A24" t="str">
+        <f>IF(TDE!B4&gt;0,TDE!B4,"")</f>
+        <v>Plan</v>
+      </c>
+      <c r="B24">
+        <f>TDE!C15</f>
+        <v>2</v>
+      </c>
+      <c r="C24">
+        <f>TDE!D15</f>
+        <v>2</v>
+      </c>
+      <c r="D24">
+        <f>TDE!E15</f>
+        <v>2</v>
+      </c>
+      <c r="E24">
+        <f>TDE!F15</f>
+        <v>2</v>
+      </c>
+      <c r="F24">
+        <f>TDE!G15</f>
+        <v>2</v>
+      </c>
+      <c r="G24">
+        <f>TDE!H15</f>
+        <v>2</v>
+      </c>
+      <c r="H24">
+        <f>TDE!I15</f>
+        <v>2</v>
+      </c>
+      <c r="I24">
+        <f>TDE!J15</f>
+        <v>2</v>
+      </c>
+      <c r="J24">
+        <f>TDE!K15</f>
+        <v>2</v>
+      </c>
+      <c r="K24">
+        <f>TDE!L15</f>
+        <v>2</v>
+      </c>
+      <c r="L24">
+        <f>TDE!M15</f>
+        <v>2</v>
+      </c>
+      <c r="M24">
+        <f>TDE!N15</f>
+        <v>2</v>
+      </c>
+      <c r="N24">
+        <f>TDE!O15</f>
+        <v>2</v>
+      </c>
+      <c r="O24">
+        <f>TDE!P15</f>
+        <v>2</v>
+      </c>
+      <c r="P24">
+        <f>TDE!Q15</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B31" t="str">
+        <f>IF(TDE!C1&gt;0,TDE!C1,"")</f>
+        <v>JAN</v>
+      </c>
+      <c r="C31" t="str">
+        <f>IF(TDE!D1&gt;0,TDE!D1,"")</f>
+        <v>FEB</v>
+      </c>
+      <c r="D31" t="str">
+        <f>IF(TDE!E1&gt;0,TDE!E1,"")</f>
+        <v>MAR</v>
+      </c>
+      <c r="E31" t="str">
+        <f>IF(TDE!F1&gt;0,TDE!F1,"")</f>
+        <v>APR</v>
+      </c>
+      <c r="F31" t="str">
+        <f>IF(TDE!G1&gt;0,TDE!G1,"")</f>
+        <v>MAY</v>
+      </c>
+      <c r="G31" t="str">
+        <f>IF(TDE!H1&gt;0,TDE!H1,"")</f>
+        <v>JUN</v>
+      </c>
+      <c r="H31" t="str">
+        <f>IF(TDE!I1&gt;0,TDE!I1,"")</f>
+        <v>JUL</v>
+      </c>
+      <c r="I31" t="str">
+        <f>IF(TDE!J1&gt;0,TDE!J1,"")</f>
+        <v>AUG</v>
+      </c>
+      <c r="J31" t="str">
+        <f>IF(TDE!K1&gt;0,TDE!K1,"")</f>
+        <v>SEP</v>
+      </c>
+      <c r="K31" t="str">
+        <f>IF(TDE!L1&gt;0,TDE!L1,"")</f>
+        <v>OCT</v>
+      </c>
+      <c r="L31" t="str">
+        <f>IF(TDE!M1&gt;0,TDE!M1,"")</f>
+        <v>NOV</v>
+      </c>
+      <c r="M31" t="str">
+        <f>IF(TDE!N1&gt;0,TDE!N1,"")</f>
+        <v>DEC</v>
+      </c>
+      <c r="N31" t="str">
+        <f>IF(TDE!O1&gt;0,TDE!O1,"")</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O31" t="str">
+        <f>IF(TDE!P1&gt;0,TDE!P1,"")</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P31" t="str">
+        <f>IF(TDE!Q1&gt;0,TDE!Q1,"")</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A32" t="str">
+        <f>IF(TDE!B2&gt;0,TDE!B2,"")</f>
+        <v>Staff</v>
+      </c>
+      <c r="B32">
+        <f>TDE!C17</f>
+        <v>0</v>
+      </c>
+      <c r="C32">
+        <f>TDE!D17</f>
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <f>TDE!E17</f>
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <f>TDE!F17</f>
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <f>TDE!G17</f>
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <f>TDE!H17</f>
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <f>TDE!I17</f>
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <f>TDE!J17</f>
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <f>TDE!K17</f>
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <f>TDE!L17</f>
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <f>TDE!M17</f>
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <f>TDE!N17</f>
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <f>TDE!O17</f>
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <f>TDE!P17</f>
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <f>TDE!Q17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A33" t="str">
+        <f>IF(TDE!B3&gt;0,TDE!B3,"")</f>
+        <v>Staff AVG</v>
+      </c>
+      <c r="B33">
+        <f>TDE!C18</f>
+        <v>0</v>
+      </c>
+      <c r="C33">
+        <f>TDE!D18</f>
+        <v>0</v>
+      </c>
+      <c r="D33">
+        <f>TDE!E18</f>
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <f>TDE!F18</f>
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <f>TDE!G18</f>
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <f>TDE!H18</f>
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <f>TDE!I18</f>
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <f>TDE!J18</f>
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <f>TDE!K18</f>
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <f>TDE!L18</f>
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <f>TDE!M18</f>
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <f>TDE!N18</f>
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <f>TDE!O18</f>
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <f>TDE!P18</f>
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <f>TDE!Q18</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A34" t="str">
+        <f>IF(TDE!B4&gt;0,TDE!B4,"")</f>
+        <v>Plan</v>
+      </c>
+      <c r="B34">
+        <f>TDE!C19</f>
+        <v>0</v>
+      </c>
+      <c r="C34">
+        <f>TDE!D19</f>
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <f>TDE!E19</f>
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <f>TDE!F19</f>
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <f>TDE!G19</f>
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <f>TDE!H19</f>
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <f>TDE!I19</f>
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <f>TDE!J19</f>
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <f>TDE!K19</f>
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <f>TDE!L19</f>
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <f>TDE!M19</f>
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <f>TDE!N19</f>
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <f>TDE!O19</f>
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <f>TDE!P19</f>
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <f>TDE!Q19</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B41" t="str">
+        <f>IF(TDE!C31&gt;0,TDE!C31,"")</f>
+        <v>Q1</v>
+      </c>
+      <c r="C41" t="str">
+        <f>IF(TDE!D31&gt;0,TDE!D31,"")</f>
+        <v>Q2</v>
+      </c>
+      <c r="D41" t="str">
+        <f>IF(TDE!E31&gt;0,TDE!E31,"")</f>
+        <v>Q3</v>
+      </c>
+      <c r="E41" t="str">
+        <f>IF(TDE!F31&gt;0,TDE!F31,"")</f>
+        <v>Q4</v>
+      </c>
+      <c r="F41" t="str">
+        <f>IF(TDE!G31&gt;0,TDE!G31,"")</f>
+        <v>Q1'27</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A42" t="str">
+        <f>IF(TDE!B32&gt;0,TDE!B32,"")</f>
+        <v>Staff</v>
+      </c>
+      <c r="B42">
+        <f>IF(TDE!C32&gt;0,TDE!C32,"")</f>
+        <v>15</v>
+      </c>
+      <c r="C42">
+        <f>IF(TDE!D32&gt;0,TDE!D32,"")</f>
+        <v>16</v>
+      </c>
+      <c r="D42">
+        <f>IF(TDE!E32&gt;0,TDE!E32,"")</f>
+        <v>16</v>
+      </c>
+      <c r="E42">
+        <f>IF(TDE!F32&gt;0,TDE!F32,"")</f>
+        <v>16</v>
+      </c>
+      <c r="F42">
+        <f>IF(TDE!G32&gt;0,TDE!G32,"")</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A43" t="str">
+        <f>IF(TDE!B33&gt;0,TDE!B33,"")</f>
+        <v>Staff AVG</v>
+      </c>
+      <c r="B43">
+        <f>IF(TDE!C33&gt;0,TDE!C33,"")</f>
+        <v>16</v>
+      </c>
+      <c r="C43">
+        <f>IF(TDE!D33&gt;0,TDE!D33,"")</f>
+        <v>16</v>
+      </c>
+      <c r="D43">
+        <f>IF(TDE!E33&gt;0,TDE!E33,"")</f>
+        <v>16</v>
+      </c>
+      <c r="E43">
+        <f>IF(TDE!F33&gt;0,TDE!F33,"")</f>
+        <v>16</v>
+      </c>
+      <c r="F43">
+        <f>IF(TDE!G33&gt;0,TDE!G33,"")</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A44" t="str">
+        <f>IF(TDE!B34&gt;0,TDE!B34,"")</f>
+        <v>Plan</v>
+      </c>
+      <c r="B44">
+        <f>IF(TDE!C34&gt;0,TDE!C34,"")</f>
+        <v>15</v>
+      </c>
+      <c r="C44">
+        <f>IF(TDE!D34&gt;0,TDE!D34,"")</f>
+        <v>16</v>
+      </c>
+      <c r="D44">
+        <f>IF(TDE!E34&gt;0,TDE!E34,"")</f>
+        <v>16</v>
+      </c>
+      <c r="E44">
+        <f>IF(TDE!F34&gt;0,TDE!F34,"")</f>
+        <v>16</v>
+      </c>
+      <c r="F44">
+        <f>IF(TDE!G34&gt;0,TDE!G34,"")</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A45" t="str">
+        <f>IF(TDE!B41&gt;0,TDE!B41,"")</f>
+        <v>PAYROLL</v>
+      </c>
+      <c r="B45">
+        <f>IF(TDE!C41&gt;0,TDE!C41,"")</f>
+        <v>13</v>
+      </c>
+      <c r="C45">
+        <f>IF(TDE!D41&gt;0,TDE!D41,"")</f>
+        <v>14</v>
+      </c>
+      <c r="D45">
+        <f>IF(TDE!E41&gt;0,TDE!E41,"")</f>
+        <v>14</v>
+      </c>
+      <c r="E45">
+        <f>IF(TDE!F41&gt;0,TDE!F41,"")</f>
+        <v>14</v>
+      </c>
+      <c r="F45">
+        <f>IF(TDE!G41&gt;0,TDE!G41,"")</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A46" t="str">
+        <f>IF(TDE!B45&gt;0,TDE!B45,"")</f>
+        <v>CONTRACTOR</v>
+      </c>
+      <c r="B46">
+        <f>IF(TDE!C45&gt;0,TDE!C45,"")</f>
+        <v>2</v>
+      </c>
+      <c r="C46">
+        <f>IF(TDE!D45&gt;0,TDE!D45,"")</f>
+        <v>2</v>
+      </c>
+      <c r="D46">
+        <f>IF(TDE!E45&gt;0,TDE!E45,"")</f>
+        <v>2</v>
+      </c>
+      <c r="E46">
+        <f>IF(TDE!F45&gt;0,TDE!F45,"")</f>
+        <v>2</v>
+      </c>
+      <c r="F46">
+        <f>IF(TDE!G45&gt;0,TDE!G45,"")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A47" t="str">
+        <f>IF(TDE!B49&gt;0,TDE!B49,"")</f>
+        <v>OUTSOURCE</v>
+      </c>
+      <c r="B47" t="str">
+        <f>IF(TDE!C49&gt;0,TDE!C49,"")</f>
+        <v/>
+      </c>
+      <c r="C47" t="str">
+        <f>IF(TDE!D49&gt;0,TDE!D49,"")</f>
+        <v/>
+      </c>
+      <c r="D47" t="str">
+        <f>IF(TDE!E49&gt;0,TDE!E49,"")</f>
+        <v/>
+      </c>
+      <c r="E47" t="str">
+        <f>IF(TDE!F49&gt;0,TDE!F49,"")</f>
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <f>IF(TDE!G49&gt;0,TDE!G49,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A51" t="str">
+        <f>TDE!A64</f>
+        <v>Talent &amp; Digital Enablement</v>
+      </c>
+      <c r="B51" t="str">
+        <f>TDE!C$61</f>
+        <v>JAN</v>
+      </c>
+      <c r="C51" t="str">
+        <f>TDE!D$61</f>
+        <v>FEB</v>
+      </c>
+      <c r="D51" t="str">
+        <f>TDE!E$61</f>
+        <v>MAR</v>
+      </c>
+      <c r="E51" t="str">
+        <f>TDE!F$61</f>
+        <v>APR</v>
+      </c>
+      <c r="F51" t="str">
+        <f>TDE!G$61</f>
+        <v>MAY</v>
+      </c>
+      <c r="G51" t="str">
+        <f>TDE!H$61</f>
+        <v>JUN</v>
+      </c>
+      <c r="H51" t="str">
+        <f>TDE!I$61</f>
+        <v>JUL</v>
+      </c>
+      <c r="I51" t="str">
+        <f>TDE!J$61</f>
+        <v>AUG</v>
+      </c>
+      <c r="J51" t="str">
+        <f>TDE!K$61</f>
+        <v>SEP</v>
+      </c>
+      <c r="K51" t="str">
+        <f>TDE!L$61</f>
+        <v>OCT</v>
+      </c>
+      <c r="L51" t="str">
+        <f>TDE!M$61</f>
+        <v>NOV</v>
+      </c>
+      <c r="M51" t="str">
+        <f>TDE!N$61</f>
+        <v>DEC</v>
+      </c>
+      <c r="N51" t="str">
+        <f>TDE!O$61</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O51" t="str">
+        <f>TDE!P$61</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P51" t="str">
+        <f>TDE!Q$61</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A52" t="str">
+        <f>IF(TDE!B64&gt;0,TDE!B64,"")</f>
+        <v>Staff</v>
+      </c>
+      <c r="B52">
+        <f>IF(TDE!C64&gt;0,TDE!C64,"")</f>
+        <v>1</v>
+      </c>
+      <c r="C52">
+        <f>IF(TDE!D64&gt;0,TDE!D64,"")</f>
+        <v>1</v>
+      </c>
+      <c r="D52">
+        <f>IF(TDE!E64&gt;0,TDE!E64,"")</f>
+        <v>1</v>
+      </c>
+      <c r="E52">
+        <f>IF(TDE!F64&gt;0,TDE!F64,"")</f>
+        <v>1</v>
+      </c>
+      <c r="F52">
+        <f>IF(TDE!G64&gt;0,TDE!G64,"")</f>
+        <v>1</v>
+      </c>
+      <c r="G52">
+        <f>IF(TDE!H64&gt;0,TDE!H64,"")</f>
+        <v>1</v>
+      </c>
+      <c r="H52">
+        <f>IF(TDE!I64&gt;0,TDE!I64,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I52">
+        <f>IF(TDE!J64&gt;0,TDE!J64,"")</f>
+        <v>1</v>
+      </c>
+      <c r="J52">
+        <f>IF(TDE!K64&gt;0,TDE!K64,"")</f>
+        <v>1</v>
+      </c>
+      <c r="K52">
+        <f>IF(TDE!L64&gt;0,TDE!L64,"")</f>
+        <v>1</v>
+      </c>
+      <c r="L52">
+        <f>IF(TDE!M64&gt;0,TDE!M64,"")</f>
+        <v>1</v>
+      </c>
+      <c r="M52">
+        <f>IF(TDE!N64&gt;0,TDE!N64,"")</f>
+        <v>1</v>
+      </c>
+      <c r="N52">
+        <f>IF(TDE!O64&gt;0,TDE!O64,"")</f>
+        <v>1</v>
+      </c>
+      <c r="O52">
+        <f>IF(TDE!P64&gt;0,TDE!P64,"")</f>
+        <v>1</v>
+      </c>
+      <c r="P52">
+        <f>IF(TDE!Q64&gt;0,TDE!Q64,"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A53" t="str">
+        <f>IF(TDE!B65&gt;0,TDE!B65,"")</f>
+        <v>Plan</v>
+      </c>
+      <c r="B53">
+        <f>IF(TDE!C65&gt;0,TDE!C65,"")</f>
+        <v>1</v>
+      </c>
+      <c r="C53">
+        <f>IF(TDE!D65&gt;0,TDE!D65,"")</f>
+        <v>1</v>
+      </c>
+      <c r="D53">
+        <f>IF(TDE!E65&gt;0,TDE!E65,"")</f>
+        <v>1</v>
+      </c>
+      <c r="E53">
+        <f>IF(TDE!F65&gt;0,TDE!F65,"")</f>
+        <v>1</v>
+      </c>
+      <c r="F53">
+        <f>IF(TDE!G65&gt;0,TDE!G65,"")</f>
+        <v>1</v>
+      </c>
+      <c r="G53">
+        <f>IF(TDE!H65&gt;0,TDE!H65,"")</f>
+        <v>1</v>
+      </c>
+      <c r="H53">
+        <f>IF(TDE!I65&gt;0,TDE!I65,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I53">
+        <f>IF(TDE!J65&gt;0,TDE!J65,"")</f>
+        <v>1</v>
+      </c>
+      <c r="J53">
+        <f>IF(TDE!K65&gt;0,TDE!K65,"")</f>
+        <v>1</v>
+      </c>
+      <c r="K53">
+        <f>IF(TDE!L65&gt;0,TDE!L65,"")</f>
+        <v>1</v>
+      </c>
+      <c r="L53">
+        <f>IF(TDE!M65&gt;0,TDE!M65,"")</f>
+        <v>1</v>
+      </c>
+      <c r="M53">
+        <f>IF(TDE!N65&gt;0,TDE!N65,"")</f>
+        <v>1</v>
+      </c>
+      <c r="N53">
+        <f>IF(TDE!O65&gt;0,TDE!O65,"")</f>
+        <v>1</v>
+      </c>
+      <c r="O53">
+        <f>IF(TDE!P65&gt;0,TDE!P65,"")</f>
+        <v>1</v>
+      </c>
+      <c r="P53">
+        <f>IF(TDE!Q65&gt;0,TDE!Q65,"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A61" t="str">
+        <f>TDE!A66</f>
+        <v>Financial Management</v>
+      </c>
+      <c r="B61" t="str">
+        <f>TDE!C$61</f>
+        <v>JAN</v>
+      </c>
+      <c r="C61" t="str">
+        <f>TDE!D$61</f>
+        <v>FEB</v>
+      </c>
+      <c r="D61" t="str">
+        <f>TDE!E$61</f>
+        <v>MAR</v>
+      </c>
+      <c r="E61" t="str">
+        <f>TDE!F$61</f>
+        <v>APR</v>
+      </c>
+      <c r="F61" t="str">
+        <f>TDE!G$61</f>
+        <v>MAY</v>
+      </c>
+      <c r="G61" t="str">
+        <f>TDE!H$61</f>
+        <v>JUN</v>
+      </c>
+      <c r="H61" t="str">
+        <f>TDE!I$61</f>
+        <v>JUL</v>
+      </c>
+      <c r="I61" t="str">
+        <f>TDE!J$61</f>
+        <v>AUG</v>
+      </c>
+      <c r="J61" t="str">
+        <f>TDE!K$61</f>
+        <v>SEP</v>
+      </c>
+      <c r="K61" t="str">
+        <f>TDE!L$61</f>
+        <v>OCT</v>
+      </c>
+      <c r="L61" t="str">
+        <f>TDE!M$61</f>
+        <v>NOV</v>
+      </c>
+      <c r="M61" t="str">
+        <f>TDE!N$61</f>
+        <v>DEC</v>
+      </c>
+      <c r="N61" t="str">
+        <f>TDE!O$61</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O61" t="str">
+        <f>TDE!P$61</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P61" t="str">
+        <f>TDE!Q$61</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A62" t="str">
+        <f>TDE!B66</f>
+        <v>Staff</v>
+      </c>
+      <c r="B62">
+        <f>TDE!C66</f>
+        <v>4</v>
+      </c>
+      <c r="C62">
+        <f>TDE!D66</f>
+        <v>4</v>
+      </c>
+      <c r="D62">
+        <f>TDE!E66</f>
+        <v>4</v>
+      </c>
+      <c r="E62">
+        <f>TDE!F66</f>
+        <v>4</v>
+      </c>
+      <c r="F62">
+        <f>TDE!G66</f>
+        <v>4</v>
+      </c>
+      <c r="G62">
+        <f>TDE!H66</f>
+        <v>4</v>
+      </c>
+      <c r="H62">
+        <f>TDE!I66</f>
+        <v>4</v>
+      </c>
+      <c r="I62">
+        <f>TDE!J66</f>
+        <v>4</v>
+      </c>
+      <c r="J62">
+        <f>TDE!K66</f>
+        <v>4</v>
+      </c>
+      <c r="K62">
+        <f>TDE!L66</f>
+        <v>4</v>
+      </c>
+      <c r="L62">
+        <f>TDE!M66</f>
+        <v>4</v>
+      </c>
+      <c r="M62">
+        <f>TDE!N66</f>
+        <v>4</v>
+      </c>
+      <c r="N62">
+        <f>TDE!O66</f>
+        <v>4</v>
+      </c>
+      <c r="O62">
+        <f>TDE!P66</f>
+        <v>4</v>
+      </c>
+      <c r="P62">
+        <f>TDE!Q66</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A63" t="str">
+        <f>TDE!B67</f>
+        <v>Plan</v>
+      </c>
+      <c r="B63">
+        <f>TDE!C67</f>
+        <v>4</v>
+      </c>
+      <c r="C63">
+        <f>TDE!D67</f>
+        <v>4</v>
+      </c>
+      <c r="D63">
+        <f>TDE!E67</f>
+        <v>4</v>
+      </c>
+      <c r="E63">
+        <f>TDE!F67</f>
+        <v>4</v>
+      </c>
+      <c r="F63">
+        <f>TDE!G67</f>
+        <v>4</v>
+      </c>
+      <c r="G63">
+        <f>TDE!H67</f>
+        <v>4</v>
+      </c>
+      <c r="H63">
+        <f>TDE!I67</f>
+        <v>4</v>
+      </c>
+      <c r="I63">
+        <f>TDE!J67</f>
+        <v>4</v>
+      </c>
+      <c r="J63">
+        <f>TDE!K67</f>
+        <v>4</v>
+      </c>
+      <c r="K63">
+        <f>TDE!L67</f>
+        <v>4</v>
+      </c>
+      <c r="L63">
+        <f>TDE!M67</f>
+        <v>4</v>
+      </c>
+      <c r="M63">
+        <f>TDE!N67</f>
+        <v>4</v>
+      </c>
+      <c r="N63">
+        <f>TDE!O67</f>
+        <v>4</v>
+      </c>
+      <c r="O63">
+        <f>TDE!P67</f>
+        <v>4</v>
+      </c>
+      <c r="P63">
+        <f>TDE!Q67</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A71" t="str">
+        <f>TDE!A68</f>
+        <v>Resource Management</v>
+      </c>
+      <c r="B71" t="str">
+        <f>TDE!C$61</f>
+        <v>JAN</v>
+      </c>
+      <c r="C71" t="str">
+        <f>TDE!D$61</f>
+        <v>FEB</v>
+      </c>
+      <c r="D71" t="str">
+        <f>TDE!E$61</f>
+        <v>MAR</v>
+      </c>
+      <c r="E71" t="str">
+        <f>TDE!F$61</f>
+        <v>APR</v>
+      </c>
+      <c r="F71" t="str">
+        <f>TDE!G$61</f>
+        <v>MAY</v>
+      </c>
+      <c r="G71" t="str">
+        <f>TDE!H$61</f>
+        <v>JUN</v>
+      </c>
+      <c r="H71" t="str">
+        <f>TDE!I$61</f>
+        <v>JUL</v>
+      </c>
+      <c r="I71" t="str">
+        <f>TDE!J$61</f>
+        <v>AUG</v>
+      </c>
+      <c r="J71" t="str">
+        <f>TDE!K$61</f>
+        <v>SEP</v>
+      </c>
+      <c r="K71" t="str">
+        <f>TDE!L$61</f>
+        <v>OCT</v>
+      </c>
+      <c r="L71" t="str">
+        <f>TDE!M$61</f>
+        <v>NOV</v>
+      </c>
+      <c r="M71" t="str">
+        <f>TDE!N$61</f>
+        <v>DEC</v>
+      </c>
+      <c r="N71" t="str">
+        <f>TDE!O$61</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O71" t="str">
+        <f>TDE!P$61</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P71" t="str">
+        <f>TDE!Q$61</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A72" t="str">
+        <f>TDE!B68</f>
+        <v>Staff</v>
+      </c>
+      <c r="B72">
+        <f>TDE!C68</f>
+        <v>5</v>
+      </c>
+      <c r="C72">
+        <f>TDE!D68</f>
+        <v>5</v>
+      </c>
+      <c r="D72">
+        <f>TDE!E68</f>
+        <v>5</v>
+      </c>
+      <c r="E72">
+        <f>TDE!F68</f>
+        <v>5</v>
+      </c>
+      <c r="F72">
+        <f>TDE!G68</f>
+        <v>5</v>
+      </c>
+      <c r="G72">
+        <f>TDE!H68</f>
+        <v>5</v>
+      </c>
+      <c r="H72">
+        <f>TDE!I68</f>
+        <v>5</v>
+      </c>
+      <c r="I72">
+        <f>TDE!J68</f>
+        <v>5</v>
+      </c>
+      <c r="J72">
+        <f>TDE!K68</f>
+        <v>5</v>
+      </c>
+      <c r="K72">
+        <f>TDE!L68</f>
+        <v>5</v>
+      </c>
+      <c r="L72">
+        <f>TDE!M68</f>
+        <v>5</v>
+      </c>
+      <c r="M72">
+        <f>TDE!N68</f>
+        <v>5</v>
+      </c>
+      <c r="N72">
+        <f>TDE!O68</f>
+        <v>5</v>
+      </c>
+      <c r="O72">
+        <f>TDE!P68</f>
+        <v>5</v>
+      </c>
+      <c r="P72">
+        <f>TDE!Q68</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A73" t="str">
+        <f>TDE!B69</f>
+        <v>Plan</v>
+      </c>
+      <c r="B73">
+        <f>TDE!C69</f>
+        <v>5</v>
+      </c>
+      <c r="C73">
+        <f>TDE!D69</f>
+        <v>5</v>
+      </c>
+      <c r="D73">
+        <f>TDE!E69</f>
+        <v>5</v>
+      </c>
+      <c r="E73">
+        <f>TDE!F69</f>
+        <v>5</v>
+      </c>
+      <c r="F73">
+        <f>TDE!G69</f>
+        <v>5</v>
+      </c>
+      <c r="G73">
+        <f>TDE!H69</f>
+        <v>5</v>
+      </c>
+      <c r="H73">
+        <f>TDE!I69</f>
+        <v>5</v>
+      </c>
+      <c r="I73">
+        <f>TDE!J69</f>
+        <v>5</v>
+      </c>
+      <c r="J73">
+        <f>TDE!K69</f>
+        <v>5</v>
+      </c>
+      <c r="K73">
+        <f>TDE!L69</f>
+        <v>5</v>
+      </c>
+      <c r="L73">
+        <f>TDE!M69</f>
+        <v>5</v>
+      </c>
+      <c r="M73">
+        <f>TDE!N69</f>
+        <v>5</v>
+      </c>
+      <c r="N73">
+        <f>TDE!O69</f>
+        <v>5</v>
+      </c>
+      <c r="O73">
+        <f>TDE!P69</f>
+        <v>5</v>
+      </c>
+      <c r="P73">
+        <f>TDE!Q69</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A81" t="str">
+        <f>TDE!A74</f>
+        <v>Talent Experience &amp; Development</v>
+      </c>
+      <c r="B81" t="str">
+        <f>TDE!C$61</f>
+        <v>JAN</v>
+      </c>
+      <c r="C81" t="str">
+        <f>TDE!D$61</f>
+        <v>FEB</v>
+      </c>
+      <c r="D81" t="str">
+        <f>TDE!E$61</f>
+        <v>MAR</v>
+      </c>
+      <c r="E81" t="str">
+        <f>TDE!F$61</f>
+        <v>APR</v>
+      </c>
+      <c r="F81" t="str">
+        <f>TDE!G$61</f>
+        <v>MAY</v>
+      </c>
+      <c r="G81" t="str">
+        <f>TDE!H$61</f>
+        <v>JUN</v>
+      </c>
+      <c r="H81" t="str">
+        <f>TDE!I$61</f>
+        <v>JUL</v>
+      </c>
+      <c r="I81" t="str">
+        <f>TDE!J$61</f>
+        <v>AUG</v>
+      </c>
+      <c r="J81" t="str">
+        <f>TDE!K$61</f>
+        <v>SEP</v>
+      </c>
+      <c r="K81" t="str">
+        <f>TDE!L$61</f>
+        <v>OCT</v>
+      </c>
+      <c r="L81" t="str">
+        <f>TDE!M$61</f>
+        <v>NOV</v>
+      </c>
+      <c r="M81" t="str">
+        <f>TDE!N$61</f>
+        <v>DEC</v>
+      </c>
+      <c r="N81" t="str">
+        <f>TDE!O$61</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O81" t="str">
+        <f>TDE!P$61</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P81" t="str">
+        <f>TDE!Q$61</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A82" t="str">
+        <f>TDE!B74</f>
+        <v>Staff</v>
+      </c>
+      <c r="B82">
+        <f>TDE!C74</f>
+        <v>3</v>
+      </c>
+      <c r="C82">
+        <f>TDE!D74</f>
+        <v>3</v>
+      </c>
+      <c r="D82">
+        <f>TDE!E74</f>
+        <v>3</v>
+      </c>
+      <c r="E82">
+        <f>TDE!F74</f>
+        <v>3</v>
+      </c>
+      <c r="F82">
+        <f>TDE!G74</f>
+        <v>3</v>
+      </c>
+      <c r="G82">
+        <f>TDE!H74</f>
+        <v>3</v>
+      </c>
+      <c r="H82">
+        <f>TDE!I74</f>
+        <v>3</v>
+      </c>
+      <c r="I82">
+        <f>TDE!J74</f>
+        <v>3</v>
+      </c>
+      <c r="J82">
+        <f>TDE!K74</f>
+        <v>3</v>
+      </c>
+      <c r="K82">
+        <f>TDE!L74</f>
+        <v>3</v>
+      </c>
+      <c r="L82">
+        <f>TDE!M74</f>
+        <v>3</v>
+      </c>
+      <c r="M82">
+        <f>TDE!N74</f>
+        <v>3</v>
+      </c>
+      <c r="N82">
+        <f>TDE!O74</f>
+        <v>3</v>
+      </c>
+      <c r="O82">
+        <f>TDE!P74</f>
+        <v>3</v>
+      </c>
+      <c r="P82">
+        <f>TDE!Q74</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A83" t="str">
+        <f>TDE!B75</f>
+        <v>Plan</v>
+      </c>
+      <c r="B83">
+        <f>TDE!C75</f>
+        <v>3</v>
+      </c>
+      <c r="C83">
+        <f>TDE!D75</f>
+        <v>3</v>
+      </c>
+      <c r="D83">
+        <f>TDE!E75</f>
+        <v>3</v>
+      </c>
+      <c r="E83">
+        <f>TDE!F75</f>
+        <v>3</v>
+      </c>
+      <c r="F83">
+        <f>TDE!G75</f>
+        <v>3</v>
+      </c>
+      <c r="G83">
+        <f>TDE!H75</f>
+        <v>3</v>
+      </c>
+      <c r="H83">
+        <f>TDE!I75</f>
+        <v>3</v>
+      </c>
+      <c r="I83">
+        <f>TDE!J75</f>
+        <v>3</v>
+      </c>
+      <c r="J83">
+        <f>TDE!K75</f>
+        <v>3</v>
+      </c>
+      <c r="K83">
+        <f>TDE!L75</f>
+        <v>3</v>
+      </c>
+      <c r="L83">
+        <f>TDE!M75</f>
+        <v>3</v>
+      </c>
+      <c r="M83">
+        <f>TDE!N75</f>
+        <v>3</v>
+      </c>
+      <c r="N83">
+        <f>TDE!O75</f>
+        <v>3</v>
+      </c>
+      <c r="O83">
+        <f>TDE!P75</f>
+        <v>3</v>
+      </c>
+      <c r="P83">
+        <f>TDE!Q75</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A91" t="str">
+        <f>TDE!A80</f>
+        <v>Center of Excellences</v>
+      </c>
+      <c r="B91" t="str">
+        <f>TDE!C$61</f>
+        <v>JAN</v>
+      </c>
+      <c r="C91" t="str">
+        <f>TDE!D$61</f>
+        <v>FEB</v>
+      </c>
+      <c r="D91" t="str">
+        <f>TDE!E$61</f>
+        <v>MAR</v>
+      </c>
+      <c r="E91" t="str">
+        <f>TDE!F$61</f>
+        <v>APR</v>
+      </c>
+      <c r="F91" t="str">
+        <f>TDE!G$61</f>
+        <v>MAY</v>
+      </c>
+      <c r="G91" t="str">
+        <f>TDE!H$61</f>
+        <v>JUN</v>
+      </c>
+      <c r="H91" t="str">
+        <f>TDE!I$61</f>
+        <v>JUL</v>
+      </c>
+      <c r="I91" t="str">
+        <f>TDE!J$61</f>
+        <v>AUG</v>
+      </c>
+      <c r="J91" t="str">
+        <f>TDE!K$61</f>
+        <v>SEP</v>
+      </c>
+      <c r="K91" t="str">
+        <f>TDE!L$61</f>
+        <v>OCT</v>
+      </c>
+      <c r="L91" t="str">
+        <f>TDE!M$61</f>
+        <v>NOV</v>
+      </c>
+      <c r="M91" t="str">
+        <f>TDE!N$61</f>
+        <v>DEC</v>
+      </c>
+      <c r="N91" t="str">
+        <f>TDE!O$61</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O91" t="str">
+        <f>TDE!P$61</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P91" t="str">
+        <f>TDE!Q$61</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A92" t="str">
+        <f>TDE!B80</f>
+        <v>Staff</v>
+      </c>
+      <c r="B92">
+        <f>TDE!C80</f>
+        <v>2</v>
+      </c>
+      <c r="C92">
+        <f>TDE!D80</f>
+        <v>2</v>
+      </c>
+      <c r="D92">
+        <f>TDE!E80</f>
+        <v>2</v>
+      </c>
+      <c r="E92">
+        <f>TDE!F80</f>
+        <v>3</v>
+      </c>
+      <c r="F92">
+        <f>TDE!G80</f>
+        <v>3</v>
+      </c>
+      <c r="G92">
+        <f>TDE!H80</f>
+        <v>3</v>
+      </c>
+      <c r="H92">
+        <f>TDE!I80</f>
+        <v>3</v>
+      </c>
+      <c r="I92">
+        <f>TDE!J80</f>
+        <v>3</v>
+      </c>
+      <c r="J92">
+        <f>TDE!K80</f>
+        <v>3</v>
+      </c>
+      <c r="K92">
+        <f>TDE!L80</f>
+        <v>3</v>
+      </c>
+      <c r="L92">
+        <f>TDE!M80</f>
+        <v>3</v>
+      </c>
+      <c r="M92">
+        <f>TDE!N80</f>
+        <v>3</v>
+      </c>
+      <c r="N92">
+        <f>TDE!O80</f>
+        <v>3</v>
+      </c>
+      <c r="O92">
+        <f>TDE!P80</f>
+        <v>3</v>
+      </c>
+      <c r="P92">
+        <f>TDE!Q80</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A93" t="str">
+        <f>TDE!B81</f>
+        <v>Plan</v>
+      </c>
+      <c r="B93">
+        <f>TDE!C81</f>
+        <v>2</v>
+      </c>
+      <c r="C93">
+        <f>TDE!D81</f>
+        <v>2</v>
+      </c>
+      <c r="D93">
+        <f>TDE!E81</f>
+        <v>2</v>
+      </c>
+      <c r="E93">
+        <f>TDE!F81</f>
+        <v>3</v>
+      </c>
+      <c r="F93">
+        <f>TDE!G81</f>
+        <v>3</v>
+      </c>
+      <c r="G93">
+        <f>TDE!H81</f>
+        <v>3</v>
+      </c>
+      <c r="H93">
+        <f>TDE!I81</f>
+        <v>3</v>
+      </c>
+      <c r="I93">
+        <f>TDE!J81</f>
+        <v>3</v>
+      </c>
+      <c r="J93">
+        <f>TDE!K81</f>
+        <v>3</v>
+      </c>
+      <c r="K93">
+        <f>TDE!L81</f>
+        <v>3</v>
+      </c>
+      <c r="L93">
+        <f>TDE!M81</f>
+        <v>3</v>
+      </c>
+      <c r="M93">
+        <f>TDE!N81</f>
+        <v>3</v>
+      </c>
+      <c r="N93">
+        <f>TDE!O81</f>
+        <v>3</v>
+      </c>
+      <c r="O93">
+        <f>TDE!P81</f>
+        <v>3</v>
+      </c>
+      <c r="P93">
+        <f>TDE!Q81</f>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -9867,40 +14763,40 @@
         <v>47</v>
       </c>
       <c r="F3" s="8">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G3" s="8">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H3" s="8">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I3" s="8">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J3" s="8">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K3" s="8">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L3" s="8">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M3" s="8">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N3" s="8">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O3" s="8">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P3" s="8">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Q3" s="8">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.2">
@@ -12160,51 +17056,51 @@
       </c>
       <c r="E3">
         <f>IF(PSE!F3&gt;0,PSE!F3,"")</f>
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F3">
         <f>IF(PSE!G3&gt;0,PSE!G3,"")</f>
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G3">
         <f>IF(PSE!H3&gt;0,PSE!H3,"")</f>
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H3">
         <f>IF(PSE!I3&gt;0,PSE!I3,"")</f>
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I3">
         <f>IF(PSE!J3&gt;0,PSE!J3,"")</f>
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J3">
         <f>IF(PSE!K3&gt;0,PSE!K3,"")</f>
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K3">
         <f>IF(PSE!L3&gt;0,PSE!L3,"")</f>
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L3">
         <f>IF(PSE!M3&gt;0,PSE!M3,"")</f>
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M3">
         <f>IF(PSE!N3&gt;0,PSE!N3,"")</f>
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N3">
         <f>IF(PSE!O3&gt;0,PSE!O3,"")</f>
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O3">
         <f>IF(PSE!P3&gt;0,PSE!P3,"")</f>
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P3">
         <f>IF(PSE!Q3&gt;0,PSE!Q3,"")</f>
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
@@ -20179,40 +25075,40 @@
         <v>20</v>
       </c>
       <c r="F3" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H3" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I3" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J3" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K3" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L3" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M3" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N3" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O3" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P3" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q3" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.2">

--- a/workforceresult.xlsx
+++ b/workforceresult.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miiintra/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBCFA21D-FA6E-1D4A-A696-6A097918C605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A4DBF4-1812-5841-8D9E-5598B497B7E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14500" yWindow="620" windowWidth="28800" windowHeight="21200" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
+    <workbookView xWindow="14500" yWindow="620" windowWidth="28800" windowHeight="21200" activeTab="11" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
   </bookViews>
   <sheets>
     <sheet name="ALL" sheetId="1" r:id="rId1"/>
@@ -7223,7 +7223,7 @@
   <sheetPr>
     <tabColor theme="3" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:P93"/>
+  <dimension ref="A1:P83"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.6640625" bestFit="1" customWidth="1"/>
@@ -8647,8 +8647,8 @@
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A51" t="str">
-        <f>TDE!A64</f>
-        <v>Talent &amp; Digital Enablement</v>
+        <f>TDE!A66</f>
+        <v>Financial Management</v>
       </c>
       <c r="B51" t="str">
         <f>TDE!C$61</f>
@@ -8713,140 +8713,140 @@
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A52" t="str">
-        <f>IF(TDE!B64&gt;0,TDE!B64,"")</f>
+        <f>TDE!B66</f>
         <v>Staff</v>
       </c>
       <c r="B52">
-        <f>IF(TDE!C64&gt;0,TDE!C64,"")</f>
-        <v>1</v>
+        <f>TDE!C66</f>
+        <v>4</v>
       </c>
       <c r="C52">
-        <f>IF(TDE!D64&gt;0,TDE!D64,"")</f>
-        <v>1</v>
+        <f>TDE!D66</f>
+        <v>4</v>
       </c>
       <c r="D52">
-        <f>IF(TDE!E64&gt;0,TDE!E64,"")</f>
-        <v>1</v>
+        <f>TDE!E66</f>
+        <v>4</v>
       </c>
       <c r="E52">
-        <f>IF(TDE!F64&gt;0,TDE!F64,"")</f>
-        <v>1</v>
+        <f>TDE!F66</f>
+        <v>4</v>
       </c>
       <c r="F52">
-        <f>IF(TDE!G64&gt;0,TDE!G64,"")</f>
-        <v>1</v>
+        <f>TDE!G66</f>
+        <v>4</v>
       </c>
       <c r="G52">
-        <f>IF(TDE!H64&gt;0,TDE!H64,"")</f>
-        <v>1</v>
+        <f>TDE!H66</f>
+        <v>4</v>
       </c>
       <c r="H52">
-        <f>IF(TDE!I64&gt;0,TDE!I64,"")</f>
-        <v>1</v>
+        <f>TDE!I66</f>
+        <v>4</v>
       </c>
       <c r="I52">
-        <f>IF(TDE!J64&gt;0,TDE!J64,"")</f>
-        <v>1</v>
+        <f>TDE!J66</f>
+        <v>4</v>
       </c>
       <c r="J52">
-        <f>IF(TDE!K64&gt;0,TDE!K64,"")</f>
-        <v>1</v>
+        <f>TDE!K66</f>
+        <v>4</v>
       </c>
       <c r="K52">
-        <f>IF(TDE!L64&gt;0,TDE!L64,"")</f>
-        <v>1</v>
+        <f>TDE!L66</f>
+        <v>4</v>
       </c>
       <c r="L52">
-        <f>IF(TDE!M64&gt;0,TDE!M64,"")</f>
-        <v>1</v>
+        <f>TDE!M66</f>
+        <v>4</v>
       </c>
       <c r="M52">
-        <f>IF(TDE!N64&gt;0,TDE!N64,"")</f>
-        <v>1</v>
+        <f>TDE!N66</f>
+        <v>4</v>
       </c>
       <c r="N52">
-        <f>IF(TDE!O64&gt;0,TDE!O64,"")</f>
-        <v>1</v>
+        <f>TDE!O66</f>
+        <v>4</v>
       </c>
       <c r="O52">
-        <f>IF(TDE!P64&gt;0,TDE!P64,"")</f>
-        <v>1</v>
+        <f>TDE!P66</f>
+        <v>4</v>
       </c>
       <c r="P52">
-        <f>IF(TDE!Q64&gt;0,TDE!Q64,"")</f>
-        <v>1</v>
+        <f>TDE!Q66</f>
+        <v>4</v>
       </c>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A53" t="str">
-        <f>IF(TDE!B65&gt;0,TDE!B65,"")</f>
+        <f>TDE!B67</f>
         <v>Plan</v>
       </c>
       <c r="B53">
-        <f>IF(TDE!C65&gt;0,TDE!C65,"")</f>
-        <v>1</v>
+        <f>TDE!C67</f>
+        <v>4</v>
       </c>
       <c r="C53">
-        <f>IF(TDE!D65&gt;0,TDE!D65,"")</f>
-        <v>1</v>
+        <f>TDE!D67</f>
+        <v>4</v>
       </c>
       <c r="D53">
-        <f>IF(TDE!E65&gt;0,TDE!E65,"")</f>
-        <v>1</v>
+        <f>TDE!E67</f>
+        <v>4</v>
       </c>
       <c r="E53">
-        <f>IF(TDE!F65&gt;0,TDE!F65,"")</f>
-        <v>1</v>
+        <f>TDE!F67</f>
+        <v>4</v>
       </c>
       <c r="F53">
-        <f>IF(TDE!G65&gt;0,TDE!G65,"")</f>
-        <v>1</v>
+        <f>TDE!G67</f>
+        <v>4</v>
       </c>
       <c r="G53">
-        <f>IF(TDE!H65&gt;0,TDE!H65,"")</f>
-        <v>1</v>
+        <f>TDE!H67</f>
+        <v>4</v>
       </c>
       <c r="H53">
-        <f>IF(TDE!I65&gt;0,TDE!I65,"")</f>
-        <v>1</v>
+        <f>TDE!I67</f>
+        <v>4</v>
       </c>
       <c r="I53">
-        <f>IF(TDE!J65&gt;0,TDE!J65,"")</f>
-        <v>1</v>
+        <f>TDE!J67</f>
+        <v>4</v>
       </c>
       <c r="J53">
-        <f>IF(TDE!K65&gt;0,TDE!K65,"")</f>
-        <v>1</v>
+        <f>TDE!K67</f>
+        <v>4</v>
       </c>
       <c r="K53">
-        <f>IF(TDE!L65&gt;0,TDE!L65,"")</f>
-        <v>1</v>
+        <f>TDE!L67</f>
+        <v>4</v>
       </c>
       <c r="L53">
-        <f>IF(TDE!M65&gt;0,TDE!M65,"")</f>
-        <v>1</v>
+        <f>TDE!M67</f>
+        <v>4</v>
       </c>
       <c r="M53">
-        <f>IF(TDE!N65&gt;0,TDE!N65,"")</f>
-        <v>1</v>
+        <f>TDE!N67</f>
+        <v>4</v>
       </c>
       <c r="N53">
-        <f>IF(TDE!O65&gt;0,TDE!O65,"")</f>
-        <v>1</v>
+        <f>TDE!O67</f>
+        <v>4</v>
       </c>
       <c r="O53">
-        <f>IF(TDE!P65&gt;0,TDE!P65,"")</f>
-        <v>1</v>
+        <f>TDE!P67</f>
+        <v>4</v>
       </c>
       <c r="P53">
-        <f>IF(TDE!Q65&gt;0,TDE!Q65,"")</f>
-        <v>1</v>
+        <f>TDE!Q67</f>
+        <v>4</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A61" t="str">
-        <f>TDE!A66</f>
-        <v>Financial Management</v>
+        <f>TDE!A68</f>
+        <v>Resource Management</v>
       </c>
       <c r="B61" t="str">
         <f>TDE!C$61</f>
@@ -8911,140 +8911,140 @@
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A62" t="str">
-        <f>TDE!B66</f>
+        <f>TDE!B68</f>
         <v>Staff</v>
       </c>
       <c r="B62">
-        <f>TDE!C66</f>
-        <v>4</v>
+        <f>TDE!C68</f>
+        <v>5</v>
       </c>
       <c r="C62">
-        <f>TDE!D66</f>
-        <v>4</v>
+        <f>TDE!D68</f>
+        <v>5</v>
       </c>
       <c r="D62">
-        <f>TDE!E66</f>
-        <v>4</v>
+        <f>TDE!E68</f>
+        <v>5</v>
       </c>
       <c r="E62">
-        <f>TDE!F66</f>
-        <v>4</v>
+        <f>TDE!F68</f>
+        <v>5</v>
       </c>
       <c r="F62">
-        <f>TDE!G66</f>
-        <v>4</v>
+        <f>TDE!G68</f>
+        <v>5</v>
       </c>
       <c r="G62">
-        <f>TDE!H66</f>
-        <v>4</v>
+        <f>TDE!H68</f>
+        <v>5</v>
       </c>
       <c r="H62">
-        <f>TDE!I66</f>
-        <v>4</v>
+        <f>TDE!I68</f>
+        <v>5</v>
       </c>
       <c r="I62">
-        <f>TDE!J66</f>
-        <v>4</v>
+        <f>TDE!J68</f>
+        <v>5</v>
       </c>
       <c r="J62">
-        <f>TDE!K66</f>
-        <v>4</v>
+        <f>TDE!K68</f>
+        <v>5</v>
       </c>
       <c r="K62">
-        <f>TDE!L66</f>
-        <v>4</v>
+        <f>TDE!L68</f>
+        <v>5</v>
       </c>
       <c r="L62">
-        <f>TDE!M66</f>
-        <v>4</v>
+        <f>TDE!M68</f>
+        <v>5</v>
       </c>
       <c r="M62">
-        <f>TDE!N66</f>
-        <v>4</v>
+        <f>TDE!N68</f>
+        <v>5</v>
       </c>
       <c r="N62">
-        <f>TDE!O66</f>
-        <v>4</v>
+        <f>TDE!O68</f>
+        <v>5</v>
       </c>
       <c r="O62">
-        <f>TDE!P66</f>
-        <v>4</v>
+        <f>TDE!P68</f>
+        <v>5</v>
       </c>
       <c r="P62">
-        <f>TDE!Q66</f>
-        <v>4</v>
+        <f>TDE!Q68</f>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A63" t="str">
-        <f>TDE!B67</f>
+        <f>TDE!B69</f>
         <v>Plan</v>
       </c>
       <c r="B63">
-        <f>TDE!C67</f>
-        <v>4</v>
+        <f>TDE!C69</f>
+        <v>5</v>
       </c>
       <c r="C63">
-        <f>TDE!D67</f>
-        <v>4</v>
+        <f>TDE!D69</f>
+        <v>5</v>
       </c>
       <c r="D63">
-        <f>TDE!E67</f>
-        <v>4</v>
+        <f>TDE!E69</f>
+        <v>5</v>
       </c>
       <c r="E63">
-        <f>TDE!F67</f>
-        <v>4</v>
+        <f>TDE!F69</f>
+        <v>5</v>
       </c>
       <c r="F63">
-        <f>TDE!G67</f>
-        <v>4</v>
+        <f>TDE!G69</f>
+        <v>5</v>
       </c>
       <c r="G63">
-        <f>TDE!H67</f>
-        <v>4</v>
+        <f>TDE!H69</f>
+        <v>5</v>
       </c>
       <c r="H63">
-        <f>TDE!I67</f>
-        <v>4</v>
+        <f>TDE!I69</f>
+        <v>5</v>
       </c>
       <c r="I63">
-        <f>TDE!J67</f>
-        <v>4</v>
+        <f>TDE!J69</f>
+        <v>5</v>
       </c>
       <c r="J63">
-        <f>TDE!K67</f>
-        <v>4</v>
+        <f>TDE!K69</f>
+        <v>5</v>
       </c>
       <c r="K63">
-        <f>TDE!L67</f>
-        <v>4</v>
+        <f>TDE!L69</f>
+        <v>5</v>
       </c>
       <c r="L63">
-        <f>TDE!M67</f>
-        <v>4</v>
+        <f>TDE!M69</f>
+        <v>5</v>
       </c>
       <c r="M63">
-        <f>TDE!N67</f>
-        <v>4</v>
+        <f>TDE!N69</f>
+        <v>5</v>
       </c>
       <c r="N63">
-        <f>TDE!O67</f>
-        <v>4</v>
+        <f>TDE!O69</f>
+        <v>5</v>
       </c>
       <c r="O63">
-        <f>TDE!P67</f>
-        <v>4</v>
+        <f>TDE!P69</f>
+        <v>5</v>
       </c>
       <c r="P63">
-        <f>TDE!Q67</f>
-        <v>4</v>
+        <f>TDE!Q69</f>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A71" t="str">
-        <f>TDE!A68</f>
-        <v>Resource Management</v>
+        <f>TDE!A74</f>
+        <v>Talent Experience &amp; Development</v>
       </c>
       <c r="B71" t="str">
         <f>TDE!C$61</f>
@@ -9109,140 +9109,140 @@
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A72" t="str">
-        <f>TDE!B68</f>
+        <f>TDE!B74</f>
         <v>Staff</v>
       </c>
       <c r="B72">
-        <f>TDE!C68</f>
-        <v>5</v>
+        <f>TDE!C74</f>
+        <v>3</v>
       </c>
       <c r="C72">
-        <f>TDE!D68</f>
-        <v>5</v>
+        <f>TDE!D74</f>
+        <v>3</v>
       </c>
       <c r="D72">
-        <f>TDE!E68</f>
-        <v>5</v>
+        <f>TDE!E74</f>
+        <v>3</v>
       </c>
       <c r="E72">
-        <f>TDE!F68</f>
-        <v>5</v>
+        <f>TDE!F74</f>
+        <v>3</v>
       </c>
       <c r="F72">
-        <f>TDE!G68</f>
-        <v>5</v>
+        <f>TDE!G74</f>
+        <v>3</v>
       </c>
       <c r="G72">
-        <f>TDE!H68</f>
-        <v>5</v>
+        <f>TDE!H74</f>
+        <v>3</v>
       </c>
       <c r="H72">
-        <f>TDE!I68</f>
-        <v>5</v>
+        <f>TDE!I74</f>
+        <v>3</v>
       </c>
       <c r="I72">
-        <f>TDE!J68</f>
-        <v>5</v>
+        <f>TDE!J74</f>
+        <v>3</v>
       </c>
       <c r="J72">
-        <f>TDE!K68</f>
-        <v>5</v>
+        <f>TDE!K74</f>
+        <v>3</v>
       </c>
       <c r="K72">
-        <f>TDE!L68</f>
-        <v>5</v>
+        <f>TDE!L74</f>
+        <v>3</v>
       </c>
       <c r="L72">
-        <f>TDE!M68</f>
-        <v>5</v>
+        <f>TDE!M74</f>
+        <v>3</v>
       </c>
       <c r="M72">
-        <f>TDE!N68</f>
-        <v>5</v>
+        <f>TDE!N74</f>
+        <v>3</v>
       </c>
       <c r="N72">
-        <f>TDE!O68</f>
-        <v>5</v>
+        <f>TDE!O74</f>
+        <v>3</v>
       </c>
       <c r="O72">
-        <f>TDE!P68</f>
-        <v>5</v>
+        <f>TDE!P74</f>
+        <v>3</v>
       </c>
       <c r="P72">
-        <f>TDE!Q68</f>
-        <v>5</v>
+        <f>TDE!Q74</f>
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A73" t="str">
-        <f>TDE!B69</f>
+        <f>TDE!B75</f>
         <v>Plan</v>
       </c>
       <c r="B73">
-        <f>TDE!C69</f>
-        <v>5</v>
+        <f>TDE!C75</f>
+        <v>3</v>
       </c>
       <c r="C73">
-        <f>TDE!D69</f>
-        <v>5</v>
+        <f>TDE!D75</f>
+        <v>3</v>
       </c>
       <c r="D73">
-        <f>TDE!E69</f>
-        <v>5</v>
+        <f>TDE!E75</f>
+        <v>3</v>
       </c>
       <c r="E73">
-        <f>TDE!F69</f>
-        <v>5</v>
+        <f>TDE!F75</f>
+        <v>3</v>
       </c>
       <c r="F73">
-        <f>TDE!G69</f>
-        <v>5</v>
+        <f>TDE!G75</f>
+        <v>3</v>
       </c>
       <c r="G73">
-        <f>TDE!H69</f>
-        <v>5</v>
+        <f>TDE!H75</f>
+        <v>3</v>
       </c>
       <c r="H73">
-        <f>TDE!I69</f>
-        <v>5</v>
+        <f>TDE!I75</f>
+        <v>3</v>
       </c>
       <c r="I73">
-        <f>TDE!J69</f>
-        <v>5</v>
+        <f>TDE!J75</f>
+        <v>3</v>
       </c>
       <c r="J73">
-        <f>TDE!K69</f>
-        <v>5</v>
+        <f>TDE!K75</f>
+        <v>3</v>
       </c>
       <c r="K73">
-        <f>TDE!L69</f>
-        <v>5</v>
+        <f>TDE!L75</f>
+        <v>3</v>
       </c>
       <c r="L73">
-        <f>TDE!M69</f>
-        <v>5</v>
+        <f>TDE!M75</f>
+        <v>3</v>
       </c>
       <c r="M73">
-        <f>TDE!N69</f>
-        <v>5</v>
+        <f>TDE!N75</f>
+        <v>3</v>
       </c>
       <c r="N73">
-        <f>TDE!O69</f>
-        <v>5</v>
+        <f>TDE!O75</f>
+        <v>3</v>
       </c>
       <c r="O73">
-        <f>TDE!P69</f>
-        <v>5</v>
+        <f>TDE!P75</f>
+        <v>3</v>
       </c>
       <c r="P73">
-        <f>TDE!Q69</f>
-        <v>5</v>
+        <f>TDE!Q75</f>
+        <v>3</v>
       </c>
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A81" t="str">
-        <f>TDE!A74</f>
-        <v>Talent Experience &amp; Development</v>
+        <f>TDE!A80</f>
+        <v>Center of Excellences</v>
       </c>
       <c r="B81" t="str">
         <f>TDE!C$61</f>
@@ -9307,330 +9307,132 @@
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A82" t="str">
-        <f>TDE!B74</f>
+        <f>TDE!B80</f>
         <v>Staff</v>
       </c>
       <c r="B82">
-        <f>TDE!C74</f>
-        <v>3</v>
+        <f>TDE!C80</f>
+        <v>2</v>
       </c>
       <c r="C82">
-        <f>TDE!D74</f>
-        <v>3</v>
+        <f>TDE!D80</f>
+        <v>2</v>
       </c>
       <c r="D82">
-        <f>TDE!E74</f>
-        <v>3</v>
+        <f>TDE!E80</f>
+        <v>2</v>
       </c>
       <c r="E82">
-        <f>TDE!F74</f>
+        <f>TDE!F80</f>
         <v>3</v>
       </c>
       <c r="F82">
-        <f>TDE!G74</f>
+        <f>TDE!G80</f>
         <v>3</v>
       </c>
       <c r="G82">
-        <f>TDE!H74</f>
+        <f>TDE!H80</f>
         <v>3</v>
       </c>
       <c r="H82">
-        <f>TDE!I74</f>
+        <f>TDE!I80</f>
         <v>3</v>
       </c>
       <c r="I82">
-        <f>TDE!J74</f>
+        <f>TDE!J80</f>
         <v>3</v>
       </c>
       <c r="J82">
-        <f>TDE!K74</f>
+        <f>TDE!K80</f>
         <v>3</v>
       </c>
       <c r="K82">
-        <f>TDE!L74</f>
+        <f>TDE!L80</f>
         <v>3</v>
       </c>
       <c r="L82">
-        <f>TDE!M74</f>
+        <f>TDE!M80</f>
         <v>3</v>
       </c>
       <c r="M82">
-        <f>TDE!N74</f>
+        <f>TDE!N80</f>
         <v>3</v>
       </c>
       <c r="N82">
-        <f>TDE!O74</f>
+        <f>TDE!O80</f>
         <v>3</v>
       </c>
       <c r="O82">
-        <f>TDE!P74</f>
+        <f>TDE!P80</f>
         <v>3</v>
       </c>
       <c r="P82">
-        <f>TDE!Q74</f>
+        <f>TDE!Q80</f>
         <v>3</v>
       </c>
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A83" t="str">
-        <f>TDE!B75</f>
-        <v>Plan</v>
-      </c>
-      <c r="B83">
-        <f>TDE!C75</f>
-        <v>3</v>
-      </c>
-      <c r="C83">
-        <f>TDE!D75</f>
-        <v>3</v>
-      </c>
-      <c r="D83">
-        <f>TDE!E75</f>
-        <v>3</v>
-      </c>
-      <c r="E83">
-        <f>TDE!F75</f>
-        <v>3</v>
-      </c>
-      <c r="F83">
-        <f>TDE!G75</f>
-        <v>3</v>
-      </c>
-      <c r="G83">
-        <f>TDE!H75</f>
-        <v>3</v>
-      </c>
-      <c r="H83">
-        <f>TDE!I75</f>
-        <v>3</v>
-      </c>
-      <c r="I83">
-        <f>TDE!J75</f>
-        <v>3</v>
-      </c>
-      <c r="J83">
-        <f>TDE!K75</f>
-        <v>3</v>
-      </c>
-      <c r="K83">
-        <f>TDE!L75</f>
-        <v>3</v>
-      </c>
-      <c r="L83">
-        <f>TDE!M75</f>
-        <v>3</v>
-      </c>
-      <c r="M83">
-        <f>TDE!N75</f>
-        <v>3</v>
-      </c>
-      <c r="N83">
-        <f>TDE!O75</f>
-        <v>3</v>
-      </c>
-      <c r="O83">
-        <f>TDE!P75</f>
-        <v>3</v>
-      </c>
-      <c r="P83">
-        <f>TDE!Q75</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A91" t="str">
-        <f>TDE!A80</f>
-        <v>Center of Excellences</v>
-      </c>
-      <c r="B91" t="str">
-        <f>TDE!C$61</f>
-        <v>JAN</v>
-      </c>
-      <c r="C91" t="str">
-        <f>TDE!D$61</f>
-        <v>FEB</v>
-      </c>
-      <c r="D91" t="str">
-        <f>TDE!E$61</f>
-        <v>MAR</v>
-      </c>
-      <c r="E91" t="str">
-        <f>TDE!F$61</f>
-        <v>APR</v>
-      </c>
-      <c r="F91" t="str">
-        <f>TDE!G$61</f>
-        <v>MAY</v>
-      </c>
-      <c r="G91" t="str">
-        <f>TDE!H$61</f>
-        <v>JUN</v>
-      </c>
-      <c r="H91" t="str">
-        <f>TDE!I$61</f>
-        <v>JUL</v>
-      </c>
-      <c r="I91" t="str">
-        <f>TDE!J$61</f>
-        <v>AUG</v>
-      </c>
-      <c r="J91" t="str">
-        <f>TDE!K$61</f>
-        <v>SEP</v>
-      </c>
-      <c r="K91" t="str">
-        <f>TDE!L$61</f>
-        <v>OCT</v>
-      </c>
-      <c r="L91" t="str">
-        <f>TDE!M$61</f>
-        <v>NOV</v>
-      </c>
-      <c r="M91" t="str">
-        <f>TDE!N$61</f>
-        <v>DEC</v>
-      </c>
-      <c r="N91" t="str">
-        <f>TDE!O$61</f>
-        <v>JAN'27</v>
-      </c>
-      <c r="O91" t="str">
-        <f>TDE!P$61</f>
-        <v>FEB'27</v>
-      </c>
-      <c r="P91" t="str">
-        <f>TDE!Q$61</f>
-        <v>MAR'27</v>
-      </c>
-    </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A92" t="str">
-        <f>TDE!B80</f>
-        <v>Staff</v>
-      </c>
-      <c r="B92">
-        <f>TDE!C80</f>
-        <v>2</v>
-      </c>
-      <c r="C92">
-        <f>TDE!D80</f>
-        <v>2</v>
-      </c>
-      <c r="D92">
-        <f>TDE!E80</f>
-        <v>2</v>
-      </c>
-      <c r="E92">
-        <f>TDE!F80</f>
-        <v>3</v>
-      </c>
-      <c r="F92">
-        <f>TDE!G80</f>
-        <v>3</v>
-      </c>
-      <c r="G92">
-        <f>TDE!H80</f>
-        <v>3</v>
-      </c>
-      <c r="H92">
-        <f>TDE!I80</f>
-        <v>3</v>
-      </c>
-      <c r="I92">
-        <f>TDE!J80</f>
-        <v>3</v>
-      </c>
-      <c r="J92">
-        <f>TDE!K80</f>
-        <v>3</v>
-      </c>
-      <c r="K92">
-        <f>TDE!L80</f>
-        <v>3</v>
-      </c>
-      <c r="L92">
-        <f>TDE!M80</f>
-        <v>3</v>
-      </c>
-      <c r="M92">
-        <f>TDE!N80</f>
-        <v>3</v>
-      </c>
-      <c r="N92">
-        <f>TDE!O80</f>
-        <v>3</v>
-      </c>
-      <c r="O92">
-        <f>TDE!P80</f>
-        <v>3</v>
-      </c>
-      <c r="P92">
-        <f>TDE!Q80</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A93" t="str">
         <f>TDE!B81</f>
         <v>Plan</v>
       </c>
-      <c r="B93">
+      <c r="B83">
         <f>TDE!C81</f>
         <v>2</v>
       </c>
-      <c r="C93">
+      <c r="C83">
         <f>TDE!D81</f>
         <v>2</v>
       </c>
-      <c r="D93">
+      <c r="D83">
         <f>TDE!E81</f>
         <v>2</v>
       </c>
-      <c r="E93">
+      <c r="E83">
         <f>TDE!F81</f>
         <v>3</v>
       </c>
-      <c r="F93">
+      <c r="F83">
         <f>TDE!G81</f>
         <v>3</v>
       </c>
-      <c r="G93">
+      <c r="G83">
         <f>TDE!H81</f>
         <v>3</v>
       </c>
-      <c r="H93">
+      <c r="H83">
         <f>TDE!I81</f>
         <v>3</v>
       </c>
-      <c r="I93">
+      <c r="I83">
         <f>TDE!J81</f>
         <v>3</v>
       </c>
-      <c r="J93">
+      <c r="J83">
         <f>TDE!K81</f>
         <v>3</v>
       </c>
-      <c r="K93">
+      <c r="K83">
         <f>TDE!L81</f>
         <v>3</v>
       </c>
-      <c r="L93">
+      <c r="L83">
         <f>TDE!M81</f>
         <v>3</v>
       </c>
-      <c r="M93">
+      <c r="M83">
         <f>TDE!N81</f>
         <v>3</v>
       </c>
-      <c r="N93">
+      <c r="N83">
         <f>TDE!O81</f>
         <v>3</v>
       </c>
-      <c r="O93">
+      <c r="O83">
         <f>TDE!P81</f>
         <v>3</v>
       </c>
-      <c r="P93">
+      <c r="P83">
         <f>TDE!Q81</f>
         <v>3</v>
       </c>

--- a/workforceresult.xlsx
+++ b/workforceresult.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miiintra/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miintra/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A4DBF4-1812-5841-8D9E-5598B497B7E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17E91E87-C843-4448-9809-B65EEDA6C041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14500" yWindow="620" windowWidth="28800" windowHeight="21200" activeTab="11" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16120" activeTab="13" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
   </bookViews>
   <sheets>
     <sheet name="ALL" sheetId="1" r:id="rId1"/>
@@ -25,6 +25,8 @@
     <sheet name="GraphAIC" sheetId="10" r:id="rId10"/>
     <sheet name="TDE" sheetId="11" r:id="rId11"/>
     <sheet name="GraphTDE" sheetId="12" r:id="rId12"/>
+    <sheet name="Project" sheetId="13" r:id="rId13"/>
+    <sheet name="GraphPJ" sheetId="14" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="128">
   <si>
     <t>Type</t>
   </si>
@@ -502,12 +504,123 @@
   <si>
     <t>Center of Excellences</t>
   </si>
+  <si>
+    <t>Group Name</t>
+  </si>
+  <si>
+    <t>IT Dist</t>
+  </si>
+  <si>
+    <t>SCGP e-Ordering</t>
+  </si>
+  <si>
+    <t>CAP (Common AI Platform)</t>
+  </si>
+  <si>
+    <t>PromptPlus</t>
+  </si>
+  <si>
+    <t>WeShape platform</t>
+  </si>
+  <si>
+    <t>Presale</t>
+  </si>
+  <si>
+    <t>Project</t>
+  </si>
+  <si>
+    <t>TM</t>
+  </si>
+  <si>
+    <t>Infra</t>
+  </si>
+  <si>
+    <t>Spatial Lab</t>
+  </si>
+  <si>
+    <t>Warmbody</t>
+  </si>
+  <si>
+    <t>Project by Team</t>
+  </si>
+  <si>
+    <t>Project by Type</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>PSE-PE</t>
+  </si>
+  <si>
+    <t>PSE-SE</t>
+  </si>
+  <si>
+    <t>SD-Design</t>
+  </si>
+  <si>
+    <t>SD-Data</t>
+  </si>
+  <si>
+    <t>SD-SA</t>
+  </si>
+  <si>
+    <t>SD-SRE</t>
+  </si>
+  <si>
+    <t>SD-CyberSec</t>
+  </si>
+  <si>
+    <t>SD-PM</t>
+  </si>
+  <si>
+    <t>SD-BA</t>
+  </si>
+  <si>
+    <t>SD-QA</t>
+  </si>
+  <si>
+    <t>SD-TM</t>
+  </si>
+  <si>
+    <t>AIC-AI</t>
+  </si>
+  <si>
+    <t>AIC-AIE</t>
+  </si>
+  <si>
+    <t>AIC-IoT</t>
+  </si>
+  <si>
+    <t>AIC-SAI</t>
+  </si>
+  <si>
+    <t>AIC-PSI</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>GINII</t>
+  </si>
+  <si>
+    <t>Industrial Solutions</t>
+  </si>
+  <si>
+    <t>RGUARD</t>
+  </si>
+  <si>
+    <t>SARA</t>
+  </si>
+  <si>
+    <t>WeShape</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -609,8 +722,22 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -701,6 +828,18 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+        <bgColor rgb="FF4472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -732,7 +871,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -812,6 +951,17 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2431,7 +2581,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:P93"/>
+  <dimension ref="A1:P153"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.83203125" bestFit="1" customWidth="1"/>
@@ -4841,6 +4991,200 @@
       <c r="P93">
         <f>AIC!Q73</f>
         <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B151" t="str">
+        <f>AIC!C1</f>
+        <v>JAN</v>
+      </c>
+      <c r="C151" t="str">
+        <f>AIC!D1</f>
+        <v>FEB</v>
+      </c>
+      <c r="D151" t="str">
+        <f>AIC!E1</f>
+        <v>MAR</v>
+      </c>
+      <c r="E151" t="str">
+        <f>AIC!F1</f>
+        <v>APR</v>
+      </c>
+      <c r="F151" t="str">
+        <f>AIC!G1</f>
+        <v>MAY</v>
+      </c>
+      <c r="G151" t="str">
+        <f>AIC!H1</f>
+        <v>JUN</v>
+      </c>
+      <c r="H151" t="str">
+        <f>AIC!I1</f>
+        <v>JUL</v>
+      </c>
+      <c r="I151" t="str">
+        <f>AIC!J1</f>
+        <v>AUG</v>
+      </c>
+      <c r="J151" t="str">
+        <f>AIC!K1</f>
+        <v>SEP</v>
+      </c>
+      <c r="K151" t="str">
+        <f>AIC!L1</f>
+        <v>OCT</v>
+      </c>
+      <c r="L151" t="str">
+        <f>AIC!M1</f>
+        <v>NOV</v>
+      </c>
+      <c r="M151" t="str">
+        <f>AIC!N1</f>
+        <v>DEC</v>
+      </c>
+      <c r="N151" t="str">
+        <f>AIC!O1</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O151" t="str">
+        <f>AIC!P1</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P151" t="str">
+        <f>AIC!Q1</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="152" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A152" t="str">
+        <f>AIC!B6</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B152" s="62">
+        <f>AIC!C6</f>
+        <v>0.66300000000000003</v>
+      </c>
+      <c r="C152" s="62">
+        <f>AIC!D6</f>
+        <v>0.75390000000000001</v>
+      </c>
+      <c r="D152" s="62">
+        <f>AIC!E6</f>
+        <v>0.749</v>
+      </c>
+      <c r="E152" s="62">
+        <f>AIC!F6</f>
+        <v>0.88400000000000001</v>
+      </c>
+      <c r="F152" s="62">
+        <f>AIC!G6</f>
+        <v>0.91969999999999996</v>
+      </c>
+      <c r="G152" s="62">
+        <f>AIC!H6</f>
+        <v>0.8982</v>
+      </c>
+      <c r="H152" s="62">
+        <f>AIC!I6</f>
+        <v>0.83279999999999998</v>
+      </c>
+      <c r="I152" s="62">
+        <f>AIC!J6</f>
+        <v>0.78800000000000003</v>
+      </c>
+      <c r="J152" s="62">
+        <f>AIC!K6</f>
+        <v>0.75639999999999996</v>
+      </c>
+      <c r="K152" s="62">
+        <f>AIC!L6</f>
+        <v>0.71499999999999997</v>
+      </c>
+      <c r="L152" s="62">
+        <f>AIC!M6</f>
+        <v>0.71760000000000002</v>
+      </c>
+      <c r="M152" s="62">
+        <f>AIC!N6</f>
+        <v>0.70179999999999998</v>
+      </c>
+      <c r="N152" s="62">
+        <f>AIC!O6</f>
+        <v>0.44130000000000003</v>
+      </c>
+      <c r="O152" s="62">
+        <f>AIC!P6</f>
+        <v>0.44130000000000003</v>
+      </c>
+      <c r="P152" s="62">
+        <f>AIC!Q6</f>
+        <v>0.44130000000000003</v>
+      </c>
+    </row>
+    <row r="153" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A153" t="str">
+        <f>AIC!B7</f>
+        <v>Available FTE</v>
+      </c>
+      <c r="B153">
+        <f>AIC!C7</f>
+        <v>8</v>
+      </c>
+      <c r="C153">
+        <f>AIC!D7</f>
+        <v>6</v>
+      </c>
+      <c r="D153">
+        <f>AIC!E7</f>
+        <v>6</v>
+      </c>
+      <c r="E153">
+        <f>AIC!F7</f>
+        <v>2</v>
+      </c>
+      <c r="F153">
+        <f>AIC!G7</f>
+        <v>2</v>
+      </c>
+      <c r="G153">
+        <f>AIC!H7</f>
+        <v>2</v>
+      </c>
+      <c r="H153">
+        <f>AIC!I7</f>
+        <v>3</v>
+      </c>
+      <c r="I153">
+        <f>AIC!J7</f>
+        <v>4</v>
+      </c>
+      <c r="J153">
+        <f>AIC!K7</f>
+        <v>5</v>
+      </c>
+      <c r="K153">
+        <f>AIC!L7</f>
+        <v>5</v>
+      </c>
+      <c r="L153">
+        <f>AIC!M7</f>
+        <v>5</v>
+      </c>
+      <c r="M153">
+        <f>AIC!N7</f>
+        <v>6</v>
+      </c>
+      <c r="N153">
+        <f>AIC!O7</f>
+        <v>11</v>
+      </c>
+      <c r="O153">
+        <f>AIC!P7</f>
+        <v>11</v>
+      </c>
+      <c r="P153">
+        <f>AIC!Q7</f>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -7223,7 +7567,7 @@
   <sheetPr>
     <tabColor theme="3" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:P83"/>
+  <dimension ref="A1:P153"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.6640625" bestFit="1" customWidth="1"/>
@@ -9435,6 +9779,3624 @@
       <c r="P83">
         <f>TDE!Q81</f>
         <v>3</v>
+      </c>
+    </row>
+    <row r="151" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B151" t="str">
+        <f>TDE!C1</f>
+        <v>JAN</v>
+      </c>
+      <c r="C151" t="str">
+        <f>TDE!D1</f>
+        <v>FEB</v>
+      </c>
+      <c r="D151" t="str">
+        <f>TDE!E1</f>
+        <v>MAR</v>
+      </c>
+      <c r="E151" t="str">
+        <f>TDE!F1</f>
+        <v>APR</v>
+      </c>
+      <c r="F151" t="str">
+        <f>TDE!G1</f>
+        <v>MAY</v>
+      </c>
+      <c r="G151" t="str">
+        <f>TDE!H1</f>
+        <v>JUN</v>
+      </c>
+      <c r="H151" t="str">
+        <f>TDE!I1</f>
+        <v>JUL</v>
+      </c>
+      <c r="I151" t="str">
+        <f>TDE!J1</f>
+        <v>AUG</v>
+      </c>
+      <c r="J151" t="str">
+        <f>TDE!K1</f>
+        <v>SEP</v>
+      </c>
+      <c r="K151" t="str">
+        <f>TDE!L1</f>
+        <v>OCT</v>
+      </c>
+      <c r="L151" t="str">
+        <f>TDE!M1</f>
+        <v>NOV</v>
+      </c>
+      <c r="M151" t="str">
+        <f>TDE!N1</f>
+        <v>DEC</v>
+      </c>
+      <c r="N151" t="str">
+        <f>TDE!O1</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O151" t="str">
+        <f>TDE!P1</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P151" t="str">
+        <f>TDE!Q1</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="152" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A152" t="str">
+        <f>TDE!B6</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B152" s="62">
+        <f>TDE!C6</f>
+        <v>1</v>
+      </c>
+      <c r="C152" s="62">
+        <f>TDE!D6</f>
+        <v>1</v>
+      </c>
+      <c r="D152" s="62">
+        <f>TDE!E6</f>
+        <v>1</v>
+      </c>
+      <c r="E152" s="62">
+        <f>TDE!F6</f>
+        <v>1</v>
+      </c>
+      <c r="F152" s="62">
+        <f>TDE!G6</f>
+        <v>1</v>
+      </c>
+      <c r="G152" s="62">
+        <f>TDE!H6</f>
+        <v>1</v>
+      </c>
+      <c r="H152" s="62">
+        <f>TDE!I6</f>
+        <v>1</v>
+      </c>
+      <c r="I152" s="62">
+        <f>TDE!J6</f>
+        <v>1</v>
+      </c>
+      <c r="J152" s="62">
+        <f>TDE!K6</f>
+        <v>1</v>
+      </c>
+      <c r="K152" s="62">
+        <f>TDE!L6</f>
+        <v>1</v>
+      </c>
+      <c r="L152" s="62">
+        <f>TDE!M6</f>
+        <v>1</v>
+      </c>
+      <c r="M152" s="62">
+        <f>TDE!N6</f>
+        <v>1</v>
+      </c>
+      <c r="N152" s="62">
+        <f>TDE!O6</f>
+        <v>1</v>
+      </c>
+      <c r="O152" s="62">
+        <f>TDE!P6</f>
+        <v>1</v>
+      </c>
+      <c r="P152" s="62">
+        <f>TDE!Q6</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A153" t="str">
+        <f>TDE!B7</f>
+        <v>Available FTE</v>
+      </c>
+      <c r="B153">
+        <f>TDE!C7</f>
+        <v>0</v>
+      </c>
+      <c r="C153">
+        <f>TDE!D7</f>
+        <v>0</v>
+      </c>
+      <c r="D153">
+        <f>TDE!E7</f>
+        <v>0</v>
+      </c>
+      <c r="E153">
+        <f>TDE!F7</f>
+        <v>0</v>
+      </c>
+      <c r="F153">
+        <f>TDE!G7</f>
+        <v>0</v>
+      </c>
+      <c r="G153">
+        <f>TDE!H7</f>
+        <v>0</v>
+      </c>
+      <c r="H153">
+        <f>TDE!I7</f>
+        <v>0</v>
+      </c>
+      <c r="I153">
+        <f>TDE!J7</f>
+        <v>0</v>
+      </c>
+      <c r="J153">
+        <f>TDE!K7</f>
+        <v>0</v>
+      </c>
+      <c r="K153">
+        <f>TDE!L7</f>
+        <v>0</v>
+      </c>
+      <c r="L153">
+        <f>TDE!M7</f>
+        <v>0</v>
+      </c>
+      <c r="M153">
+        <f>TDE!N7</f>
+        <v>0</v>
+      </c>
+      <c r="N153">
+        <f>TDE!O7</f>
+        <v>0</v>
+      </c>
+      <c r="O153">
+        <f>TDE!P7</f>
+        <v>0</v>
+      </c>
+      <c r="P153">
+        <f>TDE!Q7</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC6F03D2-F045-604C-BDE8-7CF4034DAA30}">
+  <sheetPr>
+    <tabColor rgb="FF002060"/>
+  </sheetPr>
+  <dimension ref="A1:V27"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="21.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1" s="59" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" s="59" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="59" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="59" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="59" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="59" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="59" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="59" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="59" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="59" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="59" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="59" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="59" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="59" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="55"/>
+      <c r="R1" s="55"/>
+      <c r="S1" s="55"/>
+      <c r="T1" s="55"/>
+      <c r="U1" s="55"/>
+      <c r="V1" s="55"/>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A2" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" s="8">
+        <v>2.46</v>
+      </c>
+      <c r="C2" s="8">
+        <v>2.4649999999999999</v>
+      </c>
+      <c r="D2" s="8">
+        <v>2.4649999999999999</v>
+      </c>
+      <c r="E2" s="8">
+        <v>1.95</v>
+      </c>
+      <c r="F2" s="8">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G2" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="H2" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="I2" s="8">
+        <v>2.7749999999999999</v>
+      </c>
+      <c r="J2" s="8">
+        <v>2.7749999999999999</v>
+      </c>
+      <c r="K2" s="8">
+        <v>2.6124999999999998</v>
+      </c>
+      <c r="L2" s="8">
+        <v>2.6124999999999998</v>
+      </c>
+      <c r="M2" s="8">
+        <v>2.6124999999999998</v>
+      </c>
+      <c r="N2" s="8">
+        <v>0.80249999999999999</v>
+      </c>
+      <c r="O2" s="8">
+        <v>0.80249999999999999</v>
+      </c>
+      <c r="P2" s="8">
+        <v>0.80249999999999999</v>
+      </c>
+      <c r="Q2" s="8"/>
+      <c r="R2" s="8"/>
+      <c r="S2" s="60"/>
+      <c r="T2" s="8"/>
+      <c r="U2" s="8"/>
+      <c r="V2" s="60"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A3" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="B3" s="8">
+        <v>3.37</v>
+      </c>
+      <c r="C3" s="8">
+        <v>2.77</v>
+      </c>
+      <c r="D3" s="8">
+        <v>2.59</v>
+      </c>
+      <c r="E3" s="8">
+        <v>2.08</v>
+      </c>
+      <c r="F3" s="8">
+        <v>2.13</v>
+      </c>
+      <c r="G3" s="8">
+        <v>1.75</v>
+      </c>
+      <c r="H3" s="8">
+        <v>2</v>
+      </c>
+      <c r="I3" s="8">
+        <v>2</v>
+      </c>
+      <c r="J3" s="8">
+        <v>2</v>
+      </c>
+      <c r="K3" s="8">
+        <v>2</v>
+      </c>
+      <c r="L3" s="8">
+        <v>2</v>
+      </c>
+      <c r="M3" s="8">
+        <v>2</v>
+      </c>
+      <c r="N3" s="8">
+        <v>1.55</v>
+      </c>
+      <c r="O3" s="8">
+        <v>1.55</v>
+      </c>
+      <c r="P3" s="8">
+        <v>1.55</v>
+      </c>
+      <c r="Q3" s="8"/>
+      <c r="R3" s="8"/>
+      <c r="S3" s="60"/>
+      <c r="T3" s="8"/>
+      <c r="U3" s="8"/>
+      <c r="V3" s="60"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A4" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="8">
+        <v>1.75</v>
+      </c>
+      <c r="C4" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D4" s="8">
+        <v>1.2749999999999999</v>
+      </c>
+      <c r="E4" s="8">
+        <v>0.95</v>
+      </c>
+      <c r="F4" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="G4" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="H4" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="I4" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="J4" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="K4" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="L4" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M4" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="N4" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="O4" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P4" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q4" s="8"/>
+      <c r="R4" s="8"/>
+      <c r="S4" s="60"/>
+      <c r="T4" s="8"/>
+      <c r="U4" s="8"/>
+      <c r="V4" s="60"/>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A5" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="B5" s="8">
+        <v>3.2650000000000001</v>
+      </c>
+      <c r="C5" s="8">
+        <v>3.165</v>
+      </c>
+      <c r="D5" s="8">
+        <v>3.0649999999999999</v>
+      </c>
+      <c r="E5" s="8">
+        <v>2.7250000000000001</v>
+      </c>
+      <c r="F5" s="8">
+        <v>2.875</v>
+      </c>
+      <c r="G5" s="8">
+        <v>3.46</v>
+      </c>
+      <c r="H5" s="8">
+        <v>2.6850000000000001</v>
+      </c>
+      <c r="I5" s="8">
+        <v>2.9849999999999999</v>
+      </c>
+      <c r="J5" s="8">
+        <v>2.9849999999999999</v>
+      </c>
+      <c r="K5" s="8">
+        <v>2.9224999999999999</v>
+      </c>
+      <c r="L5" s="8">
+        <v>2.9224999999999999</v>
+      </c>
+      <c r="M5" s="8">
+        <v>2.9224999999999999</v>
+      </c>
+      <c r="N5" s="8">
+        <v>2.81</v>
+      </c>
+      <c r="O5" s="8">
+        <v>2.81</v>
+      </c>
+      <c r="P5" s="8">
+        <v>2.81</v>
+      </c>
+      <c r="Q5" s="8"/>
+      <c r="R5" s="8"/>
+      <c r="S5" s="60"/>
+      <c r="T5" s="8"/>
+      <c r="U5" s="8"/>
+      <c r="V5" s="60"/>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A6" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B6" s="8">
+        <v>3.25</v>
+      </c>
+      <c r="C6" s="8">
+        <v>3.625</v>
+      </c>
+      <c r="D6" s="8">
+        <v>3.67</v>
+      </c>
+      <c r="E6" s="8">
+        <v>3.4824999999999999</v>
+      </c>
+      <c r="F6" s="8">
+        <v>2.9824999999999999</v>
+      </c>
+      <c r="G6" s="8">
+        <v>2.9874999999999998</v>
+      </c>
+      <c r="H6" s="8">
+        <v>2.3125</v>
+      </c>
+      <c r="I6" s="8">
+        <v>2.2124999999999999</v>
+      </c>
+      <c r="J6" s="8">
+        <v>3.1124999999999998</v>
+      </c>
+      <c r="K6" s="8">
+        <v>3.1124999999999998</v>
+      </c>
+      <c r="L6" s="8">
+        <v>3.1124999999999998</v>
+      </c>
+      <c r="M6" s="8">
+        <v>3.1124999999999998</v>
+      </c>
+      <c r="N6" s="8">
+        <v>3.05</v>
+      </c>
+      <c r="O6" s="8">
+        <v>3.05</v>
+      </c>
+      <c r="P6" s="8">
+        <v>3.05</v>
+      </c>
+      <c r="Q6" s="8"/>
+      <c r="R6" s="8"/>
+      <c r="S6" s="60"/>
+      <c r="T6" s="8"/>
+      <c r="U6" s="8"/>
+      <c r="V6" s="60"/>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
+      <c r="S7" s="60"/>
+      <c r="T7" s="8"/>
+      <c r="U7" s="8"/>
+      <c r="V7" s="60"/>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A9" s="61" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A11" s="53" t="s">
+        <v>91</v>
+      </c>
+      <c r="B11" s="53" t="s">
+        <v>105</v>
+      </c>
+      <c r="C11" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="53" t="s">
+        <v>106</v>
+      </c>
+      <c r="E11" s="53" t="s">
+        <v>107</v>
+      </c>
+      <c r="F11" s="53" t="s">
+        <v>108</v>
+      </c>
+      <c r="G11" s="53" t="s">
+        <v>109</v>
+      </c>
+      <c r="H11" s="53" t="s">
+        <v>110</v>
+      </c>
+      <c r="I11" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="J11" s="53" t="s">
+        <v>112</v>
+      </c>
+      <c r="K11" s="53" t="s">
+        <v>113</v>
+      </c>
+      <c r="L11" s="53" t="s">
+        <v>114</v>
+      </c>
+      <c r="M11" s="53" t="s">
+        <v>115</v>
+      </c>
+      <c r="N11" s="53" t="s">
+        <v>116</v>
+      </c>
+      <c r="O11" s="53" t="s">
+        <v>117</v>
+      </c>
+      <c r="P11" s="53" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q11" s="53" t="s">
+        <v>119</v>
+      </c>
+      <c r="R11" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="S11" s="53" t="s">
+        <v>121</v>
+      </c>
+      <c r="T11" s="53" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A12" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B12" s="8">
+        <v>216</v>
+      </c>
+      <c r="C12" s="8">
+        <v>0</v>
+      </c>
+      <c r="D12" s="8">
+        <v>0</v>
+      </c>
+      <c r="E12" s="8">
+        <v>216</v>
+      </c>
+      <c r="F12" s="8">
+        <v>0</v>
+      </c>
+      <c r="G12" s="8">
+        <v>0</v>
+      </c>
+      <c r="H12" s="8">
+        <v>0</v>
+      </c>
+      <c r="I12" s="8">
+        <v>0</v>
+      </c>
+      <c r="J12" s="8">
+        <v>0</v>
+      </c>
+      <c r="K12" s="8">
+        <v>0</v>
+      </c>
+      <c r="L12" s="8">
+        <v>0</v>
+      </c>
+      <c r="M12" s="8">
+        <v>0</v>
+      </c>
+      <c r="N12" s="8">
+        <v>0</v>
+      </c>
+      <c r="O12" s="8">
+        <v>0</v>
+      </c>
+      <c r="P12" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="8">
+        <v>0</v>
+      </c>
+      <c r="R12" s="8">
+        <v>0</v>
+      </c>
+      <c r="S12" s="8">
+        <v>0</v>
+      </c>
+      <c r="T12" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A13" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="B13" s="8">
+        <v>162.78</v>
+      </c>
+      <c r="C13" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="D13" s="8">
+        <v>0</v>
+      </c>
+      <c r="E13" s="8">
+        <v>46.3</v>
+      </c>
+      <c r="F13" s="8">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G13" s="8">
+        <v>0</v>
+      </c>
+      <c r="H13" s="8">
+        <v>1.05</v>
+      </c>
+      <c r="I13" s="8">
+        <v>1.35</v>
+      </c>
+      <c r="J13" s="8">
+        <v>0</v>
+      </c>
+      <c r="K13" s="8">
+        <v>7.6</v>
+      </c>
+      <c r="L13" s="8">
+        <v>12</v>
+      </c>
+      <c r="M13" s="8">
+        <v>83.45</v>
+      </c>
+      <c r="N13" s="8">
+        <v>5.13</v>
+      </c>
+      <c r="O13" s="8">
+        <v>0</v>
+      </c>
+      <c r="P13" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>0</v>
+      </c>
+      <c r="R13" s="8">
+        <v>0</v>
+      </c>
+      <c r="S13" s="8">
+        <v>0</v>
+      </c>
+      <c r="T13" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A14" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B14" s="8">
+        <v>63.6</v>
+      </c>
+      <c r="C14" s="8">
+        <v>0</v>
+      </c>
+      <c r="D14" s="8">
+        <v>61.8</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0</v>
+      </c>
+      <c r="F14" s="8">
+        <v>0</v>
+      </c>
+      <c r="G14" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="H14" s="8">
+        <v>0</v>
+      </c>
+      <c r="I14" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="J14" s="8">
+        <v>0</v>
+      </c>
+      <c r="K14" s="8">
+        <v>0</v>
+      </c>
+      <c r="L14" s="8">
+        <v>0</v>
+      </c>
+      <c r="M14" s="8">
+        <v>0</v>
+      </c>
+      <c r="N14" s="8">
+        <v>0</v>
+      </c>
+      <c r="O14" s="8">
+        <v>0</v>
+      </c>
+      <c r="P14" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="8">
+        <v>0</v>
+      </c>
+      <c r="R14" s="8">
+        <v>0</v>
+      </c>
+      <c r="S14" s="8">
+        <v>0</v>
+      </c>
+      <c r="T14" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A15" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="B15" s="8">
+        <v>51.075000000000003</v>
+      </c>
+      <c r="C15" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="D15" s="8">
+        <v>0</v>
+      </c>
+      <c r="E15" s="8">
+        <v>22.8</v>
+      </c>
+      <c r="F15" s="8">
+        <v>1.875</v>
+      </c>
+      <c r="G15" s="8">
+        <v>0</v>
+      </c>
+      <c r="H15" s="8">
+        <v>0</v>
+      </c>
+      <c r="I15" s="8">
+        <v>0</v>
+      </c>
+      <c r="J15" s="8">
+        <v>0</v>
+      </c>
+      <c r="K15" s="8">
+        <v>1.8</v>
+      </c>
+      <c r="L15" s="8">
+        <v>7.7</v>
+      </c>
+      <c r="M15" s="8">
+        <v>16</v>
+      </c>
+      <c r="N15" s="8">
+        <v>0</v>
+      </c>
+      <c r="O15" s="8">
+        <v>0</v>
+      </c>
+      <c r="P15" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="8">
+        <v>0</v>
+      </c>
+      <c r="R15" s="8">
+        <v>0</v>
+      </c>
+      <c r="S15" s="8">
+        <v>0</v>
+      </c>
+      <c r="T15" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A16" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B16" s="8">
+        <v>35.454999999999998</v>
+      </c>
+      <c r="C16" s="8">
+        <v>0</v>
+      </c>
+      <c r="D16" s="8">
+        <v>0</v>
+      </c>
+      <c r="E16" s="8">
+        <v>7.2</v>
+      </c>
+      <c r="F16" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="G16" s="8">
+        <v>0</v>
+      </c>
+      <c r="H16" s="8">
+        <v>1.8</v>
+      </c>
+      <c r="I16" s="8">
+        <v>0.65</v>
+      </c>
+      <c r="J16" s="8">
+        <v>0</v>
+      </c>
+      <c r="K16" s="8">
+        <v>1.65</v>
+      </c>
+      <c r="L16" s="8">
+        <v>7.2</v>
+      </c>
+      <c r="M16" s="8">
+        <v>5.4</v>
+      </c>
+      <c r="N16" s="8">
+        <v>0</v>
+      </c>
+      <c r="O16" s="8">
+        <v>0</v>
+      </c>
+      <c r="P16" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="8">
+        <v>0</v>
+      </c>
+      <c r="R16" s="8">
+        <v>11.18</v>
+      </c>
+      <c r="S16" s="8">
+        <v>0</v>
+      </c>
+      <c r="T16" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A19" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A21" s="53" t="s">
+        <v>91</v>
+      </c>
+      <c r="B21" s="53" t="s">
+        <v>97</v>
+      </c>
+      <c r="C21" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="D21" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="E21" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="F21" s="53" t="s">
+        <v>101</v>
+      </c>
+      <c r="G21" s="53" t="s">
+        <v>102</v>
+      </c>
+      <c r="H21" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="I21" s="55"/>
+      <c r="J21" s="56"/>
+      <c r="K21" s="55"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="55"/>
+      <c r="N21" s="55"/>
+      <c r="O21" s="56"/>
+      <c r="P21" s="56"/>
+      <c r="Q21" s="55"/>
+      <c r="R21" s="56"/>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A22" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B22" s="8">
+        <v>36</v>
+      </c>
+      <c r="C22" s="8"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8">
+        <v>180</v>
+      </c>
+      <c r="H22" s="8">
+        <v>216</v>
+      </c>
+      <c r="I22" s="57"/>
+      <c r="J22" s="56"/>
+      <c r="K22" s="58"/>
+      <c r="L22" s="58"/>
+      <c r="M22" s="57"/>
+      <c r="N22" s="57"/>
+      <c r="O22" s="56"/>
+      <c r="P22" s="56"/>
+      <c r="Q22" s="57"/>
+      <c r="R22" s="56"/>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A23" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="B23" s="8">
+        <v>2.7</v>
+      </c>
+      <c r="C23" s="8">
+        <v>154.05000000000001</v>
+      </c>
+      <c r="D23" s="54">
+        <v>5.13</v>
+      </c>
+      <c r="E23" s="54">
+        <v>0.9</v>
+      </c>
+      <c r="F23" s="8"/>
+      <c r="G23" s="54"/>
+      <c r="H23" s="8">
+        <v>162.78</v>
+      </c>
+      <c r="I23" s="57"/>
+      <c r="J23" s="56"/>
+      <c r="K23" s="58"/>
+      <c r="L23" s="58"/>
+      <c r="M23" s="57"/>
+      <c r="N23" s="58"/>
+      <c r="O23" s="56"/>
+      <c r="P23" s="56"/>
+      <c r="Q23" s="57"/>
+      <c r="R23" s="56"/>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A24" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8">
+        <v>63.6</v>
+      </c>
+      <c r="D24" s="54"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="54"/>
+      <c r="H24" s="8">
+        <v>63.6</v>
+      </c>
+      <c r="I24" s="57"/>
+      <c r="J24" s="56"/>
+      <c r="K24" s="58"/>
+      <c r="L24" s="58"/>
+      <c r="M24" s="57"/>
+      <c r="N24" s="58"/>
+      <c r="O24" s="56"/>
+      <c r="P24" s="56"/>
+      <c r="Q24" s="57"/>
+      <c r="R24" s="56"/>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A25" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8">
+        <v>27.375</v>
+      </c>
+      <c r="D25" s="54"/>
+      <c r="E25" s="54"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8">
+        <v>23.7</v>
+      </c>
+      <c r="H25" s="8">
+        <v>51.075000000000003</v>
+      </c>
+      <c r="I25" s="57"/>
+      <c r="J25" s="56"/>
+      <c r="K25" s="58"/>
+      <c r="L25" s="58"/>
+      <c r="M25" s="57"/>
+      <c r="N25" s="57"/>
+      <c r="O25" s="56"/>
+      <c r="P25" s="56"/>
+      <c r="Q25" s="57"/>
+      <c r="R25" s="56"/>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A26" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B26" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="C26" s="8"/>
+      <c r="D26" s="54"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="8">
+        <v>34.655000000000001</v>
+      </c>
+      <c r="G26" s="54"/>
+      <c r="H26" s="8">
+        <v>35.454999999999998</v>
+      </c>
+      <c r="I26" s="57"/>
+      <c r="J26" s="56"/>
+      <c r="K26" s="58"/>
+      <c r="L26" s="58"/>
+      <c r="M26" s="57"/>
+      <c r="N26" s="58"/>
+      <c r="O26" s="56"/>
+      <c r="P26" s="56"/>
+      <c r="Q26" s="57"/>
+      <c r="R26" s="56"/>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="I27" s="56"/>
+      <c r="J27" s="56"/>
+      <c r="K27" s="56"/>
+      <c r="L27" s="56"/>
+      <c r="M27" s="56"/>
+      <c r="N27" s="56"/>
+      <c r="O27" s="56"/>
+      <c r="P27" s="56"/>
+      <c r="Q27" s="56"/>
+      <c r="R27" s="56"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A369C834-427B-BA49-B845-305D612514AF}">
+  <sheetPr>
+    <tabColor rgb="FF0070C0"/>
+  </sheetPr>
+  <dimension ref="A1:T30"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="22.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" s="63" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="63" t="str">
+        <f>IF(Project!A1&gt;0,Project!A1,"")</f>
+        <v>Group</v>
+      </c>
+      <c r="B1" s="63" t="str">
+        <f>IF(Project!B1&gt;0,Project!B1,"")</f>
+        <v>JAN</v>
+      </c>
+      <c r="C1" s="63" t="str">
+        <f>IF(Project!C1&gt;0,Project!C1,"")</f>
+        <v>FEB</v>
+      </c>
+      <c r="D1" s="63" t="str">
+        <f>IF(Project!D1&gt;0,Project!D1,"")</f>
+        <v>MAR</v>
+      </c>
+      <c r="E1" s="63" t="str">
+        <f>IF(Project!E1&gt;0,Project!E1,"")</f>
+        <v>APR</v>
+      </c>
+      <c r="F1" s="63" t="str">
+        <f>IF(Project!F1&gt;0,Project!F1,"")</f>
+        <v>MAY</v>
+      </c>
+      <c r="G1" s="63" t="str">
+        <f>IF(Project!G1&gt;0,Project!G1,"")</f>
+        <v>JUN</v>
+      </c>
+      <c r="H1" s="63" t="str">
+        <f>IF(Project!H1&gt;0,Project!H1,"")</f>
+        <v>JUL</v>
+      </c>
+      <c r="I1" s="63" t="str">
+        <f>IF(Project!I1&gt;0,Project!I1,"")</f>
+        <v>AUG</v>
+      </c>
+      <c r="J1" s="63" t="str">
+        <f>IF(Project!J1&gt;0,Project!J1,"")</f>
+        <v>SEP</v>
+      </c>
+      <c r="K1" s="63" t="str">
+        <f>IF(Project!K1&gt;0,Project!K1,"")</f>
+        <v>OCT</v>
+      </c>
+      <c r="L1" s="63" t="str">
+        <f>IF(Project!L1&gt;0,Project!L1,"")</f>
+        <v>NOV</v>
+      </c>
+      <c r="M1" s="63" t="str">
+        <f>IF(Project!M1&gt;0,Project!M1,"")</f>
+        <v>DEC</v>
+      </c>
+      <c r="N1" s="63" t="str">
+        <f>IF(Project!N1&gt;0,Project!N1,"")</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O1" s="63" t="str">
+        <f>IF(Project!O1&gt;0,Project!O1,"")</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P1" s="63" t="str">
+        <f>IF(Project!P1&gt;0,Project!P1,"")</f>
+        <v>MAR'27</v>
+      </c>
+      <c r="Q1" s="63" t="str">
+        <f>IF(Project!Q1&gt;0,Project!Q1,"")</f>
+        <v/>
+      </c>
+      <c r="R1" s="63" t="str">
+        <f>IF(Project!R1&gt;0,Project!R1,"")</f>
+        <v/>
+      </c>
+      <c r="S1" s="63" t="str">
+        <f>IF(Project!S1&gt;0,Project!S1,"")</f>
+        <v/>
+      </c>
+      <c r="T1" s="63" t="str">
+        <f>IF(Project!T1&gt;0,Project!T1,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A2" t="str">
+        <f>IF(Project!A2&gt;0,Project!A2,"")</f>
+        <v>GINII</v>
+      </c>
+      <c r="B2">
+        <f>IF(Project!B2&gt;0,Project!B2,"")</f>
+        <v>2.46</v>
+      </c>
+      <c r="C2">
+        <f>IF(Project!C2&gt;0,Project!C2,"")</f>
+        <v>2.4649999999999999</v>
+      </c>
+      <c r="D2">
+        <f>IF(Project!D2&gt;0,Project!D2,"")</f>
+        <v>2.4649999999999999</v>
+      </c>
+      <c r="E2">
+        <f>IF(Project!E2&gt;0,Project!E2,"")</f>
+        <v>1.95</v>
+      </c>
+      <c r="F2">
+        <f>IF(Project!F2&gt;0,Project!F2,"")</f>
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G2">
+        <f>IF(Project!G2&gt;0,Project!G2,"")</f>
+        <v>3.2</v>
+      </c>
+      <c r="H2">
+        <f>IF(Project!H2&gt;0,Project!H2,"")</f>
+        <v>2.9</v>
+      </c>
+      <c r="I2">
+        <f>IF(Project!I2&gt;0,Project!I2,"")</f>
+        <v>2.7749999999999999</v>
+      </c>
+      <c r="J2">
+        <f>IF(Project!J2&gt;0,Project!J2,"")</f>
+        <v>2.7749999999999999</v>
+      </c>
+      <c r="K2">
+        <f>IF(Project!K2&gt;0,Project!K2,"")</f>
+        <v>2.6124999999999998</v>
+      </c>
+      <c r="L2">
+        <f>IF(Project!L2&gt;0,Project!L2,"")</f>
+        <v>2.6124999999999998</v>
+      </c>
+      <c r="M2">
+        <f>IF(Project!M2&gt;0,Project!M2,"")</f>
+        <v>2.6124999999999998</v>
+      </c>
+      <c r="N2">
+        <f>IF(Project!N2&gt;0,Project!N2,"")</f>
+        <v>0.80249999999999999</v>
+      </c>
+      <c r="O2">
+        <f>IF(Project!O2&gt;0,Project!O2,"")</f>
+        <v>0.80249999999999999</v>
+      </c>
+      <c r="P2">
+        <f>IF(Project!P2&gt;0,Project!P2,"")</f>
+        <v>0.80249999999999999</v>
+      </c>
+      <c r="Q2" t="str">
+        <f>IF(Project!Q2&gt;0,Project!Q2,"")</f>
+        <v/>
+      </c>
+      <c r="R2" t="str">
+        <f>IF(Project!R2&gt;0,Project!R2,"")</f>
+        <v/>
+      </c>
+      <c r="S2" t="str">
+        <f>IF(Project!S2&gt;0,Project!S2,"")</f>
+        <v/>
+      </c>
+      <c r="T2" t="str">
+        <f>IF(Project!T2&gt;0,Project!T2,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A3" t="str">
+        <f>IF(Project!A3&gt;0,Project!A3,"")</f>
+        <v>Industrial Solutions</v>
+      </c>
+      <c r="B3">
+        <f>IF(Project!B3&gt;0,Project!B3,"")</f>
+        <v>3.37</v>
+      </c>
+      <c r="C3">
+        <f>IF(Project!C3&gt;0,Project!C3,"")</f>
+        <v>2.77</v>
+      </c>
+      <c r="D3">
+        <f>IF(Project!D3&gt;0,Project!D3,"")</f>
+        <v>2.59</v>
+      </c>
+      <c r="E3">
+        <f>IF(Project!E3&gt;0,Project!E3,"")</f>
+        <v>2.08</v>
+      </c>
+      <c r="F3">
+        <f>IF(Project!F3&gt;0,Project!F3,"")</f>
+        <v>2.13</v>
+      </c>
+      <c r="G3">
+        <f>IF(Project!G3&gt;0,Project!G3,"")</f>
+        <v>1.75</v>
+      </c>
+      <c r="H3">
+        <f>IF(Project!H3&gt;0,Project!H3,"")</f>
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <f>IF(Project!I3&gt;0,Project!I3,"")</f>
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <f>IF(Project!J3&gt;0,Project!J3,"")</f>
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <f>IF(Project!K3&gt;0,Project!K3,"")</f>
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <f>IF(Project!L3&gt;0,Project!L3,"")</f>
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <f>IF(Project!M3&gt;0,Project!M3,"")</f>
+        <v>2</v>
+      </c>
+      <c r="N3">
+        <f>IF(Project!N3&gt;0,Project!N3,"")</f>
+        <v>1.55</v>
+      </c>
+      <c r="O3">
+        <f>IF(Project!O3&gt;0,Project!O3,"")</f>
+        <v>1.55</v>
+      </c>
+      <c r="P3">
+        <f>IF(Project!P3&gt;0,Project!P3,"")</f>
+        <v>1.55</v>
+      </c>
+      <c r="Q3" t="str">
+        <f>IF(Project!Q3&gt;0,Project!Q3,"")</f>
+        <v/>
+      </c>
+      <c r="R3" t="str">
+        <f>IF(Project!R3&gt;0,Project!R3,"")</f>
+        <v/>
+      </c>
+      <c r="S3" t="str">
+        <f>IF(Project!S3&gt;0,Project!S3,"")</f>
+        <v/>
+      </c>
+      <c r="T3" t="str">
+        <f>IF(Project!T3&gt;0,Project!T3,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A4" t="str">
+        <f>IF(Project!A4&gt;0,Project!A4,"")</f>
+        <v>RGUARD</v>
+      </c>
+      <c r="B4">
+        <f>IF(Project!B4&gt;0,Project!B4,"")</f>
+        <v>1.75</v>
+      </c>
+      <c r="C4">
+        <f>IF(Project!C4&gt;0,Project!C4,"")</f>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D4">
+        <f>IF(Project!D4&gt;0,Project!D4,"")</f>
+        <v>1.2749999999999999</v>
+      </c>
+      <c r="E4">
+        <f>IF(Project!E4&gt;0,Project!E4,"")</f>
+        <v>0.95</v>
+      </c>
+      <c r="F4">
+        <f>IF(Project!F4&gt;0,Project!F4,"")</f>
+        <v>0.8</v>
+      </c>
+      <c r="G4">
+        <f>IF(Project!G4&gt;0,Project!G4,"")</f>
+        <v>0.6</v>
+      </c>
+      <c r="H4">
+        <f>IF(Project!H4&gt;0,Project!H4,"")</f>
+        <v>0.5</v>
+      </c>
+      <c r="I4">
+        <f>IF(Project!I4&gt;0,Project!I4,"")</f>
+        <v>0.5</v>
+      </c>
+      <c r="J4">
+        <f>IF(Project!J4&gt;0,Project!J4,"")</f>
+        <v>0.5</v>
+      </c>
+      <c r="K4">
+        <f>IF(Project!K4&gt;0,Project!K4,"")</f>
+        <v>0.5</v>
+      </c>
+      <c r="L4">
+        <f>IF(Project!L4&gt;0,Project!L4,"")</f>
+        <v>0.5</v>
+      </c>
+      <c r="M4">
+        <f>IF(Project!M4&gt;0,Project!M4,"")</f>
+        <v>0.5</v>
+      </c>
+      <c r="N4">
+        <f>IF(Project!N4&gt;0,Project!N4,"")</f>
+        <v>0.5</v>
+      </c>
+      <c r="O4">
+        <f>IF(Project!O4&gt;0,Project!O4,"")</f>
+        <v>0.5</v>
+      </c>
+      <c r="P4">
+        <f>IF(Project!P4&gt;0,Project!P4,"")</f>
+        <v>0.5</v>
+      </c>
+      <c r="Q4" t="str">
+        <f>IF(Project!Q4&gt;0,Project!Q4,"")</f>
+        <v/>
+      </c>
+      <c r="R4" t="str">
+        <f>IF(Project!R4&gt;0,Project!R4,"")</f>
+        <v/>
+      </c>
+      <c r="S4" t="str">
+        <f>IF(Project!S4&gt;0,Project!S4,"")</f>
+        <v/>
+      </c>
+      <c r="T4" t="str">
+        <f>IF(Project!T4&gt;0,Project!T4,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A5" t="str">
+        <f>IF(Project!A5&gt;0,Project!A5,"")</f>
+        <v>SARA</v>
+      </c>
+      <c r="B5">
+        <f>IF(Project!B5&gt;0,Project!B5,"")</f>
+        <v>3.2650000000000001</v>
+      </c>
+      <c r="C5">
+        <f>IF(Project!C5&gt;0,Project!C5,"")</f>
+        <v>3.165</v>
+      </c>
+      <c r="D5">
+        <f>IF(Project!D5&gt;0,Project!D5,"")</f>
+        <v>3.0649999999999999</v>
+      </c>
+      <c r="E5">
+        <f>IF(Project!E5&gt;0,Project!E5,"")</f>
+        <v>2.7250000000000001</v>
+      </c>
+      <c r="F5">
+        <f>IF(Project!F5&gt;0,Project!F5,"")</f>
+        <v>2.875</v>
+      </c>
+      <c r="G5">
+        <f>IF(Project!G5&gt;0,Project!G5,"")</f>
+        <v>3.46</v>
+      </c>
+      <c r="H5">
+        <f>IF(Project!H5&gt;0,Project!H5,"")</f>
+        <v>2.6850000000000001</v>
+      </c>
+      <c r="I5">
+        <f>IF(Project!I5&gt;0,Project!I5,"")</f>
+        <v>2.9849999999999999</v>
+      </c>
+      <c r="J5">
+        <f>IF(Project!J5&gt;0,Project!J5,"")</f>
+        <v>2.9849999999999999</v>
+      </c>
+      <c r="K5">
+        <f>IF(Project!K5&gt;0,Project!K5,"")</f>
+        <v>2.9224999999999999</v>
+      </c>
+      <c r="L5">
+        <f>IF(Project!L5&gt;0,Project!L5,"")</f>
+        <v>2.9224999999999999</v>
+      </c>
+      <c r="M5">
+        <f>IF(Project!M5&gt;0,Project!M5,"")</f>
+        <v>2.9224999999999999</v>
+      </c>
+      <c r="N5">
+        <f>IF(Project!N5&gt;0,Project!N5,"")</f>
+        <v>2.81</v>
+      </c>
+      <c r="O5">
+        <f>IF(Project!O5&gt;0,Project!O5,"")</f>
+        <v>2.81</v>
+      </c>
+      <c r="P5">
+        <f>IF(Project!P5&gt;0,Project!P5,"")</f>
+        <v>2.81</v>
+      </c>
+      <c r="Q5" t="str">
+        <f>IF(Project!Q5&gt;0,Project!Q5,"")</f>
+        <v/>
+      </c>
+      <c r="R5" t="str">
+        <f>IF(Project!R5&gt;0,Project!R5,"")</f>
+        <v/>
+      </c>
+      <c r="S5" t="str">
+        <f>IF(Project!S5&gt;0,Project!S5,"")</f>
+        <v/>
+      </c>
+      <c r="T5" t="str">
+        <f>IF(Project!T5&gt;0,Project!T5,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A6" t="str">
+        <f>IF(Project!A6&gt;0,Project!A6,"")</f>
+        <v>WeShape</v>
+      </c>
+      <c r="B6">
+        <f>IF(Project!B6&gt;0,Project!B6,"")</f>
+        <v>3.25</v>
+      </c>
+      <c r="C6">
+        <f>IF(Project!C6&gt;0,Project!C6,"")</f>
+        <v>3.625</v>
+      </c>
+      <c r="D6">
+        <f>IF(Project!D6&gt;0,Project!D6,"")</f>
+        <v>3.67</v>
+      </c>
+      <c r="E6">
+        <f>IF(Project!E6&gt;0,Project!E6,"")</f>
+        <v>3.4824999999999999</v>
+      </c>
+      <c r="F6">
+        <f>IF(Project!F6&gt;0,Project!F6,"")</f>
+        <v>2.9824999999999999</v>
+      </c>
+      <c r="G6">
+        <f>IF(Project!G6&gt;0,Project!G6,"")</f>
+        <v>2.9874999999999998</v>
+      </c>
+      <c r="H6">
+        <f>IF(Project!H6&gt;0,Project!H6,"")</f>
+        <v>2.3125</v>
+      </c>
+      <c r="I6">
+        <f>IF(Project!I6&gt;0,Project!I6,"")</f>
+        <v>2.2124999999999999</v>
+      </c>
+      <c r="J6">
+        <f>IF(Project!J6&gt;0,Project!J6,"")</f>
+        <v>3.1124999999999998</v>
+      </c>
+      <c r="K6">
+        <f>IF(Project!K6&gt;0,Project!K6,"")</f>
+        <v>3.1124999999999998</v>
+      </c>
+      <c r="L6">
+        <f>IF(Project!L6&gt;0,Project!L6,"")</f>
+        <v>3.1124999999999998</v>
+      </c>
+      <c r="M6">
+        <f>IF(Project!M6&gt;0,Project!M6,"")</f>
+        <v>3.1124999999999998</v>
+      </c>
+      <c r="N6">
+        <f>IF(Project!N6&gt;0,Project!N6,"")</f>
+        <v>3.05</v>
+      </c>
+      <c r="O6">
+        <f>IF(Project!O6&gt;0,Project!O6,"")</f>
+        <v>3.05</v>
+      </c>
+      <c r="P6">
+        <f>IF(Project!P6&gt;0,Project!P6,"")</f>
+        <v>3.05</v>
+      </c>
+      <c r="Q6" t="str">
+        <f>IF(Project!Q6&gt;0,Project!Q6,"")</f>
+        <v/>
+      </c>
+      <c r="R6" t="str">
+        <f>IF(Project!R6&gt;0,Project!R6,"")</f>
+        <v/>
+      </c>
+      <c r="S6" t="str">
+        <f>IF(Project!S6&gt;0,Project!S6,"")</f>
+        <v/>
+      </c>
+      <c r="T6" t="str">
+        <f>IF(Project!T6&gt;0,Project!T6,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A7" t="str">
+        <f>IF(Project!A7&gt;0,Project!A7,"")</f>
+        <v/>
+      </c>
+      <c r="B7" t="str">
+        <f>IF(Project!B7&gt;0,Project!B7,"")</f>
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <f>IF(Project!C7&gt;0,Project!C7,"")</f>
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <f>IF(Project!D7&gt;0,Project!D7,"")</f>
+        <v/>
+      </c>
+      <c r="E7" t="str">
+        <f>IF(Project!E7&gt;0,Project!E7,"")</f>
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <f>IF(Project!F7&gt;0,Project!F7,"")</f>
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <f>IF(Project!G7&gt;0,Project!G7,"")</f>
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <f>IF(Project!H7&gt;0,Project!H7,"")</f>
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <f>IF(Project!I7&gt;0,Project!I7,"")</f>
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <f>IF(Project!J7&gt;0,Project!J7,"")</f>
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <f>IF(Project!K7&gt;0,Project!K7,"")</f>
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <f>IF(Project!L7&gt;0,Project!L7,"")</f>
+        <v/>
+      </c>
+      <c r="M7" t="str">
+        <f>IF(Project!M7&gt;0,Project!M7,"")</f>
+        <v/>
+      </c>
+      <c r="N7" t="str">
+        <f>IF(Project!N7&gt;0,Project!N7,"")</f>
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <f>IF(Project!O7&gt;0,Project!O7,"")</f>
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <f>IF(Project!P7&gt;0,Project!P7,"")</f>
+        <v/>
+      </c>
+      <c r="Q7" t="str">
+        <f>IF(Project!Q7&gt;0,Project!Q7,"")</f>
+        <v/>
+      </c>
+      <c r="R7" t="str">
+        <f>IF(Project!R7&gt;0,Project!R7,"")</f>
+        <v/>
+      </c>
+      <c r="S7" t="str">
+        <f>IF(Project!S7&gt;0,Project!S7,"")</f>
+        <v/>
+      </c>
+      <c r="T7" t="str">
+        <f>IF(Project!T7&gt;0,Project!T7,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A8" t="str">
+        <f>IF(Project!A8&gt;0,Project!A8,"")</f>
+        <v/>
+      </c>
+      <c r="B8" t="str">
+        <f>IF(Project!B8&gt;0,Project!B8,"")</f>
+        <v/>
+      </c>
+      <c r="C8" t="str">
+        <f>IF(Project!C8&gt;0,Project!C8,"")</f>
+        <v/>
+      </c>
+      <c r="D8" t="str">
+        <f>IF(Project!D8&gt;0,Project!D8,"")</f>
+        <v/>
+      </c>
+      <c r="E8" t="str">
+        <f>IF(Project!E8&gt;0,Project!E8,"")</f>
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <f>IF(Project!F8&gt;0,Project!F8,"")</f>
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <f>IF(Project!G8&gt;0,Project!G8,"")</f>
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <f>IF(Project!H8&gt;0,Project!H8,"")</f>
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <f>IF(Project!I8&gt;0,Project!I8,"")</f>
+        <v/>
+      </c>
+      <c r="J8" t="str">
+        <f>IF(Project!J8&gt;0,Project!J8,"")</f>
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <f>IF(Project!K8&gt;0,Project!K8,"")</f>
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <f>IF(Project!L8&gt;0,Project!L8,"")</f>
+        <v/>
+      </c>
+      <c r="M8" t="str">
+        <f>IF(Project!M8&gt;0,Project!M8,"")</f>
+        <v/>
+      </c>
+      <c r="N8" t="str">
+        <f>IF(Project!N8&gt;0,Project!N8,"")</f>
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <f>IF(Project!O8&gt;0,Project!O8,"")</f>
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <f>IF(Project!P8&gt;0,Project!P8,"")</f>
+        <v/>
+      </c>
+      <c r="Q8" t="str">
+        <f>IF(Project!Q8&gt;0,Project!Q8,"")</f>
+        <v/>
+      </c>
+      <c r="R8" t="str">
+        <f>IF(Project!R8&gt;0,Project!R8,"")</f>
+        <v/>
+      </c>
+      <c r="S8" t="str">
+        <f>IF(Project!S8&gt;0,Project!S8,"")</f>
+        <v/>
+      </c>
+      <c r="T8" t="str">
+        <f>IF(Project!T8&gt;0,Project!T8,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A9" s="63" t="str">
+        <f>IF(Project!A9&gt;0,Project!A9,"")</f>
+        <v>Project by Team</v>
+      </c>
+      <c r="B9" t="str">
+        <f>IF(Project!B9&gt;0,Project!B9,"")</f>
+        <v/>
+      </c>
+      <c r="C9" t="str">
+        <f>IF(Project!C9&gt;0,Project!C9,"")</f>
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <f>IF(Project!D9&gt;0,Project!D9,"")</f>
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <f>IF(Project!E9&gt;0,Project!E9,"")</f>
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <f>IF(Project!F9&gt;0,Project!F9,"")</f>
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <f>IF(Project!G9&gt;0,Project!G9,"")</f>
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <f>IF(Project!H9&gt;0,Project!H9,"")</f>
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <f>IF(Project!I9&gt;0,Project!I9,"")</f>
+        <v/>
+      </c>
+      <c r="J9" t="str">
+        <f>IF(Project!J9&gt;0,Project!J9,"")</f>
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <f>IF(Project!K9&gt;0,Project!K9,"")</f>
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <f>IF(Project!L9&gt;0,Project!L9,"")</f>
+        <v/>
+      </c>
+      <c r="M9" t="str">
+        <f>IF(Project!M9&gt;0,Project!M9,"")</f>
+        <v/>
+      </c>
+      <c r="N9" t="str">
+        <f>IF(Project!N9&gt;0,Project!N9,"")</f>
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <f>IF(Project!O9&gt;0,Project!O9,"")</f>
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <f>IF(Project!P9&gt;0,Project!P9,"")</f>
+        <v/>
+      </c>
+      <c r="Q9" t="str">
+        <f>IF(Project!Q9&gt;0,Project!Q9,"")</f>
+        <v/>
+      </c>
+      <c r="R9" t="str">
+        <f>IF(Project!R9&gt;0,Project!R9,"")</f>
+        <v/>
+      </c>
+      <c r="S9" t="str">
+        <f>IF(Project!S9&gt;0,Project!S9,"")</f>
+        <v/>
+      </c>
+      <c r="T9" t="str">
+        <f>IF(Project!T9&gt;0,Project!T9,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A10" t="str">
+        <f>IF(Project!A10&gt;0,Project!A10,"")</f>
+        <v/>
+      </c>
+      <c r="B10" t="str">
+        <f>IF(Project!B10&gt;0,Project!B10,"")</f>
+        <v/>
+      </c>
+      <c r="C10" t="str">
+        <f>IF(Project!C10&gt;0,Project!C10,"")</f>
+        <v/>
+      </c>
+      <c r="D10" t="str">
+        <f>IF(Project!D10&gt;0,Project!D10,"")</f>
+        <v/>
+      </c>
+      <c r="E10" t="str">
+        <f>IF(Project!E10&gt;0,Project!E10,"")</f>
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <f>IF(Project!F10&gt;0,Project!F10,"")</f>
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <f>IF(Project!G10&gt;0,Project!G10,"")</f>
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <f>IF(Project!H10&gt;0,Project!H10,"")</f>
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <f>IF(Project!I10&gt;0,Project!I10,"")</f>
+        <v/>
+      </c>
+      <c r="J10" t="str">
+        <f>IF(Project!J10&gt;0,Project!J10,"")</f>
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <f>IF(Project!K10&gt;0,Project!K10,"")</f>
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <f>IF(Project!L10&gt;0,Project!L10,"")</f>
+        <v/>
+      </c>
+      <c r="M10" t="str">
+        <f>IF(Project!M10&gt;0,Project!M10,"")</f>
+        <v/>
+      </c>
+      <c r="N10" t="str">
+        <f>IF(Project!N10&gt;0,Project!N10,"")</f>
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <f>IF(Project!O10&gt;0,Project!O10,"")</f>
+        <v/>
+      </c>
+      <c r="P10" t="str">
+        <f>IF(Project!P10&gt;0,Project!P10,"")</f>
+        <v/>
+      </c>
+      <c r="Q10" t="str">
+        <f>IF(Project!Q10&gt;0,Project!Q10,"")</f>
+        <v/>
+      </c>
+      <c r="R10" t="str">
+        <f>IF(Project!R10&gt;0,Project!R10,"")</f>
+        <v/>
+      </c>
+      <c r="S10" t="str">
+        <f>IF(Project!S10&gt;0,Project!S10,"")</f>
+        <v/>
+      </c>
+      <c r="T10" t="str">
+        <f>IF(Project!T10&gt;0,Project!T10,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:20" s="63" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="63" t="str">
+        <f>IF(Project!A11&gt;0,Project!A11,"")</f>
+        <v>Group Name</v>
+      </c>
+      <c r="B11" s="63" t="str">
+        <f>IF(Project!B11&gt;0,Project!B11,"")</f>
+        <v>Total</v>
+      </c>
+      <c r="C11" s="63" t="str">
+        <f>IF(Project!C11&gt;0,Project!C11,"")</f>
+        <v>CPS</v>
+      </c>
+      <c r="D11" s="63" t="str">
+        <f>IF(Project!D11&gt;0,Project!D11,"")</f>
+        <v>PSE-PE</v>
+      </c>
+      <c r="E11" s="63" t="str">
+        <f>IF(Project!E11&gt;0,Project!E11,"")</f>
+        <v>PSE-SE</v>
+      </c>
+      <c r="F11" s="63" t="str">
+        <f>IF(Project!F11&gt;0,Project!F11,"")</f>
+        <v>SD-Design</v>
+      </c>
+      <c r="G11" s="63" t="str">
+        <f>IF(Project!G11&gt;0,Project!G11,"")</f>
+        <v>SD-Data</v>
+      </c>
+      <c r="H11" s="63" t="str">
+        <f>IF(Project!H11&gt;0,Project!H11,"")</f>
+        <v>SD-SA</v>
+      </c>
+      <c r="I11" s="63" t="str">
+        <f>IF(Project!I11&gt;0,Project!I11,"")</f>
+        <v>SD-SRE</v>
+      </c>
+      <c r="J11" s="63" t="str">
+        <f>IF(Project!J11&gt;0,Project!J11,"")</f>
+        <v>SD-CyberSec</v>
+      </c>
+      <c r="K11" s="63" t="str">
+        <f>IF(Project!K11&gt;0,Project!K11,"")</f>
+        <v>SD-PM</v>
+      </c>
+      <c r="L11" s="63" t="str">
+        <f>IF(Project!L11&gt;0,Project!L11,"")</f>
+        <v>SD-BA</v>
+      </c>
+      <c r="M11" s="63" t="str">
+        <f>IF(Project!M11&gt;0,Project!M11,"")</f>
+        <v>SD-QA</v>
+      </c>
+      <c r="N11" s="63" t="str">
+        <f>IF(Project!N11&gt;0,Project!N11,"")</f>
+        <v>SD-TM</v>
+      </c>
+      <c r="O11" s="63" t="str">
+        <f>IF(Project!O11&gt;0,Project!O11,"")</f>
+        <v>AIC-AI</v>
+      </c>
+      <c r="P11" s="63" t="str">
+        <f>IF(Project!P11&gt;0,Project!P11,"")</f>
+        <v>AIC-AIE</v>
+      </c>
+      <c r="Q11" s="63" t="str">
+        <f>IF(Project!Q11&gt;0,Project!Q11,"")</f>
+        <v>AIC-IoT</v>
+      </c>
+      <c r="R11" s="63" t="str">
+        <f>IF(Project!R11&gt;0,Project!R11,"")</f>
+        <v>AIC-SAI</v>
+      </c>
+      <c r="S11" s="63" t="str">
+        <f>IF(Project!S11&gt;0,Project!S11,"")</f>
+        <v>AIC-PSI</v>
+      </c>
+      <c r="T11" s="63" t="str">
+        <f>IF(Project!T11&gt;0,Project!T11,"")</f>
+        <v>TDE</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A12" t="str">
+        <f>IF(Project!A12&gt;0,Project!A12,"")</f>
+        <v>IT Dist</v>
+      </c>
+      <c r="B12">
+        <f>IF(Project!B12&gt;0,Project!B12,"")</f>
+        <v>216</v>
+      </c>
+      <c r="C12" t="str">
+        <f>IF(Project!C12&gt;0,Project!C12,"")</f>
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <f>IF(Project!D12&gt;0,Project!D12,"")</f>
+        <v/>
+      </c>
+      <c r="E12">
+        <f>IF(Project!E12&gt;0,Project!E12,"")</f>
+        <v>216</v>
+      </c>
+      <c r="F12" t="str">
+        <f>IF(Project!F12&gt;0,Project!F12,"")</f>
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <f>IF(Project!G12&gt;0,Project!G12,"")</f>
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <f>IF(Project!H12&gt;0,Project!H12,"")</f>
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <f>IF(Project!I12&gt;0,Project!I12,"")</f>
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <f>IF(Project!J12&gt;0,Project!J12,"")</f>
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <f>IF(Project!K12&gt;0,Project!K12,"")</f>
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <f>IF(Project!L12&gt;0,Project!L12,"")</f>
+        <v/>
+      </c>
+      <c r="M12" t="str">
+        <f>IF(Project!M12&gt;0,Project!M12,"")</f>
+        <v/>
+      </c>
+      <c r="N12" t="str">
+        <f>IF(Project!N12&gt;0,Project!N12,"")</f>
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <f>IF(Project!O12&gt;0,Project!O12,"")</f>
+        <v/>
+      </c>
+      <c r="P12" t="str">
+        <f>IF(Project!P12&gt;0,Project!P12,"")</f>
+        <v/>
+      </c>
+      <c r="Q12" t="str">
+        <f>IF(Project!Q12&gt;0,Project!Q12,"")</f>
+        <v/>
+      </c>
+      <c r="R12" t="str">
+        <f>IF(Project!R12&gt;0,Project!R12,"")</f>
+        <v/>
+      </c>
+      <c r="S12" t="str">
+        <f>IF(Project!S12&gt;0,Project!S12,"")</f>
+        <v/>
+      </c>
+      <c r="T12" t="str">
+        <f>IF(Project!T12&gt;0,Project!T12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A13" t="str">
+        <f>IF(Project!A13&gt;0,Project!A13,"")</f>
+        <v>SCGP e-Ordering</v>
+      </c>
+      <c r="B13">
+        <f>IF(Project!B13&gt;0,Project!B13,"")</f>
+        <v>162.78</v>
+      </c>
+      <c r="C13">
+        <f>IF(Project!C13&gt;0,Project!C13,"")</f>
+        <v>3.6</v>
+      </c>
+      <c r="D13" t="str">
+        <f>IF(Project!D13&gt;0,Project!D13,"")</f>
+        <v/>
+      </c>
+      <c r="E13">
+        <f>IF(Project!E13&gt;0,Project!E13,"")</f>
+        <v>46.3</v>
+      </c>
+      <c r="F13">
+        <f>IF(Project!F13&gt;0,Project!F13,"")</f>
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G13" t="str">
+        <f>IF(Project!G13&gt;0,Project!G13,"")</f>
+        <v/>
+      </c>
+      <c r="H13">
+        <f>IF(Project!H13&gt;0,Project!H13,"")</f>
+        <v>1.05</v>
+      </c>
+      <c r="I13">
+        <f>IF(Project!I13&gt;0,Project!I13,"")</f>
+        <v>1.35</v>
+      </c>
+      <c r="J13" t="str">
+        <f>IF(Project!J13&gt;0,Project!J13,"")</f>
+        <v/>
+      </c>
+      <c r="K13">
+        <f>IF(Project!K13&gt;0,Project!K13,"")</f>
+        <v>7.6</v>
+      </c>
+      <c r="L13">
+        <f>IF(Project!L13&gt;0,Project!L13,"")</f>
+        <v>12</v>
+      </c>
+      <c r="M13">
+        <f>IF(Project!M13&gt;0,Project!M13,"")</f>
+        <v>83.45</v>
+      </c>
+      <c r="N13">
+        <f>IF(Project!N13&gt;0,Project!N13,"")</f>
+        <v>5.13</v>
+      </c>
+      <c r="O13" t="str">
+        <f>IF(Project!O13&gt;0,Project!O13,"")</f>
+        <v/>
+      </c>
+      <c r="P13" t="str">
+        <f>IF(Project!P13&gt;0,Project!P13,"")</f>
+        <v/>
+      </c>
+      <c r="Q13" t="str">
+        <f>IF(Project!Q13&gt;0,Project!Q13,"")</f>
+        <v/>
+      </c>
+      <c r="R13" t="str">
+        <f>IF(Project!R13&gt;0,Project!R13,"")</f>
+        <v/>
+      </c>
+      <c r="S13" t="str">
+        <f>IF(Project!S13&gt;0,Project!S13,"")</f>
+        <v/>
+      </c>
+      <c r="T13" t="str">
+        <f>IF(Project!T13&gt;0,Project!T13,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A14" t="str">
+        <f>IF(Project!A14&gt;0,Project!A14,"")</f>
+        <v>CAP (Common AI Platform)</v>
+      </c>
+      <c r="B14">
+        <f>IF(Project!B14&gt;0,Project!B14,"")</f>
+        <v>63.6</v>
+      </c>
+      <c r="C14" t="str">
+        <f>IF(Project!C14&gt;0,Project!C14,"")</f>
+        <v/>
+      </c>
+      <c r="D14">
+        <f>IF(Project!D14&gt;0,Project!D14,"")</f>
+        <v>61.8</v>
+      </c>
+      <c r="E14" t="str">
+        <f>IF(Project!E14&gt;0,Project!E14,"")</f>
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <f>IF(Project!F14&gt;0,Project!F14,"")</f>
+        <v/>
+      </c>
+      <c r="G14">
+        <f>IF(Project!G14&gt;0,Project!G14,"")</f>
+        <v>0.6</v>
+      </c>
+      <c r="H14" t="str">
+        <f>IF(Project!H14&gt;0,Project!H14,"")</f>
+        <v/>
+      </c>
+      <c r="I14">
+        <f>IF(Project!I14&gt;0,Project!I14,"")</f>
+        <v>1.2</v>
+      </c>
+      <c r="J14" t="str">
+        <f>IF(Project!J14&gt;0,Project!J14,"")</f>
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <f>IF(Project!K14&gt;0,Project!K14,"")</f>
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <f>IF(Project!L14&gt;0,Project!L14,"")</f>
+        <v/>
+      </c>
+      <c r="M14" t="str">
+        <f>IF(Project!M14&gt;0,Project!M14,"")</f>
+        <v/>
+      </c>
+      <c r="N14" t="str">
+        <f>IF(Project!N14&gt;0,Project!N14,"")</f>
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <f>IF(Project!O14&gt;0,Project!O14,"")</f>
+        <v/>
+      </c>
+      <c r="P14" t="str">
+        <f>IF(Project!P14&gt;0,Project!P14,"")</f>
+        <v/>
+      </c>
+      <c r="Q14" t="str">
+        <f>IF(Project!Q14&gt;0,Project!Q14,"")</f>
+        <v/>
+      </c>
+      <c r="R14" t="str">
+        <f>IF(Project!R14&gt;0,Project!R14,"")</f>
+        <v/>
+      </c>
+      <c r="S14" t="str">
+        <f>IF(Project!S14&gt;0,Project!S14,"")</f>
+        <v/>
+      </c>
+      <c r="T14" t="str">
+        <f>IF(Project!T14&gt;0,Project!T14,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A15" t="str">
+        <f>IF(Project!A15&gt;0,Project!A15,"")</f>
+        <v>PromptPlus</v>
+      </c>
+      <c r="B15">
+        <f>IF(Project!B15&gt;0,Project!B15,"")</f>
+        <v>51.075000000000003</v>
+      </c>
+      <c r="C15">
+        <f>IF(Project!C15&gt;0,Project!C15,"")</f>
+        <v>0.9</v>
+      </c>
+      <c r="D15" t="str">
+        <f>IF(Project!D15&gt;0,Project!D15,"")</f>
+        <v/>
+      </c>
+      <c r="E15">
+        <f>IF(Project!E15&gt;0,Project!E15,"")</f>
+        <v>22.8</v>
+      </c>
+      <c r="F15">
+        <f>IF(Project!F15&gt;0,Project!F15,"")</f>
+        <v>1.875</v>
+      </c>
+      <c r="G15" t="str">
+        <f>IF(Project!G15&gt;0,Project!G15,"")</f>
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <f>IF(Project!H15&gt;0,Project!H15,"")</f>
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <f>IF(Project!I15&gt;0,Project!I15,"")</f>
+        <v/>
+      </c>
+      <c r="J15" t="str">
+        <f>IF(Project!J15&gt;0,Project!J15,"")</f>
+        <v/>
+      </c>
+      <c r="K15">
+        <f>IF(Project!K15&gt;0,Project!K15,"")</f>
+        <v>1.8</v>
+      </c>
+      <c r="L15">
+        <f>IF(Project!L15&gt;0,Project!L15,"")</f>
+        <v>7.7</v>
+      </c>
+      <c r="M15">
+        <f>IF(Project!M15&gt;0,Project!M15,"")</f>
+        <v>16</v>
+      </c>
+      <c r="N15" t="str">
+        <f>IF(Project!N15&gt;0,Project!N15,"")</f>
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <f>IF(Project!O15&gt;0,Project!O15,"")</f>
+        <v/>
+      </c>
+      <c r="P15" t="str">
+        <f>IF(Project!P15&gt;0,Project!P15,"")</f>
+        <v/>
+      </c>
+      <c r="Q15" t="str">
+        <f>IF(Project!Q15&gt;0,Project!Q15,"")</f>
+        <v/>
+      </c>
+      <c r="R15" t="str">
+        <f>IF(Project!R15&gt;0,Project!R15,"")</f>
+        <v/>
+      </c>
+      <c r="S15" t="str">
+        <f>IF(Project!S15&gt;0,Project!S15,"")</f>
+        <v/>
+      </c>
+      <c r="T15" t="str">
+        <f>IF(Project!T15&gt;0,Project!T15,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A16" t="str">
+        <f>IF(Project!A16&gt;0,Project!A16,"")</f>
+        <v>WeShape platform</v>
+      </c>
+      <c r="B16">
+        <f>IF(Project!B16&gt;0,Project!B16,"")</f>
+        <v>35.454999999999998</v>
+      </c>
+      <c r="C16" t="str">
+        <f>IF(Project!C16&gt;0,Project!C16,"")</f>
+        <v/>
+      </c>
+      <c r="D16" t="str">
+        <f>IF(Project!D16&gt;0,Project!D16,"")</f>
+        <v/>
+      </c>
+      <c r="E16">
+        <f>IF(Project!E16&gt;0,Project!E16,"")</f>
+        <v>7.2</v>
+      </c>
+      <c r="F16">
+        <f>IF(Project!F16&gt;0,Project!F16,"")</f>
+        <v>0.375</v>
+      </c>
+      <c r="G16" t="str">
+        <f>IF(Project!G16&gt;0,Project!G16,"")</f>
+        <v/>
+      </c>
+      <c r="H16">
+        <f>IF(Project!H16&gt;0,Project!H16,"")</f>
+        <v>1.8</v>
+      </c>
+      <c r="I16">
+        <f>IF(Project!I16&gt;0,Project!I16,"")</f>
+        <v>0.65</v>
+      </c>
+      <c r="J16" t="str">
+        <f>IF(Project!J16&gt;0,Project!J16,"")</f>
+        <v/>
+      </c>
+      <c r="K16">
+        <f>IF(Project!K16&gt;0,Project!K16,"")</f>
+        <v>1.65</v>
+      </c>
+      <c r="L16">
+        <f>IF(Project!L16&gt;0,Project!L16,"")</f>
+        <v>7.2</v>
+      </c>
+      <c r="M16">
+        <f>IF(Project!M16&gt;0,Project!M16,"")</f>
+        <v>5.4</v>
+      </c>
+      <c r="N16" t="str">
+        <f>IF(Project!N16&gt;0,Project!N16,"")</f>
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <f>IF(Project!O16&gt;0,Project!O16,"")</f>
+        <v/>
+      </c>
+      <c r="P16" t="str">
+        <f>IF(Project!P16&gt;0,Project!P16,"")</f>
+        <v/>
+      </c>
+      <c r="Q16" t="str">
+        <f>IF(Project!Q16&gt;0,Project!Q16,"")</f>
+        <v/>
+      </c>
+      <c r="R16">
+        <f>IF(Project!R16&gt;0,Project!R16,"")</f>
+        <v>11.18</v>
+      </c>
+      <c r="S16" t="str">
+        <f>IF(Project!S16&gt;0,Project!S16,"")</f>
+        <v/>
+      </c>
+      <c r="T16" t="str">
+        <f>IF(Project!T16&gt;0,Project!T16,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A17" t="str">
+        <f>IF(Project!A17&gt;0,Project!A17,"")</f>
+        <v/>
+      </c>
+      <c r="B17" t="str">
+        <f>IF(Project!B17&gt;0,Project!B17,"")</f>
+        <v/>
+      </c>
+      <c r="C17" t="str">
+        <f>IF(Project!C17&gt;0,Project!C17,"")</f>
+        <v/>
+      </c>
+      <c r="D17" t="str">
+        <f>IF(Project!D17&gt;0,Project!D17,"")</f>
+        <v/>
+      </c>
+      <c r="E17" t="str">
+        <f>IF(Project!E17&gt;0,Project!E17,"")</f>
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <f>IF(Project!F17&gt;0,Project!F17,"")</f>
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <f>IF(Project!G17&gt;0,Project!G17,"")</f>
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <f>IF(Project!H17&gt;0,Project!H17,"")</f>
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <f>IF(Project!I17&gt;0,Project!I17,"")</f>
+        <v/>
+      </c>
+      <c r="J17" t="str">
+        <f>IF(Project!J17&gt;0,Project!J17,"")</f>
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <f>IF(Project!K17&gt;0,Project!K17,"")</f>
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <f>IF(Project!L17&gt;0,Project!L17,"")</f>
+        <v/>
+      </c>
+      <c r="M17" t="str">
+        <f>IF(Project!M17&gt;0,Project!M17,"")</f>
+        <v/>
+      </c>
+      <c r="N17" t="str">
+        <f>IF(Project!N17&gt;0,Project!N17,"")</f>
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <f>IF(Project!O17&gt;0,Project!O17,"")</f>
+        <v/>
+      </c>
+      <c r="P17" t="str">
+        <f>IF(Project!P17&gt;0,Project!P17,"")</f>
+        <v/>
+      </c>
+      <c r="Q17" t="str">
+        <f>IF(Project!Q17&gt;0,Project!Q17,"")</f>
+        <v/>
+      </c>
+      <c r="R17" t="str">
+        <f>IF(Project!R17&gt;0,Project!R17,"")</f>
+        <v/>
+      </c>
+      <c r="S17" t="str">
+        <f>IF(Project!S17&gt;0,Project!S17,"")</f>
+        <v/>
+      </c>
+      <c r="T17" t="str">
+        <f>IF(Project!T17&gt;0,Project!T17,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A18" t="str">
+        <f>IF(Project!A18&gt;0,Project!A18,"")</f>
+        <v/>
+      </c>
+      <c r="B18" t="str">
+        <f>IF(Project!B18&gt;0,Project!B18,"")</f>
+        <v/>
+      </c>
+      <c r="C18" t="str">
+        <f>IF(Project!C18&gt;0,Project!C18,"")</f>
+        <v/>
+      </c>
+      <c r="D18" t="str">
+        <f>IF(Project!D18&gt;0,Project!D18,"")</f>
+        <v/>
+      </c>
+      <c r="E18" t="str">
+        <f>IF(Project!E18&gt;0,Project!E18,"")</f>
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <f>IF(Project!F18&gt;0,Project!F18,"")</f>
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <f>IF(Project!G18&gt;0,Project!G18,"")</f>
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <f>IF(Project!H18&gt;0,Project!H18,"")</f>
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <f>IF(Project!I18&gt;0,Project!I18,"")</f>
+        <v/>
+      </c>
+      <c r="J18" t="str">
+        <f>IF(Project!J18&gt;0,Project!J18,"")</f>
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <f>IF(Project!K18&gt;0,Project!K18,"")</f>
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <f>IF(Project!L18&gt;0,Project!L18,"")</f>
+        <v/>
+      </c>
+      <c r="M18" t="str">
+        <f>IF(Project!M18&gt;0,Project!M18,"")</f>
+        <v/>
+      </c>
+      <c r="N18" t="str">
+        <f>IF(Project!N18&gt;0,Project!N18,"")</f>
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <f>IF(Project!O18&gt;0,Project!O18,"")</f>
+        <v/>
+      </c>
+      <c r="P18" t="str">
+        <f>IF(Project!P18&gt;0,Project!P18,"")</f>
+        <v/>
+      </c>
+      <c r="Q18" t="str">
+        <f>IF(Project!Q18&gt;0,Project!Q18,"")</f>
+        <v/>
+      </c>
+      <c r="R18" t="str">
+        <f>IF(Project!R18&gt;0,Project!R18,"")</f>
+        <v/>
+      </c>
+      <c r="S18" t="str">
+        <f>IF(Project!S18&gt;0,Project!S18,"")</f>
+        <v/>
+      </c>
+      <c r="T18" t="str">
+        <f>IF(Project!T18&gt;0,Project!T18,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:20" s="63" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="63" t="str">
+        <f>IF(Project!A19&gt;0,Project!A19,"")</f>
+        <v>Project by Type</v>
+      </c>
+      <c r="B19" s="63" t="str">
+        <f>IF(Project!B19&gt;0,Project!B19,"")</f>
+        <v/>
+      </c>
+      <c r="C19" s="63" t="str">
+        <f>IF(Project!C19&gt;0,Project!C19,"")</f>
+        <v/>
+      </c>
+      <c r="D19" s="63" t="str">
+        <f>IF(Project!D19&gt;0,Project!D19,"")</f>
+        <v/>
+      </c>
+      <c r="E19" s="63" t="str">
+        <f>IF(Project!E19&gt;0,Project!E19,"")</f>
+        <v/>
+      </c>
+      <c r="F19" s="63" t="str">
+        <f>IF(Project!F19&gt;0,Project!F19,"")</f>
+        <v/>
+      </c>
+      <c r="G19" s="63" t="str">
+        <f>IF(Project!G19&gt;0,Project!G19,"")</f>
+        <v/>
+      </c>
+      <c r="H19" s="63" t="str">
+        <f>IF(Project!H19&gt;0,Project!H19,"")</f>
+        <v/>
+      </c>
+      <c r="I19" s="63" t="str">
+        <f>IF(Project!I19&gt;0,Project!I19,"")</f>
+        <v/>
+      </c>
+      <c r="J19" s="63" t="str">
+        <f>IF(Project!J19&gt;0,Project!J19,"")</f>
+        <v/>
+      </c>
+      <c r="K19" s="63" t="str">
+        <f>IF(Project!K19&gt;0,Project!K19,"")</f>
+        <v/>
+      </c>
+      <c r="L19" s="63" t="str">
+        <f>IF(Project!L19&gt;0,Project!L19,"")</f>
+        <v/>
+      </c>
+      <c r="M19" s="63" t="str">
+        <f>IF(Project!M19&gt;0,Project!M19,"")</f>
+        <v/>
+      </c>
+      <c r="N19" s="63" t="str">
+        <f>IF(Project!N19&gt;0,Project!N19,"")</f>
+        <v/>
+      </c>
+      <c r="O19" s="63" t="str">
+        <f>IF(Project!O19&gt;0,Project!O19,"")</f>
+        <v/>
+      </c>
+      <c r="P19" s="63" t="str">
+        <f>IF(Project!P19&gt;0,Project!P19,"")</f>
+        <v/>
+      </c>
+      <c r="Q19" s="63" t="str">
+        <f>IF(Project!Q19&gt;0,Project!Q19,"")</f>
+        <v/>
+      </c>
+      <c r="R19" s="63" t="str">
+        <f>IF(Project!R19&gt;0,Project!R19,"")</f>
+        <v/>
+      </c>
+      <c r="S19" s="63" t="str">
+        <f>IF(Project!S19&gt;0,Project!S19,"")</f>
+        <v/>
+      </c>
+      <c r="T19" s="63" t="str">
+        <f>IF(Project!T19&gt;0,Project!T19,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:20" s="63" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="63" t="str">
+        <f>IF(Project!A20&gt;0,Project!A20,"")</f>
+        <v/>
+      </c>
+      <c r="B20" s="63" t="str">
+        <f>IF(Project!B20&gt;0,Project!B20,"")</f>
+        <v/>
+      </c>
+      <c r="C20" s="63" t="str">
+        <f>IF(Project!C20&gt;0,Project!C20,"")</f>
+        <v/>
+      </c>
+      <c r="D20" s="63" t="str">
+        <f>IF(Project!D20&gt;0,Project!D20,"")</f>
+        <v/>
+      </c>
+      <c r="E20" s="63" t="str">
+        <f>IF(Project!E20&gt;0,Project!E20,"")</f>
+        <v/>
+      </c>
+      <c r="F20" s="63" t="str">
+        <f>IF(Project!F20&gt;0,Project!F20,"")</f>
+        <v/>
+      </c>
+      <c r="G20" s="63" t="str">
+        <f>IF(Project!G20&gt;0,Project!G20,"")</f>
+        <v/>
+      </c>
+      <c r="H20" s="63" t="str">
+        <f>IF(Project!H20&gt;0,Project!H20,"")</f>
+        <v/>
+      </c>
+      <c r="I20" s="63" t="str">
+        <f>IF(Project!I20&gt;0,Project!I20,"")</f>
+        <v/>
+      </c>
+      <c r="J20" s="63" t="str">
+        <f>IF(Project!J20&gt;0,Project!J20,"")</f>
+        <v/>
+      </c>
+      <c r="K20" s="63" t="str">
+        <f>IF(Project!K20&gt;0,Project!K20,"")</f>
+        <v/>
+      </c>
+      <c r="L20" s="63" t="str">
+        <f>IF(Project!L20&gt;0,Project!L20,"")</f>
+        <v/>
+      </c>
+      <c r="M20" s="63" t="str">
+        <f>IF(Project!M20&gt;0,Project!M20,"")</f>
+        <v/>
+      </c>
+      <c r="N20" s="63" t="str">
+        <f>IF(Project!N20&gt;0,Project!N20,"")</f>
+        <v/>
+      </c>
+      <c r="O20" s="63" t="str">
+        <f>IF(Project!O20&gt;0,Project!O20,"")</f>
+        <v/>
+      </c>
+      <c r="P20" s="63" t="str">
+        <f>IF(Project!P20&gt;0,Project!P20,"")</f>
+        <v/>
+      </c>
+      <c r="Q20" s="63" t="str">
+        <f>IF(Project!Q20&gt;0,Project!Q20,"")</f>
+        <v/>
+      </c>
+      <c r="R20" s="63" t="str">
+        <f>IF(Project!R20&gt;0,Project!R20,"")</f>
+        <v/>
+      </c>
+      <c r="S20" s="63" t="str">
+        <f>IF(Project!S20&gt;0,Project!S20,"")</f>
+        <v/>
+      </c>
+      <c r="T20" s="63" t="str">
+        <f>IF(Project!T20&gt;0,Project!T20,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:20" s="63" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="63" t="str">
+        <f>IF(Project!A21&gt;0,Project!A21,"")</f>
+        <v>Group Name</v>
+      </c>
+      <c r="B21" s="63" t="str">
+        <f>IF(Project!B21&gt;0,Project!B21,"")</f>
+        <v>Presale</v>
+      </c>
+      <c r="C21" s="63" t="str">
+        <f>IF(Project!C21&gt;0,Project!C21,"")</f>
+        <v>Project</v>
+      </c>
+      <c r="D21" s="63" t="str">
+        <f>IF(Project!D21&gt;0,Project!D21,"")</f>
+        <v>TM</v>
+      </c>
+      <c r="E21" s="63" t="str">
+        <f>IF(Project!E21&gt;0,Project!E21,"")</f>
+        <v>Infra</v>
+      </c>
+      <c r="F21" s="63" t="str">
+        <f>IF(Project!F21&gt;0,Project!F21,"")</f>
+        <v>Spatial Lab</v>
+      </c>
+      <c r="G21" s="63" t="str">
+        <f>IF(Project!G21&gt;0,Project!G21,"")</f>
+        <v>Warmbody</v>
+      </c>
+      <c r="H21" s="63" t="str">
+        <f>IF(Project!H21&gt;0,Project!H21,"")</f>
+        <v>Grand Total</v>
+      </c>
+      <c r="I21" s="63" t="str">
+        <f>IF(Project!I21&gt;0,Project!I21,"")</f>
+        <v/>
+      </c>
+      <c r="J21" s="63" t="str">
+        <f>IF(Project!J21&gt;0,Project!J21,"")</f>
+        <v/>
+      </c>
+      <c r="K21" s="63" t="str">
+        <f>IF(Project!K21&gt;0,Project!K21,"")</f>
+        <v/>
+      </c>
+      <c r="L21" s="63" t="str">
+        <f>IF(Project!L21&gt;0,Project!L21,"")</f>
+        <v/>
+      </c>
+      <c r="M21" s="63" t="str">
+        <f>IF(Project!M21&gt;0,Project!M21,"")</f>
+        <v/>
+      </c>
+      <c r="N21" s="63" t="str">
+        <f>IF(Project!N21&gt;0,Project!N21,"")</f>
+        <v/>
+      </c>
+      <c r="O21" s="63" t="str">
+        <f>IF(Project!O21&gt;0,Project!O21,"")</f>
+        <v/>
+      </c>
+      <c r="P21" s="63" t="str">
+        <f>IF(Project!P21&gt;0,Project!P21,"")</f>
+        <v/>
+      </c>
+      <c r="Q21" s="63" t="str">
+        <f>IF(Project!Q21&gt;0,Project!Q21,"")</f>
+        <v/>
+      </c>
+      <c r="R21" s="63" t="str">
+        <f>IF(Project!R21&gt;0,Project!R21,"")</f>
+        <v/>
+      </c>
+      <c r="S21" s="63" t="str">
+        <f>IF(Project!S21&gt;0,Project!S21,"")</f>
+        <v/>
+      </c>
+      <c r="T21" s="63" t="str">
+        <f>IF(Project!T21&gt;0,Project!T21,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A22" t="str">
+        <f>IF(Project!A22&gt;0,Project!A22,"")</f>
+        <v>IT Dist</v>
+      </c>
+      <c r="B22">
+        <f>IF(Project!B22&gt;0,Project!B22,"")</f>
+        <v>36</v>
+      </c>
+      <c r="C22" t="str">
+        <f>IF(Project!C22&gt;0,Project!C22,"")</f>
+        <v/>
+      </c>
+      <c r="D22" t="str">
+        <f>IF(Project!D22&gt;0,Project!D22,"")</f>
+        <v/>
+      </c>
+      <c r="E22" t="str">
+        <f>IF(Project!E22&gt;0,Project!E22,"")</f>
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <f>IF(Project!F22&gt;0,Project!F22,"")</f>
+        <v/>
+      </c>
+      <c r="G22">
+        <f>IF(Project!G22&gt;0,Project!G22,"")</f>
+        <v>180</v>
+      </c>
+      <c r="H22">
+        <f>IF(Project!H22&gt;0,Project!H22,"")</f>
+        <v>216</v>
+      </c>
+      <c r="I22" t="str">
+        <f>IF(Project!I22&gt;0,Project!I22,"")</f>
+        <v/>
+      </c>
+      <c r="J22" t="str">
+        <f>IF(Project!J22&gt;0,Project!J22,"")</f>
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <f>IF(Project!K22&gt;0,Project!K22,"")</f>
+        <v/>
+      </c>
+      <c r="L22" t="str">
+        <f>IF(Project!L22&gt;0,Project!L22,"")</f>
+        <v/>
+      </c>
+      <c r="M22" t="str">
+        <f>IF(Project!M22&gt;0,Project!M22,"")</f>
+        <v/>
+      </c>
+      <c r="N22" t="str">
+        <f>IF(Project!N22&gt;0,Project!N22,"")</f>
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <f>IF(Project!O22&gt;0,Project!O22,"")</f>
+        <v/>
+      </c>
+      <c r="P22" t="str">
+        <f>IF(Project!P22&gt;0,Project!P22,"")</f>
+        <v/>
+      </c>
+      <c r="Q22" t="str">
+        <f>IF(Project!Q22&gt;0,Project!Q22,"")</f>
+        <v/>
+      </c>
+      <c r="R22" t="str">
+        <f>IF(Project!R22&gt;0,Project!R22,"")</f>
+        <v/>
+      </c>
+      <c r="S22" t="str">
+        <f>IF(Project!S22&gt;0,Project!S22,"")</f>
+        <v/>
+      </c>
+      <c r="T22" t="str">
+        <f>IF(Project!T22&gt;0,Project!T22,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A23" t="str">
+        <f>IF(Project!A23&gt;0,Project!A23,"")</f>
+        <v>SCGP e-Ordering</v>
+      </c>
+      <c r="B23">
+        <f>IF(Project!B23&gt;0,Project!B23,"")</f>
+        <v>2.7</v>
+      </c>
+      <c r="C23">
+        <f>IF(Project!C23&gt;0,Project!C23,"")</f>
+        <v>154.05000000000001</v>
+      </c>
+      <c r="D23">
+        <f>IF(Project!D23&gt;0,Project!D23,"")</f>
+        <v>5.13</v>
+      </c>
+      <c r="E23">
+        <f>IF(Project!E23&gt;0,Project!E23,"")</f>
+        <v>0.9</v>
+      </c>
+      <c r="F23" t="str">
+        <f>IF(Project!F23&gt;0,Project!F23,"")</f>
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <f>IF(Project!G23&gt;0,Project!G23,"")</f>
+        <v/>
+      </c>
+      <c r="H23">
+        <f>IF(Project!H23&gt;0,Project!H23,"")</f>
+        <v>162.78</v>
+      </c>
+      <c r="I23" t="str">
+        <f>IF(Project!I23&gt;0,Project!I23,"")</f>
+        <v/>
+      </c>
+      <c r="J23" t="str">
+        <f>IF(Project!J23&gt;0,Project!J23,"")</f>
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <f>IF(Project!K23&gt;0,Project!K23,"")</f>
+        <v/>
+      </c>
+      <c r="L23" t="str">
+        <f>IF(Project!L23&gt;0,Project!L23,"")</f>
+        <v/>
+      </c>
+      <c r="M23" t="str">
+        <f>IF(Project!M23&gt;0,Project!M23,"")</f>
+        <v/>
+      </c>
+      <c r="N23" t="str">
+        <f>IF(Project!N23&gt;0,Project!N23,"")</f>
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <f>IF(Project!O23&gt;0,Project!O23,"")</f>
+        <v/>
+      </c>
+      <c r="P23" t="str">
+        <f>IF(Project!P23&gt;0,Project!P23,"")</f>
+        <v/>
+      </c>
+      <c r="Q23" t="str">
+        <f>IF(Project!Q23&gt;0,Project!Q23,"")</f>
+        <v/>
+      </c>
+      <c r="R23" t="str">
+        <f>IF(Project!R23&gt;0,Project!R23,"")</f>
+        <v/>
+      </c>
+      <c r="S23" t="str">
+        <f>IF(Project!S23&gt;0,Project!S23,"")</f>
+        <v/>
+      </c>
+      <c r="T23" t="str">
+        <f>IF(Project!T23&gt;0,Project!T23,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A24" t="str">
+        <f>IF(Project!A24&gt;0,Project!A24,"")</f>
+        <v>CAP (Common AI Platform)</v>
+      </c>
+      <c r="B24" t="str">
+        <f>IF(Project!B24&gt;0,Project!B24,"")</f>
+        <v/>
+      </c>
+      <c r="C24">
+        <f>IF(Project!C24&gt;0,Project!C24,"")</f>
+        <v>63.6</v>
+      </c>
+      <c r="D24" t="str">
+        <f>IF(Project!D24&gt;0,Project!D24,"")</f>
+        <v/>
+      </c>
+      <c r="E24" t="str">
+        <f>IF(Project!E24&gt;0,Project!E24,"")</f>
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <f>IF(Project!F24&gt;0,Project!F24,"")</f>
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <f>IF(Project!G24&gt;0,Project!G24,"")</f>
+        <v/>
+      </c>
+      <c r="H24">
+        <f>IF(Project!H24&gt;0,Project!H24,"")</f>
+        <v>63.6</v>
+      </c>
+      <c r="I24" t="str">
+        <f>IF(Project!I24&gt;0,Project!I24,"")</f>
+        <v/>
+      </c>
+      <c r="J24" t="str">
+        <f>IF(Project!J24&gt;0,Project!J24,"")</f>
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <f>IF(Project!K24&gt;0,Project!K24,"")</f>
+        <v/>
+      </c>
+      <c r="L24" t="str">
+        <f>IF(Project!L24&gt;0,Project!L24,"")</f>
+        <v/>
+      </c>
+      <c r="M24" t="str">
+        <f>IF(Project!M24&gt;0,Project!M24,"")</f>
+        <v/>
+      </c>
+      <c r="N24" t="str">
+        <f>IF(Project!N24&gt;0,Project!N24,"")</f>
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <f>IF(Project!O24&gt;0,Project!O24,"")</f>
+        <v/>
+      </c>
+      <c r="P24" t="str">
+        <f>IF(Project!P24&gt;0,Project!P24,"")</f>
+        <v/>
+      </c>
+      <c r="Q24" t="str">
+        <f>IF(Project!Q24&gt;0,Project!Q24,"")</f>
+        <v/>
+      </c>
+      <c r="R24" t="str">
+        <f>IF(Project!R24&gt;0,Project!R24,"")</f>
+        <v/>
+      </c>
+      <c r="S24" t="str">
+        <f>IF(Project!S24&gt;0,Project!S24,"")</f>
+        <v/>
+      </c>
+      <c r="T24" t="str">
+        <f>IF(Project!T24&gt;0,Project!T24,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A25" t="str">
+        <f>IF(Project!A25&gt;0,Project!A25,"")</f>
+        <v>PromptPlus</v>
+      </c>
+      <c r="B25" t="str">
+        <f>IF(Project!B25&gt;0,Project!B25,"")</f>
+        <v/>
+      </c>
+      <c r="C25">
+        <f>IF(Project!C25&gt;0,Project!C25,"")</f>
+        <v>27.375</v>
+      </c>
+      <c r="D25" t="str">
+        <f>IF(Project!D25&gt;0,Project!D25,"")</f>
+        <v/>
+      </c>
+      <c r="E25" t="str">
+        <f>IF(Project!E25&gt;0,Project!E25,"")</f>
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <f>IF(Project!F25&gt;0,Project!F25,"")</f>
+        <v/>
+      </c>
+      <c r="G25">
+        <f>IF(Project!G25&gt;0,Project!G25,"")</f>
+        <v>23.7</v>
+      </c>
+      <c r="H25">
+        <f>IF(Project!H25&gt;0,Project!H25,"")</f>
+        <v>51.075000000000003</v>
+      </c>
+      <c r="I25" t="str">
+        <f>IF(Project!I25&gt;0,Project!I25,"")</f>
+        <v/>
+      </c>
+      <c r="J25" t="str">
+        <f>IF(Project!J25&gt;0,Project!J25,"")</f>
+        <v/>
+      </c>
+      <c r="K25" t="str">
+        <f>IF(Project!K25&gt;0,Project!K25,"")</f>
+        <v/>
+      </c>
+      <c r="L25" t="str">
+        <f>IF(Project!L25&gt;0,Project!L25,"")</f>
+        <v/>
+      </c>
+      <c r="M25" t="str">
+        <f>IF(Project!M25&gt;0,Project!M25,"")</f>
+        <v/>
+      </c>
+      <c r="N25" t="str">
+        <f>IF(Project!N25&gt;0,Project!N25,"")</f>
+        <v/>
+      </c>
+      <c r="O25" t="str">
+        <f>IF(Project!O25&gt;0,Project!O25,"")</f>
+        <v/>
+      </c>
+      <c r="P25" t="str">
+        <f>IF(Project!P25&gt;0,Project!P25,"")</f>
+        <v/>
+      </c>
+      <c r="Q25" t="str">
+        <f>IF(Project!Q25&gt;0,Project!Q25,"")</f>
+        <v/>
+      </c>
+      <c r="R25" t="str">
+        <f>IF(Project!R25&gt;0,Project!R25,"")</f>
+        <v/>
+      </c>
+      <c r="S25" t="str">
+        <f>IF(Project!S25&gt;0,Project!S25,"")</f>
+        <v/>
+      </c>
+      <c r="T25" t="str">
+        <f>IF(Project!T25&gt;0,Project!T25,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A26" t="str">
+        <f>IF(Project!A26&gt;0,Project!A26,"")</f>
+        <v>WeShape platform</v>
+      </c>
+      <c r="B26">
+        <f>IF(Project!B26&gt;0,Project!B26,"")</f>
+        <v>0.8</v>
+      </c>
+      <c r="C26" t="str">
+        <f>IF(Project!C26&gt;0,Project!C26,"")</f>
+        <v/>
+      </c>
+      <c r="D26" t="str">
+        <f>IF(Project!D26&gt;0,Project!D26,"")</f>
+        <v/>
+      </c>
+      <c r="E26" t="str">
+        <f>IF(Project!E26&gt;0,Project!E26,"")</f>
+        <v/>
+      </c>
+      <c r="F26">
+        <f>IF(Project!F26&gt;0,Project!F26,"")</f>
+        <v>34.655000000000001</v>
+      </c>
+      <c r="G26" t="str">
+        <f>IF(Project!G26&gt;0,Project!G26,"")</f>
+        <v/>
+      </c>
+      <c r="H26">
+        <f>IF(Project!H26&gt;0,Project!H26,"")</f>
+        <v>35.454999999999998</v>
+      </c>
+      <c r="I26" t="str">
+        <f>IF(Project!I26&gt;0,Project!I26,"")</f>
+        <v/>
+      </c>
+      <c r="J26" t="str">
+        <f>IF(Project!J26&gt;0,Project!J26,"")</f>
+        <v/>
+      </c>
+      <c r="K26" t="str">
+        <f>IF(Project!K26&gt;0,Project!K26,"")</f>
+        <v/>
+      </c>
+      <c r="L26" t="str">
+        <f>IF(Project!L26&gt;0,Project!L26,"")</f>
+        <v/>
+      </c>
+      <c r="M26" t="str">
+        <f>IF(Project!M26&gt;0,Project!M26,"")</f>
+        <v/>
+      </c>
+      <c r="N26" t="str">
+        <f>IF(Project!N26&gt;0,Project!N26,"")</f>
+        <v/>
+      </c>
+      <c r="O26" t="str">
+        <f>IF(Project!O26&gt;0,Project!O26,"")</f>
+        <v/>
+      </c>
+      <c r="P26" t="str">
+        <f>IF(Project!P26&gt;0,Project!P26,"")</f>
+        <v/>
+      </c>
+      <c r="Q26" t="str">
+        <f>IF(Project!Q26&gt;0,Project!Q26,"")</f>
+        <v/>
+      </c>
+      <c r="R26" t="str">
+        <f>IF(Project!R26&gt;0,Project!R26,"")</f>
+        <v/>
+      </c>
+      <c r="S26" t="str">
+        <f>IF(Project!S26&gt;0,Project!S26,"")</f>
+        <v/>
+      </c>
+      <c r="T26" t="str">
+        <f>IF(Project!T26&gt;0,Project!T26,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A27" t="str">
+        <f>IF(Project!A27&gt;0,Project!A27,"")</f>
+        <v/>
+      </c>
+      <c r="B27" t="str">
+        <f>IF(Project!B27&gt;0,Project!B27,"")</f>
+        <v/>
+      </c>
+      <c r="C27" t="str">
+        <f>IF(Project!C27&gt;0,Project!C27,"")</f>
+        <v/>
+      </c>
+      <c r="D27" t="str">
+        <f>IF(Project!D27&gt;0,Project!D27,"")</f>
+        <v/>
+      </c>
+      <c r="E27" t="str">
+        <f>IF(Project!E27&gt;0,Project!E27,"")</f>
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <f>IF(Project!F27&gt;0,Project!F27,"")</f>
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <f>IF(Project!G27&gt;0,Project!G27,"")</f>
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <f>IF(Project!H27&gt;0,Project!H27,"")</f>
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <f>IF(Project!I27&gt;0,Project!I27,"")</f>
+        <v/>
+      </c>
+      <c r="J27" t="str">
+        <f>IF(Project!J27&gt;0,Project!J27,"")</f>
+        <v/>
+      </c>
+      <c r="K27" t="str">
+        <f>IF(Project!K27&gt;0,Project!K27,"")</f>
+        <v/>
+      </c>
+      <c r="L27" t="str">
+        <f>IF(Project!L27&gt;0,Project!L27,"")</f>
+        <v/>
+      </c>
+      <c r="M27" t="str">
+        <f>IF(Project!M27&gt;0,Project!M27,"")</f>
+        <v/>
+      </c>
+      <c r="N27" t="str">
+        <f>IF(Project!N27&gt;0,Project!N27,"")</f>
+        <v/>
+      </c>
+      <c r="O27" t="str">
+        <f>IF(Project!O27&gt;0,Project!O27,"")</f>
+        <v/>
+      </c>
+      <c r="P27" t="str">
+        <f>IF(Project!P27&gt;0,Project!P27,"")</f>
+        <v/>
+      </c>
+      <c r="Q27" t="str">
+        <f>IF(Project!Q27&gt;0,Project!Q27,"")</f>
+        <v/>
+      </c>
+      <c r="R27" t="str">
+        <f>IF(Project!R27&gt;0,Project!R27,"")</f>
+        <v/>
+      </c>
+      <c r="S27" t="str">
+        <f>IF(Project!S27&gt;0,Project!S27,"")</f>
+        <v/>
+      </c>
+      <c r="T27" t="str">
+        <f>IF(Project!T27&gt;0,Project!T27,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A28" t="str">
+        <f>IF(Project!A28&gt;0,Project!A28,"")</f>
+        <v/>
+      </c>
+      <c r="B28" t="str">
+        <f>IF(Project!B28&gt;0,Project!B28,"")</f>
+        <v/>
+      </c>
+      <c r="C28" t="str">
+        <f>IF(Project!C28&gt;0,Project!C28,"")</f>
+        <v/>
+      </c>
+      <c r="D28" t="str">
+        <f>IF(Project!D28&gt;0,Project!D28,"")</f>
+        <v/>
+      </c>
+      <c r="E28" t="str">
+        <f>IF(Project!E28&gt;0,Project!E28,"")</f>
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <f>IF(Project!F28&gt;0,Project!F28,"")</f>
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <f>IF(Project!G28&gt;0,Project!G28,"")</f>
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <f>IF(Project!H28&gt;0,Project!H28,"")</f>
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <f>IF(Project!I28&gt;0,Project!I28,"")</f>
+        <v/>
+      </c>
+      <c r="J28" t="str">
+        <f>IF(Project!J28&gt;0,Project!J28,"")</f>
+        <v/>
+      </c>
+      <c r="K28" t="str">
+        <f>IF(Project!K28&gt;0,Project!K28,"")</f>
+        <v/>
+      </c>
+      <c r="L28" t="str">
+        <f>IF(Project!L28&gt;0,Project!L28,"")</f>
+        <v/>
+      </c>
+      <c r="M28" t="str">
+        <f>IF(Project!M28&gt;0,Project!M28,"")</f>
+        <v/>
+      </c>
+      <c r="N28" t="str">
+        <f>IF(Project!N28&gt;0,Project!N28,"")</f>
+        <v/>
+      </c>
+      <c r="O28" t="str">
+        <f>IF(Project!O28&gt;0,Project!O28,"")</f>
+        <v/>
+      </c>
+      <c r="P28" t="str">
+        <f>IF(Project!P28&gt;0,Project!P28,"")</f>
+        <v/>
+      </c>
+      <c r="Q28" t="str">
+        <f>IF(Project!Q28&gt;0,Project!Q28,"")</f>
+        <v/>
+      </c>
+      <c r="R28" t="str">
+        <f>IF(Project!R28&gt;0,Project!R28,"")</f>
+        <v/>
+      </c>
+      <c r="S28" t="str">
+        <f>IF(Project!S28&gt;0,Project!S28,"")</f>
+        <v/>
+      </c>
+      <c r="T28" t="str">
+        <f>IF(Project!T28&gt;0,Project!T28,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A29" t="str">
+        <f>IF(Project!A29&gt;0,Project!A29,"")</f>
+        <v/>
+      </c>
+      <c r="B29" t="str">
+        <f>IF(Project!B29&gt;0,Project!B29,"")</f>
+        <v/>
+      </c>
+      <c r="C29" t="str">
+        <f>IF(Project!C29&gt;0,Project!C29,"")</f>
+        <v/>
+      </c>
+      <c r="D29" t="str">
+        <f>IF(Project!D29&gt;0,Project!D29,"")</f>
+        <v/>
+      </c>
+      <c r="E29" t="str">
+        <f>IF(Project!E29&gt;0,Project!E29,"")</f>
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <f>IF(Project!F29&gt;0,Project!F29,"")</f>
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <f>IF(Project!G29&gt;0,Project!G29,"")</f>
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <f>IF(Project!H29&gt;0,Project!H29,"")</f>
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <f>IF(Project!I29&gt;0,Project!I29,"")</f>
+        <v/>
+      </c>
+      <c r="J29" t="str">
+        <f>IF(Project!J29&gt;0,Project!J29,"")</f>
+        <v/>
+      </c>
+      <c r="K29" t="str">
+        <f>IF(Project!K29&gt;0,Project!K29,"")</f>
+        <v/>
+      </c>
+      <c r="L29" t="str">
+        <f>IF(Project!L29&gt;0,Project!L29,"")</f>
+        <v/>
+      </c>
+      <c r="M29" t="str">
+        <f>IF(Project!M29&gt;0,Project!M29,"")</f>
+        <v/>
+      </c>
+      <c r="N29" t="str">
+        <f>IF(Project!N29&gt;0,Project!N29,"")</f>
+        <v/>
+      </c>
+      <c r="O29" t="str">
+        <f>IF(Project!O29&gt;0,Project!O29,"")</f>
+        <v/>
+      </c>
+      <c r="P29" t="str">
+        <f>IF(Project!P29&gt;0,Project!P29,"")</f>
+        <v/>
+      </c>
+      <c r="Q29" t="str">
+        <f>IF(Project!Q29&gt;0,Project!Q29,"")</f>
+        <v/>
+      </c>
+      <c r="R29" t="str">
+        <f>IF(Project!R29&gt;0,Project!R29,"")</f>
+        <v/>
+      </c>
+      <c r="S29" t="str">
+        <f>IF(Project!S29&gt;0,Project!S29,"")</f>
+        <v/>
+      </c>
+      <c r="T29" t="str">
+        <f>IF(Project!T29&gt;0,Project!T29,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A30" t="str">
+        <f>IF(Project!A30&gt;0,Project!A30,"")</f>
+        <v/>
+      </c>
+      <c r="B30" t="str">
+        <f>IF(Project!B30&gt;0,Project!B30,"")</f>
+        <v/>
+      </c>
+      <c r="C30" t="str">
+        <f>IF(Project!C30&gt;0,Project!C30,"")</f>
+        <v/>
+      </c>
+      <c r="D30" t="str">
+        <f>IF(Project!D30&gt;0,Project!D30,"")</f>
+        <v/>
+      </c>
+      <c r="E30" t="str">
+        <f>IF(Project!E30&gt;0,Project!E30,"")</f>
+        <v/>
+      </c>
+      <c r="F30" t="str">
+        <f>IF(Project!F30&gt;0,Project!F30,"")</f>
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <f>IF(Project!G30&gt;0,Project!G30,"")</f>
+        <v/>
+      </c>
+      <c r="H30" t="str">
+        <f>IF(Project!H30&gt;0,Project!H30,"")</f>
+        <v/>
+      </c>
+      <c r="I30" t="str">
+        <f>IF(Project!I30&gt;0,Project!I30,"")</f>
+        <v/>
+      </c>
+      <c r="J30" t="str">
+        <f>IF(Project!J30&gt;0,Project!J30,"")</f>
+        <v/>
+      </c>
+      <c r="K30" t="str">
+        <f>IF(Project!K30&gt;0,Project!K30,"")</f>
+        <v/>
+      </c>
+      <c r="L30" t="str">
+        <f>IF(Project!L30&gt;0,Project!L30,"")</f>
+        <v/>
+      </c>
+      <c r="M30" t="str">
+        <f>IF(Project!M30&gt;0,Project!M30,"")</f>
+        <v/>
+      </c>
+      <c r="N30" t="str">
+        <f>IF(Project!N30&gt;0,Project!N30,"")</f>
+        <v/>
+      </c>
+      <c r="O30" t="str">
+        <f>IF(Project!O30&gt;0,Project!O30,"")</f>
+        <v/>
+      </c>
+      <c r="P30" t="str">
+        <f>IF(Project!P30&gt;0,Project!P30,"")</f>
+        <v/>
+      </c>
+      <c r="Q30" t="str">
+        <f>IF(Project!Q30&gt;0,Project!Q30,"")</f>
+        <v/>
+      </c>
+      <c r="R30" t="str">
+        <f>IF(Project!R30&gt;0,Project!R30,"")</f>
+        <v/>
+      </c>
+      <c r="S30" t="str">
+        <f>IF(Project!S30&gt;0,Project!S30,"")</f>
+        <v/>
+      </c>
+      <c r="T30" t="str">
+        <f>IF(Project!T30&gt;0,Project!T30,"")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -9447,7 +13409,7 @@
   <sheetPr>
     <tabColor theme="4" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:P47"/>
+  <dimension ref="A1:P153"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.83203125" bestFit="1" customWidth="1"/>
@@ -10867,6 +14829,200 @@
       <c r="F47">
         <f>IF(ALL!G49&gt;0,ALL!G49,"")</f>
         <v>11</v>
+      </c>
+    </row>
+    <row r="151" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B151" t="str">
+        <f>ALL!C1</f>
+        <v>JAN</v>
+      </c>
+      <c r="C151" t="str">
+        <f>ALL!D1</f>
+        <v>FEB</v>
+      </c>
+      <c r="D151" t="str">
+        <f>ALL!E1</f>
+        <v>MAR</v>
+      </c>
+      <c r="E151" t="str">
+        <f>ALL!F1</f>
+        <v>APR</v>
+      </c>
+      <c r="F151" t="str">
+        <f>ALL!G1</f>
+        <v>MAY</v>
+      </c>
+      <c r="G151" t="str">
+        <f>ALL!H1</f>
+        <v>JUN</v>
+      </c>
+      <c r="H151" t="str">
+        <f>ALL!I1</f>
+        <v>JUL</v>
+      </c>
+      <c r="I151" t="str">
+        <f>ALL!J1</f>
+        <v>AUG</v>
+      </c>
+      <c r="J151" t="str">
+        <f>ALL!K1</f>
+        <v>SEP</v>
+      </c>
+      <c r="K151" t="str">
+        <f>ALL!L1</f>
+        <v>OCT</v>
+      </c>
+      <c r="L151" t="str">
+        <f>ALL!M1</f>
+        <v>NOV</v>
+      </c>
+      <c r="M151" t="str">
+        <f>ALL!N1</f>
+        <v>DEC</v>
+      </c>
+      <c r="N151" t="str">
+        <f>ALL!O1</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O151" t="str">
+        <f>ALL!P1</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P151" t="str">
+        <f>ALL!Q1</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="152" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A152" t="str">
+        <f>ALL!B6</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B152" s="62">
+        <f>ALL!C6</f>
+        <v>0.88260000000000005</v>
+      </c>
+      <c r="C152" s="62">
+        <f>ALL!D6</f>
+        <v>0.93620000000000003</v>
+      </c>
+      <c r="D152" s="62">
+        <f>ALL!E6</f>
+        <v>0.95589999999999997</v>
+      </c>
+      <c r="E152" s="62">
+        <f>ALL!F6</f>
+        <v>0.94789999999999996</v>
+      </c>
+      <c r="F152" s="62">
+        <f>ALL!G6</f>
+        <v>0.97919999999999996</v>
+      </c>
+      <c r="G152" s="62">
+        <f>ALL!H6</f>
+        <v>0.95830000000000004</v>
+      </c>
+      <c r="H152" s="62">
+        <f>ALL!I6</f>
+        <v>0.95909999999999995</v>
+      </c>
+      <c r="I152" s="62">
+        <f>ALL!J6</f>
+        <v>0.93759999999999999</v>
+      </c>
+      <c r="J152" s="62">
+        <f>ALL!K6</f>
+        <v>0.93179999999999996</v>
+      </c>
+      <c r="K152" s="62">
+        <f>ALL!L6</f>
+        <v>0.88370000000000004</v>
+      </c>
+      <c r="L152" s="62">
+        <f>ALL!M6</f>
+        <v>0.87409999999999999</v>
+      </c>
+      <c r="M152" s="62">
+        <f>ALL!N6</f>
+        <v>0.86939999999999995</v>
+      </c>
+      <c r="N152" s="62">
+        <f>ALL!O6</f>
+        <v>0.70230000000000004</v>
+      </c>
+      <c r="O152" s="62">
+        <f>ALL!P6</f>
+        <v>0.70020000000000004</v>
+      </c>
+      <c r="P152" s="62">
+        <f>ALL!Q6</f>
+        <v>0.70020000000000004</v>
+      </c>
+    </row>
+    <row r="153" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A153" t="str">
+        <f>ALL!B7</f>
+        <v>Available FTE</v>
+      </c>
+      <c r="B153">
+        <f>ALL!C7</f>
+        <v>17</v>
+      </c>
+      <c r="C153">
+        <f>ALL!D7</f>
+        <v>10</v>
+      </c>
+      <c r="D153">
+        <f>ALL!E7</f>
+        <v>7</v>
+      </c>
+      <c r="E153">
+        <f>ALL!F7</f>
+        <v>8</v>
+      </c>
+      <c r="F153">
+        <f>ALL!G7</f>
+        <v>3</v>
+      </c>
+      <c r="G153">
+        <f>ALL!H7</f>
+        <v>6</v>
+      </c>
+      <c r="H153">
+        <f>ALL!I7</f>
+        <v>6</v>
+      </c>
+      <c r="I153">
+        <f>ALL!J7</f>
+        <v>9</v>
+      </c>
+      <c r="J153">
+        <f>ALL!K7</f>
+        <v>10</v>
+      </c>
+      <c r="K153">
+        <f>ALL!L7</f>
+        <v>17</v>
+      </c>
+      <c r="L153">
+        <f>ALL!M7</f>
+        <v>19</v>
+      </c>
+      <c r="M153">
+        <f>ALL!N7</f>
+        <v>19</v>
+      </c>
+      <c r="N153">
+        <f>ALL!O7</f>
+        <v>44</v>
+      </c>
+      <c r="O153">
+        <f>ALL!P7</f>
+        <v>45</v>
+      </c>
+      <c r="P153">
+        <f>ALL!Q7</f>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -12613,7 +16769,7 @@
   <sheetPr>
     <tabColor theme="5" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:P63"/>
+  <dimension ref="A1:P153"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.83203125" bestFit="1" customWidth="1"/>
@@ -14429,6 +18585,200 @@
       <c r="P63">
         <f>CPS!Q69</f>
         <v>5</v>
+      </c>
+    </row>
+    <row r="151" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B151" t="str">
+        <f>CPS!C1</f>
+        <v>JAN</v>
+      </c>
+      <c r="C151" t="str">
+        <f>CPS!D1</f>
+        <v>FEB</v>
+      </c>
+      <c r="D151" t="str">
+        <f>CPS!E1</f>
+        <v>MAR</v>
+      </c>
+      <c r="E151" t="str">
+        <f>CPS!F1</f>
+        <v>APR</v>
+      </c>
+      <c r="F151" t="str">
+        <f>CPS!G1</f>
+        <v>MAY</v>
+      </c>
+      <c r="G151" t="str">
+        <f>CPS!H1</f>
+        <v>JUN</v>
+      </c>
+      <c r="H151" t="str">
+        <f>CPS!I1</f>
+        <v>JUL</v>
+      </c>
+      <c r="I151" t="str">
+        <f>CPS!J1</f>
+        <v>AUG</v>
+      </c>
+      <c r="J151" t="str">
+        <f>CPS!K1</f>
+        <v>SEP</v>
+      </c>
+      <c r="K151" t="str">
+        <f>CPS!L1</f>
+        <v>OCT</v>
+      </c>
+      <c r="L151" t="str">
+        <f>CPS!M1</f>
+        <v>NOV</v>
+      </c>
+      <c r="M151" t="str">
+        <f>CPS!N1</f>
+        <v>DEC</v>
+      </c>
+      <c r="N151" t="str">
+        <f>CPS!O1</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O151" t="str">
+        <f>CPS!P1</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P151" t="str">
+        <f>CPS!Q1</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="152" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A152" t="str">
+        <f>CPS!B6</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B152" s="62">
+        <f>CPS!C6</f>
+        <v>0.93610000000000004</v>
+      </c>
+      <c r="C152" s="62">
+        <f>CPS!D6</f>
+        <v>0.94169999999999998</v>
+      </c>
+      <c r="D152" s="62">
+        <f>CPS!E6</f>
+        <v>0.92500000000000004</v>
+      </c>
+      <c r="E152" s="62">
+        <f>CPS!F6</f>
+        <v>1.0235000000000001</v>
+      </c>
+      <c r="F152" s="62">
+        <f>CPS!G6</f>
+        <v>1.0294000000000001</v>
+      </c>
+      <c r="G152" s="62">
+        <f>CPS!H6</f>
+        <v>1.0235000000000001</v>
+      </c>
+      <c r="H152" s="62">
+        <f>CPS!I6</f>
+        <v>0.95289999999999997</v>
+      </c>
+      <c r="I152" s="62">
+        <f>CPS!J6</f>
+        <v>0.94120000000000004</v>
+      </c>
+      <c r="J152" s="62">
+        <f>CPS!K6</f>
+        <v>0.94120000000000004</v>
+      </c>
+      <c r="K152" s="62">
+        <f>CPS!L6</f>
+        <v>0.93530000000000002</v>
+      </c>
+      <c r="L152" s="62">
+        <f>CPS!M6</f>
+        <v>0.92349999999999999</v>
+      </c>
+      <c r="M152" s="62">
+        <f>CPS!N6</f>
+        <v>0.92349999999999999</v>
+      </c>
+      <c r="N152" s="62">
+        <f>CPS!O6</f>
+        <v>0.83530000000000004</v>
+      </c>
+      <c r="O152" s="62">
+        <f>CPS!P6</f>
+        <v>0.83530000000000004</v>
+      </c>
+      <c r="P152" s="62">
+        <f>CPS!Q6</f>
+        <v>0.83530000000000004</v>
+      </c>
+    </row>
+    <row r="153" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A153" t="str">
+        <f>CPS!B7</f>
+        <v>Available FTE</v>
+      </c>
+      <c r="B153">
+        <f>CPS!C7</f>
+        <v>1</v>
+      </c>
+      <c r="C153">
+        <f>CPS!D7</f>
+        <v>1</v>
+      </c>
+      <c r="D153">
+        <f>CPS!E7</f>
+        <v>1</v>
+      </c>
+      <c r="E153">
+        <f>CPS!F7</f>
+        <v>0</v>
+      </c>
+      <c r="F153">
+        <f>CPS!G7</f>
+        <v>0</v>
+      </c>
+      <c r="G153">
+        <f>CPS!H7</f>
+        <v>0</v>
+      </c>
+      <c r="H153">
+        <f>CPS!I7</f>
+        <v>1</v>
+      </c>
+      <c r="I153">
+        <f>CPS!J7</f>
+        <v>1</v>
+      </c>
+      <c r="J153">
+        <f>CPS!K7</f>
+        <v>1</v>
+      </c>
+      <c r="K153">
+        <f>CPS!L7</f>
+        <v>1</v>
+      </c>
+      <c r="L153">
+        <f>CPS!M7</f>
+        <v>1</v>
+      </c>
+      <c r="M153">
+        <f>CPS!N7</f>
+        <v>1</v>
+      </c>
+      <c r="N153">
+        <f>CPS!O7</f>
+        <v>3</v>
+      </c>
+      <c r="O153">
+        <f>CPS!P7</f>
+        <v>3</v>
+      </c>
+      <c r="P153">
+        <f>CPS!Q7</f>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -16705,7 +21055,7 @@
   <sheetPr>
     <tabColor theme="7" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:P63"/>
+  <dimension ref="A1:P153"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.83203125" bestFit="1" customWidth="1"/>
@@ -18521,6 +22871,200 @@
       <c r="P63">
         <f>PSE!Q73</f>
         <v>24.65</v>
+      </c>
+    </row>
+    <row r="151" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B151" t="str">
+        <f>PSE!C1</f>
+        <v>JAN</v>
+      </c>
+      <c r="C151" t="str">
+        <f>PSE!D1</f>
+        <v>FEB</v>
+      </c>
+      <c r="D151" t="str">
+        <f>PSE!E1</f>
+        <v>MAR</v>
+      </c>
+      <c r="E151" t="str">
+        <f>PSE!F1</f>
+        <v>APR</v>
+      </c>
+      <c r="F151" t="str">
+        <f>PSE!G1</f>
+        <v>MAY</v>
+      </c>
+      <c r="G151" t="str">
+        <f>PSE!H1</f>
+        <v>JUN</v>
+      </c>
+      <c r="H151" t="str">
+        <f>PSE!I1</f>
+        <v>JUL</v>
+      </c>
+      <c r="I151" t="str">
+        <f>PSE!J1</f>
+        <v>AUG</v>
+      </c>
+      <c r="J151" t="str">
+        <f>PSE!K1</f>
+        <v>SEP</v>
+      </c>
+      <c r="K151" t="str">
+        <f>PSE!L1</f>
+        <v>OCT</v>
+      </c>
+      <c r="L151" t="str">
+        <f>PSE!M1</f>
+        <v>NOV</v>
+      </c>
+      <c r="M151" t="str">
+        <f>PSE!N1</f>
+        <v>DEC</v>
+      </c>
+      <c r="N151" t="str">
+        <f>PSE!O1</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O151" t="str">
+        <f>PSE!P1</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P151" t="str">
+        <f>PSE!Q1</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="152" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A152" t="str">
+        <f>PSE!B6</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B152" s="62">
+        <f>PSE!C6</f>
+        <v>0.89780000000000004</v>
+      </c>
+      <c r="C152" s="62">
+        <f>PSE!D6</f>
+        <v>0.94130000000000003</v>
+      </c>
+      <c r="D152" s="62">
+        <f>PSE!E6</f>
+        <v>0.98819999999999997</v>
+      </c>
+      <c r="E152" s="62">
+        <f>PSE!F6</f>
+        <v>0.94650000000000001</v>
+      </c>
+      <c r="F152" s="62">
+        <f>PSE!G6</f>
+        <v>0.97460000000000002</v>
+      </c>
+      <c r="G152" s="62">
+        <f>PSE!H6</f>
+        <v>0.91479999999999995</v>
+      </c>
+      <c r="H152" s="62">
+        <f>PSE!I6</f>
+        <v>0.93979999999999997</v>
+      </c>
+      <c r="I152" s="62">
+        <f>PSE!J6</f>
+        <v>0.92830000000000001</v>
+      </c>
+      <c r="J152" s="62">
+        <f>PSE!K6</f>
+        <v>0.93879999999999997</v>
+      </c>
+      <c r="K152" s="62">
+        <f>PSE!L6</f>
+        <v>0.86850000000000005</v>
+      </c>
+      <c r="L152" s="62">
+        <f>PSE!M6</f>
+        <v>0.85419999999999996</v>
+      </c>
+      <c r="M152" s="62">
+        <f>PSE!N6</f>
+        <v>0.85419999999999996</v>
+      </c>
+      <c r="N152" s="62">
+        <f>PSE!O6</f>
+        <v>0.65939999999999999</v>
+      </c>
+      <c r="O152" s="62">
+        <f>PSE!P6</f>
+        <v>0.65939999999999999</v>
+      </c>
+      <c r="P152" s="62">
+        <f>PSE!Q6</f>
+        <v>0.65939999999999999</v>
+      </c>
+    </row>
+    <row r="153" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A153" t="str">
+        <f>PSE!B7</f>
+        <v>Available FTE</v>
+      </c>
+      <c r="B153">
+        <f>PSE!C7</f>
+        <v>5</v>
+      </c>
+      <c r="C153">
+        <f>PSE!D7</f>
+        <v>3</v>
+      </c>
+      <c r="D153">
+        <f>PSE!E7</f>
+        <v>1</v>
+      </c>
+      <c r="E153">
+        <f>PSE!F7</f>
+        <v>3</v>
+      </c>
+      <c r="F153">
+        <f>PSE!G7</f>
+        <v>1</v>
+      </c>
+      <c r="G153">
+        <f>PSE!H7</f>
+        <v>4</v>
+      </c>
+      <c r="H153">
+        <f>PSE!I7</f>
+        <v>3</v>
+      </c>
+      <c r="I153">
+        <f>PSE!J7</f>
+        <v>3</v>
+      </c>
+      <c r="J153">
+        <f>PSE!K7</f>
+        <v>3</v>
+      </c>
+      <c r="K153">
+        <f>PSE!L7</f>
+        <v>6</v>
+      </c>
+      <c r="L153">
+        <f>PSE!M7</f>
+        <v>7</v>
+      </c>
+      <c r="M153">
+        <f>PSE!N7</f>
+        <v>7</v>
+      </c>
+      <c r="N153">
+        <f>PSE!O7</f>
+        <v>16</v>
+      </c>
+      <c r="O153">
+        <f>PSE!P7</f>
+        <v>16</v>
+      </c>
+      <c r="P153">
+        <f>PSE!Q7</f>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -21539,7 +26083,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:P133"/>
+  <dimension ref="A1:P153"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.83203125" bestFit="1" customWidth="1"/>
@@ -24741,6 +29285,200 @@
       <c r="P133">
         <f>SD!Q93</f>
         <v>5.2</v>
+      </c>
+    </row>
+    <row r="151" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B151" t="str">
+        <f>SD!C1</f>
+        <v>JAN</v>
+      </c>
+      <c r="C151" t="str">
+        <f>SD!D1</f>
+        <v>FEB</v>
+      </c>
+      <c r="D151" t="str">
+        <f>SD!E1</f>
+        <v>MAR</v>
+      </c>
+      <c r="E151" t="str">
+        <f>SD!F1</f>
+        <v>APR</v>
+      </c>
+      <c r="F151" t="str">
+        <f>SD!G1</f>
+        <v>MAY</v>
+      </c>
+      <c r="G151" t="str">
+        <f>SD!H1</f>
+        <v>JUN</v>
+      </c>
+      <c r="H151" t="str">
+        <f>SD!I1</f>
+        <v>JUL</v>
+      </c>
+      <c r="I151" t="str">
+        <f>SD!J1</f>
+        <v>AUG</v>
+      </c>
+      <c r="J151" t="str">
+        <f>SD!K1</f>
+        <v>SEP</v>
+      </c>
+      <c r="K151" t="str">
+        <f>SD!L1</f>
+        <v>OCT</v>
+      </c>
+      <c r="L151" t="str">
+        <f>SD!M1</f>
+        <v>NOV</v>
+      </c>
+      <c r="M151" t="str">
+        <f>SD!N1</f>
+        <v>DEC</v>
+      </c>
+      <c r="N151" t="str">
+        <f>SD!O1</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O151" t="str">
+        <f>SD!P1</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P151" t="str">
+        <f>SD!Q1</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="152" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A152" t="str">
+        <f>SD!B6</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B152" s="62">
+        <f>SD!C6</f>
+        <v>0.94089999999999996</v>
+      </c>
+      <c r="C152" s="62">
+        <f>SD!D6</f>
+        <v>1.0186999999999999</v>
+      </c>
+      <c r="D152" s="62">
+        <f>SD!E6</f>
+        <v>1.0399</v>
+      </c>
+      <c r="E152" s="62">
+        <f>SD!F6</f>
+        <v>0.95079999999999998</v>
+      </c>
+      <c r="F152" s="62">
+        <f>SD!G6</f>
+        <v>1.0044999999999999</v>
+      </c>
+      <c r="G152" s="62">
+        <f>SD!H6</f>
+        <v>1.0102</v>
+      </c>
+      <c r="H152" s="62">
+        <f>SD!I6</f>
+        <v>1.0387</v>
+      </c>
+      <c r="I152" s="62">
+        <f>SD!J6</f>
+        <v>1.0035000000000001</v>
+      </c>
+      <c r="J152" s="62">
+        <f>SD!K6</f>
+        <v>0.98709999999999998</v>
+      </c>
+      <c r="K152" s="62">
+        <f>SD!L6</f>
+        <v>0.92390000000000005</v>
+      </c>
+      <c r="L152" s="62">
+        <f>SD!M6</f>
+        <v>0.91090000000000004</v>
+      </c>
+      <c r="M152" s="62">
+        <f>SD!N6</f>
+        <v>0.9022</v>
+      </c>
+      <c r="N152" s="62">
+        <f>SD!O6</f>
+        <v>0.70440000000000003</v>
+      </c>
+      <c r="O152" s="62">
+        <f>SD!P6</f>
+        <v>0.69789999999999996</v>
+      </c>
+      <c r="P152" s="62">
+        <f>SD!Q6</f>
+        <v>0.69789999999999996</v>
+      </c>
+    </row>
+    <row r="153" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A153" t="str">
+        <f>SD!B7</f>
+        <v>Available FTE</v>
+      </c>
+      <c r="B153">
+        <f>SD!C7</f>
+        <v>3</v>
+      </c>
+      <c r="C153">
+        <f>SD!D7</f>
+        <v>-1</v>
+      </c>
+      <c r="D153">
+        <f>SD!E7</f>
+        <v>-2</v>
+      </c>
+      <c r="E153">
+        <f>SD!F7</f>
+        <v>2</v>
+      </c>
+      <c r="F153">
+        <f>SD!G7</f>
+        <v>0</v>
+      </c>
+      <c r="G153">
+        <f>SD!H7</f>
+        <v>0</v>
+      </c>
+      <c r="H153">
+        <f>SD!I7</f>
+        <v>-2</v>
+      </c>
+      <c r="I153">
+        <f>SD!J7</f>
+        <v>0</v>
+      </c>
+      <c r="J153">
+        <f>SD!K7</f>
+        <v>1</v>
+      </c>
+      <c r="K153">
+        <f>SD!L7</f>
+        <v>4</v>
+      </c>
+      <c r="L153">
+        <f>SD!M7</f>
+        <v>4</v>
+      </c>
+      <c r="M153">
+        <f>SD!N7</f>
+        <v>4</v>
+      </c>
+      <c r="N153">
+        <f>SD!O7</f>
+        <v>14</v>
+      </c>
+      <c r="O153">
+        <f>SD!P7</f>
+        <v>14</v>
+      </c>
+      <c r="P153">
+        <f>SD!Q7</f>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/workforceresult.xlsx
+++ b/workforceresult.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miintra/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17E91E87-C843-4448-9809-B65EEDA6C041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{422918FE-CC7F-074C-870E-F32D00F51E70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16120" activeTab="13" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
   </bookViews>
@@ -871,7 +871,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -952,16 +952,12 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5060,65 +5056,65 @@
         <f>AIC!B6</f>
         <v>% Plan</v>
       </c>
-      <c r="B152" s="62">
-        <f>AIC!C6</f>
-        <v>0.66300000000000003</v>
-      </c>
-      <c r="C152" s="62">
-        <f>AIC!D6</f>
-        <v>0.75390000000000001</v>
-      </c>
-      <c r="D152" s="62">
-        <f>AIC!E6</f>
-        <v>0.749</v>
-      </c>
-      <c r="E152" s="62">
-        <f>AIC!F6</f>
-        <v>0.88400000000000001</v>
-      </c>
-      <c r="F152" s="62">
-        <f>AIC!G6</f>
-        <v>0.91969999999999996</v>
-      </c>
-      <c r="G152" s="62">
-        <f>AIC!H6</f>
-        <v>0.8982</v>
-      </c>
-      <c r="H152" s="62">
-        <f>AIC!I6</f>
-        <v>0.83279999999999998</v>
-      </c>
-      <c r="I152" s="62">
-        <f>AIC!J6</f>
-        <v>0.78800000000000003</v>
-      </c>
-      <c r="J152" s="62">
-        <f>AIC!K6</f>
-        <v>0.75639999999999996</v>
-      </c>
-      <c r="K152" s="62">
-        <f>AIC!L6</f>
-        <v>0.71499999999999997</v>
-      </c>
-      <c r="L152" s="62">
-        <f>AIC!M6</f>
-        <v>0.71760000000000002</v>
-      </c>
-      <c r="M152" s="62">
-        <f>AIC!N6</f>
-        <v>0.70179999999999998</v>
-      </c>
-      <c r="N152" s="62">
-        <f>AIC!O6</f>
-        <v>0.44130000000000003</v>
-      </c>
-      <c r="O152" s="62">
-        <f>AIC!P6</f>
-        <v>0.44130000000000003</v>
-      </c>
-      <c r="P152" s="62">
-        <f>AIC!Q6</f>
-        <v>0.44130000000000003</v>
+      <c r="B152" s="59">
+        <f>AIC!C6*100</f>
+        <v>66.3</v>
+      </c>
+      <c r="C152" s="59">
+        <f>AIC!D6*100</f>
+        <v>75.39</v>
+      </c>
+      <c r="D152" s="59">
+        <f>AIC!E6*100</f>
+        <v>74.900000000000006</v>
+      </c>
+      <c r="E152" s="59">
+        <f>AIC!F6*100</f>
+        <v>88.4</v>
+      </c>
+      <c r="F152" s="59">
+        <f>AIC!G6*100</f>
+        <v>91.97</v>
+      </c>
+      <c r="G152" s="59">
+        <f>AIC!H6*100</f>
+        <v>89.82</v>
+      </c>
+      <c r="H152" s="59">
+        <f>AIC!I6*100</f>
+        <v>83.28</v>
+      </c>
+      <c r="I152" s="59">
+        <f>AIC!J6*100</f>
+        <v>78.8</v>
+      </c>
+      <c r="J152" s="59">
+        <f>AIC!K6*100</f>
+        <v>75.64</v>
+      </c>
+      <c r="K152" s="59">
+        <f>AIC!L6*100</f>
+        <v>71.5</v>
+      </c>
+      <c r="L152" s="59">
+        <f>AIC!M6*100</f>
+        <v>71.760000000000005</v>
+      </c>
+      <c r="M152" s="59">
+        <f>AIC!N6*100</f>
+        <v>70.179999999999993</v>
+      </c>
+      <c r="N152" s="59">
+        <f>AIC!O6*100</f>
+        <v>44.13</v>
+      </c>
+      <c r="O152" s="59">
+        <f>AIC!P6*100</f>
+        <v>44.13</v>
+      </c>
+      <c r="P152" s="59">
+        <f>AIC!Q6*100</f>
+        <v>44.13</v>
       </c>
     </row>
     <row r="153" spans="1:16" x14ac:dyDescent="0.2">
@@ -9848,65 +9844,65 @@
         <f>TDE!B6</f>
         <v>% Plan</v>
       </c>
-      <c r="B152" s="62">
-        <f>TDE!C6</f>
-        <v>1</v>
-      </c>
-      <c r="C152" s="62">
-        <f>TDE!D6</f>
-        <v>1</v>
-      </c>
-      <c r="D152" s="62">
-        <f>TDE!E6</f>
-        <v>1</v>
-      </c>
-      <c r="E152" s="62">
-        <f>TDE!F6</f>
-        <v>1</v>
-      </c>
-      <c r="F152" s="62">
-        <f>TDE!G6</f>
-        <v>1</v>
-      </c>
-      <c r="G152" s="62">
-        <f>TDE!H6</f>
-        <v>1</v>
-      </c>
-      <c r="H152" s="62">
-        <f>TDE!I6</f>
-        <v>1</v>
-      </c>
-      <c r="I152" s="62">
-        <f>TDE!J6</f>
-        <v>1</v>
-      </c>
-      <c r="J152" s="62">
-        <f>TDE!K6</f>
-        <v>1</v>
-      </c>
-      <c r="K152" s="62">
-        <f>TDE!L6</f>
-        <v>1</v>
-      </c>
-      <c r="L152" s="62">
-        <f>TDE!M6</f>
-        <v>1</v>
-      </c>
-      <c r="M152" s="62">
-        <f>TDE!N6</f>
-        <v>1</v>
-      </c>
-      <c r="N152" s="62">
-        <f>TDE!O6</f>
-        <v>1</v>
-      </c>
-      <c r="O152" s="62">
-        <f>TDE!P6</f>
-        <v>1</v>
-      </c>
-      <c r="P152" s="62">
-        <f>TDE!Q6</f>
-        <v>1</v>
+      <c r="B152" s="59">
+        <f>TDE!C6*100</f>
+        <v>100</v>
+      </c>
+      <c r="C152" s="59">
+        <f>TDE!D6*100</f>
+        <v>100</v>
+      </c>
+      <c r="D152" s="59">
+        <f>TDE!E6*100</f>
+        <v>100</v>
+      </c>
+      <c r="E152" s="59">
+        <f>TDE!F6*100</f>
+        <v>100</v>
+      </c>
+      <c r="F152" s="59">
+        <f>TDE!G6*100</f>
+        <v>100</v>
+      </c>
+      <c r="G152" s="59">
+        <f>TDE!H6*100</f>
+        <v>100</v>
+      </c>
+      <c r="H152" s="59">
+        <f>TDE!I6*100</f>
+        <v>100</v>
+      </c>
+      <c r="I152" s="59">
+        <f>TDE!J6*100</f>
+        <v>100</v>
+      </c>
+      <c r="J152" s="59">
+        <f>TDE!K6*100</f>
+        <v>100</v>
+      </c>
+      <c r="K152" s="59">
+        <f>TDE!L6*100</f>
+        <v>100</v>
+      </c>
+      <c r="L152" s="59">
+        <f>TDE!M6*100</f>
+        <v>100</v>
+      </c>
+      <c r="M152" s="59">
+        <f>TDE!N6*100</f>
+        <v>100</v>
+      </c>
+      <c r="N152" s="59">
+        <f>TDE!O6*100</f>
+        <v>100</v>
+      </c>
+      <c r="O152" s="59">
+        <f>TDE!P6*100</f>
+        <v>100</v>
+      </c>
+      <c r="P152" s="59">
+        <f>TDE!Q6*100</f>
+        <v>100</v>
       </c>
     </row>
     <row r="153" spans="1:16" x14ac:dyDescent="0.2">
@@ -9985,67 +9981,67 @@
   <sheetPr>
     <tabColor rgb="FF002060"/>
   </sheetPr>
-  <dimension ref="A1:V27"/>
+  <dimension ref="A1:V26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="55" t="s">
         <v>122</v>
       </c>
-      <c r="B1" s="59" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="59" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="59" t="s">
+      <c r="B1" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="55" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="59" t="s">
+      <c r="E1" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="59" t="s">
+      <c r="F1" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="59" t="s">
+      <c r="G1" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="59" t="s">
+      <c r="H1" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="59" t="s">
+      <c r="I1" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="59" t="s">
+      <c r="J1" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="59" t="s">
+      <c r="K1" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="59" t="s">
+      <c r="L1" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="59" t="s">
+      <c r="M1" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="59" t="s">
+      <c r="N1" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="59" t="s">
+      <c r="O1" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="59" t="s">
+      <c r="P1" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="55"/>
-      <c r="R1" s="55"/>
-      <c r="S1" s="55"/>
-      <c r="T1" s="55"/>
-      <c r="U1" s="55"/>
-      <c r="V1" s="55"/>
+      <c r="Q1" s="54"/>
+      <c r="R1" s="54"/>
+      <c r="S1" s="54"/>
+      <c r="T1" s="54"/>
+      <c r="U1" s="54"/>
+      <c r="V1" s="54"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
@@ -10098,10 +10094,10 @@
       </c>
       <c r="Q2" s="8"/>
       <c r="R2" s="8"/>
-      <c r="S2" s="60"/>
+      <c r="S2" s="56"/>
       <c r="T2" s="8"/>
       <c r="U2" s="8"/>
-      <c r="V2" s="60"/>
+      <c r="V2" s="56"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
@@ -10154,10 +10150,10 @@
       </c>
       <c r="Q3" s="8"/>
       <c r="R3" s="8"/>
-      <c r="S3" s="60"/>
+      <c r="S3" s="56"/>
       <c r="T3" s="8"/>
       <c r="U3" s="8"/>
-      <c r="V3" s="60"/>
+      <c r="V3" s="56"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
@@ -10210,10 +10206,10 @@
       </c>
       <c r="Q4" s="8"/>
       <c r="R4" s="8"/>
-      <c r="S4" s="60"/>
+      <c r="S4" s="56"/>
       <c r="T4" s="8"/>
       <c r="U4" s="8"/>
-      <c r="V4" s="60"/>
+      <c r="V4" s="56"/>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
@@ -10266,10 +10262,10 @@
       </c>
       <c r="Q5" s="8"/>
       <c r="R5" s="8"/>
-      <c r="S5" s="60"/>
+      <c r="S5" s="56"/>
       <c r="T5" s="8"/>
       <c r="U5" s="8"/>
-      <c r="V5" s="60"/>
+      <c r="V5" s="56"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
@@ -10322,10 +10318,10 @@
       </c>
       <c r="Q6" s="8"/>
       <c r="R6" s="8"/>
-      <c r="S6" s="60"/>
+      <c r="S6" s="56"/>
       <c r="T6" s="8"/>
       <c r="U6" s="8"/>
-      <c r="V6" s="60"/>
+      <c r="V6" s="56"/>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A7" s="8"/>
@@ -10346,13 +10342,13 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="60"/>
+      <c r="S7" s="56"/>
       <c r="T7" s="8"/>
       <c r="U7" s="8"/>
-      <c r="V7" s="60"/>
+      <c r="V7" s="56"/>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A9" s="61" t="s">
+      <c r="A9" s="57" t="s">
         <v>103</v>
       </c>
     </row>
@@ -10728,12 +10724,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A21" s="53" t="s">
         <v>91</v>
       </c>
@@ -10758,18 +10754,14 @@
       <c r="H21" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="I21" s="55"/>
-      <c r="J21" s="56"/>
-      <c r="K21" s="55"/>
-      <c r="L21" s="55"/>
-      <c r="M21" s="55"/>
-      <c r="N21" s="55"/>
-      <c r="O21" s="56"/>
-      <c r="P21" s="56"/>
-      <c r="Q21" s="55"/>
-      <c r="R21" s="56"/>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="I21" s="54"/>
+      <c r="K21" s="54"/>
+      <c r="L21" s="54"/>
+      <c r="M21" s="54"/>
+      <c r="N21" s="54"/>
+      <c r="Q21" s="54"/>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
         <v>92</v>
       </c>
@@ -10777,8 +10769,8 @@
         <v>36</v>
       </c>
       <c r="C22" s="8"/>
-      <c r="D22" s="54"/>
-      <c r="E22" s="54"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
       <c r="F22" s="8"/>
       <c r="G22" s="8">
         <v>180</v>
@@ -10786,18 +10778,14 @@
       <c r="H22" s="8">
         <v>216</v>
       </c>
-      <c r="I22" s="57"/>
-      <c r="J22" s="56"/>
-      <c r="K22" s="58"/>
-      <c r="L22" s="58"/>
-      <c r="M22" s="57"/>
-      <c r="N22" s="57"/>
-      <c r="O22" s="56"/>
-      <c r="P22" s="56"/>
-      <c r="Q22" s="57"/>
-      <c r="R22" s="56"/>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="I22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+      <c r="Q22" s="8"/>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
         <v>93</v>
       </c>
@@ -10807,29 +10795,25 @@
       <c r="C23" s="8">
         <v>154.05000000000001</v>
       </c>
-      <c r="D23" s="54">
+      <c r="D23" s="8">
         <v>5.13</v>
       </c>
-      <c r="E23" s="54">
+      <c r="E23" s="8">
         <v>0.9</v>
       </c>
       <c r="F23" s="8"/>
-      <c r="G23" s="54"/>
+      <c r="G23" s="8"/>
       <c r="H23" s="8">
         <v>162.78</v>
       </c>
-      <c r="I23" s="57"/>
-      <c r="J23" s="56"/>
-      <c r="K23" s="58"/>
-      <c r="L23" s="58"/>
-      <c r="M23" s="57"/>
-      <c r="N23" s="58"/>
-      <c r="O23" s="56"/>
-      <c r="P23" s="56"/>
-      <c r="Q23" s="57"/>
-      <c r="R23" s="56"/>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="I23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
+      <c r="Q23" s="8"/>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
         <v>94</v>
       </c>
@@ -10837,25 +10821,21 @@
       <c r="C24" s="8">
         <v>63.6</v>
       </c>
-      <c r="D24" s="54"/>
-      <c r="E24" s="54"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
       <c r="F24" s="8"/>
-      <c r="G24" s="54"/>
+      <c r="G24" s="8"/>
       <c r="H24" s="8">
         <v>63.6</v>
       </c>
-      <c r="I24" s="57"/>
-      <c r="J24" s="56"/>
-      <c r="K24" s="58"/>
-      <c r="L24" s="58"/>
-      <c r="M24" s="57"/>
-      <c r="N24" s="58"/>
-      <c r="O24" s="56"/>
-      <c r="P24" s="56"/>
-      <c r="Q24" s="57"/>
-      <c r="R24" s="56"/>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="I24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="Q24" s="8"/>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A25" s="8" t="s">
         <v>95</v>
       </c>
@@ -10863,8 +10843,8 @@
       <c r="C25" s="8">
         <v>27.375</v>
       </c>
-      <c r="D25" s="54"/>
-      <c r="E25" s="54"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
       <c r="F25" s="8"/>
       <c r="G25" s="8">
         <v>23.7</v>
@@ -10872,18 +10852,14 @@
       <c r="H25" s="8">
         <v>51.075000000000003</v>
       </c>
-      <c r="I25" s="57"/>
-      <c r="J25" s="56"/>
-      <c r="K25" s="58"/>
-      <c r="L25" s="58"/>
-      <c r="M25" s="57"/>
-      <c r="N25" s="57"/>
-      <c r="O25" s="56"/>
-      <c r="P25" s="56"/>
-      <c r="Q25" s="57"/>
-      <c r="R25" s="56"/>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="I25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="N25" s="8"/>
+      <c r="Q25" s="8"/>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26" s="8" t="s">
         <v>96</v>
       </c>
@@ -10891,37 +10867,21 @@
         <v>0.8</v>
       </c>
       <c r="C26" s="8"/>
-      <c r="D26" s="54"/>
-      <c r="E26" s="54"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
       <c r="F26" s="8">
         <v>34.655000000000001</v>
       </c>
-      <c r="G26" s="54"/>
+      <c r="G26" s="8"/>
       <c r="H26" s="8">
         <v>35.454999999999998</v>
       </c>
-      <c r="I26" s="57"/>
-      <c r="J26" s="56"/>
-      <c r="K26" s="58"/>
-      <c r="L26" s="58"/>
-      <c r="M26" s="57"/>
-      <c r="N26" s="58"/>
-      <c r="O26" s="56"/>
-      <c r="P26" s="56"/>
-      <c r="Q26" s="57"/>
-      <c r="R26" s="56"/>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="I27" s="56"/>
-      <c r="J27" s="56"/>
-      <c r="K27" s="56"/>
-      <c r="L27" s="56"/>
-      <c r="M27" s="56"/>
-      <c r="N27" s="56"/>
-      <c r="O27" s="56"/>
-      <c r="P27" s="56"/>
-      <c r="Q27" s="56"/>
-      <c r="R27" s="56"/>
+      <c r="I26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="8"/>
+      <c r="Q26" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10939,84 +10899,84 @@
     <col min="1" max="1" width="22.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="63" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="63" t="str">
+    <row r="1" spans="1:20" s="58" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="58" t="str">
         <f>IF(Project!A1&gt;0,Project!A1,"")</f>
         <v>Group</v>
       </c>
-      <c r="B1" s="63" t="str">
+      <c r="B1" s="58" t="str">
         <f>IF(Project!B1&gt;0,Project!B1,"")</f>
         <v>JAN</v>
       </c>
-      <c r="C1" s="63" t="str">
+      <c r="C1" s="58" t="str">
         <f>IF(Project!C1&gt;0,Project!C1,"")</f>
         <v>FEB</v>
       </c>
-      <c r="D1" s="63" t="str">
+      <c r="D1" s="58" t="str">
         <f>IF(Project!D1&gt;0,Project!D1,"")</f>
         <v>MAR</v>
       </c>
-      <c r="E1" s="63" t="str">
+      <c r="E1" s="58" t="str">
         <f>IF(Project!E1&gt;0,Project!E1,"")</f>
         <v>APR</v>
       </c>
-      <c r="F1" s="63" t="str">
+      <c r="F1" s="58" t="str">
         <f>IF(Project!F1&gt;0,Project!F1,"")</f>
         <v>MAY</v>
       </c>
-      <c r="G1" s="63" t="str">
+      <c r="G1" s="58" t="str">
         <f>IF(Project!G1&gt;0,Project!G1,"")</f>
         <v>JUN</v>
       </c>
-      <c r="H1" s="63" t="str">
+      <c r="H1" s="58" t="str">
         <f>IF(Project!H1&gt;0,Project!H1,"")</f>
         <v>JUL</v>
       </c>
-      <c r="I1" s="63" t="str">
+      <c r="I1" s="58" t="str">
         <f>IF(Project!I1&gt;0,Project!I1,"")</f>
         <v>AUG</v>
       </c>
-      <c r="J1" s="63" t="str">
+      <c r="J1" s="58" t="str">
         <f>IF(Project!J1&gt;0,Project!J1,"")</f>
         <v>SEP</v>
       </c>
-      <c r="K1" s="63" t="str">
+      <c r="K1" s="58" t="str">
         <f>IF(Project!K1&gt;0,Project!K1,"")</f>
         <v>OCT</v>
       </c>
-      <c r="L1" s="63" t="str">
+      <c r="L1" s="58" t="str">
         <f>IF(Project!L1&gt;0,Project!L1,"")</f>
         <v>NOV</v>
       </c>
-      <c r="M1" s="63" t="str">
+      <c r="M1" s="58" t="str">
         <f>IF(Project!M1&gt;0,Project!M1,"")</f>
         <v>DEC</v>
       </c>
-      <c r="N1" s="63" t="str">
+      <c r="N1" s="58" t="str">
         <f>IF(Project!N1&gt;0,Project!N1,"")</f>
         <v>JAN'27</v>
       </c>
-      <c r="O1" s="63" t="str">
+      <c r="O1" s="58" t="str">
         <f>IF(Project!O1&gt;0,Project!O1,"")</f>
         <v>FEB'27</v>
       </c>
-      <c r="P1" s="63" t="str">
+      <c r="P1" s="58" t="str">
         <f>IF(Project!P1&gt;0,Project!P1,"")</f>
         <v>MAR'27</v>
       </c>
-      <c r="Q1" s="63" t="str">
+      <c r="Q1" s="58" t="str">
         <f>IF(Project!Q1&gt;0,Project!Q1,"")</f>
         <v/>
       </c>
-      <c r="R1" s="63" t="str">
+      <c r="R1" s="58" t="str">
         <f>IF(Project!R1&gt;0,Project!R1,"")</f>
         <v/>
       </c>
-      <c r="S1" s="63" t="str">
+      <c r="S1" s="58" t="str">
         <f>IF(Project!S1&gt;0,Project!S1,"")</f>
         <v/>
       </c>
-      <c r="T1" s="63" t="str">
+      <c r="T1" s="58" t="str">
         <f>IF(Project!T1&gt;0,Project!T1,"")</f>
         <v/>
       </c>
@@ -11596,7 +11556,7 @@
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A9" s="63" t="str">
+      <c r="A9" s="58" t="str">
         <f>IF(Project!A9&gt;0,Project!A9,"")</f>
         <v>Project by Team</v>
       </c>
@@ -11759,84 +11719,84 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:20" s="63" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="63" t="str">
+    <row r="11" spans="1:20" s="58" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="58" t="str">
         <f>IF(Project!A11&gt;0,Project!A11,"")</f>
         <v>Group Name</v>
       </c>
-      <c r="B11" s="63" t="str">
+      <c r="B11" s="58" t="str">
         <f>IF(Project!B11&gt;0,Project!B11,"")</f>
         <v>Total</v>
       </c>
-      <c r="C11" s="63" t="str">
+      <c r="C11" s="58" t="str">
         <f>IF(Project!C11&gt;0,Project!C11,"")</f>
         <v>CPS</v>
       </c>
-      <c r="D11" s="63" t="str">
+      <c r="D11" s="58" t="str">
         <f>IF(Project!D11&gt;0,Project!D11,"")</f>
         <v>PSE-PE</v>
       </c>
-      <c r="E11" s="63" t="str">
+      <c r="E11" s="58" t="str">
         <f>IF(Project!E11&gt;0,Project!E11,"")</f>
         <v>PSE-SE</v>
       </c>
-      <c r="F11" s="63" t="str">
+      <c r="F11" s="58" t="str">
         <f>IF(Project!F11&gt;0,Project!F11,"")</f>
         <v>SD-Design</v>
       </c>
-      <c r="G11" s="63" t="str">
+      <c r="G11" s="58" t="str">
         <f>IF(Project!G11&gt;0,Project!G11,"")</f>
         <v>SD-Data</v>
       </c>
-      <c r="H11" s="63" t="str">
+      <c r="H11" s="58" t="str">
         <f>IF(Project!H11&gt;0,Project!H11,"")</f>
         <v>SD-SA</v>
       </c>
-      <c r="I11" s="63" t="str">
+      <c r="I11" s="58" t="str">
         <f>IF(Project!I11&gt;0,Project!I11,"")</f>
         <v>SD-SRE</v>
       </c>
-      <c r="J11" s="63" t="str">
+      <c r="J11" s="58" t="str">
         <f>IF(Project!J11&gt;0,Project!J11,"")</f>
         <v>SD-CyberSec</v>
       </c>
-      <c r="K11" s="63" t="str">
+      <c r="K11" s="58" t="str">
         <f>IF(Project!K11&gt;0,Project!K11,"")</f>
         <v>SD-PM</v>
       </c>
-      <c r="L11" s="63" t="str">
+      <c r="L11" s="58" t="str">
         <f>IF(Project!L11&gt;0,Project!L11,"")</f>
         <v>SD-BA</v>
       </c>
-      <c r="M11" s="63" t="str">
+      <c r="M11" s="58" t="str">
         <f>IF(Project!M11&gt;0,Project!M11,"")</f>
         <v>SD-QA</v>
       </c>
-      <c r="N11" s="63" t="str">
+      <c r="N11" s="58" t="str">
         <f>IF(Project!N11&gt;0,Project!N11,"")</f>
         <v>SD-TM</v>
       </c>
-      <c r="O11" s="63" t="str">
+      <c r="O11" s="58" t="str">
         <f>IF(Project!O11&gt;0,Project!O11,"")</f>
         <v>AIC-AI</v>
       </c>
-      <c r="P11" s="63" t="str">
+      <c r="P11" s="58" t="str">
         <f>IF(Project!P11&gt;0,Project!P11,"")</f>
         <v>AIC-AIE</v>
       </c>
-      <c r="Q11" s="63" t="str">
+      <c r="Q11" s="58" t="str">
         <f>IF(Project!Q11&gt;0,Project!Q11,"")</f>
         <v>AIC-IoT</v>
       </c>
-      <c r="R11" s="63" t="str">
+      <c r="R11" s="58" t="str">
         <f>IF(Project!R11&gt;0,Project!R11,"")</f>
         <v>AIC-SAI</v>
       </c>
-      <c r="S11" s="63" t="str">
+      <c r="S11" s="58" t="str">
         <f>IF(Project!S11&gt;0,Project!S11,"")</f>
         <v>AIC-PSI</v>
       </c>
-      <c r="T11" s="63" t="str">
+      <c r="T11" s="58" t="str">
         <f>IF(Project!T11&gt;0,Project!T11,"")</f>
         <v>TDE</v>
       </c>
@@ -12415,248 +12375,248 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:20" s="63" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="63" t="str">
+    <row r="19" spans="1:20" s="58" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="58" t="str">
         <f>IF(Project!A19&gt;0,Project!A19,"")</f>
         <v>Project by Type</v>
       </c>
-      <c r="B19" s="63" t="str">
+      <c r="B19" s="58" t="str">
         <f>IF(Project!B19&gt;0,Project!B19,"")</f>
         <v/>
       </c>
-      <c r="C19" s="63" t="str">
+      <c r="C19" s="58" t="str">
         <f>IF(Project!C19&gt;0,Project!C19,"")</f>
         <v/>
       </c>
-      <c r="D19" s="63" t="str">
+      <c r="D19" s="58" t="str">
         <f>IF(Project!D19&gt;0,Project!D19,"")</f>
         <v/>
       </c>
-      <c r="E19" s="63" t="str">
+      <c r="E19" s="58" t="str">
         <f>IF(Project!E19&gt;0,Project!E19,"")</f>
         <v/>
       </c>
-      <c r="F19" s="63" t="str">
+      <c r="F19" s="58" t="str">
         <f>IF(Project!F19&gt;0,Project!F19,"")</f>
         <v/>
       </c>
-      <c r="G19" s="63" t="str">
+      <c r="G19" s="58" t="str">
         <f>IF(Project!G19&gt;0,Project!G19,"")</f>
         <v/>
       </c>
-      <c r="H19" s="63" t="str">
+      <c r="H19" s="58" t="str">
         <f>IF(Project!H19&gt;0,Project!H19,"")</f>
         <v/>
       </c>
-      <c r="I19" s="63" t="str">
+      <c r="I19" s="58" t="str">
         <f>IF(Project!I19&gt;0,Project!I19,"")</f>
         <v/>
       </c>
-      <c r="J19" s="63" t="str">
+      <c r="J19" s="58" t="str">
         <f>IF(Project!J19&gt;0,Project!J19,"")</f>
         <v/>
       </c>
-      <c r="K19" s="63" t="str">
+      <c r="K19" s="58" t="str">
         <f>IF(Project!K19&gt;0,Project!K19,"")</f>
         <v/>
       </c>
-      <c r="L19" s="63" t="str">
+      <c r="L19" s="58" t="str">
         <f>IF(Project!L19&gt;0,Project!L19,"")</f>
         <v/>
       </c>
-      <c r="M19" s="63" t="str">
+      <c r="M19" s="58" t="str">
         <f>IF(Project!M19&gt;0,Project!M19,"")</f>
         <v/>
       </c>
-      <c r="N19" s="63" t="str">
+      <c r="N19" s="58" t="str">
         <f>IF(Project!N19&gt;0,Project!N19,"")</f>
         <v/>
       </c>
-      <c r="O19" s="63" t="str">
+      <c r="O19" s="58" t="str">
         <f>IF(Project!O19&gt;0,Project!O19,"")</f>
         <v/>
       </c>
-      <c r="P19" s="63" t="str">
+      <c r="P19" s="58" t="str">
         <f>IF(Project!P19&gt;0,Project!P19,"")</f>
         <v/>
       </c>
-      <c r="Q19" s="63" t="str">
+      <c r="Q19" s="58" t="str">
         <f>IF(Project!Q19&gt;0,Project!Q19,"")</f>
         <v/>
       </c>
-      <c r="R19" s="63" t="str">
+      <c r="R19" s="58" t="str">
         <f>IF(Project!R19&gt;0,Project!R19,"")</f>
         <v/>
       </c>
-      <c r="S19" s="63" t="str">
+      <c r="S19" s="58" t="str">
         <f>IF(Project!S19&gt;0,Project!S19,"")</f>
         <v/>
       </c>
-      <c r="T19" s="63" t="str">
+      <c r="T19" s="58" t="str">
         <f>IF(Project!T19&gt;0,Project!T19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:20" s="63" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="63" t="str">
+    <row r="20" spans="1:20" s="58" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="58" t="str">
         <f>IF(Project!A20&gt;0,Project!A20,"")</f>
         <v/>
       </c>
-      <c r="B20" s="63" t="str">
+      <c r="B20" s="58" t="str">
         <f>IF(Project!B20&gt;0,Project!B20,"")</f>
         <v/>
       </c>
-      <c r="C20" s="63" t="str">
+      <c r="C20" s="58" t="str">
         <f>IF(Project!C20&gt;0,Project!C20,"")</f>
         <v/>
       </c>
-      <c r="D20" s="63" t="str">
+      <c r="D20" s="58" t="str">
         <f>IF(Project!D20&gt;0,Project!D20,"")</f>
         <v/>
       </c>
-      <c r="E20" s="63" t="str">
+      <c r="E20" s="58" t="str">
         <f>IF(Project!E20&gt;0,Project!E20,"")</f>
         <v/>
       </c>
-      <c r="F20" s="63" t="str">
+      <c r="F20" s="58" t="str">
         <f>IF(Project!F20&gt;0,Project!F20,"")</f>
         <v/>
       </c>
-      <c r="G20" s="63" t="str">
+      <c r="G20" s="58" t="str">
         <f>IF(Project!G20&gt;0,Project!G20,"")</f>
         <v/>
       </c>
-      <c r="H20" s="63" t="str">
+      <c r="H20" s="58" t="str">
         <f>IF(Project!H20&gt;0,Project!H20,"")</f>
         <v/>
       </c>
-      <c r="I20" s="63" t="str">
+      <c r="I20" s="58" t="str">
         <f>IF(Project!I20&gt;0,Project!I20,"")</f>
         <v/>
       </c>
-      <c r="J20" s="63" t="str">
+      <c r="J20" s="58" t="str">
         <f>IF(Project!J20&gt;0,Project!J20,"")</f>
         <v/>
       </c>
-      <c r="K20" s="63" t="str">
+      <c r="K20" s="58" t="str">
         <f>IF(Project!K20&gt;0,Project!K20,"")</f>
         <v/>
       </c>
-      <c r="L20" s="63" t="str">
+      <c r="L20" s="58" t="str">
         <f>IF(Project!L20&gt;0,Project!L20,"")</f>
         <v/>
       </c>
-      <c r="M20" s="63" t="str">
+      <c r="M20" s="58" t="str">
         <f>IF(Project!M20&gt;0,Project!M20,"")</f>
         <v/>
       </c>
-      <c r="N20" s="63" t="str">
+      <c r="N20" s="58" t="str">
         <f>IF(Project!N20&gt;0,Project!N20,"")</f>
         <v/>
       </c>
-      <c r="O20" s="63" t="str">
+      <c r="O20" s="58" t="str">
         <f>IF(Project!O20&gt;0,Project!O20,"")</f>
         <v/>
       </c>
-      <c r="P20" s="63" t="str">
+      <c r="P20" s="58" t="str">
         <f>IF(Project!P20&gt;0,Project!P20,"")</f>
         <v/>
       </c>
-      <c r="Q20" s="63" t="str">
+      <c r="Q20" s="58" t="str">
         <f>IF(Project!Q20&gt;0,Project!Q20,"")</f>
         <v/>
       </c>
-      <c r="R20" s="63" t="str">
+      <c r="R20" s="58" t="str">
         <f>IF(Project!R20&gt;0,Project!R20,"")</f>
         <v/>
       </c>
-      <c r="S20" s="63" t="str">
+      <c r="S20" s="58" t="str">
         <f>IF(Project!S20&gt;0,Project!S20,"")</f>
         <v/>
       </c>
-      <c r="T20" s="63" t="str">
+      <c r="T20" s="58" t="str">
         <f>IF(Project!T20&gt;0,Project!T20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:20" s="63" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="63" t="str">
+    <row r="21" spans="1:20" s="58" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="58" t="str">
         <f>IF(Project!A21&gt;0,Project!A21,"")</f>
         <v>Group Name</v>
       </c>
-      <c r="B21" s="63" t="str">
+      <c r="B21" s="58" t="str">
         <f>IF(Project!B21&gt;0,Project!B21,"")</f>
         <v>Presale</v>
       </c>
-      <c r="C21" s="63" t="str">
+      <c r="C21" s="58" t="str">
         <f>IF(Project!C21&gt;0,Project!C21,"")</f>
         <v>Project</v>
       </c>
-      <c r="D21" s="63" t="str">
+      <c r="D21" s="58" t="str">
         <f>IF(Project!D21&gt;0,Project!D21,"")</f>
         <v>TM</v>
       </c>
-      <c r="E21" s="63" t="str">
+      <c r="E21" s="58" t="str">
         <f>IF(Project!E21&gt;0,Project!E21,"")</f>
         <v>Infra</v>
       </c>
-      <c r="F21" s="63" t="str">
+      <c r="F21" s="58" t="str">
         <f>IF(Project!F21&gt;0,Project!F21,"")</f>
         <v>Spatial Lab</v>
       </c>
-      <c r="G21" s="63" t="str">
+      <c r="G21" s="58" t="str">
         <f>IF(Project!G21&gt;0,Project!G21,"")</f>
         <v>Warmbody</v>
       </c>
-      <c r="H21" s="63" t="str">
+      <c r="H21" s="58" t="str">
         <f>IF(Project!H21&gt;0,Project!H21,"")</f>
         <v>Grand Total</v>
       </c>
-      <c r="I21" s="63" t="str">
+      <c r="I21" s="58" t="str">
         <f>IF(Project!I21&gt;0,Project!I21,"")</f>
         <v/>
       </c>
-      <c r="J21" s="63" t="str">
+      <c r="J21" s="58" t="str">
         <f>IF(Project!J21&gt;0,Project!J21,"")</f>
         <v/>
       </c>
-      <c r="K21" s="63" t="str">
+      <c r="K21" s="58" t="str">
         <f>IF(Project!K21&gt;0,Project!K21,"")</f>
         <v/>
       </c>
-      <c r="L21" s="63" t="str">
+      <c r="L21" s="58" t="str">
         <f>IF(Project!L21&gt;0,Project!L21,"")</f>
         <v/>
       </c>
-      <c r="M21" s="63" t="str">
+      <c r="M21" s="58" t="str">
         <f>IF(Project!M21&gt;0,Project!M21,"")</f>
         <v/>
       </c>
-      <c r="N21" s="63" t="str">
+      <c r="N21" s="58" t="str">
         <f>IF(Project!N21&gt;0,Project!N21,"")</f>
         <v/>
       </c>
-      <c r="O21" s="63" t="str">
+      <c r="O21" s="58" t="str">
         <f>IF(Project!O21&gt;0,Project!O21,"")</f>
         <v/>
       </c>
-      <c r="P21" s="63" t="str">
+      <c r="P21" s="58" t="str">
         <f>IF(Project!P21&gt;0,Project!P21,"")</f>
         <v/>
       </c>
-      <c r="Q21" s="63" t="str">
+      <c r="Q21" s="58" t="str">
         <f>IF(Project!Q21&gt;0,Project!Q21,"")</f>
         <v/>
       </c>
-      <c r="R21" s="63" t="str">
+      <c r="R21" s="58" t="str">
         <f>IF(Project!R21&gt;0,Project!R21,"")</f>
         <v/>
       </c>
-      <c r="S21" s="63" t="str">
+      <c r="S21" s="58" t="str">
         <f>IF(Project!S21&gt;0,Project!S21,"")</f>
         <v/>
       </c>
-      <c r="T21" s="63" t="str">
+      <c r="T21" s="58" t="str">
         <f>IF(Project!T21&gt;0,Project!T21,"")</f>
         <v/>
       </c>
@@ -14898,65 +14858,65 @@
         <f>ALL!B6</f>
         <v>% Plan</v>
       </c>
-      <c r="B152" s="62">
-        <f>ALL!C6</f>
-        <v>0.88260000000000005</v>
-      </c>
-      <c r="C152" s="62">
-        <f>ALL!D6</f>
-        <v>0.93620000000000003</v>
-      </c>
-      <c r="D152" s="62">
-        <f>ALL!E6</f>
-        <v>0.95589999999999997</v>
-      </c>
-      <c r="E152" s="62">
-        <f>ALL!F6</f>
-        <v>0.94789999999999996</v>
-      </c>
-      <c r="F152" s="62">
-        <f>ALL!G6</f>
-        <v>0.97919999999999996</v>
-      </c>
-      <c r="G152" s="62">
-        <f>ALL!H6</f>
-        <v>0.95830000000000004</v>
-      </c>
-      <c r="H152" s="62">
-        <f>ALL!I6</f>
-        <v>0.95909999999999995</v>
-      </c>
-      <c r="I152" s="62">
-        <f>ALL!J6</f>
-        <v>0.93759999999999999</v>
-      </c>
-      <c r="J152" s="62">
-        <f>ALL!K6</f>
-        <v>0.93179999999999996</v>
-      </c>
-      <c r="K152" s="62">
-        <f>ALL!L6</f>
-        <v>0.88370000000000004</v>
-      </c>
-      <c r="L152" s="62">
-        <f>ALL!M6</f>
-        <v>0.87409999999999999</v>
-      </c>
-      <c r="M152" s="62">
-        <f>ALL!N6</f>
-        <v>0.86939999999999995</v>
-      </c>
-      <c r="N152" s="62">
-        <f>ALL!O6</f>
-        <v>0.70230000000000004</v>
-      </c>
-      <c r="O152" s="62">
-        <f>ALL!P6</f>
-        <v>0.70020000000000004</v>
-      </c>
-      <c r="P152" s="62">
-        <f>ALL!Q6</f>
-        <v>0.70020000000000004</v>
+      <c r="B152" s="59">
+        <f>ALL!C6*100</f>
+        <v>88.26</v>
+      </c>
+      <c r="C152" s="59">
+        <f>ALL!D6*100</f>
+        <v>93.62</v>
+      </c>
+      <c r="D152" s="59">
+        <f>ALL!E6*100</f>
+        <v>95.59</v>
+      </c>
+      <c r="E152" s="59">
+        <f>ALL!F6*100</f>
+        <v>94.789999999999992</v>
+      </c>
+      <c r="F152" s="59">
+        <f>ALL!G6*100</f>
+        <v>97.92</v>
+      </c>
+      <c r="G152" s="59">
+        <f>ALL!H6*100</f>
+        <v>95.83</v>
+      </c>
+      <c r="H152" s="59">
+        <f>ALL!I6*100</f>
+        <v>95.91</v>
+      </c>
+      <c r="I152" s="59">
+        <f>ALL!J6*100</f>
+        <v>93.76</v>
+      </c>
+      <c r="J152" s="59">
+        <f>ALL!K6*100</f>
+        <v>93.179999999999993</v>
+      </c>
+      <c r="K152" s="59">
+        <f>ALL!L6*100</f>
+        <v>88.37</v>
+      </c>
+      <c r="L152" s="59">
+        <f>ALL!M6*100</f>
+        <v>87.41</v>
+      </c>
+      <c r="M152" s="59">
+        <f>ALL!N6*100</f>
+        <v>86.94</v>
+      </c>
+      <c r="N152" s="59">
+        <f>ALL!O6*100</f>
+        <v>70.23</v>
+      </c>
+      <c r="O152" s="59">
+        <f>ALL!P6*100</f>
+        <v>70.02000000000001</v>
+      </c>
+      <c r="P152" s="59">
+        <f>ALL!Q6*100</f>
+        <v>70.02000000000001</v>
       </c>
     </row>
     <row r="153" spans="1:16" x14ac:dyDescent="0.2">
@@ -18654,65 +18614,65 @@
         <f>CPS!B6</f>
         <v>% Plan</v>
       </c>
-      <c r="B152" s="62">
-        <f>CPS!C6</f>
-        <v>0.93610000000000004</v>
-      </c>
-      <c r="C152" s="62">
-        <f>CPS!D6</f>
-        <v>0.94169999999999998</v>
-      </c>
-      <c r="D152" s="62">
-        <f>CPS!E6</f>
-        <v>0.92500000000000004</v>
-      </c>
-      <c r="E152" s="62">
-        <f>CPS!F6</f>
-        <v>1.0235000000000001</v>
-      </c>
-      <c r="F152" s="62">
-        <f>CPS!G6</f>
-        <v>1.0294000000000001</v>
-      </c>
-      <c r="G152" s="62">
-        <f>CPS!H6</f>
-        <v>1.0235000000000001</v>
-      </c>
-      <c r="H152" s="62">
-        <f>CPS!I6</f>
-        <v>0.95289999999999997</v>
-      </c>
-      <c r="I152" s="62">
-        <f>CPS!J6</f>
-        <v>0.94120000000000004</v>
-      </c>
-      <c r="J152" s="62">
-        <f>CPS!K6</f>
-        <v>0.94120000000000004</v>
-      </c>
-      <c r="K152" s="62">
-        <f>CPS!L6</f>
-        <v>0.93530000000000002</v>
-      </c>
-      <c r="L152" s="62">
-        <f>CPS!M6</f>
-        <v>0.92349999999999999</v>
-      </c>
-      <c r="M152" s="62">
-        <f>CPS!N6</f>
-        <v>0.92349999999999999</v>
-      </c>
-      <c r="N152" s="62">
-        <f>CPS!O6</f>
-        <v>0.83530000000000004</v>
-      </c>
-      <c r="O152" s="62">
-        <f>CPS!P6</f>
-        <v>0.83530000000000004</v>
-      </c>
-      <c r="P152" s="62">
-        <f>CPS!Q6</f>
-        <v>0.83530000000000004</v>
+      <c r="B152" s="59">
+        <f>CPS!C6*100</f>
+        <v>93.61</v>
+      </c>
+      <c r="C152" s="59">
+        <f>CPS!D6*100</f>
+        <v>94.17</v>
+      </c>
+      <c r="D152" s="59">
+        <f>CPS!E6*100</f>
+        <v>92.5</v>
+      </c>
+      <c r="E152" s="59">
+        <f>CPS!F6*100</f>
+        <v>102.35000000000001</v>
+      </c>
+      <c r="F152" s="59">
+        <f>CPS!G6*100</f>
+        <v>102.94000000000001</v>
+      </c>
+      <c r="G152" s="59">
+        <f>CPS!H6*100</f>
+        <v>102.35000000000001</v>
+      </c>
+      <c r="H152" s="59">
+        <f>CPS!I6*100</f>
+        <v>95.289999999999992</v>
+      </c>
+      <c r="I152" s="59">
+        <f>CPS!J6*100</f>
+        <v>94.12</v>
+      </c>
+      <c r="J152" s="59">
+        <f>CPS!K6*100</f>
+        <v>94.12</v>
+      </c>
+      <c r="K152" s="59">
+        <f>CPS!L6*100</f>
+        <v>93.53</v>
+      </c>
+      <c r="L152" s="59">
+        <f>CPS!M6*100</f>
+        <v>92.35</v>
+      </c>
+      <c r="M152" s="59">
+        <f>CPS!N6*100</f>
+        <v>92.35</v>
+      </c>
+      <c r="N152" s="59">
+        <f>CPS!O6*100</f>
+        <v>83.53</v>
+      </c>
+      <c r="O152" s="59">
+        <f>CPS!P6*100</f>
+        <v>83.53</v>
+      </c>
+      <c r="P152" s="59">
+        <f>CPS!Q6*100</f>
+        <v>83.53</v>
       </c>
     </row>
     <row r="153" spans="1:16" x14ac:dyDescent="0.2">
@@ -22940,65 +22900,65 @@
         <f>PSE!B6</f>
         <v>% Plan</v>
       </c>
-      <c r="B152" s="62">
-        <f>PSE!C6</f>
-        <v>0.89780000000000004</v>
-      </c>
-      <c r="C152" s="62">
-        <f>PSE!D6</f>
-        <v>0.94130000000000003</v>
-      </c>
-      <c r="D152" s="62">
-        <f>PSE!E6</f>
-        <v>0.98819999999999997</v>
-      </c>
-      <c r="E152" s="62">
-        <f>PSE!F6</f>
-        <v>0.94650000000000001</v>
-      </c>
-      <c r="F152" s="62">
-        <f>PSE!G6</f>
-        <v>0.97460000000000002</v>
-      </c>
-      <c r="G152" s="62">
-        <f>PSE!H6</f>
-        <v>0.91479999999999995</v>
-      </c>
-      <c r="H152" s="62">
-        <f>PSE!I6</f>
-        <v>0.93979999999999997</v>
-      </c>
-      <c r="I152" s="62">
-        <f>PSE!J6</f>
-        <v>0.92830000000000001</v>
-      </c>
-      <c r="J152" s="62">
-        <f>PSE!K6</f>
-        <v>0.93879999999999997</v>
-      </c>
-      <c r="K152" s="62">
-        <f>PSE!L6</f>
-        <v>0.86850000000000005</v>
-      </c>
-      <c r="L152" s="62">
-        <f>PSE!M6</f>
-        <v>0.85419999999999996</v>
-      </c>
-      <c r="M152" s="62">
-        <f>PSE!N6</f>
-        <v>0.85419999999999996</v>
-      </c>
-      <c r="N152" s="62">
-        <f>PSE!O6</f>
-        <v>0.65939999999999999</v>
-      </c>
-      <c r="O152" s="62">
-        <f>PSE!P6</f>
-        <v>0.65939999999999999</v>
-      </c>
-      <c r="P152" s="62">
-        <f>PSE!Q6</f>
-        <v>0.65939999999999999</v>
+      <c r="B152" s="59">
+        <f>PSE!C6*100</f>
+        <v>89.78</v>
+      </c>
+      <c r="C152" s="59">
+        <f>PSE!D6*100</f>
+        <v>94.13</v>
+      </c>
+      <c r="D152" s="59">
+        <f>PSE!E6*100</f>
+        <v>98.82</v>
+      </c>
+      <c r="E152" s="59">
+        <f>PSE!F6*100</f>
+        <v>94.65</v>
+      </c>
+      <c r="F152" s="59">
+        <f>PSE!G6*100</f>
+        <v>97.460000000000008</v>
+      </c>
+      <c r="G152" s="59">
+        <f>PSE!H6*100</f>
+        <v>91.47999999999999</v>
+      </c>
+      <c r="H152" s="59">
+        <f>PSE!I6*100</f>
+        <v>93.97999999999999</v>
+      </c>
+      <c r="I152" s="59">
+        <f>PSE!J6*100</f>
+        <v>92.83</v>
+      </c>
+      <c r="J152" s="59">
+        <f>PSE!K6*100</f>
+        <v>93.88</v>
+      </c>
+      <c r="K152" s="59">
+        <f>PSE!L6*100</f>
+        <v>86.850000000000009</v>
+      </c>
+      <c r="L152" s="59">
+        <f>PSE!M6*100</f>
+        <v>85.42</v>
+      </c>
+      <c r="M152" s="59">
+        <f>PSE!N6*100</f>
+        <v>85.42</v>
+      </c>
+      <c r="N152" s="59">
+        <f>PSE!O6*100</f>
+        <v>65.94</v>
+      </c>
+      <c r="O152" s="59">
+        <f>PSE!P6*100</f>
+        <v>65.94</v>
+      </c>
+      <c r="P152" s="59">
+        <f>PSE!Q6*100</f>
+        <v>65.94</v>
       </c>
     </row>
     <row r="153" spans="1:16" x14ac:dyDescent="0.2">
@@ -29354,65 +29314,65 @@
         <f>SD!B6</f>
         <v>% Plan</v>
       </c>
-      <c r="B152" s="62">
-        <f>SD!C6</f>
-        <v>0.94089999999999996</v>
-      </c>
-      <c r="C152" s="62">
-        <f>SD!D6</f>
-        <v>1.0186999999999999</v>
-      </c>
-      <c r="D152" s="62">
-        <f>SD!E6</f>
-        <v>1.0399</v>
-      </c>
-      <c r="E152" s="62">
-        <f>SD!F6</f>
-        <v>0.95079999999999998</v>
-      </c>
-      <c r="F152" s="62">
-        <f>SD!G6</f>
-        <v>1.0044999999999999</v>
-      </c>
-      <c r="G152" s="62">
-        <f>SD!H6</f>
-        <v>1.0102</v>
-      </c>
-      <c r="H152" s="62">
-        <f>SD!I6</f>
-        <v>1.0387</v>
-      </c>
-      <c r="I152" s="62">
-        <f>SD!J6</f>
-        <v>1.0035000000000001</v>
-      </c>
-      <c r="J152" s="62">
-        <f>SD!K6</f>
-        <v>0.98709999999999998</v>
-      </c>
-      <c r="K152" s="62">
-        <f>SD!L6</f>
-        <v>0.92390000000000005</v>
-      </c>
-      <c r="L152" s="62">
-        <f>SD!M6</f>
-        <v>0.91090000000000004</v>
-      </c>
-      <c r="M152" s="62">
-        <f>SD!N6</f>
-        <v>0.9022</v>
-      </c>
-      <c r="N152" s="62">
-        <f>SD!O6</f>
-        <v>0.70440000000000003</v>
-      </c>
-      <c r="O152" s="62">
-        <f>SD!P6</f>
-        <v>0.69789999999999996</v>
-      </c>
-      <c r="P152" s="62">
-        <f>SD!Q6</f>
-        <v>0.69789999999999996</v>
+      <c r="B152" s="59">
+        <f>SD!C6*100</f>
+        <v>94.089999999999989</v>
+      </c>
+      <c r="C152" s="59">
+        <f>SD!D6*100</f>
+        <v>101.86999999999999</v>
+      </c>
+      <c r="D152" s="59">
+        <f>SD!E6*100</f>
+        <v>103.99000000000001</v>
+      </c>
+      <c r="E152" s="59">
+        <f>SD!F6*100</f>
+        <v>95.08</v>
+      </c>
+      <c r="F152" s="59">
+        <f>SD!G6*100</f>
+        <v>100.44999999999999</v>
+      </c>
+      <c r="G152" s="59">
+        <f>SD!H6*100</f>
+        <v>101.02</v>
+      </c>
+      <c r="H152" s="59">
+        <f>SD!I6*100</f>
+        <v>103.86999999999999</v>
+      </c>
+      <c r="I152" s="59">
+        <f>SD!J6*100</f>
+        <v>100.35000000000001</v>
+      </c>
+      <c r="J152" s="59">
+        <f>SD!K6*100</f>
+        <v>98.71</v>
+      </c>
+      <c r="K152" s="59">
+        <f>SD!L6*100</f>
+        <v>92.39</v>
+      </c>
+      <c r="L152" s="59">
+        <f>SD!M6*100</f>
+        <v>91.09</v>
+      </c>
+      <c r="M152" s="59">
+        <f>SD!N6*100</f>
+        <v>90.22</v>
+      </c>
+      <c r="N152" s="59">
+        <f>SD!O6*100</f>
+        <v>70.44</v>
+      </c>
+      <c r="O152" s="59">
+        <f>SD!P6*100</f>
+        <v>69.789999999999992</v>
+      </c>
+      <c r="P152" s="59">
+        <f>SD!Q6*100</f>
+        <v>69.789999999999992</v>
       </c>
     </row>
     <row r="153" spans="1:16" x14ac:dyDescent="0.2">

--- a/workforceresult.xlsx
+++ b/workforceresult.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miintra/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{422918FE-CC7F-074C-870E-F32D00F51E70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E0CF2B5-E501-AF4C-94A9-24AA81D276E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16120" activeTab="13" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16120" activeTab="11" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
   </bookViews>
   <sheets>
     <sheet name="ALL" sheetId="1" r:id="rId1"/>
@@ -871,7 +871,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -957,7 +957,6 @@
     <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2577,7 +2576,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:P153"/>
+  <dimension ref="A1:P163"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.83203125" bestFit="1" customWidth="1"/>
@@ -5056,63 +5055,63 @@
         <f>AIC!B6</f>
         <v>% Plan</v>
       </c>
-      <c r="B152" s="59">
+      <c r="B152">
         <f>AIC!C6*100</f>
         <v>66.3</v>
       </c>
-      <c r="C152" s="59">
+      <c r="C152">
         <f>AIC!D6*100</f>
         <v>75.39</v>
       </c>
-      <c r="D152" s="59">
+      <c r="D152">
         <f>AIC!E6*100</f>
         <v>74.900000000000006</v>
       </c>
-      <c r="E152" s="59">
+      <c r="E152">
         <f>AIC!F6*100</f>
         <v>88.4</v>
       </c>
-      <c r="F152" s="59">
+      <c r="F152">
         <f>AIC!G6*100</f>
         <v>91.97</v>
       </c>
-      <c r="G152" s="59">
+      <c r="G152">
         <f>AIC!H6*100</f>
         <v>89.82</v>
       </c>
-      <c r="H152" s="59">
+      <c r="H152">
         <f>AIC!I6*100</f>
         <v>83.28</v>
       </c>
-      <c r="I152" s="59">
+      <c r="I152">
         <f>AIC!J6*100</f>
         <v>78.8</v>
       </c>
-      <c r="J152" s="59">
+      <c r="J152">
         <f>AIC!K6*100</f>
         <v>75.64</v>
       </c>
-      <c r="K152" s="59">
+      <c r="K152">
         <f>AIC!L6*100</f>
         <v>71.5</v>
       </c>
-      <c r="L152" s="59">
+      <c r="L152">
         <f>AIC!M6*100</f>
         <v>71.760000000000005</v>
       </c>
-      <c r="M152" s="59">
+      <c r="M152">
         <f>AIC!N6*100</f>
         <v>70.179999999999993</v>
       </c>
-      <c r="N152" s="59">
+      <c r="N152">
         <f>AIC!O6*100</f>
         <v>44.13</v>
       </c>
-      <c r="O152" s="59">
+      <c r="O152">
         <f>AIC!P6*100</f>
         <v>44.13</v>
       </c>
-      <c r="P152" s="59">
+      <c r="P152">
         <f>AIC!Q6*100</f>
         <v>44.13</v>
       </c>
@@ -5181,6 +5180,80 @@
       <c r="P153">
         <f>AIC!Q7</f>
         <v>11</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B161" t="str">
+        <f>AIC!C31</f>
+        <v>Q1</v>
+      </c>
+      <c r="C161" t="str">
+        <f>AIC!D31</f>
+        <v>Q2</v>
+      </c>
+      <c r="D161" t="str">
+        <f>AIC!E31</f>
+        <v>Q3</v>
+      </c>
+      <c r="E161" t="str">
+        <f>AIC!F31</f>
+        <v>Q4</v>
+      </c>
+      <c r="F161" t="str">
+        <f>AIC!G31</f>
+        <v>Q1'27</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A162" t="str">
+        <f>AIC!B6</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B162">
+        <f>AIC!C36*100</f>
+        <v>72.070000000000007</v>
+      </c>
+      <c r="C162">
+        <f>AIC!D36*100</f>
+        <v>90.03</v>
+      </c>
+      <c r="D162">
+        <f>AIC!E36*100</f>
+        <v>79.239999999999995</v>
+      </c>
+      <c r="E162">
+        <f>AIC!F36*100</f>
+        <v>71.150000000000006</v>
+      </c>
+      <c r="F162">
+        <f>AIC!G36*100</f>
+        <v>62.029999999999994</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A163" t="str">
+        <f>AIC!B7</f>
+        <v>Available FTE</v>
+      </c>
+      <c r="B163">
+        <f>AIC!C37</f>
+        <v>6</v>
+      </c>
+      <c r="C163">
+        <f>AIC!D37</f>
+        <v>2</v>
+      </c>
+      <c r="D163">
+        <f>AIC!E37</f>
+        <v>4</v>
+      </c>
+      <c r="E163">
+        <f>AIC!F37</f>
+        <v>5</v>
+      </c>
+      <c r="F163">
+        <f>AIC!G37</f>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -7563,7 +7636,7 @@
   <sheetPr>
     <tabColor theme="3" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:P153"/>
+  <dimension ref="A1:P163"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.6640625" bestFit="1" customWidth="1"/>
@@ -9844,63 +9917,63 @@
         <f>TDE!B6</f>
         <v>% Plan</v>
       </c>
-      <c r="B152" s="59">
+      <c r="B152">
         <f>TDE!C6*100</f>
         <v>100</v>
       </c>
-      <c r="C152" s="59">
+      <c r="C152">
         <f>TDE!D6*100</f>
         <v>100</v>
       </c>
-      <c r="D152" s="59">
+      <c r="D152">
         <f>TDE!E6*100</f>
         <v>100</v>
       </c>
-      <c r="E152" s="59">
+      <c r="E152">
         <f>TDE!F6*100</f>
         <v>100</v>
       </c>
-      <c r="F152" s="59">
+      <c r="F152">
         <f>TDE!G6*100</f>
         <v>100</v>
       </c>
-      <c r="G152" s="59">
+      <c r="G152">
         <f>TDE!H6*100</f>
         <v>100</v>
       </c>
-      <c r="H152" s="59">
+      <c r="H152">
         <f>TDE!I6*100</f>
         <v>100</v>
       </c>
-      <c r="I152" s="59">
+      <c r="I152">
         <f>TDE!J6*100</f>
         <v>100</v>
       </c>
-      <c r="J152" s="59">
+      <c r="J152">
         <f>TDE!K6*100</f>
         <v>100</v>
       </c>
-      <c r="K152" s="59">
+      <c r="K152">
         <f>TDE!L6*100</f>
         <v>100</v>
       </c>
-      <c r="L152" s="59">
+      <c r="L152">
         <f>TDE!M6*100</f>
         <v>100</v>
       </c>
-      <c r="M152" s="59">
+      <c r="M152">
         <f>TDE!N6*100</f>
         <v>100</v>
       </c>
-      <c r="N152" s="59">
+      <c r="N152">
         <f>TDE!O6*100</f>
         <v>100</v>
       </c>
-      <c r="O152" s="59">
+      <c r="O152">
         <f>TDE!P6*100</f>
         <v>100</v>
       </c>
-      <c r="P152" s="59">
+      <c r="P152">
         <f>TDE!Q6*100</f>
         <v>100</v>
       </c>
@@ -9968,6 +10041,80 @@
       </c>
       <c r="P153">
         <f>TDE!Q7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B161" t="str">
+        <f>TDE!C31</f>
+        <v>Q1</v>
+      </c>
+      <c r="C161" t="str">
+        <f>TDE!D31</f>
+        <v>Q2</v>
+      </c>
+      <c r="D161" t="str">
+        <f>TDE!E31</f>
+        <v>Q3</v>
+      </c>
+      <c r="E161" t="str">
+        <f>TDE!F31</f>
+        <v>Q4</v>
+      </c>
+      <c r="F161" t="str">
+        <f>TDE!G31</f>
+        <v>Q1'27</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A162" t="str">
+        <f>TDE!B6</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B162">
+        <f>TDE!C36*100</f>
+        <v>100</v>
+      </c>
+      <c r="C162">
+        <f>TDE!D36*100</f>
+        <v>100</v>
+      </c>
+      <c r="D162">
+        <f>TDE!E36*100</f>
+        <v>100</v>
+      </c>
+      <c r="E162">
+        <f>TDE!F36*100</f>
+        <v>100</v>
+      </c>
+      <c r="F162">
+        <f>TDE!G36*100</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A163" t="str">
+        <f>TDE!B7</f>
+        <v>Available FTE</v>
+      </c>
+      <c r="B163">
+        <f>TDE!C37</f>
+        <v>0</v>
+      </c>
+      <c r="C163">
+        <f>TDE!D37</f>
+        <v>0</v>
+      </c>
+      <c r="D163">
+        <f>TDE!E37</f>
+        <v>0</v>
+      </c>
+      <c r="E163">
+        <f>TDE!F37</f>
+        <v>0</v>
+      </c>
+      <c r="F163">
+        <f>TDE!G37</f>
         <v>0</v>
       </c>
     </row>
@@ -13369,7 +13516,7 @@
   <sheetPr>
     <tabColor theme="4" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:P153"/>
+  <dimension ref="A1:P163"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.83203125" bestFit="1" customWidth="1"/>
@@ -14858,63 +15005,63 @@
         <f>ALL!B6</f>
         <v>% Plan</v>
       </c>
-      <c r="B152" s="59">
+      <c r="B152">
         <f>ALL!C6*100</f>
         <v>88.26</v>
       </c>
-      <c r="C152" s="59">
+      <c r="C152">
         <f>ALL!D6*100</f>
         <v>93.62</v>
       </c>
-      <c r="D152" s="59">
+      <c r="D152">
         <f>ALL!E6*100</f>
         <v>95.59</v>
       </c>
-      <c r="E152" s="59">
+      <c r="E152">
         <f>ALL!F6*100</f>
         <v>94.789999999999992</v>
       </c>
-      <c r="F152" s="59">
+      <c r="F152">
         <f>ALL!G6*100</f>
         <v>97.92</v>
       </c>
-      <c r="G152" s="59">
+      <c r="G152">
         <f>ALL!H6*100</f>
         <v>95.83</v>
       </c>
-      <c r="H152" s="59">
+      <c r="H152">
         <f>ALL!I6*100</f>
         <v>95.91</v>
       </c>
-      <c r="I152" s="59">
+      <c r="I152">
         <f>ALL!J6*100</f>
         <v>93.76</v>
       </c>
-      <c r="J152" s="59">
+      <c r="J152">
         <f>ALL!K6*100</f>
         <v>93.179999999999993</v>
       </c>
-      <c r="K152" s="59">
+      <c r="K152">
         <f>ALL!L6*100</f>
         <v>88.37</v>
       </c>
-      <c r="L152" s="59">
+      <c r="L152">
         <f>ALL!M6*100</f>
         <v>87.41</v>
       </c>
-      <c r="M152" s="59">
+      <c r="M152">
         <f>ALL!N6*100</f>
         <v>86.94</v>
       </c>
-      <c r="N152" s="59">
+      <c r="N152">
         <f>ALL!O6*100</f>
         <v>70.23</v>
       </c>
-      <c r="O152" s="59">
+      <c r="O152">
         <f>ALL!P6*100</f>
         <v>70.02000000000001</v>
       </c>
-      <c r="P152" s="59">
+      <c r="P152">
         <f>ALL!Q6*100</f>
         <v>70.02000000000001</v>
       </c>
@@ -14983,6 +15130,80 @@
       <c r="P153">
         <f>ALL!Q7</f>
         <v>45</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B161" t="str">
+        <f>ALL!C31</f>
+        <v>Q1</v>
+      </c>
+      <c r="C161" t="str">
+        <f>ALL!D31</f>
+        <v>Q2</v>
+      </c>
+      <c r="D161" t="str">
+        <f>ALL!E31</f>
+        <v>Q3</v>
+      </c>
+      <c r="E161" t="str">
+        <f>ALL!F31</f>
+        <v>Q4</v>
+      </c>
+      <c r="F161" t="str">
+        <f>ALL!G31</f>
+        <v>Q1'27</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A162" t="str">
+        <f>ALL!B6</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B162">
+        <f>ALL!C36*100</f>
+        <v>92.5</v>
+      </c>
+      <c r="C162">
+        <f>ALL!D36*100</f>
+        <v>96.179999999999993</v>
+      </c>
+      <c r="D162">
+        <f>ALL!E36*100</f>
+        <v>94.28</v>
+      </c>
+      <c r="E162">
+        <f>ALL!F36*100</f>
+        <v>87.570000000000007</v>
+      </c>
+      <c r="F162">
+        <f>ALL!G36*100</f>
+        <v>81.52000000000001</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A163" t="str">
+        <f>ALL!B7</f>
+        <v>Available FTE</v>
+      </c>
+      <c r="B163">
+        <f>ALL!C37</f>
+        <v>11</v>
+      </c>
+      <c r="C163">
+        <f>ALL!D37</f>
+        <v>6</v>
+      </c>
+      <c r="D163">
+        <f>ALL!E37</f>
+        <v>9</v>
+      </c>
+      <c r="E163">
+        <f>ALL!F37</f>
+        <v>19</v>
+      </c>
+      <c r="F163">
+        <f>ALL!G37</f>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -16729,7 +16950,7 @@
   <sheetPr>
     <tabColor theme="5" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:P153"/>
+  <dimension ref="A1:P163"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.83203125" bestFit="1" customWidth="1"/>
@@ -18614,63 +18835,63 @@
         <f>CPS!B6</f>
         <v>% Plan</v>
       </c>
-      <c r="B152" s="59">
+      <c r="B152">
         <f>CPS!C6*100</f>
         <v>93.61</v>
       </c>
-      <c r="C152" s="59">
+      <c r="C152">
         <f>CPS!D6*100</f>
         <v>94.17</v>
       </c>
-      <c r="D152" s="59">
+      <c r="D152">
         <f>CPS!E6*100</f>
         <v>92.5</v>
       </c>
-      <c r="E152" s="59">
+      <c r="E152">
         <f>CPS!F6*100</f>
         <v>102.35000000000001</v>
       </c>
-      <c r="F152" s="59">
+      <c r="F152">
         <f>CPS!G6*100</f>
         <v>102.94000000000001</v>
       </c>
-      <c r="G152" s="59">
+      <c r="G152">
         <f>CPS!H6*100</f>
         <v>102.35000000000001</v>
       </c>
-      <c r="H152" s="59">
+      <c r="H152">
         <f>CPS!I6*100</f>
         <v>95.289999999999992</v>
       </c>
-      <c r="I152" s="59">
+      <c r="I152">
         <f>CPS!J6*100</f>
         <v>94.12</v>
       </c>
-      <c r="J152" s="59">
+      <c r="J152">
         <f>CPS!K6*100</f>
         <v>94.12</v>
       </c>
-      <c r="K152" s="59">
+      <c r="K152">
         <f>CPS!L6*100</f>
         <v>93.53</v>
       </c>
-      <c r="L152" s="59">
+      <c r="L152">
         <f>CPS!M6*100</f>
         <v>92.35</v>
       </c>
-      <c r="M152" s="59">
+      <c r="M152">
         <f>CPS!N6*100</f>
         <v>92.35</v>
       </c>
-      <c r="N152" s="59">
+      <c r="N152">
         <f>CPS!O6*100</f>
         <v>83.53</v>
       </c>
-      <c r="O152" s="59">
+      <c r="O152">
         <f>CPS!P6*100</f>
         <v>83.53</v>
       </c>
-      <c r="P152" s="59">
+      <c r="P152">
         <f>CPS!Q6*100</f>
         <v>83.53</v>
       </c>
@@ -18739,6 +18960,80 @@
       <c r="P153">
         <f>CPS!Q7</f>
         <v>3</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B161" t="str">
+        <f>CPS!C31</f>
+        <v>Q1</v>
+      </c>
+      <c r="C161" t="str">
+        <f>CPS!D31</f>
+        <v>Q2</v>
+      </c>
+      <c r="D161" t="str">
+        <f>CPS!E31</f>
+        <v>Q3</v>
+      </c>
+      <c r="E161" t="str">
+        <f>CPS!F31</f>
+        <v>Q4</v>
+      </c>
+      <c r="F161" t="str">
+        <f>CPS!G31</f>
+        <v>Q1'27</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A162" t="str">
+        <f>CPS!B6</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B162">
+        <f>CPS!C36*100</f>
+        <v>93.43</v>
+      </c>
+      <c r="C162">
+        <f>CPS!D36*100</f>
+        <v>102.55000000000001</v>
+      </c>
+      <c r="D162">
+        <f>CPS!E36*100</f>
+        <v>94.51</v>
+      </c>
+      <c r="E162">
+        <f>CPS!F36*100</f>
+        <v>92.75</v>
+      </c>
+      <c r="F162">
+        <f>CPS!G36*100</f>
+        <v>89.41</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A163" t="str">
+        <f>CPS!B7</f>
+        <v>Available FTE</v>
+      </c>
+      <c r="B163">
+        <f>CPS!C37</f>
+        <v>1</v>
+      </c>
+      <c r="C163">
+        <f>CPS!D37</f>
+        <v>0</v>
+      </c>
+      <c r="D163">
+        <f>CPS!E37</f>
+        <v>1</v>
+      </c>
+      <c r="E163">
+        <f>CPS!F37</f>
+        <v>1</v>
+      </c>
+      <c r="F163">
+        <f>CPS!G37</f>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -21015,7 +21310,7 @@
   <sheetPr>
     <tabColor theme="7" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:P153"/>
+  <dimension ref="A1:P163"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.83203125" bestFit="1" customWidth="1"/>
@@ -22900,63 +23195,63 @@
         <f>PSE!B6</f>
         <v>% Plan</v>
       </c>
-      <c r="B152" s="59">
+      <c r="B152">
         <f>PSE!C6*100</f>
         <v>89.78</v>
       </c>
-      <c r="C152" s="59">
+      <c r="C152">
         <f>PSE!D6*100</f>
         <v>94.13</v>
       </c>
-      <c r="D152" s="59">
+      <c r="D152">
         <f>PSE!E6*100</f>
         <v>98.82</v>
       </c>
-      <c r="E152" s="59">
+      <c r="E152">
         <f>PSE!F6*100</f>
         <v>94.65</v>
       </c>
-      <c r="F152" s="59">
+      <c r="F152">
         <f>PSE!G6*100</f>
         <v>97.460000000000008</v>
       </c>
-      <c r="G152" s="59">
+      <c r="G152">
         <f>PSE!H6*100</f>
         <v>91.47999999999999</v>
       </c>
-      <c r="H152" s="59">
+      <c r="H152">
         <f>PSE!I6*100</f>
         <v>93.97999999999999</v>
       </c>
-      <c r="I152" s="59">
+      <c r="I152">
         <f>PSE!J6*100</f>
         <v>92.83</v>
       </c>
-      <c r="J152" s="59">
+      <c r="J152">
         <f>PSE!K6*100</f>
         <v>93.88</v>
       </c>
-      <c r="K152" s="59">
+      <c r="K152">
         <f>PSE!L6*100</f>
         <v>86.850000000000009</v>
       </c>
-      <c r="L152" s="59">
+      <c r="L152">
         <f>PSE!M6*100</f>
         <v>85.42</v>
       </c>
-      <c r="M152" s="59">
+      <c r="M152">
         <f>PSE!N6*100</f>
         <v>85.42</v>
       </c>
-      <c r="N152" s="59">
+      <c r="N152">
         <f>PSE!O6*100</f>
         <v>65.94</v>
       </c>
-      <c r="O152" s="59">
+      <c r="O152">
         <f>PSE!P6*100</f>
         <v>65.94</v>
       </c>
-      <c r="P152" s="59">
+      <c r="P152">
         <f>PSE!Q6*100</f>
         <v>65.94</v>
       </c>
@@ -23025,6 +23320,80 @@
       <c r="P153">
         <f>PSE!Q7</f>
         <v>16</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B161" t="str">
+        <f>PSE!C31</f>
+        <v>Q1</v>
+      </c>
+      <c r="C161" t="str">
+        <f>PSE!D31</f>
+        <v>Q2</v>
+      </c>
+      <c r="D161" t="str">
+        <f>PSE!E31</f>
+        <v>Q3</v>
+      </c>
+      <c r="E161" t="str">
+        <f>PSE!F31</f>
+        <v>Q4</v>
+      </c>
+      <c r="F161" t="str">
+        <f>PSE!G31</f>
+        <v>Q1'27</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A162" t="str">
+        <f>PSE!B6</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B162">
+        <f>PSE!C36*100</f>
+        <v>94.24</v>
+      </c>
+      <c r="C162">
+        <f>PSE!D36*100</f>
+        <v>94.53</v>
+      </c>
+      <c r="D162">
+        <f>PSE!E36*100</f>
+        <v>93.56</v>
+      </c>
+      <c r="E162">
+        <f>PSE!F36*100</f>
+        <v>85.9</v>
+      </c>
+      <c r="F162">
+        <f>PSE!G36*100</f>
+        <v>78.92</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A163" t="str">
+        <f>PSE!B7</f>
+        <v>Available FTE</v>
+      </c>
+      <c r="B163">
+        <f>PSE!C37</f>
+        <v>3</v>
+      </c>
+      <c r="C163">
+        <f>PSE!D37</f>
+        <v>3</v>
+      </c>
+      <c r="D163">
+        <f>PSE!E37</f>
+        <v>3</v>
+      </c>
+      <c r="E163">
+        <f>PSE!F37</f>
+        <v>7</v>
+      </c>
+      <c r="F163">
+        <f>PSE!G37</f>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -26043,7 +26412,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:P153"/>
+  <dimension ref="A1:P163"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.83203125" bestFit="1" customWidth="1"/>
@@ -29314,63 +29683,63 @@
         <f>SD!B6</f>
         <v>% Plan</v>
       </c>
-      <c r="B152" s="59">
+      <c r="B152">
         <f>SD!C6*100</f>
         <v>94.089999999999989</v>
       </c>
-      <c r="C152" s="59">
+      <c r="C152">
         <f>SD!D6*100</f>
         <v>101.86999999999999</v>
       </c>
-      <c r="D152" s="59">
+      <c r="D152">
         <f>SD!E6*100</f>
         <v>103.99000000000001</v>
       </c>
-      <c r="E152" s="59">
+      <c r="E152">
         <f>SD!F6*100</f>
         <v>95.08</v>
       </c>
-      <c r="F152" s="59">
+      <c r="F152">
         <f>SD!G6*100</f>
         <v>100.44999999999999</v>
       </c>
-      <c r="G152" s="59">
+      <c r="G152">
         <f>SD!H6*100</f>
         <v>101.02</v>
       </c>
-      <c r="H152" s="59">
+      <c r="H152">
         <f>SD!I6*100</f>
         <v>103.86999999999999</v>
       </c>
-      <c r="I152" s="59">
+      <c r="I152">
         <f>SD!J6*100</f>
         <v>100.35000000000001</v>
       </c>
-      <c r="J152" s="59">
+      <c r="J152">
         <f>SD!K6*100</f>
         <v>98.71</v>
       </c>
-      <c r="K152" s="59">
+      <c r="K152">
         <f>SD!L6*100</f>
         <v>92.39</v>
       </c>
-      <c r="L152" s="59">
+      <c r="L152">
         <f>SD!M6*100</f>
         <v>91.09</v>
       </c>
-      <c r="M152" s="59">
+      <c r="M152">
         <f>SD!N6*100</f>
         <v>90.22</v>
       </c>
-      <c r="N152" s="59">
+      <c r="N152">
         <f>SD!O6*100</f>
         <v>70.44</v>
       </c>
-      <c r="O152" s="59">
+      <c r="O152">
         <f>SD!P6*100</f>
         <v>69.789999999999992</v>
       </c>
-      <c r="P152" s="59">
+      <c r="P152">
         <f>SD!Q6*100</f>
         <v>69.789999999999992</v>
       </c>
@@ -29439,6 +29808,80 @@
       <c r="P153">
         <f>SD!Q7</f>
         <v>14</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B161" t="str">
+        <f>SD!C31</f>
+        <v>Q1</v>
+      </c>
+      <c r="C161" t="str">
+        <f>SD!D31</f>
+        <v>Q2</v>
+      </c>
+      <c r="D161" t="str">
+        <f>SD!E31</f>
+        <v>Q3</v>
+      </c>
+      <c r="E161" t="str">
+        <f>SD!F31</f>
+        <v>Q4</v>
+      </c>
+      <c r="F161" t="str">
+        <f>SD!G31</f>
+        <v>Q1'27</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A162" t="str">
+        <f>SD!B6</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B162">
+        <f>SD!C36*100</f>
+        <v>100.1</v>
+      </c>
+      <c r="C162">
+        <f>SD!D36*100</f>
+        <v>98.850000000000009</v>
+      </c>
+      <c r="D162">
+        <f>SD!E36*100</f>
+        <v>100.98</v>
+      </c>
+      <c r="E162">
+        <f>SD!F36*100</f>
+        <v>91.24</v>
+      </c>
+      <c r="F162">
+        <f>SD!G36*100</f>
+        <v>83.919999999999987</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A163" t="str">
+        <f>SD!B7</f>
+        <v>Available FTE</v>
+      </c>
+      <c r="B163">
+        <f>SD!C37</f>
+        <v>0</v>
+      </c>
+      <c r="C163">
+        <f>SD!D37</f>
+        <v>1</v>
+      </c>
+      <c r="D163">
+        <f>SD!E37</f>
+        <v>0</v>
+      </c>
+      <c r="E163">
+        <f>SD!F37</f>
+        <v>4</v>
+      </c>
+      <c r="F163">
+        <f>SD!G37</f>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/workforceresult.xlsx
+++ b/workforceresult.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miintra/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E0CF2B5-E501-AF4C-94A9-24AA81D276E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78DE1ADC-4D1C-3844-B53D-F31607A4D9CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16120" activeTab="11" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16120" activeTab="3" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
   </bookViews>
   <sheets>
     <sheet name="ALL" sheetId="1" r:id="rId1"/>
@@ -620,7 +620,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -736,8 +736,22 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="5"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFC00000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="18">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -840,6 +854,12 @@
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -871,7 +891,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -957,6 +977,10 @@
     <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2576,7 +2600,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:P163"/>
+  <dimension ref="A1:P157"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.83203125" bestFit="1" customWidth="1"/>
@@ -3999,7 +4023,7 @@
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A51" t="str">
+      <c r="A51" s="58" t="str">
         <f>AIC!A64</f>
         <v>AI Research &amp; Alliance</v>
       </c>
@@ -4196,8 +4220,122 @@
         <v>2.9</v>
       </c>
     </row>
+    <row r="54" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="59" t="str">
+        <f>$A$152</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B54" s="59">
+        <f>(B53/B52)*100</f>
+        <v>70</v>
+      </c>
+      <c r="C54" s="59">
+        <f t="shared" ref="C54:P54" si="0">(C53/C52)*100</f>
+        <v>70</v>
+      </c>
+      <c r="D54" s="59">
+        <f t="shared" si="0"/>
+        <v>93.333333333333329</v>
+      </c>
+      <c r="E54" s="59">
+        <f t="shared" si="0"/>
+        <v>96.666666666666671</v>
+      </c>
+      <c r="F54" s="59">
+        <f t="shared" si="0"/>
+        <v>96.666666666666671</v>
+      </c>
+      <c r="G54" s="59">
+        <f t="shared" si="0"/>
+        <v>96.666666666666671</v>
+      </c>
+      <c r="H54" s="59">
+        <f t="shared" si="0"/>
+        <v>96.666666666666671</v>
+      </c>
+      <c r="I54" s="59">
+        <f t="shared" si="0"/>
+        <v>96.666666666666671</v>
+      </c>
+      <c r="J54" s="59">
+        <f t="shared" si="0"/>
+        <v>96.666666666666671</v>
+      </c>
+      <c r="K54" s="59">
+        <f t="shared" si="0"/>
+        <v>96.666666666666671</v>
+      </c>
+      <c r="L54" s="59">
+        <f t="shared" si="0"/>
+        <v>96.666666666666671</v>
+      </c>
+      <c r="M54" s="59">
+        <f t="shared" si="0"/>
+        <v>96.666666666666671</v>
+      </c>
+      <c r="N54" s="59">
+        <f t="shared" si="0"/>
+        <v>96.666666666666671</v>
+      </c>
+      <c r="O54" s="59">
+        <f t="shared" si="0"/>
+        <v>96.666666666666671</v>
+      </c>
+      <c r="P54" s="59">
+        <f t="shared" si="0"/>
+        <v>96.666666666666671</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B55" s="60" t="str">
+        <f>B$155</f>
+        <v>Q1</v>
+      </c>
+      <c r="C55" s="60" t="str">
+        <f t="shared" ref="C55:F55" si="1">C$155</f>
+        <v>Q2</v>
+      </c>
+      <c r="D55" s="60" t="str">
+        <f t="shared" si="1"/>
+        <v>Q3</v>
+      </c>
+      <c r="E55" s="60" t="str">
+        <f t="shared" si="1"/>
+        <v>Q4</v>
+      </c>
+      <c r="F55" s="60" t="str">
+        <f t="shared" si="1"/>
+        <v>Q1'27</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="60" t="str">
+        <f>$A$156</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B56" s="60">
+        <f>(AVERAGE(B53:D53)/AVERAGE(B52:D52))*100</f>
+        <v>76.363636363636346</v>
+      </c>
+      <c r="C56" s="60">
+        <f>(AVERAGE(E53:G53)/AVERAGE(E52:G52))*100</f>
+        <v>96.666666666666671</v>
+      </c>
+      <c r="D56" s="60">
+        <f>(AVERAGE(H53:J53)/AVERAGE(H52:J52))*100</f>
+        <v>96.666666666666671</v>
+      </c>
+      <c r="E56" s="60">
+        <f>(AVERAGE(K53:M53)/AVERAGE(K52:M52))*100</f>
+        <v>96.666666666666671</v>
+      </c>
+      <c r="F56" s="60">
+        <f>(AVERAGE(N53:P53)/AVERAGE(N52:P52))*100</f>
+        <v>96.666666666666671</v>
+      </c>
+    </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A61" t="str">
+      <c r="A61" s="58" t="str">
         <f>AIC!A66</f>
         <v>AIET AI Engineering</v>
       </c>
@@ -4394,8 +4532,122 @@
         <v>3.6850000000000001</v>
       </c>
     </row>
+    <row r="64" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="59" t="str">
+        <f>$A$152</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B64" s="59">
+        <f>(B63/B62)*100</f>
+        <v>65.15625</v>
+      </c>
+      <c r="C64" s="59">
+        <f t="shared" ref="C64:P64" si="2">(C63/C62)*100</f>
+        <v>78.0078125</v>
+      </c>
+      <c r="D64" s="59">
+        <f t="shared" si="2"/>
+        <v>76.7578125</v>
+      </c>
+      <c r="E64" s="59">
+        <f t="shared" si="2"/>
+        <v>87.6640625</v>
+      </c>
+      <c r="F64" s="59">
+        <f t="shared" si="2"/>
+        <v>88.6015625</v>
+      </c>
+      <c r="G64" s="59">
+        <f t="shared" si="2"/>
+        <v>87.3515625</v>
+      </c>
+      <c r="H64" s="59">
+        <f t="shared" si="2"/>
+        <v>66.84375</v>
+      </c>
+      <c r="I64" s="59">
+        <f t="shared" si="2"/>
+        <v>64.34375</v>
+      </c>
+      <c r="J64" s="59">
+        <f t="shared" si="2"/>
+        <v>64.34375</v>
+      </c>
+      <c r="K64" s="59">
+        <f t="shared" si="2"/>
+        <v>51.375000000000007</v>
+      </c>
+      <c r="L64" s="59">
+        <f t="shared" si="2"/>
+        <v>51.375000000000007</v>
+      </c>
+      <c r="M64" s="59">
+        <f t="shared" si="2"/>
+        <v>51.375000000000007</v>
+      </c>
+      <c r="N64" s="59">
+        <f t="shared" si="2"/>
+        <v>46.0625</v>
+      </c>
+      <c r="O64" s="59">
+        <f t="shared" si="2"/>
+        <v>46.0625</v>
+      </c>
+      <c r="P64" s="59">
+        <f t="shared" si="2"/>
+        <v>46.0625</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B65" s="60" t="str">
+        <f>B$155</f>
+        <v>Q1</v>
+      </c>
+      <c r="C65" s="60" t="str">
+        <f t="shared" ref="C65:F65" si="3">C$155</f>
+        <v>Q2</v>
+      </c>
+      <c r="D65" s="60" t="str">
+        <f t="shared" si="3"/>
+        <v>Q3</v>
+      </c>
+      <c r="E65" s="60" t="str">
+        <f t="shared" si="3"/>
+        <v>Q4</v>
+      </c>
+      <c r="F65" s="60" t="str">
+        <f t="shared" si="3"/>
+        <v>Q1'27</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="60" t="str">
+        <f>$A$156</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B66" s="60">
+        <f>(AVERAGE(B63:D63)/AVERAGE(B62:D62))*100</f>
+        <v>73.307291666666657</v>
+      </c>
+      <c r="C66" s="60">
+        <f>(AVERAGE(E63:G63)/AVERAGE(E62:G62))*100</f>
+        <v>87.872395833333343</v>
+      </c>
+      <c r="D66" s="60">
+        <f>(AVERAGE(H63:J63)/AVERAGE(H62:J62))*100</f>
+        <v>65.177083333333343</v>
+      </c>
+      <c r="E66" s="60">
+        <f>(AVERAGE(K63:M63)/AVERAGE(K62:M62))*100</f>
+        <v>51.375000000000007</v>
+      </c>
+      <c r="F66" s="60">
+        <f>(AVERAGE(N63:P63)/AVERAGE(N62:P62))*100</f>
+        <v>46.0625</v>
+      </c>
+    </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A71" t="str">
+      <c r="A71" s="58" t="str">
         <f>AIC!A68</f>
         <v>AIET IoT Engineering</v>
       </c>
@@ -4592,8 +4844,122 @@
         <v>1.4</v>
       </c>
     </row>
+    <row r="74" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="59" t="str">
+        <f>$A$152</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B74" s="59">
+        <f>(B73/B72)*100</f>
+        <v>60</v>
+      </c>
+      <c r="C74" s="59">
+        <f t="shared" ref="C74:P74" si="4">(C73/C72)*100</f>
+        <v>75</v>
+      </c>
+      <c r="D74" s="59">
+        <f t="shared" si="4"/>
+        <v>69.166666666666671</v>
+      </c>
+      <c r="E74" s="59">
+        <f t="shared" si="4"/>
+        <v>84.166666666666671</v>
+      </c>
+      <c r="F74" s="59">
+        <f t="shared" si="4"/>
+        <v>88.333333333333329</v>
+      </c>
+      <c r="G74" s="59">
+        <f t="shared" si="4"/>
+        <v>82.5</v>
+      </c>
+      <c r="H74" s="59">
+        <f t="shared" si="4"/>
+        <v>89</v>
+      </c>
+      <c r="I74" s="59">
+        <f t="shared" si="4"/>
+        <v>76</v>
+      </c>
+      <c r="J74" s="59">
+        <f t="shared" si="4"/>
+        <v>75</v>
+      </c>
+      <c r="K74" s="59">
+        <f t="shared" si="4"/>
+        <v>74</v>
+      </c>
+      <c r="L74" s="59">
+        <f t="shared" si="4"/>
+        <v>74</v>
+      </c>
+      <c r="M74" s="59">
+        <f t="shared" si="4"/>
+        <v>74</v>
+      </c>
+      <c r="N74" s="59">
+        <f t="shared" si="4"/>
+        <v>27.999999999999996</v>
+      </c>
+      <c r="O74" s="59">
+        <f t="shared" si="4"/>
+        <v>27.999999999999996</v>
+      </c>
+      <c r="P74" s="59">
+        <f t="shared" si="4"/>
+        <v>27.999999999999996</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B75" s="60" t="str">
+        <f>B$155</f>
+        <v>Q1</v>
+      </c>
+      <c r="C75" s="60" t="str">
+        <f t="shared" ref="C75:F75" si="5">C$155</f>
+        <v>Q2</v>
+      </c>
+      <c r="D75" s="60" t="str">
+        <f t="shared" si="5"/>
+        <v>Q3</v>
+      </c>
+      <c r="E75" s="60" t="str">
+        <f t="shared" si="5"/>
+        <v>Q4</v>
+      </c>
+      <c r="F75" s="60" t="str">
+        <f t="shared" si="5"/>
+        <v>Q1'27</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="60" t="str">
+        <f>$A$156</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B76" s="60">
+        <f>(AVERAGE(B73:D73)/AVERAGE(B72:D72))*100</f>
+        <v>67.631578947368425</v>
+      </c>
+      <c r="C76" s="60">
+        <f>(AVERAGE(E73:G73)/AVERAGE(E72:G72))*100</f>
+        <v>85.000000000000014</v>
+      </c>
+      <c r="D76" s="60">
+        <f>(AVERAGE(H73:J73)/AVERAGE(H72:J72))*100</f>
+        <v>80</v>
+      </c>
+      <c r="E76" s="60">
+        <f>(AVERAGE(K73:M73)/AVERAGE(K72:M72))*100</f>
+        <v>74.000000000000014</v>
+      </c>
+      <c r="F76" s="60">
+        <f>(AVERAGE(N73:P73)/AVERAGE(N72:P72))*100</f>
+        <v>27.999999999999993</v>
+      </c>
+    </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A81" t="str">
+      <c r="A81" s="58" t="str">
         <f>AIC!A70</f>
         <v>AIET Spatial AI Engineering</v>
       </c>
@@ -4790,8 +5156,122 @@
         <v>0.4</v>
       </c>
     </row>
+    <row r="84" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="59" t="str">
+        <f>$A$152</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B84" s="59">
+        <f>(B83/B82)*100</f>
+        <v>77.5</v>
+      </c>
+      <c r="C84" s="59">
+        <f t="shared" ref="C84:P84" si="6">(C83/C82)*100</f>
+        <v>80</v>
+      </c>
+      <c r="D84" s="59">
+        <f t="shared" si="6"/>
+        <v>74.6875</v>
+      </c>
+      <c r="E84" s="59">
+        <f t="shared" si="6"/>
+        <v>90</v>
+      </c>
+      <c r="F84" s="59">
+        <f t="shared" si="6"/>
+        <v>103.49999999999999</v>
+      </c>
+      <c r="G84" s="59">
+        <f t="shared" si="6"/>
+        <v>104.16666666666667</v>
+      </c>
+      <c r="H84" s="59">
+        <f t="shared" si="6"/>
+        <v>104.16666666666667</v>
+      </c>
+      <c r="I84" s="59">
+        <f t="shared" si="6"/>
+        <v>104.16666666666667</v>
+      </c>
+      <c r="J84" s="59">
+        <f t="shared" si="6"/>
+        <v>85.833333333333343</v>
+      </c>
+      <c r="K84" s="59">
+        <f t="shared" si="6"/>
+        <v>95.833333333333343</v>
+      </c>
+      <c r="L84" s="59">
+        <f t="shared" si="6"/>
+        <v>97.5</v>
+      </c>
+      <c r="M84" s="59">
+        <f t="shared" si="6"/>
+        <v>87.5</v>
+      </c>
+      <c r="N84" s="59">
+        <f t="shared" si="6"/>
+        <v>13.333333333333334</v>
+      </c>
+      <c r="O84" s="59">
+        <f t="shared" si="6"/>
+        <v>13.333333333333334</v>
+      </c>
+      <c r="P84" s="59">
+        <f t="shared" si="6"/>
+        <v>13.333333333333334</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B85" s="60" t="str">
+        <f>B$155</f>
+        <v>Q1</v>
+      </c>
+      <c r="C85" s="60" t="str">
+        <f t="shared" ref="C85:F85" si="7">C$155</f>
+        <v>Q2</v>
+      </c>
+      <c r="D85" s="60" t="str">
+        <f t="shared" si="7"/>
+        <v>Q3</v>
+      </c>
+      <c r="E85" s="60" t="str">
+        <f t="shared" si="7"/>
+        <v>Q4</v>
+      </c>
+      <c r="F85" s="60" t="str">
+        <f t="shared" si="7"/>
+        <v>Q1'27</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="60" t="str">
+        <f>$A$156</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B86" s="60">
+        <f>(AVERAGE(B83:D83)/AVERAGE(B82:D82))*100</f>
+        <v>77.395833333333343</v>
+      </c>
+      <c r="C86" s="60">
+        <f>(AVERAGE(E83:G83)/AVERAGE(E82:G82))*100</f>
+        <v>98.3</v>
+      </c>
+      <c r="D86" s="60">
+        <f>(AVERAGE(H83:J83)/AVERAGE(H82:J82))*100</f>
+        <v>98.055555555555557</v>
+      </c>
+      <c r="E86" s="60">
+        <f>(AVERAGE(K83:M83)/AVERAGE(K82:M82))*100</f>
+        <v>93.611111111111128</v>
+      </c>
+      <c r="F86" s="60">
+        <f>(AVERAGE(N83:P83)/AVERAGE(N82:P82))*100</f>
+        <v>13.333333333333336</v>
+      </c>
+    </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A91" t="str">
+      <c r="A91" s="58" t="str">
         <f>AIC!A72</f>
         <v>Product Innovation</v>
       </c>
@@ -4988,6 +5468,116 @@
         <v>0</v>
       </c>
     </row>
+    <row r="94" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="59" t="str">
+        <f>$A$152</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B94" s="59">
+        <f>(B93/B92)*100</f>
+        <v>60</v>
+      </c>
+      <c r="C94" s="59">
+        <f t="shared" ref="C94:P94" si="8">(C93/C92)*100</f>
+        <v>60</v>
+      </c>
+      <c r="D94" s="59">
+        <f t="shared" si="8"/>
+        <v>40</v>
+      </c>
+      <c r="E94" s="62">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="F94" s="62">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="G94" s="62">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="H94" s="62">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="I94" s="62">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="J94" s="62">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="K94" s="62">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="L94" s="62">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="M94" s="62">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="N94" s="62">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="O94" s="62">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="P94" s="62">
+        <f>0</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B95" s="60" t="str">
+        <f>B$155</f>
+        <v>Q1</v>
+      </c>
+      <c r="C95" s="60" t="str">
+        <f t="shared" ref="C95:F95" si="9">C$155</f>
+        <v>Q2</v>
+      </c>
+      <c r="D95" s="60" t="str">
+        <f t="shared" si="9"/>
+        <v>Q3</v>
+      </c>
+      <c r="E95" s="60" t="str">
+        <f t="shared" si="9"/>
+        <v>Q4</v>
+      </c>
+      <c r="F95" s="60" t="str">
+        <f t="shared" si="9"/>
+        <v>Q1'27</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="60" t="str">
+        <f>$A$156</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B96" s="60">
+        <f>(AVERAGE(B93:D93)/AVERAGE(B92:D92))*100</f>
+        <v>53.333333333333336</v>
+      </c>
+      <c r="C96" s="61">
+        <v>0</v>
+      </c>
+      <c r="D96" s="61">
+        <v>0</v>
+      </c>
+      <c r="E96" s="61">
+        <v>0</v>
+      </c>
+      <c r="F96" s="61">
+        <v>0</v>
+      </c>
+    </row>
     <row r="151" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B151" t="str">
         <f>AIC!C1</f>
@@ -5182,76 +5772,76 @@
         <v>11</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B161" t="str">
+    <row r="155" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B155" t="str">
         <f>AIC!C31</f>
         <v>Q1</v>
       </c>
-      <c r="C161" t="str">
+      <c r="C155" t="str">
         <f>AIC!D31</f>
         <v>Q2</v>
       </c>
-      <c r="D161" t="str">
+      <c r="D155" t="str">
         <f>AIC!E31</f>
         <v>Q3</v>
       </c>
-      <c r="E161" t="str">
+      <c r="E155" t="str">
         <f>AIC!F31</f>
         <v>Q4</v>
       </c>
-      <c r="F161" t="str">
+      <c r="F155" t="str">
         <f>AIC!G31</f>
         <v>Q1'27</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A162" t="str">
+    <row r="156" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A156" t="str">
         <f>AIC!B6</f>
         <v>% Plan</v>
       </c>
-      <c r="B162">
+      <c r="B156">
         <f>AIC!C36*100</f>
         <v>72.070000000000007</v>
       </c>
-      <c r="C162">
+      <c r="C156">
         <f>AIC!D36*100</f>
         <v>90.03</v>
       </c>
-      <c r="D162">
+      <c r="D156">
         <f>AIC!E36*100</f>
         <v>79.239999999999995</v>
       </c>
-      <c r="E162">
+      <c r="E156">
         <f>AIC!F36*100</f>
         <v>71.150000000000006</v>
       </c>
-      <c r="F162">
+      <c r="F156">
         <f>AIC!G36*100</f>
         <v>62.029999999999994</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A163" t="str">
+    <row r="157" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A157" t="str">
         <f>AIC!B7</f>
         <v>Available FTE</v>
       </c>
-      <c r="B163">
+      <c r="B157">
         <f>AIC!C37</f>
         <v>6</v>
       </c>
-      <c r="C163">
+      <c r="C157">
         <f>AIC!D37</f>
         <v>2</v>
       </c>
-      <c r="D163">
+      <c r="D157">
         <f>AIC!E37</f>
         <v>4</v>
       </c>
-      <c r="E163">
+      <c r="E157">
         <f>AIC!F37</f>
         <v>5</v>
       </c>
-      <c r="F163">
+      <c r="F157">
         <f>AIC!G37</f>
         <v>7</v>
       </c>
@@ -7636,7 +8226,7 @@
   <sheetPr>
     <tabColor theme="3" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:P163"/>
+  <dimension ref="A1:P157"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.6640625" bestFit="1" customWidth="1"/>
@@ -9059,7 +9649,7 @@
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A51" t="str">
+      <c r="A51" s="58" t="str">
         <f>TDE!A66</f>
         <v>Financial Management</v>
       </c>
@@ -9256,8 +9846,122 @@
         <v>4</v>
       </c>
     </row>
+    <row r="54" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="59" t="str">
+        <f>$A$152</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B54" s="59">
+        <f>(B53/B52)*100</f>
+        <v>100</v>
+      </c>
+      <c r="C54" s="59">
+        <f t="shared" ref="C54:P54" si="0">(C53/C52)*100</f>
+        <v>100</v>
+      </c>
+      <c r="D54" s="59">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E54" s="59">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F54" s="59">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="G54" s="59">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H54" s="59">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="I54" s="59">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="J54" s="59">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="K54" s="59">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="L54" s="59">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="M54" s="59">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="N54" s="59">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="O54" s="59">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="P54" s="59">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B55" s="60" t="str">
+        <f>B$155</f>
+        <v>Q1</v>
+      </c>
+      <c r="C55" s="60" t="str">
+        <f t="shared" ref="C55:F55" si="1">C$155</f>
+        <v>Q2</v>
+      </c>
+      <c r="D55" s="60" t="str">
+        <f t="shared" si="1"/>
+        <v>Q3</v>
+      </c>
+      <c r="E55" s="60" t="str">
+        <f t="shared" si="1"/>
+        <v>Q4</v>
+      </c>
+      <c r="F55" s="60" t="str">
+        <f t="shared" si="1"/>
+        <v>Q1'27</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="60" t="str">
+        <f>$A$156</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B56" s="60">
+        <f>(AVERAGE(B53:D53)/AVERAGE(B52:D52))*100</f>
+        <v>100</v>
+      </c>
+      <c r="C56" s="60">
+        <f>(AVERAGE(E53:G53)/AVERAGE(E52:G52))*100</f>
+        <v>100</v>
+      </c>
+      <c r="D56" s="60">
+        <f>(AVERAGE(H53:J53)/AVERAGE(H52:J52))*100</f>
+        <v>100</v>
+      </c>
+      <c r="E56" s="60">
+        <f>(AVERAGE(K53:M53)/AVERAGE(K52:M52))*100</f>
+        <v>100</v>
+      </c>
+      <c r="F56" s="60">
+        <f>(AVERAGE(N53:P53)/AVERAGE(N52:P52))*100</f>
+        <v>100</v>
+      </c>
+    </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A61" t="str">
+      <c r="A61" s="58" t="str">
         <f>TDE!A68</f>
         <v>Resource Management</v>
       </c>
@@ -9454,8 +10158,122 @@
         <v>5</v>
       </c>
     </row>
+    <row r="64" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="59" t="str">
+        <f>$A$152</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B64" s="59">
+        <f>(B63/B62)*100</f>
+        <v>100</v>
+      </c>
+      <c r="C64" s="59">
+        <f t="shared" ref="C64:P64" si="2">(C63/C62)*100</f>
+        <v>100</v>
+      </c>
+      <c r="D64" s="59">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="E64" s="59">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="F64" s="59">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="G64" s="59">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="H64" s="59">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="I64" s="59">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="J64" s="59">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="K64" s="59">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="L64" s="59">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="M64" s="59">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="N64" s="59">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="O64" s="59">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="P64" s="59">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B65" s="60" t="str">
+        <f>B$155</f>
+        <v>Q1</v>
+      </c>
+      <c r="C65" s="60" t="str">
+        <f t="shared" ref="C65:F65" si="3">C$155</f>
+        <v>Q2</v>
+      </c>
+      <c r="D65" s="60" t="str">
+        <f t="shared" si="3"/>
+        <v>Q3</v>
+      </c>
+      <c r="E65" s="60" t="str">
+        <f t="shared" si="3"/>
+        <v>Q4</v>
+      </c>
+      <c r="F65" s="60" t="str">
+        <f t="shared" si="3"/>
+        <v>Q1'27</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="60" t="str">
+        <f>$A$156</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B66" s="60">
+        <f>(AVERAGE(B63:D63)/AVERAGE(B62:D62))*100</f>
+        <v>100</v>
+      </c>
+      <c r="C66" s="60">
+        <f>(AVERAGE(E63:G63)/AVERAGE(E62:G62))*100</f>
+        <v>100</v>
+      </c>
+      <c r="D66" s="60">
+        <f>(AVERAGE(H63:J63)/AVERAGE(H62:J62))*100</f>
+        <v>100</v>
+      </c>
+      <c r="E66" s="60">
+        <f>(AVERAGE(K63:M63)/AVERAGE(K62:M62))*100</f>
+        <v>100</v>
+      </c>
+      <c r="F66" s="60">
+        <f>(AVERAGE(N63:P63)/AVERAGE(N62:P62))*100</f>
+        <v>100</v>
+      </c>
+    </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A71" t="str">
+      <c r="A71" s="58" t="str">
         <f>TDE!A74</f>
         <v>Talent Experience &amp; Development</v>
       </c>
@@ -9652,8 +10470,122 @@
         <v>3</v>
       </c>
     </row>
+    <row r="74" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="59" t="str">
+        <f>$A$152</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B74" s="59">
+        <f>(B73/B72)*100</f>
+        <v>100</v>
+      </c>
+      <c r="C74" s="59">
+        <f t="shared" ref="C74:P74" si="4">(C73/C72)*100</f>
+        <v>100</v>
+      </c>
+      <c r="D74" s="59">
+        <f t="shared" si="4"/>
+        <v>100</v>
+      </c>
+      <c r="E74" s="59">
+        <f t="shared" si="4"/>
+        <v>100</v>
+      </c>
+      <c r="F74" s="59">
+        <f t="shared" si="4"/>
+        <v>100</v>
+      </c>
+      <c r="G74" s="59">
+        <f t="shared" si="4"/>
+        <v>100</v>
+      </c>
+      <c r="H74" s="59">
+        <f t="shared" si="4"/>
+        <v>100</v>
+      </c>
+      <c r="I74" s="59">
+        <f t="shared" si="4"/>
+        <v>100</v>
+      </c>
+      <c r="J74" s="59">
+        <f t="shared" si="4"/>
+        <v>100</v>
+      </c>
+      <c r="K74" s="59">
+        <f t="shared" si="4"/>
+        <v>100</v>
+      </c>
+      <c r="L74" s="59">
+        <f t="shared" si="4"/>
+        <v>100</v>
+      </c>
+      <c r="M74" s="59">
+        <f t="shared" si="4"/>
+        <v>100</v>
+      </c>
+      <c r="N74" s="59">
+        <f t="shared" si="4"/>
+        <v>100</v>
+      </c>
+      <c r="O74" s="59">
+        <f t="shared" si="4"/>
+        <v>100</v>
+      </c>
+      <c r="P74" s="59">
+        <f t="shared" si="4"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B75" s="60" t="str">
+        <f>B$155</f>
+        <v>Q1</v>
+      </c>
+      <c r="C75" s="60" t="str">
+        <f t="shared" ref="C75:F75" si="5">C$155</f>
+        <v>Q2</v>
+      </c>
+      <c r="D75" s="60" t="str">
+        <f t="shared" si="5"/>
+        <v>Q3</v>
+      </c>
+      <c r="E75" s="60" t="str">
+        <f t="shared" si="5"/>
+        <v>Q4</v>
+      </c>
+      <c r="F75" s="60" t="str">
+        <f t="shared" si="5"/>
+        <v>Q1'27</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="60" t="str">
+        <f>$A$156</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B76" s="60">
+        <f>(AVERAGE(B73:D73)/AVERAGE(B72:D72))*100</f>
+        <v>100</v>
+      </c>
+      <c r="C76" s="60">
+        <f>(AVERAGE(E73:G73)/AVERAGE(E72:G72))*100</f>
+        <v>100</v>
+      </c>
+      <c r="D76" s="60">
+        <f>(AVERAGE(H73:J73)/AVERAGE(H72:J72))*100</f>
+        <v>100</v>
+      </c>
+      <c r="E76" s="60">
+        <f>(AVERAGE(K73:M73)/AVERAGE(K72:M72))*100</f>
+        <v>100</v>
+      </c>
+      <c r="F76" s="60">
+        <f>(AVERAGE(N73:P73)/AVERAGE(N72:P72))*100</f>
+        <v>100</v>
+      </c>
+    </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A81" t="str">
+      <c r="A81" s="58" t="str">
         <f>TDE!A80</f>
         <v>Center of Excellences</v>
       </c>
@@ -9850,6 +10782,120 @@
         <v>3</v>
       </c>
     </row>
+    <row r="84" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="59" t="str">
+        <f>$A$152</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B84" s="59">
+        <f>(B83/B82)*100</f>
+        <v>100</v>
+      </c>
+      <c r="C84" s="59">
+        <f t="shared" ref="C84:P84" si="6">(C83/C82)*100</f>
+        <v>100</v>
+      </c>
+      <c r="D84" s="59">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+      <c r="E84" s="59">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+      <c r="F84" s="59">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+      <c r="G84" s="59">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+      <c r="H84" s="59">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+      <c r="I84" s="59">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+      <c r="J84" s="59">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+      <c r="K84" s="59">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+      <c r="L84" s="59">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+      <c r="M84" s="59">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+      <c r="N84" s="59">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+      <c r="O84" s="59">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+      <c r="P84" s="59">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B85" s="60" t="str">
+        <f>B$155</f>
+        <v>Q1</v>
+      </c>
+      <c r="C85" s="60" t="str">
+        <f t="shared" ref="C85:F85" si="7">C$155</f>
+        <v>Q2</v>
+      </c>
+      <c r="D85" s="60" t="str">
+        <f t="shared" si="7"/>
+        <v>Q3</v>
+      </c>
+      <c r="E85" s="60" t="str">
+        <f t="shared" si="7"/>
+        <v>Q4</v>
+      </c>
+      <c r="F85" s="60" t="str">
+        <f t="shared" si="7"/>
+        <v>Q1'27</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="60" t="str">
+        <f>$A$156</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B86" s="60">
+        <f>(AVERAGE(B83:D83)/AVERAGE(B82:D82))*100</f>
+        <v>100</v>
+      </c>
+      <c r="C86" s="60">
+        <f>(AVERAGE(E83:G83)/AVERAGE(E82:G82))*100</f>
+        <v>100</v>
+      </c>
+      <c r="D86" s="60">
+        <f>(AVERAGE(H83:J83)/AVERAGE(H82:J82))*100</f>
+        <v>100</v>
+      </c>
+      <c r="E86" s="60">
+        <f>(AVERAGE(K83:M83)/AVERAGE(K82:M82))*100</f>
+        <v>100</v>
+      </c>
+      <c r="F86" s="60">
+        <f>(AVERAGE(N83:P83)/AVERAGE(N82:P82))*100</f>
+        <v>100</v>
+      </c>
+    </row>
     <row r="151" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B151" t="str">
         <f>TDE!C1</f>
@@ -10044,76 +11090,76 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B161" t="str">
+    <row r="155" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B155" t="str">
         <f>TDE!C31</f>
         <v>Q1</v>
       </c>
-      <c r="C161" t="str">
+      <c r="C155" t="str">
         <f>TDE!D31</f>
         <v>Q2</v>
       </c>
-      <c r="D161" t="str">
+      <c r="D155" t="str">
         <f>TDE!E31</f>
         <v>Q3</v>
       </c>
-      <c r="E161" t="str">
+      <c r="E155" t="str">
         <f>TDE!F31</f>
         <v>Q4</v>
       </c>
-      <c r="F161" t="str">
+      <c r="F155" t="str">
         <f>TDE!G31</f>
         <v>Q1'27</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A162" t="str">
+    <row r="156" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A156" t="str">
         <f>TDE!B6</f>
         <v>% Plan</v>
       </c>
-      <c r="B162">
+      <c r="B156">
         <f>TDE!C36*100</f>
         <v>100</v>
       </c>
-      <c r="C162">
+      <c r="C156">
         <f>TDE!D36*100</f>
         <v>100</v>
       </c>
-      <c r="D162">
+      <c r="D156">
         <f>TDE!E36*100</f>
         <v>100</v>
       </c>
-      <c r="E162">
+      <c r="E156">
         <f>TDE!F36*100</f>
         <v>100</v>
       </c>
-      <c r="F162">
+      <c r="F156">
         <f>TDE!G36*100</f>
         <v>100</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A163" t="str">
+    <row r="157" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A157" t="str">
         <f>TDE!B7</f>
         <v>Available FTE</v>
       </c>
-      <c r="B163">
+      <c r="B157">
         <f>TDE!C37</f>
         <v>0</v>
       </c>
-      <c r="C163">
+      <c r="C157">
         <f>TDE!D37</f>
         <v>0</v>
       </c>
-      <c r="D163">
+      <c r="D157">
         <f>TDE!E37</f>
         <v>0</v>
       </c>
-      <c r="E163">
+      <c r="E157">
         <f>TDE!F37</f>
         <v>0</v>
       </c>
-      <c r="F163">
+      <c r="F157">
         <f>TDE!G37</f>
         <v>0</v>
       </c>
@@ -13516,7 +14562,7 @@
   <sheetPr>
     <tabColor theme="4" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:P163"/>
+  <dimension ref="A1:P157"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.83203125" bestFit="1" customWidth="1"/>
@@ -15132,76 +16178,76 @@
         <v>45</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B161" t="str">
+    <row r="155" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B155" t="str">
         <f>ALL!C31</f>
         <v>Q1</v>
       </c>
-      <c r="C161" t="str">
+      <c r="C155" t="str">
         <f>ALL!D31</f>
         <v>Q2</v>
       </c>
-      <c r="D161" t="str">
+      <c r="D155" t="str">
         <f>ALL!E31</f>
         <v>Q3</v>
       </c>
-      <c r="E161" t="str">
+      <c r="E155" t="str">
         <f>ALL!F31</f>
         <v>Q4</v>
       </c>
-      <c r="F161" t="str">
+      <c r="F155" t="str">
         <f>ALL!G31</f>
         <v>Q1'27</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A162" t="str">
+    <row r="156" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A156" t="str">
         <f>ALL!B6</f>
         <v>% Plan</v>
       </c>
-      <c r="B162">
+      <c r="B156">
         <f>ALL!C36*100</f>
         <v>92.5</v>
       </c>
-      <c r="C162">
+      <c r="C156">
         <f>ALL!D36*100</f>
         <v>96.179999999999993</v>
       </c>
-      <c r="D162">
+      <c r="D156">
         <f>ALL!E36*100</f>
         <v>94.28</v>
       </c>
-      <c r="E162">
+      <c r="E156">
         <f>ALL!F36*100</f>
         <v>87.570000000000007</v>
       </c>
-      <c r="F162">
+      <c r="F156">
         <f>ALL!G36*100</f>
         <v>81.52000000000001</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A163" t="str">
+    <row r="157" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A157" t="str">
         <f>ALL!B7</f>
         <v>Available FTE</v>
       </c>
-      <c r="B163">
+      <c r="B157">
         <f>ALL!C37</f>
         <v>11</v>
       </c>
-      <c r="C163">
+      <c r="C157">
         <f>ALL!D37</f>
         <v>6</v>
       </c>
-      <c r="D163">
+      <c r="D157">
         <f>ALL!E37</f>
         <v>9</v>
       </c>
-      <c r="E163">
+      <c r="E157">
         <f>ALL!F37</f>
         <v>19</v>
       </c>
-      <c r="F163">
+      <c r="F157">
         <f>ALL!G37</f>
         <v>28</v>
       </c>
@@ -16950,10 +17996,10 @@
   <sheetPr>
     <tabColor theme="5" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:P163"/>
+  <dimension ref="A1:P157"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
@@ -18373,7 +19419,7 @@
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A51" t="str">
+      <c r="A51" s="58" t="str">
         <f>CPS!A66</f>
         <v>Business Development &amp; Partnerships</v>
       </c>
@@ -18570,8 +19616,122 @@
         <v>8.1999999999999993</v>
       </c>
     </row>
+    <row r="54" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="59" t="str">
+        <f>$A$152</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B54" s="59">
+        <f>(B53/B52)*100</f>
+        <v>93.75</v>
+      </c>
+      <c r="C54" s="59">
+        <f t="shared" ref="C54:P54" si="0">(C53/C52)*100</f>
+        <v>94.583333333333329</v>
+      </c>
+      <c r="D54" s="59">
+        <f t="shared" si="0"/>
+        <v>92.083333333333343</v>
+      </c>
+      <c r="E54" s="59">
+        <f t="shared" si="0"/>
+        <v>103.63636363636364</v>
+      </c>
+      <c r="F54" s="59">
+        <f t="shared" si="0"/>
+        <v>104.54545454545455</v>
+      </c>
+      <c r="G54" s="59">
+        <f t="shared" si="0"/>
+        <v>103.63636363636364</v>
+      </c>
+      <c r="H54" s="59">
+        <f t="shared" si="0"/>
+        <v>92.72727272727272</v>
+      </c>
+      <c r="I54" s="59">
+        <f t="shared" si="0"/>
+        <v>90.909090909090907</v>
+      </c>
+      <c r="J54" s="59">
+        <f t="shared" si="0"/>
+        <v>90.909090909090907</v>
+      </c>
+      <c r="K54" s="59">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+      <c r="L54" s="59">
+        <f t="shared" si="0"/>
+        <v>88.181818181818173</v>
+      </c>
+      <c r="M54" s="59">
+        <f t="shared" si="0"/>
+        <v>88.181818181818173</v>
+      </c>
+      <c r="N54" s="59">
+        <f t="shared" si="0"/>
+        <v>74.545454545454533</v>
+      </c>
+      <c r="O54" s="59">
+        <f t="shared" si="0"/>
+        <v>74.545454545454533</v>
+      </c>
+      <c r="P54" s="59">
+        <f t="shared" si="0"/>
+        <v>74.545454545454533</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B55" s="60" t="str">
+        <f>B$155</f>
+        <v>Q1</v>
+      </c>
+      <c r="C55" s="60" t="str">
+        <f t="shared" ref="C55:F55" si="1">C$155</f>
+        <v>Q2</v>
+      </c>
+      <c r="D55" s="60" t="str">
+        <f t="shared" si="1"/>
+        <v>Q3</v>
+      </c>
+      <c r="E55" s="60" t="str">
+        <f t="shared" si="1"/>
+        <v>Q4</v>
+      </c>
+      <c r="F55" s="60" t="str">
+        <f t="shared" si="1"/>
+        <v>Q1'27</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="60" t="str">
+        <f>$A$156</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B56" s="60">
+        <f>(AVERAGE(B53:D53)/AVERAGE(B52:D52))*100</f>
+        <v>93.472222222222229</v>
+      </c>
+      <c r="C56" s="60">
+        <f>(AVERAGE(E53:G53)/AVERAGE(E52:G52))*100</f>
+        <v>103.93939393939394</v>
+      </c>
+      <c r="D56" s="60">
+        <f>(AVERAGE(H53:J53)/AVERAGE(H52:J52))*100</f>
+        <v>91.515151515151516</v>
+      </c>
+      <c r="E56" s="60">
+        <f>(AVERAGE(K53:M53)/AVERAGE(K52:M52))*100</f>
+        <v>88.787878787878796</v>
+      </c>
+      <c r="F56" s="60">
+        <f>(AVERAGE(N53:P53)/AVERAGE(N52:P52))*100</f>
+        <v>74.545454545454533</v>
+      </c>
+    </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A61" t="str">
+      <c r="A61" s="58" t="str">
         <f>CPS!A68</f>
         <v>Product Commercialization</v>
       </c>
@@ -18768,6 +19928,120 @@
         <v>5</v>
       </c>
     </row>
+    <row r="64" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="59" t="str">
+        <f>$A$152</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B64" s="59">
+        <f>(B63/B62)*100</f>
+        <v>92</v>
+      </c>
+      <c r="C64" s="59">
+        <f t="shared" ref="C64" si="2">(C63/C62)*100</f>
+        <v>92</v>
+      </c>
+      <c r="D64" s="59">
+        <f t="shared" ref="D64" si="3">(D63/D62)*100</f>
+        <v>92</v>
+      </c>
+      <c r="E64" s="59">
+        <f t="shared" ref="E64" si="4">(E63/E62)*100</f>
+        <v>100</v>
+      </c>
+      <c r="F64" s="59">
+        <f t="shared" ref="F64" si="5">(F63/F62)*100</f>
+        <v>100</v>
+      </c>
+      <c r="G64" s="59">
+        <f t="shared" ref="G64" si="6">(G63/G62)*100</f>
+        <v>100</v>
+      </c>
+      <c r="H64" s="59">
+        <f t="shared" ref="H64" si="7">(H63/H62)*100</f>
+        <v>100</v>
+      </c>
+      <c r="I64" s="59">
+        <f t="shared" ref="I64" si="8">(I63/I62)*100</f>
+        <v>100</v>
+      </c>
+      <c r="J64" s="59">
+        <f t="shared" ref="J64" si="9">(J63/J62)*100</f>
+        <v>100</v>
+      </c>
+      <c r="K64" s="59">
+        <f t="shared" ref="K64" si="10">(K63/K62)*100</f>
+        <v>100</v>
+      </c>
+      <c r="L64" s="59">
+        <f t="shared" ref="L64" si="11">(L63/L62)*100</f>
+        <v>100</v>
+      </c>
+      <c r="M64" s="59">
+        <f t="shared" ref="M64" si="12">(M63/M62)*100</f>
+        <v>100</v>
+      </c>
+      <c r="N64" s="59">
+        <f t="shared" ref="N64" si="13">(N63/N62)*100</f>
+        <v>100</v>
+      </c>
+      <c r="O64" s="59">
+        <f t="shared" ref="O64" si="14">(O63/O62)*100</f>
+        <v>100</v>
+      </c>
+      <c r="P64" s="59">
+        <f t="shared" ref="P64" si="15">(P63/P62)*100</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B65" s="60" t="str">
+        <f>B$155</f>
+        <v>Q1</v>
+      </c>
+      <c r="C65" s="60" t="str">
+        <f t="shared" ref="C65:F65" si="16">C$155</f>
+        <v>Q2</v>
+      </c>
+      <c r="D65" s="60" t="str">
+        <f t="shared" si="16"/>
+        <v>Q3</v>
+      </c>
+      <c r="E65" s="60" t="str">
+        <f t="shared" si="16"/>
+        <v>Q4</v>
+      </c>
+      <c r="F65" s="60" t="str">
+        <f t="shared" si="16"/>
+        <v>Q1'27</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="60" t="str">
+        <f>$A$156</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B66" s="60">
+        <f>(AVERAGE(B63:D63)/AVERAGE(B62:D62))*100</f>
+        <v>92</v>
+      </c>
+      <c r="C66" s="60">
+        <f>(AVERAGE(E63:G63)/AVERAGE(E62:G62))*100</f>
+        <v>100</v>
+      </c>
+      <c r="D66" s="60">
+        <f>(AVERAGE(H63:J63)/AVERAGE(H62:J62))*100</f>
+        <v>100</v>
+      </c>
+      <c r="E66" s="60">
+        <f>(AVERAGE(K63:M63)/AVERAGE(K62:M62))*100</f>
+        <v>100</v>
+      </c>
+      <c r="F66" s="60">
+        <f>(AVERAGE(N63:P63)/AVERAGE(N62:P62))*100</f>
+        <v>100</v>
+      </c>
+    </row>
     <row r="151" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B151" t="str">
         <f>CPS!C1</f>
@@ -18962,76 +20236,76 @@
         <v>3</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B161" t="str">
+    <row r="155" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B155" t="str">
         <f>CPS!C31</f>
         <v>Q1</v>
       </c>
-      <c r="C161" t="str">
+      <c r="C155" t="str">
         <f>CPS!D31</f>
         <v>Q2</v>
       </c>
-      <c r="D161" t="str">
+      <c r="D155" t="str">
         <f>CPS!E31</f>
         <v>Q3</v>
       </c>
-      <c r="E161" t="str">
+      <c r="E155" t="str">
         <f>CPS!F31</f>
         <v>Q4</v>
       </c>
-      <c r="F161" t="str">
+      <c r="F155" t="str">
         <f>CPS!G31</f>
         <v>Q1'27</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A162" t="str">
+    <row r="156" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A156" t="str">
         <f>CPS!B6</f>
         <v>% Plan</v>
       </c>
-      <c r="B162">
+      <c r="B156">
         <f>CPS!C36*100</f>
         <v>93.43</v>
       </c>
-      <c r="C162">
+      <c r="C156">
         <f>CPS!D36*100</f>
         <v>102.55000000000001</v>
       </c>
-      <c r="D162">
+      <c r="D156">
         <f>CPS!E36*100</f>
         <v>94.51</v>
       </c>
-      <c r="E162">
+      <c r="E156">
         <f>CPS!F36*100</f>
         <v>92.75</v>
       </c>
-      <c r="F162">
+      <c r="F156">
         <f>CPS!G36*100</f>
         <v>89.41</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A163" t="str">
+    <row r="157" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A157" t="str">
         <f>CPS!B7</f>
         <v>Available FTE</v>
       </c>
-      <c r="B163">
+      <c r="B157">
         <f>CPS!C37</f>
         <v>1</v>
       </c>
-      <c r="C163">
+      <c r="C157">
         <f>CPS!D37</f>
         <v>0</v>
       </c>
-      <c r="D163">
+      <c r="D157">
         <f>CPS!E37</f>
         <v>1</v>
       </c>
-      <c r="E163">
+      <c r="E157">
         <f>CPS!F37</f>
         <v>1</v>
       </c>
-      <c r="F163">
+      <c r="F157">
         <f>CPS!G37</f>
         <v>2</v>
       </c>
@@ -21310,7 +22584,7 @@
   <sheetPr>
     <tabColor theme="7" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:P163"/>
+  <dimension ref="A1:P157"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.83203125" bestFit="1" customWidth="1"/>
@@ -22733,7 +24007,7 @@
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A51" t="str">
+      <c r="A51" s="58" t="str">
         <f>PSE!A66</f>
         <v>Platform Engineering</v>
       </c>
@@ -22930,8 +24204,122 @@
         <v>6</v>
       </c>
     </row>
+    <row r="54" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="59" t="str">
+        <f>$A$152</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B54" s="59">
+        <f>(B53/B52)*100</f>
+        <v>100</v>
+      </c>
+      <c r="C54" s="59">
+        <f t="shared" ref="C54:P54" si="0">(C53/C52)*100</f>
+        <v>100</v>
+      </c>
+      <c r="D54" s="59">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E54" s="59">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F54" s="59">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="G54" s="59">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H54" s="59">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="I54" s="59">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="J54" s="59">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="K54" s="59">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="L54" s="59">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="M54" s="59">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="N54" s="59">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="O54" s="59">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="P54" s="59">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B55" s="60" t="str">
+        <f>B$155</f>
+        <v>Q1</v>
+      </c>
+      <c r="C55" s="60" t="str">
+        <f t="shared" ref="C55:F55" si="1">C$155</f>
+        <v>Q2</v>
+      </c>
+      <c r="D55" s="60" t="str">
+        <f t="shared" si="1"/>
+        <v>Q3</v>
+      </c>
+      <c r="E55" s="60" t="str">
+        <f t="shared" si="1"/>
+        <v>Q4</v>
+      </c>
+      <c r="F55" s="60" t="str">
+        <f t="shared" si="1"/>
+        <v>Q1'27</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="60" t="str">
+        <f>$A$156</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B56" s="60">
+        <f>(AVERAGE(B53:D53)/AVERAGE(B52:D52))*100</f>
+        <v>100</v>
+      </c>
+      <c r="C56" s="60">
+        <f>(AVERAGE(E53:G53)/AVERAGE(E52:G52))*100</f>
+        <v>100</v>
+      </c>
+      <c r="D56" s="60">
+        <f>(AVERAGE(H53:J53)/AVERAGE(H52:J52))*100</f>
+        <v>100</v>
+      </c>
+      <c r="E56" s="60">
+        <f>(AVERAGE(K53:M53)/AVERAGE(K52:M52))*100</f>
+        <v>100</v>
+      </c>
+      <c r="F56" s="60">
+        <f>(AVERAGE(N53:P53)/AVERAGE(N52:P52))*100</f>
+        <v>100</v>
+      </c>
+    </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A61" t="str">
+      <c r="A61" s="58" t="str">
         <f>PSE!A72</f>
         <v>Software Engineering</v>
       </c>
@@ -23128,6 +24516,120 @@
         <v>24.65</v>
       </c>
     </row>
+    <row r="64" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="59" t="str">
+        <f>$A$152</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B64" s="59">
+        <f>(B63/B62)*100</f>
+        <v>88.205128205128204</v>
+      </c>
+      <c r="C64" s="59">
+        <f t="shared" ref="C64:P64" si="2">(C63/C62)*100</f>
+        <v>93.230769230769226</v>
+      </c>
+      <c r="D64" s="59">
+        <f t="shared" si="2"/>
+        <v>98.641025641025635</v>
+      </c>
+      <c r="E64" s="59">
+        <f t="shared" si="2"/>
+        <v>93.731707317073159</v>
+      </c>
+      <c r="F64" s="59">
+        <f t="shared" si="2"/>
+        <v>97.024390243902431</v>
+      </c>
+      <c r="G64" s="59">
+        <f t="shared" si="2"/>
+        <v>90.024390243902431</v>
+      </c>
+      <c r="H64" s="59">
+        <f t="shared" si="2"/>
+        <v>92.951219512195109</v>
+      </c>
+      <c r="I64" s="59">
+        <f t="shared" si="2"/>
+        <v>91.609756097560975</v>
+      </c>
+      <c r="J64" s="59">
+        <f t="shared" si="2"/>
+        <v>92.829268292682926</v>
+      </c>
+      <c r="K64" s="59">
+        <f t="shared" si="2"/>
+        <v>84.609756097560975</v>
+      </c>
+      <c r="L64" s="59">
+        <f t="shared" si="2"/>
+        <v>82.926829268292678</v>
+      </c>
+      <c r="M64" s="59">
+        <f t="shared" si="2"/>
+        <v>82.926829268292678</v>
+      </c>
+      <c r="N64" s="59">
+        <f t="shared" si="2"/>
+        <v>60.121951219512191</v>
+      </c>
+      <c r="O64" s="59">
+        <f t="shared" si="2"/>
+        <v>60.121951219512191</v>
+      </c>
+      <c r="P64" s="59">
+        <f t="shared" si="2"/>
+        <v>60.121951219512191</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B65" s="60" t="str">
+        <f>B$155</f>
+        <v>Q1</v>
+      </c>
+      <c r="C65" s="60" t="str">
+        <f t="shared" ref="C65:F65" si="3">C$155</f>
+        <v>Q2</v>
+      </c>
+      <c r="D65" s="60" t="str">
+        <f t="shared" si="3"/>
+        <v>Q3</v>
+      </c>
+      <c r="E65" s="60" t="str">
+        <f t="shared" si="3"/>
+        <v>Q4</v>
+      </c>
+      <c r="F65" s="60" t="str">
+        <f t="shared" si="3"/>
+        <v>Q1'27</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="60" t="str">
+        <f>$A$156</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B66" s="60">
+        <f>(AVERAGE(B63:D63)/AVERAGE(B62:D62))*100</f>
+        <v>93.358974358974351</v>
+      </c>
+      <c r="C66" s="60">
+        <f>(AVERAGE(E63:G63)/AVERAGE(E62:G62))*100</f>
+        <v>93.593495934959364</v>
+      </c>
+      <c r="D66" s="60">
+        <f>(AVERAGE(H63:J63)/AVERAGE(H62:J62))*100</f>
+        <v>92.463414634146346</v>
+      </c>
+      <c r="E66" s="60">
+        <f>(AVERAGE(K63:M63)/AVERAGE(K62:M62))*100</f>
+        <v>83.487804878048777</v>
+      </c>
+      <c r="F66" s="60">
+        <f>(AVERAGE(N63:P63)/AVERAGE(N62:P62))*100</f>
+        <v>60.121951219512184</v>
+      </c>
+    </row>
     <row r="151" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B151" t="str">
         <f>PSE!C1</f>
@@ -23322,76 +24824,76 @@
         <v>16</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B161" t="str">
+    <row r="155" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B155" t="str">
         <f>PSE!C31</f>
         <v>Q1</v>
       </c>
-      <c r="C161" t="str">
+      <c r="C155" t="str">
         <f>PSE!D31</f>
         <v>Q2</v>
       </c>
-      <c r="D161" t="str">
+      <c r="D155" t="str">
         <f>PSE!E31</f>
         <v>Q3</v>
       </c>
-      <c r="E161" t="str">
+      <c r="E155" t="str">
         <f>PSE!F31</f>
         <v>Q4</v>
       </c>
-      <c r="F161" t="str">
+      <c r="F155" t="str">
         <f>PSE!G31</f>
         <v>Q1'27</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A162" t="str">
+    <row r="156" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A156" t="str">
         <f>PSE!B6</f>
         <v>% Plan</v>
       </c>
-      <c r="B162">
+      <c r="B156">
         <f>PSE!C36*100</f>
         <v>94.24</v>
       </c>
-      <c r="C162">
+      <c r="C156">
         <f>PSE!D36*100</f>
         <v>94.53</v>
       </c>
-      <c r="D162">
+      <c r="D156">
         <f>PSE!E36*100</f>
         <v>93.56</v>
       </c>
-      <c r="E162">
+      <c r="E156">
         <f>PSE!F36*100</f>
         <v>85.9</v>
       </c>
-      <c r="F162">
+      <c r="F156">
         <f>PSE!G36*100</f>
         <v>78.92</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A163" t="str">
+    <row r="157" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A157" t="str">
         <f>PSE!B7</f>
         <v>Available FTE</v>
       </c>
-      <c r="B163">
+      <c r="B157">
         <f>PSE!C37</f>
         <v>3</v>
       </c>
-      <c r="C163">
+      <c r="C157">
         <f>PSE!D37</f>
         <v>3</v>
       </c>
-      <c r="D163">
+      <c r="D157">
         <f>PSE!E37</f>
         <v>3</v>
       </c>
-      <c r="E163">
+      <c r="E157">
         <f>PSE!F37</f>
         <v>7</v>
       </c>
-      <c r="F163">
+      <c r="F157">
         <f>PSE!G37</f>
         <v>10</v>
       </c>
@@ -26412,10 +27914,10 @@
   <sheetPr>
     <tabColor theme="8" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:P163"/>
+  <dimension ref="A1:P157"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
@@ -27835,7 +29337,7 @@
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A51" t="str">
+      <c r="A51" s="58" t="str">
         <f>SD!A66</f>
         <v>Design</v>
       </c>
@@ -28032,8 +29534,122 @@
         <v>1.03125</v>
       </c>
     </row>
+    <row r="54" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="59" t="str">
+        <f>$A$152</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B54" s="59">
+        <f>(B53/B52)*100</f>
+        <v>76.5625</v>
+      </c>
+      <c r="C54" s="59">
+        <f t="shared" ref="C54:P54" si="0">(C53/C52)*100</f>
+        <v>96.25</v>
+      </c>
+      <c r="D54" s="59">
+        <f t="shared" si="0"/>
+        <v>91.25</v>
+      </c>
+      <c r="E54" s="59">
+        <f t="shared" si="0"/>
+        <v>82.5</v>
+      </c>
+      <c r="F54" s="59">
+        <f t="shared" si="0"/>
+        <v>100.62500000000001</v>
+      </c>
+      <c r="G54" s="59">
+        <f t="shared" si="0"/>
+        <v>100.62500000000001</v>
+      </c>
+      <c r="H54" s="59">
+        <f t="shared" si="0"/>
+        <v>99.53125</v>
+      </c>
+      <c r="I54" s="59">
+        <f t="shared" si="0"/>
+        <v>82.34375</v>
+      </c>
+      <c r="J54" s="59">
+        <f t="shared" si="0"/>
+        <v>73.28125</v>
+      </c>
+      <c r="K54" s="59">
+        <f t="shared" si="0"/>
+        <v>67.8125</v>
+      </c>
+      <c r="L54" s="59">
+        <f t="shared" si="0"/>
+        <v>64.6875</v>
+      </c>
+      <c r="M54" s="59">
+        <f t="shared" si="0"/>
+        <v>59.687500000000007</v>
+      </c>
+      <c r="N54" s="59">
+        <f t="shared" si="0"/>
+        <v>32.03125</v>
+      </c>
+      <c r="O54" s="59">
+        <f t="shared" si="0"/>
+        <v>25.78125</v>
+      </c>
+      <c r="P54" s="59">
+        <f t="shared" si="0"/>
+        <v>25.78125</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B55" s="60" t="str">
+        <f>B$155</f>
+        <v>Q1</v>
+      </c>
+      <c r="C55" s="60" t="str">
+        <f t="shared" ref="C55:F55" si="1">C$155</f>
+        <v>Q2</v>
+      </c>
+      <c r="D55" s="60" t="str">
+        <f t="shared" si="1"/>
+        <v>Q3</v>
+      </c>
+      <c r="E55" s="60" t="str">
+        <f t="shared" si="1"/>
+        <v>Q4</v>
+      </c>
+      <c r="F55" s="60" t="str">
+        <f t="shared" si="1"/>
+        <v>Q1'27</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="60" t="str">
+        <f>$A$156</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B56" s="60">
+        <f>(AVERAGE(B53:D53)/AVERAGE(B52:D52))*100</f>
+        <v>88.020833333333343</v>
+      </c>
+      <c r="C56" s="60">
+        <f>(AVERAGE(E53:G53)/AVERAGE(E52:G52))*100</f>
+        <v>94.583333333333343</v>
+      </c>
+      <c r="D56" s="60">
+        <f>(AVERAGE(H53:J53)/AVERAGE(H52:J52))*100</f>
+        <v>85.052083333333343</v>
+      </c>
+      <c r="E56" s="60">
+        <f>(AVERAGE(K53:M53)/AVERAGE(K52:M52))*100</f>
+        <v>64.0625</v>
+      </c>
+      <c r="F56" s="60">
+        <f>(AVERAGE(N53:P53)/AVERAGE(N52:P52))*100</f>
+        <v>27.864583333333332</v>
+      </c>
+    </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A61" t="str">
+      <c r="A61" s="58" t="str">
         <f>SD!A68</f>
         <v>Data Technology</v>
       </c>
@@ -28230,8 +29846,122 @@
         <v>4.3150000000000004</v>
       </c>
     </row>
+    <row r="64" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="59" t="str">
+        <f>$A$152</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B64" s="59">
+        <f>(B63/B62)*100</f>
+        <v>101.07142857142857</v>
+      </c>
+      <c r="C64" s="59">
+        <f t="shared" ref="C64:P64" si="2">(C63/C62)*100</f>
+        <v>103.21428571428571</v>
+      </c>
+      <c r="D64" s="59">
+        <f t="shared" si="2"/>
+        <v>98.071428571428569</v>
+      </c>
+      <c r="E64" s="59">
+        <f t="shared" si="2"/>
+        <v>87.428571428571431</v>
+      </c>
+      <c r="F64" s="59">
+        <f t="shared" si="2"/>
+        <v>81.535714285714278</v>
+      </c>
+      <c r="G64" s="59">
+        <f t="shared" si="2"/>
+        <v>91.607142857142847</v>
+      </c>
+      <c r="H64" s="59">
+        <f t="shared" si="2"/>
+        <v>83.75</v>
+      </c>
+      <c r="I64" s="59">
+        <f t="shared" si="2"/>
+        <v>80.464285714285722</v>
+      </c>
+      <c r="J64" s="59">
+        <f t="shared" si="2"/>
+        <v>80.464285714285722</v>
+      </c>
+      <c r="K64" s="59">
+        <f t="shared" si="2"/>
+        <v>75.642857142857139</v>
+      </c>
+      <c r="L64" s="59">
+        <f t="shared" si="2"/>
+        <v>73.5</v>
+      </c>
+      <c r="M64" s="59">
+        <f t="shared" si="2"/>
+        <v>73.5</v>
+      </c>
+      <c r="N64" s="59">
+        <f t="shared" si="2"/>
+        <v>61.642857142857146</v>
+      </c>
+      <c r="O64" s="59">
+        <f t="shared" si="2"/>
+        <v>61.642857142857146</v>
+      </c>
+      <c r="P64" s="59">
+        <f t="shared" si="2"/>
+        <v>61.642857142857146</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B65" s="60" t="str">
+        <f>B$155</f>
+        <v>Q1</v>
+      </c>
+      <c r="C65" s="60" t="str">
+        <f t="shared" ref="C65:F65" si="3">C$155</f>
+        <v>Q2</v>
+      </c>
+      <c r="D65" s="60" t="str">
+        <f t="shared" si="3"/>
+        <v>Q3</v>
+      </c>
+      <c r="E65" s="60" t="str">
+        <f t="shared" si="3"/>
+        <v>Q4</v>
+      </c>
+      <c r="F65" s="60" t="str">
+        <f t="shared" si="3"/>
+        <v>Q1'27</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="60" t="str">
+        <f>$A$156</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B66" s="60">
+        <f>(AVERAGE(B63:D63)/AVERAGE(B62:D62))*100</f>
+        <v>100.78571428571428</v>
+      </c>
+      <c r="C66" s="60">
+        <f>(AVERAGE(E63:G63)/AVERAGE(E62:G62))*100</f>
+        <v>86.857142857142861</v>
+      </c>
+      <c r="D66" s="60">
+        <f>(AVERAGE(H63:J63)/AVERAGE(H62:J62))*100</f>
+        <v>81.55952380952381</v>
+      </c>
+      <c r="E66" s="60">
+        <f>(AVERAGE(K63:M63)/AVERAGE(K62:M62))*100</f>
+        <v>74.214285714285708</v>
+      </c>
+      <c r="F66" s="60">
+        <f>(AVERAGE(N63:P63)/AVERAGE(N62:P62))*100</f>
+        <v>61.642857142857146</v>
+      </c>
+    </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A71" t="str">
+      <c r="A71" s="58" t="str">
         <f>SD!A74</f>
         <v>Solution Architecture</v>
       </c>
@@ -28428,8 +30158,122 @@
         <v>2.78</v>
       </c>
     </row>
+    <row r="74" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="59" t="str">
+        <f>$A$152</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B74" s="59">
+        <f>(B73/B72)*100</f>
+        <v>82.5</v>
+      </c>
+      <c r="C74" s="59">
+        <f t="shared" ref="C74:P74" si="4">(C73/C72)*100</f>
+        <v>109.375</v>
+      </c>
+      <c r="D74" s="59">
+        <f t="shared" si="4"/>
+        <v>108.125</v>
+      </c>
+      <c r="E74" s="59">
+        <f t="shared" si="4"/>
+        <v>97.5</v>
+      </c>
+      <c r="F74" s="59">
+        <f t="shared" si="4"/>
+        <v>87.875</v>
+      </c>
+      <c r="G74" s="59">
+        <f t="shared" si="4"/>
+        <v>86.625</v>
+      </c>
+      <c r="H74" s="59">
+        <f t="shared" si="4"/>
+        <v>84.125</v>
+      </c>
+      <c r="I74" s="59">
+        <f t="shared" si="4"/>
+        <v>86</v>
+      </c>
+      <c r="J74" s="59">
+        <f t="shared" si="4"/>
+        <v>78</v>
+      </c>
+      <c r="K74" s="59">
+        <f t="shared" si="4"/>
+        <v>78</v>
+      </c>
+      <c r="L74" s="59">
+        <f t="shared" si="4"/>
+        <v>78</v>
+      </c>
+      <c r="M74" s="59">
+        <f t="shared" si="4"/>
+        <v>76.125</v>
+      </c>
+      <c r="N74" s="59">
+        <f t="shared" si="4"/>
+        <v>69.5</v>
+      </c>
+      <c r="O74" s="59">
+        <f t="shared" si="4"/>
+        <v>69.5</v>
+      </c>
+      <c r="P74" s="59">
+        <f t="shared" si="4"/>
+        <v>69.5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B75" s="60" t="str">
+        <f>B$155</f>
+        <v>Q1</v>
+      </c>
+      <c r="C75" s="60" t="str">
+        <f t="shared" ref="C75:F75" si="5">C$155</f>
+        <v>Q2</v>
+      </c>
+      <c r="D75" s="60" t="str">
+        <f t="shared" si="5"/>
+        <v>Q3</v>
+      </c>
+      <c r="E75" s="60" t="str">
+        <f t="shared" si="5"/>
+        <v>Q4</v>
+      </c>
+      <c r="F75" s="60" t="str">
+        <f t="shared" si="5"/>
+        <v>Q1'27</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="60" t="str">
+        <f>$A$156</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B76" s="60">
+        <f>(AVERAGE(B73:D73)/AVERAGE(B72:D72))*100</f>
+        <v>100</v>
+      </c>
+      <c r="C76" s="60">
+        <f>(AVERAGE(E73:G73)/AVERAGE(E72:G72))*100</f>
+        <v>90.666666666666657</v>
+      </c>
+      <c r="D76" s="60">
+        <f>(AVERAGE(H73:J73)/AVERAGE(H72:J72))*100</f>
+        <v>82.708333333333343</v>
+      </c>
+      <c r="E76" s="60">
+        <f>(AVERAGE(K73:M73)/AVERAGE(K72:M72))*100</f>
+        <v>77.375</v>
+      </c>
+      <c r="F76" s="60">
+        <f>(AVERAGE(N73:P73)/AVERAGE(N72:P72))*100</f>
+        <v>69.5</v>
+      </c>
+    </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A81" t="str">
+      <c r="A81" s="58" t="str">
         <f>SD!A76</f>
         <v>Site Reliability Engineering</v>
       </c>
@@ -28626,8 +30470,122 @@
         <v>1.4550000000000001</v>
       </c>
     </row>
+    <row r="84" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="59" t="str">
+        <f>$A$152</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B84" s="59">
+        <f>(B83/B82)*100</f>
+        <v>169.25</v>
+      </c>
+      <c r="C84" s="59">
+        <f t="shared" ref="C84:P84" si="6">(C83/C82)*100</f>
+        <v>153.75</v>
+      </c>
+      <c r="D84" s="59">
+        <f t="shared" si="6"/>
+        <v>211</v>
+      </c>
+      <c r="E84" s="59">
+        <f t="shared" si="6"/>
+        <v>132.75</v>
+      </c>
+      <c r="F84" s="59">
+        <f t="shared" si="6"/>
+        <v>134.25</v>
+      </c>
+      <c r="G84" s="59">
+        <f t="shared" si="6"/>
+        <v>123.25</v>
+      </c>
+      <c r="H84" s="59">
+        <f t="shared" si="6"/>
+        <v>115.75</v>
+      </c>
+      <c r="I84" s="59">
+        <f t="shared" si="6"/>
+        <v>113.25</v>
+      </c>
+      <c r="J84" s="59">
+        <f t="shared" si="6"/>
+        <v>105.75000000000001</v>
+      </c>
+      <c r="K84" s="59">
+        <f t="shared" si="6"/>
+        <v>113.25</v>
+      </c>
+      <c r="L84" s="59">
+        <f t="shared" si="6"/>
+        <v>103.25</v>
+      </c>
+      <c r="M84" s="59">
+        <f t="shared" si="6"/>
+        <v>103.25</v>
+      </c>
+      <c r="N84" s="59">
+        <f t="shared" si="6"/>
+        <v>75.25</v>
+      </c>
+      <c r="O84" s="59">
+        <f t="shared" si="6"/>
+        <v>72.75</v>
+      </c>
+      <c r="P84" s="59">
+        <f t="shared" si="6"/>
+        <v>72.75</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B85" s="60" t="str">
+        <f>B$155</f>
+        <v>Q1</v>
+      </c>
+      <c r="C85" s="60" t="str">
+        <f t="shared" ref="C85:F85" si="7">C$155</f>
+        <v>Q2</v>
+      </c>
+      <c r="D85" s="60" t="str">
+        <f t="shared" si="7"/>
+        <v>Q3</v>
+      </c>
+      <c r="E85" s="60" t="str">
+        <f t="shared" si="7"/>
+        <v>Q4</v>
+      </c>
+      <c r="F85" s="60" t="str">
+        <f t="shared" si="7"/>
+        <v>Q1'27</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="60" t="str">
+        <f>$A$156</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B86" s="60">
+        <f>(AVERAGE(B83:D83)/AVERAGE(B82:D82))*100</f>
+        <v>178</v>
+      </c>
+      <c r="C86" s="60">
+        <f>(AVERAGE(E83:G83)/AVERAGE(E82:G82))*100</f>
+        <v>130.08333333333331</v>
+      </c>
+      <c r="D86" s="60">
+        <f>(AVERAGE(H83:J83)/AVERAGE(H82:J82))*100</f>
+        <v>111.58333333333334</v>
+      </c>
+      <c r="E86" s="60">
+        <f>(AVERAGE(K83:M83)/AVERAGE(K82:M82))*100</f>
+        <v>106.58333333333331</v>
+      </c>
+      <c r="F86" s="60">
+        <f>(AVERAGE(N83:P83)/AVERAGE(N82:P82))*100</f>
+        <v>73.583333333333329</v>
+      </c>
+    </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A91" t="str">
+      <c r="A91" s="58" t="str">
         <f>SD!A78</f>
         <v>Cyber Security</v>
       </c>
@@ -28824,8 +30782,122 @@
         <v>2.5</v>
       </c>
     </row>
+    <row r="94" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="59" t="str">
+        <f>$A$152</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B94" s="59">
+        <f>(B93/B92)*100</f>
+        <v>109.16666666666666</v>
+      </c>
+      <c r="C94" s="59">
+        <f t="shared" ref="C94:P94" si="8">(C93/C92)*100</f>
+        <v>109.16666666666666</v>
+      </c>
+      <c r="D94" s="59">
+        <f t="shared" si="8"/>
+        <v>107.5</v>
+      </c>
+      <c r="E94" s="59">
+        <f t="shared" si="8"/>
+        <v>95.833333333333343</v>
+      </c>
+      <c r="F94" s="59">
+        <f t="shared" si="8"/>
+        <v>103.74999999999999</v>
+      </c>
+      <c r="G94" s="59">
+        <f t="shared" si="8"/>
+        <v>95.416666666666657</v>
+      </c>
+      <c r="H94" s="59">
+        <f t="shared" si="8"/>
+        <v>86.666666666666671</v>
+      </c>
+      <c r="I94" s="59">
+        <f t="shared" si="8"/>
+        <v>86.666666666666671</v>
+      </c>
+      <c r="J94" s="59">
+        <f t="shared" si="8"/>
+        <v>86.666666666666671</v>
+      </c>
+      <c r="K94" s="59">
+        <f t="shared" si="8"/>
+        <v>86.666666666666671</v>
+      </c>
+      <c r="L94" s="59">
+        <f t="shared" si="8"/>
+        <v>86.666666666666671</v>
+      </c>
+      <c r="M94" s="59">
+        <f t="shared" si="8"/>
+        <v>86.666666666666671</v>
+      </c>
+      <c r="N94" s="59">
+        <f t="shared" si="8"/>
+        <v>83.333333333333343</v>
+      </c>
+      <c r="O94" s="59">
+        <f t="shared" si="8"/>
+        <v>83.333333333333343</v>
+      </c>
+      <c r="P94" s="59">
+        <f t="shared" si="8"/>
+        <v>83.333333333333343</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B95" s="60" t="str">
+        <f>B$155</f>
+        <v>Q1</v>
+      </c>
+      <c r="C95" s="60" t="str">
+        <f t="shared" ref="C95:F95" si="9">C$155</f>
+        <v>Q2</v>
+      </c>
+      <c r="D95" s="60" t="str">
+        <f t="shared" si="9"/>
+        <v>Q3</v>
+      </c>
+      <c r="E95" s="60" t="str">
+        <f t="shared" si="9"/>
+        <v>Q4</v>
+      </c>
+      <c r="F95" s="60" t="str">
+        <f t="shared" si="9"/>
+        <v>Q1'27</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="60" t="str">
+        <f>$A$156</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B96" s="60">
+        <f>(AVERAGE(B93:D93)/AVERAGE(B92:D92))*100</f>
+        <v>108.6111111111111</v>
+      </c>
+      <c r="C96" s="60">
+        <f>(AVERAGE(E93:G93)/AVERAGE(E92:G92))*100</f>
+        <v>98.333333333333329</v>
+      </c>
+      <c r="D96" s="60">
+        <f>(AVERAGE(H93:J93)/AVERAGE(H92:J92))*100</f>
+        <v>86.666666666666671</v>
+      </c>
+      <c r="E96" s="60">
+        <f>(AVERAGE(K93:M93)/AVERAGE(K92:M92))*100</f>
+        <v>86.666666666666671</v>
+      </c>
+      <c r="F96" s="60">
+        <f>(AVERAGE(N93:P93)/AVERAGE(N92:P92))*100</f>
+        <v>83.333333333333343</v>
+      </c>
+    </row>
     <row r="101" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A101" t="str">
+      <c r="A101" s="58" t="str">
         <f>SD!A80</f>
         <v>Project Management</v>
       </c>
@@ -29022,8 +31094,122 @@
         <v>1</v>
       </c>
     </row>
+    <row r="104" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="59" t="str">
+        <f>$A$152</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B104" s="59">
+        <f>(B103/B102)*100</f>
+        <v>91.25</v>
+      </c>
+      <c r="C104" s="59">
+        <f t="shared" ref="C104:P104" si="10">(C103/C102)*100</f>
+        <v>93.75</v>
+      </c>
+      <c r="D104" s="59">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+      <c r="E104" s="59">
+        <f t="shared" si="10"/>
+        <v>96.25</v>
+      </c>
+      <c r="F104" s="59">
+        <f t="shared" si="10"/>
+        <v>104</v>
+      </c>
+      <c r="G104" s="59">
+        <f t="shared" si="10"/>
+        <v>101.49999999999999</v>
+      </c>
+      <c r="H104" s="59">
+        <f t="shared" si="10"/>
+        <v>106.87500000000001</v>
+      </c>
+      <c r="I104" s="59">
+        <f t="shared" si="10"/>
+        <v>103.8</v>
+      </c>
+      <c r="J104" s="59">
+        <f t="shared" si="10"/>
+        <v>98.174999999999997</v>
+      </c>
+      <c r="K104" s="59">
+        <f t="shared" si="10"/>
+        <v>93.174999999999997</v>
+      </c>
+      <c r="L104" s="59">
+        <f t="shared" si="10"/>
+        <v>87.125</v>
+      </c>
+      <c r="M104" s="59">
+        <f t="shared" si="10"/>
+        <v>67.75</v>
+      </c>
+      <c r="N104" s="59">
+        <f t="shared" si="10"/>
+        <v>25</v>
+      </c>
+      <c r="O104" s="59">
+        <f t="shared" si="10"/>
+        <v>25</v>
+      </c>
+      <c r="P104" s="59">
+        <f t="shared" si="10"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B105" s="60" t="str">
+        <f>B$155</f>
+        <v>Q1</v>
+      </c>
+      <c r="C105" s="60" t="str">
+        <f t="shared" ref="C105:F105" si="11">C$155</f>
+        <v>Q2</v>
+      </c>
+      <c r="D105" s="60" t="str">
+        <f t="shared" si="11"/>
+        <v>Q3</v>
+      </c>
+      <c r="E105" s="60" t="str">
+        <f t="shared" si="11"/>
+        <v>Q4</v>
+      </c>
+      <c r="F105" s="60" t="str">
+        <f t="shared" si="11"/>
+        <v>Q1'27</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A106" s="60" t="str">
+        <f>$A$156</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B106" s="60">
+        <f>(AVERAGE(B103:D103)/AVERAGE(B102:D102))*100</f>
+        <v>95</v>
+      </c>
+      <c r="C106" s="60">
+        <f>(AVERAGE(E103:G103)/AVERAGE(E102:G102))*100</f>
+        <v>100.58333333333334</v>
+      </c>
+      <c r="D106" s="60">
+        <f>(AVERAGE(H103:J103)/AVERAGE(H102:J102))*100</f>
+        <v>102.94999999999999</v>
+      </c>
+      <c r="E106" s="60">
+        <f>(AVERAGE(K103:M103)/AVERAGE(K102:M102))*100</f>
+        <v>82.683333333333337</v>
+      </c>
+      <c r="F106" s="60">
+        <f>(AVERAGE(N103:P103)/AVERAGE(N102:P102))*100</f>
+        <v>25</v>
+      </c>
+    </row>
     <row r="111" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A111" t="str">
+      <c r="A111" s="58" t="str">
         <f>SD!A82</f>
         <v>Technology Analyst</v>
       </c>
@@ -29220,8 +31406,122 @@
         <v>3.22</v>
       </c>
     </row>
+    <row r="114" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A114" s="59" t="str">
+        <f>$A$152</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B114" s="59">
+        <f>(B113/B112)*100</f>
+        <v>94</v>
+      </c>
+      <c r="C114" s="59">
+        <f t="shared" ref="C114:P114" si="12">(C113/C112)*100</f>
+        <v>101</v>
+      </c>
+      <c r="D114" s="59">
+        <f t="shared" si="12"/>
+        <v>101</v>
+      </c>
+      <c r="E114" s="59">
+        <f t="shared" si="12"/>
+        <v>105.60000000000001</v>
+      </c>
+      <c r="F114" s="59">
+        <f t="shared" si="12"/>
+        <v>119.8</v>
+      </c>
+      <c r="G114" s="59">
+        <f t="shared" si="12"/>
+        <v>109.80000000000001</v>
+      </c>
+      <c r="H114" s="59">
+        <f t="shared" si="12"/>
+        <v>103</v>
+      </c>
+      <c r="I114" s="59">
+        <f t="shared" si="12"/>
+        <v>94</v>
+      </c>
+      <c r="J114" s="59">
+        <f t="shared" si="12"/>
+        <v>90</v>
+      </c>
+      <c r="K114" s="59">
+        <f t="shared" si="12"/>
+        <v>90</v>
+      </c>
+      <c r="L114" s="59">
+        <f t="shared" si="12"/>
+        <v>90</v>
+      </c>
+      <c r="M114" s="59">
+        <f t="shared" si="12"/>
+        <v>90</v>
+      </c>
+      <c r="N114" s="59">
+        <f t="shared" si="12"/>
+        <v>64.400000000000006</v>
+      </c>
+      <c r="O114" s="59">
+        <f t="shared" si="12"/>
+        <v>64.400000000000006</v>
+      </c>
+      <c r="P114" s="59">
+        <f t="shared" si="12"/>
+        <v>64.400000000000006</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B115" s="60" t="str">
+        <f>B$155</f>
+        <v>Q1</v>
+      </c>
+      <c r="C115" s="60" t="str">
+        <f t="shared" ref="C115:F115" si="13">C$155</f>
+        <v>Q2</v>
+      </c>
+      <c r="D115" s="60" t="str">
+        <f t="shared" si="13"/>
+        <v>Q3</v>
+      </c>
+      <c r="E115" s="60" t="str">
+        <f t="shared" si="13"/>
+        <v>Q4</v>
+      </c>
+      <c r="F115" s="60" t="str">
+        <f t="shared" si="13"/>
+        <v>Q1'27</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A116" s="60" t="str">
+        <f>$A$156</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B116" s="60">
+        <f>(AVERAGE(B113:D113)/AVERAGE(B112:D112))*100</f>
+        <v>98.666666666666671</v>
+      </c>
+      <c r="C116" s="60">
+        <f>(AVERAGE(E113:G113)/AVERAGE(E112:G112))*100</f>
+        <v>111.73333333333333</v>
+      </c>
+      <c r="D116" s="60">
+        <f>(AVERAGE(H113:J113)/AVERAGE(H112:J112))*100</f>
+        <v>95.666666666666671</v>
+      </c>
+      <c r="E116" s="60">
+        <f>(AVERAGE(K113:M113)/AVERAGE(K112:M112))*100</f>
+        <v>90</v>
+      </c>
+      <c r="F116" s="60">
+        <f>(AVERAGE(N113:P113)/AVERAGE(N112:P112))*100</f>
+        <v>64.400000000000006</v>
+      </c>
+    </row>
     <row r="121" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A121" t="str">
+      <c r="A121" s="58" t="str">
         <f>SD!A84</f>
         <v>Technology QA</v>
       </c>
@@ -29418,8 +31718,122 @@
         <v>9.6</v>
       </c>
     </row>
+    <row r="124" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A124" s="59" t="str">
+        <f>$A$152</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B124" s="59">
+        <f>(B123/B122)*100</f>
+        <v>88.1111111111111</v>
+      </c>
+      <c r="C124" s="59">
+        <f t="shared" ref="C124:P124" si="14">(C123/C122)*100</f>
+        <v>102.72727272727273</v>
+      </c>
+      <c r="D124" s="59">
+        <f t="shared" si="14"/>
+        <v>104.25</v>
+      </c>
+      <c r="E124" s="59">
+        <f t="shared" si="14"/>
+        <v>97.375</v>
+      </c>
+      <c r="F124" s="59">
+        <f t="shared" si="14"/>
+        <v>107.83333333333334</v>
+      </c>
+      <c r="G124" s="59">
+        <f t="shared" si="14"/>
+        <v>112.16666666666669</v>
+      </c>
+      <c r="H124" s="59">
+        <f t="shared" si="14"/>
+        <v>128.33333333333334</v>
+      </c>
+      <c r="I124" s="59">
+        <f t="shared" si="14"/>
+        <v>127.08333333333333</v>
+      </c>
+      <c r="J124" s="59">
+        <f t="shared" si="14"/>
+        <v>131.25</v>
+      </c>
+      <c r="K124" s="59">
+        <f t="shared" si="14"/>
+        <v>112.08333333333333</v>
+      </c>
+      <c r="L124" s="59">
+        <f t="shared" si="14"/>
+        <v>109.99999999999999</v>
+      </c>
+      <c r="M124" s="59">
+        <f t="shared" si="14"/>
+        <v>107.08333333333333</v>
+      </c>
+      <c r="N124" s="59">
+        <f t="shared" si="14"/>
+        <v>80</v>
+      </c>
+      <c r="O124" s="59">
+        <f t="shared" si="14"/>
+        <v>80</v>
+      </c>
+      <c r="P124" s="59">
+        <f t="shared" si="14"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B125" s="60" t="str">
+        <f>B$155</f>
+        <v>Q1</v>
+      </c>
+      <c r="C125" s="60" t="str">
+        <f t="shared" ref="C125:F125" si="15">C$155</f>
+        <v>Q2</v>
+      </c>
+      <c r="D125" s="60" t="str">
+        <f t="shared" si="15"/>
+        <v>Q3</v>
+      </c>
+      <c r="E125" s="60" t="str">
+        <f t="shared" si="15"/>
+        <v>Q4</v>
+      </c>
+      <c r="F125" s="60" t="str">
+        <f t="shared" si="15"/>
+        <v>Q1'27</v>
+      </c>
+    </row>
+    <row r="126" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A126" s="60" t="str">
+        <f>$A$156</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B126" s="60">
+        <f>(AVERAGE(B123:D123)/AVERAGE(B122:D122))*100</f>
+        <v>99.1875</v>
+      </c>
+      <c r="C126" s="60">
+        <f>(AVERAGE(E123:G123)/AVERAGE(E122:G122))*100</f>
+        <v>105.79166666666666</v>
+      </c>
+      <c r="D126" s="60">
+        <f>(AVERAGE(H123:J123)/AVERAGE(H122:J122))*100</f>
+        <v>128.88888888888889</v>
+      </c>
+      <c r="E126" s="60">
+        <f>(AVERAGE(K123:M123)/AVERAGE(K122:M122))*100</f>
+        <v>109.72222222222221</v>
+      </c>
+      <c r="F126" s="60">
+        <f>(AVERAGE(N123:P123)/AVERAGE(N122:P122))*100</f>
+        <v>80</v>
+      </c>
+    </row>
     <row r="131" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A131" t="str">
+      <c r="A131" s="58" t="str">
         <f>SD!A92</f>
         <v>Technology Management</v>
       </c>
@@ -29616,6 +32030,120 @@
         <v>5.2</v>
       </c>
     </row>
+    <row r="134" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A134" s="59" t="str">
+        <f>$A$152</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B134" s="59">
+        <f>(B133/B132)*100</f>
+        <v>77</v>
+      </c>
+      <c r="C134" s="59">
+        <f t="shared" ref="C134:P134" si="16">(C133/C132)*100</f>
+        <v>73.5</v>
+      </c>
+      <c r="D134" s="59">
+        <f t="shared" si="16"/>
+        <v>74.75</v>
+      </c>
+      <c r="E134" s="59">
+        <f t="shared" si="16"/>
+        <v>76.75</v>
+      </c>
+      <c r="F134" s="59">
+        <f t="shared" si="16"/>
+        <v>76.75</v>
+      </c>
+      <c r="G134" s="59">
+        <f t="shared" si="16"/>
+        <v>80.75</v>
+      </c>
+      <c r="H134" s="59">
+        <f t="shared" si="16"/>
+        <v>95.75</v>
+      </c>
+      <c r="I134" s="59">
+        <f t="shared" si="16"/>
+        <v>95.75</v>
+      </c>
+      <c r="J134" s="59">
+        <f t="shared" si="16"/>
+        <v>95.75</v>
+      </c>
+      <c r="K134" s="59">
+        <f t="shared" si="16"/>
+        <v>95.75</v>
+      </c>
+      <c r="L134" s="59">
+        <f t="shared" si="16"/>
+        <v>105</v>
+      </c>
+      <c r="M134" s="59">
+        <f t="shared" si="16"/>
+        <v>130</v>
+      </c>
+      <c r="N134" s="59">
+        <f t="shared" si="16"/>
+        <v>130</v>
+      </c>
+      <c r="O134" s="59">
+        <f t="shared" si="16"/>
+        <v>130</v>
+      </c>
+      <c r="P134" s="59">
+        <f t="shared" si="16"/>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="135" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B135" s="60" t="str">
+        <f>B$155</f>
+        <v>Q1</v>
+      </c>
+      <c r="C135" s="60" t="str">
+        <f t="shared" ref="C135:F135" si="17">C$155</f>
+        <v>Q2</v>
+      </c>
+      <c r="D135" s="60" t="str">
+        <f t="shared" si="17"/>
+        <v>Q3</v>
+      </c>
+      <c r="E135" s="60" t="str">
+        <f t="shared" si="17"/>
+        <v>Q4</v>
+      </c>
+      <c r="F135" s="60" t="str">
+        <f t="shared" si="17"/>
+        <v>Q1'27</v>
+      </c>
+    </row>
+    <row r="136" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A136" s="60" t="str">
+        <f>$A$156</f>
+        <v>% Plan</v>
+      </c>
+      <c r="B136" s="60">
+        <f>(AVERAGE(B133:D133)/AVERAGE(B132:D132))*100</f>
+        <v>75.083333333333329</v>
+      </c>
+      <c r="C136" s="60">
+        <f>(AVERAGE(E133:G133)/AVERAGE(E132:G132))*100</f>
+        <v>78.083333333333329</v>
+      </c>
+      <c r="D136" s="60">
+        <f>(AVERAGE(H133:J133)/AVERAGE(H132:J132))*100</f>
+        <v>95.75</v>
+      </c>
+      <c r="E136" s="60">
+        <f>(AVERAGE(K133:M133)/AVERAGE(K132:M132))*100</f>
+        <v>110.25</v>
+      </c>
+      <c r="F136" s="60">
+        <f>(AVERAGE(N133:P133)/AVERAGE(N132:P132))*100</f>
+        <v>130</v>
+      </c>
+    </row>
     <row r="151" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B151" t="str">
         <f>SD!C1</f>
@@ -29810,76 +32338,76 @@
         <v>14</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B161" t="str">
+    <row r="155" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B155" t="str">
         <f>SD!C31</f>
         <v>Q1</v>
       </c>
-      <c r="C161" t="str">
+      <c r="C155" t="str">
         <f>SD!D31</f>
         <v>Q2</v>
       </c>
-      <c r="D161" t="str">
+      <c r="D155" t="str">
         <f>SD!E31</f>
         <v>Q3</v>
       </c>
-      <c r="E161" t="str">
+      <c r="E155" t="str">
         <f>SD!F31</f>
         <v>Q4</v>
       </c>
-      <c r="F161" t="str">
+      <c r="F155" t="str">
         <f>SD!G31</f>
         <v>Q1'27</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A162" t="str">
+    <row r="156" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A156" t="str">
         <f>SD!B6</f>
         <v>% Plan</v>
       </c>
-      <c r="B162">
+      <c r="B156">
         <f>SD!C36*100</f>
         <v>100.1</v>
       </c>
-      <c r="C162">
+      <c r="C156">
         <f>SD!D36*100</f>
         <v>98.850000000000009</v>
       </c>
-      <c r="D162">
+      <c r="D156">
         <f>SD!E36*100</f>
         <v>100.98</v>
       </c>
-      <c r="E162">
+      <c r="E156">
         <f>SD!F36*100</f>
         <v>91.24</v>
       </c>
-      <c r="F162">
+      <c r="F156">
         <f>SD!G36*100</f>
         <v>83.919999999999987</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A163" t="str">
+    <row r="157" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A157" t="str">
         <f>SD!B7</f>
         <v>Available FTE</v>
       </c>
-      <c r="B163">
+      <c r="B157">
         <f>SD!C37</f>
         <v>0</v>
       </c>
-      <c r="C163">
+      <c r="C157">
         <f>SD!D37</f>
         <v>1</v>
       </c>
-      <c r="D163">
+      <c r="D157">
         <f>SD!E37</f>
         <v>0</v>
       </c>
-      <c r="E163">
+      <c r="E157">
         <f>SD!F37</f>
         <v>4</v>
       </c>
-      <c r="F163">
+      <c r="F157">
         <f>SD!G37</f>
         <v>7</v>
       </c>

--- a/workforceresult.xlsx
+++ b/workforceresult.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miintra/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78DE1ADC-4D1C-3844-B53D-F31607A4D9CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1F03ACC-3D81-C94C-B03B-FFCE323B397A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16120" activeTab="3" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16120" activeTab="13" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
   </bookViews>
   <sheets>
     <sheet name="ALL" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="129">
   <si>
     <t>Type</t>
   </si>
@@ -615,6 +615,9 @@
   <si>
     <t>WeShape</t>
   </si>
+  <si>
+    <t>FTE</t>
+  </si>
 </sst>
 </file>
 
@@ -751,7 +754,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -860,6 +863,30 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -891,7 +918,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -981,6 +1008,11 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5478,7 +5510,7 @@
         <v>60</v>
       </c>
       <c r="C94" s="59">
-        <f t="shared" ref="C94:P94" si="8">(C93/C92)*100</f>
+        <f t="shared" ref="C94:D94" si="8">(C93/C92)*100</f>
         <v>60</v>
       </c>
       <c r="D94" s="59">
@@ -11945,7 +11977,7 @@
         <v>102</v>
       </c>
       <c r="H21" s="53" t="s">
-        <v>30</v>
+        <v>128</v>
       </c>
       <c r="I21" s="54"/>
       <c r="K21" s="54"/>
@@ -12086,7 +12118,7 @@
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
-  <dimension ref="A1:T30"/>
+  <dimension ref="A1:T29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.83203125" bestFit="1" customWidth="1"/>
@@ -13732,825 +13764,216 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:20" s="58" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A21" s="58" t="str">
         <f>IF(Project!A21&gt;0,Project!A21,"")</f>
         <v>Group Name</v>
       </c>
-      <c r="B21" s="58" t="str">
+      <c r="B21" s="63" t="str">
+        <f>IF(Project!A22&gt;0,Project!A22,"")</f>
+        <v>IT Dist</v>
+      </c>
+      <c r="C21" s="64" t="str">
+        <f>IF(Project!A23&gt;0,Project!A23,"")</f>
+        <v>SCGP e-Ordering</v>
+      </c>
+      <c r="D21" s="65" t="str">
+        <f>IF(Project!A24&gt;0,Project!A24,"")</f>
+        <v>CAP (Common AI Platform)</v>
+      </c>
+      <c r="E21" s="67" t="str">
+        <f>IF(Project!A25&gt;0,Project!A25,"")</f>
+        <v>PromptPlus</v>
+      </c>
+      <c r="F21" s="66" t="str">
+        <f>IF(Project!A26&gt;0,Project!A26,"")</f>
+        <v>WeShape platform</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A22" s="58" t="str">
         <f>IF(Project!B21&gt;0,Project!B21,"")</f>
         <v>Presale</v>
       </c>
-      <c r="C21" s="58" t="str">
+      <c r="B22" s="63">
+        <f>IF(Project!B22&gt;0,Project!B22,"")</f>
+        <v>36</v>
+      </c>
+      <c r="C22" s="64">
+        <f>IF(Project!B23&gt;0,Project!B23,"")</f>
+        <v>2.7</v>
+      </c>
+      <c r="D22" s="65" t="str">
+        <f>IF(Project!B24&gt;0,Project!B24,"")</f>
+        <v/>
+      </c>
+      <c r="E22" s="67" t="str">
+        <f>IF(Project!B25&gt;0,Project!B25,"")</f>
+        <v/>
+      </c>
+      <c r="F22" s="66">
+        <f>IF(Project!B26&gt;0,Project!B26,"")</f>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A23" s="58" t="str">
         <f>IF(Project!C21&gt;0,Project!C21,"")</f>
         <v>Project</v>
       </c>
-      <c r="D21" s="58" t="str">
+      <c r="B23" s="63" t="str">
+        <f>IF(Project!C22&gt;0,Project!C22,"")</f>
+        <v/>
+      </c>
+      <c r="C23" s="64">
+        <f>IF(Project!C23&gt;0,Project!C23,"")</f>
+        <v>154.05000000000001</v>
+      </c>
+      <c r="D23" s="65">
+        <f>IF(Project!C24&gt;0,Project!C24,"")</f>
+        <v>63.6</v>
+      </c>
+      <c r="E23" s="67">
+        <f>IF(Project!C25&gt;0,Project!C25,"")</f>
+        <v>27.375</v>
+      </c>
+      <c r="F23" s="66" t="str">
+        <f>IF(Project!C26&gt;0,Project!C26,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A24" s="58" t="str">
         <f>IF(Project!D21&gt;0,Project!D21,"")</f>
         <v>TM</v>
       </c>
-      <c r="E21" s="58" t="str">
+      <c r="B24" s="63" t="str">
+        <f>IF(Project!D22&gt;0,Project!D22,"")</f>
+        <v/>
+      </c>
+      <c r="C24" s="64">
+        <f>IF(Project!D23&gt;0,Project!D23,"")</f>
+        <v>5.13</v>
+      </c>
+      <c r="D24" s="65" t="str">
+        <f>IF(Project!D24&gt;0,Project!D24,"")</f>
+        <v/>
+      </c>
+      <c r="E24" s="67" t="str">
+        <f>IF(Project!D25&gt;0,Project!D25,"")</f>
+        <v/>
+      </c>
+      <c r="F24" s="66" t="str">
+        <f>IF(Project!D26&gt;0,Project!D26,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A25" s="58" t="str">
         <f>IF(Project!E21&gt;0,Project!E21,"")</f>
         <v>Infra</v>
       </c>
-      <c r="F21" s="58" t="str">
+      <c r="B25" s="63" t="str">
+        <f>IF(Project!E22&gt;0,Project!E22,"")</f>
+        <v/>
+      </c>
+      <c r="C25" s="64">
+        <f>IF(Project!E23&gt;0,Project!E23,"")</f>
+        <v>0.9</v>
+      </c>
+      <c r="D25" s="65" t="str">
+        <f>IF(Project!E24&gt;0,Project!E24,"")</f>
+        <v/>
+      </c>
+      <c r="E25" s="67" t="str">
+        <f>IF(Project!E25&gt;0,Project!E25,"")</f>
+        <v/>
+      </c>
+      <c r="F25" s="66" t="str">
+        <f>IF(Project!E26&gt;0,Project!E26,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A26" s="58" t="str">
         <f>IF(Project!F21&gt;0,Project!F21,"")</f>
         <v>Spatial Lab</v>
       </c>
-      <c r="G21" s="58" t="str">
+      <c r="B26" s="63" t="str">
+        <f>IF(Project!F22&gt;0,Project!F22,"")</f>
+        <v/>
+      </c>
+      <c r="C26" s="64" t="str">
+        <f>IF(Project!F23&gt;0,Project!F23,"")</f>
+        <v/>
+      </c>
+      <c r="D26" s="65" t="str">
+        <f>IF(Project!F24&gt;0,Project!F24,"")</f>
+        <v/>
+      </c>
+      <c r="E26" s="67" t="str">
+        <f>IF(Project!F25&gt;0,Project!F25,"")</f>
+        <v/>
+      </c>
+      <c r="F26" s="66">
+        <f>IF(Project!F26&gt;0,Project!F26,"")</f>
+        <v>34.655000000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A27" s="58" t="str">
         <f>IF(Project!G21&gt;0,Project!G21,"")</f>
         <v>Warmbody</v>
       </c>
-      <c r="H21" s="58" t="str">
-        <f>IF(Project!H21&gt;0,Project!H21,"")</f>
-        <v>Grand Total</v>
-      </c>
-      <c r="I21" s="58" t="str">
-        <f>IF(Project!I21&gt;0,Project!I21,"")</f>
-        <v/>
-      </c>
-      <c r="J21" s="58" t="str">
-        <f>IF(Project!J21&gt;0,Project!J21,"")</f>
-        <v/>
-      </c>
-      <c r="K21" s="58" t="str">
-        <f>IF(Project!K21&gt;0,Project!K21,"")</f>
-        <v/>
-      </c>
-      <c r="L21" s="58" t="str">
-        <f>IF(Project!L21&gt;0,Project!L21,"")</f>
-        <v/>
-      </c>
-      <c r="M21" s="58" t="str">
-        <f>IF(Project!M21&gt;0,Project!M21,"")</f>
-        <v/>
-      </c>
-      <c r="N21" s="58" t="str">
-        <f>IF(Project!N21&gt;0,Project!N21,"")</f>
-        <v/>
-      </c>
-      <c r="O21" s="58" t="str">
-        <f>IF(Project!O21&gt;0,Project!O21,"")</f>
-        <v/>
-      </c>
-      <c r="P21" s="58" t="str">
-        <f>IF(Project!P21&gt;0,Project!P21,"")</f>
-        <v/>
-      </c>
-      <c r="Q21" s="58" t="str">
-        <f>IF(Project!Q21&gt;0,Project!Q21,"")</f>
-        <v/>
-      </c>
-      <c r="R21" s="58" t="str">
-        <f>IF(Project!R21&gt;0,Project!R21,"")</f>
-        <v/>
-      </c>
-      <c r="S21" s="58" t="str">
-        <f>IF(Project!S21&gt;0,Project!S21,"")</f>
-        <v/>
-      </c>
-      <c r="T21" s="58" t="str">
-        <f>IF(Project!T21&gt;0,Project!T21,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A22" t="str">
-        <f>IF(Project!A22&gt;0,Project!A22,"")</f>
-        <v>IT Dist</v>
-      </c>
-      <c r="B22">
-        <f>IF(Project!B22&gt;0,Project!B22,"")</f>
-        <v>36</v>
-      </c>
-      <c r="C22" t="str">
-        <f>IF(Project!C22&gt;0,Project!C22,"")</f>
-        <v/>
-      </c>
-      <c r="D22" t="str">
-        <f>IF(Project!D22&gt;0,Project!D22,"")</f>
-        <v/>
-      </c>
-      <c r="E22" t="str">
-        <f>IF(Project!E22&gt;0,Project!E22,"")</f>
-        <v/>
-      </c>
-      <c r="F22" t="str">
-        <f>IF(Project!F22&gt;0,Project!F22,"")</f>
-        <v/>
-      </c>
-      <c r="G22">
+      <c r="B27" s="63">
         <f>IF(Project!G22&gt;0,Project!G22,"")</f>
         <v>180</v>
       </c>
-      <c r="H22">
+      <c r="C27" s="64" t="str">
+        <f>IF(Project!G23&gt;0,Project!G23,"")</f>
+        <v/>
+      </c>
+      <c r="D27" s="65" t="str">
+        <f>IF(Project!G24&gt;0,Project!G24,"")</f>
+        <v/>
+      </c>
+      <c r="E27" s="67">
+        <f>IF(Project!G25&gt;0,Project!G25,"")</f>
+        <v>23.7</v>
+      </c>
+      <c r="F27" s="66" t="str">
+        <f>IF(Project!G26&gt;0,Project!G26,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A28" s="58" t="str">
+        <f>IF(Project!H21&gt;0,Project!H21,"")</f>
+        <v>FTE</v>
+      </c>
+      <c r="B28" s="63">
         <f>IF(Project!H22&gt;0,Project!H22,"")</f>
         <v>216</v>
       </c>
-      <c r="I22" t="str">
-        <f>IF(Project!I22&gt;0,Project!I22,"")</f>
-        <v/>
-      </c>
-      <c r="J22" t="str">
-        <f>IF(Project!J22&gt;0,Project!J22,"")</f>
-        <v/>
-      </c>
-      <c r="K22" t="str">
-        <f>IF(Project!K22&gt;0,Project!K22,"")</f>
-        <v/>
-      </c>
-      <c r="L22" t="str">
-        <f>IF(Project!L22&gt;0,Project!L22,"")</f>
-        <v/>
-      </c>
-      <c r="M22" t="str">
-        <f>IF(Project!M22&gt;0,Project!M22,"")</f>
-        <v/>
-      </c>
-      <c r="N22" t="str">
-        <f>IF(Project!N22&gt;0,Project!N22,"")</f>
-        <v/>
-      </c>
-      <c r="O22" t="str">
-        <f>IF(Project!O22&gt;0,Project!O22,"")</f>
-        <v/>
-      </c>
-      <c r="P22" t="str">
-        <f>IF(Project!P22&gt;0,Project!P22,"")</f>
-        <v/>
-      </c>
-      <c r="Q22" t="str">
-        <f>IF(Project!Q22&gt;0,Project!Q22,"")</f>
-        <v/>
-      </c>
-      <c r="R22" t="str">
-        <f>IF(Project!R22&gt;0,Project!R22,"")</f>
-        <v/>
-      </c>
-      <c r="S22" t="str">
-        <f>IF(Project!S22&gt;0,Project!S22,"")</f>
-        <v/>
-      </c>
-      <c r="T22" t="str">
-        <f>IF(Project!T22&gt;0,Project!T22,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A23" t="str">
-        <f>IF(Project!A23&gt;0,Project!A23,"")</f>
-        <v>SCGP e-Ordering</v>
-      </c>
-      <c r="B23">
-        <f>IF(Project!B23&gt;0,Project!B23,"")</f>
-        <v>2.7</v>
-      </c>
-      <c r="C23">
-        <f>IF(Project!C23&gt;0,Project!C23,"")</f>
-        <v>154.05000000000001</v>
-      </c>
-      <c r="D23">
-        <f>IF(Project!D23&gt;0,Project!D23,"")</f>
-        <v>5.13</v>
-      </c>
-      <c r="E23">
-        <f>IF(Project!E23&gt;0,Project!E23,"")</f>
-        <v>0.9</v>
-      </c>
-      <c r="F23" t="str">
-        <f>IF(Project!F23&gt;0,Project!F23,"")</f>
-        <v/>
-      </c>
-      <c r="G23" t="str">
-        <f>IF(Project!G23&gt;0,Project!G23,"")</f>
-        <v/>
-      </c>
-      <c r="H23">
+      <c r="C28" s="64">
         <f>IF(Project!H23&gt;0,Project!H23,"")</f>
         <v>162.78</v>
       </c>
-      <c r="I23" t="str">
-        <f>IF(Project!I23&gt;0,Project!I23,"")</f>
-        <v/>
-      </c>
-      <c r="J23" t="str">
-        <f>IF(Project!J23&gt;0,Project!J23,"")</f>
-        <v/>
-      </c>
-      <c r="K23" t="str">
-        <f>IF(Project!K23&gt;0,Project!K23,"")</f>
-        <v/>
-      </c>
-      <c r="L23" t="str">
-        <f>IF(Project!L23&gt;0,Project!L23,"")</f>
-        <v/>
-      </c>
-      <c r="M23" t="str">
-        <f>IF(Project!M23&gt;0,Project!M23,"")</f>
-        <v/>
-      </c>
-      <c r="N23" t="str">
-        <f>IF(Project!N23&gt;0,Project!N23,"")</f>
-        <v/>
-      </c>
-      <c r="O23" t="str">
-        <f>IF(Project!O23&gt;0,Project!O23,"")</f>
-        <v/>
-      </c>
-      <c r="P23" t="str">
-        <f>IF(Project!P23&gt;0,Project!P23,"")</f>
-        <v/>
-      </c>
-      <c r="Q23" t="str">
-        <f>IF(Project!Q23&gt;0,Project!Q23,"")</f>
-        <v/>
-      </c>
-      <c r="R23" t="str">
-        <f>IF(Project!R23&gt;0,Project!R23,"")</f>
-        <v/>
-      </c>
-      <c r="S23" t="str">
-        <f>IF(Project!S23&gt;0,Project!S23,"")</f>
-        <v/>
-      </c>
-      <c r="T23" t="str">
-        <f>IF(Project!T23&gt;0,Project!T23,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A24" t="str">
-        <f>IF(Project!A24&gt;0,Project!A24,"")</f>
-        <v>CAP (Common AI Platform)</v>
-      </c>
-      <c r="B24" t="str">
-        <f>IF(Project!B24&gt;0,Project!B24,"")</f>
-        <v/>
-      </c>
-      <c r="C24">
-        <f>IF(Project!C24&gt;0,Project!C24,"")</f>
-        <v>63.6</v>
-      </c>
-      <c r="D24" t="str">
-        <f>IF(Project!D24&gt;0,Project!D24,"")</f>
-        <v/>
-      </c>
-      <c r="E24" t="str">
-        <f>IF(Project!E24&gt;0,Project!E24,"")</f>
-        <v/>
-      </c>
-      <c r="F24" t="str">
-        <f>IF(Project!F24&gt;0,Project!F24,"")</f>
-        <v/>
-      </c>
-      <c r="G24" t="str">
-        <f>IF(Project!G24&gt;0,Project!G24,"")</f>
-        <v/>
-      </c>
-      <c r="H24">
+      <c r="D28" s="65">
         <f>IF(Project!H24&gt;0,Project!H24,"")</f>
         <v>63.6</v>
       </c>
-      <c r="I24" t="str">
-        <f>IF(Project!I24&gt;0,Project!I24,"")</f>
-        <v/>
-      </c>
-      <c r="J24" t="str">
-        <f>IF(Project!J24&gt;0,Project!J24,"")</f>
-        <v/>
-      </c>
-      <c r="K24" t="str">
-        <f>IF(Project!K24&gt;0,Project!K24,"")</f>
-        <v/>
-      </c>
-      <c r="L24" t="str">
-        <f>IF(Project!L24&gt;0,Project!L24,"")</f>
-        <v/>
-      </c>
-      <c r="M24" t="str">
-        <f>IF(Project!M24&gt;0,Project!M24,"")</f>
-        <v/>
-      </c>
-      <c r="N24" t="str">
-        <f>IF(Project!N24&gt;0,Project!N24,"")</f>
-        <v/>
-      </c>
-      <c r="O24" t="str">
-        <f>IF(Project!O24&gt;0,Project!O24,"")</f>
-        <v/>
-      </c>
-      <c r="P24" t="str">
-        <f>IF(Project!P24&gt;0,Project!P24,"")</f>
-        <v/>
-      </c>
-      <c r="Q24" t="str">
-        <f>IF(Project!Q24&gt;0,Project!Q24,"")</f>
-        <v/>
-      </c>
-      <c r="R24" t="str">
-        <f>IF(Project!R24&gt;0,Project!R24,"")</f>
-        <v/>
-      </c>
-      <c r="S24" t="str">
-        <f>IF(Project!S24&gt;0,Project!S24,"")</f>
-        <v/>
-      </c>
-      <c r="T24" t="str">
-        <f>IF(Project!T24&gt;0,Project!T24,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A25" t="str">
-        <f>IF(Project!A25&gt;0,Project!A25,"")</f>
-        <v>PromptPlus</v>
-      </c>
-      <c r="B25" t="str">
-        <f>IF(Project!B25&gt;0,Project!B25,"")</f>
-        <v/>
-      </c>
-      <c r="C25">
-        <f>IF(Project!C25&gt;0,Project!C25,"")</f>
-        <v>27.375</v>
-      </c>
-      <c r="D25" t="str">
-        <f>IF(Project!D25&gt;0,Project!D25,"")</f>
-        <v/>
-      </c>
-      <c r="E25" t="str">
-        <f>IF(Project!E25&gt;0,Project!E25,"")</f>
-        <v/>
-      </c>
-      <c r="F25" t="str">
-        <f>IF(Project!F25&gt;0,Project!F25,"")</f>
-        <v/>
-      </c>
-      <c r="G25">
-        <f>IF(Project!G25&gt;0,Project!G25,"")</f>
-        <v>23.7</v>
-      </c>
-      <c r="H25">
+      <c r="E28" s="67">
         <f>IF(Project!H25&gt;0,Project!H25,"")</f>
         <v>51.075000000000003</v>
       </c>
-      <c r="I25" t="str">
-        <f>IF(Project!I25&gt;0,Project!I25,"")</f>
-        <v/>
-      </c>
-      <c r="J25" t="str">
-        <f>IF(Project!J25&gt;0,Project!J25,"")</f>
-        <v/>
-      </c>
-      <c r="K25" t="str">
-        <f>IF(Project!K25&gt;0,Project!K25,"")</f>
-        <v/>
-      </c>
-      <c r="L25" t="str">
-        <f>IF(Project!L25&gt;0,Project!L25,"")</f>
-        <v/>
-      </c>
-      <c r="M25" t="str">
-        <f>IF(Project!M25&gt;0,Project!M25,"")</f>
-        <v/>
-      </c>
-      <c r="N25" t="str">
-        <f>IF(Project!N25&gt;0,Project!N25,"")</f>
-        <v/>
-      </c>
-      <c r="O25" t="str">
-        <f>IF(Project!O25&gt;0,Project!O25,"")</f>
-        <v/>
-      </c>
-      <c r="P25" t="str">
-        <f>IF(Project!P25&gt;0,Project!P25,"")</f>
-        <v/>
-      </c>
-      <c r="Q25" t="str">
-        <f>IF(Project!Q25&gt;0,Project!Q25,"")</f>
-        <v/>
-      </c>
-      <c r="R25" t="str">
-        <f>IF(Project!R25&gt;0,Project!R25,"")</f>
-        <v/>
-      </c>
-      <c r="S25" t="str">
-        <f>IF(Project!S25&gt;0,Project!S25,"")</f>
-        <v/>
-      </c>
-      <c r="T25" t="str">
-        <f>IF(Project!T25&gt;0,Project!T25,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A26" t="str">
-        <f>IF(Project!A26&gt;0,Project!A26,"")</f>
-        <v>WeShape platform</v>
-      </c>
-      <c r="B26">
-        <f>IF(Project!B26&gt;0,Project!B26,"")</f>
-        <v>0.8</v>
-      </c>
-      <c r="C26" t="str">
-        <f>IF(Project!C26&gt;0,Project!C26,"")</f>
-        <v/>
-      </c>
-      <c r="D26" t="str">
-        <f>IF(Project!D26&gt;0,Project!D26,"")</f>
-        <v/>
-      </c>
-      <c r="E26" t="str">
-        <f>IF(Project!E26&gt;0,Project!E26,"")</f>
-        <v/>
-      </c>
-      <c r="F26">
-        <f>IF(Project!F26&gt;0,Project!F26,"")</f>
-        <v>34.655000000000001</v>
-      </c>
-      <c r="G26" t="str">
-        <f>IF(Project!G26&gt;0,Project!G26,"")</f>
-        <v/>
-      </c>
-      <c r="H26">
+      <c r="F28" s="66">
         <f>IF(Project!H26&gt;0,Project!H26,"")</f>
         <v>35.454999999999998</v>
       </c>
-      <c r="I26" t="str">
-        <f>IF(Project!I26&gt;0,Project!I26,"")</f>
-        <v/>
-      </c>
-      <c r="J26" t="str">
-        <f>IF(Project!J26&gt;0,Project!J26,"")</f>
-        <v/>
-      </c>
-      <c r="K26" t="str">
-        <f>IF(Project!K26&gt;0,Project!K26,"")</f>
-        <v/>
-      </c>
-      <c r="L26" t="str">
-        <f>IF(Project!L26&gt;0,Project!L26,"")</f>
-        <v/>
-      </c>
-      <c r="M26" t="str">
-        <f>IF(Project!M26&gt;0,Project!M26,"")</f>
-        <v/>
-      </c>
-      <c r="N26" t="str">
-        <f>IF(Project!N26&gt;0,Project!N26,"")</f>
-        <v/>
-      </c>
-      <c r="O26" t="str">
-        <f>IF(Project!O26&gt;0,Project!O26,"")</f>
-        <v/>
-      </c>
-      <c r="P26" t="str">
-        <f>IF(Project!P26&gt;0,Project!P26,"")</f>
-        <v/>
-      </c>
-      <c r="Q26" t="str">
-        <f>IF(Project!Q26&gt;0,Project!Q26,"")</f>
-        <v/>
-      </c>
-      <c r="R26" t="str">
-        <f>IF(Project!R26&gt;0,Project!R26,"")</f>
-        <v/>
-      </c>
-      <c r="S26" t="str">
-        <f>IF(Project!S26&gt;0,Project!S26,"")</f>
-        <v/>
-      </c>
-      <c r="T26" t="str">
-        <f>IF(Project!T26&gt;0,Project!T26,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A27" t="str">
-        <f>IF(Project!A27&gt;0,Project!A27,"")</f>
-        <v/>
-      </c>
-      <c r="B27" t="str">
-        <f>IF(Project!B27&gt;0,Project!B27,"")</f>
-        <v/>
-      </c>
-      <c r="C27" t="str">
-        <f>IF(Project!C27&gt;0,Project!C27,"")</f>
-        <v/>
-      </c>
-      <c r="D27" t="str">
-        <f>IF(Project!D27&gt;0,Project!D27,"")</f>
-        <v/>
-      </c>
-      <c r="E27" t="str">
-        <f>IF(Project!E27&gt;0,Project!E27,"")</f>
-        <v/>
-      </c>
-      <c r="F27" t="str">
-        <f>IF(Project!F27&gt;0,Project!F27,"")</f>
-        <v/>
-      </c>
-      <c r="G27" t="str">
-        <f>IF(Project!G27&gt;0,Project!G27,"")</f>
-        <v/>
-      </c>
-      <c r="H27" t="str">
-        <f>IF(Project!H27&gt;0,Project!H27,"")</f>
-        <v/>
-      </c>
-      <c r="I27" t="str">
-        <f>IF(Project!I27&gt;0,Project!I27,"")</f>
-        <v/>
-      </c>
-      <c r="J27" t="str">
-        <f>IF(Project!J27&gt;0,Project!J27,"")</f>
-        <v/>
-      </c>
-      <c r="K27" t="str">
-        <f>IF(Project!K27&gt;0,Project!K27,"")</f>
-        <v/>
-      </c>
-      <c r="L27" t="str">
-        <f>IF(Project!L27&gt;0,Project!L27,"")</f>
-        <v/>
-      </c>
-      <c r="M27" t="str">
-        <f>IF(Project!M27&gt;0,Project!M27,"")</f>
-        <v/>
-      </c>
-      <c r="N27" t="str">
-        <f>IF(Project!N27&gt;0,Project!N27,"")</f>
-        <v/>
-      </c>
-      <c r="O27" t="str">
-        <f>IF(Project!O27&gt;0,Project!O27,"")</f>
-        <v/>
-      </c>
-      <c r="P27" t="str">
-        <f>IF(Project!P27&gt;0,Project!P27,"")</f>
-        <v/>
-      </c>
-      <c r="Q27" t="str">
-        <f>IF(Project!Q27&gt;0,Project!Q27,"")</f>
-        <v/>
-      </c>
-      <c r="R27" t="str">
-        <f>IF(Project!R27&gt;0,Project!R27,"")</f>
-        <v/>
-      </c>
-      <c r="S27" t="str">
-        <f>IF(Project!S27&gt;0,Project!S27,"")</f>
-        <v/>
-      </c>
-      <c r="T27" t="str">
-        <f>IF(Project!T27&gt;0,Project!T27,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A28" t="str">
-        <f>IF(Project!A28&gt;0,Project!A28,"")</f>
-        <v/>
-      </c>
-      <c r="B28" t="str">
-        <f>IF(Project!B28&gt;0,Project!B28,"")</f>
-        <v/>
-      </c>
-      <c r="C28" t="str">
-        <f>IF(Project!C28&gt;0,Project!C28,"")</f>
-        <v/>
-      </c>
-      <c r="D28" t="str">
-        <f>IF(Project!D28&gt;0,Project!D28,"")</f>
-        <v/>
-      </c>
-      <c r="E28" t="str">
-        <f>IF(Project!E28&gt;0,Project!E28,"")</f>
-        <v/>
-      </c>
-      <c r="F28" t="str">
-        <f>IF(Project!F28&gt;0,Project!F28,"")</f>
-        <v/>
-      </c>
-      <c r="G28" t="str">
-        <f>IF(Project!G28&gt;0,Project!G28,"")</f>
-        <v/>
-      </c>
-      <c r="H28" t="str">
-        <f>IF(Project!H28&gt;0,Project!H28,"")</f>
-        <v/>
-      </c>
-      <c r="I28" t="str">
-        <f>IF(Project!I28&gt;0,Project!I28,"")</f>
-        <v/>
-      </c>
-      <c r="J28" t="str">
-        <f>IF(Project!J28&gt;0,Project!J28,"")</f>
-        <v/>
-      </c>
-      <c r="K28" t="str">
-        <f>IF(Project!K28&gt;0,Project!K28,"")</f>
-        <v/>
-      </c>
-      <c r="L28" t="str">
-        <f>IF(Project!L28&gt;0,Project!L28,"")</f>
-        <v/>
-      </c>
-      <c r="M28" t="str">
-        <f>IF(Project!M28&gt;0,Project!M28,"")</f>
-        <v/>
-      </c>
-      <c r="N28" t="str">
-        <f>IF(Project!N28&gt;0,Project!N28,"")</f>
-        <v/>
-      </c>
-      <c r="O28" t="str">
-        <f>IF(Project!O28&gt;0,Project!O28,"")</f>
-        <v/>
-      </c>
-      <c r="P28" t="str">
-        <f>IF(Project!P28&gt;0,Project!P28,"")</f>
-        <v/>
-      </c>
-      <c r="Q28" t="str">
-        <f>IF(Project!Q28&gt;0,Project!Q28,"")</f>
-        <v/>
-      </c>
-      <c r="R28" t="str">
-        <f>IF(Project!R28&gt;0,Project!R28,"")</f>
-        <v/>
-      </c>
-      <c r="S28" t="str">
-        <f>IF(Project!S28&gt;0,Project!S28,"")</f>
-        <v/>
-      </c>
-      <c r="T28" t="str">
-        <f>IF(Project!T28&gt;0,Project!T28,"")</f>
-        <v/>
-      </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A29" t="str">
-        <f>IF(Project!A29&gt;0,Project!A29,"")</f>
-        <v/>
-      </c>
-      <c r="B29" t="str">
-        <f>IF(Project!B29&gt;0,Project!B29,"")</f>
-        <v/>
-      </c>
-      <c r="C29" t="str">
-        <f>IF(Project!C29&gt;0,Project!C29,"")</f>
-        <v/>
-      </c>
-      <c r="D29" t="str">
-        <f>IF(Project!D29&gt;0,Project!D29,"")</f>
-        <v/>
-      </c>
-      <c r="E29" t="str">
-        <f>IF(Project!E29&gt;0,Project!E29,"")</f>
-        <v/>
-      </c>
-      <c r="F29" t="str">
-        <f>IF(Project!F29&gt;0,Project!F29,"")</f>
-        <v/>
-      </c>
-      <c r="G29" t="str">
-        <f>IF(Project!G29&gt;0,Project!G29,"")</f>
-        <v/>
-      </c>
-      <c r="H29" t="str">
-        <f>IF(Project!H29&gt;0,Project!H29,"")</f>
-        <v/>
-      </c>
-      <c r="I29" t="str">
-        <f>IF(Project!I29&gt;0,Project!I29,"")</f>
-        <v/>
-      </c>
-      <c r="J29" t="str">
-        <f>IF(Project!J29&gt;0,Project!J29,"")</f>
-        <v/>
-      </c>
-      <c r="K29" t="str">
-        <f>IF(Project!K29&gt;0,Project!K29,"")</f>
-        <v/>
-      </c>
-      <c r="L29" t="str">
-        <f>IF(Project!L29&gt;0,Project!L29,"")</f>
-        <v/>
-      </c>
-      <c r="M29" t="str">
-        <f>IF(Project!M29&gt;0,Project!M29,"")</f>
-        <v/>
-      </c>
-      <c r="N29" t="str">
-        <f>IF(Project!N29&gt;0,Project!N29,"")</f>
-        <v/>
-      </c>
-      <c r="O29" t="str">
-        <f>IF(Project!O29&gt;0,Project!O29,"")</f>
-        <v/>
-      </c>
-      <c r="P29" t="str">
-        <f>IF(Project!P29&gt;0,Project!P29,"")</f>
-        <v/>
-      </c>
-      <c r="Q29" t="str">
-        <f>IF(Project!Q29&gt;0,Project!Q29,"")</f>
-        <v/>
-      </c>
-      <c r="R29" t="str">
-        <f>IF(Project!R29&gt;0,Project!R29,"")</f>
-        <v/>
-      </c>
-      <c r="S29" t="str">
-        <f>IF(Project!S29&gt;0,Project!S29,"")</f>
-        <v/>
-      </c>
-      <c r="T29" t="str">
-        <f>IF(Project!T29&gt;0,Project!T29,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A30" t="str">
-        <f>IF(Project!A30&gt;0,Project!A30,"")</f>
-        <v/>
-      </c>
-      <c r="B30" t="str">
-        <f>IF(Project!B30&gt;0,Project!B30,"")</f>
-        <v/>
-      </c>
-      <c r="C30" t="str">
-        <f>IF(Project!C30&gt;0,Project!C30,"")</f>
-        <v/>
-      </c>
-      <c r="D30" t="str">
-        <f>IF(Project!D30&gt;0,Project!D30,"")</f>
-        <v/>
-      </c>
-      <c r="E30" t="str">
-        <f>IF(Project!E30&gt;0,Project!E30,"")</f>
-        <v/>
-      </c>
-      <c r="F30" t="str">
-        <f>IF(Project!F30&gt;0,Project!F30,"")</f>
-        <v/>
-      </c>
-      <c r="G30" t="str">
-        <f>IF(Project!G30&gt;0,Project!G30,"")</f>
-        <v/>
-      </c>
-      <c r="H30" t="str">
-        <f>IF(Project!H30&gt;0,Project!H30,"")</f>
-        <v/>
-      </c>
-      <c r="I30" t="str">
-        <f>IF(Project!I30&gt;0,Project!I30,"")</f>
-        <v/>
-      </c>
-      <c r="J30" t="str">
-        <f>IF(Project!J30&gt;0,Project!J30,"")</f>
-        <v/>
-      </c>
-      <c r="K30" t="str">
-        <f>IF(Project!K30&gt;0,Project!K30,"")</f>
-        <v/>
-      </c>
-      <c r="L30" t="str">
-        <f>IF(Project!L30&gt;0,Project!L30,"")</f>
-        <v/>
-      </c>
-      <c r="M30" t="str">
-        <f>IF(Project!M30&gt;0,Project!M30,"")</f>
-        <v/>
-      </c>
-      <c r="N30" t="str">
-        <f>IF(Project!N30&gt;0,Project!N30,"")</f>
-        <v/>
-      </c>
-      <c r="O30" t="str">
-        <f>IF(Project!O30&gt;0,Project!O30,"")</f>
-        <v/>
-      </c>
-      <c r="P30" t="str">
-        <f>IF(Project!P30&gt;0,Project!P30,"")</f>
-        <v/>
-      </c>
-      <c r="Q30" t="str">
-        <f>IF(Project!Q30&gt;0,Project!Q30,"")</f>
-        <v/>
-      </c>
-      <c r="R30" t="str">
-        <f>IF(Project!R30&gt;0,Project!R30,"")</f>
-        <v/>
-      </c>
-      <c r="S30" t="str">
-        <f>IF(Project!S30&gt;0,Project!S30,"")</f>
-        <v/>
-      </c>
-      <c r="T30" t="str">
-        <f>IF(Project!T30&gt;0,Project!T30,"")</f>
-        <v/>
-      </c>
+      <c r="A29" s="58"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/workforceresult.xlsx
+++ b/workforceresult.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miintra/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1F03ACC-3D81-C94C-B03B-FFCE323B397A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF888867-9EB3-F44C-B325-3497241AC874}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16120" activeTab="13" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="130">
   <si>
     <t>Type</t>
   </si>
@@ -617,6 +617,9 @@
   </si>
   <si>
     <t>FTE</t>
+  </si>
+  <si>
+    <t>Total FTE</t>
   </si>
 </sst>
 </file>
@@ -13947,9 +13950,8 @@
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A28" s="58" t="str">
-        <f>IF(Project!H21&gt;0,Project!H21,"")</f>
-        <v>FTE</v>
+      <c r="A28" s="58" t="s">
+        <v>129</v>
       </c>
       <c r="B28" s="63">
         <f>IF(Project!H22&gt;0,Project!H22,"")</f>

--- a/workforceresult.xlsx
+++ b/workforceresult.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miintra/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miiintra/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF888867-9EB3-F44C-B325-3497241AC874}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C33F6567-D1FF-AA48-A45B-03D4B95897F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16120" activeTab="13" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="16120" activeTab="4" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
   </bookViews>
   <sheets>
     <sheet name="ALL" sheetId="1" r:id="rId1"/>
@@ -2311,7 +2311,7 @@
         <v>130</v>
       </c>
       <c r="G34" s="21">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="H34" s="21"/>
     </row>
@@ -2331,7 +2331,7 @@
         <v>0.12429999999999999</v>
       </c>
       <c r="G35" s="28">
-        <v>0.18479999999999999</v>
+        <v>0.29909999999999998</v>
       </c>
       <c r="H35" s="8"/>
     </row>
@@ -2353,7 +2353,7 @@
         <v>0.87570000000000003</v>
       </c>
       <c r="G36" s="19">
-        <v>0.81520000000000004</v>
+        <v>0.70089999999999997</v>
       </c>
       <c r="H36" s="20"/>
     </row>
@@ -2457,7 +2457,7 @@
         <v>99</v>
       </c>
       <c r="G41" s="21">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H41" s="21"/>
     </row>
@@ -2539,7 +2539,7 @@
         <v>19</v>
       </c>
       <c r="G45" s="21">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H45" s="21"/>
     </row>
@@ -2621,7 +2621,7 @@
         <v>12</v>
       </c>
       <c r="G49" s="21">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H49" s="21"/>
     </row>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F43">
         <f>IF(AIC!G33&gt;0,AIC!G33,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.2">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="F44">
         <f>IF(AIC!G34&gt;0,AIC!G34,"")</f>
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.2">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="F45">
         <f>IF(AIC!G41&gt;0,AIC!G41,"")</f>
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.2">
@@ -5852,7 +5852,7 @@
       </c>
       <c r="F156">
         <f>AIC!G36*100</f>
-        <v>62.029999999999994</v>
+        <v>44.13</v>
       </c>
     </row>
     <row r="157" spans="1:16" x14ac:dyDescent="0.2">
@@ -15328,7 +15328,7 @@
       </c>
       <c r="F44">
         <f>IF(ALL!G34&gt;0,ALL!G34,"")</f>
-        <v>121</v>
+        <v>104</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.2">
@@ -15354,7 +15354,7 @@
       </c>
       <c r="F45">
         <f>IF(ALL!G41&gt;0,ALL!G41,"")</f>
-        <v>93</v>
+        <v>81</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.2">
@@ -15380,7 +15380,7 @@
       </c>
       <c r="F46">
         <f>IF(ALL!G45&gt;0,ALL!G45,"")</f>
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.2">
@@ -15406,7 +15406,7 @@
       </c>
       <c r="F47">
         <f>IF(ALL!G49&gt;0,ALL!G49,"")</f>
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="151" spans="1:16" x14ac:dyDescent="0.2">
@@ -15648,7 +15648,7 @@
       </c>
       <c r="F156">
         <f>ALL!G36*100</f>
-        <v>81.52000000000001</v>
+        <v>70.09</v>
       </c>
     </row>
     <row r="157" spans="1:16" x14ac:dyDescent="0.2">
@@ -16642,7 +16642,7 @@
         <v>16</v>
       </c>
       <c r="G34" s="21">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
@@ -16661,7 +16661,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
       <c r="G35" s="28">
-        <v>0.10589999999999999</v>
+        <v>0.16470000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
@@ -16682,7 +16682,7 @@
         <v>0.92749999999999999</v>
       </c>
       <c r="G36" s="19">
-        <v>0.89410000000000001</v>
+        <v>0.83530000000000004</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
@@ -16781,7 +16781,7 @@
         <v>16</v>
       </c>
       <c r="G41" s="21">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
@@ -18762,7 +18762,7 @@
       </c>
       <c r="F44">
         <f>IF(CPS!G34&gt;0,CPS!G34,"")</f>
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.2">
@@ -18788,7 +18788,7 @@
       </c>
       <c r="F45">
         <f>IF(CPS!G41&gt;0,CPS!G41,"")</f>
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.2">
@@ -19706,7 +19706,7 @@
       </c>
       <c r="F156">
         <f>CPS!G36*100</f>
-        <v>89.41</v>
+        <v>83.53</v>
       </c>
     </row>
     <row r="157" spans="1:16" x14ac:dyDescent="0.2">
@@ -20677,7 +20677,7 @@
         <v>48</v>
       </c>
       <c r="G33" s="21">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
@@ -20700,7 +20700,7 @@
         <v>41</v>
       </c>
       <c r="G34" s="21">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
@@ -20719,7 +20719,7 @@
         <v>0.14099999999999999</v>
       </c>
       <c r="G35" s="28">
-        <v>0.21079999999999999</v>
+        <v>0.34060000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
@@ -20740,7 +20740,7 @@
         <v>0.85899999999999999</v>
       </c>
       <c r="G36" s="19">
-        <v>0.78920000000000001</v>
+        <v>0.65939999999999999</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
@@ -20839,7 +20839,7 @@
         <v>24</v>
       </c>
       <c r="G41" s="21">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
@@ -20917,7 +20917,7 @@
         <v>15</v>
       </c>
       <c r="G45" s="21">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
@@ -20995,7 +20995,7 @@
         <v>2</v>
       </c>
       <c r="G49" s="21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.2">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="F43">
         <f>IF(PSE!G33&gt;0,PSE!G33,"")</f>
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.2">
@@ -23350,7 +23350,7 @@
       </c>
       <c r="F44">
         <f>IF(PSE!G34&gt;0,PSE!G34,"")</f>
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.2">
@@ -23376,7 +23376,7 @@
       </c>
       <c r="F45">
         <f>IF(PSE!G41&gt;0,PSE!G41,"")</f>
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.2">
@@ -23402,7 +23402,7 @@
       </c>
       <c r="F46">
         <f>IF(PSE!G45&gt;0,PSE!G45,"")</f>
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.2">
@@ -23426,9 +23426,9 @@
         <f>IF(PSE!F49&gt;0,PSE!F49,"")</f>
         <v>2</v>
       </c>
-      <c r="F47">
+      <c r="F47" t="str">
         <f>IF(PSE!G49&gt;0,PSE!G49,"")</f>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.2">
@@ -24294,7 +24294,7 @@
       </c>
       <c r="F156">
         <f>PSE!G36*100</f>
-        <v>78.92</v>
+        <v>65.94</v>
       </c>
     </row>
     <row r="157" spans="1:16" x14ac:dyDescent="0.2">
@@ -25288,7 +25288,7 @@
         <v>42</v>
       </c>
       <c r="G34" s="21">
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
@@ -25307,7 +25307,7 @@
         <v>8.7599999999999997E-2</v>
       </c>
       <c r="G35" s="28">
-        <v>0.1608</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
@@ -25328,7 +25328,7 @@
         <v>0.91239999999999999</v>
       </c>
       <c r="G36" s="19">
-        <v>0.83919999999999995</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
@@ -25427,7 +25427,7 @@
         <v>30</v>
       </c>
       <c r="G41" s="21">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
@@ -25582,8 +25582,8 @@
       <c r="F49" s="14">
         <v>10</v>
       </c>
-      <c r="G49" s="14">
-        <v>9</v>
+      <c r="G49" s="21">
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.2">
@@ -28680,7 +28680,7 @@
       </c>
       <c r="F44">
         <f>IF(SD!G34&gt;0,SD!G34,"")</f>
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.2">
@@ -28706,7 +28706,7 @@
       </c>
       <c r="F45">
         <f>IF(SD!G41&gt;0,SD!G41,"")</f>
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.2">
@@ -28758,7 +28758,7 @@
       </c>
       <c r="F47">
         <f>IF(SD!G49&gt;0,SD!G49,"")</f>
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.2">
@@ -31808,7 +31808,7 @@
       </c>
       <c r="F156">
         <f>SD!G36*100</f>
-        <v>83.919999999999987</v>
+        <v>70</v>
       </c>
     </row>
     <row r="157" spans="1:16" x14ac:dyDescent="0.2">
@@ -32779,7 +32779,7 @@
         <v>19</v>
       </c>
       <c r="G33" s="21">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
@@ -32802,7 +32802,7 @@
         <v>14</v>
       </c>
       <c r="G34" s="21">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
@@ -32821,7 +32821,7 @@
         <v>0.28849999999999998</v>
       </c>
       <c r="G35" s="28">
-        <v>0.37969999999999998</v>
+        <v>0.55869999999999997</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
@@ -32842,7 +32842,7 @@
         <v>0.71150000000000002</v>
       </c>
       <c r="G36" s="19">
-        <v>0.62029999999999996</v>
+        <v>0.44130000000000003</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
@@ -32941,7 +32941,7 @@
         <v>14</v>
       </c>
       <c r="G41" s="21">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">

--- a/workforceresult.xlsx
+++ b/workforceresult.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miiintra/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C33F6567-D1FF-AA48-A45B-03D4B95897F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0986F6E-E61E-4446-9A49-D4A51E61CEF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="16120" activeTab="4" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
+    <workbookView xWindow="8000" yWindow="3500" windowWidth="28800" windowHeight="16120" activeTab="3" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
   </bookViews>
   <sheets>
     <sheet name="ALL" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="131">
   <si>
     <t>Type</t>
   </si>
@@ -621,12 +621,15 @@
   <si>
     <t>Total FTE</t>
   </si>
+  <si>
+    <t>Available</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -752,6 +755,13 @@
     <font>
       <sz val="12"/>
       <color rgb="FFC00000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="7"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -921,7 +931,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1016,6 +1026,7 @@
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -19041,70 +19052,69 @@
         <v>8.1999999999999993</v>
       </c>
     </row>
-    <row r="54" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="59" t="str">
-        <f>$A$152</f>
-        <v>% Plan</v>
-      </c>
-      <c r="B54" s="59">
-        <f>(B53/B52)*100</f>
-        <v>93.75</v>
-      </c>
-      <c r="C54" s="59">
-        <f t="shared" ref="C54:P54" si="0">(C53/C52)*100</f>
-        <v>94.583333333333329</v>
-      </c>
-      <c r="D54" s="59">
+    <row r="54" spans="1:16" s="68" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="68" t="s">
+        <v>130</v>
+      </c>
+      <c r="B54" s="68">
+        <f>B52-B53</f>
+        <v>0.75</v>
+      </c>
+      <c r="C54" s="68">
+        <f t="shared" ref="C54:P54" si="0">C52-C53</f>
+        <v>0.65000000000000036</v>
+      </c>
+      <c r="D54" s="68">
         <f t="shared" si="0"/>
-        <v>92.083333333333343</v>
-      </c>
-      <c r="E54" s="59">
+        <v>0.94999999999999929</v>
+      </c>
+      <c r="E54" s="68">
         <f t="shared" si="0"/>
-        <v>103.63636363636364</v>
-      </c>
-      <c r="F54" s="59">
+        <v>-0.40000000000000036</v>
+      </c>
+      <c r="F54" s="68">
         <f t="shared" si="0"/>
-        <v>104.54545454545455</v>
-      </c>
-      <c r="G54" s="59">
+        <v>-0.5</v>
+      </c>
+      <c r="G54" s="68">
         <f t="shared" si="0"/>
-        <v>103.63636363636364</v>
-      </c>
-      <c r="H54" s="59">
+        <v>-0.40000000000000036</v>
+      </c>
+      <c r="H54" s="68">
         <f t="shared" si="0"/>
-        <v>92.72727272727272</v>
-      </c>
-      <c r="I54" s="59">
+        <v>0.80000000000000071</v>
+      </c>
+      <c r="I54" s="68">
         <f t="shared" si="0"/>
-        <v>90.909090909090907</v>
-      </c>
-      <c r="J54" s="59">
+        <v>1</v>
+      </c>
+      <c r="J54" s="68">
         <f t="shared" si="0"/>
-        <v>90.909090909090907</v>
-      </c>
-      <c r="K54" s="59">
+        <v>1</v>
+      </c>
+      <c r="K54" s="68">
         <f t="shared" si="0"/>
-        <v>90</v>
-      </c>
-      <c r="L54" s="59">
+        <v>1.0999999999999996</v>
+      </c>
+      <c r="L54" s="68">
         <f t="shared" si="0"/>
-        <v>88.181818181818173</v>
-      </c>
-      <c r="M54" s="59">
+        <v>1.3000000000000007</v>
+      </c>
+      <c r="M54" s="68">
         <f t="shared" si="0"/>
-        <v>88.181818181818173</v>
-      </c>
-      <c r="N54" s="59">
+        <v>1.3000000000000007</v>
+      </c>
+      <c r="N54" s="68">
         <f t="shared" si="0"/>
-        <v>74.545454545454533</v>
-      </c>
-      <c r="O54" s="59">
+        <v>2.8000000000000007</v>
+      </c>
+      <c r="O54" s="68">
         <f t="shared" si="0"/>
-        <v>74.545454545454533</v>
-      </c>
-      <c r="P54" s="59">
+        <v>2.8000000000000007</v>
+      </c>
+      <c r="P54" s="68">
         <f t="shared" si="0"/>
-        <v>74.545454545454533</v>
+        <v>2.8000000000000007</v>
       </c>
     </row>
     <row r="55" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
@@ -19353,70 +19363,69 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="59" t="str">
-        <f>$A$152</f>
-        <v>% Plan</v>
-      </c>
-      <c r="B64" s="59">
-        <f>(B63/B62)*100</f>
-        <v>92</v>
-      </c>
-      <c r="C64" s="59">
-        <f t="shared" ref="C64" si="2">(C63/C62)*100</f>
-        <v>92</v>
-      </c>
-      <c r="D64" s="59">
-        <f t="shared" ref="D64" si="3">(D63/D62)*100</f>
-        <v>92</v>
-      </c>
-      <c r="E64" s="59">
-        <f t="shared" ref="E64" si="4">(E63/E62)*100</f>
-        <v>100</v>
-      </c>
-      <c r="F64" s="59">
-        <f t="shared" ref="F64" si="5">(F63/F62)*100</f>
-        <v>100</v>
-      </c>
-      <c r="G64" s="59">
-        <f t="shared" ref="G64" si="6">(G63/G62)*100</f>
-        <v>100</v>
-      </c>
-      <c r="H64" s="59">
-        <f t="shared" ref="H64" si="7">(H63/H62)*100</f>
-        <v>100</v>
-      </c>
-      <c r="I64" s="59">
-        <f t="shared" ref="I64" si="8">(I63/I62)*100</f>
-        <v>100</v>
-      </c>
-      <c r="J64" s="59">
-        <f t="shared" ref="J64" si="9">(J63/J62)*100</f>
-        <v>100</v>
-      </c>
-      <c r="K64" s="59">
-        <f t="shared" ref="K64" si="10">(K63/K62)*100</f>
-        <v>100</v>
-      </c>
-      <c r="L64" s="59">
-        <f t="shared" ref="L64" si="11">(L63/L62)*100</f>
-        <v>100</v>
-      </c>
-      <c r="M64" s="59">
-        <f t="shared" ref="M64" si="12">(M63/M62)*100</f>
-        <v>100</v>
-      </c>
-      <c r="N64" s="59">
-        <f t="shared" ref="N64" si="13">(N63/N62)*100</f>
-        <v>100</v>
-      </c>
-      <c r="O64" s="59">
-        <f t="shared" ref="O64" si="14">(O63/O62)*100</f>
-        <v>100</v>
-      </c>
-      <c r="P64" s="59">
-        <f t="shared" ref="P64" si="15">(P63/P62)*100</f>
-        <v>100</v>
+    <row r="64" spans="1:16" s="68" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="68" t="s">
+        <v>130</v>
+      </c>
+      <c r="B64" s="68">
+        <f>B62-B63</f>
+        <v>0.40000000000000036</v>
+      </c>
+      <c r="C64" s="68">
+        <f t="shared" ref="C64" si="2">C62-C63</f>
+        <v>0.40000000000000036</v>
+      </c>
+      <c r="D64" s="68">
+        <f t="shared" ref="D64" si="3">D62-D63</f>
+        <v>0.40000000000000036</v>
+      </c>
+      <c r="E64" s="68">
+        <f t="shared" ref="E64" si="4">E62-E63</f>
+        <v>0</v>
+      </c>
+      <c r="F64" s="68">
+        <f t="shared" ref="F64" si="5">F62-F63</f>
+        <v>0</v>
+      </c>
+      <c r="G64" s="68">
+        <f t="shared" ref="G64" si="6">G62-G63</f>
+        <v>0</v>
+      </c>
+      <c r="H64" s="68">
+        <f t="shared" ref="H64" si="7">H62-H63</f>
+        <v>0</v>
+      </c>
+      <c r="I64" s="68">
+        <f t="shared" ref="I64" si="8">I62-I63</f>
+        <v>0</v>
+      </c>
+      <c r="J64" s="68">
+        <f t="shared" ref="J64" si="9">J62-J63</f>
+        <v>0</v>
+      </c>
+      <c r="K64" s="68">
+        <f t="shared" ref="K64" si="10">K62-K63</f>
+        <v>0</v>
+      </c>
+      <c r="L64" s="68">
+        <f t="shared" ref="L64" si="11">L62-L63</f>
+        <v>0</v>
+      </c>
+      <c r="M64" s="68">
+        <f t="shared" ref="M64" si="12">M62-M63</f>
+        <v>0</v>
+      </c>
+      <c r="N64" s="68">
+        <f t="shared" ref="N64" si="13">N62-N63</f>
+        <v>0</v>
+      </c>
+      <c r="O64" s="68">
+        <f t="shared" ref="O64" si="14">O62-O63</f>
+        <v>0</v>
+      </c>
+      <c r="P64" s="68">
+        <f t="shared" ref="P64" si="15">P62-P63</f>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:6" s="60" customFormat="1" x14ac:dyDescent="0.2">

--- a/workforceresult.xlsx
+++ b/workforceresult.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miiintra/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0986F6E-E61E-4446-9A49-D4A51E61CEF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EC10C9C-6F5A-AB49-BF8E-53C950956132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8000" yWindow="3500" windowWidth="28800" windowHeight="16120" activeTab="3" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
+    <workbookView xWindow="8000" yWindow="3500" windowWidth="28800" windowHeight="16120" activeTab="11" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
   </bookViews>
   <sheets>
     <sheet name="ALL" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="130">
   <si>
     <t>Type</t>
   </si>
@@ -621,15 +621,15 @@
   <si>
     <t>Total FTE</t>
   </si>
-  <si>
-    <t>Available</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -743,13 +743,6 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="5"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -931,7 +924,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1018,15 +1011,14 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4266,116 +4258,115 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="54" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="59" t="str">
-        <f>$A$152</f>
-        <v>% Plan</v>
-      </c>
-      <c r="B54" s="59">
-        <f>(B53/B52)*100</f>
-        <v>70</v>
-      </c>
-      <c r="C54" s="59">
-        <f t="shared" ref="C54:P54" si="0">(C53/C52)*100</f>
-        <v>70</v>
-      </c>
-      <c r="D54" s="59">
+    <row r="54" spans="1:16" s="66" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="B54" s="67">
+        <f>B52-B53</f>
+        <v>1.2000000000000002</v>
+      </c>
+      <c r="C54" s="67">
+        <f t="shared" ref="C54:P54" si="0">C52-C53</f>
+        <v>1.2000000000000002</v>
+      </c>
+      <c r="D54" s="67">
         <f t="shared" si="0"/>
-        <v>93.333333333333329</v>
-      </c>
-      <c r="E54" s="59">
+        <v>0.20000000000000018</v>
+      </c>
+      <c r="E54" s="67">
         <f t="shared" si="0"/>
-        <v>96.666666666666671</v>
-      </c>
-      <c r="F54" s="59">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="F54" s="67">
         <f t="shared" si="0"/>
-        <v>96.666666666666671</v>
-      </c>
-      <c r="G54" s="59">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="G54" s="67">
         <f t="shared" si="0"/>
-        <v>96.666666666666671</v>
-      </c>
-      <c r="H54" s="59">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H54" s="67">
         <f t="shared" si="0"/>
-        <v>96.666666666666671</v>
-      </c>
-      <c r="I54" s="59">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="I54" s="67">
         <f t="shared" si="0"/>
-        <v>96.666666666666671</v>
-      </c>
-      <c r="J54" s="59">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="J54" s="67">
         <f t="shared" si="0"/>
-        <v>96.666666666666671</v>
-      </c>
-      <c r="K54" s="59">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="K54" s="67">
         <f t="shared" si="0"/>
-        <v>96.666666666666671</v>
-      </c>
-      <c r="L54" s="59">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="L54" s="67">
         <f t="shared" si="0"/>
-        <v>96.666666666666671</v>
-      </c>
-      <c r="M54" s="59">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="M54" s="67">
         <f t="shared" si="0"/>
-        <v>96.666666666666671</v>
-      </c>
-      <c r="N54" s="59">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="N54" s="67">
         <f t="shared" si="0"/>
-        <v>96.666666666666671</v>
-      </c>
-      <c r="O54" s="59">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="O54" s="67">
         <f t="shared" si="0"/>
-        <v>96.666666666666671</v>
-      </c>
-      <c r="P54" s="59">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="P54" s="67">
         <f t="shared" si="0"/>
-        <v>96.666666666666671</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="60" t="str">
+        <v>0.10000000000000009</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B55" s="59" t="str">
         <f>B$155</f>
         <v>Q1</v>
       </c>
-      <c r="C55" s="60" t="str">
+      <c r="C55" s="59" t="str">
         <f t="shared" ref="C55:F55" si="1">C$155</f>
         <v>Q2</v>
       </c>
-      <c r="D55" s="60" t="str">
+      <c r="D55" s="59" t="str">
         <f t="shared" si="1"/>
         <v>Q3</v>
       </c>
-      <c r="E55" s="60" t="str">
+      <c r="E55" s="59" t="str">
         <f t="shared" si="1"/>
         <v>Q4</v>
       </c>
-      <c r="F55" s="60" t="str">
+      <c r="F55" s="59" t="str">
         <f t="shared" si="1"/>
         <v>Q1'27</v>
       </c>
     </row>
-    <row r="56" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="60" t="str">
+    <row r="56" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="59" t="str">
         <f>$A$156</f>
         <v>% Plan</v>
       </c>
-      <c r="B56" s="60">
+      <c r="B56" s="59">
         <f>(AVERAGE(B53:D53)/AVERAGE(B52:D52))*100</f>
         <v>76.363636363636346</v>
       </c>
-      <c r="C56" s="60">
+      <c r="C56" s="59">
         <f>(AVERAGE(E53:G53)/AVERAGE(E52:G52))*100</f>
         <v>96.666666666666671</v>
       </c>
-      <c r="D56" s="60">
+      <c r="D56" s="59">
         <f>(AVERAGE(H53:J53)/AVERAGE(H52:J52))*100</f>
         <v>96.666666666666671</v>
       </c>
-      <c r="E56" s="60">
+      <c r="E56" s="59">
         <f>(AVERAGE(K53:M53)/AVERAGE(K52:M52))*100</f>
         <v>96.666666666666671</v>
       </c>
-      <c r="F56" s="60">
+      <c r="F56" s="59">
         <f>(AVERAGE(N53:P53)/AVERAGE(N52:P52))*100</f>
         <v>96.666666666666671</v>
       </c>
@@ -4578,116 +4569,115 @@
         <v>3.6850000000000001</v>
       </c>
     </row>
-    <row r="64" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="59" t="str">
-        <f>$A$152</f>
-        <v>% Plan</v>
-      </c>
-      <c r="B64" s="59">
-        <f>(B63/B62)*100</f>
-        <v>65.15625</v>
-      </c>
-      <c r="C64" s="59">
-        <f t="shared" ref="C64:P64" si="2">(C63/C62)*100</f>
-        <v>78.0078125</v>
-      </c>
-      <c r="D64" s="59">
+    <row r="64" spans="1:16" s="66" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="B64" s="67">
+        <f>B62-B63</f>
+        <v>2.7874999999999996</v>
+      </c>
+      <c r="C64" s="67">
+        <f t="shared" ref="C64:P64" si="2">C62-C63</f>
+        <v>1.7593750000000004</v>
+      </c>
+      <c r="D64" s="67">
         <f t="shared" si="2"/>
-        <v>76.7578125</v>
-      </c>
-      <c r="E64" s="59">
+        <v>1.859375</v>
+      </c>
+      <c r="E64" s="67">
         <f t="shared" si="2"/>
-        <v>87.6640625</v>
-      </c>
-      <c r="F64" s="59">
+        <v>0.98687500000000039</v>
+      </c>
+      <c r="F64" s="67">
         <f t="shared" si="2"/>
-        <v>88.6015625</v>
-      </c>
-      <c r="G64" s="59">
+        <v>0.91187500000000021</v>
+      </c>
+      <c r="G64" s="67">
         <f t="shared" si="2"/>
-        <v>87.3515625</v>
-      </c>
-      <c r="H64" s="59">
+        <v>1.0118749999999999</v>
+      </c>
+      <c r="H64" s="67">
         <f t="shared" si="2"/>
-        <v>66.84375</v>
-      </c>
-      <c r="I64" s="59">
+        <v>2.6524999999999999</v>
+      </c>
+      <c r="I64" s="67">
         <f t="shared" si="2"/>
-        <v>64.34375</v>
-      </c>
-      <c r="J64" s="59">
+        <v>2.8525</v>
+      </c>
+      <c r="J64" s="67">
         <f t="shared" si="2"/>
-        <v>64.34375</v>
-      </c>
-      <c r="K64" s="59">
+        <v>2.8525</v>
+      </c>
+      <c r="K64" s="67">
         <f t="shared" si="2"/>
-        <v>51.375000000000007</v>
-      </c>
-      <c r="L64" s="59">
+        <v>3.8899999999999997</v>
+      </c>
+      <c r="L64" s="67">
         <f t="shared" si="2"/>
-        <v>51.375000000000007</v>
-      </c>
-      <c r="M64" s="59">
+        <v>3.8899999999999997</v>
+      </c>
+      <c r="M64" s="67">
         <f t="shared" si="2"/>
-        <v>51.375000000000007</v>
-      </c>
-      <c r="N64" s="59">
+        <v>3.8899999999999997</v>
+      </c>
+      <c r="N64" s="67">
         <f t="shared" si="2"/>
-        <v>46.0625</v>
-      </c>
-      <c r="O64" s="59">
+        <v>4.3149999999999995</v>
+      </c>
+      <c r="O64" s="67">
         <f t="shared" si="2"/>
-        <v>46.0625</v>
-      </c>
-      <c r="P64" s="59">
+        <v>4.3149999999999995</v>
+      </c>
+      <c r="P64" s="67">
         <f t="shared" si="2"/>
-        <v>46.0625</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B65" s="60" t="str">
+        <v>4.3149999999999995</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B65" s="59" t="str">
         <f>B$155</f>
         <v>Q1</v>
       </c>
-      <c r="C65" s="60" t="str">
+      <c r="C65" s="59" t="str">
         <f t="shared" ref="C65:F65" si="3">C$155</f>
         <v>Q2</v>
       </c>
-      <c r="D65" s="60" t="str">
+      <c r="D65" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Q3</v>
       </c>
-      <c r="E65" s="60" t="str">
+      <c r="E65" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Q4</v>
       </c>
-      <c r="F65" s="60" t="str">
+      <c r="F65" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Q1'27</v>
       </c>
     </row>
-    <row r="66" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="60" t="str">
+    <row r="66" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="59" t="str">
         <f>$A$156</f>
         <v>% Plan</v>
       </c>
-      <c r="B66" s="60">
+      <c r="B66" s="59">
         <f>(AVERAGE(B63:D63)/AVERAGE(B62:D62))*100</f>
         <v>73.307291666666657</v>
       </c>
-      <c r="C66" s="60">
+      <c r="C66" s="59">
         <f>(AVERAGE(E63:G63)/AVERAGE(E62:G62))*100</f>
         <v>87.872395833333343</v>
       </c>
-      <c r="D66" s="60">
+      <c r="D66" s="59">
         <f>(AVERAGE(H63:J63)/AVERAGE(H62:J62))*100</f>
         <v>65.177083333333343</v>
       </c>
-      <c r="E66" s="60">
+      <c r="E66" s="59">
         <f>(AVERAGE(K63:M63)/AVERAGE(K62:M62))*100</f>
         <v>51.375000000000007</v>
       </c>
-      <c r="F66" s="60">
+      <c r="F66" s="59">
         <f>(AVERAGE(N63:P63)/AVERAGE(N62:P62))*100</f>
         <v>46.0625</v>
       </c>
@@ -4890,116 +4880,115 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="74" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="59" t="str">
-        <f>$A$152</f>
-        <v>% Plan</v>
-      </c>
-      <c r="B74" s="59">
-        <f>(B73/B72)*100</f>
-        <v>60</v>
-      </c>
-      <c r="C74" s="59">
-        <f t="shared" ref="C74:P74" si="4">(C73/C72)*100</f>
-        <v>75</v>
-      </c>
-      <c r="D74" s="59">
+    <row r="74" spans="1:16" s="66" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="B74" s="67">
+        <f>B72-B73</f>
+        <v>2.8</v>
+      </c>
+      <c r="C74" s="67">
+        <f t="shared" ref="C74:P74" si="4">C72-C73</f>
+        <v>1.5</v>
+      </c>
+      <c r="D74" s="67">
         <f t="shared" si="4"/>
-        <v>69.166666666666671</v>
-      </c>
-      <c r="E74" s="59">
+        <v>1.8499999999999996</v>
+      </c>
+      <c r="E74" s="67">
         <f t="shared" si="4"/>
-        <v>84.166666666666671</v>
-      </c>
-      <c r="F74" s="59">
+        <v>0.95000000000000018</v>
+      </c>
+      <c r="F74" s="67">
         <f t="shared" si="4"/>
-        <v>88.333333333333329</v>
-      </c>
-      <c r="G74" s="59">
+        <v>0.70000000000000018</v>
+      </c>
+      <c r="G74" s="67">
         <f t="shared" si="4"/>
-        <v>82.5</v>
-      </c>
-      <c r="H74" s="59">
+        <v>1.0499999999999998</v>
+      </c>
+      <c r="H74" s="67">
         <f t="shared" si="4"/>
-        <v>89</v>
-      </c>
-      <c r="I74" s="59">
+        <v>0.54999999999999982</v>
+      </c>
+      <c r="I74" s="67">
         <f t="shared" si="4"/>
-        <v>76</v>
-      </c>
-      <c r="J74" s="59">
+        <v>1.2000000000000002</v>
+      </c>
+      <c r="J74" s="67">
         <f t="shared" si="4"/>
-        <v>75</v>
-      </c>
-      <c r="K74" s="59">
+        <v>1.25</v>
+      </c>
+      <c r="K74" s="67">
         <f t="shared" si="4"/>
-        <v>74</v>
-      </c>
-      <c r="L74" s="59">
+        <v>1.2999999999999998</v>
+      </c>
+      <c r="L74" s="67">
         <f t="shared" si="4"/>
-        <v>74</v>
-      </c>
-      <c r="M74" s="59">
+        <v>1.2999999999999998</v>
+      </c>
+      <c r="M74" s="67">
         <f t="shared" si="4"/>
-        <v>74</v>
-      </c>
-      <c r="N74" s="59">
+        <v>1.2999999999999998</v>
+      </c>
+      <c r="N74" s="67">
         <f t="shared" si="4"/>
-        <v>27.999999999999996</v>
-      </c>
-      <c r="O74" s="59">
+        <v>3.6</v>
+      </c>
+      <c r="O74" s="67">
         <f t="shared" si="4"/>
-        <v>27.999999999999996</v>
-      </c>
-      <c r="P74" s="59">
+        <v>3.6</v>
+      </c>
+      <c r="P74" s="67">
         <f t="shared" si="4"/>
-        <v>27.999999999999996</v>
-      </c>
-    </row>
-    <row r="75" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B75" s="60" t="str">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B75" s="59" t="str">
         <f>B$155</f>
         <v>Q1</v>
       </c>
-      <c r="C75" s="60" t="str">
+      <c r="C75" s="59" t="str">
         <f t="shared" ref="C75:F75" si="5">C$155</f>
         <v>Q2</v>
       </c>
-      <c r="D75" s="60" t="str">
+      <c r="D75" s="59" t="str">
         <f t="shared" si="5"/>
         <v>Q3</v>
       </c>
-      <c r="E75" s="60" t="str">
+      <c r="E75" s="59" t="str">
         <f t="shared" si="5"/>
         <v>Q4</v>
       </c>
-      <c r="F75" s="60" t="str">
+      <c r="F75" s="59" t="str">
         <f t="shared" si="5"/>
         <v>Q1'27</v>
       </c>
     </row>
-    <row r="76" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="60" t="str">
+    <row r="76" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="59" t="str">
         <f>$A$156</f>
         <v>% Plan</v>
       </c>
-      <c r="B76" s="60">
+      <c r="B76" s="59">
         <f>(AVERAGE(B73:D73)/AVERAGE(B72:D72))*100</f>
         <v>67.631578947368425</v>
       </c>
-      <c r="C76" s="60">
+      <c r="C76" s="59">
         <f>(AVERAGE(E73:G73)/AVERAGE(E72:G72))*100</f>
         <v>85.000000000000014</v>
       </c>
-      <c r="D76" s="60">
+      <c r="D76" s="59">
         <f>(AVERAGE(H73:J73)/AVERAGE(H72:J72))*100</f>
         <v>80</v>
       </c>
-      <c r="E76" s="60">
+      <c r="E76" s="59">
         <f>(AVERAGE(K73:M73)/AVERAGE(K72:M72))*100</f>
         <v>74.000000000000014</v>
       </c>
-      <c r="F76" s="60">
+      <c r="F76" s="59">
         <f>(AVERAGE(N73:P73)/AVERAGE(N72:P72))*100</f>
         <v>27.999999999999993</v>
       </c>
@@ -5202,116 +5191,115 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="84" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="59" t="str">
-        <f>$A$152</f>
-        <v>% Plan</v>
-      </c>
-      <c r="B84" s="59">
-        <f>(B83/B82)*100</f>
-        <v>77.5</v>
-      </c>
-      <c r="C84" s="59">
-        <f t="shared" ref="C84:P84" si="6">(C83/C82)*100</f>
-        <v>80</v>
-      </c>
-      <c r="D84" s="59">
+    <row r="84" spans="1:16" s="66" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="B84" s="67">
+        <f>B82-B83</f>
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="C84" s="67">
+        <f t="shared" ref="C84:P84" si="6">C82-C83</f>
+        <v>0.79999999999999982</v>
+      </c>
+      <c r="D84" s="67">
         <f t="shared" si="6"/>
-        <v>74.6875</v>
-      </c>
-      <c r="E84" s="59">
+        <v>1.0125000000000002</v>
+      </c>
+      <c r="E84" s="67">
         <f t="shared" si="6"/>
-        <v>90</v>
-      </c>
-      <c r="F84" s="59">
+        <v>0.39999999999999991</v>
+      </c>
+      <c r="F84" s="67">
         <f t="shared" si="6"/>
-        <v>103.49999999999999</v>
-      </c>
-      <c r="G84" s="59">
+        <v>-0.10499999999999998</v>
+      </c>
+      <c r="G84" s="67">
         <f t="shared" si="6"/>
-        <v>104.16666666666667</v>
-      </c>
-      <c r="H84" s="59">
+        <v>-0.125</v>
+      </c>
+      <c r="H84" s="67">
         <f t="shared" si="6"/>
-        <v>104.16666666666667</v>
-      </c>
-      <c r="I84" s="59">
+        <v>-0.125</v>
+      </c>
+      <c r="I84" s="67">
         <f t="shared" si="6"/>
-        <v>104.16666666666667</v>
-      </c>
-      <c r="J84" s="59">
+        <v>-0.125</v>
+      </c>
+      <c r="J84" s="67">
         <f t="shared" si="6"/>
-        <v>85.833333333333343</v>
-      </c>
-      <c r="K84" s="59">
+        <v>0.42499999999999982</v>
+      </c>
+      <c r="K84" s="67">
         <f t="shared" si="6"/>
-        <v>95.833333333333343</v>
-      </c>
-      <c r="L84" s="59">
+        <v>0.125</v>
+      </c>
+      <c r="L84" s="67">
         <f t="shared" si="6"/>
-        <v>97.5</v>
-      </c>
-      <c r="M84" s="59">
+        <v>7.5000000000000178E-2</v>
+      </c>
+      <c r="M84" s="67">
         <f t="shared" si="6"/>
-        <v>87.5</v>
-      </c>
-      <c r="N84" s="59">
+        <v>0.375</v>
+      </c>
+      <c r="N84" s="67">
         <f t="shared" si="6"/>
-        <v>13.333333333333334</v>
-      </c>
-      <c r="O84" s="59">
+        <v>2.6</v>
+      </c>
+      <c r="O84" s="67">
         <f t="shared" si="6"/>
-        <v>13.333333333333334</v>
-      </c>
-      <c r="P84" s="59">
+        <v>2.6</v>
+      </c>
+      <c r="P84" s="67">
         <f t="shared" si="6"/>
-        <v>13.333333333333334</v>
-      </c>
-    </row>
-    <row r="85" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B85" s="60" t="str">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B85" s="59" t="str">
         <f>B$155</f>
         <v>Q1</v>
       </c>
-      <c r="C85" s="60" t="str">
+      <c r="C85" s="59" t="str">
         <f t="shared" ref="C85:F85" si="7">C$155</f>
         <v>Q2</v>
       </c>
-      <c r="D85" s="60" t="str">
+      <c r="D85" s="59" t="str">
         <f t="shared" si="7"/>
         <v>Q3</v>
       </c>
-      <c r="E85" s="60" t="str">
+      <c r="E85" s="59" t="str">
         <f t="shared" si="7"/>
         <v>Q4</v>
       </c>
-      <c r="F85" s="60" t="str">
+      <c r="F85" s="59" t="str">
         <f t="shared" si="7"/>
         <v>Q1'27</v>
       </c>
     </row>
-    <row r="86" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="60" t="str">
+    <row r="86" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="59" t="str">
         <f>$A$156</f>
         <v>% Plan</v>
       </c>
-      <c r="B86" s="60">
+      <c r="B86" s="59">
         <f>(AVERAGE(B83:D83)/AVERAGE(B82:D82))*100</f>
         <v>77.395833333333343</v>
       </c>
-      <c r="C86" s="60">
+      <c r="C86" s="59">
         <f>(AVERAGE(E83:G83)/AVERAGE(E82:G82))*100</f>
         <v>98.3</v>
       </c>
-      <c r="D86" s="60">
+      <c r="D86" s="59">
         <f>(AVERAGE(H83:J83)/AVERAGE(H82:J82))*100</f>
         <v>98.055555555555557</v>
       </c>
-      <c r="E86" s="60">
+      <c r="E86" s="59">
         <f>(AVERAGE(K83:M83)/AVERAGE(K82:M82))*100</f>
         <v>93.611111111111128</v>
       </c>
-      <c r="F86" s="60">
+      <c r="F86" s="59">
         <f>(AVERAGE(N83:P83)/AVERAGE(N82:P82))*100</f>
         <v>13.333333333333336</v>
       </c>
@@ -5514,113 +5502,112 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="59" t="str">
-        <f>$A$152</f>
-        <v>% Plan</v>
-      </c>
-      <c r="B94" s="59">
-        <f>(B93/B92)*100</f>
-        <v>60</v>
-      </c>
-      <c r="C94" s="59">
-        <f t="shared" ref="C94:D94" si="8">(C93/C92)*100</f>
-        <v>60</v>
-      </c>
-      <c r="D94" s="59">
+    <row r="94" spans="1:16" s="66" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="B94" s="67">
+        <f>B92-B93</f>
+        <v>0.4</v>
+      </c>
+      <c r="C94" s="67">
+        <f t="shared" ref="C94:P94" si="8">C92-C93</f>
+        <v>0.4</v>
+      </c>
+      <c r="D94" s="67">
         <f t="shared" si="8"/>
-        <v>40</v>
-      </c>
-      <c r="E94" s="62">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="F94" s="62">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="G94" s="62">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="H94" s="62">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="I94" s="62">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="J94" s="62">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="K94" s="62">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="L94" s="62">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="M94" s="62">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="N94" s="62">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="O94" s="62">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="P94" s="62">
-        <f>0</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B95" s="60" t="str">
+        <v>0.6</v>
+      </c>
+      <c r="E94" s="67">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F94" s="67">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="G94" s="67">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="H94" s="67">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="I94" s="67">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J94" s="67">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K94" s="67">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="L94" s="67">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M94" s="67">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="N94" s="67">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="O94" s="67">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="P94" s="67">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B95" s="59" t="str">
         <f>B$155</f>
         <v>Q1</v>
       </c>
-      <c r="C95" s="60" t="str">
+      <c r="C95" s="59" t="str">
         <f t="shared" ref="C95:F95" si="9">C$155</f>
         <v>Q2</v>
       </c>
-      <c r="D95" s="60" t="str">
+      <c r="D95" s="59" t="str">
         <f t="shared" si="9"/>
         <v>Q3</v>
       </c>
-      <c r="E95" s="60" t="str">
+      <c r="E95" s="59" t="str">
         <f t="shared" si="9"/>
         <v>Q4</v>
       </c>
-      <c r="F95" s="60" t="str">
+      <c r="F95" s="59" t="str">
         <f t="shared" si="9"/>
         <v>Q1'27</v>
       </c>
     </row>
-    <row r="96" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="60" t="str">
+    <row r="96" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="59" t="str">
         <f>$A$156</f>
         <v>% Plan</v>
       </c>
-      <c r="B96" s="60">
+      <c r="B96" s="59">
         <f>(AVERAGE(B93:D93)/AVERAGE(B92:D92))*100</f>
         <v>53.333333333333336</v>
       </c>
-      <c r="C96" s="61">
-        <v>0</v>
-      </c>
-      <c r="D96" s="61">
-        <v>0</v>
-      </c>
-      <c r="E96" s="61">
-        <v>0</v>
-      </c>
-      <c r="F96" s="61">
+      <c r="C96" s="60">
+        <v>0</v>
+      </c>
+      <c r="D96" s="60">
+        <v>0</v>
+      </c>
+      <c r="E96" s="60">
+        <v>0</v>
+      </c>
+      <c r="F96" s="60">
         <v>0</v>
       </c>
     </row>
@@ -9892,116 +9879,115 @@
         <v>4</v>
       </c>
     </row>
-    <row r="54" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="59" t="str">
-        <f>$A$152</f>
-        <v>% Plan</v>
-      </c>
-      <c r="B54" s="59">
-        <f>(B53/B52)*100</f>
-        <v>100</v>
-      </c>
-      <c r="C54" s="59">
-        <f t="shared" ref="C54:P54" si="0">(C53/C52)*100</f>
-        <v>100</v>
-      </c>
-      <c r="D54" s="59">
+    <row r="54" spans="1:16" s="66" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="B54" s="67">
+        <f>B52-B53</f>
+        <v>0</v>
+      </c>
+      <c r="C54" s="67">
+        <f t="shared" ref="C54:P54" si="0">C52-C53</f>
+        <v>0</v>
+      </c>
+      <c r="D54" s="67">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="E54" s="59">
+        <v>0</v>
+      </c>
+      <c r="E54" s="67">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="F54" s="59">
+        <v>0</v>
+      </c>
+      <c r="F54" s="67">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="G54" s="59">
+        <v>0</v>
+      </c>
+      <c r="G54" s="67">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="H54" s="59">
+        <v>0</v>
+      </c>
+      <c r="H54" s="67">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="I54" s="59">
+        <v>0</v>
+      </c>
+      <c r="I54" s="67">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="J54" s="59">
+        <v>0</v>
+      </c>
+      <c r="J54" s="67">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="K54" s="59">
+        <v>0</v>
+      </c>
+      <c r="K54" s="67">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="L54" s="59">
+        <v>0</v>
+      </c>
+      <c r="L54" s="67">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="M54" s="59">
+        <v>0</v>
+      </c>
+      <c r="M54" s="67">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="N54" s="59">
+        <v>0</v>
+      </c>
+      <c r="N54" s="67">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="O54" s="59">
+        <v>0</v>
+      </c>
+      <c r="O54" s="67">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="P54" s="59">
+        <v>0</v>
+      </c>
+      <c r="P54" s="67">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="60" t="str">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B55" s="59" t="str">
         <f>B$155</f>
         <v>Q1</v>
       </c>
-      <c r="C55" s="60" t="str">
+      <c r="C55" s="59" t="str">
         <f t="shared" ref="C55:F55" si="1">C$155</f>
         <v>Q2</v>
       </c>
-      <c r="D55" s="60" t="str">
+      <c r="D55" s="59" t="str">
         <f t="shared" si="1"/>
         <v>Q3</v>
       </c>
-      <c r="E55" s="60" t="str">
+      <c r="E55" s="59" t="str">
         <f t="shared" si="1"/>
         <v>Q4</v>
       </c>
-      <c r="F55" s="60" t="str">
+      <c r="F55" s="59" t="str">
         <f t="shared" si="1"/>
         <v>Q1'27</v>
       </c>
     </row>
-    <row r="56" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="60" t="str">
+    <row r="56" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="59" t="str">
         <f>$A$156</f>
         <v>% Plan</v>
       </c>
-      <c r="B56" s="60">
+      <c r="B56" s="59">
         <f>(AVERAGE(B53:D53)/AVERAGE(B52:D52))*100</f>
         <v>100</v>
       </c>
-      <c r="C56" s="60">
+      <c r="C56" s="59">
         <f>(AVERAGE(E53:G53)/AVERAGE(E52:G52))*100</f>
         <v>100</v>
       </c>
-      <c r="D56" s="60">
+      <c r="D56" s="59">
         <f>(AVERAGE(H53:J53)/AVERAGE(H52:J52))*100</f>
         <v>100</v>
       </c>
-      <c r="E56" s="60">
+      <c r="E56" s="59">
         <f>(AVERAGE(K53:M53)/AVERAGE(K52:M52))*100</f>
         <v>100</v>
       </c>
-      <c r="F56" s="60">
+      <c r="F56" s="59">
         <f>(AVERAGE(N53:P53)/AVERAGE(N52:P52))*100</f>
         <v>100</v>
       </c>
@@ -10204,116 +10190,115 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="59" t="str">
-        <f>$A$152</f>
-        <v>% Plan</v>
-      </c>
-      <c r="B64" s="59">
-        <f>(B63/B62)*100</f>
-        <v>100</v>
-      </c>
-      <c r="C64" s="59">
-        <f t="shared" ref="C64:P64" si="2">(C63/C62)*100</f>
-        <v>100</v>
-      </c>
-      <c r="D64" s="59">
+    <row r="64" spans="1:16" s="66" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="B64" s="67">
+        <f>B62-B63</f>
+        <v>0</v>
+      </c>
+      <c r="C64" s="67">
+        <f t="shared" ref="C64:P64" si="2">C62-C63</f>
+        <v>0</v>
+      </c>
+      <c r="D64" s="67">
         <f t="shared" si="2"/>
-        <v>100</v>
-      </c>
-      <c r="E64" s="59">
+        <v>0</v>
+      </c>
+      <c r="E64" s="67">
         <f t="shared" si="2"/>
-        <v>100</v>
-      </c>
-      <c r="F64" s="59">
+        <v>0</v>
+      </c>
+      <c r="F64" s="67">
         <f t="shared" si="2"/>
-        <v>100</v>
-      </c>
-      <c r="G64" s="59">
+        <v>0</v>
+      </c>
+      <c r="G64" s="67">
         <f t="shared" si="2"/>
-        <v>100</v>
-      </c>
-      <c r="H64" s="59">
+        <v>0</v>
+      </c>
+      <c r="H64" s="67">
         <f t="shared" si="2"/>
-        <v>100</v>
-      </c>
-      <c r="I64" s="59">
+        <v>0</v>
+      </c>
+      <c r="I64" s="67">
         <f t="shared" si="2"/>
-        <v>100</v>
-      </c>
-      <c r="J64" s="59">
+        <v>0</v>
+      </c>
+      <c r="J64" s="67">
         <f t="shared" si="2"/>
-        <v>100</v>
-      </c>
-      <c r="K64" s="59">
+        <v>0</v>
+      </c>
+      <c r="K64" s="67">
         <f t="shared" si="2"/>
-        <v>100</v>
-      </c>
-      <c r="L64" s="59">
+        <v>0</v>
+      </c>
+      <c r="L64" s="67">
         <f t="shared" si="2"/>
-        <v>100</v>
-      </c>
-      <c r="M64" s="59">
+        <v>0</v>
+      </c>
+      <c r="M64" s="67">
         <f t="shared" si="2"/>
-        <v>100</v>
-      </c>
-      <c r="N64" s="59">
+        <v>0</v>
+      </c>
+      <c r="N64" s="67">
         <f t="shared" si="2"/>
-        <v>100</v>
-      </c>
-      <c r="O64" s="59">
+        <v>0</v>
+      </c>
+      <c r="O64" s="67">
         <f t="shared" si="2"/>
-        <v>100</v>
-      </c>
-      <c r="P64" s="59">
+        <v>0</v>
+      </c>
+      <c r="P64" s="67">
         <f t="shared" si="2"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B65" s="60" t="str">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B65" s="59" t="str">
         <f>B$155</f>
         <v>Q1</v>
       </c>
-      <c r="C65" s="60" t="str">
+      <c r="C65" s="59" t="str">
         <f t="shared" ref="C65:F65" si="3">C$155</f>
         <v>Q2</v>
       </c>
-      <c r="D65" s="60" t="str">
+      <c r="D65" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Q3</v>
       </c>
-      <c r="E65" s="60" t="str">
+      <c r="E65" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Q4</v>
       </c>
-      <c r="F65" s="60" t="str">
+      <c r="F65" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Q1'27</v>
       </c>
     </row>
-    <row r="66" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="60" t="str">
+    <row r="66" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="59" t="str">
         <f>$A$156</f>
         <v>% Plan</v>
       </c>
-      <c r="B66" s="60">
+      <c r="B66" s="59">
         <f>(AVERAGE(B63:D63)/AVERAGE(B62:D62))*100</f>
         <v>100</v>
       </c>
-      <c r="C66" s="60">
+      <c r="C66" s="59">
         <f>(AVERAGE(E63:G63)/AVERAGE(E62:G62))*100</f>
         <v>100</v>
       </c>
-      <c r="D66" s="60">
+      <c r="D66" s="59">
         <f>(AVERAGE(H63:J63)/AVERAGE(H62:J62))*100</f>
         <v>100</v>
       </c>
-      <c r="E66" s="60">
+      <c r="E66" s="59">
         <f>(AVERAGE(K63:M63)/AVERAGE(K62:M62))*100</f>
         <v>100</v>
       </c>
-      <c r="F66" s="60">
+      <c r="F66" s="59">
         <f>(AVERAGE(N63:P63)/AVERAGE(N62:P62))*100</f>
         <v>100</v>
       </c>
@@ -10516,116 +10501,115 @@
         <v>3</v>
       </c>
     </row>
-    <row r="74" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="59" t="str">
-        <f>$A$152</f>
-        <v>% Plan</v>
-      </c>
-      <c r="B74" s="59">
-        <f>(B73/B72)*100</f>
-        <v>100</v>
-      </c>
-      <c r="C74" s="59">
-        <f t="shared" ref="C74:P74" si="4">(C73/C72)*100</f>
-        <v>100</v>
-      </c>
-      <c r="D74" s="59">
+    <row r="74" spans="1:16" s="66" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="B74" s="67">
+        <f>B72-B73</f>
+        <v>0</v>
+      </c>
+      <c r="C74" s="67">
+        <f t="shared" ref="C74:P74" si="4">C72-C73</f>
+        <v>0</v>
+      </c>
+      <c r="D74" s="67">
         <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-      <c r="E74" s="59">
+        <v>0</v>
+      </c>
+      <c r="E74" s="67">
         <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-      <c r="F74" s="59">
+        <v>0</v>
+      </c>
+      <c r="F74" s="67">
         <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-      <c r="G74" s="59">
+        <v>0</v>
+      </c>
+      <c r="G74" s="67">
         <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-      <c r="H74" s="59">
+        <v>0</v>
+      </c>
+      <c r="H74" s="67">
         <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-      <c r="I74" s="59">
+        <v>0</v>
+      </c>
+      <c r="I74" s="67">
         <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-      <c r="J74" s="59">
+        <v>0</v>
+      </c>
+      <c r="J74" s="67">
         <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-      <c r="K74" s="59">
+        <v>0</v>
+      </c>
+      <c r="K74" s="67">
         <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-      <c r="L74" s="59">
+        <v>0</v>
+      </c>
+      <c r="L74" s="67">
         <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-      <c r="M74" s="59">
+        <v>0</v>
+      </c>
+      <c r="M74" s="67">
         <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-      <c r="N74" s="59">
+        <v>0</v>
+      </c>
+      <c r="N74" s="67">
         <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-      <c r="O74" s="59">
+        <v>0</v>
+      </c>
+      <c r="O74" s="67">
         <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-      <c r="P74" s="59">
+        <v>0</v>
+      </c>
+      <c r="P74" s="67">
         <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="75" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B75" s="60" t="str">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B75" s="59" t="str">
         <f>B$155</f>
         <v>Q1</v>
       </c>
-      <c r="C75" s="60" t="str">
+      <c r="C75" s="59" t="str">
         <f t="shared" ref="C75:F75" si="5">C$155</f>
         <v>Q2</v>
       </c>
-      <c r="D75" s="60" t="str">
+      <c r="D75" s="59" t="str">
         <f t="shared" si="5"/>
         <v>Q3</v>
       </c>
-      <c r="E75" s="60" t="str">
+      <c r="E75" s="59" t="str">
         <f t="shared" si="5"/>
         <v>Q4</v>
       </c>
-      <c r="F75" s="60" t="str">
+      <c r="F75" s="59" t="str">
         <f t="shared" si="5"/>
         <v>Q1'27</v>
       </c>
     </row>
-    <row r="76" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="60" t="str">
+    <row r="76" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="59" t="str">
         <f>$A$156</f>
         <v>% Plan</v>
       </c>
-      <c r="B76" s="60">
+      <c r="B76" s="59">
         <f>(AVERAGE(B73:D73)/AVERAGE(B72:D72))*100</f>
         <v>100</v>
       </c>
-      <c r="C76" s="60">
+      <c r="C76" s="59">
         <f>(AVERAGE(E73:G73)/AVERAGE(E72:G72))*100</f>
         <v>100</v>
       </c>
-      <c r="D76" s="60">
+      <c r="D76" s="59">
         <f>(AVERAGE(H73:J73)/AVERAGE(H72:J72))*100</f>
         <v>100</v>
       </c>
-      <c r="E76" s="60">
+      <c r="E76" s="59">
         <f>(AVERAGE(K73:M73)/AVERAGE(K72:M72))*100</f>
         <v>100</v>
       </c>
-      <c r="F76" s="60">
+      <c r="F76" s="59">
         <f>(AVERAGE(N73:P73)/AVERAGE(N72:P72))*100</f>
         <v>100</v>
       </c>
@@ -10828,116 +10812,115 @@
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="59" t="str">
-        <f>$A$152</f>
-        <v>% Plan</v>
-      </c>
-      <c r="B84" s="59">
-        <f>(B83/B82)*100</f>
-        <v>100</v>
-      </c>
-      <c r="C84" s="59">
-        <f t="shared" ref="C84:P84" si="6">(C83/C82)*100</f>
-        <v>100</v>
-      </c>
-      <c r="D84" s="59">
+    <row r="84" spans="1:16" s="66" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="B84" s="67">
+        <f>B82-B83</f>
+        <v>0</v>
+      </c>
+      <c r="C84" s="67">
+        <f t="shared" ref="C84:P84" si="6">C82-C83</f>
+        <v>0</v>
+      </c>
+      <c r="D84" s="67">
         <f t="shared" si="6"/>
-        <v>100</v>
-      </c>
-      <c r="E84" s="59">
+        <v>0</v>
+      </c>
+      <c r="E84" s="67">
         <f t="shared" si="6"/>
-        <v>100</v>
-      </c>
-      <c r="F84" s="59">
+        <v>0</v>
+      </c>
+      <c r="F84" s="67">
         <f t="shared" si="6"/>
-        <v>100</v>
-      </c>
-      <c r="G84" s="59">
+        <v>0</v>
+      </c>
+      <c r="G84" s="67">
         <f t="shared" si="6"/>
-        <v>100</v>
-      </c>
-      <c r="H84" s="59">
+        <v>0</v>
+      </c>
+      <c r="H84" s="67">
         <f t="shared" si="6"/>
-        <v>100</v>
-      </c>
-      <c r="I84" s="59">
+        <v>0</v>
+      </c>
+      <c r="I84" s="67">
         <f t="shared" si="6"/>
-        <v>100</v>
-      </c>
-      <c r="J84" s="59">
+        <v>0</v>
+      </c>
+      <c r="J84" s="67">
         <f t="shared" si="6"/>
-        <v>100</v>
-      </c>
-      <c r="K84" s="59">
+        <v>0</v>
+      </c>
+      <c r="K84" s="67">
         <f t="shared" si="6"/>
-        <v>100</v>
-      </c>
-      <c r="L84" s="59">
+        <v>0</v>
+      </c>
+      <c r="L84" s="67">
         <f t="shared" si="6"/>
-        <v>100</v>
-      </c>
-      <c r="M84" s="59">
+        <v>0</v>
+      </c>
+      <c r="M84" s="67">
         <f t="shared" si="6"/>
-        <v>100</v>
-      </c>
-      <c r="N84" s="59">
+        <v>0</v>
+      </c>
+      <c r="N84" s="67">
         <f t="shared" si="6"/>
-        <v>100</v>
-      </c>
-      <c r="O84" s="59">
+        <v>0</v>
+      </c>
+      <c r="O84" s="67">
         <f t="shared" si="6"/>
-        <v>100</v>
-      </c>
-      <c r="P84" s="59">
+        <v>0</v>
+      </c>
+      <c r="P84" s="67">
         <f t="shared" si="6"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="85" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B85" s="60" t="str">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B85" s="59" t="str">
         <f>B$155</f>
         <v>Q1</v>
       </c>
-      <c r="C85" s="60" t="str">
+      <c r="C85" s="59" t="str">
         <f t="shared" ref="C85:F85" si="7">C$155</f>
         <v>Q2</v>
       </c>
-      <c r="D85" s="60" t="str">
+      <c r="D85" s="59" t="str">
         <f t="shared" si="7"/>
         <v>Q3</v>
       </c>
-      <c r="E85" s="60" t="str">
+      <c r="E85" s="59" t="str">
         <f t="shared" si="7"/>
         <v>Q4</v>
       </c>
-      <c r="F85" s="60" t="str">
+      <c r="F85" s="59" t="str">
         <f t="shared" si="7"/>
         <v>Q1'27</v>
       </c>
     </row>
-    <row r="86" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="60" t="str">
+    <row r="86" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="59" t="str">
         <f>$A$156</f>
         <v>% Plan</v>
       </c>
-      <c r="B86" s="60">
+      <c r="B86" s="59">
         <f>(AVERAGE(B83:D83)/AVERAGE(B82:D82))*100</f>
         <v>100</v>
       </c>
-      <c r="C86" s="60">
+      <c r="C86" s="59">
         <f>(AVERAGE(E83:G83)/AVERAGE(E82:G82))*100</f>
         <v>100</v>
       </c>
-      <c r="D86" s="60">
+      <c r="D86" s="59">
         <f>(AVERAGE(H83:J83)/AVERAGE(H82:J82))*100</f>
         <v>100</v>
       </c>
-      <c r="E86" s="60">
+      <c r="E86" s="59">
         <f>(AVERAGE(K83:M83)/AVERAGE(K82:M82))*100</f>
         <v>100</v>
       </c>
-      <c r="F86" s="60">
+      <c r="F86" s="59">
         <f>(AVERAGE(N83:P83)/AVERAGE(N82:P82))*100</f>
         <v>100</v>
       </c>
@@ -13783,23 +13766,23 @@
         <f>IF(Project!A21&gt;0,Project!A21,"")</f>
         <v>Group Name</v>
       </c>
-      <c r="B21" s="63" t="str">
+      <c r="B21" s="61" t="str">
         <f>IF(Project!A22&gt;0,Project!A22,"")</f>
         <v>IT Dist</v>
       </c>
-      <c r="C21" s="64" t="str">
+      <c r="C21" s="62" t="str">
         <f>IF(Project!A23&gt;0,Project!A23,"")</f>
         <v>SCGP e-Ordering</v>
       </c>
-      <c r="D21" s="65" t="str">
+      <c r="D21" s="63" t="str">
         <f>IF(Project!A24&gt;0,Project!A24,"")</f>
         <v>CAP (Common AI Platform)</v>
       </c>
-      <c r="E21" s="67" t="str">
+      <c r="E21" s="65" t="str">
         <f>IF(Project!A25&gt;0,Project!A25,"")</f>
         <v>PromptPlus</v>
       </c>
-      <c r="F21" s="66" t="str">
+      <c r="F21" s="64" t="str">
         <f>IF(Project!A26&gt;0,Project!A26,"")</f>
         <v>WeShape platform</v>
       </c>
@@ -13809,23 +13792,23 @@
         <f>IF(Project!B21&gt;0,Project!B21,"")</f>
         <v>Presale</v>
       </c>
-      <c r="B22" s="63">
+      <c r="B22" s="61">
         <f>IF(Project!B22&gt;0,Project!B22,"")</f>
         <v>36</v>
       </c>
-      <c r="C22" s="64">
+      <c r="C22" s="62">
         <f>IF(Project!B23&gt;0,Project!B23,"")</f>
         <v>2.7</v>
       </c>
-      <c r="D22" s="65" t="str">
+      <c r="D22" s="63" t="str">
         <f>IF(Project!B24&gt;0,Project!B24,"")</f>
         <v/>
       </c>
-      <c r="E22" s="67" t="str">
+      <c r="E22" s="65" t="str">
         <f>IF(Project!B25&gt;0,Project!B25,"")</f>
         <v/>
       </c>
-      <c r="F22" s="66">
+      <c r="F22" s="64">
         <f>IF(Project!B26&gt;0,Project!B26,"")</f>
         <v>0.8</v>
       </c>
@@ -13835,23 +13818,23 @@
         <f>IF(Project!C21&gt;0,Project!C21,"")</f>
         <v>Project</v>
       </c>
-      <c r="B23" s="63" t="str">
+      <c r="B23" s="61" t="str">
         <f>IF(Project!C22&gt;0,Project!C22,"")</f>
         <v/>
       </c>
-      <c r="C23" s="64">
+      <c r="C23" s="62">
         <f>IF(Project!C23&gt;0,Project!C23,"")</f>
         <v>154.05000000000001</v>
       </c>
-      <c r="D23" s="65">
+      <c r="D23" s="63">
         <f>IF(Project!C24&gt;0,Project!C24,"")</f>
         <v>63.6</v>
       </c>
-      <c r="E23" s="67">
+      <c r="E23" s="65">
         <f>IF(Project!C25&gt;0,Project!C25,"")</f>
         <v>27.375</v>
       </c>
-      <c r="F23" s="66" t="str">
+      <c r="F23" s="64" t="str">
         <f>IF(Project!C26&gt;0,Project!C26,"")</f>
         <v/>
       </c>
@@ -13861,23 +13844,23 @@
         <f>IF(Project!D21&gt;0,Project!D21,"")</f>
         <v>TM</v>
       </c>
-      <c r="B24" s="63" t="str">
+      <c r="B24" s="61" t="str">
         <f>IF(Project!D22&gt;0,Project!D22,"")</f>
         <v/>
       </c>
-      <c r="C24" s="64">
+      <c r="C24" s="62">
         <f>IF(Project!D23&gt;0,Project!D23,"")</f>
         <v>5.13</v>
       </c>
-      <c r="D24" s="65" t="str">
+      <c r="D24" s="63" t="str">
         <f>IF(Project!D24&gt;0,Project!D24,"")</f>
         <v/>
       </c>
-      <c r="E24" s="67" t="str">
+      <c r="E24" s="65" t="str">
         <f>IF(Project!D25&gt;0,Project!D25,"")</f>
         <v/>
       </c>
-      <c r="F24" s="66" t="str">
+      <c r="F24" s="64" t="str">
         <f>IF(Project!D26&gt;0,Project!D26,"")</f>
         <v/>
       </c>
@@ -13887,23 +13870,23 @@
         <f>IF(Project!E21&gt;0,Project!E21,"")</f>
         <v>Infra</v>
       </c>
-      <c r="B25" s="63" t="str">
+      <c r="B25" s="61" t="str">
         <f>IF(Project!E22&gt;0,Project!E22,"")</f>
         <v/>
       </c>
-      <c r="C25" s="64">
+      <c r="C25" s="62">
         <f>IF(Project!E23&gt;0,Project!E23,"")</f>
         <v>0.9</v>
       </c>
-      <c r="D25" s="65" t="str">
+      <c r="D25" s="63" t="str">
         <f>IF(Project!E24&gt;0,Project!E24,"")</f>
         <v/>
       </c>
-      <c r="E25" s="67" t="str">
+      <c r="E25" s="65" t="str">
         <f>IF(Project!E25&gt;0,Project!E25,"")</f>
         <v/>
       </c>
-      <c r="F25" s="66" t="str">
+      <c r="F25" s="64" t="str">
         <f>IF(Project!E26&gt;0,Project!E26,"")</f>
         <v/>
       </c>
@@ -13913,23 +13896,23 @@
         <f>IF(Project!F21&gt;0,Project!F21,"")</f>
         <v>Spatial Lab</v>
       </c>
-      <c r="B26" s="63" t="str">
+      <c r="B26" s="61" t="str">
         <f>IF(Project!F22&gt;0,Project!F22,"")</f>
         <v/>
       </c>
-      <c r="C26" s="64" t="str">
+      <c r="C26" s="62" t="str">
         <f>IF(Project!F23&gt;0,Project!F23,"")</f>
         <v/>
       </c>
-      <c r="D26" s="65" t="str">
+      <c r="D26" s="63" t="str">
         <f>IF(Project!F24&gt;0,Project!F24,"")</f>
         <v/>
       </c>
-      <c r="E26" s="67" t="str">
+      <c r="E26" s="65" t="str">
         <f>IF(Project!F25&gt;0,Project!F25,"")</f>
         <v/>
       </c>
-      <c r="F26" s="66">
+      <c r="F26" s="64">
         <f>IF(Project!F26&gt;0,Project!F26,"")</f>
         <v>34.655000000000001</v>
       </c>
@@ -13939,23 +13922,23 @@
         <f>IF(Project!G21&gt;0,Project!G21,"")</f>
         <v>Warmbody</v>
       </c>
-      <c r="B27" s="63">
+      <c r="B27" s="61">
         <f>IF(Project!G22&gt;0,Project!G22,"")</f>
         <v>180</v>
       </c>
-      <c r="C27" s="64" t="str">
+      <c r="C27" s="62" t="str">
         <f>IF(Project!G23&gt;0,Project!G23,"")</f>
         <v/>
       </c>
-      <c r="D27" s="65" t="str">
+      <c r="D27" s="63" t="str">
         <f>IF(Project!G24&gt;0,Project!G24,"")</f>
         <v/>
       </c>
-      <c r="E27" s="67">
+      <c r="E27" s="65">
         <f>IF(Project!G25&gt;0,Project!G25,"")</f>
         <v>23.7</v>
       </c>
-      <c r="F27" s="66" t="str">
+      <c r="F27" s="64" t="str">
         <f>IF(Project!G26&gt;0,Project!G26,"")</f>
         <v/>
       </c>
@@ -13964,23 +13947,23 @@
       <c r="A28" s="58" t="s">
         <v>129</v>
       </c>
-      <c r="B28" s="63">
+      <c r="B28" s="61">
         <f>IF(Project!H22&gt;0,Project!H22,"")</f>
         <v>216</v>
       </c>
-      <c r="C28" s="64">
+      <c r="C28" s="62">
         <f>IF(Project!H23&gt;0,Project!H23,"")</f>
         <v>162.78</v>
       </c>
-      <c r="D28" s="65">
+      <c r="D28" s="63">
         <f>IF(Project!H24&gt;0,Project!H24,"")</f>
         <v>63.6</v>
       </c>
-      <c r="E28" s="67">
+      <c r="E28" s="65">
         <f>IF(Project!H25&gt;0,Project!H25,"")</f>
         <v>51.075000000000003</v>
       </c>
-      <c r="F28" s="66">
+      <c r="F28" s="64">
         <f>IF(Project!H26&gt;0,Project!H26,"")</f>
         <v>35.454999999999998</v>
       </c>
@@ -16212,7 +16195,7 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" s="8"/>
-      <c r="B12" s="17"/>
+      <c r="B12" s="18"/>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
@@ -19052,115 +19035,115 @@
         <v>8.1999999999999993</v>
       </c>
     </row>
-    <row r="54" spans="1:16" s="68" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="68" t="s">
-        <v>130</v>
-      </c>
-      <c r="B54" s="68">
+    <row r="54" spans="1:16" s="66" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="B54" s="67">
         <f>B52-B53</f>
         <v>0.75</v>
       </c>
-      <c r="C54" s="68">
+      <c r="C54" s="67">
         <f t="shared" ref="C54:P54" si="0">C52-C53</f>
         <v>0.65000000000000036</v>
       </c>
-      <c r="D54" s="68">
+      <c r="D54" s="67">
         <f t="shared" si="0"/>
         <v>0.94999999999999929</v>
       </c>
-      <c r="E54" s="68">
+      <c r="E54" s="67">
         <f t="shared" si="0"/>
         <v>-0.40000000000000036</v>
       </c>
-      <c r="F54" s="68">
+      <c r="F54" s="67">
         <f t="shared" si="0"/>
         <v>-0.5</v>
       </c>
-      <c r="G54" s="68">
+      <c r="G54" s="67">
         <f t="shared" si="0"/>
         <v>-0.40000000000000036</v>
       </c>
-      <c r="H54" s="68">
+      <c r="H54" s="67">
         <f t="shared" si="0"/>
         <v>0.80000000000000071</v>
       </c>
-      <c r="I54" s="68">
+      <c r="I54" s="67">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J54" s="68">
+      <c r="J54" s="67">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K54" s="68">
+      <c r="K54" s="67">
         <f t="shared" si="0"/>
         <v>1.0999999999999996</v>
       </c>
-      <c r="L54" s="68">
+      <c r="L54" s="67">
         <f t="shared" si="0"/>
         <v>1.3000000000000007</v>
       </c>
-      <c r="M54" s="68">
+      <c r="M54" s="67">
         <f t="shared" si="0"/>
         <v>1.3000000000000007</v>
       </c>
-      <c r="N54" s="68">
+      <c r="N54" s="67">
         <f t="shared" si="0"/>
         <v>2.8000000000000007</v>
       </c>
-      <c r="O54" s="68">
+      <c r="O54" s="67">
         <f t="shared" si="0"/>
         <v>2.8000000000000007</v>
       </c>
-      <c r="P54" s="68">
+      <c r="P54" s="67">
         <f t="shared" si="0"/>
         <v>2.8000000000000007</v>
       </c>
     </row>
-    <row r="55" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="60" t="str">
+    <row r="55" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B55" s="59" t="str">
         <f>B$155</f>
         <v>Q1</v>
       </c>
-      <c r="C55" s="60" t="str">
+      <c r="C55" s="59" t="str">
         <f t="shared" ref="C55:F55" si="1">C$155</f>
         <v>Q2</v>
       </c>
-      <c r="D55" s="60" t="str">
+      <c r="D55" s="59" t="str">
         <f t="shared" si="1"/>
         <v>Q3</v>
       </c>
-      <c r="E55" s="60" t="str">
+      <c r="E55" s="59" t="str">
         <f t="shared" si="1"/>
         <v>Q4</v>
       </c>
-      <c r="F55" s="60" t="str">
+      <c r="F55" s="59" t="str">
         <f t="shared" si="1"/>
         <v>Q1'27</v>
       </c>
     </row>
-    <row r="56" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="60" t="str">
+    <row r="56" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="59" t="str">
         <f>$A$156</f>
         <v>% Plan</v>
       </c>
-      <c r="B56" s="60">
+      <c r="B56" s="59">
         <f>(AVERAGE(B53:D53)/AVERAGE(B52:D52))*100</f>
         <v>93.472222222222229</v>
       </c>
-      <c r="C56" s="60">
+      <c r="C56" s="59">
         <f>(AVERAGE(E53:G53)/AVERAGE(E52:G52))*100</f>
         <v>103.93939393939394</v>
       </c>
-      <c r="D56" s="60">
+      <c r="D56" s="59">
         <f>(AVERAGE(H53:J53)/AVERAGE(H52:J52))*100</f>
         <v>91.515151515151516</v>
       </c>
-      <c r="E56" s="60">
+      <c r="E56" s="59">
         <f>(AVERAGE(K53:M53)/AVERAGE(K52:M52))*100</f>
         <v>88.787878787878796</v>
       </c>
-      <c r="F56" s="60">
+      <c r="F56" s="59">
         <f>(AVERAGE(N53:P53)/AVERAGE(N52:P52))*100</f>
         <v>74.545454545454533</v>
       </c>
@@ -19363,115 +19346,115 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:16" s="68" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="68" t="s">
-        <v>130</v>
-      </c>
-      <c r="B64" s="68">
+    <row r="64" spans="1:16" s="66" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="B64" s="67">
         <f>B62-B63</f>
         <v>0.40000000000000036</v>
       </c>
-      <c r="C64" s="68">
-        <f t="shared" ref="C64" si="2">C62-C63</f>
+      <c r="C64" s="67">
+        <f t="shared" ref="C64:P64" si="2">C62-C63</f>
         <v>0.40000000000000036</v>
       </c>
-      <c r="D64" s="68">
-        <f t="shared" ref="D64" si="3">D62-D63</f>
+      <c r="D64" s="67">
+        <f t="shared" si="2"/>
         <v>0.40000000000000036</v>
       </c>
-      <c r="E64" s="68">
-        <f t="shared" ref="E64" si="4">E62-E63</f>
-        <v>0</v>
-      </c>
-      <c r="F64" s="68">
-        <f t="shared" ref="F64" si="5">F62-F63</f>
-        <v>0</v>
-      </c>
-      <c r="G64" s="68">
-        <f t="shared" ref="G64" si="6">G62-G63</f>
-        <v>0</v>
-      </c>
-      <c r="H64" s="68">
-        <f t="shared" ref="H64" si="7">H62-H63</f>
-        <v>0</v>
-      </c>
-      <c r="I64" s="68">
-        <f t="shared" ref="I64" si="8">I62-I63</f>
-        <v>0</v>
-      </c>
-      <c r="J64" s="68">
-        <f t="shared" ref="J64" si="9">J62-J63</f>
-        <v>0</v>
-      </c>
-      <c r="K64" s="68">
-        <f t="shared" ref="K64" si="10">K62-K63</f>
-        <v>0</v>
-      </c>
-      <c r="L64" s="68">
-        <f t="shared" ref="L64" si="11">L62-L63</f>
-        <v>0</v>
-      </c>
-      <c r="M64" s="68">
-        <f t="shared" ref="M64" si="12">M62-M63</f>
-        <v>0</v>
-      </c>
-      <c r="N64" s="68">
-        <f t="shared" ref="N64" si="13">N62-N63</f>
-        <v>0</v>
-      </c>
-      <c r="O64" s="68">
-        <f t="shared" ref="O64" si="14">O62-O63</f>
-        <v>0</v>
-      </c>
-      <c r="P64" s="68">
-        <f t="shared" ref="P64" si="15">P62-P63</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B65" s="60" t="str">
+      <c r="E64" s="67">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F64" s="67">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G64" s="67">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H64" s="67">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I64" s="67">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J64" s="67">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K64" s="67">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L64" s="67">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M64" s="67">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N64" s="67">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O64" s="67">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P64" s="67">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B65" s="59" t="str">
         <f>B$155</f>
         <v>Q1</v>
       </c>
-      <c r="C65" s="60" t="str">
-        <f t="shared" ref="C65:F65" si="16">C$155</f>
+      <c r="C65" s="59" t="str">
+        <f t="shared" ref="C65:F65" si="3">C$155</f>
         <v>Q2</v>
       </c>
-      <c r="D65" s="60" t="str">
-        <f t="shared" si="16"/>
+      <c r="D65" s="59" t="str">
+        <f t="shared" si="3"/>
         <v>Q3</v>
       </c>
-      <c r="E65" s="60" t="str">
-        <f t="shared" si="16"/>
+      <c r="E65" s="59" t="str">
+        <f t="shared" si="3"/>
         <v>Q4</v>
       </c>
-      <c r="F65" s="60" t="str">
-        <f t="shared" si="16"/>
+      <c r="F65" s="59" t="str">
+        <f t="shared" si="3"/>
         <v>Q1'27</v>
       </c>
     </row>
-    <row r="66" spans="1:6" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="60" t="str">
+    <row r="66" spans="1:6" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="59" t="str">
         <f>$A$156</f>
         <v>% Plan</v>
       </c>
-      <c r="B66" s="60">
+      <c r="B66" s="59">
         <f>(AVERAGE(B63:D63)/AVERAGE(B62:D62))*100</f>
         <v>92</v>
       </c>
-      <c r="C66" s="60">
+      <c r="C66" s="59">
         <f>(AVERAGE(E63:G63)/AVERAGE(E62:G62))*100</f>
         <v>100</v>
       </c>
-      <c r="D66" s="60">
+      <c r="D66" s="59">
         <f>(AVERAGE(H63:J63)/AVERAGE(H62:J62))*100</f>
         <v>100</v>
       </c>
-      <c r="E66" s="60">
+      <c r="E66" s="59">
         <f>(AVERAGE(K63:M63)/AVERAGE(K62:M62))*100</f>
         <v>100</v>
       </c>
-      <c r="F66" s="60">
+      <c r="F66" s="59">
         <f>(AVERAGE(N63:P63)/AVERAGE(N62:P62))*100</f>
         <v>100</v>
       </c>
@@ -23638,116 +23621,115 @@
         <v>6</v>
       </c>
     </row>
-    <row r="54" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="59" t="str">
-        <f>$A$152</f>
-        <v>% Plan</v>
-      </c>
-      <c r="B54" s="59">
-        <f>(B53/B52)*100</f>
-        <v>100</v>
-      </c>
-      <c r="C54" s="59">
-        <f t="shared" ref="C54:P54" si="0">(C53/C52)*100</f>
-        <v>100</v>
-      </c>
-      <c r="D54" s="59">
+    <row r="54" spans="1:16" s="66" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="B54" s="67">
+        <f>B52-B53</f>
+        <v>0</v>
+      </c>
+      <c r="C54" s="67">
+        <f t="shared" ref="C54:P54" si="0">C52-C53</f>
+        <v>0</v>
+      </c>
+      <c r="D54" s="67">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="E54" s="59">
+        <v>0</v>
+      </c>
+      <c r="E54" s="67">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="F54" s="59">
+        <v>0</v>
+      </c>
+      <c r="F54" s="67">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="G54" s="59">
+        <v>0</v>
+      </c>
+      <c r="G54" s="67">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="H54" s="59">
+        <v>0</v>
+      </c>
+      <c r="H54" s="67">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="I54" s="59">
+        <v>0</v>
+      </c>
+      <c r="I54" s="67">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="J54" s="59">
+        <v>0</v>
+      </c>
+      <c r="J54" s="67">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="K54" s="59">
+        <v>0</v>
+      </c>
+      <c r="K54" s="67">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="L54" s="59">
+        <v>0</v>
+      </c>
+      <c r="L54" s="67">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="M54" s="59">
+        <v>0</v>
+      </c>
+      <c r="M54" s="67">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="N54" s="59">
+        <v>0</v>
+      </c>
+      <c r="N54" s="67">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="O54" s="59">
+        <v>0</v>
+      </c>
+      <c r="O54" s="67">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="P54" s="59">
+        <v>0</v>
+      </c>
+      <c r="P54" s="67">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="60" t="str">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B55" s="59" t="str">
         <f>B$155</f>
         <v>Q1</v>
       </c>
-      <c r="C55" s="60" t="str">
+      <c r="C55" s="59" t="str">
         <f t="shared" ref="C55:F55" si="1">C$155</f>
         <v>Q2</v>
       </c>
-      <c r="D55" s="60" t="str">
+      <c r="D55" s="59" t="str">
         <f t="shared" si="1"/>
         <v>Q3</v>
       </c>
-      <c r="E55" s="60" t="str">
+      <c r="E55" s="59" t="str">
         <f t="shared" si="1"/>
         <v>Q4</v>
       </c>
-      <c r="F55" s="60" t="str">
+      <c r="F55" s="59" t="str">
         <f t="shared" si="1"/>
         <v>Q1'27</v>
       </c>
     </row>
-    <row r="56" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="60" t="str">
+    <row r="56" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="59" t="str">
         <f>$A$156</f>
         <v>% Plan</v>
       </c>
-      <c r="B56" s="60">
+      <c r="B56" s="59">
         <f>(AVERAGE(B53:D53)/AVERAGE(B52:D52))*100</f>
         <v>100</v>
       </c>
-      <c r="C56" s="60">
+      <c r="C56" s="59">
         <f>(AVERAGE(E53:G53)/AVERAGE(E52:G52))*100</f>
         <v>100</v>
       </c>
-      <c r="D56" s="60">
+      <c r="D56" s="59">
         <f>(AVERAGE(H53:J53)/AVERAGE(H52:J52))*100</f>
         <v>100</v>
       </c>
-      <c r="E56" s="60">
+      <c r="E56" s="59">
         <f>(AVERAGE(K53:M53)/AVERAGE(K52:M52))*100</f>
         <v>100</v>
       </c>
-      <c r="F56" s="60">
+      <c r="F56" s="59">
         <f>(AVERAGE(N53:P53)/AVERAGE(N52:P52))*100</f>
         <v>100</v>
       </c>
@@ -23950,116 +23932,115 @@
         <v>24.65</v>
       </c>
     </row>
-    <row r="64" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="59" t="str">
-        <f>$A$152</f>
-        <v>% Plan</v>
-      </c>
-      <c r="B64" s="59">
-        <f>(B63/B62)*100</f>
-        <v>88.205128205128204</v>
-      </c>
-      <c r="C64" s="59">
-        <f t="shared" ref="C64:P64" si="2">(C63/C62)*100</f>
-        <v>93.230769230769226</v>
-      </c>
-      <c r="D64" s="59">
+    <row r="64" spans="1:16" s="66" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="B64" s="67">
+        <f>B62-B63</f>
+        <v>4.6000000000000014</v>
+      </c>
+      <c r="C64" s="67">
+        <f t="shared" ref="C64:P64" si="2">C62-C63</f>
+        <v>2.6400000000000006</v>
+      </c>
+      <c r="D64" s="67">
         <f t="shared" si="2"/>
-        <v>98.641025641025635</v>
-      </c>
-      <c r="E64" s="59">
+        <v>0.53000000000000114</v>
+      </c>
+      <c r="E64" s="67">
         <f t="shared" si="2"/>
-        <v>93.731707317073159</v>
-      </c>
-      <c r="F64" s="59">
+        <v>2.5700000000000003</v>
+      </c>
+      <c r="F64" s="67">
         <f t="shared" si="2"/>
-        <v>97.024390243902431</v>
-      </c>
-      <c r="G64" s="59">
+        <v>1.2199999999999989</v>
+      </c>
+      <c r="G64" s="67">
         <f t="shared" si="2"/>
-        <v>90.024390243902431</v>
-      </c>
-      <c r="H64" s="59">
+        <v>4.0900000000000034</v>
+      </c>
+      <c r="H64" s="67">
         <f t="shared" si="2"/>
-        <v>92.951219512195109</v>
-      </c>
-      <c r="I64" s="59">
+        <v>2.8900000000000006</v>
+      </c>
+      <c r="I64" s="67">
         <f t="shared" si="2"/>
-        <v>91.609756097560975</v>
-      </c>
-      <c r="J64" s="59">
+        <v>3.4399999999999977</v>
+      </c>
+      <c r="J64" s="67">
         <f t="shared" si="2"/>
-        <v>92.829268292682926</v>
-      </c>
-      <c r="K64" s="59">
+        <v>2.9399999999999977</v>
+      </c>
+      <c r="K64" s="67">
         <f t="shared" si="2"/>
-        <v>84.609756097560975</v>
-      </c>
-      <c r="L64" s="59">
+        <v>6.3100000000000023</v>
+      </c>
+      <c r="L64" s="67">
         <f t="shared" si="2"/>
-        <v>82.926829268292678</v>
-      </c>
-      <c r="M64" s="59">
+        <v>7</v>
+      </c>
+      <c r="M64" s="67">
         <f t="shared" si="2"/>
-        <v>82.926829268292678</v>
-      </c>
-      <c r="N64" s="59">
+        <v>7</v>
+      </c>
+      <c r="N64" s="67">
         <f t="shared" si="2"/>
-        <v>60.121951219512191</v>
-      </c>
-      <c r="O64" s="59">
+        <v>16.350000000000001</v>
+      </c>
+      <c r="O64" s="67">
         <f t="shared" si="2"/>
-        <v>60.121951219512191</v>
-      </c>
-      <c r="P64" s="59">
+        <v>16.350000000000001</v>
+      </c>
+      <c r="P64" s="67">
         <f t="shared" si="2"/>
-        <v>60.121951219512191</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B65" s="60" t="str">
+        <v>16.350000000000001</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B65" s="59" t="str">
         <f>B$155</f>
         <v>Q1</v>
       </c>
-      <c r="C65" s="60" t="str">
+      <c r="C65" s="59" t="str">
         <f t="shared" ref="C65:F65" si="3">C$155</f>
         <v>Q2</v>
       </c>
-      <c r="D65" s="60" t="str">
+      <c r="D65" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Q3</v>
       </c>
-      <c r="E65" s="60" t="str">
+      <c r="E65" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Q4</v>
       </c>
-      <c r="F65" s="60" t="str">
+      <c r="F65" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Q1'27</v>
       </c>
     </row>
-    <row r="66" spans="1:6" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="60" t="str">
+    <row r="66" spans="1:6" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="59" t="str">
         <f>$A$156</f>
         <v>% Plan</v>
       </c>
-      <c r="B66" s="60">
+      <c r="B66" s="59">
         <f>(AVERAGE(B63:D63)/AVERAGE(B62:D62))*100</f>
         <v>93.358974358974351</v>
       </c>
-      <c r="C66" s="60">
+      <c r="C66" s="59">
         <f>(AVERAGE(E63:G63)/AVERAGE(E62:G62))*100</f>
         <v>93.593495934959364</v>
       </c>
-      <c r="D66" s="60">
+      <c r="D66" s="59">
         <f>(AVERAGE(H63:J63)/AVERAGE(H62:J62))*100</f>
         <v>92.463414634146346</v>
       </c>
-      <c r="E66" s="60">
+      <c r="E66" s="59">
         <f>(AVERAGE(K63:M63)/AVERAGE(K62:M62))*100</f>
         <v>83.487804878048777</v>
       </c>
-      <c r="F66" s="60">
+      <c r="F66" s="59">
         <f>(AVERAGE(N63:P63)/AVERAGE(N62:P62))*100</f>
         <v>60.121951219512184</v>
       </c>
@@ -28968,116 +28949,115 @@
         <v>1.03125</v>
       </c>
     </row>
-    <row r="54" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="59" t="str">
-        <f>$A$152</f>
-        <v>% Plan</v>
-      </c>
-      <c r="B54" s="59">
-        <f>(B53/B52)*100</f>
-        <v>76.5625</v>
-      </c>
-      <c r="C54" s="59">
-        <f t="shared" ref="C54:P54" si="0">(C53/C52)*100</f>
-        <v>96.25</v>
-      </c>
-      <c r="D54" s="59">
+    <row r="54" spans="1:16" s="66" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="B54" s="67">
+        <f>B52-B53</f>
+        <v>0.9375</v>
+      </c>
+      <c r="C54" s="67">
+        <f t="shared" ref="C54:P54" si="0">C52-C53</f>
+        <v>0.14999999999999991</v>
+      </c>
+      <c r="D54" s="67">
         <f t="shared" si="0"/>
-        <v>91.25</v>
-      </c>
-      <c r="E54" s="59">
+        <v>0.35000000000000009</v>
+      </c>
+      <c r="E54" s="67">
         <f t="shared" si="0"/>
-        <v>82.5</v>
-      </c>
-      <c r="F54" s="59">
+        <v>0.70000000000000018</v>
+      </c>
+      <c r="F54" s="67">
         <f t="shared" si="0"/>
-        <v>100.62500000000001</v>
-      </c>
-      <c r="G54" s="59">
+        <v>-2.5000000000000355E-2</v>
+      </c>
+      <c r="G54" s="67">
         <f t="shared" si="0"/>
-        <v>100.62500000000001</v>
-      </c>
-      <c r="H54" s="59">
+        <v>-2.5000000000000355E-2</v>
+      </c>
+      <c r="H54" s="67">
         <f t="shared" si="0"/>
-        <v>99.53125</v>
-      </c>
-      <c r="I54" s="59">
+        <v>1.8749999999999822E-2</v>
+      </c>
+      <c r="I54" s="67">
         <f t="shared" si="0"/>
-        <v>82.34375</v>
-      </c>
-      <c r="J54" s="59">
+        <v>0.70624999999999982</v>
+      </c>
+      <c r="J54" s="67">
         <f t="shared" si="0"/>
-        <v>73.28125</v>
-      </c>
-      <c r="K54" s="59">
+        <v>1.0687500000000001</v>
+      </c>
+      <c r="K54" s="67">
         <f t="shared" si="0"/>
-        <v>67.8125</v>
-      </c>
-      <c r="L54" s="59">
+        <v>1.2875000000000001</v>
+      </c>
+      <c r="L54" s="67">
         <f t="shared" si="0"/>
-        <v>64.6875</v>
-      </c>
-      <c r="M54" s="59">
+        <v>1.4125000000000001</v>
+      </c>
+      <c r="M54" s="67">
         <f t="shared" si="0"/>
-        <v>59.687500000000007</v>
-      </c>
-      <c r="N54" s="59">
+        <v>1.6124999999999998</v>
+      </c>
+      <c r="N54" s="67">
         <f t="shared" si="0"/>
-        <v>32.03125</v>
-      </c>
-      <c r="O54" s="59">
+        <v>2.71875</v>
+      </c>
+      <c r="O54" s="67">
         <f t="shared" si="0"/>
-        <v>25.78125</v>
-      </c>
-      <c r="P54" s="59">
+        <v>2.96875</v>
+      </c>
+      <c r="P54" s="67">
         <f t="shared" si="0"/>
-        <v>25.78125</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="60" t="str">
+        <v>2.96875</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B55" s="59" t="str">
         <f>B$155</f>
         <v>Q1</v>
       </c>
-      <c r="C55" s="60" t="str">
+      <c r="C55" s="59" t="str">
         <f t="shared" ref="C55:F55" si="1">C$155</f>
         <v>Q2</v>
       </c>
-      <c r="D55" s="60" t="str">
+      <c r="D55" s="59" t="str">
         <f t="shared" si="1"/>
         <v>Q3</v>
       </c>
-      <c r="E55" s="60" t="str">
+      <c r="E55" s="59" t="str">
         <f t="shared" si="1"/>
         <v>Q4</v>
       </c>
-      <c r="F55" s="60" t="str">
+      <c r="F55" s="59" t="str">
         <f t="shared" si="1"/>
         <v>Q1'27</v>
       </c>
     </row>
-    <row r="56" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="60" t="str">
+    <row r="56" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="59" t="str">
         <f>$A$156</f>
         <v>% Plan</v>
       </c>
-      <c r="B56" s="60">
+      <c r="B56" s="59">
         <f>(AVERAGE(B53:D53)/AVERAGE(B52:D52))*100</f>
         <v>88.020833333333343</v>
       </c>
-      <c r="C56" s="60">
+      <c r="C56" s="59">
         <f>(AVERAGE(E53:G53)/AVERAGE(E52:G52))*100</f>
         <v>94.583333333333343</v>
       </c>
-      <c r="D56" s="60">
+      <c r="D56" s="59">
         <f>(AVERAGE(H53:J53)/AVERAGE(H52:J52))*100</f>
         <v>85.052083333333343</v>
       </c>
-      <c r="E56" s="60">
+      <c r="E56" s="59">
         <f>(AVERAGE(K53:M53)/AVERAGE(K52:M52))*100</f>
         <v>64.0625</v>
       </c>
-      <c r="F56" s="60">
+      <c r="F56" s="59">
         <f>(AVERAGE(N53:P53)/AVERAGE(N52:P52))*100</f>
         <v>27.864583333333332</v>
       </c>
@@ -29280,116 +29260,115 @@
         <v>4.3150000000000004</v>
       </c>
     </row>
-    <row r="64" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="59" t="str">
-        <f>$A$152</f>
-        <v>% Plan</v>
-      </c>
-      <c r="B64" s="59">
-        <f>(B63/B62)*100</f>
-        <v>101.07142857142857</v>
-      </c>
-      <c r="C64" s="59">
-        <f t="shared" ref="C64:P64" si="2">(C63/C62)*100</f>
-        <v>103.21428571428571</v>
-      </c>
-      <c r="D64" s="59">
+    <row r="64" spans="1:16" s="66" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="B64" s="67">
+        <f>B62-B63</f>
+        <v>-7.5000000000000178E-2</v>
+      </c>
+      <c r="C64" s="67">
+        <f t="shared" ref="C64:P64" si="2">C62-C63</f>
+        <v>-0.22499999999999964</v>
+      </c>
+      <c r="D64" s="67">
         <f t="shared" si="2"/>
-        <v>98.071428571428569</v>
-      </c>
-      <c r="E64" s="59">
+        <v>0.13499999999999979</v>
+      </c>
+      <c r="E64" s="67">
         <f t="shared" si="2"/>
-        <v>87.428571428571431</v>
-      </c>
-      <c r="F64" s="59">
+        <v>0.87999999999999989</v>
+      </c>
+      <c r="F64" s="67">
         <f t="shared" si="2"/>
-        <v>81.535714285714278</v>
-      </c>
-      <c r="G64" s="59">
+        <v>1.2925000000000004</v>
+      </c>
+      <c r="G64" s="67">
         <f t="shared" si="2"/>
-        <v>91.607142857142847</v>
-      </c>
-      <c r="H64" s="59">
+        <v>0.58750000000000036</v>
+      </c>
+      <c r="H64" s="67">
         <f t="shared" si="2"/>
-        <v>83.75</v>
-      </c>
-      <c r="I64" s="59">
+        <v>1.1375000000000002</v>
+      </c>
+      <c r="I64" s="67">
         <f t="shared" si="2"/>
-        <v>80.464285714285722</v>
-      </c>
-      <c r="J64" s="59">
+        <v>1.3674999999999997</v>
+      </c>
+      <c r="J64" s="67">
         <f t="shared" si="2"/>
-        <v>80.464285714285722</v>
-      </c>
-      <c r="K64" s="59">
+        <v>1.3674999999999997</v>
+      </c>
+      <c r="K64" s="67">
         <f t="shared" si="2"/>
-        <v>75.642857142857139</v>
-      </c>
-      <c r="L64" s="59">
+        <v>1.7050000000000001</v>
+      </c>
+      <c r="L64" s="67">
         <f t="shared" si="2"/>
-        <v>73.5</v>
-      </c>
-      <c r="M64" s="59">
+        <v>1.8550000000000004</v>
+      </c>
+      <c r="M64" s="67">
         <f t="shared" si="2"/>
-        <v>73.5</v>
-      </c>
-      <c r="N64" s="59">
+        <v>1.8550000000000004</v>
+      </c>
+      <c r="N64" s="67">
         <f t="shared" si="2"/>
-        <v>61.642857142857146</v>
-      </c>
-      <c r="O64" s="59">
+        <v>2.6849999999999996</v>
+      </c>
+      <c r="O64" s="67">
         <f t="shared" si="2"/>
-        <v>61.642857142857146</v>
-      </c>
-      <c r="P64" s="59">
+        <v>2.6849999999999996</v>
+      </c>
+      <c r="P64" s="67">
         <f t="shared" si="2"/>
-        <v>61.642857142857146</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B65" s="60" t="str">
+        <v>2.6849999999999996</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B65" s="59" t="str">
         <f>B$155</f>
         <v>Q1</v>
       </c>
-      <c r="C65" s="60" t="str">
+      <c r="C65" s="59" t="str">
         <f t="shared" ref="C65:F65" si="3">C$155</f>
         <v>Q2</v>
       </c>
-      <c r="D65" s="60" t="str">
+      <c r="D65" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Q3</v>
       </c>
-      <c r="E65" s="60" t="str">
+      <c r="E65" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Q4</v>
       </c>
-      <c r="F65" s="60" t="str">
+      <c r="F65" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Q1'27</v>
       </c>
     </row>
-    <row r="66" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="60" t="str">
+    <row r="66" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="59" t="str">
         <f>$A$156</f>
         <v>% Plan</v>
       </c>
-      <c r="B66" s="60">
+      <c r="B66" s="59">
         <f>(AVERAGE(B63:D63)/AVERAGE(B62:D62))*100</f>
         <v>100.78571428571428</v>
       </c>
-      <c r="C66" s="60">
+      <c r="C66" s="59">
         <f>(AVERAGE(E63:G63)/AVERAGE(E62:G62))*100</f>
         <v>86.857142857142861</v>
       </c>
-      <c r="D66" s="60">
+      <c r="D66" s="59">
         <f>(AVERAGE(H63:J63)/AVERAGE(H62:J62))*100</f>
         <v>81.55952380952381</v>
       </c>
-      <c r="E66" s="60">
+      <c r="E66" s="59">
         <f>(AVERAGE(K63:M63)/AVERAGE(K62:M62))*100</f>
         <v>74.214285714285708</v>
       </c>
-      <c r="F66" s="60">
+      <c r="F66" s="59">
         <f>(AVERAGE(N63:P63)/AVERAGE(N62:P62))*100</f>
         <v>61.642857142857146</v>
       </c>
@@ -29592,116 +29571,115 @@
         <v>2.78</v>
       </c>
     </row>
-    <row r="74" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="59" t="str">
-        <f>$A$152</f>
-        <v>% Plan</v>
-      </c>
-      <c r="B74" s="59">
-        <f>(B73/B72)*100</f>
-        <v>82.5</v>
-      </c>
-      <c r="C74" s="59">
-        <f t="shared" ref="C74:P74" si="4">(C73/C72)*100</f>
-        <v>109.375</v>
-      </c>
-      <c r="D74" s="59">
+    <row r="74" spans="1:16" s="66" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="B74" s="67">
+        <f>B72-B73</f>
+        <v>0.70000000000000018</v>
+      </c>
+      <c r="C74" s="67">
+        <f t="shared" ref="C74:P74" si="4">C72-C73</f>
+        <v>-0.375</v>
+      </c>
+      <c r="D74" s="67">
         <f t="shared" si="4"/>
-        <v>108.125</v>
-      </c>
-      <c r="E74" s="59">
+        <v>-0.32500000000000018</v>
+      </c>
+      <c r="E74" s="67">
         <f t="shared" si="4"/>
-        <v>97.5</v>
-      </c>
-      <c r="F74" s="59">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="F74" s="67">
         <f t="shared" si="4"/>
-        <v>87.875</v>
-      </c>
-      <c r="G74" s="59">
+        <v>0.48499999999999988</v>
+      </c>
+      <c r="G74" s="67">
         <f t="shared" si="4"/>
-        <v>86.625</v>
-      </c>
-      <c r="H74" s="59">
+        <v>0.53500000000000014</v>
+      </c>
+      <c r="H74" s="67">
         <f t="shared" si="4"/>
-        <v>84.125</v>
-      </c>
-      <c r="I74" s="59">
+        <v>0.63499999999999979</v>
+      </c>
+      <c r="I74" s="67">
         <f t="shared" si="4"/>
-        <v>86</v>
-      </c>
-      <c r="J74" s="59">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="J74" s="67">
         <f t="shared" si="4"/>
-        <v>78</v>
-      </c>
-      <c r="K74" s="59">
+        <v>0.87999999999999989</v>
+      </c>
+      <c r="K74" s="67">
         <f t="shared" si="4"/>
-        <v>78</v>
-      </c>
-      <c r="L74" s="59">
+        <v>0.87999999999999989</v>
+      </c>
+      <c r="L74" s="67">
         <f t="shared" si="4"/>
-        <v>78</v>
-      </c>
-      <c r="M74" s="59">
+        <v>0.87999999999999989</v>
+      </c>
+      <c r="M74" s="67">
         <f t="shared" si="4"/>
-        <v>76.125</v>
-      </c>
-      <c r="N74" s="59">
+        <v>0.95500000000000007</v>
+      </c>
+      <c r="N74" s="67">
         <f t="shared" si="4"/>
-        <v>69.5</v>
-      </c>
-      <c r="O74" s="59">
+        <v>1.2200000000000002</v>
+      </c>
+      <c r="O74" s="67">
         <f t="shared" si="4"/>
-        <v>69.5</v>
-      </c>
-      <c r="P74" s="59">
+        <v>1.2200000000000002</v>
+      </c>
+      <c r="P74" s="67">
         <f t="shared" si="4"/>
-        <v>69.5</v>
-      </c>
-    </row>
-    <row r="75" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B75" s="60" t="str">
+        <v>1.2200000000000002</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B75" s="59" t="str">
         <f>B$155</f>
         <v>Q1</v>
       </c>
-      <c r="C75" s="60" t="str">
+      <c r="C75" s="59" t="str">
         <f t="shared" ref="C75:F75" si="5">C$155</f>
         <v>Q2</v>
       </c>
-      <c r="D75" s="60" t="str">
+      <c r="D75" s="59" t="str">
         <f t="shared" si="5"/>
         <v>Q3</v>
       </c>
-      <c r="E75" s="60" t="str">
+      <c r="E75" s="59" t="str">
         <f t="shared" si="5"/>
         <v>Q4</v>
       </c>
-      <c r="F75" s="60" t="str">
+      <c r="F75" s="59" t="str">
         <f t="shared" si="5"/>
         <v>Q1'27</v>
       </c>
     </row>
-    <row r="76" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="60" t="str">
+    <row r="76" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="59" t="str">
         <f>$A$156</f>
         <v>% Plan</v>
       </c>
-      <c r="B76" s="60">
+      <c r="B76" s="59">
         <f>(AVERAGE(B73:D73)/AVERAGE(B72:D72))*100</f>
         <v>100</v>
       </c>
-      <c r="C76" s="60">
+      <c r="C76" s="59">
         <f>(AVERAGE(E73:G73)/AVERAGE(E72:G72))*100</f>
         <v>90.666666666666657</v>
       </c>
-      <c r="D76" s="60">
+      <c r="D76" s="59">
         <f>(AVERAGE(H73:J73)/AVERAGE(H72:J72))*100</f>
         <v>82.708333333333343</v>
       </c>
-      <c r="E76" s="60">
+      <c r="E76" s="59">
         <f>(AVERAGE(K73:M73)/AVERAGE(K72:M72))*100</f>
         <v>77.375</v>
       </c>
-      <c r="F76" s="60">
+      <c r="F76" s="59">
         <f>(AVERAGE(N73:P73)/AVERAGE(N72:P72))*100</f>
         <v>69.5</v>
       </c>
@@ -29904,116 +29882,115 @@
         <v>1.4550000000000001</v>
       </c>
     </row>
-    <row r="84" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="59" t="str">
-        <f>$A$152</f>
-        <v>% Plan</v>
-      </c>
-      <c r="B84" s="59">
-        <f>(B83/B82)*100</f>
-        <v>169.25</v>
-      </c>
-      <c r="C84" s="59">
-        <f t="shared" ref="C84:P84" si="6">(C83/C82)*100</f>
-        <v>153.75</v>
-      </c>
-      <c r="D84" s="59">
+    <row r="84" spans="1:16" s="66" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="B84" s="67">
+        <f>B82-B83</f>
+        <v>-1.3849999999999998</v>
+      </c>
+      <c r="C84" s="67">
+        <f t="shared" ref="C84:P84" si="6">C82-C83</f>
+        <v>-1.0750000000000002</v>
+      </c>
+      <c r="D84" s="67">
         <f t="shared" si="6"/>
-        <v>211</v>
-      </c>
-      <c r="E84" s="59">
+        <v>-2.2199999999999998</v>
+      </c>
+      <c r="E84" s="67">
         <f t="shared" si="6"/>
-        <v>132.75</v>
-      </c>
-      <c r="F84" s="59">
+        <v>-0.6549999999999998</v>
+      </c>
+      <c r="F84" s="67">
         <f t="shared" si="6"/>
-        <v>134.25</v>
-      </c>
-      <c r="G84" s="59">
+        <v>-0.68500000000000005</v>
+      </c>
+      <c r="G84" s="67">
         <f t="shared" si="6"/>
-        <v>123.25</v>
-      </c>
-      <c r="H84" s="59">
+        <v>-0.46499999999999986</v>
+      </c>
+      <c r="H84" s="67">
         <f t="shared" si="6"/>
-        <v>115.75</v>
-      </c>
-      <c r="I84" s="59">
+        <v>-0.31499999999999995</v>
+      </c>
+      <c r="I84" s="67">
         <f t="shared" si="6"/>
-        <v>113.25</v>
-      </c>
-      <c r="J84" s="59">
+        <v>-0.26500000000000012</v>
+      </c>
+      <c r="J84" s="67">
         <f t="shared" si="6"/>
-        <v>105.75000000000001</v>
-      </c>
-      <c r="K84" s="59">
+        <v>-0.11500000000000021</v>
+      </c>
+      <c r="K84" s="67">
         <f t="shared" si="6"/>
-        <v>113.25</v>
-      </c>
-      <c r="L84" s="59">
+        <v>-0.26500000000000012</v>
+      </c>
+      <c r="L84" s="67">
         <f t="shared" si="6"/>
-        <v>103.25</v>
-      </c>
-      <c r="M84" s="59">
+        <v>-6.4999999999999947E-2</v>
+      </c>
+      <c r="M84" s="67">
         <f t="shared" si="6"/>
-        <v>103.25</v>
-      </c>
-      <c r="N84" s="59">
+        <v>-6.4999999999999947E-2</v>
+      </c>
+      <c r="N84" s="67">
         <f t="shared" si="6"/>
-        <v>75.25</v>
-      </c>
-      <c r="O84" s="59">
+        <v>0.49500000000000011</v>
+      </c>
+      <c r="O84" s="67">
         <f t="shared" si="6"/>
-        <v>72.75</v>
-      </c>
-      <c r="P84" s="59">
+        <v>0.54499999999999993</v>
+      </c>
+      <c r="P84" s="67">
         <f t="shared" si="6"/>
-        <v>72.75</v>
-      </c>
-    </row>
-    <row r="85" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B85" s="60" t="str">
+        <v>0.54499999999999993</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B85" s="59" t="str">
         <f>B$155</f>
         <v>Q1</v>
       </c>
-      <c r="C85" s="60" t="str">
+      <c r="C85" s="59" t="str">
         <f t="shared" ref="C85:F85" si="7">C$155</f>
         <v>Q2</v>
       </c>
-      <c r="D85" s="60" t="str">
+      <c r="D85" s="59" t="str">
         <f t="shared" si="7"/>
         <v>Q3</v>
       </c>
-      <c r="E85" s="60" t="str">
+      <c r="E85" s="59" t="str">
         <f t="shared" si="7"/>
         <v>Q4</v>
       </c>
-      <c r="F85" s="60" t="str">
+      <c r="F85" s="59" t="str">
         <f t="shared" si="7"/>
         <v>Q1'27</v>
       </c>
     </row>
-    <row r="86" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="60" t="str">
+    <row r="86" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="59" t="str">
         <f>$A$156</f>
         <v>% Plan</v>
       </c>
-      <c r="B86" s="60">
+      <c r="B86" s="59">
         <f>(AVERAGE(B83:D83)/AVERAGE(B82:D82))*100</f>
         <v>178</v>
       </c>
-      <c r="C86" s="60">
+      <c r="C86" s="59">
         <f>(AVERAGE(E83:G83)/AVERAGE(E82:G82))*100</f>
         <v>130.08333333333331</v>
       </c>
-      <c r="D86" s="60">
+      <c r="D86" s="59">
         <f>(AVERAGE(H83:J83)/AVERAGE(H82:J82))*100</f>
         <v>111.58333333333334</v>
       </c>
-      <c r="E86" s="60">
+      <c r="E86" s="59">
         <f>(AVERAGE(K83:M83)/AVERAGE(K82:M82))*100</f>
         <v>106.58333333333331</v>
       </c>
-      <c r="F86" s="60">
+      <c r="F86" s="59">
         <f>(AVERAGE(N83:P83)/AVERAGE(N82:P82))*100</f>
         <v>73.583333333333329</v>
       </c>
@@ -30216,116 +30193,115 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="94" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="59" t="str">
-        <f>$A$152</f>
-        <v>% Plan</v>
-      </c>
-      <c r="B94" s="59">
-        <f>(B93/B92)*100</f>
-        <v>109.16666666666666</v>
-      </c>
-      <c r="C94" s="59">
-        <f t="shared" ref="C94:P94" si="8">(C93/C92)*100</f>
-        <v>109.16666666666666</v>
-      </c>
-      <c r="D94" s="59">
+    <row r="94" spans="1:16" s="66" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="B94" s="67">
+        <f>B92-B93</f>
+        <v>-0.27499999999999991</v>
+      </c>
+      <c r="C94" s="67">
+        <f t="shared" ref="C94:P94" si="8">C92-C93</f>
+        <v>-0.27499999999999991</v>
+      </c>
+      <c r="D94" s="67">
         <f t="shared" si="8"/>
-        <v>107.5</v>
-      </c>
-      <c r="E94" s="59">
+        <v>-0.22500000000000009</v>
+      </c>
+      <c r="E94" s="67">
         <f t="shared" si="8"/>
-        <v>95.833333333333343</v>
-      </c>
-      <c r="F94" s="59">
+        <v>0.125</v>
+      </c>
+      <c r="F94" s="67">
         <f t="shared" si="8"/>
-        <v>103.74999999999999</v>
-      </c>
-      <c r="G94" s="59">
+        <v>-0.11249999999999982</v>
+      </c>
+      <c r="G94" s="67">
         <f t="shared" si="8"/>
-        <v>95.416666666666657</v>
-      </c>
-      <c r="H94" s="59">
+        <v>0.13750000000000018</v>
+      </c>
+      <c r="H94" s="67">
         <f t="shared" si="8"/>
-        <v>86.666666666666671</v>
-      </c>
-      <c r="I94" s="59">
+        <v>0.39999999999999991</v>
+      </c>
+      <c r="I94" s="67">
         <f t="shared" si="8"/>
-        <v>86.666666666666671</v>
-      </c>
-      <c r="J94" s="59">
+        <v>0.39999999999999991</v>
+      </c>
+      <c r="J94" s="67">
         <f t="shared" si="8"/>
-        <v>86.666666666666671</v>
-      </c>
-      <c r="K94" s="59">
+        <v>0.39999999999999991</v>
+      </c>
+      <c r="K94" s="67">
         <f t="shared" si="8"/>
-        <v>86.666666666666671</v>
-      </c>
-      <c r="L94" s="59">
+        <v>0.39999999999999991</v>
+      </c>
+      <c r="L94" s="67">
         <f t="shared" si="8"/>
-        <v>86.666666666666671</v>
-      </c>
-      <c r="M94" s="59">
+        <v>0.39999999999999991</v>
+      </c>
+      <c r="M94" s="67">
         <f t="shared" si="8"/>
-        <v>86.666666666666671</v>
-      </c>
-      <c r="N94" s="59">
+        <v>0.39999999999999991</v>
+      </c>
+      <c r="N94" s="67">
         <f t="shared" si="8"/>
-        <v>83.333333333333343</v>
-      </c>
-      <c r="O94" s="59">
+        <v>0.5</v>
+      </c>
+      <c r="O94" s="67">
         <f t="shared" si="8"/>
-        <v>83.333333333333343</v>
-      </c>
-      <c r="P94" s="59">
+        <v>0.5</v>
+      </c>
+      <c r="P94" s="67">
         <f t="shared" si="8"/>
-        <v>83.333333333333343</v>
-      </c>
-    </row>
-    <row r="95" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B95" s="60" t="str">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B95" s="59" t="str">
         <f>B$155</f>
         <v>Q1</v>
       </c>
-      <c r="C95" s="60" t="str">
+      <c r="C95" s="59" t="str">
         <f t="shared" ref="C95:F95" si="9">C$155</f>
         <v>Q2</v>
       </c>
-      <c r="D95" s="60" t="str">
+      <c r="D95" s="59" t="str">
         <f t="shared" si="9"/>
         <v>Q3</v>
       </c>
-      <c r="E95" s="60" t="str">
+      <c r="E95" s="59" t="str">
         <f t="shared" si="9"/>
         <v>Q4</v>
       </c>
-      <c r="F95" s="60" t="str">
+      <c r="F95" s="59" t="str">
         <f t="shared" si="9"/>
         <v>Q1'27</v>
       </c>
     </row>
-    <row r="96" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="60" t="str">
+    <row r="96" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="59" t="str">
         <f>$A$156</f>
         <v>% Plan</v>
       </c>
-      <c r="B96" s="60">
+      <c r="B96" s="59">
         <f>(AVERAGE(B93:D93)/AVERAGE(B92:D92))*100</f>
         <v>108.6111111111111</v>
       </c>
-      <c r="C96" s="60">
+      <c r="C96" s="59">
         <f>(AVERAGE(E93:G93)/AVERAGE(E92:G92))*100</f>
         <v>98.333333333333329</v>
       </c>
-      <c r="D96" s="60">
+      <c r="D96" s="59">
         <f>(AVERAGE(H93:J93)/AVERAGE(H92:J92))*100</f>
         <v>86.666666666666671</v>
       </c>
-      <c r="E96" s="60">
+      <c r="E96" s="59">
         <f>(AVERAGE(K93:M93)/AVERAGE(K92:M92))*100</f>
         <v>86.666666666666671</v>
       </c>
-      <c r="F96" s="60">
+      <c r="F96" s="59">
         <f>(AVERAGE(N93:P93)/AVERAGE(N92:P92))*100</f>
         <v>83.333333333333343</v>
       </c>
@@ -30528,116 +30504,115 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="59" t="str">
-        <f>$A$152</f>
-        <v>% Plan</v>
-      </c>
-      <c r="B104" s="59">
-        <f>(B103/B102)*100</f>
-        <v>91.25</v>
-      </c>
-      <c r="C104" s="59">
-        <f t="shared" ref="C104:P104" si="10">(C103/C102)*100</f>
-        <v>93.75</v>
-      </c>
-      <c r="D104" s="59">
+    <row r="104" spans="1:16" s="66" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="B104" s="67">
+        <f>B102-B103</f>
+        <v>0.35000000000000009</v>
+      </c>
+      <c r="C104" s="67">
+        <f t="shared" ref="C104:P104" si="10">C102-C103</f>
+        <v>0.25</v>
+      </c>
+      <c r="D104" s="67">
         <f t="shared" si="10"/>
-        <v>100</v>
-      </c>
-      <c r="E104" s="59">
+        <v>0</v>
+      </c>
+      <c r="E104" s="67">
         <f t="shared" si="10"/>
-        <v>96.25</v>
-      </c>
-      <c r="F104" s="59">
+        <v>0.14999999999999991</v>
+      </c>
+      <c r="F104" s="67">
         <f t="shared" si="10"/>
-        <v>104</v>
-      </c>
-      <c r="G104" s="59">
+        <v>-0.16000000000000014</v>
+      </c>
+      <c r="G104" s="67">
         <f t="shared" si="10"/>
-        <v>101.49999999999999</v>
-      </c>
-      <c r="H104" s="59">
+        <v>-5.9999999999999609E-2</v>
+      </c>
+      <c r="H104" s="67">
         <f t="shared" si="10"/>
-        <v>106.87500000000001</v>
-      </c>
-      <c r="I104" s="59">
+        <v>-0.27500000000000036</v>
+      </c>
+      <c r="I104" s="67">
         <f t="shared" si="10"/>
-        <v>103.8</v>
-      </c>
-      <c r="J104" s="59">
+        <v>-0.15200000000000014</v>
+      </c>
+      <c r="J104" s="67">
         <f t="shared" si="10"/>
-        <v>98.174999999999997</v>
-      </c>
-      <c r="K104" s="59">
+        <v>7.2999999999999954E-2</v>
+      </c>
+      <c r="K104" s="67">
         <f t="shared" si="10"/>
-        <v>93.174999999999997</v>
-      </c>
-      <c r="L104" s="59">
+        <v>0.27300000000000013</v>
+      </c>
+      <c r="L104" s="67">
         <f t="shared" si="10"/>
-        <v>87.125</v>
-      </c>
-      <c r="M104" s="59">
+        <v>0.51500000000000012</v>
+      </c>
+      <c r="M104" s="67">
         <f t="shared" si="10"/>
-        <v>67.75</v>
-      </c>
-      <c r="N104" s="59">
+        <v>1.29</v>
+      </c>
+      <c r="N104" s="67">
         <f t="shared" si="10"/>
-        <v>25</v>
-      </c>
-      <c r="O104" s="59">
+        <v>3</v>
+      </c>
+      <c r="O104" s="67">
         <f t="shared" si="10"/>
-        <v>25</v>
-      </c>
-      <c r="P104" s="59">
+        <v>3</v>
+      </c>
+      <c r="P104" s="67">
         <f t="shared" si="10"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="105" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B105" s="60" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B105" s="59" t="str">
         <f>B$155</f>
         <v>Q1</v>
       </c>
-      <c r="C105" s="60" t="str">
+      <c r="C105" s="59" t="str">
         <f t="shared" ref="C105:F105" si="11">C$155</f>
         <v>Q2</v>
       </c>
-      <c r="D105" s="60" t="str">
+      <c r="D105" s="59" t="str">
         <f t="shared" si="11"/>
         <v>Q3</v>
       </c>
-      <c r="E105" s="60" t="str">
+      <c r="E105" s="59" t="str">
         <f t="shared" si="11"/>
         <v>Q4</v>
       </c>
-      <c r="F105" s="60" t="str">
+      <c r="F105" s="59" t="str">
         <f t="shared" si="11"/>
         <v>Q1'27</v>
       </c>
     </row>
-    <row r="106" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="60" t="str">
+    <row r="106" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A106" s="59" t="str">
         <f>$A$156</f>
         <v>% Plan</v>
       </c>
-      <c r="B106" s="60">
+      <c r="B106" s="59">
         <f>(AVERAGE(B103:D103)/AVERAGE(B102:D102))*100</f>
         <v>95</v>
       </c>
-      <c r="C106" s="60">
+      <c r="C106" s="59">
         <f>(AVERAGE(E103:G103)/AVERAGE(E102:G102))*100</f>
         <v>100.58333333333334</v>
       </c>
-      <c r="D106" s="60">
+      <c r="D106" s="59">
         <f>(AVERAGE(H103:J103)/AVERAGE(H102:J102))*100</f>
         <v>102.94999999999999</v>
       </c>
-      <c r="E106" s="60">
+      <c r="E106" s="59">
         <f>(AVERAGE(K103:M103)/AVERAGE(K102:M102))*100</f>
         <v>82.683333333333337</v>
       </c>
-      <c r="F106" s="60">
+      <c r="F106" s="59">
         <f>(AVERAGE(N103:P103)/AVERAGE(N102:P102))*100</f>
         <v>25</v>
       </c>
@@ -30840,116 +30815,115 @@
         <v>3.22</v>
       </c>
     </row>
-    <row r="114" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="59" t="str">
-        <f>$A$152</f>
-        <v>% Plan</v>
-      </c>
-      <c r="B114" s="59">
-        <f>(B113/B112)*100</f>
-        <v>94</v>
-      </c>
-      <c r="C114" s="59">
-        <f t="shared" ref="C114:P114" si="12">(C113/C112)*100</f>
-        <v>101</v>
-      </c>
-      <c r="D114" s="59">
+    <row r="114" spans="1:16" s="66" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A114" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="B114" s="67">
+        <f>B112-B113</f>
+        <v>0.29999999999999982</v>
+      </c>
+      <c r="C114" s="67">
+        <f t="shared" ref="C114:P114" si="12">C112-C113</f>
+        <v>-4.9999999999999822E-2</v>
+      </c>
+      <c r="D114" s="67">
         <f t="shared" si="12"/>
-        <v>101</v>
-      </c>
-      <c r="E114" s="59">
+        <v>-4.9999999999999822E-2</v>
+      </c>
+      <c r="E114" s="67">
         <f t="shared" si="12"/>
-        <v>105.60000000000001</v>
-      </c>
-      <c r="F114" s="59">
+        <v>-0.28000000000000025</v>
+      </c>
+      <c r="F114" s="67">
         <f t="shared" si="12"/>
-        <v>119.8</v>
-      </c>
-      <c r="G114" s="59">
+        <v>-0.99000000000000021</v>
+      </c>
+      <c r="G114" s="67">
         <f t="shared" si="12"/>
-        <v>109.80000000000001</v>
-      </c>
-      <c r="H114" s="59">
+        <v>-0.49000000000000021</v>
+      </c>
+      <c r="H114" s="67">
         <f t="shared" si="12"/>
-        <v>103</v>
-      </c>
-      <c r="I114" s="59">
+        <v>-0.15000000000000036</v>
+      </c>
+      <c r="I114" s="67">
         <f t="shared" si="12"/>
-        <v>94</v>
-      </c>
-      <c r="J114" s="59">
+        <v>0.29999999999999982</v>
+      </c>
+      <c r="J114" s="67">
         <f t="shared" si="12"/>
-        <v>90</v>
-      </c>
-      <c r="K114" s="59">
+        <v>0.5</v>
+      </c>
+      <c r="K114" s="67">
         <f t="shared" si="12"/>
-        <v>90</v>
-      </c>
-      <c r="L114" s="59">
+        <v>0.5</v>
+      </c>
+      <c r="L114" s="67">
         <f t="shared" si="12"/>
-        <v>90</v>
-      </c>
-      <c r="M114" s="59">
+        <v>0.5</v>
+      </c>
+      <c r="M114" s="67">
         <f t="shared" si="12"/>
-        <v>90</v>
-      </c>
-      <c r="N114" s="59">
+        <v>0.5</v>
+      </c>
+      <c r="N114" s="67">
         <f t="shared" si="12"/>
-        <v>64.400000000000006</v>
-      </c>
-      <c r="O114" s="59">
+        <v>1.7799999999999998</v>
+      </c>
+      <c r="O114" s="67">
         <f t="shared" si="12"/>
-        <v>64.400000000000006</v>
-      </c>
-      <c r="P114" s="59">
+        <v>1.7799999999999998</v>
+      </c>
+      <c r="P114" s="67">
         <f t="shared" si="12"/>
-        <v>64.400000000000006</v>
-      </c>
-    </row>
-    <row r="115" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B115" s="60" t="str">
+        <v>1.7799999999999998</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B115" s="59" t="str">
         <f>B$155</f>
         <v>Q1</v>
       </c>
-      <c r="C115" s="60" t="str">
+      <c r="C115" s="59" t="str">
         <f t="shared" ref="C115:F115" si="13">C$155</f>
         <v>Q2</v>
       </c>
-      <c r="D115" s="60" t="str">
+      <c r="D115" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Q3</v>
       </c>
-      <c r="E115" s="60" t="str">
+      <c r="E115" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Q4</v>
       </c>
-      <c r="F115" s="60" t="str">
+      <c r="F115" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Q1'27</v>
       </c>
     </row>
-    <row r="116" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="60" t="str">
+    <row r="116" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A116" s="59" t="str">
         <f>$A$156</f>
         <v>% Plan</v>
       </c>
-      <c r="B116" s="60">
+      <c r="B116" s="59">
         <f>(AVERAGE(B113:D113)/AVERAGE(B112:D112))*100</f>
         <v>98.666666666666671</v>
       </c>
-      <c r="C116" s="60">
+      <c r="C116" s="59">
         <f>(AVERAGE(E113:G113)/AVERAGE(E112:G112))*100</f>
         <v>111.73333333333333</v>
       </c>
-      <c r="D116" s="60">
+      <c r="D116" s="59">
         <f>(AVERAGE(H113:J113)/AVERAGE(H112:J112))*100</f>
         <v>95.666666666666671</v>
       </c>
-      <c r="E116" s="60">
+      <c r="E116" s="59">
         <f>(AVERAGE(K113:M113)/AVERAGE(K112:M112))*100</f>
         <v>90</v>
       </c>
-      <c r="F116" s="60">
+      <c r="F116" s="59">
         <f>(AVERAGE(N113:P113)/AVERAGE(N112:P112))*100</f>
         <v>64.400000000000006</v>
       </c>
@@ -31152,116 +31126,115 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="124" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="59" t="str">
-        <f>$A$152</f>
-        <v>% Plan</v>
-      </c>
-      <c r="B124" s="59">
-        <f>(B123/B122)*100</f>
-        <v>88.1111111111111</v>
-      </c>
-      <c r="C124" s="59">
-        <f t="shared" ref="C124:P124" si="14">(C123/C122)*100</f>
-        <v>102.72727272727273</v>
-      </c>
-      <c r="D124" s="59">
+    <row r="124" spans="1:16" s="66" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A124" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="B124" s="67">
+        <f>B122-B123</f>
+        <v>1.0700000000000003</v>
+      </c>
+      <c r="C124" s="67">
+        <f t="shared" ref="C124:P124" si="14">C122-C123</f>
+        <v>-0.30000000000000071</v>
+      </c>
+      <c r="D124" s="67">
         <f t="shared" si="14"/>
-        <v>104.25</v>
-      </c>
-      <c r="E124" s="59">
+        <v>-0.50999999999999979</v>
+      </c>
+      <c r="E124" s="67">
         <f t="shared" si="14"/>
-        <v>97.375</v>
-      </c>
-      <c r="F124" s="59">
+        <v>0.3149999999999995</v>
+      </c>
+      <c r="F124" s="67">
         <f t="shared" si="14"/>
-        <v>107.83333333333334</v>
-      </c>
-      <c r="G124" s="59">
+        <v>-0.9399999999999995</v>
+      </c>
+      <c r="G124" s="67">
         <f t="shared" si="14"/>
-        <v>112.16666666666669</v>
-      </c>
-      <c r="H124" s="59">
+        <v>-1.4600000000000009</v>
+      </c>
+      <c r="H124" s="67">
         <f t="shared" si="14"/>
-        <v>128.33333333333334</v>
-      </c>
-      <c r="I124" s="59">
+        <v>-3.4000000000000004</v>
+      </c>
+      <c r="I124" s="67">
         <f t="shared" si="14"/>
-        <v>127.08333333333333</v>
-      </c>
-      <c r="J124" s="59">
+        <v>-3.25</v>
+      </c>
+      <c r="J124" s="67">
         <f t="shared" si="14"/>
-        <v>131.25</v>
-      </c>
-      <c r="K124" s="59">
+        <v>-3.75</v>
+      </c>
+      <c r="K124" s="67">
         <f t="shared" si="14"/>
-        <v>112.08333333333333</v>
-      </c>
-      <c r="L124" s="59">
+        <v>-1.4499999999999993</v>
+      </c>
+      <c r="L124" s="67">
         <f t="shared" si="14"/>
-        <v>109.99999999999999</v>
-      </c>
-      <c r="M124" s="59">
+        <v>-1.1999999999999993</v>
+      </c>
+      <c r="M124" s="67">
         <f t="shared" si="14"/>
-        <v>107.08333333333333</v>
-      </c>
-      <c r="N124" s="59">
+        <v>-0.84999999999999964</v>
+      </c>
+      <c r="N124" s="67">
         <f t="shared" si="14"/>
-        <v>80</v>
-      </c>
-      <c r="O124" s="59">
+        <v>2.4000000000000004</v>
+      </c>
+      <c r="O124" s="67">
         <f t="shared" si="14"/>
-        <v>80</v>
-      </c>
-      <c r="P124" s="59">
+        <v>2.4000000000000004</v>
+      </c>
+      <c r="P124" s="67">
         <f t="shared" si="14"/>
-        <v>80</v>
-      </c>
-    </row>
-    <row r="125" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B125" s="60" t="str">
+        <v>2.4000000000000004</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B125" s="59" t="str">
         <f>B$155</f>
         <v>Q1</v>
       </c>
-      <c r="C125" s="60" t="str">
+      <c r="C125" s="59" t="str">
         <f t="shared" ref="C125:F125" si="15">C$155</f>
         <v>Q2</v>
       </c>
-      <c r="D125" s="60" t="str">
+      <c r="D125" s="59" t="str">
         <f t="shared" si="15"/>
         <v>Q3</v>
       </c>
-      <c r="E125" s="60" t="str">
+      <c r="E125" s="59" t="str">
         <f t="shared" si="15"/>
         <v>Q4</v>
       </c>
-      <c r="F125" s="60" t="str">
+      <c r="F125" s="59" t="str">
         <f t="shared" si="15"/>
         <v>Q1'27</v>
       </c>
     </row>
-    <row r="126" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A126" s="60" t="str">
+    <row r="126" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A126" s="59" t="str">
         <f>$A$156</f>
         <v>% Plan</v>
       </c>
-      <c r="B126" s="60">
+      <c r="B126" s="59">
         <f>(AVERAGE(B123:D123)/AVERAGE(B122:D122))*100</f>
         <v>99.1875</v>
       </c>
-      <c r="C126" s="60">
+      <c r="C126" s="59">
         <f>(AVERAGE(E123:G123)/AVERAGE(E122:G122))*100</f>
         <v>105.79166666666666</v>
       </c>
-      <c r="D126" s="60">
+      <c r="D126" s="59">
         <f>(AVERAGE(H123:J123)/AVERAGE(H122:J122))*100</f>
         <v>128.88888888888889</v>
       </c>
-      <c r="E126" s="60">
+      <c r="E126" s="59">
         <f>(AVERAGE(K123:M123)/AVERAGE(K122:M122))*100</f>
         <v>109.72222222222221</v>
       </c>
-      <c r="F126" s="60">
+      <c r="F126" s="59">
         <f>(AVERAGE(N123:P123)/AVERAGE(N122:P122))*100</f>
         <v>80</v>
       </c>
@@ -31464,116 +31437,115 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="134" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A134" s="59" t="str">
-        <f>$A$152</f>
-        <v>% Plan</v>
-      </c>
-      <c r="B134" s="59">
-        <f>(B133/B132)*100</f>
-        <v>77</v>
-      </c>
-      <c r="C134" s="59">
-        <f t="shared" ref="C134:P134" si="16">(C133/C132)*100</f>
-        <v>73.5</v>
-      </c>
-      <c r="D134" s="59">
+    <row r="134" spans="1:16" s="66" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A134" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="B134" s="67">
+        <f>B132-B133</f>
+        <v>0.91999999999999993</v>
+      </c>
+      <c r="C134" s="67">
+        <f t="shared" ref="C134:P134" si="16">C132-C133</f>
+        <v>1.06</v>
+      </c>
+      <c r="D134" s="67">
         <f t="shared" si="16"/>
-        <v>74.75</v>
-      </c>
-      <c r="E134" s="59">
+        <v>1.0099999999999998</v>
+      </c>
+      <c r="E134" s="67">
         <f t="shared" si="16"/>
-        <v>76.75</v>
-      </c>
-      <c r="F134" s="59">
+        <v>0.93000000000000016</v>
+      </c>
+      <c r="F134" s="67">
         <f t="shared" si="16"/>
-        <v>76.75</v>
-      </c>
-      <c r="G134" s="59">
+        <v>0.93000000000000016</v>
+      </c>
+      <c r="G134" s="67">
         <f t="shared" si="16"/>
-        <v>80.75</v>
-      </c>
-      <c r="H134" s="59">
+        <v>0.77</v>
+      </c>
+      <c r="H134" s="67">
         <f t="shared" si="16"/>
-        <v>95.75</v>
-      </c>
-      <c r="I134" s="59">
+        <v>0.16999999999999993</v>
+      </c>
+      <c r="I134" s="67">
         <f t="shared" si="16"/>
-        <v>95.75</v>
-      </c>
-      <c r="J134" s="59">
+        <v>0.16999999999999993</v>
+      </c>
+      <c r="J134" s="67">
         <f t="shared" si="16"/>
-        <v>95.75</v>
-      </c>
-      <c r="K134" s="59">
+        <v>0.16999999999999993</v>
+      </c>
+      <c r="K134" s="67">
         <f t="shared" si="16"/>
-        <v>95.75</v>
-      </c>
-      <c r="L134" s="59">
+        <v>0.16999999999999993</v>
+      </c>
+      <c r="L134" s="67">
         <f t="shared" si="16"/>
-        <v>105</v>
-      </c>
-      <c r="M134" s="59">
+        <v>-0.20000000000000018</v>
+      </c>
+      <c r="M134" s="67">
         <f t="shared" si="16"/>
-        <v>130</v>
-      </c>
-      <c r="N134" s="59">
+        <v>-1.2000000000000002</v>
+      </c>
+      <c r="N134" s="67">
         <f t="shared" si="16"/>
-        <v>130</v>
-      </c>
-      <c r="O134" s="59">
+        <v>-1.2000000000000002</v>
+      </c>
+      <c r="O134" s="67">
         <f t="shared" si="16"/>
-        <v>130</v>
-      </c>
-      <c r="P134" s="59">
+        <v>-1.2000000000000002</v>
+      </c>
+      <c r="P134" s="67">
         <f t="shared" si="16"/>
-        <v>130</v>
-      </c>
-    </row>
-    <row r="135" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B135" s="60" t="str">
+        <v>-1.2000000000000002</v>
+      </c>
+    </row>
+    <row r="135" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B135" s="59" t="str">
         <f>B$155</f>
         <v>Q1</v>
       </c>
-      <c r="C135" s="60" t="str">
+      <c r="C135" s="59" t="str">
         <f t="shared" ref="C135:F135" si="17">C$155</f>
         <v>Q2</v>
       </c>
-      <c r="D135" s="60" t="str">
+      <c r="D135" s="59" t="str">
         <f t="shared" si="17"/>
         <v>Q3</v>
       </c>
-      <c r="E135" s="60" t="str">
+      <c r="E135" s="59" t="str">
         <f t="shared" si="17"/>
         <v>Q4</v>
       </c>
-      <c r="F135" s="60" t="str">
+      <c r="F135" s="59" t="str">
         <f t="shared" si="17"/>
         <v>Q1'27</v>
       </c>
     </row>
-    <row r="136" spans="1:16" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A136" s="60" t="str">
+    <row r="136" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A136" s="59" t="str">
         <f>$A$156</f>
         <v>% Plan</v>
       </c>
-      <c r="B136" s="60">
+      <c r="B136" s="59">
         <f>(AVERAGE(B133:D133)/AVERAGE(B132:D132))*100</f>
         <v>75.083333333333329</v>
       </c>
-      <c r="C136" s="60">
+      <c r="C136" s="59">
         <f>(AVERAGE(E133:G133)/AVERAGE(E132:G132))*100</f>
         <v>78.083333333333329</v>
       </c>
-      <c r="D136" s="60">
+      <c r="D136" s="59">
         <f>(AVERAGE(H133:J133)/AVERAGE(H132:J132))*100</f>
         <v>95.75</v>
       </c>
-      <c r="E136" s="60">
+      <c r="E136" s="59">
         <f>(AVERAGE(K133:M133)/AVERAGE(K132:M132))*100</f>
         <v>110.25</v>
       </c>
-      <c r="F136" s="60">
+      <c r="F136" s="59">
         <f>(AVERAGE(N133:P133)/AVERAGE(N132:P132))*100</f>
         <v>130</v>
       </c>

--- a/workforceresult.xlsx
+++ b/workforceresult.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miiintra/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EC10C9C-6F5A-AB49-BF8E-53C950956132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{917671F0-8611-264C-9970-BB70DD899070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8000" yWindow="3500" windowWidth="28800" windowHeight="16120" activeTab="11" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
+    <workbookView xWindow="8000" yWindow="3500" windowWidth="28800" windowHeight="16120" activeTab="1" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
   </bookViews>
   <sheets>
     <sheet name="ALL" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="134">
   <si>
     <t>Type</t>
   </si>
@@ -621,6 +621,18 @@
   <si>
     <t>Total FTE</t>
   </si>
+  <si>
+    <t>Actual</t>
+  </si>
+  <si>
+    <t>Mgmt</t>
+  </si>
+  <si>
+    <t>Logged</t>
+  </si>
+  <si>
+    <t>Q1 Plan</t>
+  </si>
 </sst>
 </file>
 
@@ -629,7 +641,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -759,8 +771,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF548235"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF548235"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="23">
+  <fills count="24">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -893,6 +917,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -924,7 +954,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1019,6 +1049,10 @@
     <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2224,6 +2258,57 @@
         <v>7</v>
       </c>
     </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A22" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="69" t="s">
+        <v>131</v>
+      </c>
+      <c r="C22" s="70">
+        <v>11</v>
+      </c>
+      <c r="D22" s="70">
+        <v>11</v>
+      </c>
+      <c r="E22" s="70">
+        <v>11</v>
+      </c>
+      <c r="F22" s="70">
+        <v>11</v>
+      </c>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
+      <c r="P22" s="8"/>
+      <c r="Q22" s="8"/>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A23" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="69" t="s">
+        <v>132</v>
+      </c>
+      <c r="C23" s="71">
+        <v>117.04</v>
+      </c>
+      <c r="D23" s="71">
+        <v>125.05</v>
+      </c>
+      <c r="E23" s="70">
+        <v>126.04</v>
+      </c>
+      <c r="F23" s="70">
+        <v>126.8</v>
+      </c>
+    </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A31" s="17"/>
       <c r="B31" s="1" t="s">
@@ -13981,7 +14066,7 @@
   <sheetPr>
     <tabColor theme="4" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:P157"/>
+  <dimension ref="A1:P165"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.83203125" bestFit="1" customWidth="1"/>
@@ -15669,6 +15754,262 @@
       <c r="F157">
         <f>ALL!G37</f>
         <v>28</v>
+      </c>
+    </row>
+    <row r="161" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B161" t="str">
+        <f>ALL!C1</f>
+        <v>JAN</v>
+      </c>
+      <c r="C161" t="str">
+        <f>ALL!D1</f>
+        <v>FEB</v>
+      </c>
+      <c r="D161" t="str">
+        <f>ALL!E1</f>
+        <v>MAR</v>
+      </c>
+      <c r="E161" t="str">
+        <f>ALL!F1</f>
+        <v>APR</v>
+      </c>
+      <c r="F161" t="str">
+        <f>ALL!G1</f>
+        <v>MAY</v>
+      </c>
+      <c r="G161" t="str">
+        <f>ALL!H1</f>
+        <v>JUN</v>
+      </c>
+      <c r="H161" t="str">
+        <f>ALL!I1</f>
+        <v>JUL</v>
+      </c>
+      <c r="I161" t="str">
+        <f>ALL!J1</f>
+        <v>AUG</v>
+      </c>
+      <c r="J161" t="str">
+        <f>ALL!K1</f>
+        <v>SEP</v>
+      </c>
+      <c r="K161" t="str">
+        <f>ALL!L1</f>
+        <v>OCT</v>
+      </c>
+      <c r="L161" t="str">
+        <f>ALL!M1</f>
+        <v>NOV</v>
+      </c>
+      <c r="M161" t="str">
+        <f>ALL!N1</f>
+        <v>DEC</v>
+      </c>
+      <c r="N161" t="str">
+        <f>ALL!O1</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O161" t="str">
+        <f>ALL!P1</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P161" t="str">
+        <f>ALL!Q1</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="162" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A162" t="str">
+        <f>A2</f>
+        <v>Staff</v>
+      </c>
+      <c r="B162">
+        <f t="shared" ref="B162:P162" si="0">B2</f>
+        <v>148</v>
+      </c>
+      <c r="C162">
+        <f t="shared" si="0"/>
+        <v>149</v>
+      </c>
+      <c r="D162">
+        <f t="shared" si="0"/>
+        <v>149</v>
+      </c>
+      <c r="E162">
+        <f t="shared" si="0"/>
+        <v>151</v>
+      </c>
+      <c r="F162">
+        <f t="shared" si="0"/>
+        <v>150</v>
+      </c>
+      <c r="G162">
+        <f t="shared" si="0"/>
+        <v>150</v>
+      </c>
+      <c r="H162">
+        <f t="shared" si="0"/>
+        <v>149</v>
+      </c>
+      <c r="I162">
+        <f t="shared" si="0"/>
+        <v>149</v>
+      </c>
+      <c r="J162">
+        <f t="shared" si="0"/>
+        <v>149</v>
+      </c>
+      <c r="K162">
+        <f t="shared" si="0"/>
+        <v>149</v>
+      </c>
+      <c r="L162">
+        <f t="shared" si="0"/>
+        <v>149</v>
+      </c>
+      <c r="M162">
+        <f t="shared" si="0"/>
+        <v>149</v>
+      </c>
+      <c r="N162">
+        <f t="shared" si="0"/>
+        <v>149</v>
+      </c>
+      <c r="O162">
+        <f t="shared" si="0"/>
+        <v>149</v>
+      </c>
+      <c r="P162">
+        <f t="shared" si="0"/>
+        <v>149</v>
+      </c>
+    </row>
+    <row r="163" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A163" t="str">
+        <f>A4</f>
+        <v>Plan</v>
+      </c>
+      <c r="B163">
+        <f t="shared" ref="B163:P163" si="1">B4</f>
+        <v>131</v>
+      </c>
+      <c r="C163">
+        <f t="shared" si="1"/>
+        <v>139</v>
+      </c>
+      <c r="D163">
+        <f t="shared" si="1"/>
+        <v>142</v>
+      </c>
+      <c r="E163">
+        <f t="shared" si="1"/>
+        <v>143</v>
+      </c>
+      <c r="F163">
+        <f t="shared" si="1"/>
+        <v>147</v>
+      </c>
+      <c r="G163">
+        <f t="shared" si="1"/>
+        <v>144</v>
+      </c>
+      <c r="H163">
+        <f t="shared" si="1"/>
+        <v>143</v>
+      </c>
+      <c r="I163">
+        <f t="shared" si="1"/>
+        <v>140</v>
+      </c>
+      <c r="J163">
+        <f t="shared" si="1"/>
+        <v>139</v>
+      </c>
+      <c r="K163">
+        <f t="shared" si="1"/>
+        <v>132</v>
+      </c>
+      <c r="L163">
+        <f t="shared" si="1"/>
+        <v>130</v>
+      </c>
+      <c r="M163">
+        <f t="shared" si="1"/>
+        <v>130</v>
+      </c>
+      <c r="N163">
+        <f t="shared" si="1"/>
+        <v>105</v>
+      </c>
+      <c r="O163">
+        <f t="shared" si="1"/>
+        <v>104</v>
+      </c>
+      <c r="P163">
+        <f t="shared" si="1"/>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="164" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A164" t="s">
+        <v>130</v>
+      </c>
+      <c r="B164">
+        <f>SUM(ALL!C22:C23)</f>
+        <v>128.04000000000002</v>
+      </c>
+      <c r="C164">
+        <f>SUM(ALL!D22:D23)</f>
+        <v>136.05000000000001</v>
+      </c>
+      <c r="D164">
+        <f>SUM(ALL!E22:E23)</f>
+        <v>137.04000000000002</v>
+      </c>
+      <c r="E164">
+        <f>SUM(ALL!F22:F23)</f>
+        <v>137.80000000000001</v>
+      </c>
+    </row>
+    <row r="165" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A165" t="s">
+        <v>133</v>
+      </c>
+      <c r="B165">
+        <v>127</v>
+      </c>
+      <c r="C165">
+        <v>136</v>
+      </c>
+      <c r="D165">
+        <v>136</v>
+      </c>
+      <c r="E165">
+        <v>132</v>
+      </c>
+      <c r="F165">
+        <v>132</v>
+      </c>
+      <c r="G165">
+        <v>130</v>
+      </c>
+      <c r="H165">
+        <v>118</v>
+      </c>
+      <c r="I165">
+        <v>114</v>
+      </c>
+      <c r="J165">
+        <v>111</v>
+      </c>
+      <c r="K165">
+        <v>109</v>
+      </c>
+      <c r="L165">
+        <v>105</v>
+      </c>
+      <c r="M165">
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/workforceresult.xlsx
+++ b/workforceresult.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miiintra/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{917671F0-8611-264C-9970-BB70DD899070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CC0CA11-70C6-4548-81CB-89823E7ADEAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8000" yWindow="3500" windowWidth="28800" windowHeight="16120" activeTab="1" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
   </bookViews>
@@ -15889,24 +15889,8 @@
         <f>A4</f>
         <v>Plan</v>
       </c>
-      <c r="B163">
-        <f t="shared" ref="B163:P163" si="1">B4</f>
-        <v>131</v>
-      </c>
-      <c r="C163">
-        <f t="shared" si="1"/>
-        <v>139</v>
-      </c>
-      <c r="D163">
-        <f t="shared" si="1"/>
-        <v>142</v>
-      </c>
-      <c r="E163">
-        <f t="shared" si="1"/>
-        <v>143</v>
-      </c>
       <c r="F163">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="B163:P163" si="1">F4</f>
         <v>147</v>
       </c>
       <c r="G163">

--- a/workforceresult.xlsx
+++ b/workforceresult.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miiintra/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CC0CA11-70C6-4548-81CB-89823E7ADEAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BFA2D2E-6DA8-8247-8F8F-9B1782DFC9BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8000" yWindow="3500" windowWidth="28800" windowHeight="16120" activeTab="1" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
   </bookViews>
@@ -15889,8 +15889,12 @@
         <f>A4</f>
         <v>Plan</v>
       </c>
+      <c r="E163">
+        <f t="shared" ref="E163:P163" si="1">E4</f>
+        <v>143</v>
+      </c>
       <c r="F163">
-        <f t="shared" ref="B163:P163" si="1">F4</f>
+        <f t="shared" si="1"/>
         <v>147</v>
       </c>
       <c r="G163">

--- a/workforceresult.xlsx
+++ b/workforceresult.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miiintra/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BFA2D2E-6DA8-8247-8F8F-9B1782DFC9BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7675D964-8ACC-2A4D-A466-0049CC9290EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8000" yWindow="3500" windowWidth="28800" windowHeight="16120" activeTab="1" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
+    <workbookView xWindow="9320" yWindow="7920" windowWidth="28360" windowHeight="12340" activeTab="13" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
   </bookViews>
   <sheets>
     <sheet name="ALL" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,21 @@
     <sheet name="Project" sheetId="13" r:id="rId13"/>
     <sheet name="GraphPJ" sheetId="14" r:id="rId14"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">Project!$A$31</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Project!$A$32</definedName>
+    <definedName name="_xlchart.v1.10" hidden="1">Project!$B$34:$M$34</definedName>
+    <definedName name="_xlchart.v1.11" hidden="1">Project!$B$35:$M$35</definedName>
+    <definedName name="_xlchart.v1.12" hidden="1">Project!$B$36:$M$36</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Project!$A$33</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">Project!$A$34</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">Project!$A$35</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">Project!$A$36</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">Project!$B$30:$M$30</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">Project!$B$31:$M$31</definedName>
+    <definedName name="_xlchart.v1.8" hidden="1">Project!$B$32:$M$32</definedName>
+    <definedName name="_xlchart.v1.9" hidden="1">Project!$B$33:$M$33</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -48,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="139">
   <si>
     <t>Type</t>
   </si>
@@ -633,6 +648,21 @@
   <si>
     <t>Q1 Plan</t>
   </si>
+  <si>
+    <t>Plan-PS</t>
+  </si>
+  <si>
+    <t>Plan-PD</t>
+  </si>
+  <si>
+    <t>Actual-PS</t>
+  </si>
+  <si>
+    <t>Actual-PD</t>
+  </si>
+  <si>
+    <t>Project Plan and Actual Income</t>
+  </si>
 </sst>
 </file>
 
@@ -641,7 +671,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -783,8 +813,21 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="24">
+  <fills count="27">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -923,6 +966,24 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -954,7 +1015,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1053,6 +1114,16 @@
     <xf numFmtId="0" fontId="3" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11288,7 +11359,7 @@
   <sheetPr>
     <tabColor rgb="FF002060"/>
   </sheetPr>
-  <dimension ref="A1:V26"/>
+  <dimension ref="A1:V36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.6640625" bestFit="1" customWidth="1"/>
@@ -12190,6 +12261,237 @@
       <c r="N26" s="8"/>
       <c r="Q26" s="8"/>
     </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B30" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="C30" s="55" t="s">
+        <v>2</v>
+      </c>
+      <c r="D30" s="55" t="s">
+        <v>3</v>
+      </c>
+      <c r="E30" s="55" t="s">
+        <v>4</v>
+      </c>
+      <c r="F30" s="55" t="s">
+        <v>5</v>
+      </c>
+      <c r="G30" s="55" t="s">
+        <v>6</v>
+      </c>
+      <c r="H30" s="55" t="s">
+        <v>7</v>
+      </c>
+      <c r="I30" s="55" t="s">
+        <v>8</v>
+      </c>
+      <c r="J30" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="K30" s="55" t="s">
+        <v>10</v>
+      </c>
+      <c r="L30" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="M30" s="55" t="s">
+        <v>12</v>
+      </c>
+      <c r="N30" s="72"/>
+      <c r="O30" s="72"/>
+      <c r="P30" s="72"/>
+    </row>
+    <row r="31" spans="1:17" s="74" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A31" s="81" t="s">
+        <v>18</v>
+      </c>
+      <c r="B31" s="75">
+        <f>SUM(B32,B33)</f>
+        <v>2717433</v>
+      </c>
+      <c r="C31" s="75">
+        <f>SUM(C32,C33)</f>
+        <v>6209433</v>
+      </c>
+      <c r="D31" s="75">
+        <f>SUM(D32,D33)</f>
+        <v>13563433</v>
+      </c>
+      <c r="E31" s="75">
+        <f>SUM(E32,E33)</f>
+        <v>7233433</v>
+      </c>
+      <c r="F31" s="75">
+        <f>SUM(F32,F33)</f>
+        <v>7406433</v>
+      </c>
+      <c r="G31" s="75">
+        <f>SUM(G32,G33)</f>
+        <v>19319433</v>
+      </c>
+      <c r="H31" s="75">
+        <f>SUM(H32,H33)</f>
+        <v>13479433</v>
+      </c>
+      <c r="I31" s="75">
+        <f>SUM(I32,I33)</f>
+        <v>10679433</v>
+      </c>
+      <c r="J31" s="75">
+        <f>SUM(J32,J33)</f>
+        <v>18089433</v>
+      </c>
+      <c r="K31" s="75">
+        <f>SUM(K32,K33)</f>
+        <v>16179433</v>
+      </c>
+      <c r="L31" s="75">
+        <f>SUM(L32,L33)</f>
+        <v>14539433</v>
+      </c>
+      <c r="M31" s="75">
+        <f>SUM(M32,M33)</f>
+        <v>19853233</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" s="73" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A32" s="78" t="s">
+        <v>134</v>
+      </c>
+      <c r="B32" s="76">
+        <v>1787433</v>
+      </c>
+      <c r="C32" s="76">
+        <v>4779433</v>
+      </c>
+      <c r="D32" s="76">
+        <v>7833433</v>
+      </c>
+      <c r="E32" s="76">
+        <v>5233433</v>
+      </c>
+      <c r="F32" s="76">
+        <v>4206433</v>
+      </c>
+      <c r="G32" s="76">
+        <v>14379433</v>
+      </c>
+      <c r="H32" s="76">
+        <v>9279433</v>
+      </c>
+      <c r="I32" s="76">
+        <v>6279433</v>
+      </c>
+      <c r="J32" s="76">
+        <v>10379433</v>
+      </c>
+      <c r="K32" s="76">
+        <v>11279433</v>
+      </c>
+      <c r="L32" s="76">
+        <v>4379433</v>
+      </c>
+      <c r="M32" s="76">
+        <v>10453233</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" s="73" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A33" s="78" t="s">
+        <v>135</v>
+      </c>
+      <c r="B33" s="76">
+        <v>930000</v>
+      </c>
+      <c r="C33" s="76">
+        <v>1430000</v>
+      </c>
+      <c r="D33" s="76">
+        <v>5730000</v>
+      </c>
+      <c r="E33" s="76">
+        <v>2000000</v>
+      </c>
+      <c r="F33" s="76">
+        <v>3200000</v>
+      </c>
+      <c r="G33" s="76">
+        <v>4940000</v>
+      </c>
+      <c r="H33" s="76">
+        <v>4200000</v>
+      </c>
+      <c r="I33" s="76">
+        <v>4400000</v>
+      </c>
+      <c r="J33" s="76">
+        <v>7710000</v>
+      </c>
+      <c r="K33" s="76">
+        <v>4900000</v>
+      </c>
+      <c r="L33" s="76">
+        <v>10160000</v>
+      </c>
+      <c r="M33" s="76">
+        <v>9400000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" s="74" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A34" s="80" t="s">
+        <v>130</v>
+      </c>
+      <c r="B34" s="75">
+        <f>SUM(B35,B36)</f>
+        <v>1049908</v>
+      </c>
+      <c r="C34" s="75">
+        <f t="shared" ref="C34:E34" si="0">SUM(C35,C36)</f>
+        <v>6155989</v>
+      </c>
+      <c r="D34" s="75">
+        <f t="shared" si="0"/>
+        <v>9094371</v>
+      </c>
+      <c r="E34" s="75">
+        <f t="shared" si="0"/>
+        <v>6308025</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" s="73" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A35" s="79" t="s">
+        <v>136</v>
+      </c>
+      <c r="B35" s="77">
+        <v>1002658</v>
+      </c>
+      <c r="C35" s="77">
+        <v>5710093</v>
+      </c>
+      <c r="D35" s="77">
+        <v>8544505</v>
+      </c>
+      <c r="E35" s="77">
+        <v>4855248</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" s="73" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A36" s="79" t="s">
+        <v>137</v>
+      </c>
+      <c r="B36" s="77">
+        <v>47250</v>
+      </c>
+      <c r="C36" s="77">
+        <v>445896</v>
+      </c>
+      <c r="D36" s="77">
+        <v>549866</v>
+      </c>
+      <c r="E36" s="77">
+        <v>1452777</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -12200,10 +12502,10 @@
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
-  <dimension ref="A1:T29"/>
+  <dimension ref="A1:T37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" s="58" customFormat="1" x14ac:dyDescent="0.2">
@@ -14055,6 +14357,287 @@
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A29" s="58"/>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A31" s="58" t="s">
+        <v>138</v>
+      </c>
+      <c r="B31" s="58" t="str">
+        <f>Project!B30</f>
+        <v>JAN</v>
+      </c>
+      <c r="C31" s="58" t="str">
+        <f>Project!C30</f>
+        <v>FEB</v>
+      </c>
+      <c r="D31" s="58" t="str">
+        <f>Project!D30</f>
+        <v>MAR</v>
+      </c>
+      <c r="E31" s="58" t="str">
+        <f>Project!E30</f>
+        <v>APR</v>
+      </c>
+      <c r="F31" s="58" t="str">
+        <f>Project!F30</f>
+        <v>MAY</v>
+      </c>
+      <c r="G31" s="58" t="str">
+        <f>Project!G30</f>
+        <v>JUN</v>
+      </c>
+      <c r="H31" s="58" t="str">
+        <f>Project!H30</f>
+        <v>JUL</v>
+      </c>
+      <c r="I31" s="58" t="str">
+        <f>Project!I30</f>
+        <v>AUG</v>
+      </c>
+      <c r="J31" s="58" t="str">
+        <f>Project!J30</f>
+        <v>SEP</v>
+      </c>
+      <c r="K31" s="58" t="str">
+        <f>Project!K30</f>
+        <v>OCT</v>
+      </c>
+      <c r="L31" s="58" t="str">
+        <f>Project!L30</f>
+        <v>NOV</v>
+      </c>
+      <c r="M31" s="58" t="str">
+        <f>Project!M30</f>
+        <v>DEC</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A32" t="str">
+        <f>Project!A31</f>
+        <v>Plan</v>
+      </c>
+      <c r="B32">
+        <f>Project!B31</f>
+        <v>2717433</v>
+      </c>
+      <c r="C32">
+        <f>Project!C31</f>
+        <v>6209433</v>
+      </c>
+      <c r="D32">
+        <f>Project!D31</f>
+        <v>13563433</v>
+      </c>
+      <c r="E32">
+        <f>Project!E31</f>
+        <v>7233433</v>
+      </c>
+      <c r="F32">
+        <f>Project!F31</f>
+        <v>7406433</v>
+      </c>
+      <c r="G32">
+        <f>Project!G31</f>
+        <v>19319433</v>
+      </c>
+      <c r="H32">
+        <f>Project!H31</f>
+        <v>13479433</v>
+      </c>
+      <c r="I32">
+        <f>Project!I31</f>
+        <v>10679433</v>
+      </c>
+      <c r="J32">
+        <f>Project!J31</f>
+        <v>18089433</v>
+      </c>
+      <c r="K32">
+        <f>Project!K31</f>
+        <v>16179433</v>
+      </c>
+      <c r="L32">
+        <f>Project!L31</f>
+        <v>14539433</v>
+      </c>
+      <c r="M32">
+        <f>Project!M31</f>
+        <v>19853233</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A33" t="str">
+        <f>Project!A34</f>
+        <v>Actual</v>
+      </c>
+      <c r="B33">
+        <f>Project!B34</f>
+        <v>1049908</v>
+      </c>
+      <c r="C33">
+        <f>Project!C34</f>
+        <v>6155989</v>
+      </c>
+      <c r="D33">
+        <f>Project!D34</f>
+        <v>9094371</v>
+      </c>
+      <c r="E33">
+        <f>Project!E34</f>
+        <v>6308025</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A34" t="str">
+        <f>Project!A32</f>
+        <v>Plan-PS</v>
+      </c>
+      <c r="B34">
+        <f>Project!B32</f>
+        <v>1787433</v>
+      </c>
+      <c r="C34">
+        <f>Project!C32</f>
+        <v>4779433</v>
+      </c>
+      <c r="D34">
+        <f>Project!D32</f>
+        <v>7833433</v>
+      </c>
+      <c r="E34">
+        <f>Project!E32</f>
+        <v>5233433</v>
+      </c>
+      <c r="F34">
+        <f>Project!F32</f>
+        <v>4206433</v>
+      </c>
+      <c r="G34">
+        <f>Project!G32</f>
+        <v>14379433</v>
+      </c>
+      <c r="H34">
+        <f>Project!H32</f>
+        <v>9279433</v>
+      </c>
+      <c r="I34">
+        <f>Project!I32</f>
+        <v>6279433</v>
+      </c>
+      <c r="J34">
+        <f>Project!J32</f>
+        <v>10379433</v>
+      </c>
+      <c r="K34">
+        <f>Project!K32</f>
+        <v>11279433</v>
+      </c>
+      <c r="L34">
+        <f>Project!L32</f>
+        <v>4379433</v>
+      </c>
+      <c r="M34">
+        <f>Project!M32</f>
+        <v>10453233</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A35" t="str">
+        <f>Project!A35</f>
+        <v>Actual-PS</v>
+      </c>
+      <c r="B35">
+        <f>Project!B35</f>
+        <v>1002658</v>
+      </c>
+      <c r="C35">
+        <f>Project!C35</f>
+        <v>5710093</v>
+      </c>
+      <c r="D35">
+        <f>Project!D35</f>
+        <v>8544505</v>
+      </c>
+      <c r="E35">
+        <f>Project!E35</f>
+        <v>4855248</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A36" t="str">
+        <f>Project!A33</f>
+        <v>Plan-PD</v>
+      </c>
+      <c r="B36">
+        <f>Project!B33</f>
+        <v>930000</v>
+      </c>
+      <c r="C36">
+        <f>Project!C33</f>
+        <v>1430000</v>
+      </c>
+      <c r="D36">
+        <f>Project!D33</f>
+        <v>5730000</v>
+      </c>
+      <c r="E36">
+        <f>Project!E33</f>
+        <v>2000000</v>
+      </c>
+      <c r="F36">
+        <f>Project!F33</f>
+        <v>3200000</v>
+      </c>
+      <c r="G36">
+        <f>Project!G33</f>
+        <v>4940000</v>
+      </c>
+      <c r="H36">
+        <f>Project!H33</f>
+        <v>4200000</v>
+      </c>
+      <c r="I36">
+        <f>Project!I33</f>
+        <v>4400000</v>
+      </c>
+      <c r="J36">
+        <f>Project!J33</f>
+        <v>7710000</v>
+      </c>
+      <c r="K36">
+        <f>Project!K33</f>
+        <v>4900000</v>
+      </c>
+      <c r="L36">
+        <f>Project!L33</f>
+        <v>10160000</v>
+      </c>
+      <c r="M36">
+        <f>Project!M33</f>
+        <v>9400000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A37" t="str">
+        <f>Project!A36</f>
+        <v>Actual-PD</v>
+      </c>
+      <c r="B37">
+        <f>Project!B36</f>
+        <v>47250</v>
+      </c>
+      <c r="C37">
+        <f>Project!C36</f>
+        <v>445896</v>
+      </c>
+      <c r="D37">
+        <f>Project!D36</f>
+        <v>549866</v>
+      </c>
+      <c r="E37">
+        <f>Project!E36</f>
+        <v>1452777</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/workforceresult.xlsx
+++ b/workforceresult.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miiintra/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7675D964-8ACC-2A4D-A466-0049CC9290EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{866B959A-1F95-544D-9FD8-F34B37D49CE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9320" yWindow="7920" windowWidth="28360" windowHeight="12340" activeTab="13" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
   </bookViews>
@@ -28,21 +28,6 @@
     <sheet name="Project" sheetId="13" r:id="rId13"/>
     <sheet name="GraphPJ" sheetId="14" r:id="rId14"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Project!$A$31</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Project!$A$32</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">Project!$B$34:$M$34</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">Project!$B$35:$M$35</definedName>
-    <definedName name="_xlchart.v1.12" hidden="1">Project!$B$36:$M$36</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Project!$A$33</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Project!$A$34</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Project!$A$35</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Project!$A$36</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">Project!$B$30:$M$30</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">Project!$B$31:$M$31</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">Project!$B$32:$M$32</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">Project!$B$33:$M$33</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1015,7 +1000,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1114,12 +1099,10 @@
     <xf numFmtId="0" fontId="3" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="21" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="22" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -12298,197 +12281,197 @@
       <c r="M30" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="N30" s="72"/>
-      <c r="O30" s="72"/>
-      <c r="P30" s="72"/>
-    </row>
-    <row r="31" spans="1:17" s="74" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A31" s="81" t="s">
+      <c r="N30" s="17"/>
+      <c r="O30" s="17"/>
+      <c r="P30" s="17"/>
+    </row>
+    <row r="31" spans="1:17" s="73" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A31" s="79" t="s">
         <v>18</v>
       </c>
-      <c r="B31" s="75">
-        <f>SUM(B32,B33)</f>
+      <c r="B31" s="74">
+        <f t="shared" ref="B31:M31" si="0">SUM(B32,B33)</f>
         <v>2717433</v>
       </c>
-      <c r="C31" s="75">
-        <f>SUM(C32,C33)</f>
+      <c r="C31" s="74">
+        <f t="shared" si="0"/>
         <v>6209433</v>
       </c>
-      <c r="D31" s="75">
-        <f>SUM(D32,D33)</f>
+      <c r="D31" s="74">
+        <f t="shared" si="0"/>
         <v>13563433</v>
       </c>
-      <c r="E31" s="75">
-        <f>SUM(E32,E33)</f>
+      <c r="E31" s="74">
+        <f t="shared" si="0"/>
         <v>7233433</v>
       </c>
-      <c r="F31" s="75">
-        <f>SUM(F32,F33)</f>
+      <c r="F31" s="74">
+        <f t="shared" si="0"/>
         <v>7406433</v>
       </c>
-      <c r="G31" s="75">
-        <f>SUM(G32,G33)</f>
+      <c r="G31" s="74">
+        <f t="shared" si="0"/>
         <v>19319433</v>
       </c>
-      <c r="H31" s="75">
-        <f>SUM(H32,H33)</f>
+      <c r="H31" s="74">
+        <f t="shared" si="0"/>
         <v>13479433</v>
       </c>
-      <c r="I31" s="75">
-        <f>SUM(I32,I33)</f>
+      <c r="I31" s="74">
+        <f t="shared" si="0"/>
         <v>10679433</v>
       </c>
-      <c r="J31" s="75">
-        <f>SUM(J32,J33)</f>
+      <c r="J31" s="74">
+        <f t="shared" si="0"/>
         <v>18089433</v>
       </c>
-      <c r="K31" s="75">
-        <f>SUM(K32,K33)</f>
+      <c r="K31" s="74">
+        <f t="shared" si="0"/>
         <v>16179433</v>
       </c>
-      <c r="L31" s="75">
-        <f>SUM(L32,L33)</f>
+      <c r="L31" s="74">
+        <f t="shared" si="0"/>
         <v>14539433</v>
       </c>
-      <c r="M31" s="75">
-        <f>SUM(M32,M33)</f>
+      <c r="M31" s="74">
+        <f t="shared" si="0"/>
         <v>19853233</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="73" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A32" s="78" t="s">
+    <row r="32" spans="1:17" s="72" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A32" s="76" t="s">
         <v>134</v>
       </c>
-      <c r="B32" s="76">
+      <c r="B32" s="75">
         <v>1787433</v>
       </c>
-      <c r="C32" s="76">
+      <c r="C32" s="75">
         <v>4779433</v>
       </c>
-      <c r="D32" s="76">
+      <c r="D32" s="75">
         <v>7833433</v>
       </c>
-      <c r="E32" s="76">
+      <c r="E32" s="75">
         <v>5233433</v>
       </c>
-      <c r="F32" s="76">
+      <c r="F32" s="75">
         <v>4206433</v>
       </c>
-      <c r="G32" s="76">
+      <c r="G32" s="75">
         <v>14379433</v>
       </c>
-      <c r="H32" s="76">
+      <c r="H32" s="75">
         <v>9279433</v>
       </c>
-      <c r="I32" s="76">
+      <c r="I32" s="75">
         <v>6279433</v>
       </c>
-      <c r="J32" s="76">
+      <c r="J32" s="75">
         <v>10379433</v>
       </c>
-      <c r="K32" s="76">
+      <c r="K32" s="75">
         <v>11279433</v>
       </c>
-      <c r="L32" s="76">
+      <c r="L32" s="75">
         <v>4379433</v>
       </c>
-      <c r="M32" s="76">
+      <c r="M32" s="75">
         <v>10453233</v>
       </c>
     </row>
-    <row r="33" spans="1:13" s="73" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A33" s="78" t="s">
+    <row r="33" spans="1:13" s="72" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A33" s="76" t="s">
         <v>135</v>
       </c>
-      <c r="B33" s="76">
+      <c r="B33" s="75">
         <v>930000</v>
       </c>
-      <c r="C33" s="76">
+      <c r="C33" s="75">
         <v>1430000</v>
       </c>
-      <c r="D33" s="76">
+      <c r="D33" s="75">
         <v>5730000</v>
       </c>
-      <c r="E33" s="76">
+      <c r="E33" s="75">
         <v>2000000</v>
       </c>
-      <c r="F33" s="76">
+      <c r="F33" s="75">
         <v>3200000</v>
       </c>
-      <c r="G33" s="76">
+      <c r="G33" s="75">
         <v>4940000</v>
       </c>
-      <c r="H33" s="76">
+      <c r="H33" s="75">
         <v>4200000</v>
       </c>
-      <c r="I33" s="76">
+      <c r="I33" s="75">
         <v>4400000</v>
       </c>
-      <c r="J33" s="76">
+      <c r="J33" s="75">
         <v>7710000</v>
       </c>
-      <c r="K33" s="76">
+      <c r="K33" s="75">
         <v>4900000</v>
       </c>
-      <c r="L33" s="76">
+      <c r="L33" s="75">
         <v>10160000</v>
       </c>
-      <c r="M33" s="76">
+      <c r="M33" s="75">
         <v>9400000</v>
       </c>
     </row>
-    <row r="34" spans="1:13" s="74" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A34" s="80" t="s">
+    <row r="34" spans="1:13" s="73" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A34" s="78" t="s">
         <v>130</v>
       </c>
-      <c r="B34" s="75">
+      <c r="B34" s="74">
         <f>SUM(B35,B36)</f>
         <v>1049908</v>
       </c>
-      <c r="C34" s="75">
-        <f t="shared" ref="C34:E34" si="0">SUM(C35,C36)</f>
+      <c r="C34" s="74">
+        <f t="shared" ref="C34:E34" si="1">SUM(C35,C36)</f>
         <v>6155989</v>
       </c>
-      <c r="D34" s="75">
-        <f t="shared" si="0"/>
+      <c r="D34" s="74">
+        <f t="shared" si="1"/>
         <v>9094371</v>
       </c>
-      <c r="E34" s="75">
-        <f t="shared" si="0"/>
+      <c r="E34" s="74">
+        <f t="shared" si="1"/>
         <v>6308025</v>
       </c>
     </row>
-    <row r="35" spans="1:13" s="73" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A35" s="79" t="s">
+    <row r="35" spans="1:13" s="72" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A35" s="77" t="s">
         <v>136</v>
       </c>
-      <c r="B35" s="77">
+      <c r="B35" s="75">
         <v>1002658</v>
       </c>
-      <c r="C35" s="77">
+      <c r="C35" s="75">
         <v>5710093</v>
       </c>
-      <c r="D35" s="77">
+      <c r="D35" s="75">
         <v>8544505</v>
       </c>
-      <c r="E35" s="77">
+      <c r="E35" s="75">
         <v>4855248</v>
       </c>
     </row>
-    <row r="36" spans="1:13" s="73" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A36" s="79" t="s">
+    <row r="36" spans="1:13" s="72" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A36" s="77" t="s">
         <v>137</v>
       </c>
-      <c r="B36" s="77">
+      <c r="B36" s="75">
         <v>47250</v>
       </c>
-      <c r="C36" s="77">
+      <c r="C36" s="75">
         <v>445896</v>
       </c>
-      <c r="D36" s="77">
+      <c r="D36" s="75">
         <v>549866</v>
       </c>
-      <c r="E36" s="77">
+      <c r="E36" s="75">
         <v>1452777</v>
       </c>
     </row>
@@ -14417,52 +14400,52 @@
         <v>Plan</v>
       </c>
       <c r="B32">
-        <f>Project!B31</f>
-        <v>2717433</v>
+        <f>(Project!B31)/1000000</f>
+        <v>2.7174330000000002</v>
       </c>
       <c r="C32">
-        <f>Project!C31</f>
-        <v>6209433</v>
+        <f>(Project!C31)/1000000</f>
+        <v>6.2094329999999998</v>
       </c>
       <c r="D32">
-        <f>Project!D31</f>
-        <v>13563433</v>
+        <f>(Project!D31)/1000000</f>
+        <v>13.563433</v>
       </c>
       <c r="E32">
-        <f>Project!E31</f>
-        <v>7233433</v>
+        <f>(Project!E31)/1000000</f>
+        <v>7.2334329999999998</v>
       </c>
       <c r="F32">
-        <f>Project!F31</f>
-        <v>7406433</v>
+        <f>(Project!F31)/1000000</f>
+        <v>7.4064329999999998</v>
       </c>
       <c r="G32">
-        <f>Project!G31</f>
-        <v>19319433</v>
+        <f>(Project!G31)/1000000</f>
+        <v>19.319433</v>
       </c>
       <c r="H32">
-        <f>Project!H31</f>
-        <v>13479433</v>
+        <f>(Project!H31)/1000000</f>
+        <v>13.479433</v>
       </c>
       <c r="I32">
-        <f>Project!I31</f>
-        <v>10679433</v>
+        <f>(Project!I31)/1000000</f>
+        <v>10.679433</v>
       </c>
       <c r="J32">
-        <f>Project!J31</f>
-        <v>18089433</v>
+        <f>(Project!J31)/1000000</f>
+        <v>18.089433</v>
       </c>
       <c r="K32">
-        <f>Project!K31</f>
-        <v>16179433</v>
+        <f>(Project!K31)/1000000</f>
+        <v>16.179433</v>
       </c>
       <c r="L32">
-        <f>Project!L31</f>
-        <v>14539433</v>
+        <f>(Project!L31)/1000000</f>
+        <v>14.539433000000001</v>
       </c>
       <c r="M32">
-        <f>Project!M31</f>
-        <v>19853233</v>
+        <f>(Project!M31)/1000000</f>
+        <v>19.853232999999999</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.2">
@@ -14471,20 +14454,20 @@
         <v>Actual</v>
       </c>
       <c r="B33">
-        <f>Project!B34</f>
-        <v>1049908</v>
+        <f>(Project!B34)/1000000</f>
+        <v>1.0499080000000001</v>
       </c>
       <c r="C33">
-        <f>Project!C34</f>
-        <v>6155989</v>
+        <f>(Project!C34)/1000000</f>
+        <v>6.1559889999999999</v>
       </c>
       <c r="D33">
-        <f>Project!D34</f>
-        <v>9094371</v>
+        <f>(Project!D34)/1000000</f>
+        <v>9.0943710000000006</v>
       </c>
       <c r="E33">
-        <f>Project!E34</f>
-        <v>6308025</v>
+        <f>(Project!E34)/1000000</f>
+        <v>6.3080249999999998</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.2">
@@ -14493,52 +14476,52 @@
         <v>Plan-PS</v>
       </c>
       <c r="B34">
-        <f>Project!B32</f>
-        <v>1787433</v>
+        <f>(Project!B32)/1000000</f>
+        <v>1.787433</v>
       </c>
       <c r="C34">
-        <f>Project!C32</f>
-        <v>4779433</v>
+        <f>(Project!C32)/1000000</f>
+        <v>4.779433</v>
       </c>
       <c r="D34">
-        <f>Project!D32</f>
-        <v>7833433</v>
+        <f>(Project!D32)/1000000</f>
+        <v>7.8334330000000003</v>
       </c>
       <c r="E34">
-        <f>Project!E32</f>
-        <v>5233433</v>
+        <f>(Project!E32)/1000000</f>
+        <v>5.2334329999999998</v>
       </c>
       <c r="F34">
-        <f>Project!F32</f>
-        <v>4206433</v>
+        <f>(Project!F32)/1000000</f>
+        <v>4.2064329999999996</v>
       </c>
       <c r="G34">
-        <f>Project!G32</f>
-        <v>14379433</v>
+        <f>(Project!G32)/1000000</f>
+        <v>14.379433000000001</v>
       </c>
       <c r="H34">
-        <f>Project!H32</f>
-        <v>9279433</v>
+        <f>(Project!H32)/1000000</f>
+        <v>9.2794329999999992</v>
       </c>
       <c r="I34">
-        <f>Project!I32</f>
-        <v>6279433</v>
+        <f>(Project!I32)/1000000</f>
+        <v>6.279433</v>
       </c>
       <c r="J34">
-        <f>Project!J32</f>
-        <v>10379433</v>
+        <f>(Project!J32)/1000000</f>
+        <v>10.379433000000001</v>
       </c>
       <c r="K34">
-        <f>Project!K32</f>
-        <v>11279433</v>
+        <f>(Project!K32)/1000000</f>
+        <v>11.279432999999999</v>
       </c>
       <c r="L34">
-        <f>Project!L32</f>
-        <v>4379433</v>
+        <f>(Project!L32)/1000000</f>
+        <v>4.3794329999999997</v>
       </c>
       <c r="M34">
-        <f>Project!M32</f>
-        <v>10453233</v>
+        <f>(Project!M32)/1000000</f>
+        <v>10.453233000000001</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.2">
@@ -14547,20 +14530,20 @@
         <v>Actual-PS</v>
       </c>
       <c r="B35">
-        <f>Project!B35</f>
-        <v>1002658</v>
+        <f>(Project!B35)/1000000</f>
+        <v>1.002658</v>
       </c>
       <c r="C35">
-        <f>Project!C35</f>
-        <v>5710093</v>
+        <f>(Project!C35)/1000000</f>
+        <v>5.7100929999999996</v>
       </c>
       <c r="D35">
-        <f>Project!D35</f>
-        <v>8544505</v>
+        <f>(Project!D35)/1000000</f>
+        <v>8.5445049999999991</v>
       </c>
       <c r="E35">
-        <f>Project!E35</f>
-        <v>4855248</v>
+        <f>(Project!E35)/1000000</f>
+        <v>4.8552479999999996</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.2">
@@ -14569,52 +14552,52 @@
         <v>Plan-PD</v>
       </c>
       <c r="B36">
-        <f>Project!B33</f>
-        <v>930000</v>
+        <f>(Project!B33)/1000000</f>
+        <v>0.93</v>
       </c>
       <c r="C36">
-        <f>Project!C33</f>
-        <v>1430000</v>
+        <f>(Project!C33)/1000000</f>
+        <v>1.43</v>
       </c>
       <c r="D36">
-        <f>Project!D33</f>
-        <v>5730000</v>
+        <f>(Project!D33)/1000000</f>
+        <v>5.73</v>
       </c>
       <c r="E36">
-        <f>Project!E33</f>
-        <v>2000000</v>
+        <f>(Project!E33)/1000000</f>
+        <v>2</v>
       </c>
       <c r="F36">
-        <f>Project!F33</f>
-        <v>3200000</v>
+        <f>(Project!F33)/1000000</f>
+        <v>3.2</v>
       </c>
       <c r="G36">
-        <f>Project!G33</f>
-        <v>4940000</v>
+        <f>(Project!G33)/1000000</f>
+        <v>4.9400000000000004</v>
       </c>
       <c r="H36">
-        <f>Project!H33</f>
-        <v>4200000</v>
+        <f>(Project!H33)/1000000</f>
+        <v>4.2</v>
       </c>
       <c r="I36">
-        <f>Project!I33</f>
-        <v>4400000</v>
+        <f>(Project!I33)/1000000</f>
+        <v>4.4000000000000004</v>
       </c>
       <c r="J36">
-        <f>Project!J33</f>
-        <v>7710000</v>
+        <f>(Project!J33)/1000000</f>
+        <v>7.71</v>
       </c>
       <c r="K36">
-        <f>Project!K33</f>
-        <v>4900000</v>
+        <f>(Project!K33)/1000000</f>
+        <v>4.9000000000000004</v>
       </c>
       <c r="L36">
-        <f>Project!L33</f>
-        <v>10160000</v>
+        <f>(Project!L33)/1000000</f>
+        <v>10.16</v>
       </c>
       <c r="M36">
-        <f>Project!M33</f>
-        <v>9400000</v>
+        <f>(Project!M33)/1000000</f>
+        <v>9.4</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.2">
@@ -14623,20 +14606,20 @@
         <v>Actual-PD</v>
       </c>
       <c r="B37">
-        <f>Project!B36</f>
-        <v>47250</v>
+        <f>(Project!B36)/1000000</f>
+        <v>4.725E-2</v>
       </c>
       <c r="C37">
-        <f>Project!C36</f>
-        <v>445896</v>
+        <f>(Project!C36)/1000000</f>
+        <v>0.44589600000000001</v>
       </c>
       <c r="D37">
-        <f>Project!D36</f>
-        <v>549866</v>
+        <f>(Project!D36)/1000000</f>
+        <v>0.54986599999999997</v>
       </c>
       <c r="E37">
-        <f>Project!E36</f>
-        <v>1452777</v>
+        <f>(Project!E36)/1000000</f>
+        <v>1.452777</v>
       </c>
     </row>
   </sheetData>

--- a/workforceresult.xlsx
+++ b/workforceresult.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miiintra/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{866B959A-1F95-544D-9FD8-F34B37D49CE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABBBC3E4-162B-5345-A64F-83D1ED82DC8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9320" yWindow="7920" windowWidth="28360" windowHeight="12340" activeTab="13" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
+    <workbookView xWindow="18180" yWindow="7760" windowWidth="28360" windowHeight="12340" activeTab="13" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
   </bookViews>
   <sheets>
     <sheet name="ALL" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="138">
   <si>
     <t>Type</t>
   </si>
@@ -645,9 +645,6 @@
   <si>
     <t>Actual-PD</t>
   </si>
-  <si>
-    <t>Project Plan and Actual Income</t>
-  </si>
 </sst>
 </file>
 
@@ -656,7 +653,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -810,6 +807,14 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="27">
@@ -997,10 +1002,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1107,12 +1113,23 @@
     <xf numFmtId="0" fontId="21" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="22" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="22" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF007D39"/>
+      <color rgb="FF009744"/>
+      <color rgb="FF006930"/>
+      <color rgb="FF008C40"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -12485,7 +12502,7 @@
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
-  <dimension ref="A1:T37"/>
+  <dimension ref="A1:T46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.1640625" bestFit="1" customWidth="1"/>
@@ -14342,9 +14359,7 @@
       <c r="A29" s="58"/>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A31" s="58" t="s">
-        <v>138</v>
-      </c>
+      <c r="A31" s="58"/>
       <c r="B31" s="58" t="str">
         <f>Project!B30</f>
         <v>JAN</v>
@@ -14622,6 +14637,18 @@
         <v>1.452777</v>
       </c>
     </row>
+    <row r="39" spans="1:13" s="80" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="40" spans="1:13" s="80" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="41" spans="1:13" s="80" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="42" spans="1:13" s="80" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="43" spans="1:13" s="80" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="44" spans="1:13" s="80" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B44" s="81"/>
+    </row>
+    <row r="45" spans="1:13" s="80" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B45" s="81"/>
+    </row>
+    <row r="46" spans="1:13" s="80" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/workforceresult.xlsx
+++ b/workforceresult.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miiintra/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABBBC3E4-162B-5345-A64F-83D1ED82DC8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{872FD1FC-0569-B542-924A-E879454B919E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18180" yWindow="7760" windowWidth="28360" windowHeight="12340" activeTab="13" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
+    <workbookView xWindow="16440" yWindow="7760" windowWidth="28360" windowHeight="12340" activeTab="13" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
   </bookViews>
   <sheets>
     <sheet name="ALL" sheetId="1" r:id="rId1"/>
@@ -653,7 +653,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -812,6 +812,13 @@
       <u/>
       <sz val="12"/>
       <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="6"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1006,7 +1013,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1113,8 +1120,9 @@
     <xf numFmtId="0" fontId="21" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="22" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="22" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -11359,7 +11367,7 @@
   <sheetPr>
     <tabColor rgb="FF002060"/>
   </sheetPr>
-  <dimension ref="A1:V36"/>
+  <dimension ref="A1:V57"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.6640625" bestFit="1" customWidth="1"/>
@@ -12492,6 +12500,544 @@
         <v>1452777</v>
       </c>
     </row>
+    <row r="40" spans="1:13" s="81" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B40" s="81" t="str">
+        <f>B30</f>
+        <v>JAN</v>
+      </c>
+      <c r="C40" s="81" t="str">
+        <f t="shared" ref="C40:M40" si="2">C30</f>
+        <v>FEB</v>
+      </c>
+      <c r="D40" s="81" t="str">
+        <f t="shared" si="2"/>
+        <v>MAR</v>
+      </c>
+      <c r="E40" s="81" t="str">
+        <f t="shared" si="2"/>
+        <v>APR</v>
+      </c>
+      <c r="F40" s="81" t="str">
+        <f t="shared" si="2"/>
+        <v>MAY</v>
+      </c>
+      <c r="G40" s="81" t="str">
+        <f t="shared" si="2"/>
+        <v>JUN</v>
+      </c>
+      <c r="H40" s="81" t="str">
+        <f t="shared" si="2"/>
+        <v>JUL</v>
+      </c>
+      <c r="I40" s="81" t="str">
+        <f t="shared" si="2"/>
+        <v>AUG</v>
+      </c>
+      <c r="J40" s="81" t="str">
+        <f t="shared" si="2"/>
+        <v>SEP</v>
+      </c>
+      <c r="K40" s="81" t="str">
+        <f t="shared" si="2"/>
+        <v>OCT</v>
+      </c>
+      <c r="L40" s="81" t="str">
+        <f t="shared" si="2"/>
+        <v>NOV</v>
+      </c>
+      <c r="M40" s="81" t="str">
+        <f t="shared" si="2"/>
+        <v>DEC</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" s="81" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="81" t="str">
+        <f>A31</f>
+        <v>Plan</v>
+      </c>
+      <c r="B41" s="82">
+        <f>B31/1000000</f>
+        <v>2.7174330000000002</v>
+      </c>
+      <c r="C41" s="82">
+        <f t="shared" ref="C41:M41" si="3">C31/1000000</f>
+        <v>6.2094329999999998</v>
+      </c>
+      <c r="D41" s="82">
+        <f t="shared" si="3"/>
+        <v>13.563433</v>
+      </c>
+      <c r="E41" s="82">
+        <f t="shared" si="3"/>
+        <v>7.2334329999999998</v>
+      </c>
+      <c r="F41" s="82">
+        <f t="shared" si="3"/>
+        <v>7.4064329999999998</v>
+      </c>
+      <c r="G41" s="82">
+        <f t="shared" si="3"/>
+        <v>19.319433</v>
+      </c>
+      <c r="H41" s="82">
+        <f t="shared" si="3"/>
+        <v>13.479433</v>
+      </c>
+      <c r="I41" s="82">
+        <f t="shared" si="3"/>
+        <v>10.679433</v>
+      </c>
+      <c r="J41" s="82">
+        <f t="shared" si="3"/>
+        <v>18.089433</v>
+      </c>
+      <c r="K41" s="82">
+        <f t="shared" si="3"/>
+        <v>16.179433</v>
+      </c>
+      <c r="L41" s="82">
+        <f t="shared" si="3"/>
+        <v>14.539433000000001</v>
+      </c>
+      <c r="M41" s="82">
+        <f t="shared" si="3"/>
+        <v>19.853232999999999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" s="81" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="81" t="str">
+        <f>A34</f>
+        <v>Actual</v>
+      </c>
+      <c r="B42" s="82">
+        <f>B34/1000000</f>
+        <v>1.0499080000000001</v>
+      </c>
+      <c r="C42" s="82">
+        <f t="shared" ref="C42:E42" si="4">C34/1000000</f>
+        <v>6.1559889999999999</v>
+      </c>
+      <c r="D42" s="82">
+        <f t="shared" si="4"/>
+        <v>9.0943710000000006</v>
+      </c>
+      <c r="E42" s="82">
+        <f t="shared" si="4"/>
+        <v>6.3080249999999998</v>
+      </c>
+      <c r="F42" s="82"/>
+      <c r="G42" s="82"/>
+      <c r="H42" s="82"/>
+      <c r="I42" s="82"/>
+      <c r="J42" s="82"/>
+      <c r="K42" s="82"/>
+      <c r="L42" s="82"/>
+      <c r="M42" s="82"/>
+    </row>
+    <row r="43" spans="1:13" s="81" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="81" t="str">
+        <f>A32</f>
+        <v>Plan-PS</v>
+      </c>
+      <c r="B43" s="82">
+        <f>B32/1000000</f>
+        <v>1.787433</v>
+      </c>
+      <c r="C43" s="82">
+        <f t="shared" ref="C43:M43" si="5">C32/1000000</f>
+        <v>4.779433</v>
+      </c>
+      <c r="D43" s="82">
+        <f t="shared" si="5"/>
+        <v>7.8334330000000003</v>
+      </c>
+      <c r="E43" s="82">
+        <f t="shared" si="5"/>
+        <v>5.2334329999999998</v>
+      </c>
+      <c r="F43" s="82">
+        <f t="shared" si="5"/>
+        <v>4.2064329999999996</v>
+      </c>
+      <c r="G43" s="82">
+        <f t="shared" si="5"/>
+        <v>14.379433000000001</v>
+      </c>
+      <c r="H43" s="82">
+        <f t="shared" si="5"/>
+        <v>9.2794329999999992</v>
+      </c>
+      <c r="I43" s="82">
+        <f t="shared" si="5"/>
+        <v>6.279433</v>
+      </c>
+      <c r="J43" s="82">
+        <f t="shared" si="5"/>
+        <v>10.379433000000001</v>
+      </c>
+      <c r="K43" s="82">
+        <f t="shared" si="5"/>
+        <v>11.279432999999999</v>
+      </c>
+      <c r="L43" s="82">
+        <f t="shared" si="5"/>
+        <v>4.3794329999999997</v>
+      </c>
+      <c r="M43" s="82">
+        <f t="shared" si="5"/>
+        <v>10.453233000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" s="81" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="81" t="str">
+        <f>A35</f>
+        <v>Actual-PS</v>
+      </c>
+      <c r="B44" s="82">
+        <f>B35/1000000</f>
+        <v>1.002658</v>
+      </c>
+      <c r="C44" s="82">
+        <f t="shared" ref="C44:E44" si="6">C35/1000000</f>
+        <v>5.7100929999999996</v>
+      </c>
+      <c r="D44" s="82">
+        <f t="shared" si="6"/>
+        <v>8.5445049999999991</v>
+      </c>
+      <c r="E44" s="82">
+        <f t="shared" si="6"/>
+        <v>4.8552479999999996</v>
+      </c>
+      <c r="F44" s="82"/>
+      <c r="G44" s="82"/>
+      <c r="H44" s="82"/>
+      <c r="I44" s="82"/>
+      <c r="J44" s="82"/>
+      <c r="K44" s="82"/>
+      <c r="L44" s="82"/>
+      <c r="M44" s="82"/>
+    </row>
+    <row r="45" spans="1:13" s="81" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="81" t="str">
+        <f>A33</f>
+        <v>Plan-PD</v>
+      </c>
+      <c r="B45" s="82">
+        <f>B33/1000000</f>
+        <v>0.93</v>
+      </c>
+      <c r="C45" s="82">
+        <f t="shared" ref="C45:M45" si="7">C33/1000000</f>
+        <v>1.43</v>
+      </c>
+      <c r="D45" s="82">
+        <f t="shared" si="7"/>
+        <v>5.73</v>
+      </c>
+      <c r="E45" s="82">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="F45" s="82">
+        <f t="shared" si="7"/>
+        <v>3.2</v>
+      </c>
+      <c r="G45" s="82">
+        <f t="shared" si="7"/>
+        <v>4.9400000000000004</v>
+      </c>
+      <c r="H45" s="82">
+        <f t="shared" si="7"/>
+        <v>4.2</v>
+      </c>
+      <c r="I45" s="82">
+        <f t="shared" si="7"/>
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="J45" s="82">
+        <f t="shared" si="7"/>
+        <v>7.71</v>
+      </c>
+      <c r="K45" s="82">
+        <f t="shared" si="7"/>
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="L45" s="82">
+        <f t="shared" si="7"/>
+        <v>10.16</v>
+      </c>
+      <c r="M45" s="82">
+        <f t="shared" si="7"/>
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" s="81" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="81" t="str">
+        <f>A36</f>
+        <v>Actual-PD</v>
+      </c>
+      <c r="B46" s="82">
+        <f>B36/1000000</f>
+        <v>4.725E-2</v>
+      </c>
+      <c r="C46" s="82">
+        <f t="shared" ref="C46:E46" si="8">C36/1000000</f>
+        <v>0.44589600000000001</v>
+      </c>
+      <c r="D46" s="82">
+        <f t="shared" si="8"/>
+        <v>0.54986599999999997</v>
+      </c>
+      <c r="E46" s="82">
+        <f t="shared" si="8"/>
+        <v>1.452777</v>
+      </c>
+      <c r="F46" s="82"/>
+      <c r="G46" s="82"/>
+      <c r="H46" s="82"/>
+      <c r="I46" s="82"/>
+      <c r="J46" s="82"/>
+      <c r="K46" s="82"/>
+      <c r="L46" s="82"/>
+      <c r="M46" s="82"/>
+    </row>
+    <row r="47" spans="1:13" s="81" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="48" spans="1:13" s="81" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="49" spans="1:13" s="81" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="50" spans="1:13" s="81" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="51" spans="1:13" s="81" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B51" s="81" t="str">
+        <f>B40</f>
+        <v>JAN</v>
+      </c>
+      <c r="C51" s="81" t="str">
+        <f>C40</f>
+        <v>FEB</v>
+      </c>
+      <c r="D51" s="81" t="str">
+        <f>D40</f>
+        <v>MAR</v>
+      </c>
+      <c r="E51" s="81" t="str">
+        <f>E40</f>
+        <v>APR</v>
+      </c>
+      <c r="F51" s="81" t="str">
+        <f>F40</f>
+        <v>MAY</v>
+      </c>
+      <c r="G51" s="81" t="str">
+        <f>G40</f>
+        <v>JUN</v>
+      </c>
+      <c r="H51" s="81" t="str">
+        <f>H40</f>
+        <v>JUL</v>
+      </c>
+      <c r="I51" s="81" t="str">
+        <f>I40</f>
+        <v>AUG</v>
+      </c>
+      <c r="J51" s="81" t="str">
+        <f>J40</f>
+        <v>SEP</v>
+      </c>
+      <c r="K51" s="81" t="str">
+        <f>K40</f>
+        <v>OCT</v>
+      </c>
+      <c r="L51" s="81" t="str">
+        <f>L40</f>
+        <v>NOV</v>
+      </c>
+      <c r="M51" s="81" t="str">
+        <f>M40</f>
+        <v>DEC</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" s="81" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="81" t="str">
+        <f>A41</f>
+        <v>Plan</v>
+      </c>
+      <c r="B52" s="81">
+        <v>2.72</v>
+      </c>
+      <c r="C52" s="81">
+        <v>6.21</v>
+      </c>
+      <c r="D52" s="81">
+        <v>13.56</v>
+      </c>
+      <c r="E52" s="81">
+        <v>7.23</v>
+      </c>
+      <c r="F52" s="81">
+        <v>7.41</v>
+      </c>
+      <c r="G52" s="81">
+        <v>19.32</v>
+      </c>
+      <c r="H52" s="81">
+        <v>13.48</v>
+      </c>
+      <c r="I52" s="81">
+        <v>10.68</v>
+      </c>
+      <c r="J52" s="81">
+        <v>18.09</v>
+      </c>
+      <c r="K52" s="81">
+        <v>16.18</v>
+      </c>
+      <c r="L52" s="81">
+        <v>14.54</v>
+      </c>
+      <c r="M52" s="81">
+        <v>19.850000000000001</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" s="81" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="81" t="str">
+        <f t="shared" ref="A53:A57" si="9">A42</f>
+        <v>Actual</v>
+      </c>
+      <c r="B53" s="81">
+        <v>1.05</v>
+      </c>
+      <c r="C53" s="81">
+        <v>6.16</v>
+      </c>
+      <c r="D53" s="81">
+        <v>9.09</v>
+      </c>
+      <c r="E53" s="81">
+        <v>6.31</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" s="81" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="81" t="str">
+        <f t="shared" si="9"/>
+        <v>Plan-PS</v>
+      </c>
+      <c r="B54" s="81">
+        <v>1.79</v>
+      </c>
+      <c r="C54" s="81">
+        <v>4.78</v>
+      </c>
+      <c r="D54" s="81">
+        <v>7.83</v>
+      </c>
+      <c r="E54" s="81">
+        <v>5.23</v>
+      </c>
+      <c r="F54" s="81">
+        <v>4.21</v>
+      </c>
+      <c r="G54" s="81">
+        <v>14.38</v>
+      </c>
+      <c r="H54" s="81">
+        <v>9.2799999999999994</v>
+      </c>
+      <c r="I54" s="81">
+        <v>6.28</v>
+      </c>
+      <c r="J54" s="81">
+        <v>10.38</v>
+      </c>
+      <c r="K54" s="81">
+        <v>11.28</v>
+      </c>
+      <c r="L54" s="81">
+        <v>4.38</v>
+      </c>
+      <c r="M54" s="81">
+        <v>10.45</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" s="81" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="81" t="str">
+        <f t="shared" si="9"/>
+        <v>Actual-PS</v>
+      </c>
+      <c r="B55" s="81">
+        <v>1</v>
+      </c>
+      <c r="C55" s="81">
+        <v>5.71</v>
+      </c>
+      <c r="D55" s="81">
+        <v>8.5399999999999991</v>
+      </c>
+      <c r="E55" s="81">
+        <v>4.8600000000000003</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" s="81" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="81" t="str">
+        <f t="shared" si="9"/>
+        <v>Plan-PD</v>
+      </c>
+      <c r="B56" s="81">
+        <v>0.93</v>
+      </c>
+      <c r="C56" s="81">
+        <v>1.43</v>
+      </c>
+      <c r="D56" s="81">
+        <v>5.73</v>
+      </c>
+      <c r="E56" s="81">
+        <v>2</v>
+      </c>
+      <c r="F56" s="81">
+        <v>3.2</v>
+      </c>
+      <c r="G56" s="81">
+        <v>4.9400000000000004</v>
+      </c>
+      <c r="H56" s="81">
+        <v>4.2</v>
+      </c>
+      <c r="I56" s="81">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="J56" s="81">
+        <v>7.71</v>
+      </c>
+      <c r="K56" s="81">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="L56" s="81">
+        <v>10.16</v>
+      </c>
+      <c r="M56" s="81">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" s="81" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="81" t="str">
+        <f t="shared" si="9"/>
+        <v>Actual-PD</v>
+      </c>
+      <c r="B57" s="81">
+        <v>0.05</v>
+      </c>
+      <c r="C57" s="81">
+        <v>0.45</v>
+      </c>
+      <c r="D57" s="81">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="E57" s="81">
+        <v>1.45</v>
+      </c>
+      <c r="F57" s="82"/>
+      <c r="L57" s="82"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -12502,7 +13048,7 @@
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
-  <dimension ref="A1:T46"/>
+  <dimension ref="A1:T45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.1640625" bestFit="1" customWidth="1"/>
@@ -14361,294 +14907,288 @@
     <row r="31" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A31" s="58"/>
       <c r="B31" s="58" t="str">
-        <f>Project!B30</f>
+        <f>Project!B51</f>
         <v>JAN</v>
       </c>
       <c r="C31" s="58" t="str">
-        <f>Project!C30</f>
+        <f>Project!C51</f>
         <v>FEB</v>
       </c>
       <c r="D31" s="58" t="str">
-        <f>Project!D30</f>
+        <f>Project!D51</f>
         <v>MAR</v>
       </c>
       <c r="E31" s="58" t="str">
-        <f>Project!E30</f>
+        <f>Project!E51</f>
         <v>APR</v>
       </c>
       <c r="F31" s="58" t="str">
-        <f>Project!F30</f>
+        <f>Project!F51</f>
         <v>MAY</v>
       </c>
       <c r="G31" s="58" t="str">
-        <f>Project!G30</f>
+        <f>Project!G51</f>
         <v>JUN</v>
       </c>
       <c r="H31" s="58" t="str">
-        <f>Project!H30</f>
+        <f>Project!H51</f>
         <v>JUL</v>
       </c>
       <c r="I31" s="58" t="str">
-        <f>Project!I30</f>
+        <f>Project!I51</f>
         <v>AUG</v>
       </c>
       <c r="J31" s="58" t="str">
-        <f>Project!J30</f>
+        <f>Project!J51</f>
         <v>SEP</v>
       </c>
       <c r="K31" s="58" t="str">
-        <f>Project!K30</f>
+        <f>Project!K51</f>
         <v>OCT</v>
       </c>
       <c r="L31" s="58" t="str">
-        <f>Project!L30</f>
+        <f>Project!L51</f>
         <v>NOV</v>
       </c>
       <c r="M31" s="58" t="str">
-        <f>Project!M30</f>
+        <f>Project!M51</f>
         <v>DEC</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A32" t="str">
-        <f>Project!A31</f>
+        <f>Project!A52</f>
         <v>Plan</v>
       </c>
       <c r="B32">
-        <f>(Project!B31)/1000000</f>
-        <v>2.7174330000000002</v>
+        <f>Project!B52</f>
+        <v>2.72</v>
       </c>
       <c r="C32">
-        <f>(Project!C31)/1000000</f>
-        <v>6.2094329999999998</v>
+        <f>Project!C52</f>
+        <v>6.21</v>
       </c>
       <c r="D32">
-        <f>(Project!D31)/1000000</f>
-        <v>13.563433</v>
+        <f>Project!D52</f>
+        <v>13.56</v>
       </c>
       <c r="E32">
-        <f>(Project!E31)/1000000</f>
-        <v>7.2334329999999998</v>
+        <f>Project!E52</f>
+        <v>7.23</v>
       </c>
       <c r="F32">
-        <f>(Project!F31)/1000000</f>
-        <v>7.4064329999999998</v>
+        <f>Project!F52</f>
+        <v>7.41</v>
       </c>
       <c r="G32">
-        <f>(Project!G31)/1000000</f>
-        <v>19.319433</v>
+        <f>Project!G52</f>
+        <v>19.32</v>
       </c>
       <c r="H32">
-        <f>(Project!H31)/1000000</f>
-        <v>13.479433</v>
+        <f>Project!H52</f>
+        <v>13.48</v>
       </c>
       <c r="I32">
-        <f>(Project!I31)/1000000</f>
-        <v>10.679433</v>
+        <f>Project!I52</f>
+        <v>10.68</v>
       </c>
       <c r="J32">
-        <f>(Project!J31)/1000000</f>
-        <v>18.089433</v>
+        <f>Project!J52</f>
+        <v>18.09</v>
       </c>
       <c r="K32">
-        <f>(Project!K31)/1000000</f>
-        <v>16.179433</v>
+        <f>Project!K52</f>
+        <v>16.18</v>
       </c>
       <c r="L32">
-        <f>(Project!L31)/1000000</f>
-        <v>14.539433000000001</v>
+        <f>Project!L52</f>
+        <v>14.54</v>
       </c>
       <c r="M32">
-        <f>(Project!M31)/1000000</f>
-        <v>19.853232999999999</v>
+        <f>Project!M52</f>
+        <v>19.850000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33" t="str">
-        <f>Project!A34</f>
+        <f>Project!A53</f>
         <v>Actual</v>
       </c>
       <c r="B33">
-        <f>(Project!B34)/1000000</f>
-        <v>1.0499080000000001</v>
+        <f>Project!B53</f>
+        <v>1.05</v>
       </c>
       <c r="C33">
-        <f>(Project!C34)/1000000</f>
-        <v>6.1559889999999999</v>
+        <f>Project!C53</f>
+        <v>6.16</v>
       </c>
       <c r="D33">
-        <f>(Project!D34)/1000000</f>
-        <v>9.0943710000000006</v>
+        <f>Project!D53</f>
+        <v>9.09</v>
       </c>
       <c r="E33">
-        <f>(Project!E34)/1000000</f>
-        <v>6.3080249999999998</v>
+        <f>Project!E53</f>
+        <v>6.31</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34" t="str">
-        <f>Project!A32</f>
+        <f>Project!A54</f>
         <v>Plan-PS</v>
       </c>
       <c r="B34">
-        <f>(Project!B32)/1000000</f>
-        <v>1.787433</v>
+        <f>Project!B54</f>
+        <v>1.79</v>
       </c>
       <c r="C34">
-        <f>(Project!C32)/1000000</f>
-        <v>4.779433</v>
+        <f>Project!C54</f>
+        <v>4.78</v>
       </c>
       <c r="D34">
-        <f>(Project!D32)/1000000</f>
-        <v>7.8334330000000003</v>
+        <f>Project!D54</f>
+        <v>7.83</v>
       </c>
       <c r="E34">
-        <f>(Project!E32)/1000000</f>
-        <v>5.2334329999999998</v>
+        <f>Project!E54</f>
+        <v>5.23</v>
       </c>
       <c r="F34">
-        <f>(Project!F32)/1000000</f>
-        <v>4.2064329999999996</v>
+        <f>Project!F54</f>
+        <v>4.21</v>
       </c>
       <c r="G34">
-        <f>(Project!G32)/1000000</f>
-        <v>14.379433000000001</v>
+        <f>Project!G54</f>
+        <v>14.38</v>
       </c>
       <c r="H34">
-        <f>(Project!H32)/1000000</f>
-        <v>9.2794329999999992</v>
+        <f>Project!H54</f>
+        <v>9.2799999999999994</v>
       </c>
       <c r="I34">
-        <f>(Project!I32)/1000000</f>
-        <v>6.279433</v>
+        <f>Project!I54</f>
+        <v>6.28</v>
       </c>
       <c r="J34">
-        <f>(Project!J32)/1000000</f>
-        <v>10.379433000000001</v>
+        <f>Project!J54</f>
+        <v>10.38</v>
       </c>
       <c r="K34">
-        <f>(Project!K32)/1000000</f>
-        <v>11.279432999999999</v>
+        <f>Project!K54</f>
+        <v>11.28</v>
       </c>
       <c r="L34">
-        <f>(Project!L32)/1000000</f>
-        <v>4.3794329999999997</v>
+        <f>Project!L54</f>
+        <v>4.38</v>
       </c>
       <c r="M34">
-        <f>(Project!M32)/1000000</f>
-        <v>10.453233000000001</v>
+        <f>Project!M54</f>
+        <v>10.45</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35" t="str">
-        <f>Project!A35</f>
+        <f>Project!A55</f>
         <v>Actual-PS</v>
       </c>
       <c r="B35">
-        <f>(Project!B35)/1000000</f>
-        <v>1.002658</v>
+        <f>Project!B55</f>
+        <v>1</v>
       </c>
       <c r="C35">
-        <f>(Project!C35)/1000000</f>
-        <v>5.7100929999999996</v>
+        <f>Project!C55</f>
+        <v>5.71</v>
       </c>
       <c r="D35">
-        <f>(Project!D35)/1000000</f>
-        <v>8.5445049999999991</v>
+        <f>Project!D55</f>
+        <v>8.5399999999999991</v>
       </c>
       <c r="E35">
-        <f>(Project!E35)/1000000</f>
-        <v>4.8552479999999996</v>
+        <f>Project!E55</f>
+        <v>4.8600000000000003</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36" t="str">
-        <f>Project!A33</f>
+        <f>Project!A56</f>
         <v>Plan-PD</v>
       </c>
       <c r="B36">
-        <f>(Project!B33)/1000000</f>
+        <f>Project!B56</f>
         <v>0.93</v>
       </c>
       <c r="C36">
-        <f>(Project!C33)/1000000</f>
+        <f>Project!C56</f>
         <v>1.43</v>
       </c>
       <c r="D36">
-        <f>(Project!D33)/1000000</f>
+        <f>Project!D56</f>
         <v>5.73</v>
       </c>
       <c r="E36">
-        <f>(Project!E33)/1000000</f>
+        <f>Project!E56</f>
         <v>2</v>
       </c>
       <c r="F36">
-        <f>(Project!F33)/1000000</f>
+        <f>Project!F56</f>
         <v>3.2</v>
       </c>
       <c r="G36">
-        <f>(Project!G33)/1000000</f>
+        <f>Project!G56</f>
         <v>4.9400000000000004</v>
       </c>
       <c r="H36">
-        <f>(Project!H33)/1000000</f>
+        <f>Project!H56</f>
         <v>4.2</v>
       </c>
       <c r="I36">
-        <f>(Project!I33)/1000000</f>
+        <f>Project!I56</f>
         <v>4.4000000000000004</v>
       </c>
       <c r="J36">
-        <f>(Project!J33)/1000000</f>
+        <f>Project!J56</f>
         <v>7.71</v>
       </c>
       <c r="K36">
-        <f>(Project!K33)/1000000</f>
+        <f>Project!K56</f>
         <v>4.9000000000000004</v>
       </c>
       <c r="L36">
-        <f>(Project!L33)/1000000</f>
+        <f>Project!L56</f>
         <v>10.16</v>
       </c>
       <c r="M36">
-        <f>(Project!M33)/1000000</f>
+        <f>Project!M56</f>
         <v>9.4</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37" t="str">
-        <f>Project!A36</f>
+        <f>Project!A57</f>
         <v>Actual-PD</v>
       </c>
       <c r="B37">
-        <f>(Project!B36)/1000000</f>
-        <v>4.725E-2</v>
+        <f>Project!B57</f>
+        <v>0.05</v>
       </c>
       <c r="C37">
-        <f>(Project!C36)/1000000</f>
-        <v>0.44589600000000001</v>
+        <f>Project!C57</f>
+        <v>0.45</v>
       </c>
       <c r="D37">
-        <f>(Project!D36)/1000000</f>
-        <v>0.54986599999999997</v>
+        <f>Project!D57</f>
+        <v>0.55000000000000004</v>
       </c>
       <c r="E37">
-        <f>(Project!E36)/1000000</f>
-        <v>1.452777</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" s="80" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="40" spans="1:13" s="80" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="41" spans="1:13" s="80" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="42" spans="1:13" s="80" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="43" spans="1:13" s="80" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="44" spans="1:13" s="80" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="81"/>
-    </row>
-    <row r="45" spans="1:13" s="80" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B45" s="81"/>
-    </row>
-    <row r="46" spans="1:13" s="80" customFormat="1" x14ac:dyDescent="0.2"/>
+        <f>Project!E57</f>
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B44" s="80"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B45" s="80"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/workforceresult.xlsx
+++ b/workforceresult.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miiintra/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{872FD1FC-0569-B542-924A-E879454B919E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B51CF386-5A2B-274B-A089-E111F78B4B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16440" yWindow="7760" windowWidth="28360" windowHeight="12340" activeTab="13" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
+    <workbookView xWindow="4080" yWindow="4220" windowWidth="40720" windowHeight="15880" activeTab="13" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
   </bookViews>
   <sheets>
     <sheet name="ALL" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="144">
   <si>
     <t>Type</t>
   </si>
@@ -645,6 +645,24 @@
   <si>
     <t>Actual-PD</t>
   </si>
+  <si>
+    <t>CAP</t>
+  </si>
+  <si>
+    <t>SCG Home</t>
+  </si>
+  <si>
+    <t>1.1 PS</t>
+  </si>
+  <si>
+    <t>1.2 Product</t>
+  </si>
+  <si>
+    <t>2 R&amp;D</t>
+  </si>
+  <si>
+    <t>3 Policy</t>
+  </si>
 </sst>
 </file>
 
@@ -809,19 +827,17 @@
       <family val="2"/>
     </font>
     <font>
-      <u/>
       <sz val="12"/>
-      <color theme="10"/>
+      <color theme="6"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="6"/>
-      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="27">
@@ -1009,11 +1025,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1120,12 +1135,12 @@
     <xf numFmtId="0" fontId="21" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="22" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="22" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -11367,7 +11382,7 @@
   <sheetPr>
     <tabColor rgb="FF002060"/>
   </sheetPr>
-  <dimension ref="A1:V57"/>
+  <dimension ref="A1:V71"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.6640625" bestFit="1" customWidth="1"/>
@@ -11434,49 +11449,49 @@
         <v>123</v>
       </c>
       <c r="B2" s="8">
-        <v>2.46</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="C2" s="8">
-        <v>2.4649999999999999</v>
+        <v>1.2250000000000001</v>
       </c>
       <c r="D2" s="8">
-        <v>2.4649999999999999</v>
+        <v>1.2250000000000001</v>
       </c>
       <c r="E2" s="8">
-        <v>1.95</v>
+        <v>0.8</v>
       </c>
       <c r="F2" s="8">
-        <v>2.2999999999999998</v>
+        <v>0.8</v>
       </c>
       <c r="G2" s="8">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="H2" s="8">
-        <v>2.9</v>
+        <v>0.75</v>
       </c>
       <c r="I2" s="8">
-        <v>2.7749999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="J2" s="8">
-        <v>2.7749999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="K2" s="8">
-        <v>2.6124999999999998</v>
+        <v>0.58750000000000002</v>
       </c>
       <c r="L2" s="8">
-        <v>2.6124999999999998</v>
+        <v>0.58750000000000002</v>
       </c>
       <c r="M2" s="8">
-        <v>2.6124999999999998</v>
+        <v>0.58750000000000002</v>
       </c>
       <c r="N2" s="8">
-        <v>0.80249999999999999</v>
+        <v>0.1125</v>
       </c>
       <c r="O2" s="8">
-        <v>0.80249999999999999</v>
+        <v>0.1125</v>
       </c>
       <c r="P2" s="8">
-        <v>0.80249999999999999</v>
+        <v>0.1125</v>
       </c>
       <c r="Q2" s="8"/>
       <c r="R2" s="8"/>
@@ -11490,49 +11505,49 @@
         <v>124</v>
       </c>
       <c r="B3" s="8">
-        <v>3.37</v>
+        <v>3.27</v>
       </c>
       <c r="C3" s="8">
-        <v>2.77</v>
+        <v>2.52</v>
       </c>
       <c r="D3" s="8">
-        <v>2.59</v>
+        <v>2.34</v>
       </c>
       <c r="E3" s="8">
-        <v>2.08</v>
+        <v>1.83</v>
       </c>
       <c r="F3" s="8">
-        <v>2.13</v>
+        <v>1.88</v>
       </c>
       <c r="G3" s="8">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="H3" s="8">
-        <v>2</v>
+        <v>1.375</v>
       </c>
       <c r="I3" s="8">
-        <v>2</v>
+        <v>1.375</v>
       </c>
       <c r="J3" s="8">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="K3" s="8">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="L3" s="8">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="M3" s="8">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="N3" s="8">
-        <v>1.55</v>
+        <v>0.8</v>
       </c>
       <c r="O3" s="8">
-        <v>1.55</v>
+        <v>0.8</v>
       </c>
       <c r="P3" s="8">
-        <v>1.55</v>
+        <v>0.8</v>
       </c>
       <c r="Q3" s="8"/>
       <c r="R3" s="8"/>
@@ -11546,49 +11561,49 @@
         <v>125</v>
       </c>
       <c r="B4" s="8">
+        <v>2.0249999999999999</v>
+      </c>
+      <c r="C4" s="8">
+        <v>1.375</v>
+      </c>
+      <c r="D4" s="8">
         <v>1.75</v>
       </c>
-      <c r="C4" s="8">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="D4" s="8">
-        <v>1.2749999999999999</v>
-      </c>
       <c r="E4" s="8">
-        <v>0.95</v>
+        <v>1.7</v>
       </c>
       <c r="F4" s="8">
-        <v>0.8</v>
+        <v>1.675</v>
       </c>
       <c r="G4" s="8">
-        <v>0.6</v>
+        <v>1.4750000000000001</v>
       </c>
       <c r="H4" s="8">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="I4" s="8">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="J4" s="8">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="K4" s="8">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="L4" s="8">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="M4" s="8">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="N4" s="8">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="O4" s="8">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="P4" s="8">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="Q4" s="8"/>
       <c r="R4" s="8"/>
@@ -11611,40 +11626,40 @@
         <v>3.0649999999999999</v>
       </c>
       <c r="E5" s="8">
-        <v>2.7250000000000001</v>
+        <v>3.125</v>
       </c>
       <c r="F5" s="8">
-        <v>2.875</v>
+        <v>3.2749999999999999</v>
       </c>
       <c r="G5" s="8">
-        <v>3.46</v>
+        <v>3.86</v>
       </c>
       <c r="H5" s="8">
-        <v>2.6850000000000001</v>
+        <v>3.085</v>
       </c>
       <c r="I5" s="8">
-        <v>2.9849999999999999</v>
+        <v>3.3849999999999998</v>
       </c>
       <c r="J5" s="8">
-        <v>2.9849999999999999</v>
+        <v>3.3849999999999998</v>
       </c>
       <c r="K5" s="8">
-        <v>2.9224999999999999</v>
+        <v>3.3224999999999998</v>
       </c>
       <c r="L5" s="8">
-        <v>2.9224999999999999</v>
+        <v>3.3224999999999998</v>
       </c>
       <c r="M5" s="8">
-        <v>2.9224999999999999</v>
+        <v>3.3224999999999998</v>
       </c>
       <c r="N5" s="8">
-        <v>2.81</v>
+        <v>3.21</v>
       </c>
       <c r="O5" s="8">
-        <v>2.81</v>
+        <v>3.21</v>
       </c>
       <c r="P5" s="8">
-        <v>2.81</v>
+        <v>3.21</v>
       </c>
       <c r="Q5" s="8"/>
       <c r="R5" s="8"/>
@@ -11658,49 +11673,49 @@
         <v>127</v>
       </c>
       <c r="B6" s="8">
-        <v>3.25</v>
+        <v>7.4</v>
       </c>
       <c r="C6" s="8">
-        <v>3.625</v>
+        <v>8.1750000000000007</v>
       </c>
       <c r="D6" s="8">
-        <v>3.67</v>
+        <v>7.22</v>
       </c>
       <c r="E6" s="8">
-        <v>3.4824999999999999</v>
+        <v>6.5949999999999998</v>
       </c>
       <c r="F6" s="8">
-        <v>2.9824999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="G6" s="8">
-        <v>2.9874999999999998</v>
+        <v>5.375</v>
       </c>
       <c r="H6" s="8">
-        <v>2.3125</v>
+        <v>5.1312499999999996</v>
       </c>
       <c r="I6" s="8">
-        <v>2.2124999999999999</v>
+        <v>5.1062500000000002</v>
       </c>
       <c r="J6" s="8">
-        <v>3.1124999999999998</v>
+        <v>5.4562499999999998</v>
       </c>
       <c r="K6" s="8">
-        <v>3.1124999999999998</v>
+        <v>5.2562499999999996</v>
       </c>
       <c r="L6" s="8">
-        <v>3.1124999999999998</v>
+        <v>5.7062499999999998</v>
       </c>
       <c r="M6" s="8">
-        <v>3.1124999999999998</v>
+        <v>5.5062499999999996</v>
       </c>
       <c r="N6" s="8">
-        <v>3.05</v>
+        <v>3.9249999999999998</v>
       </c>
       <c r="O6" s="8">
-        <v>3.05</v>
+        <v>3.9249999999999998</v>
       </c>
       <c r="P6" s="8">
-        <v>3.05</v>
+        <v>3.9249999999999998</v>
       </c>
       <c r="Q6" s="8"/>
       <c r="R6" s="8"/>
@@ -11710,22 +11725,54 @@
       <c r="V6" s="56"/>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
+      <c r="A7" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="B7" s="8">
+        <v>6.4124999999999996</v>
+      </c>
+      <c r="C7" s="8">
+        <v>5.9124999999999996</v>
+      </c>
+      <c r="D7" s="8">
+        <v>6.6624999999999996</v>
+      </c>
+      <c r="E7" s="8">
+        <v>7.7</v>
+      </c>
+      <c r="F7" s="8">
+        <v>7.875</v>
+      </c>
+      <c r="G7" s="8">
+        <v>7.875</v>
+      </c>
+      <c r="H7" s="8">
+        <v>8.1374999999999993</v>
+      </c>
+      <c r="I7" s="8">
+        <v>8.1374999999999993</v>
+      </c>
+      <c r="J7" s="8">
+        <v>8.1374999999999993</v>
+      </c>
+      <c r="K7" s="8">
+        <v>8.1374999999999993</v>
+      </c>
+      <c r="L7" s="8">
+        <v>8.1374999999999993</v>
+      </c>
+      <c r="M7" s="8">
+        <v>8.1374999999999993</v>
+      </c>
+      <c r="N7" s="8">
+        <v>8.1374999999999993</v>
+      </c>
+      <c r="O7" s="8">
+        <v>8.0124999999999993</v>
+      </c>
+      <c r="P7" s="8">
+        <v>8.0124999999999993</v>
+      </c>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
       <c r="S7" s="56"/>
@@ -12500,543 +12547,901 @@
         <v>1452777</v>
       </c>
     </row>
-    <row r="40" spans="1:13" s="81" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="81" t="str">
+    <row r="40" spans="1:13" s="80" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B40" s="80" t="str">
         <f>B30</f>
         <v>JAN</v>
       </c>
-      <c r="C40" s="81" t="str">
+      <c r="C40" s="80" t="str">
         <f t="shared" ref="C40:M40" si="2">C30</f>
         <v>FEB</v>
       </c>
-      <c r="D40" s="81" t="str">
+      <c r="D40" s="80" t="str">
         <f t="shared" si="2"/>
         <v>MAR</v>
       </c>
-      <c r="E40" s="81" t="str">
+      <c r="E40" s="80" t="str">
         <f t="shared" si="2"/>
         <v>APR</v>
       </c>
-      <c r="F40" s="81" t="str">
+      <c r="F40" s="80" t="str">
         <f t="shared" si="2"/>
         <v>MAY</v>
       </c>
-      <c r="G40" s="81" t="str">
+      <c r="G40" s="80" t="str">
         <f t="shared" si="2"/>
         <v>JUN</v>
       </c>
-      <c r="H40" s="81" t="str">
+      <c r="H40" s="80" t="str">
         <f t="shared" si="2"/>
         <v>JUL</v>
       </c>
-      <c r="I40" s="81" t="str">
+      <c r="I40" s="80" t="str">
         <f t="shared" si="2"/>
         <v>AUG</v>
       </c>
-      <c r="J40" s="81" t="str">
+      <c r="J40" s="80" t="str">
         <f t="shared" si="2"/>
         <v>SEP</v>
       </c>
-      <c r="K40" s="81" t="str">
+      <c r="K40" s="80" t="str">
         <f t="shared" si="2"/>
         <v>OCT</v>
       </c>
-      <c r="L40" s="81" t="str">
+      <c r="L40" s="80" t="str">
         <f t="shared" si="2"/>
         <v>NOV</v>
       </c>
-      <c r="M40" s="81" t="str">
+      <c r="M40" s="80" t="str">
         <f t="shared" si="2"/>
         <v>DEC</v>
       </c>
     </row>
-    <row r="41" spans="1:13" s="81" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="81" t="str">
+    <row r="41" spans="1:13" s="80" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="80" t="str">
         <f>A31</f>
         <v>Plan</v>
       </c>
-      <c r="B41" s="82">
+      <c r="B41" s="81">
         <f>B31/1000000</f>
         <v>2.7174330000000002</v>
       </c>
-      <c r="C41" s="82">
+      <c r="C41" s="81">
         <f t="shared" ref="C41:M41" si="3">C31/1000000</f>
         <v>6.2094329999999998</v>
       </c>
-      <c r="D41" s="82">
+      <c r="D41" s="81">
         <f t="shared" si="3"/>
         <v>13.563433</v>
       </c>
-      <c r="E41" s="82">
+      <c r="E41" s="81">
         <f t="shared" si="3"/>
         <v>7.2334329999999998</v>
       </c>
-      <c r="F41" s="82">
+      <c r="F41" s="81">
         <f t="shared" si="3"/>
         <v>7.4064329999999998</v>
       </c>
-      <c r="G41" s="82">
+      <c r="G41" s="81">
         <f t="shared" si="3"/>
         <v>19.319433</v>
       </c>
-      <c r="H41" s="82">
+      <c r="H41" s="81">
         <f t="shared" si="3"/>
         <v>13.479433</v>
       </c>
-      <c r="I41" s="82">
+      <c r="I41" s="81">
         <f t="shared" si="3"/>
         <v>10.679433</v>
       </c>
-      <c r="J41" s="82">
+      <c r="J41" s="81">
         <f t="shared" si="3"/>
         <v>18.089433</v>
       </c>
-      <c r="K41" s="82">
+      <c r="K41" s="81">
         <f t="shared" si="3"/>
         <v>16.179433</v>
       </c>
-      <c r="L41" s="82">
+      <c r="L41" s="81">
         <f t="shared" si="3"/>
         <v>14.539433000000001</v>
       </c>
-      <c r="M41" s="82">
+      <c r="M41" s="81">
         <f t="shared" si="3"/>
         <v>19.853232999999999</v>
       </c>
     </row>
-    <row r="42" spans="1:13" s="81" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="81" t="str">
+    <row r="42" spans="1:13" s="80" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="80" t="str">
         <f>A34</f>
         <v>Actual</v>
       </c>
-      <c r="B42" s="82">
+      <c r="B42" s="81">
         <f>B34/1000000</f>
         <v>1.0499080000000001</v>
       </c>
-      <c r="C42" s="82">
+      <c r="C42" s="81">
         <f t="shared" ref="C42:E42" si="4">C34/1000000</f>
         <v>6.1559889999999999</v>
       </c>
-      <c r="D42" s="82">
+      <c r="D42" s="81">
         <f t="shared" si="4"/>
         <v>9.0943710000000006</v>
       </c>
-      <c r="E42" s="82">
+      <c r="E42" s="81">
         <f t="shared" si="4"/>
         <v>6.3080249999999998</v>
       </c>
-      <c r="F42" s="82"/>
-      <c r="G42" s="82"/>
-      <c r="H42" s="82"/>
-      <c r="I42" s="82"/>
-      <c r="J42" s="82"/>
-      <c r="K42" s="82"/>
-      <c r="L42" s="82"/>
-      <c r="M42" s="82"/>
-    </row>
-    <row r="43" spans="1:13" s="81" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="81" t="str">
+      <c r="F42" s="81"/>
+      <c r="G42" s="81"/>
+      <c r="H42" s="81"/>
+      <c r="I42" s="81"/>
+      <c r="J42" s="81"/>
+      <c r="K42" s="81"/>
+      <c r="L42" s="81"/>
+      <c r="M42" s="81"/>
+    </row>
+    <row r="43" spans="1:13" s="80" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="80" t="str">
         <f>A32</f>
         <v>Plan-PS</v>
       </c>
-      <c r="B43" s="82">
+      <c r="B43" s="81">
         <f>B32/1000000</f>
         <v>1.787433</v>
       </c>
-      <c r="C43" s="82">
+      <c r="C43" s="81">
         <f t="shared" ref="C43:M43" si="5">C32/1000000</f>
         <v>4.779433</v>
       </c>
-      <c r="D43" s="82">
+      <c r="D43" s="81">
         <f t="shared" si="5"/>
         <v>7.8334330000000003</v>
       </c>
-      <c r="E43" s="82">
+      <c r="E43" s="81">
         <f t="shared" si="5"/>
         <v>5.2334329999999998</v>
       </c>
-      <c r="F43" s="82">
+      <c r="F43" s="81">
         <f t="shared" si="5"/>
         <v>4.2064329999999996</v>
       </c>
-      <c r="G43" s="82">
+      <c r="G43" s="81">
         <f t="shared" si="5"/>
         <v>14.379433000000001</v>
       </c>
-      <c r="H43" s="82">
+      <c r="H43" s="81">
         <f t="shared" si="5"/>
         <v>9.2794329999999992</v>
       </c>
-      <c r="I43" s="82">
+      <c r="I43" s="81">
         <f t="shared" si="5"/>
         <v>6.279433</v>
       </c>
-      <c r="J43" s="82">
+      <c r="J43" s="81">
         <f t="shared" si="5"/>
         <v>10.379433000000001</v>
       </c>
-      <c r="K43" s="82">
+      <c r="K43" s="81">
         <f t="shared" si="5"/>
         <v>11.279432999999999</v>
       </c>
-      <c r="L43" s="82">
+      <c r="L43" s="81">
         <f t="shared" si="5"/>
         <v>4.3794329999999997</v>
       </c>
-      <c r="M43" s="82">
+      <c r="M43" s="81">
         <f t="shared" si="5"/>
         <v>10.453233000000001</v>
       </c>
     </row>
-    <row r="44" spans="1:13" s="81" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="81" t="str">
+    <row r="44" spans="1:13" s="80" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="80" t="str">
         <f>A35</f>
         <v>Actual-PS</v>
       </c>
-      <c r="B44" s="82">
+      <c r="B44" s="81">
         <f>B35/1000000</f>
         <v>1.002658</v>
       </c>
-      <c r="C44" s="82">
+      <c r="C44" s="81">
         <f t="shared" ref="C44:E44" si="6">C35/1000000</f>
         <v>5.7100929999999996</v>
       </c>
-      <c r="D44" s="82">
+      <c r="D44" s="81">
         <f t="shared" si="6"/>
         <v>8.5445049999999991</v>
       </c>
-      <c r="E44" s="82">
+      <c r="E44" s="81">
         <f t="shared" si="6"/>
         <v>4.8552479999999996</v>
       </c>
-      <c r="F44" s="82"/>
-      <c r="G44" s="82"/>
-      <c r="H44" s="82"/>
-      <c r="I44" s="82"/>
-      <c r="J44" s="82"/>
-      <c r="K44" s="82"/>
-      <c r="L44" s="82"/>
-      <c r="M44" s="82"/>
-    </row>
-    <row r="45" spans="1:13" s="81" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="81" t="str">
+      <c r="F44" s="81"/>
+      <c r="G44" s="81"/>
+      <c r="H44" s="81"/>
+      <c r="I44" s="81"/>
+      <c r="J44" s="81"/>
+      <c r="K44" s="81"/>
+      <c r="L44" s="81"/>
+      <c r="M44" s="81"/>
+    </row>
+    <row r="45" spans="1:13" s="80" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="80" t="str">
         <f>A33</f>
         <v>Plan-PD</v>
       </c>
-      <c r="B45" s="82">
+      <c r="B45" s="81">
         <f>B33/1000000</f>
         <v>0.93</v>
       </c>
-      <c r="C45" s="82">
+      <c r="C45" s="81">
         <f t="shared" ref="C45:M45" si="7">C33/1000000</f>
         <v>1.43</v>
       </c>
-      <c r="D45" s="82">
+      <c r="D45" s="81">
         <f t="shared" si="7"/>
         <v>5.73</v>
       </c>
-      <c r="E45" s="82">
+      <c r="E45" s="81">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="F45" s="82">
+      <c r="F45" s="81">
         <f t="shared" si="7"/>
         <v>3.2</v>
       </c>
-      <c r="G45" s="82">
+      <c r="G45" s="81">
         <f t="shared" si="7"/>
         <v>4.9400000000000004</v>
       </c>
-      <c r="H45" s="82">
+      <c r="H45" s="81">
         <f t="shared" si="7"/>
         <v>4.2</v>
       </c>
-      <c r="I45" s="82">
+      <c r="I45" s="81">
         <f t="shared" si="7"/>
         <v>4.4000000000000004</v>
       </c>
-      <c r="J45" s="82">
+      <c r="J45" s="81">
         <f t="shared" si="7"/>
         <v>7.71</v>
       </c>
-      <c r="K45" s="82">
+      <c r="K45" s="81">
         <f t="shared" si="7"/>
         <v>4.9000000000000004</v>
       </c>
-      <c r="L45" s="82">
+      <c r="L45" s="81">
         <f t="shared" si="7"/>
         <v>10.16</v>
       </c>
-      <c r="M45" s="82">
+      <c r="M45" s="81">
         <f t="shared" si="7"/>
         <v>9.4</v>
       </c>
     </row>
-    <row r="46" spans="1:13" s="81" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="81" t="str">
+    <row r="46" spans="1:13" s="80" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="80" t="str">
         <f>A36</f>
         <v>Actual-PD</v>
       </c>
-      <c r="B46" s="82">
+      <c r="B46" s="81">
         <f>B36/1000000</f>
         <v>4.725E-2</v>
       </c>
-      <c r="C46" s="82">
+      <c r="C46" s="81">
         <f t="shared" ref="C46:E46" si="8">C36/1000000</f>
         <v>0.44589600000000001</v>
       </c>
-      <c r="D46" s="82">
+      <c r="D46" s="81">
         <f t="shared" si="8"/>
         <v>0.54986599999999997</v>
       </c>
-      <c r="E46" s="82">
+      <c r="E46" s="81">
         <f t="shared" si="8"/>
         <v>1.452777</v>
       </c>
-      <c r="F46" s="82"/>
-      <c r="G46" s="82"/>
-      <c r="H46" s="82"/>
-      <c r="I46" s="82"/>
-      <c r="J46" s="82"/>
-      <c r="K46" s="82"/>
-      <c r="L46" s="82"/>
-      <c r="M46" s="82"/>
-    </row>
-    <row r="47" spans="1:13" s="81" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="48" spans="1:13" s="81" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="49" spans="1:13" s="81" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="50" spans="1:13" s="81" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="51" spans="1:13" s="81" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B51" s="81" t="str">
-        <f>B40</f>
+      <c r="F46" s="81"/>
+      <c r="G46" s="81"/>
+      <c r="H46" s="81"/>
+      <c r="I46" s="81"/>
+      <c r="J46" s="81"/>
+      <c r="K46" s="81"/>
+      <c r="L46" s="81"/>
+      <c r="M46" s="81"/>
+    </row>
+    <row r="47" spans="1:13" s="80" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="48" spans="1:13" s="80" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="49" spans="1:16" s="80" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="50" spans="1:16" s="80" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="51" spans="1:16" s="80" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B51" s="80" t="str">
+        <f t="shared" ref="B51:M51" si="9">B40</f>
         <v>JAN</v>
       </c>
-      <c r="C51" s="81" t="str">
-        <f>C40</f>
+      <c r="C51" s="80" t="str">
+        <f t="shared" si="9"/>
         <v>FEB</v>
       </c>
-      <c r="D51" s="81" t="str">
-        <f>D40</f>
+      <c r="D51" s="80" t="str">
+        <f t="shared" si="9"/>
         <v>MAR</v>
       </c>
-      <c r="E51" s="81" t="str">
-        <f>E40</f>
+      <c r="E51" s="80" t="str">
+        <f t="shared" si="9"/>
         <v>APR</v>
       </c>
-      <c r="F51" s="81" t="str">
-        <f>F40</f>
+      <c r="F51" s="80" t="str">
+        <f t="shared" si="9"/>
         <v>MAY</v>
       </c>
-      <c r="G51" s="81" t="str">
-        <f>G40</f>
+      <c r="G51" s="80" t="str">
+        <f t="shared" si="9"/>
         <v>JUN</v>
       </c>
-      <c r="H51" s="81" t="str">
-        <f>H40</f>
+      <c r="H51" s="80" t="str">
+        <f t="shared" si="9"/>
         <v>JUL</v>
       </c>
-      <c r="I51" s="81" t="str">
-        <f>I40</f>
+      <c r="I51" s="80" t="str">
+        <f t="shared" si="9"/>
         <v>AUG</v>
       </c>
-      <c r="J51" s="81" t="str">
-        <f>J40</f>
+      <c r="J51" s="80" t="str">
+        <f t="shared" si="9"/>
         <v>SEP</v>
       </c>
-      <c r="K51" s="81" t="str">
-        <f>K40</f>
+      <c r="K51" s="80" t="str">
+        <f t="shared" si="9"/>
         <v>OCT</v>
       </c>
-      <c r="L51" s="81" t="str">
-        <f>L40</f>
+      <c r="L51" s="80" t="str">
+        <f t="shared" si="9"/>
         <v>NOV</v>
       </c>
-      <c r="M51" s="81" t="str">
-        <f>M40</f>
+      <c r="M51" s="80" t="str">
+        <f t="shared" si="9"/>
         <v>DEC</v>
       </c>
     </row>
-    <row r="52" spans="1:13" s="81" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="81" t="str">
+    <row r="52" spans="1:16" s="80" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="80" t="str">
         <f>A41</f>
         <v>Plan</v>
       </c>
-      <c r="B52" s="81">
+      <c r="B52" s="80">
         <v>2.72</v>
       </c>
-      <c r="C52" s="81">
+      <c r="C52" s="80">
         <v>6.21</v>
       </c>
-      <c r="D52" s="81">
+      <c r="D52" s="80">
         <v>13.56</v>
       </c>
-      <c r="E52" s="81">
+      <c r="E52" s="80">
         <v>7.23</v>
       </c>
-      <c r="F52" s="81">
+      <c r="F52" s="80">
         <v>7.41</v>
       </c>
-      <c r="G52" s="81">
+      <c r="G52" s="80">
         <v>19.32</v>
       </c>
-      <c r="H52" s="81">
+      <c r="H52" s="80">
         <v>13.48</v>
       </c>
-      <c r="I52" s="81">
+      <c r="I52" s="80">
         <v>10.68</v>
       </c>
-      <c r="J52" s="81">
+      <c r="J52" s="80">
         <v>18.09</v>
       </c>
-      <c r="K52" s="81">
+      <c r="K52" s="80">
         <v>16.18</v>
       </c>
-      <c r="L52" s="81">
+      <c r="L52" s="80">
         <v>14.54</v>
       </c>
-      <c r="M52" s="81">
+      <c r="M52" s="80">
         <v>19.850000000000001</v>
       </c>
     </row>
-    <row r="53" spans="1:13" s="81" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="81" t="str">
-        <f t="shared" ref="A53:A57" si="9">A42</f>
+    <row r="53" spans="1:16" s="80" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="80" t="str">
+        <f t="shared" ref="A53:A57" si="10">A42</f>
         <v>Actual</v>
       </c>
-      <c r="B53" s="81">
+      <c r="B53" s="80">
         <v>1.05</v>
       </c>
-      <c r="C53" s="81">
+      <c r="C53" s="80">
         <v>6.16</v>
       </c>
-      <c r="D53" s="81">
+      <c r="D53" s="80">
         <v>9.09</v>
       </c>
-      <c r="E53" s="81">
+      <c r="E53" s="80">
         <v>6.31</v>
       </c>
     </row>
-    <row r="54" spans="1:13" s="81" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="81" t="str">
-        <f t="shared" si="9"/>
+    <row r="54" spans="1:16" s="80" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="80" t="str">
+        <f t="shared" si="10"/>
         <v>Plan-PS</v>
       </c>
-      <c r="B54" s="81">
+      <c r="B54" s="80">
         <v>1.79</v>
       </c>
-      <c r="C54" s="81">
+      <c r="C54" s="80">
         <v>4.78</v>
       </c>
-      <c r="D54" s="81">
+      <c r="D54" s="80">
         <v>7.83</v>
       </c>
-      <c r="E54" s="81">
+      <c r="E54" s="80">
         <v>5.23</v>
       </c>
-      <c r="F54" s="81">
+      <c r="F54" s="80">
         <v>4.21</v>
       </c>
-      <c r="G54" s="81">
+      <c r="G54" s="80">
         <v>14.38</v>
       </c>
-      <c r="H54" s="81">
+      <c r="H54" s="80">
         <v>9.2799999999999994</v>
       </c>
-      <c r="I54" s="81">
+      <c r="I54" s="80">
         <v>6.28</v>
       </c>
-      <c r="J54" s="81">
+      <c r="J54" s="80">
         <v>10.38</v>
       </c>
-      <c r="K54" s="81">
+      <c r="K54" s="80">
         <v>11.28</v>
       </c>
-      <c r="L54" s="81">
+      <c r="L54" s="80">
         <v>4.38</v>
       </c>
-      <c r="M54" s="81">
+      <c r="M54" s="80">
         <v>10.45</v>
       </c>
     </row>
-    <row r="55" spans="1:13" s="81" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="81" t="str">
-        <f t="shared" si="9"/>
+    <row r="55" spans="1:16" s="80" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="80" t="str">
+        <f t="shared" si="10"/>
         <v>Actual-PS</v>
       </c>
-      <c r="B55" s="81">
+      <c r="B55" s="80">
         <v>1</v>
       </c>
-      <c r="C55" s="81">
+      <c r="C55" s="80">
         <v>5.71</v>
       </c>
-      <c r="D55" s="81">
+      <c r="D55" s="80">
         <v>8.5399999999999991</v>
       </c>
-      <c r="E55" s="81">
+      <c r="E55" s="80">
         <v>4.8600000000000003</v>
       </c>
     </row>
-    <row r="56" spans="1:13" s="81" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="81" t="str">
-        <f t="shared" si="9"/>
+    <row r="56" spans="1:16" s="80" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="80" t="str">
+        <f t="shared" si="10"/>
         <v>Plan-PD</v>
       </c>
-      <c r="B56" s="81">
+      <c r="B56" s="80">
         <v>0.93</v>
       </c>
-      <c r="C56" s="81">
+      <c r="C56" s="80">
         <v>1.43</v>
       </c>
-      <c r="D56" s="81">
+      <c r="D56" s="80">
         <v>5.73</v>
       </c>
-      <c r="E56" s="81">
-        <v>2</v>
-      </c>
-      <c r="F56" s="81">
+      <c r="E56" s="80">
+        <v>2</v>
+      </c>
+      <c r="F56" s="80">
         <v>3.2</v>
       </c>
-      <c r="G56" s="81">
+      <c r="G56" s="80">
         <v>4.9400000000000004</v>
       </c>
-      <c r="H56" s="81">
+      <c r="H56" s="80">
         <v>4.2</v>
       </c>
-      <c r="I56" s="81">
+      <c r="I56" s="80">
         <v>4.4000000000000004</v>
       </c>
-      <c r="J56" s="81">
+      <c r="J56" s="80">
         <v>7.71</v>
       </c>
-      <c r="K56" s="81">
+      <c r="K56" s="80">
         <v>4.9000000000000004</v>
       </c>
-      <c r="L56" s="81">
+      <c r="L56" s="80">
         <v>10.16</v>
       </c>
-      <c r="M56" s="81">
+      <c r="M56" s="80">
         <v>9.4</v>
       </c>
     </row>
-    <row r="57" spans="1:13" s="81" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="81" t="str">
-        <f t="shared" si="9"/>
+    <row r="57" spans="1:16" s="80" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="80" t="str">
+        <f t="shared" si="10"/>
         <v>Actual-PD</v>
       </c>
-      <c r="B57" s="81">
+      <c r="B57" s="80">
         <v>0.05</v>
       </c>
-      <c r="C57" s="81">
+      <c r="C57" s="80">
         <v>0.45</v>
       </c>
-      <c r="D57" s="81">
+      <c r="D57" s="80">
         <v>0.55000000000000004</v>
       </c>
-      <c r="E57" s="81">
+      <c r="E57" s="80">
         <v>1.45</v>
       </c>
-      <c r="F57" s="82"/>
-      <c r="L57" s="82"/>
+      <c r="F57" s="81"/>
+      <c r="L57" s="81"/>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A61" s="53" t="s">
+        <v>122</v>
+      </c>
+      <c r="B61" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="C61" s="55" t="s">
+        <v>2</v>
+      </c>
+      <c r="D61" s="55" t="s">
+        <v>3</v>
+      </c>
+      <c r="E61" s="55" t="s">
+        <v>4</v>
+      </c>
+      <c r="F61" s="55" t="s">
+        <v>5</v>
+      </c>
+      <c r="G61" s="55" t="s">
+        <v>6</v>
+      </c>
+      <c r="H61" s="55" t="s">
+        <v>7</v>
+      </c>
+      <c r="I61" s="55" t="s">
+        <v>8</v>
+      </c>
+      <c r="J61" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="K61" s="55" t="s">
+        <v>10</v>
+      </c>
+      <c r="L61" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="M61" s="55" t="s">
+        <v>12</v>
+      </c>
+      <c r="N61" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="O61" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="P61" s="55" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A62" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="B62" s="8">
+        <v>64.239999999999995</v>
+      </c>
+      <c r="C62" s="8">
+        <v>70.52</v>
+      </c>
+      <c r="D62" s="8">
+        <v>74.53</v>
+      </c>
+      <c r="E62" s="8">
+        <v>73.02</v>
+      </c>
+      <c r="F62" s="8">
+        <v>78.36</v>
+      </c>
+      <c r="G62" s="8">
+        <v>74.459999999999994</v>
+      </c>
+      <c r="H62" s="8">
+        <v>77.349999999999994</v>
+      </c>
+      <c r="I62" s="8">
+        <v>74.92</v>
+      </c>
+      <c r="J62" s="8">
+        <v>73.989999999999995</v>
+      </c>
+      <c r="K62" s="8">
+        <v>68.13</v>
+      </c>
+      <c r="L62" s="8">
+        <v>66.87</v>
+      </c>
+      <c r="M62" s="8">
+        <v>66.739999999999995</v>
+      </c>
+      <c r="N62" s="8">
+        <v>48.29</v>
+      </c>
+      <c r="O62" s="8">
+        <v>48.11</v>
+      </c>
+      <c r="P62" s="8">
+        <v>48.11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A63" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="B63" s="8">
+        <v>27.83</v>
+      </c>
+      <c r="C63" s="8">
+        <v>26.6</v>
+      </c>
+      <c r="D63" s="8">
+        <v>26.34</v>
+      </c>
+      <c r="E63" s="8">
+        <v>25.01</v>
+      </c>
+      <c r="F63" s="8">
+        <v>23.52</v>
+      </c>
+      <c r="G63" s="8">
+        <v>24.04</v>
+      </c>
+      <c r="H63" s="8">
+        <v>21.89</v>
+      </c>
+      <c r="I63" s="8">
+        <v>22.11</v>
+      </c>
+      <c r="J63" s="8">
+        <v>22.34</v>
+      </c>
+      <c r="K63" s="8">
+        <v>21.37</v>
+      </c>
+      <c r="L63" s="8">
+        <v>21.77</v>
+      </c>
+      <c r="M63" s="8">
+        <v>21.37</v>
+      </c>
+      <c r="N63" s="8">
+        <v>18.559999999999999</v>
+      </c>
+      <c r="O63" s="8">
+        <v>18.43</v>
+      </c>
+      <c r="P63" s="8">
+        <v>18.43</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A64" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="B64" s="8">
+        <v>7.89</v>
+      </c>
+      <c r="C64" s="8">
+        <v>10.74</v>
+      </c>
+      <c r="D64" s="8">
+        <v>9.69</v>
+      </c>
+      <c r="E64" s="8">
+        <v>11.7</v>
+      </c>
+      <c r="F64" s="8">
+        <v>11.65</v>
+      </c>
+      <c r="G64" s="8">
+        <v>11.9</v>
+      </c>
+      <c r="H64" s="8">
+        <v>10.27</v>
+      </c>
+      <c r="I64" s="8">
+        <v>9.4700000000000006</v>
+      </c>
+      <c r="J64" s="8">
+        <v>9.1199999999999992</v>
+      </c>
+      <c r="K64" s="8">
+        <v>8.67</v>
+      </c>
+      <c r="L64" s="8">
+        <v>8.2200000000000006</v>
+      </c>
+      <c r="M64" s="8">
+        <v>7.92</v>
+      </c>
+      <c r="N64" s="8">
+        <v>4.66</v>
+      </c>
+      <c r="O64" s="8">
+        <v>4.66</v>
+      </c>
+      <c r="P64" s="8">
+        <v>4.66</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A65" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="B65" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="C65" s="8">
+        <v>0.71</v>
+      </c>
+      <c r="D65" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="E65" s="8">
+        <v>0.26</v>
+      </c>
+      <c r="F65" s="8">
+        <v>0.21</v>
+      </c>
+      <c r="G65" s="8">
+        <v>0.21</v>
+      </c>
+      <c r="H65" s="8">
+        <v>0.31</v>
+      </c>
+      <c r="I65" s="8">
+        <v>0.32</v>
+      </c>
+      <c r="J65" s="8">
+        <v>0.32</v>
+      </c>
+      <c r="K65" s="8">
+        <v>0.32</v>
+      </c>
+      <c r="L65" s="8">
+        <v>0.32</v>
+      </c>
+      <c r="M65" s="8">
+        <v>0.32</v>
+      </c>
+      <c r="N65" s="8">
+        <v>0.11</v>
+      </c>
+      <c r="O65" s="8">
+        <v>0.11</v>
+      </c>
+      <c r="P65" s="8">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A66" s="8"/>
+      <c r="B66" s="8"/>
+      <c r="C66" s="8"/>
+      <c r="D66" s="82"/>
+      <c r="E66" s="82"/>
+      <c r="F66" s="82"/>
+      <c r="G66" s="82"/>
+      <c r="H66" s="82"/>
+      <c r="I66" s="82"/>
+      <c r="J66" s="82"/>
+      <c r="K66" s="82"/>
+      <c r="L66" s="82"/>
+      <c r="M66" s="82"/>
+      <c r="N66" s="82"/>
+      <c r="O66" s="82"/>
+      <c r="P66" s="8"/>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A67" s="8"/>
+      <c r="B67" s="8"/>
+      <c r="C67" s="8"/>
+      <c r="D67" s="8"/>
+      <c r="E67" s="82"/>
+      <c r="F67" s="82"/>
+      <c r="G67" s="82"/>
+      <c r="H67" s="82"/>
+      <c r="I67" s="82"/>
+      <c r="J67" s="82"/>
+      <c r="K67" s="82"/>
+      <c r="L67" s="82"/>
+      <c r="M67" s="82"/>
+      <c r="N67" s="82"/>
+      <c r="O67" s="82"/>
+      <c r="P67" s="8"/>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A68" s="8"/>
+      <c r="B68" s="8"/>
+      <c r="C68" s="8"/>
+      <c r="D68" s="82"/>
+      <c r="E68" s="82"/>
+      <c r="F68" s="82"/>
+      <c r="G68" s="82"/>
+      <c r="H68" s="82"/>
+      <c r="I68" s="82"/>
+      <c r="J68" s="82"/>
+      <c r="K68" s="82"/>
+      <c r="L68" s="82"/>
+      <c r="M68" s="82"/>
+      <c r="N68" s="82"/>
+      <c r="O68" s="82"/>
+      <c r="P68" s="8"/>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A69" s="8"/>
+      <c r="B69" s="8"/>
+      <c r="C69" s="8"/>
+      <c r="D69" s="8"/>
+      <c r="E69" s="8"/>
+      <c r="F69" s="8"/>
+      <c r="G69" s="8"/>
+      <c r="H69" s="8"/>
+      <c r="I69" s="8"/>
+      <c r="J69" s="8"/>
+      <c r="K69" s="8"/>
+      <c r="L69" s="8"/>
+      <c r="M69" s="8"/>
+      <c r="N69" s="8"/>
+      <c r="O69" s="8"/>
+      <c r="P69" s="8"/>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A70" s="8"/>
+      <c r="B70" s="8"/>
+      <c r="C70" s="8"/>
+      <c r="D70" s="8"/>
+      <c r="E70" s="8"/>
+      <c r="F70" s="8"/>
+      <c r="G70" s="8"/>
+      <c r="H70" s="8"/>
+      <c r="I70" s="8"/>
+      <c r="J70" s="8"/>
+      <c r="K70" s="8"/>
+      <c r="L70" s="8"/>
+      <c r="M70" s="8"/>
+      <c r="N70" s="8"/>
+      <c r="O70" s="8"/>
+      <c r="P70" s="8"/>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A71" s="8"/>
+      <c r="B71" s="8"/>
+      <c r="C71" s="8"/>
+      <c r="D71" s="82"/>
+      <c r="E71" s="82"/>
+      <c r="F71" s="82"/>
+      <c r="G71" s="82"/>
+      <c r="H71" s="82"/>
+      <c r="I71" s="82"/>
+      <c r="J71" s="82"/>
+      <c r="K71" s="82"/>
+      <c r="L71" s="82"/>
+      <c r="M71" s="82"/>
+      <c r="N71" s="82"/>
+      <c r="O71" s="82"/>
+      <c r="P71" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13143,63 +13548,63 @@
       </c>
       <c r="B2">
         <f>IF(Project!B2&gt;0,Project!B2,"")</f>
-        <v>2.46</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="C2">
         <f>IF(Project!C2&gt;0,Project!C2,"")</f>
-        <v>2.4649999999999999</v>
+        <v>1.2250000000000001</v>
       </c>
       <c r="D2">
         <f>IF(Project!D2&gt;0,Project!D2,"")</f>
-        <v>2.4649999999999999</v>
+        <v>1.2250000000000001</v>
       </c>
       <c r="E2">
         <f>IF(Project!E2&gt;0,Project!E2,"")</f>
-        <v>1.95</v>
+        <v>0.8</v>
       </c>
       <c r="F2">
         <f>IF(Project!F2&gt;0,Project!F2,"")</f>
-        <v>2.2999999999999998</v>
+        <v>0.8</v>
       </c>
       <c r="G2">
         <f>IF(Project!G2&gt;0,Project!G2,"")</f>
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="H2">
         <f>IF(Project!H2&gt;0,Project!H2,"")</f>
-        <v>2.9</v>
+        <v>0.75</v>
       </c>
       <c r="I2">
         <f>IF(Project!I2&gt;0,Project!I2,"")</f>
-        <v>2.7749999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="J2">
         <f>IF(Project!J2&gt;0,Project!J2,"")</f>
-        <v>2.7749999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="K2">
         <f>IF(Project!K2&gt;0,Project!K2,"")</f>
-        <v>2.6124999999999998</v>
+        <v>0.58750000000000002</v>
       </c>
       <c r="L2">
         <f>IF(Project!L2&gt;0,Project!L2,"")</f>
-        <v>2.6124999999999998</v>
+        <v>0.58750000000000002</v>
       </c>
       <c r="M2">
         <f>IF(Project!M2&gt;0,Project!M2,"")</f>
-        <v>2.6124999999999998</v>
+        <v>0.58750000000000002</v>
       </c>
       <c r="N2">
         <f>IF(Project!N2&gt;0,Project!N2,"")</f>
-        <v>0.80249999999999999</v>
+        <v>0.1125</v>
       </c>
       <c r="O2">
         <f>IF(Project!O2&gt;0,Project!O2,"")</f>
-        <v>0.80249999999999999</v>
+        <v>0.1125</v>
       </c>
       <c r="P2">
         <f>IF(Project!P2&gt;0,Project!P2,"")</f>
-        <v>0.80249999999999999</v>
+        <v>0.1125</v>
       </c>
       <c r="Q2" t="str">
         <f>IF(Project!Q2&gt;0,Project!Q2,"")</f>
@@ -13225,63 +13630,63 @@
       </c>
       <c r="B3">
         <f>IF(Project!B3&gt;0,Project!B3,"")</f>
-        <v>3.37</v>
+        <v>3.27</v>
       </c>
       <c r="C3">
         <f>IF(Project!C3&gt;0,Project!C3,"")</f>
-        <v>2.77</v>
+        <v>2.52</v>
       </c>
       <c r="D3">
         <f>IF(Project!D3&gt;0,Project!D3,"")</f>
-        <v>2.59</v>
+        <v>2.34</v>
       </c>
       <c r="E3">
         <f>IF(Project!E3&gt;0,Project!E3,"")</f>
-        <v>2.08</v>
+        <v>1.83</v>
       </c>
       <c r="F3">
         <f>IF(Project!F3&gt;0,Project!F3,"")</f>
-        <v>2.13</v>
+        <v>1.88</v>
       </c>
       <c r="G3">
         <f>IF(Project!G3&gt;0,Project!G3,"")</f>
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="H3">
         <f>IF(Project!H3&gt;0,Project!H3,"")</f>
-        <v>2</v>
+        <v>1.375</v>
       </c>
       <c r="I3">
         <f>IF(Project!I3&gt;0,Project!I3,"")</f>
-        <v>2</v>
+        <v>1.375</v>
       </c>
       <c r="J3">
         <f>IF(Project!J3&gt;0,Project!J3,"")</f>
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="K3">
         <f>IF(Project!K3&gt;0,Project!K3,"")</f>
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="L3">
         <f>IF(Project!L3&gt;0,Project!L3,"")</f>
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="M3">
         <f>IF(Project!M3&gt;0,Project!M3,"")</f>
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="N3">
         <f>IF(Project!N3&gt;0,Project!N3,"")</f>
-        <v>1.55</v>
+        <v>0.8</v>
       </c>
       <c r="O3">
         <f>IF(Project!O3&gt;0,Project!O3,"")</f>
-        <v>1.55</v>
+        <v>0.8</v>
       </c>
       <c r="P3">
         <f>IF(Project!P3&gt;0,Project!P3,"")</f>
-        <v>1.55</v>
+        <v>0.8</v>
       </c>
       <c r="Q3" t="str">
         <f>IF(Project!Q3&gt;0,Project!Q3,"")</f>
@@ -13307,63 +13712,63 @@
       </c>
       <c r="B4">
         <f>IF(Project!B4&gt;0,Project!B4,"")</f>
-        <v>1.75</v>
+        <v>2.0249999999999999</v>
       </c>
       <c r="C4">
         <f>IF(Project!C4&gt;0,Project!C4,"")</f>
-        <v>1.1000000000000001</v>
+        <v>1.375</v>
       </c>
       <c r="D4">
         <f>IF(Project!D4&gt;0,Project!D4,"")</f>
-        <v>1.2749999999999999</v>
+        <v>1.75</v>
       </c>
       <c r="E4">
         <f>IF(Project!E4&gt;0,Project!E4,"")</f>
-        <v>0.95</v>
+        <v>1.7</v>
       </c>
       <c r="F4">
         <f>IF(Project!F4&gt;0,Project!F4,"")</f>
-        <v>0.8</v>
+        <v>1.675</v>
       </c>
       <c r="G4">
         <f>IF(Project!G4&gt;0,Project!G4,"")</f>
-        <v>0.6</v>
+        <v>1.4750000000000001</v>
       </c>
       <c r="H4">
         <f>IF(Project!H4&gt;0,Project!H4,"")</f>
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="I4">
         <f>IF(Project!I4&gt;0,Project!I4,"")</f>
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="J4">
         <f>IF(Project!J4&gt;0,Project!J4,"")</f>
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="K4">
         <f>IF(Project!K4&gt;0,Project!K4,"")</f>
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="L4">
         <f>IF(Project!L4&gt;0,Project!L4,"")</f>
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="M4">
         <f>IF(Project!M4&gt;0,Project!M4,"")</f>
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="N4">
         <f>IF(Project!N4&gt;0,Project!N4,"")</f>
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="O4">
         <f>IF(Project!O4&gt;0,Project!O4,"")</f>
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="P4">
         <f>IF(Project!P4&gt;0,Project!P4,"")</f>
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="Q4" t="str">
         <f>IF(Project!Q4&gt;0,Project!Q4,"")</f>
@@ -13401,51 +13806,51 @@
       </c>
       <c r="E5">
         <f>IF(Project!E5&gt;0,Project!E5,"")</f>
-        <v>2.7250000000000001</v>
+        <v>3.125</v>
       </c>
       <c r="F5">
         <f>IF(Project!F5&gt;0,Project!F5,"")</f>
-        <v>2.875</v>
+        <v>3.2749999999999999</v>
       </c>
       <c r="G5">
         <f>IF(Project!G5&gt;0,Project!G5,"")</f>
-        <v>3.46</v>
+        <v>3.86</v>
       </c>
       <c r="H5">
         <f>IF(Project!H5&gt;0,Project!H5,"")</f>
-        <v>2.6850000000000001</v>
+        <v>3.085</v>
       </c>
       <c r="I5">
         <f>IF(Project!I5&gt;0,Project!I5,"")</f>
-        <v>2.9849999999999999</v>
+        <v>3.3849999999999998</v>
       </c>
       <c r="J5">
         <f>IF(Project!J5&gt;0,Project!J5,"")</f>
-        <v>2.9849999999999999</v>
+        <v>3.3849999999999998</v>
       </c>
       <c r="K5">
         <f>IF(Project!K5&gt;0,Project!K5,"")</f>
-        <v>2.9224999999999999</v>
+        <v>3.3224999999999998</v>
       </c>
       <c r="L5">
         <f>IF(Project!L5&gt;0,Project!L5,"")</f>
-        <v>2.9224999999999999</v>
+        <v>3.3224999999999998</v>
       </c>
       <c r="M5">
         <f>IF(Project!M5&gt;0,Project!M5,"")</f>
-        <v>2.9224999999999999</v>
+        <v>3.3224999999999998</v>
       </c>
       <c r="N5">
         <f>IF(Project!N5&gt;0,Project!N5,"")</f>
-        <v>2.81</v>
+        <v>3.21</v>
       </c>
       <c r="O5">
         <f>IF(Project!O5&gt;0,Project!O5,"")</f>
-        <v>2.81</v>
+        <v>3.21</v>
       </c>
       <c r="P5">
         <f>IF(Project!P5&gt;0,Project!P5,"")</f>
-        <v>2.81</v>
+        <v>3.21</v>
       </c>
       <c r="Q5" t="str">
         <f>IF(Project!Q5&gt;0,Project!Q5,"")</f>
@@ -13471,63 +13876,63 @@
       </c>
       <c r="B6">
         <f>IF(Project!B6&gt;0,Project!B6,"")</f>
-        <v>3.25</v>
+        <v>7.4</v>
       </c>
       <c r="C6">
         <f>IF(Project!C6&gt;0,Project!C6,"")</f>
-        <v>3.625</v>
+        <v>8.1750000000000007</v>
       </c>
       <c r="D6">
         <f>IF(Project!D6&gt;0,Project!D6,"")</f>
-        <v>3.67</v>
+        <v>7.22</v>
       </c>
       <c r="E6">
         <f>IF(Project!E6&gt;0,Project!E6,"")</f>
-        <v>3.4824999999999999</v>
+        <v>6.5949999999999998</v>
       </c>
       <c r="F6">
         <f>IF(Project!F6&gt;0,Project!F6,"")</f>
-        <v>2.9824999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="G6">
         <f>IF(Project!G6&gt;0,Project!G6,"")</f>
-        <v>2.9874999999999998</v>
+        <v>5.375</v>
       </c>
       <c r="H6">
         <f>IF(Project!H6&gt;0,Project!H6,"")</f>
-        <v>2.3125</v>
+        <v>5.1312499999999996</v>
       </c>
       <c r="I6">
         <f>IF(Project!I6&gt;0,Project!I6,"")</f>
-        <v>2.2124999999999999</v>
+        <v>5.1062500000000002</v>
       </c>
       <c r="J6">
         <f>IF(Project!J6&gt;0,Project!J6,"")</f>
-        <v>3.1124999999999998</v>
+        <v>5.4562499999999998</v>
       </c>
       <c r="K6">
         <f>IF(Project!K6&gt;0,Project!K6,"")</f>
-        <v>3.1124999999999998</v>
+        <v>5.2562499999999996</v>
       </c>
       <c r="L6">
         <f>IF(Project!L6&gt;0,Project!L6,"")</f>
-        <v>3.1124999999999998</v>
+        <v>5.7062499999999998</v>
       </c>
       <c r="M6">
         <f>IF(Project!M6&gt;0,Project!M6,"")</f>
-        <v>3.1124999999999998</v>
+        <v>5.5062499999999996</v>
       </c>
       <c r="N6">
         <f>IF(Project!N6&gt;0,Project!N6,"")</f>
-        <v>3.05</v>
+        <v>3.9249999999999998</v>
       </c>
       <c r="O6">
         <f>IF(Project!O6&gt;0,Project!O6,"")</f>
-        <v>3.05</v>
+        <v>3.9249999999999998</v>
       </c>
       <c r="P6">
         <f>IF(Project!P6&gt;0,Project!P6,"")</f>
-        <v>3.05</v>
+        <v>3.9249999999999998</v>
       </c>
       <c r="Q6" t="str">
         <f>IF(Project!Q6&gt;0,Project!Q6,"")</f>
@@ -13549,67 +13954,67 @@
     <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" t="str">
         <f>IF(Project!A7&gt;0,Project!A7,"")</f>
-        <v/>
-      </c>
-      <c r="B7" t="str">
+        <v>CAP</v>
+      </c>
+      <c r="B7">
         <f>IF(Project!B7&gt;0,Project!B7,"")</f>
-        <v/>
-      </c>
-      <c r="C7" t="str">
+        <v>6.4124999999999996</v>
+      </c>
+      <c r="C7">
         <f>IF(Project!C7&gt;0,Project!C7,"")</f>
-        <v/>
-      </c>
-      <c r="D7" t="str">
+        <v>5.9124999999999996</v>
+      </c>
+      <c r="D7">
         <f>IF(Project!D7&gt;0,Project!D7,"")</f>
-        <v/>
-      </c>
-      <c r="E7" t="str">
+        <v>6.6624999999999996</v>
+      </c>
+      <c r="E7">
         <f>IF(Project!E7&gt;0,Project!E7,"")</f>
-        <v/>
-      </c>
-      <c r="F7" t="str">
+        <v>7.7</v>
+      </c>
+      <c r="F7">
         <f>IF(Project!F7&gt;0,Project!F7,"")</f>
-        <v/>
-      </c>
-      <c r="G7" t="str">
+        <v>7.875</v>
+      </c>
+      <c r="G7">
         <f>IF(Project!G7&gt;0,Project!G7,"")</f>
-        <v/>
-      </c>
-      <c r="H7" t="str">
+        <v>7.875</v>
+      </c>
+      <c r="H7">
         <f>IF(Project!H7&gt;0,Project!H7,"")</f>
-        <v/>
-      </c>
-      <c r="I7" t="str">
+        <v>8.1374999999999993</v>
+      </c>
+      <c r="I7">
         <f>IF(Project!I7&gt;0,Project!I7,"")</f>
-        <v/>
-      </c>
-      <c r="J7" t="str">
+        <v>8.1374999999999993</v>
+      </c>
+      <c r="J7">
         <f>IF(Project!J7&gt;0,Project!J7,"")</f>
-        <v/>
-      </c>
-      <c r="K7" t="str">
+        <v>8.1374999999999993</v>
+      </c>
+      <c r="K7">
         <f>IF(Project!K7&gt;0,Project!K7,"")</f>
-        <v/>
-      </c>
-      <c r="L7" t="str">
+        <v>8.1374999999999993</v>
+      </c>
+      <c r="L7">
         <f>IF(Project!L7&gt;0,Project!L7,"")</f>
-        <v/>
-      </c>
-      <c r="M7" t="str">
+        <v>8.1374999999999993</v>
+      </c>
+      <c r="M7">
         <f>IF(Project!M7&gt;0,Project!M7,"")</f>
-        <v/>
-      </c>
-      <c r="N7" t="str">
+        <v>8.1374999999999993</v>
+      </c>
+      <c r="N7">
         <f>IF(Project!N7&gt;0,Project!N7,"")</f>
-        <v/>
-      </c>
-      <c r="O7" t="str">
+        <v>8.1374999999999993</v>
+      </c>
+      <c r="O7">
         <f>IF(Project!O7&gt;0,Project!O7,"")</f>
-        <v/>
-      </c>
-      <c r="P7" t="str">
+        <v>8.0124999999999993</v>
+      </c>
+      <c r="P7">
         <f>IF(Project!P7&gt;0,Project!P7,"")</f>
-        <v/>
+        <v>8.0124999999999993</v>
       </c>
       <c r="Q7" t="str">
         <f>IF(Project!Q7&gt;0,Project!Q7,"")</f>
@@ -14715,9 +15120,8 @@
         <f>IF(Project!A25&gt;0,Project!A25,"")</f>
         <v>PromptPlus</v>
       </c>
-      <c r="F21" s="64" t="str">
-        <f>IF(Project!A26&gt;0,Project!A26,"")</f>
-        <v>WeShape platform</v>
+      <c r="F21" s="64" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.2">
@@ -14741,10 +15145,7 @@
         <f>IF(Project!B25&gt;0,Project!B25,"")</f>
         <v/>
       </c>
-      <c r="F22" s="64">
-        <f>IF(Project!B26&gt;0,Project!B26,"")</f>
-        <v>0.8</v>
-      </c>
+      <c r="F22" s="64"/>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A23" s="58" t="str">
@@ -14845,10 +15246,7 @@
         <f>IF(Project!F25&gt;0,Project!F25,"")</f>
         <v/>
       </c>
-      <c r="F26" s="64">
-        <f>IF(Project!F26&gt;0,Project!F26,"")</f>
-        <v>34.655000000000001</v>
-      </c>
+      <c r="F26" s="64"/>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A27" s="58" t="str">
@@ -14871,9 +15269,8 @@
         <f>IF(Project!G25&gt;0,Project!G25,"")</f>
         <v>23.7</v>
       </c>
-      <c r="F27" s="64" t="str">
-        <f>IF(Project!G26&gt;0,Project!G26,"")</f>
-        <v/>
+      <c r="F27" s="64">
+        <v>28.8</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.2">
@@ -15009,7 +15406,7 @@
         <v>19.850000000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33" t="str">
         <f>Project!A53</f>
         <v>Actual</v>
@@ -15031,7 +15428,7 @@
         <v>6.31</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34" t="str">
         <f>Project!A54</f>
         <v>Plan-PS</v>
@@ -15085,7 +15482,7 @@
         <v>10.45</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35" t="str">
         <f>Project!A55</f>
         <v>Actual-PS</v>
@@ -15107,7 +15504,7 @@
         <v>4.8600000000000003</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36" t="str">
         <f>Project!A56</f>
         <v>Plan-PD</v>
@@ -15161,7 +15558,7 @@
         <v>9.4</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37" t="str">
         <f>Project!A57</f>
         <v>Actual-PD</v>
@@ -15183,11 +15580,302 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B44" s="80"/>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B45" s="80"/>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A40" s="83"/>
+      <c r="B40" s="58"/>
+      <c r="C40" s="58"/>
+      <c r="D40" s="58"/>
+      <c r="E40" s="58"/>
+      <c r="F40" s="58"/>
+      <c r="G40" s="58"/>
+      <c r="H40" s="58"/>
+      <c r="I40" s="58"/>
+      <c r="J40" s="58"/>
+      <c r="K40" s="58"/>
+      <c r="L40" s="58"/>
+      <c r="M40" s="58"/>
+      <c r="N40" s="58"/>
+      <c r="O40" s="58"/>
+      <c r="P40" s="58"/>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A41" s="8"/>
+      <c r="B41" s="17" t="str">
+        <f>Project!B61</f>
+        <v>JAN</v>
+      </c>
+      <c r="C41" s="17" t="str">
+        <f>Project!C61</f>
+        <v>FEB</v>
+      </c>
+      <c r="D41" s="17" t="str">
+        <f>Project!D61</f>
+        <v>MAR</v>
+      </c>
+      <c r="E41" s="17" t="str">
+        <f>Project!E61</f>
+        <v>APR</v>
+      </c>
+      <c r="F41" s="17" t="str">
+        <f>Project!F61</f>
+        <v>MAY</v>
+      </c>
+      <c r="G41" s="17" t="str">
+        <f>Project!G61</f>
+        <v>JUN</v>
+      </c>
+      <c r="H41" s="17" t="str">
+        <f>Project!H61</f>
+        <v>JUL</v>
+      </c>
+      <c r="I41" s="17" t="str">
+        <f>Project!I61</f>
+        <v>AUG</v>
+      </c>
+      <c r="J41" s="17" t="str">
+        <f>Project!J61</f>
+        <v>SEP</v>
+      </c>
+      <c r="K41" s="17" t="str">
+        <f>Project!K61</f>
+        <v>OCT</v>
+      </c>
+      <c r="L41" s="17" t="str">
+        <f>Project!L61</f>
+        <v>NOV</v>
+      </c>
+      <c r="M41" s="17" t="str">
+        <f>Project!M61</f>
+        <v>DEC</v>
+      </c>
+      <c r="N41" s="8"/>
+      <c r="O41" s="8"/>
+      <c r="P41" s="8"/>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A42" s="8" t="str">
+        <f>Project!A62</f>
+        <v>1.1 PS</v>
+      </c>
+      <c r="B42" s="8">
+        <f>Project!B62</f>
+        <v>64.239999999999995</v>
+      </c>
+      <c r="C42" s="8">
+        <f>Project!C62</f>
+        <v>70.52</v>
+      </c>
+      <c r="D42" s="8">
+        <f>Project!D62</f>
+        <v>74.53</v>
+      </c>
+      <c r="E42" s="8">
+        <f>Project!E62</f>
+        <v>73.02</v>
+      </c>
+      <c r="F42" s="8">
+        <f>Project!F62</f>
+        <v>78.36</v>
+      </c>
+      <c r="G42" s="8">
+        <f>Project!G62</f>
+        <v>74.459999999999994</v>
+      </c>
+      <c r="H42" s="8">
+        <f>Project!H62</f>
+        <v>77.349999999999994</v>
+      </c>
+      <c r="I42" s="8">
+        <f>Project!I62</f>
+        <v>74.92</v>
+      </c>
+      <c r="J42" s="8">
+        <f>Project!J62</f>
+        <v>73.989999999999995</v>
+      </c>
+      <c r="K42" s="8">
+        <f>Project!K62</f>
+        <v>68.13</v>
+      </c>
+      <c r="L42" s="8">
+        <f>Project!L62</f>
+        <v>66.87</v>
+      </c>
+      <c r="M42" s="8">
+        <f>Project!M62</f>
+        <v>66.739999999999995</v>
+      </c>
+      <c r="N42" s="8"/>
+      <c r="O42" s="8"/>
+      <c r="P42" s="8"/>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A43" s="8" t="str">
+        <f>Project!A63</f>
+        <v>1.2 Product</v>
+      </c>
+      <c r="B43" s="8">
+        <f>Project!B63</f>
+        <v>27.83</v>
+      </c>
+      <c r="C43" s="8">
+        <f>Project!C63</f>
+        <v>26.6</v>
+      </c>
+      <c r="D43" s="8">
+        <f>Project!D63</f>
+        <v>26.34</v>
+      </c>
+      <c r="E43" s="8">
+        <f>Project!E63</f>
+        <v>25.01</v>
+      </c>
+      <c r="F43" s="8">
+        <f>Project!F63</f>
+        <v>23.52</v>
+      </c>
+      <c r="G43" s="8">
+        <f>Project!G63</f>
+        <v>24.04</v>
+      </c>
+      <c r="H43" s="8">
+        <f>Project!H63</f>
+        <v>21.89</v>
+      </c>
+      <c r="I43" s="8">
+        <f>Project!I63</f>
+        <v>22.11</v>
+      </c>
+      <c r="J43" s="8">
+        <f>Project!J63</f>
+        <v>22.34</v>
+      </c>
+      <c r="K43" s="8">
+        <f>Project!K63</f>
+        <v>21.37</v>
+      </c>
+      <c r="L43" s="8">
+        <f>Project!L63</f>
+        <v>21.77</v>
+      </c>
+      <c r="M43" s="8">
+        <f>Project!M63</f>
+        <v>21.37</v>
+      </c>
+      <c r="N43" s="8"/>
+      <c r="O43" s="8"/>
+      <c r="P43" s="8"/>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A44" s="8" t="str">
+        <f>Project!A64</f>
+        <v>2 R&amp;D</v>
+      </c>
+      <c r="B44" s="8">
+        <f>Project!B64</f>
+        <v>7.89</v>
+      </c>
+      <c r="C44" s="8">
+        <f>Project!C64</f>
+        <v>10.74</v>
+      </c>
+      <c r="D44" s="8">
+        <f>Project!D64</f>
+        <v>9.69</v>
+      </c>
+      <c r="E44" s="8">
+        <f>Project!E64</f>
+        <v>11.7</v>
+      </c>
+      <c r="F44" s="8">
+        <f>Project!F64</f>
+        <v>11.65</v>
+      </c>
+      <c r="G44" s="8">
+        <f>Project!G64</f>
+        <v>11.9</v>
+      </c>
+      <c r="H44" s="8">
+        <f>Project!H64</f>
+        <v>10.27</v>
+      </c>
+      <c r="I44" s="8">
+        <f>Project!I64</f>
+        <v>9.4700000000000006</v>
+      </c>
+      <c r="J44" s="8">
+        <f>Project!J64</f>
+        <v>9.1199999999999992</v>
+      </c>
+      <c r="K44" s="8">
+        <f>Project!K64</f>
+        <v>8.67</v>
+      </c>
+      <c r="L44" s="8">
+        <f>Project!L64</f>
+        <v>8.2200000000000006</v>
+      </c>
+      <c r="M44" s="8">
+        <f>Project!M64</f>
+        <v>7.92</v>
+      </c>
+      <c r="N44" s="8"/>
+      <c r="O44" s="8"/>
+      <c r="P44" s="8"/>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A45" t="str">
+        <f>Project!A65</f>
+        <v>3 Policy</v>
+      </c>
+      <c r="B45">
+        <f>Project!B65</f>
+        <v>0.1</v>
+      </c>
+      <c r="C45">
+        <f>Project!C65</f>
+        <v>0.71</v>
+      </c>
+      <c r="D45">
+        <f>Project!D65</f>
+        <v>0.75</v>
+      </c>
+      <c r="E45">
+        <f>Project!E65</f>
+        <v>0.26</v>
+      </c>
+      <c r="F45">
+        <f>Project!F65</f>
+        <v>0.21</v>
+      </c>
+      <c r="G45">
+        <f>Project!G65</f>
+        <v>0.21</v>
+      </c>
+      <c r="H45">
+        <f>Project!H65</f>
+        <v>0.31</v>
+      </c>
+      <c r="I45">
+        <f>Project!I65</f>
+        <v>0.32</v>
+      </c>
+      <c r="J45">
+        <f>Project!J65</f>
+        <v>0.32</v>
+      </c>
+      <c r="K45">
+        <f>Project!K65</f>
+        <v>0.32</v>
+      </c>
+      <c r="L45">
+        <f>Project!L65</f>
+        <v>0.32</v>
+      </c>
+      <c r="M45">
+        <f>Project!M65</f>
+        <v>0.32</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/workforceresult.xlsx
+++ b/workforceresult.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miiintra/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B51CF386-5A2B-274B-A089-E111F78B4B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CCBFC89-6BD5-3743-B358-7586DA0B8797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4080" yWindow="4220" windowWidth="40720" windowHeight="15880" activeTab="13" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="145">
   <si>
     <t>Type</t>
   </si>
@@ -601,16 +601,7 @@
     <t>Group</t>
   </si>
   <si>
-    <t>GINII</t>
-  </si>
-  <si>
     <t>Industrial Solutions</t>
-  </si>
-  <si>
-    <t>RGUARD</t>
-  </si>
-  <si>
-    <t>SARA</t>
   </si>
   <si>
     <t>WeShape</t>
@@ -662,6 +653,18 @@
   </si>
   <si>
     <t>3 Policy</t>
+  </si>
+  <si>
+    <t>7 DO Tools</t>
+  </si>
+  <si>
+    <t>KM</t>
+  </si>
+  <si>
+    <t>R-Guard</t>
+  </si>
+  <si>
+    <t>SA-RA</t>
   </si>
 </sst>
 </file>
@@ -1028,7 +1031,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1138,7 +1141,6 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2357,7 +2359,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="69" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C22" s="70">
         <v>11</v>
@@ -2388,7 +2390,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="69" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C23" s="71">
         <v>117.04</v>
@@ -11446,7 +11448,7 @@
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="B2" s="8">
         <v>1.1000000000000001</v>
@@ -11502,7 +11504,7 @@
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B3" s="8">
         <v>3.27</v>
@@ -11558,7 +11560,7 @@
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="B4" s="8">
         <v>2.0249999999999999</v>
@@ -11614,7 +11616,7 @@
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="B5" s="8">
         <v>3.2650000000000001</v>
@@ -11670,7 +11672,7 @@
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B6" s="8">
         <v>7.4</v>
@@ -11726,7 +11728,7 @@
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B7" s="8">
         <v>6.4124999999999996</v>
@@ -12185,7 +12187,7 @@
         <v>102</v>
       </c>
       <c r="H21" s="53" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I21" s="54"/>
       <c r="K21" s="54"/>
@@ -12412,7 +12414,7 @@
     </row>
     <row r="32" spans="1:17" s="72" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A32" s="76" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B32" s="75">
         <v>1787433</v>
@@ -12453,7 +12455,7 @@
     </row>
     <row r="33" spans="1:13" s="72" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A33" s="76" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B33" s="75">
         <v>930000</v>
@@ -12494,7 +12496,7 @@
     </row>
     <row r="34" spans="1:13" s="73" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A34" s="78" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B34" s="74">
         <f>SUM(B35,B36)</f>
@@ -12515,7 +12517,7 @@
     </row>
     <row r="35" spans="1:13" s="72" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A35" s="77" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B35" s="75">
         <v>1002658</v>
@@ -12532,7 +12534,7 @@
     </row>
     <row r="36" spans="1:13" s="72" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A36" s="77" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B36" s="75">
         <v>47250</v>
@@ -13137,7 +13139,7 @@
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A62" s="8" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B62" s="8">
         <v>64.239999999999995</v>
@@ -13187,7 +13189,7 @@
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A63" s="8" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B63" s="8">
         <v>27.83</v>
@@ -13237,7 +13239,7 @@
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A64" s="8" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B64" s="8">
         <v>7.89</v>
@@ -13287,7 +13289,7 @@
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A65" s="8" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B65" s="8">
         <v>0.1</v>
@@ -13336,22 +13338,54 @@
       </c>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A66" s="8"/>
-      <c r="B66" s="8"/>
-      <c r="C66" s="8"/>
-      <c r="D66" s="82"/>
-      <c r="E66" s="82"/>
-      <c r="F66" s="82"/>
-      <c r="G66" s="82"/>
-      <c r="H66" s="82"/>
-      <c r="I66" s="82"/>
-      <c r="J66" s="82"/>
-      <c r="K66" s="82"/>
-      <c r="L66" s="82"/>
-      <c r="M66" s="82"/>
-      <c r="N66" s="82"/>
-      <c r="O66" s="82"/>
-      <c r="P66" s="8"/>
+      <c r="A66" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="B66" s="8">
+        <v>0</v>
+      </c>
+      <c r="C66" s="8">
+        <v>0.15</v>
+      </c>
+      <c r="D66" s="8">
+        <v>0.15</v>
+      </c>
+      <c r="E66" s="8">
+        <v>0.38</v>
+      </c>
+      <c r="F66" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="G66" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="H66" s="8">
+        <v>0.73</v>
+      </c>
+      <c r="I66" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="J66" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="K66" s="8">
+        <v>0.63</v>
+      </c>
+      <c r="L66" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M66" s="8">
+        <v>0.63</v>
+      </c>
+      <c r="N66" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="O66" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P66" s="8">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A67" s="8"/>
@@ -13453,7 +13487,7 @@
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
-  <dimension ref="A1:T45"/>
+  <dimension ref="A1:T46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.1640625" bestFit="1" customWidth="1"/>
@@ -13544,7 +13578,7 @@
     <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" t="str">
         <f>IF(Project!A2&gt;0,Project!A2,"")</f>
-        <v>GINII</v>
+        <v>KM</v>
       </c>
       <c r="B2">
         <f>IF(Project!B2&gt;0,Project!B2,"")</f>
@@ -13708,7 +13742,7 @@
     <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" t="str">
         <f>IF(Project!A4&gt;0,Project!A4,"")</f>
-        <v>RGUARD</v>
+        <v>R-Guard</v>
       </c>
       <c r="B4">
         <f>IF(Project!B4&gt;0,Project!B4,"")</f>
@@ -13790,7 +13824,7 @@
     <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" t="str">
         <f>IF(Project!A5&gt;0,Project!A5,"")</f>
-        <v>SARA</v>
+        <v>SA-RA</v>
       </c>
       <c r="B5">
         <f>IF(Project!B5&gt;0,Project!B5,"")</f>
@@ -15121,7 +15155,7 @@
         <v>PromptPlus</v>
       </c>
       <c r="F21" s="64" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.2">
@@ -15275,7 +15309,7 @@
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A28" s="58" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B28" s="61">
         <f>IF(Project!H22&gt;0,Project!H22,"")</f>
@@ -15581,7 +15615,7 @@
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A40" s="83"/>
+      <c r="A40" s="54"/>
       <c r="B40" s="58"/>
       <c r="C40" s="58"/>
       <c r="D40" s="58"/>
@@ -15648,9 +15682,18 @@
         <f>Project!M61</f>
         <v>DEC</v>
       </c>
-      <c r="N41" s="8"/>
-      <c r="O41" s="8"/>
-      <c r="P41" s="8"/>
+      <c r="N41" s="17" t="str">
+        <f>Project!N61</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O41" s="17" t="str">
+        <f>Project!O61</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P41" s="17" t="str">
+        <f>Project!P61</f>
+        <v>MAR'27</v>
+      </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A42" s="8" t="str">
@@ -15705,9 +15748,18 @@
         <f>Project!M62</f>
         <v>66.739999999999995</v>
       </c>
-      <c r="N42" s="8"/>
-      <c r="O42" s="8"/>
-      <c r="P42" s="8"/>
+      <c r="N42" s="8">
+        <f>Project!N62</f>
+        <v>48.29</v>
+      </c>
+      <c r="O42" s="8">
+        <f>Project!O62</f>
+        <v>48.11</v>
+      </c>
+      <c r="P42" s="8">
+        <f>Project!P62</f>
+        <v>48.11</v>
+      </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A43" s="8" t="str">
@@ -15762,9 +15814,18 @@
         <f>Project!M63</f>
         <v>21.37</v>
       </c>
-      <c r="N43" s="8"/>
-      <c r="O43" s="8"/>
-      <c r="P43" s="8"/>
+      <c r="N43" s="8">
+        <f>Project!N63</f>
+        <v>18.559999999999999</v>
+      </c>
+      <c r="O43" s="8">
+        <f>Project!O63</f>
+        <v>18.43</v>
+      </c>
+      <c r="P43" s="8">
+        <f>Project!P63</f>
+        <v>18.43</v>
+      </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A44" s="8" t="str">
@@ -15819,9 +15880,18 @@
         <f>Project!M64</f>
         <v>7.92</v>
       </c>
-      <c r="N44" s="8"/>
-      <c r="O44" s="8"/>
-      <c r="P44" s="8"/>
+      <c r="N44" s="8">
+        <f>Project!N64</f>
+        <v>4.66</v>
+      </c>
+      <c r="O44" s="8">
+        <f>Project!O64</f>
+        <v>4.66</v>
+      </c>
+      <c r="P44" s="8">
+        <f>Project!P64</f>
+        <v>4.66</v>
+      </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A45" t="str">
@@ -15875,6 +15945,84 @@
       <c r="M45">
         <f>Project!M65</f>
         <v>0.32</v>
+      </c>
+      <c r="N45">
+        <f>Project!N65</f>
+        <v>0.11</v>
+      </c>
+      <c r="O45">
+        <f>Project!O65</f>
+        <v>0.11</v>
+      </c>
+      <c r="P45">
+        <f>Project!P65</f>
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A46" t="str">
+        <f>Project!A66</f>
+        <v>7 DO Tools</v>
+      </c>
+      <c r="B46">
+        <f>Project!B66</f>
+        <v>0</v>
+      </c>
+      <c r="C46">
+        <f>Project!C66</f>
+        <v>0.15</v>
+      </c>
+      <c r="D46">
+        <f>Project!D66</f>
+        <v>0.15</v>
+      </c>
+      <c r="E46">
+        <f>Project!E66</f>
+        <v>0.38</v>
+      </c>
+      <c r="F46">
+        <f>Project!F66</f>
+        <v>0.5</v>
+      </c>
+      <c r="G46">
+        <f>Project!G66</f>
+        <v>0.6</v>
+      </c>
+      <c r="H46">
+        <f>Project!H66</f>
+        <v>0.73</v>
+      </c>
+      <c r="I46">
+        <f>Project!I66</f>
+        <v>0.5</v>
+      </c>
+      <c r="J46">
+        <f>Project!J66</f>
+        <v>0.5</v>
+      </c>
+      <c r="K46">
+        <f>Project!K66</f>
+        <v>0.63</v>
+      </c>
+      <c r="L46">
+        <f>Project!L66</f>
+        <v>0.5</v>
+      </c>
+      <c r="M46">
+        <f>Project!M66</f>
+        <v>0.63</v>
+      </c>
+      <c r="N46">
+        <f>Project!N66</f>
+        <v>0.5</v>
+      </c>
+      <c r="O46">
+        <f>Project!O66</f>
+        <v>0.5</v>
+      </c>
+      <c r="P46">
+        <f>Project!P66</f>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -17761,7 +17909,7 @@
     </row>
     <row r="164" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B164">
         <f>SUM(ALL!C22:C23)</f>
@@ -17782,7 +17930,7 @@
     </row>
     <row r="165" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B165">
         <v>127</v>

--- a/workforceresult.xlsx
+++ b/workforceresult.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miiintra/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CCBFC89-6BD5-3743-B358-7586DA0B8797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A7F6156-3B4F-F44D-AB08-43EDDE261955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4080" yWindow="4220" windowWidth="40720" windowHeight="15880" activeTab="13" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
   </bookViews>
@@ -1031,7 +1031,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1141,6 +1141,7 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1547,50 +1548,50 @@
       <c r="B2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2">
         <v>148</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2">
         <v>149</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2">
         <v>149</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F2">
         <v>151</v>
       </c>
-      <c r="G2" s="8">
+      <c r="G2">
+        <v>152</v>
+      </c>
+      <c r="H2">
+        <v>151</v>
+      </c>
+      <c r="I2">
         <v>150</v>
       </c>
-      <c r="H2" s="8">
+      <c r="J2">
         <v>150</v>
       </c>
-      <c r="I2" s="8">
-        <v>149</v>
-      </c>
-      <c r="J2" s="8">
-        <v>149</v>
-      </c>
-      <c r="K2" s="8">
-        <v>149</v>
-      </c>
-      <c r="L2" s="8">
-        <v>149</v>
-      </c>
-      <c r="M2" s="8">
-        <v>149</v>
-      </c>
-      <c r="N2" s="8">
-        <v>149</v>
-      </c>
-      <c r="O2" s="8">
-        <v>149</v>
-      </c>
-      <c r="P2" s="8">
-        <v>149</v>
-      </c>
-      <c r="Q2" s="8">
-        <v>149</v>
+      <c r="K2">
+        <v>150</v>
+      </c>
+      <c r="L2">
+        <v>150</v>
+      </c>
+      <c r="M2">
+        <v>150</v>
+      </c>
+      <c r="N2">
+        <v>150</v>
+      </c>
+      <c r="O2">
+        <v>150</v>
+      </c>
+      <c r="P2">
+        <v>150</v>
+      </c>
+      <c r="Q2">
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.2">
@@ -1600,50 +1601,50 @@
       <c r="B3" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="8">
-        <v>149</v>
-      </c>
-      <c r="D3" s="8">
-        <v>149</v>
-      </c>
-      <c r="E3" s="8">
-        <v>149</v>
-      </c>
-      <c r="F3" s="8">
-        <v>149</v>
-      </c>
-      <c r="G3" s="8">
-        <v>149</v>
-      </c>
-      <c r="H3" s="8">
-        <v>149</v>
-      </c>
-      <c r="I3" s="8">
-        <v>149</v>
-      </c>
-      <c r="J3" s="8">
-        <v>149</v>
-      </c>
-      <c r="K3" s="8">
-        <v>149</v>
-      </c>
-      <c r="L3" s="8">
-        <v>149</v>
-      </c>
-      <c r="M3" s="8">
-        <v>149</v>
-      </c>
-      <c r="N3" s="8">
-        <v>149</v>
-      </c>
-      <c r="O3" s="8">
-        <v>149</v>
-      </c>
-      <c r="P3" s="8">
-        <v>149</v>
-      </c>
-      <c r="Q3" s="8">
-        <v>149</v>
+      <c r="C3">
+        <v>150</v>
+      </c>
+      <c r="D3">
+        <v>150</v>
+      </c>
+      <c r="E3">
+        <v>150</v>
+      </c>
+      <c r="F3">
+        <v>150</v>
+      </c>
+      <c r="G3">
+        <v>150</v>
+      </c>
+      <c r="H3">
+        <v>150</v>
+      </c>
+      <c r="I3">
+        <v>150</v>
+      </c>
+      <c r="J3">
+        <v>150</v>
+      </c>
+      <c r="K3">
+        <v>150</v>
+      </c>
+      <c r="L3">
+        <v>150</v>
+      </c>
+      <c r="M3">
+        <v>150</v>
+      </c>
+      <c r="N3">
+        <v>150</v>
+      </c>
+      <c r="O3">
+        <v>150</v>
+      </c>
+      <c r="P3">
+        <v>150</v>
+      </c>
+      <c r="Q3">
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.2">
@@ -1653,120 +1654,105 @@
       <c r="B4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4">
         <v>131</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4">
         <v>139</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4">
         <v>142</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4">
         <v>143</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4">
         <v>147</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4">
         <v>144</v>
       </c>
-      <c r="I4" s="8">
+      <c r="I4">
         <v>143</v>
       </c>
-      <c r="J4" s="8">
+      <c r="J4">
         <v>140</v>
       </c>
-      <c r="K4" s="8">
+      <c r="K4">
         <v>139</v>
       </c>
-      <c r="L4" s="8">
+      <c r="L4">
         <v>132</v>
       </c>
-      <c r="M4" s="8">
+      <c r="M4">
         <v>130</v>
       </c>
-      <c r="N4" s="8">
+      <c r="N4">
         <v>130</v>
       </c>
-      <c r="O4" s="8">
+      <c r="O4">
         <v>105</v>
       </c>
-      <c r="P4" s="8">
+      <c r="P4">
         <v>104</v>
       </c>
-      <c r="Q4" s="8">
+      <c r="Q4">
         <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="17"/>
       <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8"/>
-      <c r="N5" s="8"/>
-      <c r="O5" s="8"/>
-      <c r="P5" s="8"/>
-      <c r="Q5" s="8"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" s="8"/>
       <c r="B6" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="83">
         <v>0.88260000000000005</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="83">
         <v>0.93620000000000003</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="83">
         <v>0.95589999999999997</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="83">
         <v>0.94789999999999996</v>
       </c>
-      <c r="G6" s="19">
-        <v>0.97919999999999996</v>
-      </c>
-      <c r="H6" s="19">
-        <v>0.95830000000000004</v>
-      </c>
-      <c r="I6" s="19">
-        <v>0.95909999999999995</v>
-      </c>
-      <c r="J6" s="19">
-        <v>0.93759999999999999</v>
-      </c>
-      <c r="K6" s="19">
-        <v>0.93179999999999996</v>
-      </c>
-      <c r="L6" s="19">
-        <v>0.88370000000000004</v>
-      </c>
-      <c r="M6" s="19">
-        <v>0.87409999999999999</v>
-      </c>
-      <c r="N6" s="19">
-        <v>0.86939999999999995</v>
-      </c>
-      <c r="O6" s="19">
-        <v>0.70230000000000004</v>
-      </c>
-      <c r="P6" s="19">
-        <v>0.70020000000000004</v>
-      </c>
-      <c r="Q6" s="19">
-        <v>0.70020000000000004</v>
+      <c r="G6" s="83">
+        <v>0.96630000000000005</v>
+      </c>
+      <c r="H6" s="83">
+        <v>0.95189999999999997</v>
+      </c>
+      <c r="I6" s="83">
+        <v>0.95269999999999999</v>
+      </c>
+      <c r="J6" s="83">
+        <v>0.93130000000000002</v>
+      </c>
+      <c r="K6" s="83">
+        <v>0.92559999999999998</v>
+      </c>
+      <c r="L6" s="83">
+        <v>0.87780000000000002</v>
+      </c>
+      <c r="M6" s="83">
+        <v>0.86829999999999996</v>
+      </c>
+      <c r="N6" s="83">
+        <v>0.86360000000000003</v>
+      </c>
+      <c r="O6" s="83">
+        <v>0.6976</v>
+      </c>
+      <c r="P6" s="83">
+        <v>0.6956</v>
+      </c>
+      <c r="Q6" s="83">
+        <v>0.6956</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
@@ -1774,70 +1760,55 @@
       <c r="B7" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="20">
+      <c r="C7">
         <v>17</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7">
         <v>10</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7">
         <v>7</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7">
         <v>8</v>
       </c>
-      <c r="G7" s="20">
-        <v>3</v>
-      </c>
-      <c r="H7" s="20">
-        <v>6</v>
-      </c>
-      <c r="I7" s="20">
-        <v>6</v>
-      </c>
-      <c r="J7" s="20">
-        <v>9</v>
-      </c>
-      <c r="K7" s="20">
+      <c r="G7">
+        <v>5</v>
+      </c>
+      <c r="H7">
+        <v>7</v>
+      </c>
+      <c r="I7">
+        <v>7</v>
+      </c>
+      <c r="J7">
         <v>10</v>
       </c>
-      <c r="L7" s="20">
-        <v>17</v>
-      </c>
-      <c r="M7" s="20">
-        <v>19</v>
-      </c>
-      <c r="N7" s="20">
-        <v>19</v>
-      </c>
-      <c r="O7" s="20">
-        <v>44</v>
-      </c>
-      <c r="P7" s="20">
+      <c r="K7">
+        <v>11</v>
+      </c>
+      <c r="L7">
+        <v>18</v>
+      </c>
+      <c r="M7">
+        <v>20</v>
+      </c>
+      <c r="N7">
+        <v>20</v>
+      </c>
+      <c r="O7">
         <v>45</v>
       </c>
-      <c r="Q7" s="20">
-        <v>45</v>
+      <c r="P7">
+        <v>46</v>
+      </c>
+      <c r="Q7">
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" s="17"/>
       <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="8"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" s="15" t="s">
@@ -1846,50 +1817,50 @@
       <c r="B9" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9">
         <v>121</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9">
         <v>120</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9">
         <v>118</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9">
         <v>118</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9">
+        <v>119</v>
+      </c>
+      <c r="H9">
+        <v>118</v>
+      </c>
+      <c r="I9">
         <v>117</v>
       </c>
-      <c r="H9" s="8">
+      <c r="J9">
         <v>117</v>
       </c>
-      <c r="I9" s="8">
-        <v>116</v>
-      </c>
-      <c r="J9" s="8">
-        <v>116</v>
-      </c>
-      <c r="K9" s="8">
-        <v>116</v>
-      </c>
-      <c r="L9" s="8">
-        <v>116</v>
-      </c>
-      <c r="M9" s="8">
-        <v>116</v>
-      </c>
-      <c r="N9" s="8">
-        <v>116</v>
-      </c>
-      <c r="O9" s="8">
-        <v>116</v>
-      </c>
-      <c r="P9" s="8">
-        <v>116</v>
-      </c>
-      <c r="Q9" s="8">
-        <v>116</v>
+      <c r="K9">
+        <v>117</v>
+      </c>
+      <c r="L9">
+        <v>117</v>
+      </c>
+      <c r="M9">
+        <v>117</v>
+      </c>
+      <c r="N9">
+        <v>117</v>
+      </c>
+      <c r="O9">
+        <v>117</v>
+      </c>
+      <c r="P9">
+        <v>117</v>
+      </c>
+      <c r="Q9">
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.2">
@@ -1899,50 +1870,50 @@
       <c r="B10" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10">
+        <v>118</v>
+      </c>
+      <c r="D10">
+        <v>118</v>
+      </c>
+      <c r="E10">
+        <v>118</v>
+      </c>
+      <c r="F10">
         <v>117</v>
       </c>
-      <c r="D10" s="8">
+      <c r="G10">
         <v>117</v>
       </c>
-      <c r="E10" s="8">
+      <c r="H10">
         <v>117</v>
       </c>
-      <c r="F10" s="8">
-        <v>116</v>
-      </c>
-      <c r="G10" s="8">
-        <v>116</v>
-      </c>
-      <c r="H10" s="8">
-        <v>116</v>
-      </c>
-      <c r="I10" s="8">
-        <v>116</v>
-      </c>
-      <c r="J10" s="8">
-        <v>116</v>
-      </c>
-      <c r="K10" s="8">
-        <v>116</v>
-      </c>
-      <c r="L10" s="8">
-        <v>116</v>
-      </c>
-      <c r="M10" s="8">
-        <v>116</v>
-      </c>
-      <c r="N10" s="8">
-        <v>116</v>
-      </c>
-      <c r="O10" s="8">
-        <v>116</v>
-      </c>
-      <c r="P10" s="8">
-        <v>116</v>
-      </c>
-      <c r="Q10" s="8">
-        <v>116</v>
+      <c r="I10">
+        <v>117</v>
+      </c>
+      <c r="J10">
+        <v>117</v>
+      </c>
+      <c r="K10">
+        <v>117</v>
+      </c>
+      <c r="L10">
+        <v>117</v>
+      </c>
+      <c r="M10">
+        <v>117</v>
+      </c>
+      <c r="N10">
+        <v>117</v>
+      </c>
+      <c r="O10">
+        <v>117</v>
+      </c>
+      <c r="P10">
+        <v>117</v>
+      </c>
+      <c r="Q10">
+        <v>117</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
@@ -1952,70 +1923,55 @@
       <c r="B11" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11">
         <v>105</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11">
         <v>111</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11">
         <v>111</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11">
         <v>112</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11">
         <v>113</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H11">
         <v>111</v>
       </c>
-      <c r="I11" s="8">
+      <c r="I11">
         <v>108</v>
       </c>
-      <c r="J11" s="8">
+      <c r="J11">
         <v>105</v>
       </c>
-      <c r="K11" s="8">
+      <c r="K11">
         <v>103</v>
       </c>
-      <c r="L11" s="8">
+      <c r="L11">
         <v>100</v>
       </c>
-      <c r="M11" s="8">
+      <c r="M11">
         <v>99</v>
       </c>
-      <c r="N11" s="8">
+      <c r="N11">
         <v>98</v>
       </c>
-      <c r="O11" s="8">
+      <c r="O11">
         <v>81</v>
       </c>
-      <c r="P11" s="8">
+      <c r="P11">
         <v>81</v>
       </c>
-      <c r="Q11" s="8">
+      <c r="Q11">
         <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" s="8"/>
       <c r="B12" s="17"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="8"/>
-      <c r="Q12" s="8"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" s="15" t="s">
@@ -2024,49 +1980,49 @@
       <c r="B13" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13">
         <v>21</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13">
         <v>21</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13">
         <v>21</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F13">
         <v>21</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13">
         <v>21</v>
       </c>
-      <c r="H13" s="8">
+      <c r="H13">
         <v>21</v>
       </c>
-      <c r="I13" s="8">
+      <c r="I13">
         <v>21</v>
       </c>
-      <c r="J13" s="8">
+      <c r="J13">
         <v>21</v>
       </c>
-      <c r="K13" s="8">
+      <c r="K13">
         <v>21</v>
       </c>
-      <c r="L13" s="8">
+      <c r="L13">
         <v>21</v>
       </c>
-      <c r="M13" s="8">
+      <c r="M13">
         <v>21</v>
       </c>
-      <c r="N13" s="8">
+      <c r="N13">
         <v>21</v>
       </c>
-      <c r="O13" s="8">
+      <c r="O13">
         <v>21</v>
       </c>
-      <c r="P13" s="8">
+      <c r="P13">
         <v>21</v>
       </c>
-      <c r="Q13" s="8">
+      <c r="Q13">
         <v>21</v>
       </c>
     </row>
@@ -2077,49 +2033,49 @@
       <c r="B14" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14">
         <v>21</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14">
         <v>21</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14">
         <v>21</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F14">
         <v>21</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14">
         <v>21</v>
       </c>
-      <c r="H14" s="8">
+      <c r="H14">
         <v>21</v>
       </c>
-      <c r="I14" s="8">
+      <c r="I14">
         <v>21</v>
       </c>
-      <c r="J14" s="8">
+      <c r="J14">
         <v>21</v>
       </c>
-      <c r="K14" s="8">
+      <c r="K14">
         <v>21</v>
       </c>
-      <c r="L14" s="8">
+      <c r="L14">
         <v>21</v>
       </c>
-      <c r="M14" s="8">
+      <c r="M14">
         <v>21</v>
       </c>
-      <c r="N14" s="8">
+      <c r="N14">
         <v>21</v>
       </c>
-      <c r="O14" s="8">
+      <c r="O14">
         <v>21</v>
       </c>
-      <c r="P14" s="8">
+      <c r="P14">
         <v>21</v>
       </c>
-      <c r="Q14" s="8">
+      <c r="Q14">
         <v>21</v>
       </c>
     </row>
@@ -2130,70 +2086,55 @@
       <c r="B15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15">
         <v>20</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15">
         <v>20</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15">
         <v>22</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F15">
         <v>21</v>
       </c>
-      <c r="G15" s="8">
+      <c r="G15">
         <v>21</v>
       </c>
-      <c r="H15" s="8">
+      <c r="H15">
         <v>20</v>
       </c>
-      <c r="I15" s="8">
+      <c r="I15">
         <v>20</v>
       </c>
-      <c r="J15" s="8">
+      <c r="J15">
         <v>20</v>
       </c>
-      <c r="K15" s="8">
+      <c r="K15">
         <v>20</v>
       </c>
-      <c r="L15" s="8">
+      <c r="L15">
         <v>19</v>
       </c>
-      <c r="M15" s="8">
+      <c r="M15">
         <v>19</v>
       </c>
-      <c r="N15" s="8">
+      <c r="N15">
         <v>19</v>
       </c>
-      <c r="O15" s="8">
+      <c r="O15">
         <v>17</v>
       </c>
-      <c r="P15" s="8">
+      <c r="P15">
         <v>17</v>
       </c>
-      <c r="Q15" s="8">
+      <c r="Q15">
         <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" s="8"/>
       <c r="B16" s="17"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
-      <c r="N16" s="8"/>
-      <c r="O16" s="8"/>
-      <c r="P16" s="8"/>
-      <c r="Q16" s="8"/>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" s="15" t="s">
@@ -2202,49 +2143,49 @@
       <c r="B17" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17">
         <v>6</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17">
         <v>8</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17">
         <v>10</v>
       </c>
-      <c r="F17" s="8">
+      <c r="F17">
         <v>12</v>
       </c>
-      <c r="G17" s="8">
+      <c r="G17">
         <v>12</v>
       </c>
-      <c r="H17" s="8">
+      <c r="H17">
         <v>12</v>
       </c>
-      <c r="I17" s="8">
+      <c r="I17">
         <v>12</v>
       </c>
-      <c r="J17" s="8">
+      <c r="J17">
         <v>12</v>
       </c>
-      <c r="K17" s="8">
+      <c r="K17">
         <v>12</v>
       </c>
-      <c r="L17" s="8">
+      <c r="L17">
         <v>12</v>
       </c>
-      <c r="M17" s="8">
+      <c r="M17">
         <v>12</v>
       </c>
-      <c r="N17" s="8">
+      <c r="N17">
         <v>12</v>
       </c>
-      <c r="O17" s="8">
+      <c r="O17">
         <v>12</v>
       </c>
-      <c r="P17" s="8">
+      <c r="P17">
         <v>12</v>
       </c>
-      <c r="Q17" s="8">
+      <c r="Q17">
         <v>12</v>
       </c>
     </row>
@@ -2255,49 +2196,49 @@
       <c r="B18" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18">
         <v>11</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18">
         <v>11</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E18">
         <v>11</v>
       </c>
-      <c r="F18" s="8">
+      <c r="F18">
         <v>11</v>
       </c>
-      <c r="G18" s="8">
+      <c r="G18">
         <v>11</v>
       </c>
-      <c r="H18" s="8">
+      <c r="H18">
         <v>11</v>
       </c>
-      <c r="I18" s="8">
+      <c r="I18">
         <v>11</v>
       </c>
-      <c r="J18" s="8">
+      <c r="J18">
         <v>11</v>
       </c>
-      <c r="K18" s="8">
+      <c r="K18">
         <v>11</v>
       </c>
-      <c r="L18" s="8">
+      <c r="L18">
         <v>11</v>
       </c>
-      <c r="M18" s="8">
+      <c r="M18">
         <v>11</v>
       </c>
-      <c r="N18" s="8">
+      <c r="N18">
         <v>11</v>
       </c>
-      <c r="O18" s="8">
+      <c r="O18">
         <v>11</v>
       </c>
-      <c r="P18" s="8">
+      <c r="P18">
         <v>11</v>
       </c>
-      <c r="Q18" s="8">
+      <c r="Q18">
         <v>11</v>
       </c>
     </row>
@@ -2308,49 +2249,49 @@
       <c r="B19" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19">
         <v>6</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D19">
         <v>8</v>
       </c>
-      <c r="E19" s="8">
+      <c r="E19">
         <v>10</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F19">
         <v>10</v>
       </c>
-      <c r="G19" s="14">
+      <c r="G19">
         <v>12</v>
       </c>
-      <c r="H19" s="14">
+      <c r="H19">
         <v>14</v>
       </c>
-      <c r="I19" s="14">
+      <c r="I19">
         <v>15</v>
       </c>
-      <c r="J19" s="14">
+      <c r="J19">
         <v>15</v>
       </c>
-      <c r="K19" s="14">
+      <c r="K19">
         <v>16</v>
       </c>
-      <c r="L19" s="14">
+      <c r="L19">
         <v>12</v>
       </c>
-      <c r="M19" s="14">
+      <c r="M19">
         <v>12</v>
       </c>
-      <c r="N19" s="14">
+      <c r="N19">
         <v>12</v>
       </c>
-      <c r="O19" s="8">
+      <c r="O19">
         <v>7</v>
       </c>
-      <c r="P19" s="8">
+      <c r="P19">
         <v>7</v>
       </c>
-      <c r="Q19" s="8">
+      <c r="Q19">
         <v>7</v>
       </c>
     </row>
@@ -2438,16 +2379,16 @@
         <v>149</v>
       </c>
       <c r="D32" s="21">
+        <v>151</v>
+      </c>
+      <c r="E32" s="21">
         <v>150</v>
       </c>
-      <c r="E32" s="21">
-        <v>149</v>
-      </c>
       <c r="F32" s="21">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G32" s="21">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H32" s="21"/>
     </row>
@@ -2459,19 +2400,19 @@
         <v>17</v>
       </c>
       <c r="C33" s="26">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D33" s="21">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E33" s="21">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F33" s="21">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G33" s="21">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H33" s="21"/>
     </row>
@@ -2506,16 +2447,16 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="D35" s="28">
-        <v>3.8199999999999998E-2</v>
+        <v>4.4600000000000001E-2</v>
       </c>
       <c r="E35" s="28">
-        <v>5.7200000000000001E-2</v>
+        <v>6.3500000000000001E-2</v>
       </c>
       <c r="F35" s="28">
-        <v>0.12429999999999999</v>
+        <v>0.13009999999999999</v>
       </c>
       <c r="G35" s="28">
-        <v>0.29909999999999998</v>
+        <v>0.30380000000000001</v>
       </c>
       <c r="H35" s="8"/>
     </row>
@@ -2528,16 +2469,16 @@
         <v>0.92500000000000004</v>
       </c>
       <c r="D36" s="19">
-        <v>0.96179999999999999</v>
+        <v>0.95540000000000003</v>
       </c>
       <c r="E36" s="19">
-        <v>0.94279999999999997</v>
+        <v>0.9365</v>
       </c>
       <c r="F36" s="19">
-        <v>0.87570000000000003</v>
+        <v>0.86990000000000001</v>
       </c>
       <c r="G36" s="19">
-        <v>0.70089999999999997</v>
+        <v>0.69620000000000004</v>
       </c>
       <c r="H36" s="20"/>
     </row>
@@ -2550,16 +2491,16 @@
         <v>11</v>
       </c>
       <c r="D37" s="20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E37" s="20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F37" s="20">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G37" s="20">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H37" s="20"/>
     </row>
@@ -2584,16 +2525,16 @@
         <v>120</v>
       </c>
       <c r="D39" s="21">
+        <v>118</v>
+      </c>
+      <c r="E39" s="21">
         <v>117</v>
       </c>
-      <c r="E39" s="21">
-        <v>116</v>
-      </c>
       <c r="F39" s="21">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G39" s="21">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H39" s="21"/>
     </row>
@@ -2605,19 +2546,19 @@
         <v>19</v>
       </c>
       <c r="C40" s="26">
+        <v>118</v>
+      </c>
+      <c r="D40" s="21">
         <v>117</v>
       </c>
-      <c r="D40" s="21">
-        <v>116</v>
-      </c>
       <c r="E40" s="21">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F40" s="21">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G40" s="21">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H40" s="21"/>
     </row>
@@ -2910,47 +2851,47 @@
       </c>
       <c r="F2">
         <f>IF(AIC!G2&gt;0,AIC!G2,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G2">
         <f>IF(AIC!H2&gt;0,AIC!H2,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H2">
         <f>IF(AIC!I2&gt;0,AIC!I2,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I2">
         <f>IF(AIC!J2&gt;0,AIC!J2,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J2">
         <f>IF(AIC!K2&gt;0,AIC!K2,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K2">
         <f>IF(AIC!L2&gt;0,AIC!L2,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L2">
         <f>IF(AIC!M2&gt;0,AIC!M2,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M2">
         <f>IF(AIC!N2&gt;0,AIC!N2,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N2">
         <f>IF(AIC!O2&gt;0,AIC!O2,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O2">
         <f>IF(AIC!P2&gt;0,AIC!P2,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P2">
         <f>IF(AIC!Q2&gt;0,AIC!Q2,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
@@ -2960,63 +2901,63 @@
       </c>
       <c r="B3">
         <f>IF(AIC!C3&gt;0,AIC!C3,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3">
         <f>IF(AIC!D3&gt;0,AIC!D3,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3">
         <f>IF(AIC!E3&gt;0,AIC!E3,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3">
         <f>IF(AIC!F3&gt;0,AIC!F3,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3">
         <f>IF(AIC!G3&gt;0,AIC!G3,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3">
         <f>IF(AIC!H3&gt;0,AIC!H3,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H3">
         <f>IF(AIC!I3&gt;0,AIC!I3,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I3">
         <f>IF(AIC!J3&gt;0,AIC!J3,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J3">
         <f>IF(AIC!K3&gt;0,AIC!K3,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K3">
         <f>IF(AIC!L3&gt;0,AIC!L3,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L3">
         <f>IF(AIC!M3&gt;0,AIC!M3,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M3">
         <f>IF(AIC!N3&gt;0,AIC!N3,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N3">
         <f>IF(AIC!O3&gt;0,AIC!O3,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O3">
         <f>IF(AIC!P3&gt;0,AIC!P3,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P3">
         <f>IF(AIC!Q3&gt;0,AIC!Q3,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
@@ -3368,47 +3309,47 @@
       </c>
       <c r="F12">
         <f>IF(AIC!G9&gt;0,AIC!G9,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G12">
         <f>IF(AIC!H9&gt;0,AIC!H9,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H12">
         <f>IF(AIC!I9&gt;0,AIC!I9,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I12">
         <f>IF(AIC!J9&gt;0,AIC!J9,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J12">
         <f>IF(AIC!K9&gt;0,AIC!K9,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K12">
         <f>IF(AIC!L9&gt;0,AIC!L9,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L12">
         <f>IF(AIC!M9&gt;0,AIC!M9,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M12">
         <f>IF(AIC!N9&gt;0,AIC!N9,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N12">
         <f>IF(AIC!O9&gt;0,AIC!O9,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O12">
         <f>IF(AIC!P9&gt;0,AIC!P9,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P12">
         <f>IF(AIC!Q9&gt;0,AIC!Q9,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
@@ -3418,63 +3359,63 @@
       </c>
       <c r="B13">
         <f>IF(AIC!C10&gt;0,AIC!C10,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13">
         <f>IF(AIC!D10&gt;0,AIC!D10,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D13">
         <f>IF(AIC!E10&gt;0,AIC!E10,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E13">
         <f>IF(AIC!F10&gt;0,AIC!F10,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F13">
         <f>IF(AIC!G10&gt;0,AIC!G10,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G13">
         <f>IF(AIC!H10&gt;0,AIC!H10,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H13">
         <f>IF(AIC!I10&gt;0,AIC!I10,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I13">
         <f>IF(AIC!J10&gt;0,AIC!J10,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J13">
         <f>IF(AIC!K10&gt;0,AIC!K10,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K13">
         <f>IF(AIC!L10&gt;0,AIC!L10,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L13">
         <f>IF(AIC!M10&gt;0,AIC!M10,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M13">
         <f>IF(AIC!N10&gt;0,AIC!N10,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N13">
         <f>IF(AIC!O10&gt;0,AIC!O10,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O13">
         <f>IF(AIC!P10&gt;0,AIC!P10,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P13">
         <f>IF(AIC!Q10&gt;0,AIC!Q10,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
@@ -4096,19 +4037,19 @@
       </c>
       <c r="C42">
         <f>IF(AIC!D32&gt;0,AIC!D32,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D42">
         <f>IF(AIC!E32&gt;0,AIC!E32,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E42">
         <f>IF(AIC!F32&gt;0,AIC!F32,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F42">
         <f>IF(AIC!G32&gt;0,AIC!G32,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.2">
@@ -4118,23 +4059,23 @@
       </c>
       <c r="B43">
         <f>IF(AIC!C33&gt;0,AIC!C33,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C43">
         <f>IF(AIC!D33&gt;0,AIC!D33,"")</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D43">
         <f>IF(AIC!E33&gt;0,AIC!E33,"")</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E43">
         <f>IF(AIC!F33&gt;0,AIC!F33,"")</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F43">
         <f>IF(AIC!G33&gt;0,AIC!G33,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.2">
@@ -5263,47 +5204,47 @@
       </c>
       <c r="F82">
         <f>AIC!G70</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G82">
         <f>AIC!H70</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H82">
         <f>AIC!I70</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I82">
         <f>AIC!J70</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J82">
         <f>AIC!K70</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K82">
         <f>AIC!L70</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L82">
         <f>AIC!M70</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M82">
         <f>AIC!N70</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N82">
         <f>AIC!O70</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O82">
         <f>AIC!P70</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P82">
         <f>AIC!Q70</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.2">
@@ -5394,47 +5335,47 @@
       </c>
       <c r="F84" s="67">
         <f t="shared" si="6"/>
-        <v>-0.10499999999999998</v>
+        <v>0.89500000000000002</v>
       </c>
       <c r="G84" s="67">
         <f t="shared" si="6"/>
-        <v>-0.125</v>
+        <v>0.875</v>
       </c>
       <c r="H84" s="67">
         <f t="shared" si="6"/>
-        <v>-0.125</v>
+        <v>0.875</v>
       </c>
       <c r="I84" s="67">
         <f t="shared" si="6"/>
-        <v>-0.125</v>
+        <v>0.875</v>
       </c>
       <c r="J84" s="67">
         <f t="shared" si="6"/>
-        <v>0.42499999999999982</v>
+        <v>1.4249999999999998</v>
       </c>
       <c r="K84" s="67">
         <f t="shared" si="6"/>
-        <v>0.125</v>
+        <v>1.125</v>
       </c>
       <c r="L84" s="67">
         <f t="shared" si="6"/>
-        <v>7.5000000000000178E-2</v>
+        <v>1.0750000000000002</v>
       </c>
       <c r="M84" s="67">
         <f t="shared" si="6"/>
-        <v>0.375</v>
+        <v>1.375</v>
       </c>
       <c r="N84" s="67">
         <f t="shared" si="6"/>
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="O84" s="67">
         <f t="shared" si="6"/>
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="P84" s="67">
         <f t="shared" si="6"/>
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="85" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
@@ -5470,19 +5411,19 @@
       </c>
       <c r="C86" s="59">
         <f>(AVERAGE(E83:G83)/AVERAGE(E82:G82))*100</f>
-        <v>98.3</v>
+        <v>81.916666666666671</v>
       </c>
       <c r="D86" s="59">
         <f>(AVERAGE(H83:J83)/AVERAGE(H82:J82))*100</f>
-        <v>98.055555555555557</v>
+        <v>73.541666666666657</v>
       </c>
       <c r="E86" s="59">
         <f>(AVERAGE(K83:M83)/AVERAGE(K82:M82))*100</f>
-        <v>93.611111111111128</v>
+        <v>70.208333333333343</v>
       </c>
       <c r="F86" s="59">
         <f>(AVERAGE(N83:P83)/AVERAGE(N82:P82))*100</f>
-        <v>13.333333333333336</v>
+        <v>10.000000000000002</v>
       </c>
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.2">
@@ -5877,47 +5818,47 @@
       </c>
       <c r="F152">
         <f>AIC!G6*100</f>
-        <v>91.97</v>
+        <v>87.59</v>
       </c>
       <c r="G152">
         <f>AIC!H6*100</f>
-        <v>89.82</v>
+        <v>85.54</v>
       </c>
       <c r="H152">
         <f>AIC!I6*100</f>
-        <v>83.28</v>
+        <v>79.11</v>
       </c>
       <c r="I152">
         <f>AIC!J6*100</f>
-        <v>78.8</v>
+        <v>74.86</v>
       </c>
       <c r="J152">
         <f>AIC!K6*100</f>
-        <v>75.64</v>
+        <v>71.86</v>
       </c>
       <c r="K152">
         <f>AIC!L6*100</f>
-        <v>71.5</v>
+        <v>67.930000000000007</v>
       </c>
       <c r="L152">
         <f>AIC!M6*100</f>
-        <v>71.760000000000005</v>
+        <v>68.179999999999993</v>
       </c>
       <c r="M152">
         <f>AIC!N6*100</f>
-        <v>70.179999999999993</v>
+        <v>66.679999999999993</v>
       </c>
       <c r="N152">
         <f>AIC!O6*100</f>
-        <v>44.13</v>
+        <v>41.93</v>
       </c>
       <c r="O152">
         <f>AIC!P6*100</f>
-        <v>44.13</v>
+        <v>41.93</v>
       </c>
       <c r="P152">
         <f>AIC!Q6*100</f>
-        <v>44.13</v>
+        <v>41.93</v>
       </c>
     </row>
     <row r="153" spans="1:16" x14ac:dyDescent="0.2">
@@ -5943,47 +5884,47 @@
       </c>
       <c r="F153">
         <f>AIC!G7</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G153">
         <f>AIC!H7</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H153">
         <f>AIC!I7</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I153">
         <f>AIC!J7</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J153">
         <f>AIC!K7</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K153">
         <f>AIC!L7</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L153">
         <f>AIC!M7</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M153">
         <f>AIC!N7</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N153">
         <f>AIC!O7</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O153">
         <f>AIC!P7</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P153">
         <f>AIC!Q7</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="155" spans="1:16" x14ac:dyDescent="0.2">
@@ -6019,19 +5960,19 @@
       </c>
       <c r="C156">
         <f>AIC!D36*100</f>
-        <v>90.03</v>
+        <v>87.17</v>
       </c>
       <c r="D156">
         <f>AIC!E36*100</f>
-        <v>79.239999999999995</v>
+        <v>75.28</v>
       </c>
       <c r="E156">
         <f>AIC!F36*100</f>
-        <v>71.150000000000006</v>
+        <v>67.589999999999989</v>
       </c>
       <c r="F156">
         <f>AIC!G36*100</f>
-        <v>44.13</v>
+        <v>41.93</v>
       </c>
     </row>
     <row r="157" spans="1:16" x14ac:dyDescent="0.2">
@@ -6045,19 +5986,19 @@
       </c>
       <c r="C157">
         <f>AIC!D37</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D157">
         <f>AIC!E37</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E157">
         <f>AIC!F37</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F157">
         <f>AIC!G37</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -16126,47 +16067,47 @@
       </c>
       <c r="F2">
         <f>IF(ALL!G2&gt;0,ALL!G2,"")</f>
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G2">
         <f>IF(ALL!H2&gt;0,ALL!H2,"")</f>
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H2">
         <f>IF(ALL!I2&gt;0,ALL!I2,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I2">
         <f>IF(ALL!J2&gt;0,ALL!J2,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J2">
         <f>IF(ALL!K2&gt;0,ALL!K2,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K2">
         <f>IF(ALL!L2&gt;0,ALL!L2,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L2">
         <f>IF(ALL!M2&gt;0,ALL!M2,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M2">
         <f>IF(ALL!N2&gt;0,ALL!N2,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N2">
         <f>IF(ALL!O2&gt;0,ALL!O2,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O2">
         <f>IF(ALL!P2&gt;0,ALL!P2,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P2">
         <f>IF(ALL!Q2&gt;0,ALL!Q2,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
@@ -16176,63 +16117,63 @@
       </c>
       <c r="B3">
         <f>IF(ALL!C3&gt;0,ALL!C3,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C3">
         <f>IF(ALL!D3&gt;0,ALL!D3,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D3">
         <f>IF(ALL!E3&gt;0,ALL!E3,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E3">
         <f>IF(ALL!F3&gt;0,ALL!F3,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F3">
         <f>IF(ALL!G3&gt;0,ALL!G3,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G3">
         <f>IF(ALL!H3&gt;0,ALL!H3,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H3">
         <f>IF(ALL!I3&gt;0,ALL!I3,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I3">
         <f>IF(ALL!J3&gt;0,ALL!J3,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J3">
         <f>IF(ALL!K3&gt;0,ALL!K3,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K3">
         <f>IF(ALL!L3&gt;0,ALL!L3,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L3">
         <f>IF(ALL!M3&gt;0,ALL!M3,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M3">
         <f>IF(ALL!N3&gt;0,ALL!N3,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N3">
         <f>IF(ALL!O3&gt;0,ALL!O3,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O3">
         <f>IF(ALL!P3&gt;0,ALL!P3,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P3">
         <f>IF(ALL!Q3&gt;0,ALL!Q3,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
@@ -16584,47 +16525,47 @@
       </c>
       <c r="F12">
         <f>IF(ALL!G9&gt;0,ALL!G9,"")</f>
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G12">
         <f>IF(ALL!H9&gt;0,ALL!H9,"")</f>
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H12">
         <f>IF(ALL!I9&gt;0,ALL!I9,"")</f>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I12">
         <f>IF(ALL!J9&gt;0,ALL!J9,"")</f>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J12">
         <f>IF(ALL!K9&gt;0,ALL!K9,"")</f>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K12">
         <f>IF(ALL!L9&gt;0,ALL!L9,"")</f>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L12">
         <f>IF(ALL!M9&gt;0,ALL!M9,"")</f>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M12">
         <f>IF(ALL!N9&gt;0,ALL!N9,"")</f>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N12">
         <f>IF(ALL!O9&gt;0,ALL!O9,"")</f>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O12">
         <f>IF(ALL!P9&gt;0,ALL!P9,"")</f>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P12">
         <f>IF(ALL!Q9&gt;0,ALL!Q9,"")</f>
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
@@ -16634,63 +16575,63 @@
       </c>
       <c r="B13">
         <f>IF(ALL!C10&gt;0,ALL!C10,"")</f>
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C13">
         <f>IF(ALL!D10&gt;0,ALL!D10,"")</f>
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D13">
         <f>IF(ALL!E10&gt;0,ALL!E10,"")</f>
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E13">
         <f>IF(ALL!F10&gt;0,ALL!F10,"")</f>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F13">
         <f>IF(ALL!G10&gt;0,ALL!G10,"")</f>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G13">
         <f>IF(ALL!H10&gt;0,ALL!H10,"")</f>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H13">
         <f>IF(ALL!I10&gt;0,ALL!I10,"")</f>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I13">
         <f>IF(ALL!J10&gt;0,ALL!J10,"")</f>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J13">
         <f>IF(ALL!K10&gt;0,ALL!K10,"")</f>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K13">
         <f>IF(ALL!L10&gt;0,ALL!L10,"")</f>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L13">
         <f>IF(ALL!M10&gt;0,ALL!M10,"")</f>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M13">
         <f>IF(ALL!N10&gt;0,ALL!N10,"")</f>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N13">
         <f>IF(ALL!O10&gt;0,ALL!O10,"")</f>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O13">
         <f>IF(ALL!P10&gt;0,ALL!P10,"")</f>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P13">
         <f>IF(ALL!Q10&gt;0,ALL!Q10,"")</f>
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
@@ -17312,19 +17253,19 @@
       </c>
       <c r="C42">
         <f>IF(ALL!D32&gt;0,ALL!D32,"")</f>
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D42">
         <f>IF(ALL!E32&gt;0,ALL!E32,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E42">
         <f>IF(ALL!F32&gt;0,ALL!F32,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F42">
         <f>IF(ALL!G32&gt;0,ALL!G32,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.2">
@@ -17334,23 +17275,23 @@
       </c>
       <c r="B43">
         <f>IF(ALL!C33&gt;0,ALL!C33,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C43">
         <f>IF(ALL!D33&gt;0,ALL!D33,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D43">
         <f>IF(ALL!E33&gt;0,ALL!E33,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E43">
         <f>IF(ALL!F33&gt;0,ALL!F33,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F43">
         <f>IF(ALL!G33&gt;0,ALL!G33,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.2">
@@ -17542,47 +17483,47 @@
       </c>
       <c r="F152">
         <f>ALL!G6*100</f>
-        <v>97.92</v>
+        <v>96.63000000000001</v>
       </c>
       <c r="G152">
         <f>ALL!H6*100</f>
-        <v>95.83</v>
+        <v>95.19</v>
       </c>
       <c r="H152">
         <f>ALL!I6*100</f>
-        <v>95.91</v>
+        <v>95.27</v>
       </c>
       <c r="I152">
         <f>ALL!J6*100</f>
-        <v>93.76</v>
+        <v>93.13</v>
       </c>
       <c r="J152">
         <f>ALL!K6*100</f>
-        <v>93.179999999999993</v>
+        <v>92.56</v>
       </c>
       <c r="K152">
         <f>ALL!L6*100</f>
-        <v>88.37</v>
+        <v>87.78</v>
       </c>
       <c r="L152">
         <f>ALL!M6*100</f>
-        <v>87.41</v>
+        <v>86.83</v>
       </c>
       <c r="M152">
         <f>ALL!N6*100</f>
-        <v>86.94</v>
+        <v>86.36</v>
       </c>
       <c r="N152">
         <f>ALL!O6*100</f>
-        <v>70.23</v>
+        <v>69.760000000000005</v>
       </c>
       <c r="O152">
         <f>ALL!P6*100</f>
-        <v>70.02000000000001</v>
+        <v>69.56</v>
       </c>
       <c r="P152">
         <f>ALL!Q6*100</f>
-        <v>70.02000000000001</v>
+        <v>69.56</v>
       </c>
     </row>
     <row r="153" spans="1:16" x14ac:dyDescent="0.2">
@@ -17608,47 +17549,47 @@
       </c>
       <c r="F153">
         <f>ALL!G7</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G153">
         <f>ALL!H7</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H153">
         <f>ALL!I7</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I153">
         <f>ALL!J7</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J153">
         <f>ALL!K7</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K153">
         <f>ALL!L7</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L153">
         <f>ALL!M7</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M153">
         <f>ALL!N7</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N153">
         <f>ALL!O7</f>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O153">
         <f>ALL!P7</f>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P153">
         <f>ALL!Q7</f>
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="155" spans="1:16" x14ac:dyDescent="0.2">
@@ -17684,19 +17625,19 @@
       </c>
       <c r="C156">
         <f>ALL!D36*100</f>
-        <v>96.179999999999993</v>
+        <v>95.54</v>
       </c>
       <c r="D156">
         <f>ALL!E36*100</f>
-        <v>94.28</v>
+        <v>93.65</v>
       </c>
       <c r="E156">
         <f>ALL!F36*100</f>
-        <v>87.570000000000007</v>
+        <v>86.99</v>
       </c>
       <c r="F156">
         <f>ALL!G36*100</f>
-        <v>70.09</v>
+        <v>69.62</v>
       </c>
     </row>
     <row r="157" spans="1:16" x14ac:dyDescent="0.2">
@@ -17710,19 +17651,19 @@
       </c>
       <c r="C157">
         <f>ALL!D37</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D157">
         <f>ALL!E37</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E157">
         <f>ALL!F37</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F157">
         <f>ALL!G37</f>
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="161" spans="1:16" x14ac:dyDescent="0.2">
@@ -17810,47 +17751,47 @@
       </c>
       <c r="F162">
         <f t="shared" si="0"/>
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G162">
         <f t="shared" si="0"/>
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H162">
         <f t="shared" si="0"/>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I162">
         <f t="shared" si="0"/>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J162">
         <f t="shared" si="0"/>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K162">
         <f t="shared" si="0"/>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L162">
         <f t="shared" si="0"/>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M162">
         <f t="shared" si="0"/>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N162">
         <f t="shared" si="0"/>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O162">
         <f t="shared" si="0"/>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P162">
         <f t="shared" si="0"/>
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="163" spans="1:16" x14ac:dyDescent="0.2">
@@ -18094,49 +18035,49 @@
         <v>17</v>
       </c>
       <c r="C3" s="8">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="D3" s="8">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="E3" s="8">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="F3" s="8">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="G3" s="8">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="H3" s="8">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="I3" s="8">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="J3" s="8">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="K3" s="8">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="L3" s="8">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="M3" s="8">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="N3" s="8">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="O3" s="8">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="P3" s="8">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="Q3" s="8">
-        <v>17</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.2">
@@ -18147,25 +18088,25 @@
         <v>18</v>
       </c>
       <c r="C4" s="8">
-        <v>17</v>
+        <v>16.850000000000001</v>
       </c>
       <c r="D4" s="8">
-        <v>17</v>
+        <v>16.95</v>
       </c>
       <c r="E4" s="8">
-        <v>17</v>
+        <v>16.649999999999999</v>
       </c>
       <c r="F4" s="14">
-        <v>17</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="G4" s="14">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="H4" s="14">
-        <v>17</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="I4" s="8">
-        <v>16</v>
+        <v>16.2</v>
       </c>
       <c r="J4" s="8">
         <v>16</v>
@@ -18174,22 +18115,22 @@
         <v>16</v>
       </c>
       <c r="L4" s="8">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="M4" s="8">
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="N4" s="8">
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="O4" s="8">
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="P4" s="8">
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="Q4" s="8">
-        <v>14</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.2">
@@ -18393,13 +18334,13 @@
         <v>19</v>
       </c>
       <c r="C10" s="8">
-        <v>17</v>
+        <v>17.25</v>
       </c>
       <c r="D10" s="8">
-        <v>17</v>
+        <v>17.25</v>
       </c>
       <c r="E10" s="8">
-        <v>17</v>
+        <v>17.25</v>
       </c>
       <c r="F10" s="8">
         <v>17</v>
@@ -18446,25 +18387,25 @@
         <v>19</v>
       </c>
       <c r="C11" s="8">
-        <v>17</v>
+        <v>16.850000000000001</v>
       </c>
       <c r="D11" s="8">
-        <v>17</v>
+        <v>16.95</v>
       </c>
       <c r="E11" s="8">
-        <v>17</v>
+        <v>16.649999999999999</v>
       </c>
       <c r="F11" s="14">
-        <v>17</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="G11" s="14">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="H11" s="14">
-        <v>17</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="I11" s="8">
-        <v>16</v>
+        <v>16.2</v>
       </c>
       <c r="J11" s="8">
         <v>16</v>
@@ -18473,22 +18414,22 @@
         <v>16</v>
       </c>
       <c r="L11" s="8">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="M11" s="8">
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="N11" s="8">
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="O11" s="8">
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="P11" s="8">
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="Q11" s="8">
-        <v>14</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
@@ -18875,19 +18816,19 @@
       <c r="B32" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C32" s="26">
+      <c r="C32">
         <v>18</v>
       </c>
-      <c r="D32" s="21">
+      <c r="D32">
         <v>17</v>
       </c>
-      <c r="E32" s="21">
+      <c r="E32">
         <v>17</v>
       </c>
-      <c r="F32" s="21">
+      <c r="F32">
         <v>17</v>
       </c>
-      <c r="G32" s="21">
+      <c r="G32">
         <v>17</v>
       </c>
     </row>
@@ -18898,20 +18839,20 @@
       <c r="B33" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C33" s="26">
-        <v>17</v>
-      </c>
-      <c r="D33" s="21">
-        <v>17</v>
-      </c>
-      <c r="E33" s="21">
-        <v>17</v>
-      </c>
-      <c r="F33" s="21">
-        <v>17</v>
-      </c>
-      <c r="G33" s="21">
-        <v>17</v>
+      <c r="C33">
+        <v>17.2</v>
+      </c>
+      <c r="D33">
+        <v>17.2</v>
+      </c>
+      <c r="E33">
+        <v>17.2</v>
+      </c>
+      <c r="F33">
+        <v>17.2</v>
+      </c>
+      <c r="G33">
+        <v>17.2</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
@@ -18921,38 +18862,38 @@
       <c r="B34" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C34" s="26">
-        <v>17</v>
-      </c>
-      <c r="D34" s="14">
-        <v>17</v>
-      </c>
-      <c r="E34" s="21">
-        <v>16</v>
-      </c>
-      <c r="F34" s="21">
-        <v>16</v>
-      </c>
-      <c r="G34" s="21">
-        <v>14</v>
+      <c r="C34">
+        <v>16.816669999999998</v>
+      </c>
+      <c r="D34">
+        <v>17.433330000000002</v>
+      </c>
+      <c r="E34">
+        <v>16.066669999999998</v>
+      </c>
+      <c r="F34">
+        <v>15.76667</v>
+      </c>
+      <c r="G34">
+        <v>14.2</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="17"/>
       <c r="B35" s="8"/>
-      <c r="C35" s="27">
+      <c r="C35" s="83">
         <v>6.5699999999999995E-2</v>
       </c>
-      <c r="D35" s="28">
+      <c r="D35" s="83">
         <v>-2.5499999999999998E-2</v>
       </c>
-      <c r="E35" s="28">
+      <c r="E35" s="83">
         <v>5.4899999999999997E-2</v>
       </c>
-      <c r="F35" s="28">
+      <c r="F35" s="83">
         <v>7.2499999999999995E-2</v>
       </c>
-      <c r="G35" s="28">
+      <c r="G35" s="83">
         <v>0.16470000000000001</v>
       </c>
     </row>
@@ -18961,19 +18902,19 @@
       <c r="B36" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="C36" s="29">
+      <c r="C36" s="83">
         <v>0.93430000000000002</v>
       </c>
-      <c r="D36" s="19">
+      <c r="D36" s="83">
         <v>1.0255000000000001</v>
       </c>
-      <c r="E36" s="19">
+      <c r="E36" s="83">
         <v>0.94510000000000005</v>
       </c>
-      <c r="F36" s="19">
+      <c r="F36" s="83">
         <v>0.92749999999999999</v>
       </c>
-      <c r="G36" s="19">
+      <c r="G36" s="83">
         <v>0.83530000000000004</v>
       </c>
     </row>
@@ -18982,30 +18923,25 @@
       <c r="B37" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="C37" s="30">
-        <v>1</v>
-      </c>
-      <c r="D37" s="20">
-        <v>0</v>
-      </c>
-      <c r="E37" s="20">
-        <v>1</v>
-      </c>
-      <c r="F37" s="20">
-        <v>1</v>
-      </c>
-      <c r="G37" s="20">
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>1</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+      <c r="G37">
         <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="17"/>
       <c r="B38" s="8"/>
-      <c r="C38" s="31"/>
-      <c r="D38" s="21"/>
-      <c r="E38" s="21"/>
-      <c r="F38" s="21"/>
-      <c r="G38" s="21"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="15" t="s">
@@ -19014,19 +18950,19 @@
       <c r="B39" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="26">
+      <c r="C39">
         <v>18</v>
       </c>
-      <c r="D39" s="21">
+      <c r="D39">
         <v>17</v>
       </c>
-      <c r="E39" s="21">
+      <c r="E39">
         <v>17</v>
       </c>
-      <c r="F39" s="21">
+      <c r="F39">
         <v>17</v>
       </c>
-      <c r="G39" s="21">
+      <c r="G39">
         <v>17</v>
       </c>
     </row>
@@ -19037,19 +18973,19 @@
       <c r="B40" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C40" s="26">
+      <c r="C40">
         <v>17</v>
       </c>
-      <c r="D40" s="21">
+      <c r="D40">
         <v>17</v>
       </c>
-      <c r="E40" s="21">
+      <c r="E40">
         <v>17</v>
       </c>
-      <c r="F40" s="21">
+      <c r="F40">
         <v>17</v>
       </c>
-      <c r="G40" s="21">
+      <c r="G40">
         <v>17</v>
       </c>
     </row>
@@ -19060,30 +18996,25 @@
       <c r="B41" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C41" s="26">
+      <c r="C41">
         <v>17</v>
       </c>
-      <c r="D41" s="14">
+      <c r="D41">
         <v>17</v>
       </c>
-      <c r="E41" s="21">
+      <c r="E41">
         <v>16</v>
       </c>
-      <c r="F41" s="21">
+      <c r="F41">
         <v>16</v>
       </c>
-      <c r="G41" s="21">
+      <c r="G41">
         <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="8"/>
       <c r="B42" s="17"/>
-      <c r="C42" s="26"/>
-      <c r="D42" s="21"/>
-      <c r="E42" s="21"/>
-      <c r="F42" s="21"/>
-      <c r="G42" s="21"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="15" t="s">
@@ -19092,19 +19023,19 @@
       <c r="B43" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C43" s="26">
-        <v>0</v>
-      </c>
-      <c r="D43" s="21">
-        <v>0</v>
-      </c>
-      <c r="E43" s="21">
-        <v>0</v>
-      </c>
-      <c r="F43" s="21">
-        <v>0</v>
-      </c>
-      <c r="G43" s="21">
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
         <v>0</v>
       </c>
     </row>
@@ -19115,19 +19046,19 @@
       <c r="B44" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C44" s="26">
-        <v>0</v>
-      </c>
-      <c r="D44" s="21">
-        <v>0</v>
-      </c>
-      <c r="E44" s="21">
-        <v>0</v>
-      </c>
-      <c r="F44" s="21">
-        <v>0</v>
-      </c>
-      <c r="G44" s="21">
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
         <v>0</v>
       </c>
     </row>
@@ -19138,30 +19069,25 @@
       <c r="B45" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C45" s="26">
-        <v>0</v>
-      </c>
-      <c r="D45" s="21">
-        <v>0</v>
-      </c>
-      <c r="E45" s="21">
-        <v>0</v>
-      </c>
-      <c r="F45" s="21">
-        <v>0</v>
-      </c>
-      <c r="G45" s="21">
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="8"/>
       <c r="B46" s="17"/>
-      <c r="C46" s="26"/>
-      <c r="D46" s="21"/>
-      <c r="E46" s="21"/>
-      <c r="F46" s="21"/>
-      <c r="G46" s="21"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="15" t="s">
@@ -19170,19 +19096,19 @@
       <c r="B47" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C47" s="26">
-        <v>0</v>
-      </c>
-      <c r="D47" s="21">
-        <v>0</v>
-      </c>
-      <c r="E47" s="21">
-        <v>0</v>
-      </c>
-      <c r="F47" s="21">
-        <v>0</v>
-      </c>
-      <c r="G47" s="21">
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
         <v>0</v>
       </c>
     </row>
@@ -19193,19 +19119,19 @@
       <c r="B48" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C48" s="26">
-        <v>0</v>
-      </c>
-      <c r="D48" s="21">
-        <v>0</v>
-      </c>
-      <c r="E48" s="21">
-        <v>0</v>
-      </c>
-      <c r="F48" s="21">
-        <v>0</v>
-      </c>
-      <c r="G48" s="21">
+      <c r="C48">
+        <v>0</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
         <v>0</v>
       </c>
     </row>
@@ -19216,19 +19142,19 @@
       <c r="B49" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C49" s="26">
-        <v>0</v>
-      </c>
-      <c r="D49" s="21">
-        <v>0</v>
-      </c>
-      <c r="E49" s="21">
-        <v>0</v>
-      </c>
-      <c r="F49" s="21">
-        <v>0</v>
-      </c>
-      <c r="G49" s="21">
+      <c r="C49">
+        <v>0</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
         <v>0</v>
       </c>
     </row>
@@ -19854,63 +19780,63 @@
       </c>
       <c r="B3">
         <f>IF(CPS!C3&gt;0,CPS!C3,"")</f>
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="C3">
         <f>IF(CPS!D3&gt;0,CPS!D3,"")</f>
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="D3">
         <f>IF(CPS!E3&gt;0,CPS!E3,"")</f>
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="E3">
         <f>IF(CPS!F3&gt;0,CPS!F3,"")</f>
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="F3">
         <f>IF(CPS!G3&gt;0,CPS!G3,"")</f>
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="G3">
         <f>IF(CPS!H3&gt;0,CPS!H3,"")</f>
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="H3">
         <f>IF(CPS!I3&gt;0,CPS!I3,"")</f>
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="I3">
         <f>IF(CPS!J3&gt;0,CPS!J3,"")</f>
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="J3">
         <f>IF(CPS!K3&gt;0,CPS!K3,"")</f>
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="K3">
         <f>IF(CPS!L3&gt;0,CPS!L3,"")</f>
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="L3">
         <f>IF(CPS!M3&gt;0,CPS!M3,"")</f>
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="M3">
         <f>IF(CPS!N3&gt;0,CPS!N3,"")</f>
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="N3">
         <f>IF(CPS!O3&gt;0,CPS!O3,"")</f>
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="O3">
         <f>IF(CPS!P3&gt;0,CPS!P3,"")</f>
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="P3">
         <f>IF(CPS!Q3&gt;0,CPS!Q3,"")</f>
-        <v>17</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
@@ -19920,31 +19846,31 @@
       </c>
       <c r="B4">
         <f>IF(CPS!C4&gt;0,CPS!C4,"")</f>
-        <v>17</v>
+        <v>16.850000000000001</v>
       </c>
       <c r="C4">
         <f>IF(CPS!D4&gt;0,CPS!D4,"")</f>
-        <v>17</v>
+        <v>16.95</v>
       </c>
       <c r="D4">
         <f>IF(CPS!E4&gt;0,CPS!E4,"")</f>
-        <v>17</v>
+        <v>16.649999999999999</v>
       </c>
       <c r="E4">
         <f>IF(CPS!F4&gt;0,CPS!F4,"")</f>
-        <v>17</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="F4">
         <f>IF(CPS!G4&gt;0,CPS!G4,"")</f>
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="G4">
         <f>IF(CPS!H4&gt;0,CPS!H4,"")</f>
-        <v>17</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="H4">
         <f>IF(CPS!I4&gt;0,CPS!I4,"")</f>
-        <v>16</v>
+        <v>16.2</v>
       </c>
       <c r="I4">
         <f>IF(CPS!J4&gt;0,CPS!J4,"")</f>
@@ -19956,27 +19882,27 @@
       </c>
       <c r="K4">
         <f>IF(CPS!L4&gt;0,CPS!L4,"")</f>
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="L4">
         <f>IF(CPS!M4&gt;0,CPS!M4,"")</f>
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="M4">
         <f>IF(CPS!N4&gt;0,CPS!N4,"")</f>
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="N4">
         <f>IF(CPS!O4&gt;0,CPS!O4,"")</f>
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="O4">
         <f>IF(CPS!P4&gt;0,CPS!P4,"")</f>
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="P4">
         <f>IF(CPS!Q4&gt;0,CPS!Q4,"")</f>
-        <v>14</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
@@ -19986,31 +19912,31 @@
       </c>
       <c r="B5">
         <f>IF(CPS!C11&gt;0,CPS!C11,"")</f>
-        <v>17</v>
+        <v>16.850000000000001</v>
       </c>
       <c r="C5">
         <f>IF(CPS!D11&gt;0,CPS!D11,"")</f>
-        <v>17</v>
+        <v>16.95</v>
       </c>
       <c r="D5">
         <f>IF(CPS!E11&gt;0,CPS!E11,"")</f>
-        <v>17</v>
+        <v>16.649999999999999</v>
       </c>
       <c r="E5">
         <f>IF(CPS!F11&gt;0,CPS!F11,"")</f>
-        <v>17</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="F5">
         <f>IF(CPS!G11&gt;0,CPS!G11,"")</f>
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="G5">
         <f>IF(CPS!H11&gt;0,CPS!H11,"")</f>
-        <v>17</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="H5">
         <f>IF(CPS!I11&gt;0,CPS!I11,"")</f>
-        <v>16</v>
+        <v>16.2</v>
       </c>
       <c r="I5">
         <f>IF(CPS!J11&gt;0,CPS!J11,"")</f>
@@ -20022,27 +19948,27 @@
       </c>
       <c r="K5">
         <f>IF(CPS!L11&gt;0,CPS!L11,"")</f>
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="L5">
         <f>IF(CPS!M11&gt;0,CPS!M11,"")</f>
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="M5">
         <f>IF(CPS!N11&gt;0,CPS!N11,"")</f>
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="N5">
         <f>IF(CPS!O11&gt;0,CPS!O11,"")</f>
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="O5">
         <f>IF(CPS!P11&gt;0,CPS!P11,"")</f>
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="P5">
         <f>IF(CPS!Q11&gt;0,CPS!Q11,"")</f>
-        <v>14</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
@@ -20312,15 +20238,15 @@
       </c>
       <c r="B13">
         <f>IF(CPS!C10&gt;0,CPS!C10,"")</f>
-        <v>17</v>
+        <v>17.25</v>
       </c>
       <c r="C13">
         <f>IF(CPS!D10&gt;0,CPS!D10,"")</f>
-        <v>17</v>
+        <v>17.25</v>
       </c>
       <c r="D13">
         <f>IF(CPS!E10&gt;0,CPS!E10,"")</f>
-        <v>17</v>
+        <v>17.25</v>
       </c>
       <c r="E13">
         <f>IF(CPS!F10&gt;0,CPS!F10,"")</f>
@@ -20378,31 +20304,31 @@
       </c>
       <c r="B14">
         <f>IF(CPS!C11&gt;0,CPS!C11,"")</f>
-        <v>17</v>
+        <v>16.850000000000001</v>
       </c>
       <c r="C14">
         <f>IF(CPS!D11&gt;0,CPS!D11,"")</f>
-        <v>17</v>
+        <v>16.95</v>
       </c>
       <c r="D14">
         <f>IF(CPS!E11&gt;0,CPS!E11,"")</f>
-        <v>17</v>
+        <v>16.649999999999999</v>
       </c>
       <c r="E14">
         <f>IF(CPS!F11&gt;0,CPS!F11,"")</f>
-        <v>17</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="F14">
         <f>IF(CPS!G11&gt;0,CPS!G11,"")</f>
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="G14">
         <f>IF(CPS!H11&gt;0,CPS!H11,"")</f>
-        <v>17</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="H14">
         <f>IF(CPS!I11&gt;0,CPS!I11,"")</f>
-        <v>16</v>
+        <v>16.2</v>
       </c>
       <c r="I14">
         <f>IF(CPS!J11&gt;0,CPS!J11,"")</f>
@@ -20414,27 +20340,27 @@
       </c>
       <c r="K14">
         <f>IF(CPS!L11&gt;0,CPS!L11,"")</f>
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="L14">
         <f>IF(CPS!M11&gt;0,CPS!M11,"")</f>
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="M14">
         <f>IF(CPS!N11&gt;0,CPS!N11,"")</f>
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="N14">
         <f>IF(CPS!O11&gt;0,CPS!O11,"")</f>
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="O14">
         <f>IF(CPS!P11&gt;0,CPS!P11,"")</f>
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="P14">
         <f>IF(CPS!Q11&gt;0,CPS!Q11,"")</f>
-        <v>14</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
@@ -21012,23 +20938,23 @@
       </c>
       <c r="B43">
         <f>IF(CPS!C33&gt;0,CPS!C33,"")</f>
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="C43">
         <f>IF(CPS!D33&gt;0,CPS!D33,"")</f>
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="D43">
         <f>IF(CPS!E33&gt;0,CPS!E33,"")</f>
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="E43">
         <f>IF(CPS!F33&gt;0,CPS!F33,"")</f>
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="F43">
         <f>IF(CPS!G33&gt;0,CPS!G33,"")</f>
-        <v>17</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.2">
@@ -21038,23 +20964,23 @@
       </c>
       <c r="B44">
         <f>IF(CPS!C34&gt;0,CPS!C34,"")</f>
-        <v>17</v>
+        <v>16.816669999999998</v>
       </c>
       <c r="C44">
         <f>IF(CPS!D34&gt;0,CPS!D34,"")</f>
-        <v>17</v>
+        <v>17.433330000000002</v>
       </c>
       <c r="D44">
         <f>IF(CPS!E34&gt;0,CPS!E34,"")</f>
-        <v>16</v>
+        <v>16.066669999999998</v>
       </c>
       <c r="E44">
         <f>IF(CPS!F34&gt;0,CPS!F34,"")</f>
-        <v>16</v>
+        <v>15.76667</v>
       </c>
       <c r="F44">
         <f>IF(CPS!G34&gt;0,CPS!G34,"")</f>
-        <v>14</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.2">
@@ -22958,13 +22884,13 @@
         <v>47</v>
       </c>
       <c r="D33" s="21">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E33" s="21">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F33" s="21">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G33" s="21">
         <v>47</v>
@@ -25602,15 +25528,15 @@
       </c>
       <c r="C43">
         <f>IF(PSE!D33&gt;0,PSE!D33,"")</f>
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D43">
         <f>IF(PSE!E33&gt;0,PSE!E33,"")</f>
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E43">
         <f>IF(PSE!F33&gt;0,PSE!F33,"")</f>
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F43">
         <f>IF(PSE!G33&gt;0,PSE!G33,"")</f>
@@ -26695,7 +26621,7 @@
         <v>46</v>
       </c>
       <c r="G2" s="8">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H2" s="8">
         <v>46</v>
@@ -26800,7 +26726,7 @@
       <c r="F4" s="8">
         <v>44</v>
       </c>
-      <c r="G4" s="14">
+      <c r="G4" s="8">
         <v>46</v>
       </c>
       <c r="H4" s="14">
@@ -26871,7 +26797,7 @@
         <v>0.95079999999999998</v>
       </c>
       <c r="G6" s="19">
-        <v>1.0044999999999999</v>
+        <v>0.98309999999999997</v>
       </c>
       <c r="H6" s="19">
         <v>1.0102</v>
@@ -26922,7 +26848,7 @@
         <v>2</v>
       </c>
       <c r="G7" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="20">
         <v>0</v>
@@ -26994,7 +26920,7 @@
         <v>35</v>
       </c>
       <c r="G9" s="8">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H9" s="8">
         <v>35</v>
@@ -27586,7 +27512,7 @@
         <v>-1E-3</v>
       </c>
       <c r="D35" s="28">
-        <v>1.15E-2</v>
+        <v>1.8599999999999998E-2</v>
       </c>
       <c r="E35" s="28">
         <v>-9.7999999999999997E-3</v>
@@ -27607,7 +27533,7 @@
         <v>1.0009999999999999</v>
       </c>
       <c r="D36" s="19">
-        <v>0.98850000000000005</v>
+        <v>0.98140000000000005</v>
       </c>
       <c r="E36" s="19">
         <v>1.0098</v>
@@ -27943,7 +27869,7 @@
         <v>46</v>
       </c>
       <c r="G62" s="12">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H62" s="12">
         <v>46</v>
@@ -29001,7 +28927,7 @@
         <v>5</v>
       </c>
       <c r="G82" s="49">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H82" s="49">
         <v>5</v>
@@ -29718,7 +29644,7 @@
       </c>
       <c r="F2">
         <f>IF(SD!G2&gt;0,SD!G2,"")</f>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G2">
         <f>IF(SD!H2&gt;0,SD!H2,"")</f>
@@ -30176,7 +30102,7 @@
       </c>
       <c r="F12">
         <f>IF(SD!G9&gt;0,SD!G9,"")</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G12">
         <f>IF(SD!H9&gt;0,SD!H9,"")</f>
@@ -33004,7 +32930,7 @@
       </c>
       <c r="F112">
         <f>SD!G82</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G112">
         <f>SD!H82</f>
@@ -33135,7 +33061,7 @@
       </c>
       <c r="F114" s="67">
         <f t="shared" si="12"/>
-        <v>-0.99000000000000021</v>
+        <v>9.9999999999997868E-3</v>
       </c>
       <c r="G114" s="67">
         <f t="shared" si="12"/>
@@ -33211,7 +33137,7 @@
       </c>
       <c r="C116" s="59">
         <f>(AVERAGE(E113:G113)/AVERAGE(E112:G112))*100</f>
-        <v>111.73333333333333</v>
+        <v>104.74999999999999</v>
       </c>
       <c r="D116" s="59">
         <f>(AVERAGE(H113:J113)/AVERAGE(H112:J112))*100</f>
@@ -33933,7 +33859,7 @@
       </c>
       <c r="F152">
         <f>SD!G6*100</f>
-        <v>100.44999999999999</v>
+        <v>98.31</v>
       </c>
       <c r="G152">
         <f>SD!H6*100</f>
@@ -33999,7 +33925,7 @@
       </c>
       <c r="F153">
         <f>SD!G7</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G153">
         <f>SD!H7</f>
@@ -34075,7 +34001,7 @@
       </c>
       <c r="C156">
         <f>SD!D36*100</f>
-        <v>98.850000000000009</v>
+        <v>98.14</v>
       </c>
       <c r="D156">
         <f>SD!E36*100</f>
@@ -34200,37 +34126,37 @@
         <v>21</v>
       </c>
       <c r="G2" s="8">
+        <v>21</v>
+      </c>
+      <c r="H2" s="8">
+        <v>21</v>
+      </c>
+      <c r="I2" s="8">
         <v>20</v>
       </c>
-      <c r="H2" s="8">
+      <c r="J2" s="8">
         <v>20</v>
       </c>
-      <c r="I2" s="8">
-        <v>19</v>
-      </c>
-      <c r="J2" s="8">
-        <v>19</v>
-      </c>
       <c r="K2" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L2" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M2" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N2" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O2" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P2" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q2" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.2">
@@ -34241,49 +34167,49 @@
         <v>17</v>
       </c>
       <c r="C3" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H3" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I3" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J3" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K3" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L3" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M3" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N3" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O3" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P3" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q3" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.2">
@@ -34376,37 +34302,37 @@
         <v>0.88400000000000001</v>
       </c>
       <c r="G6" s="19">
-        <v>0.91969999999999996</v>
+        <v>0.87590000000000001</v>
       </c>
       <c r="H6" s="19">
-        <v>0.8982</v>
+        <v>0.85540000000000005</v>
       </c>
       <c r="I6" s="19">
-        <v>0.83279999999999998</v>
+        <v>0.79110000000000003</v>
       </c>
       <c r="J6" s="19">
-        <v>0.78800000000000003</v>
+        <v>0.74860000000000004</v>
       </c>
       <c r="K6" s="19">
-        <v>0.75639999999999996</v>
+        <v>0.71860000000000002</v>
       </c>
       <c r="L6" s="19">
-        <v>0.71499999999999997</v>
+        <v>0.67930000000000001</v>
       </c>
       <c r="M6" s="19">
-        <v>0.71760000000000002</v>
+        <v>0.68179999999999996</v>
       </c>
       <c r="N6" s="19">
-        <v>0.70179999999999998</v>
+        <v>0.66679999999999995</v>
       </c>
       <c r="O6" s="19">
-        <v>0.44130000000000003</v>
+        <v>0.41930000000000001</v>
       </c>
       <c r="P6" s="19">
-        <v>0.44130000000000003</v>
+        <v>0.41930000000000001</v>
       </c>
       <c r="Q6" s="19">
-        <v>0.44130000000000003</v>
+        <v>0.41930000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
@@ -34427,37 +34353,37 @@
         <v>2</v>
       </c>
       <c r="G7" s="20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H7" s="20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I7" s="20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J7" s="20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K7" s="20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L7" s="20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M7" s="20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N7" s="20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O7" s="20">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P7" s="20">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q7" s="20">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
@@ -34499,37 +34425,37 @@
         <v>21</v>
       </c>
       <c r="G9" s="8">
+        <v>21</v>
+      </c>
+      <c r="H9" s="8">
+        <v>21</v>
+      </c>
+      <c r="I9" s="8">
         <v>20</v>
       </c>
-      <c r="H9" s="8">
+      <c r="J9" s="8">
         <v>20</v>
       </c>
-      <c r="I9" s="8">
-        <v>19</v>
-      </c>
-      <c r="J9" s="8">
-        <v>19</v>
-      </c>
       <c r="K9" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L9" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M9" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N9" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O9" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P9" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q9" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.2">
@@ -34540,49 +34466,49 @@
         <v>19</v>
       </c>
       <c r="C10" s="8">
+        <v>21</v>
+      </c>
+      <c r="D10" s="8">
+        <v>21</v>
+      </c>
+      <c r="E10" s="8">
+        <v>21</v>
+      </c>
+      <c r="F10" s="8">
         <v>20</v>
       </c>
-      <c r="D10" s="8">
+      <c r="G10" s="8">
         <v>20</v>
       </c>
-      <c r="E10" s="8">
+      <c r="H10" s="8">
         <v>20</v>
       </c>
-      <c r="F10" s="8">
-        <v>19</v>
-      </c>
-      <c r="G10" s="8">
-        <v>19</v>
-      </c>
-      <c r="H10" s="8">
-        <v>19</v>
-      </c>
       <c r="I10" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J10" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K10" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L10" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M10" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N10" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O10" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P10" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q10" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
@@ -35026,16 +34952,16 @@
         <v>23</v>
       </c>
       <c r="D32" s="21">
+        <v>21</v>
+      </c>
+      <c r="E32" s="21">
         <v>20</v>
       </c>
-      <c r="E32" s="21">
-        <v>19</v>
-      </c>
       <c r="F32" s="21">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G32" s="21">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
@@ -35046,19 +34972,19 @@
         <v>17</v>
       </c>
       <c r="C33" s="26">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D33" s="21">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E33" s="21">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F33" s="21">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G33" s="21">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
@@ -35091,16 +35017,16 @@
         <v>0.27929999999999999</v>
       </c>
       <c r="D35" s="28">
-        <v>9.9699999999999997E-2</v>
+        <v>0.1283</v>
       </c>
       <c r="E35" s="28">
-        <v>0.20760000000000001</v>
+        <v>0.2472</v>
       </c>
       <c r="F35" s="28">
-        <v>0.28849999999999998</v>
+        <v>0.3241</v>
       </c>
       <c r="G35" s="28">
-        <v>0.55869999999999997</v>
+        <v>0.58079999999999998</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
@@ -35112,16 +35038,16 @@
         <v>0.72070000000000001</v>
       </c>
       <c r="D36" s="19">
-        <v>0.90029999999999999</v>
+        <v>0.87170000000000003</v>
       </c>
       <c r="E36" s="19">
-        <v>0.79239999999999999</v>
+        <v>0.75280000000000002</v>
       </c>
       <c r="F36" s="19">
-        <v>0.71150000000000002</v>
+        <v>0.67589999999999995</v>
       </c>
       <c r="G36" s="19">
-        <v>0.44130000000000003</v>
+        <v>0.41930000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
@@ -35133,16 +35059,16 @@
         <v>6</v>
       </c>
       <c r="D37" s="20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E37" s="20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F37" s="20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G37" s="20">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
@@ -35165,16 +35091,16 @@
         <v>23</v>
       </c>
       <c r="D39" s="21">
+        <v>21</v>
+      </c>
+      <c r="E39" s="21">
         <v>20</v>
       </c>
-      <c r="E39" s="21">
-        <v>19</v>
-      </c>
       <c r="F39" s="21">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G39" s="21">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
@@ -35185,19 +35111,19 @@
         <v>19</v>
       </c>
       <c r="C40" s="26">
+        <v>21</v>
+      </c>
+      <c r="D40" s="21">
         <v>20</v>
       </c>
-      <c r="D40" s="21">
-        <v>19</v>
-      </c>
       <c r="E40" s="21">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F40" s="21">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G40" s="21">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
@@ -35448,37 +35374,37 @@
         <v>21</v>
       </c>
       <c r="G62" s="12">
+        <v>21</v>
+      </c>
+      <c r="H62" s="12">
+        <v>21</v>
+      </c>
+      <c r="I62" s="12">
         <v>20</v>
       </c>
-      <c r="H62" s="12">
+      <c r="J62" s="12">
         <v>20</v>
       </c>
-      <c r="I62" s="12">
-        <v>19</v>
-      </c>
-      <c r="J62" s="12">
-        <v>19</v>
-      </c>
       <c r="K62" s="12">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L62" s="12">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M62" s="12">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N62" s="12">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O62" s="12">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P62" s="12">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q62" s="12">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.2">
@@ -35870,37 +35796,37 @@
         <v>4</v>
       </c>
       <c r="G70" s="35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H70" s="35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I70" s="35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J70" s="35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K70" s="35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L70" s="35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M70" s="35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N70" s="35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O70" s="35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P70" s="35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q70" s="35">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.2">

--- a/workforceresult.xlsx
+++ b/workforceresult.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miiintra/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A7F6156-3B4F-F44D-AB08-43EDDE261955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B3B4170-FDE9-BC49-83AF-DA3215772A36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4080" yWindow="4220" windowWidth="40720" windowHeight="15880" activeTab="13" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
+    <workbookView xWindow="4080" yWindow="4220" windowWidth="40720" windowHeight="15880" activeTab="6" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
   </bookViews>
   <sheets>
     <sheet name="ALL" sheetId="1" r:id="rId1"/>
@@ -1548,49 +1548,49 @@
       <c r="B2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="8">
         <v>148</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="8">
         <v>149</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="8">
         <v>149</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="8">
         <v>151</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="8">
         <v>152</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="8">
         <v>151</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="8">
         <v>150</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="8">
         <v>150</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="8">
         <v>150</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="8">
         <v>150</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="8">
         <v>150</v>
       </c>
-      <c r="N2">
+      <c r="N2" s="8">
         <v>150</v>
       </c>
-      <c r="O2">
+      <c r="O2" s="8">
         <v>150</v>
       </c>
-      <c r="P2">
+      <c r="P2" s="8">
         <v>150</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" s="8">
         <v>150</v>
       </c>
     </row>
@@ -1601,49 +1601,49 @@
       <c r="B3" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="8">
         <v>150</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="8">
         <v>150</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="8">
         <v>150</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="8">
         <v>150</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="8">
         <v>150</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="8">
         <v>150</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="8">
         <v>150</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="8">
         <v>150</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="8">
         <v>150</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="8">
         <v>150</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="8">
         <v>150</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="8">
         <v>150</v>
       </c>
-      <c r="O3">
+      <c r="O3" s="8">
         <v>150</v>
       </c>
-      <c r="P3">
+      <c r="P3" s="8">
         <v>150</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="8">
         <v>150</v>
       </c>
     </row>
@@ -1654,104 +1654,119 @@
       <c r="B4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="8">
         <v>131</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="8">
         <v>139</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="8">
         <v>142</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="8">
         <v>143</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="8">
         <v>147</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="8">
         <v>144</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="8">
         <v>143</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="8">
         <v>140</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="8">
         <v>139</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="8">
         <v>132</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="8">
         <v>130</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="8">
         <v>130</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="8">
         <v>105</v>
       </c>
-      <c r="P4">
+      <c r="P4" s="8">
         <v>104</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="8">
         <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="17"/>
       <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
+      <c r="Q5" s="8"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" s="8"/>
       <c r="B6" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="83">
+      <c r="C6" s="19">
         <v>0.88260000000000005</v>
       </c>
-      <c r="D6" s="83">
+      <c r="D6" s="19">
         <v>0.93620000000000003</v>
       </c>
-      <c r="E6" s="83">
+      <c r="E6" s="19">
         <v>0.95589999999999997</v>
       </c>
-      <c r="F6" s="83">
+      <c r="F6" s="19">
         <v>0.94789999999999996</v>
       </c>
-      <c r="G6" s="83">
+      <c r="G6" s="19">
         <v>0.96630000000000005</v>
       </c>
-      <c r="H6" s="83">
+      <c r="H6" s="19">
         <v>0.95189999999999997</v>
       </c>
-      <c r="I6" s="83">
+      <c r="I6" s="19">
         <v>0.95269999999999999</v>
       </c>
-      <c r="J6" s="83">
+      <c r="J6" s="19">
         <v>0.93130000000000002</v>
       </c>
-      <c r="K6" s="83">
+      <c r="K6" s="19">
         <v>0.92559999999999998</v>
       </c>
-      <c r="L6" s="83">
+      <c r="L6" s="19">
         <v>0.87780000000000002</v>
       </c>
-      <c r="M6" s="83">
+      <c r="M6" s="19">
         <v>0.86829999999999996</v>
       </c>
-      <c r="N6" s="83">
+      <c r="N6" s="19">
         <v>0.86360000000000003</v>
       </c>
-      <c r="O6" s="83">
+      <c r="O6" s="19">
         <v>0.6976</v>
       </c>
-      <c r="P6" s="83">
+      <c r="P6" s="19">
         <v>0.6956</v>
       </c>
-      <c r="Q6" s="83">
+      <c r="Q6" s="19">
         <v>0.6956</v>
       </c>
     </row>
@@ -1760,55 +1775,70 @@
       <c r="B7" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="20">
         <v>17</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="20">
         <v>10</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="20">
         <v>7</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="20">
         <v>8</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="20">
         <v>5</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="20">
         <v>7</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="20">
         <v>7</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="20">
         <v>10</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="20">
         <v>11</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="20">
         <v>18</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="20">
         <v>20</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="20">
         <v>20</v>
       </c>
-      <c r="O7">
+      <c r="O7" s="20">
         <v>45</v>
       </c>
-      <c r="P7">
+      <c r="P7" s="20">
         <v>46</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" s="20">
         <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" s="17"/>
       <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" s="15" t="s">
@@ -1817,49 +1847,49 @@
       <c r="B9" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="8">
         <v>121</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="8">
         <v>120</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="8">
         <v>118</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="8">
         <v>118</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="8">
         <v>119</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="8">
         <v>118</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="8">
         <v>117</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="8">
         <v>117</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="8">
         <v>117</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="8">
         <v>117</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="8">
         <v>117</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="8">
         <v>117</v>
       </c>
-      <c r="O9">
+      <c r="O9" s="8">
         <v>117</v>
       </c>
-      <c r="P9">
+      <c r="P9" s="8">
         <v>117</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" s="8">
         <v>117</v>
       </c>
     </row>
@@ -1870,49 +1900,49 @@
       <c r="B10" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="8">
         <v>118</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="8">
         <v>118</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="8">
         <v>118</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="8">
         <v>117</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="8">
         <v>117</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="8">
         <v>117</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="8">
         <v>117</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="8">
         <v>117</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="8">
         <v>117</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="8">
         <v>117</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="8">
         <v>117</v>
       </c>
-      <c r="N10">
+      <c r="N10" s="8">
         <v>117</v>
       </c>
-      <c r="O10">
+      <c r="O10" s="8">
         <v>117</v>
       </c>
-      <c r="P10">
+      <c r="P10" s="8">
         <v>117</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" s="8">
         <v>117</v>
       </c>
     </row>
@@ -1923,55 +1953,70 @@
       <c r="B11" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="8">
         <v>105</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="8">
         <v>111</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="8">
         <v>111</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="8">
         <v>112</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="8">
         <v>113</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="8">
         <v>111</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="8">
         <v>108</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="8">
         <v>105</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="8">
         <v>103</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="8">
         <v>100</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="8">
         <v>99</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="8">
         <v>98</v>
       </c>
-      <c r="O11">
+      <c r="O11" s="8">
         <v>81</v>
       </c>
-      <c r="P11">
+      <c r="P11" s="8">
         <v>81</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" s="8">
         <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" s="8"/>
       <c r="B12" s="17"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
+      <c r="Q12" s="8"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" s="15" t="s">
@@ -1980,49 +2025,49 @@
       <c r="B13" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="8">
         <v>21</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="8">
         <v>21</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="8">
         <v>21</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="8">
         <v>21</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="8">
         <v>21</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="8">
         <v>21</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="8">
         <v>21</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="8">
         <v>21</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="8">
         <v>21</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="8">
         <v>21</v>
       </c>
-      <c r="M13">
+      <c r="M13" s="8">
         <v>21</v>
       </c>
-      <c r="N13">
+      <c r="N13" s="8">
         <v>21</v>
       </c>
-      <c r="O13">
+      <c r="O13" s="8">
         <v>21</v>
       </c>
-      <c r="P13">
+      <c r="P13" s="8">
         <v>21</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" s="8">
         <v>21</v>
       </c>
     </row>
@@ -2033,49 +2078,49 @@
       <c r="B14" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="8">
         <v>21</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="8">
         <v>21</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="8">
         <v>21</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="8">
         <v>21</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="8">
         <v>21</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="8">
         <v>21</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="8">
         <v>21</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="8">
         <v>21</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="8">
         <v>21</v>
       </c>
-      <c r="L14">
+      <c r="L14" s="8">
         <v>21</v>
       </c>
-      <c r="M14">
+      <c r="M14" s="8">
         <v>21</v>
       </c>
-      <c r="N14">
+      <c r="N14" s="8">
         <v>21</v>
       </c>
-      <c r="O14">
+      <c r="O14" s="8">
         <v>21</v>
       </c>
-      <c r="P14">
+      <c r="P14" s="8">
         <v>21</v>
       </c>
-      <c r="Q14">
+      <c r="Q14" s="8">
         <v>21</v>
       </c>
     </row>
@@ -2086,55 +2131,70 @@
       <c r="B15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="8">
         <v>20</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="8">
         <v>20</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="14">
         <v>22</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="8">
         <v>21</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="8">
         <v>21</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="8">
         <v>20</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="8">
         <v>20</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="8">
         <v>20</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="8">
         <v>20</v>
       </c>
-      <c r="L15">
+      <c r="L15" s="8">
         <v>19</v>
       </c>
-      <c r="M15">
+      <c r="M15" s="8">
         <v>19</v>
       </c>
-      <c r="N15">
+      <c r="N15" s="8">
         <v>19</v>
       </c>
-      <c r="O15">
+      <c r="O15" s="8">
         <v>17</v>
       </c>
-      <c r="P15">
+      <c r="P15" s="8">
         <v>17</v>
       </c>
-      <c r="Q15">
+      <c r="Q15" s="8">
         <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" s="8"/>
       <c r="B16" s="17"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="8"/>
+      <c r="Q16" s="8"/>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" s="15" t="s">
@@ -2143,49 +2203,49 @@
       <c r="B17" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="8">
         <v>6</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="8">
         <v>8</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="8">
         <v>10</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="8">
         <v>12</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="8">
         <v>12</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="8">
         <v>12</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="8">
         <v>12</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="8">
         <v>12</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="8">
         <v>12</v>
       </c>
-      <c r="L17">
+      <c r="L17" s="8">
         <v>12</v>
       </c>
-      <c r="M17">
+      <c r="M17" s="8">
         <v>12</v>
       </c>
-      <c r="N17">
+      <c r="N17" s="8">
         <v>12</v>
       </c>
-      <c r="O17">
+      <c r="O17" s="8">
         <v>12</v>
       </c>
-      <c r="P17">
+      <c r="P17" s="8">
         <v>12</v>
       </c>
-      <c r="Q17">
+      <c r="Q17" s="8">
         <v>12</v>
       </c>
     </row>
@@ -2196,49 +2256,49 @@
       <c r="B18" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="8">
         <v>11</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="8">
         <v>11</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="8">
         <v>11</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="8">
         <v>11</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="8">
         <v>11</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="8">
         <v>11</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="8">
         <v>11</v>
       </c>
-      <c r="J18">
+      <c r="J18" s="8">
         <v>11</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="8">
         <v>11</v>
       </c>
-      <c r="L18">
+      <c r="L18" s="8">
         <v>11</v>
       </c>
-      <c r="M18">
+      <c r="M18" s="8">
         <v>11</v>
       </c>
-      <c r="N18">
+      <c r="N18" s="8">
         <v>11</v>
       </c>
-      <c r="O18">
+      <c r="O18" s="8">
         <v>11</v>
       </c>
-      <c r="P18">
+      <c r="P18" s="8">
         <v>11</v>
       </c>
-      <c r="Q18">
+      <c r="Q18" s="8">
         <v>11</v>
       </c>
     </row>
@@ -2249,49 +2309,49 @@
       <c r="B19" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="8">
         <v>6</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="14">
         <v>8</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="8">
         <v>10</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="8">
         <v>10</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="14">
         <v>12</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="14">
         <v>14</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="14">
         <v>15</v>
       </c>
-      <c r="J19">
+      <c r="J19" s="14">
         <v>15</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="14">
         <v>16</v>
       </c>
-      <c r="L19">
+      <c r="L19" s="14">
         <v>12</v>
       </c>
-      <c r="M19">
+      <c r="M19" s="14">
         <v>12</v>
       </c>
-      <c r="N19">
+      <c r="N19" s="14">
         <v>12</v>
       </c>
-      <c r="O19">
+      <c r="O19" s="8">
         <v>7</v>
       </c>
-      <c r="P19">
+      <c r="P19" s="8">
         <v>7</v>
       </c>
-      <c r="Q19">
+      <c r="Q19" s="8">
         <v>7</v>
       </c>
     </row>
@@ -27908,49 +27968,49 @@
         <v>18</v>
       </c>
       <c r="C63" s="48">
-        <v>34.077500000000001</v>
+        <v>40.457500000000003</v>
       </c>
       <c r="D63" s="48">
-        <v>38.524999999999999</v>
+        <v>45.84</v>
       </c>
       <c r="E63" s="48">
-        <v>40.520000000000003</v>
+        <v>47.835000000000001</v>
       </c>
       <c r="F63" s="48">
-        <v>36.765000000000001</v>
+        <v>43.734999999999999</v>
       </c>
       <c r="G63" s="48">
-        <v>39.619999999999997</v>
+        <v>46.204999999999998</v>
       </c>
       <c r="H63" s="48">
-        <v>39.774999999999999</v>
+        <v>46.47</v>
       </c>
       <c r="I63" s="48">
-        <v>40.583750000000002</v>
+        <v>47.778750000000002</v>
       </c>
       <c r="J63" s="48">
-        <v>38.893250000000002</v>
+        <v>46.163249999999998</v>
       </c>
       <c r="K63" s="48">
-        <v>38.455750000000002</v>
+        <v>45.405749999999998</v>
       </c>
       <c r="L63" s="48">
-        <v>35.549500000000002</v>
+        <v>42.499499999999998</v>
       </c>
       <c r="M63" s="48">
-        <v>34.582500000000003</v>
+        <v>41.902500000000003</v>
       </c>
       <c r="N63" s="48">
-        <v>33.2575</v>
+        <v>41.502499999999998</v>
       </c>
       <c r="O63" s="48">
-        <v>24.421250000000001</v>
+        <v>32.401249999999997</v>
       </c>
       <c r="P63" s="48">
-        <v>24.12125</v>
+        <v>32.10125</v>
       </c>
       <c r="Q63" s="48">
-        <v>24.12125</v>
+        <v>32.10125</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.2">
